--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -1848,7 +1848,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1924,6 +1924,30 @@
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>欢迎通过页面下方的微信或电话直接咨询我们。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>小猫的价格范围？</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>5000–30000 元不等，具体取决于脸版品相、骨量结构与毛量毛色，欢迎微信咨询心仪的小猫。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>猫舍有哪些花色？</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>银虎斑、棕虎斑、烟灰系、凯米尔、红虎斑、纯白、纯黑、蓝虎斑等。</t>
         </is>
       </c>
     </row>

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -1918,36 +1918,36 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>还有其他问题？</t>
+          <t>小猫的价格范围？</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>欢迎通过页面下方的微信或电话直接咨询我们。</t>
+          <t>5000–30000 元不等，具体取决于脸版品相、骨量结构与毛量毛色，欢迎微信咨询心仪的小猫。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>小猫的价格范围？</t>
+          <t>猫舍有哪些花色？</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>5000–30000 元不等，具体取决于脸版品相、骨量结构与毛量毛色，欢迎微信咨询心仪的小猫。</t>
+          <t>银虎斑、棕虎斑、烟灰系、凯米尔、红虎斑、纯白、纯黑、蓝虎斑等。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>猫舍有哪些花色？</t>
+          <t>还有其他问题？</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>银虎斑、棕虎斑、烟灰系、凯米尔、红虎斑、纯白、纯黑、蓝虎斑等。</t>
+          <t>欢迎通过页面下方的微信或电话直接咨询我们。</t>
         </is>
       </c>
     </row>

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -615,7 +615,11 @@
           <t>2026-06-05</t>
         </is>
       </c>
-      <c r="F5" s="2" t="n"/>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>重庆</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -719,7 +723,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -727,7 +731,11 @@
           <t>2026-06-05</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>黑龙江</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1591,7 +1599,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>assets/1785912551260-jplefm937nk.jpeg, assets/videos/02.mp4</t>
+          <t>assets/1785912551260-jplefm937nk.jpeg</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -1731,7 +1739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1770,6 +1778,40 @@
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Shakoshako 猫舍官网全新上线，欢迎关注！</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>出售</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>银虎斑弟弟找到新家，前往黑龙江。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>出售</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>烟灰色弟弟找到新家，前往重庆。</t>
         </is>
       </c>
     </row>

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -1599,7 +1599,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>assets/1785912551260-jplefm937nk.jpeg</t>
+          <t>assets/1785912551260-jplefm937nk.jpeg, assets/videos/02.mp4</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -1020,7 +1020,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>棕虎斑补丁色</t>
+          <t>棕虎斑补丁</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -564,7 +564,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>银虎斑补丁色</t>
+          <t>银虎斑补丁</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -652,7 +652,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>银虎斑补丁色</t>
+          <t>银虎斑补丁</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:K43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -504,6 +504,16 @@
           <t>名字</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>定新家日期</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>出发照片</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1152,7 +1162,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1173,6 +1183,16 @@
       <c r="I24" s="2" t="inlineStr">
         <is>
           <t>驺驺</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>assets/diary/zouzou-depart.jpg</t>
         </is>
       </c>
     </row>

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K43"/>
+  <dimension ref="A1:N43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -514,6 +514,21 @@
           <t>出发照片</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>打疫苗日期</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>血清检测日期</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>出发日期</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1193,6 +1208,21 @@
       <c r="K24" t="inlineStr">
         <is>
           <t>assets/diary/zouzou-depart.jpg</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
         </is>
       </c>
     </row>

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -1220,11 +1220,6 @@
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>2026-11-03</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -1905,7 +1905,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>在荷兰的新家适应得很好，活泼又粘人。</t>
+          <t>五个月10天了。</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N43"/>
+  <dimension ref="A1:O43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -529,6 +529,11 @@
           <t>出发日期</t>
         </is>
       </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>体重记录</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1218,6 +1223,11 @@
       <c r="M24" t="inlineStr">
         <is>
           <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>2026-07-30 · 6.2斤</t>
         </is>
       </c>
     </row>

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -1928,11 +1928,7 @@
           <t>五个月10天了。</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>assets/feedback/zouzou-1.jpg</t>
-        </is>
-      </c>
+      <c r="D2" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -1928,7 +1928,11 @@
           <t>五个月10天了。</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n"/>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>assets/feedback/zouzou-1.jpg</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -1227,7 +1227,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2026-07-30 · 6.2斤</t>
+          <t>2026-07-30 · 6.2斤 · 五个月10天了 · assets/feedback/zouzou-1.jpg</t>
         </is>
       </c>
     </row>
@@ -1881,7 +1881,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1909,28 +1909,6 @@
       <c r="D1" s="1" t="inlineStr">
         <is>
           <t>图片路径</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>驺驺</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>五个月10天了。</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>assets/feedback/zouzou-1.jpg</t>
         </is>
       </c>
     </row>

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -654,7 +654,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>棕虎斑玳瑁色</t>
+          <t>棕虎斑玳瑁</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -2084,7 +2084,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>中国、荷兰</t>
+          <t>中国、荷兰、新疆</t>
         </is>
       </c>
     </row>

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -933,13 +933,13 @@
         <v>assets/1785842639100-82k775dhwiv.jpg</v>
       </c>
       <c r="D12" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E12" t="str">
-        <v>2026-06-05</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F12" t="str">
-        <v/>
+        <v>四川自贡</v>
       </c>
       <c r="G12" t="str">
         <v/>

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -454,7 +454,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>浅色烟灰色</v>
+        <v>浅烟灰色妹妹</v>
       </c>
       <c r="B2" t="str">
         <v>妹妹</v>
@@ -466,7 +466,7 @@
         <v>否</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-04-05</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F2" t="str">
         <v/>

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -463,13 +463,13 @@
         <v>assets/1785843720843-63qz159daui.jpg</v>
       </c>
       <c r="D2" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E2" t="str">
         <v>2026-03-21</v>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>四川成都</v>
       </c>
       <c r="G2" t="str">
         <v/>

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -513,7 +513,7 @@
         <v>否</v>
       </c>
       <c r="E3" t="str">
-        <v>2026-03-05</v>
+        <v>2026-02-14</v>
       </c>
       <c r="F3" t="str">
         <v/>

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -604,13 +604,13 @@
         <v>assets/1785843953805-mxl3x1982io.jpg</v>
       </c>
       <c r="D5" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E5" t="str">
-        <v>2026-06-05</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F5" t="str">
-        <v>重庆</v>
+        <v/>
       </c>
       <c r="G5" t="str">
         <v/>

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -654,7 +654,7 @@
         <v>否</v>
       </c>
       <c r="E6" t="str">
-        <v>2026-03-05</v>
+        <v>2026-02-14</v>
       </c>
       <c r="F6" t="str">
         <v/>

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -701,7 +701,7 @@
         <v>否</v>
       </c>
       <c r="E7" t="str">
-        <v>2026-06-05</v>
+        <v>2026-05-24</v>
       </c>
       <c r="F7" t="str">
         <v/>

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -745,13 +745,13 @@
         <v>assets/1785838787730-s5f333sc3u.jpg</v>
       </c>
       <c r="D8" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E8" t="str">
         <v>2026-06-05</v>
       </c>
       <c r="F8" t="str">
-        <v/>
+        <v>湖南恩施</v>
       </c>
       <c r="G8" t="str">
         <v/>

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -798,7 +798,7 @@
         <v>2026-06-05</v>
       </c>
       <c r="F9" t="str">
-        <v>黑龙江</v>
+        <v>湖北恩施</v>
       </c>
       <c r="G9" t="str">
         <v/>

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -845,7 +845,7 @@
         <v>2025-11-05</v>
       </c>
       <c r="F10" t="str">
-        <v/>
+        <v>韩国</v>
       </c>
       <c r="G10" t="str">
         <v/>

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O43"/>
+  <dimension ref="A1:O42"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -889,7 +889,7 @@
         <v>否</v>
       </c>
       <c r="E11" t="str">
-        <v>2026-06-05</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -983,7 +983,7 @@
         <v>否</v>
       </c>
       <c r="E13" t="str">
-        <v>2026-07-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F13" t="str">
         <v/>
@@ -1018,19 +1018,19 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>浅色银虎斑</v>
+        <v>纯黑色</v>
       </c>
       <c r="B14" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C14" t="str">
-        <v>assets/1785842739140-h77kakknqsr.jpg</v>
+        <v>assets/1785842779532-5u1j0igrw1s.jpg</v>
       </c>
       <c r="D14" t="str">
         <v>否</v>
       </c>
       <c r="E14" t="str">
-        <v>2026-06-05</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F14" t="str">
         <v/>
@@ -1065,13 +1065,13 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>纯黑色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B15" t="str">
         <v>妹妹</v>
       </c>
       <c r="C15" t="str">
-        <v>assets/1785842779532-5u1j0igrw1s.jpg</v>
+        <v>assets/1785842817046-6keqv4rw4yf.jpg</v>
       </c>
       <c r="D15" t="str">
         <v>否</v>
@@ -1112,19 +1112,19 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>银虎斑</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B16" t="str">
         <v>妹妹</v>
       </c>
       <c r="C16" t="str">
-        <v>assets/1785842817046-6keqv4rw4yf.jpg</v>
+        <v>assets/1785842950972-a88lbrskpc.jpg</v>
       </c>
       <c r="D16" t="str">
         <v>否</v>
       </c>
       <c r="E16" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F16" t="str">
         <v/>
@@ -1159,13 +1159,13 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>浅色银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B17" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C17" t="str">
-        <v>assets/1785842950972-a88lbrskpc.jpg</v>
+        <v>assets/1785843011477-n3l1wi6ech.jpg</v>
       </c>
       <c r="D17" t="str">
         <v>否</v>
@@ -1206,19 +1206,19 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>棕虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B18" t="str">
         <v>弟弟</v>
       </c>
       <c r="C18" t="str">
-        <v>assets/1785843011477-n3l1wi6ech.jpg</v>
+        <v>assets/1785843237517-ga449iqess5.jpg</v>
       </c>
       <c r="D18" t="str">
         <v>否</v>
       </c>
       <c r="E18" t="str">
-        <v>2026-06-05</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F18" t="str">
         <v/>
@@ -1253,13 +1253,13 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎斑补丁</v>
       </c>
       <c r="B19" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C19" t="str">
-        <v>assets/1785843237517-ga449iqess5.jpg</v>
+        <v>assets/1785842523893-7nwnnhwi4ns.jpg</v>
       </c>
       <c r="D19" t="str">
         <v>否</v>
@@ -1300,19 +1300,19 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>棕虎斑补丁</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B20" t="str">
         <v>妹妹</v>
       </c>
       <c r="C20" t="str">
-        <v>assets/1785842523893-7nwnnhwi4ns.jpg</v>
+        <v>assets/1785843497557-st27fk8drqi.jpg</v>
       </c>
       <c r="D20" t="str">
         <v>否</v>
       </c>
       <c r="E20" t="str">
-        <v>2026-03-05</v>
+        <v>2026-04-05</v>
       </c>
       <c r="F20" t="str">
         <v/>
@@ -1347,19 +1347,19 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>蓝虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B21" t="str">
         <v>妹妹</v>
       </c>
       <c r="C21" t="str">
-        <v>assets/1785843497557-st27fk8drqi.jpg</v>
+        <v>assets/1785843621923-ylhakbtw13i.jpg</v>
       </c>
       <c r="D21" t="str">
         <v>否</v>
       </c>
       <c r="E21" t="str">
-        <v>2026-04-05</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F21" t="str">
         <v/>
@@ -1400,7 +1400,7 @@
         <v>妹妹</v>
       </c>
       <c r="C22" t="str">
-        <v>assets/1785843621923-ylhakbtw13i.jpg</v>
+        <v>assets/1785843663884-sfxvpmiet7.jpg</v>
       </c>
       <c r="D22" t="str">
         <v>否</v>
@@ -1441,96 +1441,96 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B23" t="str">
         <v>妹妹</v>
       </c>
       <c r="C23" t="str">
-        <v>assets/1785843663884-sfxvpmiet7.jpg</v>
+        <v>assets/1785852601940-o236xtv7yx.jpeg</v>
       </c>
       <c r="D23" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E23" t="str">
-        <v>2026-03-05</v>
+        <v>2026-02-20</v>
       </c>
       <c r="F23" t="str">
-        <v/>
+        <v>荷兰</v>
       </c>
       <c r="G23" t="str">
-        <v/>
+        <v>阿泽</v>
       </c>
       <c r="H23" t="str">
-        <v/>
+        <v>小辫子</v>
       </c>
       <c r="I23" t="str">
-        <v/>
+        <v>驺驺</v>
       </c>
       <c r="J23" t="str">
-        <v/>
+        <v>2026-07-02</v>
       </c>
       <c r="K23" t="str">
-        <v/>
+        <v>assets/diary/zouzou-depart.jpg</v>
       </c>
       <c r="L23" t="str">
-        <v/>
+        <v>2026-07-02</v>
       </c>
       <c r="M23" t="str">
-        <v/>
+        <v>2026-08-03</v>
       </c>
       <c r="N23" t="str">
-        <v/>
+        <v>2026-11-04</v>
       </c>
       <c r="O23" t="str">
-        <v/>
+        <v>2026-07-30 · 6.2斤 · 五个月10天了 · assets/feedback/zouzou-1.jpg</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>蓝虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B24" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C24" t="str">
-        <v>assets/1785852601940-o236xtv7yx.jpeg</v>
+        <v>assets/1785853950207-cedor66ou2q.jpeg</v>
       </c>
       <c r="D24" t="str">
         <v>是</v>
       </c>
       <c r="E24" t="str">
-        <v>2026-02-20</v>
+        <v/>
       </c>
       <c r="F24" t="str">
-        <v>荷兰</v>
+        <v/>
       </c>
       <c r="G24" t="str">
-        <v>阿泽</v>
+        <v/>
       </c>
       <c r="H24" t="str">
-        <v>小辫子</v>
+        <v/>
       </c>
       <c r="I24" t="str">
-        <v>驺驺</v>
+        <v/>
       </c>
       <c r="J24" t="str">
-        <v>2026-07-02</v>
+        <v/>
       </c>
       <c r="K24" t="str">
-        <v>assets/diary/zouzou-depart.jpg</v>
+        <v/>
       </c>
       <c r="L24" t="str">
-        <v>2026-07-02</v>
+        <v/>
       </c>
       <c r="M24" t="str">
-        <v>2026-08-03</v>
+        <v/>
       </c>
       <c r="N24" t="str">
-        <v>2026-11-04</v>
+        <v/>
       </c>
       <c r="O24" t="str">
-        <v>2026-07-30 · 6.2斤 · 五个月10天了 · assets/feedback/zouzou-1.jpg</v>
+        <v/>
       </c>
     </row>
     <row r="25">
@@ -1541,7 +1541,7 @@
         <v>弟弟</v>
       </c>
       <c r="C25" t="str">
-        <v>assets/1785853950207-cedor66ou2q.jpeg</v>
+        <v>assets/1785854129383-c8qkvl537x.jpeg</v>
       </c>
       <c r="D25" t="str">
         <v>是</v>
@@ -1582,13 +1582,13 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>红虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B26" t="str">
         <v>弟弟</v>
       </c>
       <c r="C26" t="str">
-        <v>assets/1785854129383-c8qkvl537x.jpeg</v>
+        <v>assets/1785854166720-48r17hry9cd.jpeg</v>
       </c>
       <c r="D26" t="str">
         <v>是</v>
@@ -1597,7 +1597,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v/>
+        <v>山西朔州</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1632,10 +1632,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B27" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C27" t="str">
-        <v>assets/1785854166720-48r17hry9cd.jpeg</v>
+        <v>assets/1785854224521-2cpg6xipfn6.jpeg</v>
       </c>
       <c r="D27" t="str">
         <v>是</v>
@@ -1644,7 +1644,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v/>
+        <v>浙江宁波</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1679,10 +1679,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B28" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C28" t="str">
-        <v>assets/1785854224521-2cpg6xipfn6.jpeg</v>
+        <v>assets/1785854260793-steez4s972l.jpeg</v>
       </c>
       <c r="D28" t="str">
         <v>是</v>
@@ -1691,7 +1691,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v/>
+        <v>陕西西安</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1729,7 +1729,7 @@
         <v>弟弟</v>
       </c>
       <c r="C29" t="str">
-        <v>assets/1785854260793-steez4s972l.jpeg</v>
+        <v>assets/1785854319988-cohio08aod5.jpeg</v>
       </c>
       <c r="D29" t="str">
         <v>是</v>
@@ -1738,7 +1738,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v/>
+        <v>黑龙江漠河</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1770,13 +1770,13 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B30" t="str">
         <v>弟弟</v>
       </c>
       <c r="C30" t="str">
-        <v>assets/1785854319988-cohio08aod5.jpeg</v>
+        <v>assets/1785854520974-96b8b1ekqd9.jpeg</v>
       </c>
       <c r="D30" t="str">
         <v>是</v>
@@ -1785,7 +1785,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v/>
+        <v>日本</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1817,13 +1817,13 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B31" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C31" t="str">
-        <v>assets/1785854520974-96b8b1ekqd9.jpeg</v>
+        <v>assets/1785854664100-haqoiu1h7hj.jpeg</v>
       </c>
       <c r="D31" t="str">
         <v>是</v>
@@ -1832,7 +1832,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v/>
+        <v>浙江杭州</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1870,7 +1870,7 @@
         <v>妹妹</v>
       </c>
       <c r="C32" t="str">
-        <v>assets/1785854664100-haqoiu1h7hj.jpeg</v>
+        <v>assets/1785854690732-orrs40sx9rs.jpeg</v>
       </c>
       <c r="D32" t="str">
         <v>是</v>
@@ -1917,7 +1917,7 @@
         <v>妹妹</v>
       </c>
       <c r="C33" t="str">
-        <v>assets/1785854690732-orrs40sx9rs.jpeg</v>
+        <v>assets/1785854734122-wcpmib4m7.jpeg</v>
       </c>
       <c r="D33" t="str">
         <v>是</v>
@@ -1961,10 +1961,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B34" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C34" t="str">
-        <v>assets/1785854734122-wcpmib4m7.jpeg</v>
+        <v>assets/1785854758707-1kxdkfvs6jc.jpeg</v>
       </c>
       <c r="D34" t="str">
         <v>是</v>
@@ -2005,13 +2005,13 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>银虎斑</v>
+        <v>纯蓝色</v>
       </c>
       <c r="B35" t="str">
         <v>弟弟</v>
       </c>
       <c r="C35" t="str">
-        <v>assets/1785854758707-1kxdkfvs6jc.jpeg</v>
+        <v>assets/1785854784780-3g0u60pdo93.jpeg</v>
       </c>
       <c r="D35" t="str">
         <v>是</v>
@@ -2052,13 +2052,13 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>纯蓝色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B36" t="str">
         <v>弟弟</v>
       </c>
       <c r="C36" t="str">
-        <v>assets/1785854784780-3g0u60pdo93.jpeg</v>
+        <v>assets/1785854813179-8oyxr0h2bbu.jpeg</v>
       </c>
       <c r="D36" t="str">
         <v>是</v>
@@ -2099,13 +2099,13 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B37" t="str">
         <v>弟弟</v>
       </c>
       <c r="C37" t="str">
-        <v>assets/1785854813179-8oyxr0h2bbu.jpeg</v>
+        <v>assets/1785854838933-uq6amircyzd.jpeg</v>
       </c>
       <c r="D37" t="str">
         <v>是</v>
@@ -2146,13 +2146,13 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>棕虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B38" t="str">
         <v>弟弟</v>
       </c>
       <c r="C38" t="str">
-        <v>assets/1785854838933-uq6amircyzd.jpeg</v>
+        <v>assets/1785854869973-za3p6wikqpo.jpeg</v>
       </c>
       <c r="D38" t="str">
         <v>是</v>
@@ -2193,13 +2193,13 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>烟灰色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B39" t="str">
         <v>弟弟</v>
       </c>
       <c r="C39" t="str">
-        <v>assets/1785854869973-za3p6wikqpo.jpeg</v>
+        <v>assets/1785854997023-mawkallt2a.jpeg</v>
       </c>
       <c r="D39" t="str">
         <v>是</v>
@@ -2240,13 +2240,13 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>银虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B40" t="str">
         <v>弟弟</v>
       </c>
       <c r="C40" t="str">
-        <v>assets/1785854997023-mawkallt2a.jpeg</v>
+        <v>assets/1785855043327-wdc5pxwm34k.jpeg</v>
       </c>
       <c r="D40" t="str">
         <v>是</v>
@@ -2287,19 +2287,19 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>凯米尔色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B41" t="str">
         <v>弟弟</v>
       </c>
       <c r="C41" t="str">
-        <v>assets/1785855043327-wdc5pxwm34k.jpeg</v>
+        <v>assets/1785912551260-jplefm937nk.jpeg, assets/videos/02.mp4</v>
       </c>
       <c r="D41" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E41" t="str">
-        <v/>
+        <v>2026-07-05</v>
       </c>
       <c r="F41" t="str">
         <v/>
@@ -2337,10 +2337,10 @@
         <v>棕虎斑</v>
       </c>
       <c r="B42" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C42" t="str">
-        <v>assets/1785912551260-jplefm937nk.jpeg, assets/videos/02.mp4</v>
+        <v>assets/1785912694000-m20f5kvvrr.jpeg</v>
       </c>
       <c r="D42" t="str">
         <v>否</v>
@@ -2379,56 +2379,9 @@
         <v/>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="str">
-        <v>棕虎斑</v>
-      </c>
-      <c r="B43" t="str">
-        <v>妹妹</v>
-      </c>
-      <c r="C43" t="str">
-        <v>assets/1785912694000-m20f5kvvrr.jpeg</v>
-      </c>
-      <c r="D43" t="str">
-        <v>否</v>
-      </c>
-      <c r="E43" t="str">
-        <v>2026-07-05</v>
-      </c>
-      <c r="F43" t="str">
-        <v/>
-      </c>
-      <c r="G43" t="str">
-        <v/>
-      </c>
-      <c r="H43" t="str">
-        <v/>
-      </c>
-      <c r="I43" t="str">
-        <v/>
-      </c>
-      <c r="J43" t="str">
-        <v/>
-      </c>
-      <c r="K43" t="str">
-        <v/>
-      </c>
-      <c r="L43" t="str">
-        <v/>
-      </c>
-      <c r="M43" t="str">
-        <v/>
-      </c>
-      <c r="N43" t="str">
-        <v/>
-      </c>
-      <c r="O43" t="str">
-        <v/>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O43"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O42"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -1074,13 +1074,13 @@
         <v>assets/1785842817046-6keqv4rw4yf.jpg</v>
       </c>
       <c r="D15" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E15" t="str">
         <v>2026-03-05</v>
       </c>
       <c r="F15" t="str">
-        <v/>
+        <v>韩国</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -1127,7 +1127,7 @@
         <v>2026-06-05</v>
       </c>
       <c r="F16" t="str">
-        <v/>
+        <v>河边邢台</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1174,7 +1174,7 @@
         <v>2026-06-05</v>
       </c>
       <c r="F17" t="str">
-        <v/>
+        <v>四川自贡</v>
       </c>
       <c r="G17" t="str">
         <v/>

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -839,7 +839,7 @@
         <v>assets/1785842429109-porc98rel5.jpg</v>
       </c>
       <c r="D10" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E10" t="str">
         <v>2025-11-05</v>
@@ -1121,7 +1121,7 @@
         <v>assets/1785842950972-a88lbrskpc.jpg</v>
       </c>
       <c r="D16" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E16" t="str">
         <v>2026-06-05</v>
@@ -1168,7 +1168,7 @@
         <v>assets/1785843011477-n3l1wi6ech.jpg</v>
       </c>
       <c r="D17" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E17" t="str">
         <v>2026-06-05</v>
@@ -1503,7 +1503,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v/>
+        <v>广东广州</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1550,7 +1550,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v/>
+        <v>广东广州</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1879,7 +1879,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v/>
+        <v>贵州安顺</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1926,7 +1926,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v/>
+        <v>山东青岛</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1973,7 +1973,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v/>
+        <v>黑龙江漠河</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -2020,7 +2020,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v/>
+        <v>河南鹤壁</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -2067,7 +2067,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v/>
+        <v>陕西西安</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -2114,7 +2114,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v/>
+        <v>四川成都</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>assets/1785854869973-za3p6wikqpo.jpeg</v>
       </c>
       <c r="D38" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -2255,7 +2255,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v/>
+        <v>上海浦东</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -2296,13 +2296,13 @@
         <v>assets/1785912551260-jplefm937nk.jpeg, assets/videos/02.mp4</v>
       </c>
       <c r="D41" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E41" t="str">
-        <v>2026-07-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F41" t="str">
-        <v/>
+        <v>浙江温州</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -2346,7 +2346,7 @@
         <v>否</v>
       </c>
       <c r="E42" t="str">
-        <v>2026-07-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F42" t="str">
         <v/>

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -2158,7 +2158,7 @@
         <v>否</v>
       </c>
       <c r="E38" t="str">
-        <v/>
+        <v>2026-05-18</v>
       </c>
       <c r="F38" t="str">
         <v/>

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O42"/>
+  <dimension ref="A1:O44"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -454,22 +454,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>浅烟灰色妹妹</v>
+        <v>阴影色NS11</v>
       </c>
       <c r="B2" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C2" t="str">
-        <v>assets/1785843720843-63qz159daui.jpg</v>
+        <v>assets/1787280590041-vzcwebdok1.jpg</v>
       </c>
       <c r="D2" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-03-21</v>
+        <v/>
       </c>
       <c r="F2" t="str">
-        <v>四川成都</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -501,19 +501,19 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>红虎斑</v>
+        <v/>
       </c>
       <c r="B3" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C3" t="str">
-        <v>assets/1785843763310-elg05ur61ri.jpg</v>
+        <v/>
       </c>
       <c r="D3" t="str">
         <v>否</v>
       </c>
       <c r="E3" t="str">
-        <v>2026-02-14</v>
+        <v/>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -548,22 +548,22 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>银虎斑补丁</v>
+        <v>浅烟灰色妹妹</v>
       </c>
       <c r="B4" t="str">
         <v>妹妹</v>
       </c>
       <c r="C4" t="str">
-        <v>assets/1785843820715-9kz7gy4mbr7.jpg</v>
+        <v>assets/1785843720843-63qz159daui.jpg</v>
       </c>
       <c r="D4" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E4" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F4" t="str">
-        <v/>
+        <v>四川成都</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -595,19 +595,19 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>烟灰色</v>
+        <v>红虎斑</v>
       </c>
       <c r="B5" t="str">
         <v>弟弟</v>
       </c>
       <c r="C5" t="str">
-        <v>assets/1785843953805-mxl3x1982io.jpg</v>
+        <v>assets/1785843763310-elg05ur61ri.jpg</v>
       </c>
       <c r="D5" t="str">
         <v>否</v>
       </c>
       <c r="E5" t="str">
-        <v>2026-05-18</v>
+        <v>2026-02-14</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -642,19 +642,19 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>棕虎斑玳瑁</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B6" t="str">
         <v>妹妹</v>
       </c>
       <c r="C6" t="str">
-        <v>assets/1785844013835-ek4xpcje7kh.jpg</v>
+        <v>assets/1785843820715-9kz7gy4mbr7.jpg</v>
       </c>
       <c r="D6" t="str">
         <v>否</v>
       </c>
       <c r="E6" t="str">
-        <v>2026-02-14</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -689,19 +689,19 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>银虎斑补丁</v>
+        <v>烟灰色</v>
       </c>
       <c r="B7" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C7" t="str">
-        <v>assets/1785844434338-ek5zbdgdcne.jpg</v>
+        <v>assets/1785843953805-mxl3x1982io.jpg</v>
       </c>
       <c r="D7" t="str">
         <v>否</v>
       </c>
       <c r="E7" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F7" t="str">
         <v/>
@@ -736,22 +736,22 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑玳瑁</v>
       </c>
       <c r="B8" t="str">
         <v>妹妹</v>
       </c>
       <c r="C8" t="str">
-        <v>assets/1785838787730-s5f333sc3u.jpg</v>
+        <v>assets/1785844013835-ek4xpcje7kh.jpg</v>
       </c>
       <c r="D8" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E8" t="str">
-        <v>2026-06-05</v>
+        <v>2026-02-14</v>
       </c>
       <c r="F8" t="str">
-        <v>湖南恩施</v>
+        <v/>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -783,22 +783,22 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>银虎斑</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B9" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C9" t="str">
-        <v>assets/1785842296661-6qw3zs3as8h.jpg</v>
+        <v>assets/1785844434338-ek5zbdgdcne.jpg</v>
       </c>
       <c r="D9" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E9" t="str">
-        <v>2026-06-05</v>
+        <v>2026-05-24</v>
       </c>
       <c r="F9" t="str">
-        <v>湖北恩施</v>
+        <v/>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -833,19 +833,19 @@
         <v>银虎斑</v>
       </c>
       <c r="B10" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C10" t="str">
-        <v>assets/1785842429109-porc98rel5.jpg</v>
+        <v>assets/1785838787730-s5f333sc3u.jpg</v>
       </c>
       <c r="D10" t="str">
         <v>是</v>
       </c>
       <c r="E10" t="str">
-        <v>2025-11-05</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F10" t="str">
-        <v>韩国</v>
+        <v>湖南恩施</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -880,19 +880,19 @@
         <v>银虎斑</v>
       </c>
       <c r="B11" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C11" t="str">
-        <v>assets/1785842594141-fcglbzjp509.jpg</v>
+        <v>assets/1785842296661-6qw3zs3as8h.jpg</v>
       </c>
       <c r="D11" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E11" t="str">
-        <v>2026-05-18</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F11" t="str">
-        <v/>
+        <v>湖北恩施</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -924,22 +924,22 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B12" t="str">
         <v>弟弟</v>
       </c>
       <c r="C12" t="str">
-        <v>assets/1785842639100-82k775dhwiv.jpg</v>
+        <v>assets/1785842429109-porc98rel5.jpg</v>
       </c>
       <c r="D12" t="str">
         <v>是</v>
       </c>
       <c r="E12" t="str">
-        <v>2026-05-28</v>
+        <v>2025-11-05</v>
       </c>
       <c r="F12" t="str">
-        <v>四川自贡</v>
+        <v>韩国</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -971,19 +971,19 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B13" t="str">
         <v>妹妹</v>
       </c>
       <c r="C13" t="str">
-        <v>assets/1785842684502-mnhr0r96eee.jpg</v>
+        <v>assets/1785842594141-fcglbzjp509.jpg</v>
       </c>
       <c r="D13" t="str">
         <v>否</v>
       </c>
       <c r="E13" t="str">
-        <v>2026-06-06</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F13" t="str">
         <v/>
@@ -1018,22 +1018,22 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>纯黑色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B14" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C14" t="str">
-        <v>assets/1785842779532-5u1j0igrw1s.jpg</v>
+        <v>assets/1785842639100-82k775dhwiv.jpg</v>
       </c>
       <c r="D14" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E14" t="str">
-        <v>2026-03-05</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F14" t="str">
-        <v/>
+        <v>四川自贡</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -1065,22 +1065,22 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B15" t="str">
         <v>妹妹</v>
       </c>
       <c r="C15" t="str">
-        <v>assets/1785842817046-6keqv4rw4yf.jpg</v>
+        <v>assets/1785842684502-mnhr0r96eee.jpg</v>
       </c>
       <c r="D15" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E15" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F15" t="str">
-        <v>韩国</v>
+        <v/>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -1112,22 +1112,22 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>浅色银虎斑</v>
+        <v>纯黑色</v>
       </c>
       <c r="B16" t="str">
         <v>妹妹</v>
       </c>
       <c r="C16" t="str">
-        <v>assets/1785842950972-a88lbrskpc.jpg</v>
+        <v>assets/1785842779532-5u1j0igrw1s.jpg</v>
       </c>
       <c r="D16" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E16" t="str">
-        <v>2026-06-05</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F16" t="str">
-        <v>河边邢台</v>
+        <v/>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1159,22 +1159,22 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B17" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C17" t="str">
-        <v>assets/1785843011477-n3l1wi6ech.jpg</v>
+        <v>assets/1785842817046-6keqv4rw4yf.jpg</v>
       </c>
       <c r="D17" t="str">
         <v>是</v>
       </c>
       <c r="E17" t="str">
-        <v>2026-06-05</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F17" t="str">
-        <v>四川自贡</v>
+        <v>韩国</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1206,22 +1206,22 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>蓝虎斑</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B18" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C18" t="str">
-        <v>assets/1785843237517-ga449iqess5.jpg</v>
+        <v>assets/1785842950972-a88lbrskpc.jpg</v>
       </c>
       <c r="D18" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E18" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F18" t="str">
-        <v/>
+        <v>河边邢台</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1253,22 +1253,22 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>棕虎斑补丁</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B19" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C19" t="str">
-        <v>assets/1785842523893-7nwnnhwi4ns.jpg</v>
+        <v>assets/1785843011477-n3l1wi6ech.jpg</v>
       </c>
       <c r="D19" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E19" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F19" t="str">
-        <v/>
+        <v>四川自贡</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1303,16 +1303,16 @@
         <v>蓝虎斑</v>
       </c>
       <c r="B20" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C20" t="str">
-        <v>assets/1785843497557-st27fk8drqi.jpg</v>
+        <v>assets/1785843237517-ga449iqess5.jpg</v>
       </c>
       <c r="D20" t="str">
         <v>否</v>
       </c>
       <c r="E20" t="str">
-        <v>2026-04-05</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F20" t="str">
         <v/>
@@ -1347,13 +1347,13 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑补丁</v>
       </c>
       <c r="B21" t="str">
         <v>妹妹</v>
       </c>
       <c r="C21" t="str">
-        <v>assets/1785843621923-ylhakbtw13i.jpg</v>
+        <v>assets/1785842523893-7nwnnhwi4ns.jpg</v>
       </c>
       <c r="D21" t="str">
         <v>否</v>
@@ -1394,19 +1394,19 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B22" t="str">
         <v>妹妹</v>
       </c>
       <c r="C22" t="str">
-        <v>assets/1785843663884-sfxvpmiet7.jpg</v>
+        <v>assets/1785843497557-st27fk8drqi.jpg</v>
       </c>
       <c r="D22" t="str">
         <v>否</v>
       </c>
       <c r="E22" t="str">
-        <v>2026-03-05</v>
+        <v>2026-04-05</v>
       </c>
       <c r="F22" t="str">
         <v/>
@@ -1441,69 +1441,69 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>蓝虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B23" t="str">
         <v>妹妹</v>
       </c>
       <c r="C23" t="str">
-        <v>assets/1785852601940-o236xtv7yx.jpeg</v>
+        <v>assets/1785843621923-ylhakbtw13i.jpg</v>
       </c>
       <c r="D23" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E23" t="str">
-        <v>2026-02-20</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F23" t="str">
-        <v>荷兰</v>
+        <v/>
       </c>
       <c r="G23" t="str">
-        <v>阿泽</v>
+        <v/>
       </c>
       <c r="H23" t="str">
-        <v>小辫子</v>
+        <v/>
       </c>
       <c r="I23" t="str">
-        <v>驺驺</v>
+        <v/>
       </c>
       <c r="J23" t="str">
-        <v>2026-07-02</v>
+        <v/>
       </c>
       <c r="K23" t="str">
-        <v>assets/diary/zouzou-depart.jpg</v>
+        <v/>
       </c>
       <c r="L23" t="str">
-        <v>2026-07-02</v>
+        <v/>
       </c>
       <c r="M23" t="str">
-        <v>2026-08-03</v>
+        <v/>
       </c>
       <c r="N23" t="str">
-        <v>2026-11-04</v>
+        <v/>
       </c>
       <c r="O23" t="str">
-        <v>2026-07-30 · 6.2斤 · 五个月10天了 · assets/feedback/zouzou-1.jpg</v>
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>红虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B24" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C24" t="str">
-        <v>assets/1785853950207-cedor66ou2q.jpeg</v>
+        <v>assets/1785843663884-sfxvpmiet7.jpg</v>
       </c>
       <c r="D24" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E24" t="str">
-        <v/>
+        <v>2026-03-05</v>
       </c>
       <c r="F24" t="str">
-        <v>广东广州</v>
+        <v/>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1535,60 +1535,60 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>红虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B25" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C25" t="str">
-        <v>assets/1785854129383-c8qkvl537x.jpeg</v>
+        <v>assets/1785852601940-o236xtv7yx.jpeg</v>
       </c>
       <c r="D25" t="str">
         <v>是</v>
       </c>
       <c r="E25" t="str">
-        <v/>
+        <v>2026-02-20</v>
       </c>
       <c r="F25" t="str">
-        <v>广东广州</v>
+        <v>荷兰</v>
       </c>
       <c r="G25" t="str">
-        <v/>
+        <v>阿泽</v>
       </c>
       <c r="H25" t="str">
-        <v/>
+        <v>小辫子</v>
       </c>
       <c r="I25" t="str">
-        <v/>
+        <v>驺驺</v>
       </c>
       <c r="J25" t="str">
-        <v/>
+        <v>2026-07-02</v>
       </c>
       <c r="K25" t="str">
-        <v/>
+        <v>assets/diary/zouzou-depart.jpg</v>
       </c>
       <c r="L25" t="str">
-        <v/>
+        <v>2026-07-02</v>
       </c>
       <c r="M25" t="str">
-        <v/>
+        <v>2026-08-03</v>
       </c>
       <c r="N25" t="str">
-        <v/>
+        <v>2026-11-04</v>
       </c>
       <c r="O25" t="str">
-        <v/>
+        <v>2026-07-30 · 6.2斤 · 五个月10天了 · assets/feedback/zouzou-1.jpg</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B26" t="str">
         <v>弟弟</v>
       </c>
       <c r="C26" t="str">
-        <v>assets/1785854166720-48r17hry9cd.jpeg</v>
+        <v>assets/1785853950207-cedor66ou2q.jpeg</v>
       </c>
       <c r="D26" t="str">
         <v>是</v>
@@ -1597,7 +1597,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>山西朔州</v>
+        <v>广东广州</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1629,13 +1629,13 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B27" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C27" t="str">
-        <v>assets/1785854224521-2cpg6xipfn6.jpeg</v>
+        <v>assets/1785854129383-c8qkvl537x.jpeg</v>
       </c>
       <c r="D27" t="str">
         <v>是</v>
@@ -1644,7 +1644,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>浙江宁波</v>
+        <v>广东广州</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1682,7 +1682,7 @@
         <v>弟弟</v>
       </c>
       <c r="C28" t="str">
-        <v>assets/1785854260793-steez4s972l.jpeg</v>
+        <v>assets/1785854166720-48r17hry9cd.jpeg</v>
       </c>
       <c r="D28" t="str">
         <v>是</v>
@@ -1691,7 +1691,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>陕西西安</v>
+        <v>山西朔州</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1726,10 +1726,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B29" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C29" t="str">
-        <v>assets/1785854319988-cohio08aod5.jpeg</v>
+        <v>assets/1785854224521-2cpg6xipfn6.jpeg</v>
       </c>
       <c r="D29" t="str">
         <v>是</v>
@@ -1738,7 +1738,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>黑龙江漠河</v>
+        <v>浙江宁波</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1770,13 +1770,13 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B30" t="str">
         <v>弟弟</v>
       </c>
       <c r="C30" t="str">
-        <v>assets/1785854520974-96b8b1ekqd9.jpeg</v>
+        <v>assets/1785854260793-steez4s972l.jpeg</v>
       </c>
       <c r="D30" t="str">
         <v>是</v>
@@ -1785,7 +1785,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>日本</v>
+        <v>陕西西安</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1820,10 +1820,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B31" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C31" t="str">
-        <v>assets/1785854664100-haqoiu1h7hj.jpeg</v>
+        <v>assets/1785854319988-cohio08aod5.jpeg</v>
       </c>
       <c r="D31" t="str">
         <v>是</v>
@@ -1832,7 +1832,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>浙江杭州</v>
+        <v>黑龙江漠河</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1864,13 +1864,13 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B32" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C32" t="str">
-        <v>assets/1785854690732-orrs40sx9rs.jpeg</v>
+        <v>assets/1785854520974-96b8b1ekqd9.jpeg</v>
       </c>
       <c r="D32" t="str">
         <v>是</v>
@@ -1879,7 +1879,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>贵州安顺</v>
+        <v>日本</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1917,7 +1917,7 @@
         <v>妹妹</v>
       </c>
       <c r="C33" t="str">
-        <v>assets/1785854734122-wcpmib4m7.jpeg</v>
+        <v>assets/1785854664100-haqoiu1h7hj.jpeg</v>
       </c>
       <c r="D33" t="str">
         <v>是</v>
@@ -1926,7 +1926,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>山东青岛</v>
+        <v>浙江杭州</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1961,10 +1961,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B34" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C34" t="str">
-        <v>assets/1785854758707-1kxdkfvs6jc.jpeg</v>
+        <v>assets/1785854690732-orrs40sx9rs.jpeg</v>
       </c>
       <c r="D34" t="str">
         <v>是</v>
@@ -1973,7 +1973,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>黑龙江漠河</v>
+        <v>贵州安顺</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -2005,13 +2005,13 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>纯蓝色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B35" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C35" t="str">
-        <v>assets/1785854784780-3g0u60pdo93.jpeg</v>
+        <v>assets/1785854734122-wcpmib4m7.jpeg</v>
       </c>
       <c r="D35" t="str">
         <v>是</v>
@@ -2020,7 +2020,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>河南鹤壁</v>
+        <v>山东青岛</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -2058,7 +2058,7 @@
         <v>弟弟</v>
       </c>
       <c r="C36" t="str">
-        <v>assets/1785854813179-8oyxr0h2bbu.jpeg</v>
+        <v>assets/1785854758707-1kxdkfvs6jc.jpeg</v>
       </c>
       <c r="D36" t="str">
         <v>是</v>
@@ -2067,7 +2067,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>陕西西安</v>
+        <v>黑龙江漠河</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -2099,13 +2099,13 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>棕虎斑</v>
+        <v>纯蓝色</v>
       </c>
       <c r="B37" t="str">
         <v>弟弟</v>
       </c>
       <c r="C37" t="str">
-        <v>assets/1785854838933-uq6amircyzd.jpeg</v>
+        <v>assets/1785854784780-3g0u60pdo93.jpeg</v>
       </c>
       <c r="D37" t="str">
         <v>是</v>
@@ -2114,7 +2114,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>四川成都</v>
+        <v>河南鹤壁</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -2146,22 +2146,22 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>烟灰色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B38" t="str">
         <v>弟弟</v>
       </c>
       <c r="C38" t="str">
-        <v>assets/1785854869973-za3p6wikqpo.jpeg</v>
+        <v>assets/1785854813179-8oyxr0h2bbu.jpeg</v>
       </c>
       <c r="D38" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E38" t="str">
-        <v>2026-05-18</v>
+        <v/>
       </c>
       <c r="F38" t="str">
-        <v/>
+        <v>陕西西安</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -2193,13 +2193,13 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B39" t="str">
         <v>弟弟</v>
       </c>
       <c r="C39" t="str">
-        <v>assets/1785854997023-mawkallt2a.jpeg</v>
+        <v>assets/1785854838933-uq6amircyzd.jpeg</v>
       </c>
       <c r="D39" t="str">
         <v>是</v>
@@ -2208,7 +2208,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v/>
+        <v>四川成都</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -2240,22 +2240,22 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>凯米尔色</v>
+        <v>烟灰色</v>
       </c>
       <c r="B40" t="str">
         <v>弟弟</v>
       </c>
       <c r="C40" t="str">
-        <v>assets/1785855043327-wdc5pxwm34k.jpeg</v>
+        <v>assets/1785854869973-za3p6wikqpo.jpeg</v>
       </c>
       <c r="D40" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E40" t="str">
-        <v/>
+        <v>2026-05-18</v>
       </c>
       <c r="F40" t="str">
-        <v>上海浦东</v>
+        <v/>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -2287,22 +2287,22 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B41" t="str">
         <v>弟弟</v>
       </c>
       <c r="C41" t="str">
-        <v>assets/1785912551260-jplefm937nk.jpeg, assets/videos/02.mp4</v>
+        <v>assets/1785854997023-mawkallt2a.jpeg</v>
       </c>
       <c r="D41" t="str">
         <v>是</v>
       </c>
       <c r="E41" t="str">
-        <v>2026-06-06</v>
+        <v/>
       </c>
       <c r="F41" t="str">
-        <v>浙江温州</v>
+        <v/>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -2334,54 +2334,148 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
+        <v>凯米尔色</v>
+      </c>
+      <c r="B42" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C42" t="str">
+        <v>assets/1785855043327-wdc5pxwm34k.jpeg</v>
+      </c>
+      <c r="D42" t="str">
+        <v>是</v>
+      </c>
+      <c r="E42" t="str">
+        <v/>
+      </c>
+      <c r="F42" t="str">
+        <v>上海浦东</v>
+      </c>
+      <c r="G42" t="str">
+        <v/>
+      </c>
+      <c r="H42" t="str">
+        <v/>
+      </c>
+      <c r="I42" t="str">
+        <v/>
+      </c>
+      <c r="J42" t="str">
+        <v/>
+      </c>
+      <c r="K42" t="str">
+        <v/>
+      </c>
+      <c r="L42" t="str">
+        <v/>
+      </c>
+      <c r="M42" t="str">
+        <v/>
+      </c>
+      <c r="N42" t="str">
+        <v/>
+      </c>
+      <c r="O42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
         <v>棕虎斑</v>
       </c>
-      <c r="B42" t="str">
+      <c r="B43" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C43" t="str">
+        <v>assets/1785912551260-jplefm937nk.jpeg, assets/videos/02.mp4</v>
+      </c>
+      <c r="D43" t="str">
+        <v>是</v>
+      </c>
+      <c r="E43" t="str">
+        <v>2026-06-06</v>
+      </c>
+      <c r="F43" t="str">
+        <v>浙江温州</v>
+      </c>
+      <c r="G43" t="str">
+        <v/>
+      </c>
+      <c r="H43" t="str">
+        <v/>
+      </c>
+      <c r="I43" t="str">
+        <v/>
+      </c>
+      <c r="J43" t="str">
+        <v/>
+      </c>
+      <c r="K43" t="str">
+        <v/>
+      </c>
+      <c r="L43" t="str">
+        <v/>
+      </c>
+      <c r="M43" t="str">
+        <v/>
+      </c>
+      <c r="N43" t="str">
+        <v/>
+      </c>
+      <c r="O43" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>棕虎斑</v>
+      </c>
+      <c r="B44" t="str">
         <v>妹妹</v>
       </c>
-      <c r="C42" t="str">
+      <c r="C44" t="str">
         <v>assets/1785912694000-m20f5kvvrr.jpeg</v>
       </c>
-      <c r="D42" t="str">
+      <c r="D44" t="str">
         <v>否</v>
       </c>
-      <c r="E42" t="str">
+      <c r="E44" t="str">
         <v>2026-06-06</v>
       </c>
-      <c r="F42" t="str">
-        <v/>
-      </c>
-      <c r="G42" t="str">
-        <v/>
-      </c>
-      <c r="H42" t="str">
-        <v/>
-      </c>
-      <c r="I42" t="str">
-        <v/>
-      </c>
-      <c r="J42" t="str">
-        <v/>
-      </c>
-      <c r="K42" t="str">
-        <v/>
-      </c>
-      <c r="L42" t="str">
-        <v/>
-      </c>
-      <c r="M42" t="str">
-        <v/>
-      </c>
-      <c r="N42" t="str">
-        <v/>
-      </c>
-      <c r="O42" t="str">
+      <c r="F44" t="str">
+        <v/>
+      </c>
+      <c r="G44" t="str">
+        <v/>
+      </c>
+      <c r="H44" t="str">
+        <v/>
+      </c>
+      <c r="I44" t="str">
+        <v/>
+      </c>
+      <c r="J44" t="str">
+        <v/>
+      </c>
+      <c r="K44" t="str">
+        <v/>
+      </c>
+      <c r="L44" t="str">
+        <v/>
+      </c>
+      <c r="M44" t="str">
+        <v/>
+      </c>
+      <c r="N44" t="str">
+        <v/>
+      </c>
+      <c r="O44" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O42"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O44"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -466,7 +466,7 @@
         <v>否</v>
       </c>
       <c r="E2" t="str">
-        <v/>
+        <v>2026-05-28</v>
       </c>
       <c r="F2" t="str">
         <v/>

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -501,19 +501,19 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v/>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B3" t="str">
         <v>妹妹</v>
       </c>
       <c r="C3" t="str">
-        <v/>
+        <v>assets/1787281786169-9ia0h837ct.jpg</v>
       </c>
       <c r="D3" t="str">
         <v>否</v>
       </c>
       <c r="E3" t="str">
-        <v/>
+        <v>2026-06-15</v>
       </c>
       <c r="F3" t="str">
         <v/>

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -2666,12 +2666,13 @@
         <v>5000–30000 元不等，具体取决于脸版品相、骨量结构与毛量毛色，欢迎微信咨询心仪的小猫。</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" xml:space="preserve">
       <c r="A7" t="str">
         <v>猫舍有哪些花色？</v>
       </c>
-      <c r="B7" t="str">
-        <v>银虎斑、棕虎斑、烟灰系、凯米尔、红虎斑、纯白、纯黑、蓝虎斑等。</v>
+      <c r="B7" t="str" xml:space="preserve">
+        <v xml:space="preserve">银虎斑、棕虎斑、蓝虎斑、红虎斑、补丁虎斑、烟灰色、凯米尔、阴影色、纯白、纯黑、纯蓝等！
+</v>
       </c>
     </row>
     <row r="8">

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O44"/>
+  <dimension ref="A1:O45"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -454,19 +454,19 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>阴影色NS11</v>
+        <v>银虎斑</v>
       </c>
       <c r="B2" t="str">
         <v>弟弟</v>
       </c>
       <c r="C2" t="str">
-        <v>assets/1787280590041-vzcwebdok1.jpg</v>
+        <v>assets/1787282064159-6b4z8c5msd.jpg</v>
       </c>
       <c r="D2" t="str">
         <v>否</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-05-28</v>
+        <v>2026-06-10</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -501,19 +501,19 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>浅色银虎斑</v>
+        <v>阴影色NS11</v>
       </c>
       <c r="B3" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C3" t="str">
-        <v>assets/1787281786169-9ia0h837ct.jpg</v>
+        <v>assets/1787280590041-vzcwebdok1.jpg</v>
       </c>
       <c r="D3" t="str">
         <v>否</v>
       </c>
       <c r="E3" t="str">
-        <v>2026-06-15</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -548,22 +548,22 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>浅烟灰色妹妹</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B4" t="str">
         <v>妹妹</v>
       </c>
       <c r="C4" t="str">
-        <v>assets/1785843720843-63qz159daui.jpg</v>
+        <v>assets/1787281786169-9ia0h837ct.jpg</v>
       </c>
       <c r="D4" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E4" t="str">
-        <v>2026-03-21</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F4" t="str">
-        <v>四川成都</v>
+        <v/>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -595,22 +595,22 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>红虎斑</v>
+        <v>浅烟灰色妹妹</v>
       </c>
       <c r="B5" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C5" t="str">
-        <v>assets/1785843763310-elg05ur61ri.jpg</v>
+        <v>assets/1785843720843-63qz159daui.jpg</v>
       </c>
       <c r="D5" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E5" t="str">
-        <v>2026-02-14</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F5" t="str">
-        <v/>
+        <v>四川成都</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -642,19 +642,19 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>银虎斑补丁</v>
+        <v>红虎斑</v>
       </c>
       <c r="B6" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C6" t="str">
-        <v>assets/1785843820715-9kz7gy4mbr7.jpg</v>
+        <v>assets/1785843763310-elg05ur61ri.jpg</v>
       </c>
       <c r="D6" t="str">
         <v>否</v>
       </c>
       <c r="E6" t="str">
-        <v>2026-03-05</v>
+        <v>2026-02-14</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -689,19 +689,19 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>烟灰色</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B7" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C7" t="str">
-        <v>assets/1785843953805-mxl3x1982io.jpg</v>
+        <v>assets/1785843820715-9kz7gy4mbr7.jpg</v>
       </c>
       <c r="D7" t="str">
         <v>否</v>
       </c>
       <c r="E7" t="str">
-        <v>2026-05-18</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F7" t="str">
         <v/>
@@ -736,19 +736,19 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>棕虎斑玳瑁</v>
+        <v>烟灰色</v>
       </c>
       <c r="B8" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C8" t="str">
-        <v>assets/1785844013835-ek4xpcje7kh.jpg</v>
+        <v>assets/1785843953805-mxl3x1982io.jpg</v>
       </c>
       <c r="D8" t="str">
         <v>否</v>
       </c>
       <c r="E8" t="str">
-        <v>2026-02-14</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -783,19 +783,19 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>银虎斑补丁</v>
+        <v>棕虎斑玳瑁</v>
       </c>
       <c r="B9" t="str">
         <v>妹妹</v>
       </c>
       <c r="C9" t="str">
-        <v>assets/1785844434338-ek5zbdgdcne.jpg</v>
+        <v>assets/1785844013835-ek4xpcje7kh.jpg</v>
       </c>
       <c r="D9" t="str">
         <v>否</v>
       </c>
       <c r="E9" t="str">
-        <v>2026-05-24</v>
+        <v>2026-02-14</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -830,22 +830,22 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>银虎斑</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B10" t="str">
         <v>妹妹</v>
       </c>
       <c r="C10" t="str">
-        <v>assets/1785838787730-s5f333sc3u.jpg</v>
+        <v>assets/1785844434338-ek5zbdgdcne.jpg</v>
       </c>
       <c r="D10" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E10" t="str">
-        <v>2026-06-05</v>
+        <v>2026-05-24</v>
       </c>
       <c r="F10" t="str">
-        <v>湖南恩施</v>
+        <v/>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -880,10 +880,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B11" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C11" t="str">
-        <v>assets/1785842296661-6qw3zs3as8h.jpg</v>
+        <v>assets/1785838787730-s5f333sc3u.jpg</v>
       </c>
       <c r="D11" t="str">
         <v>是</v>
@@ -892,7 +892,7 @@
         <v>2026-06-05</v>
       </c>
       <c r="F11" t="str">
-        <v>湖北恩施</v>
+        <v>湖南恩施</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -930,16 +930,16 @@
         <v>弟弟</v>
       </c>
       <c r="C12" t="str">
-        <v>assets/1785842429109-porc98rel5.jpg</v>
+        <v>assets/1785842296661-6qw3zs3as8h.jpg</v>
       </c>
       <c r="D12" t="str">
         <v>是</v>
       </c>
       <c r="E12" t="str">
-        <v>2025-11-05</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F12" t="str">
-        <v>韩国</v>
+        <v>湖北恩施</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -974,19 +974,19 @@
         <v>银虎斑</v>
       </c>
       <c r="B13" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C13" t="str">
-        <v>assets/1785842594141-fcglbzjp509.jpg</v>
+        <v>assets/1785842429109-porc98rel5.jpg</v>
       </c>
       <c r="D13" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E13" t="str">
-        <v>2026-05-18</v>
+        <v>2025-11-05</v>
       </c>
       <c r="F13" t="str">
-        <v/>
+        <v>韩国</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -1018,22 +1018,22 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B14" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C14" t="str">
-        <v>assets/1785842639100-82k775dhwiv.jpg</v>
+        <v>assets/1785842594141-fcglbzjp509.jpg</v>
       </c>
       <c r="D14" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E14" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F14" t="str">
-        <v>四川自贡</v>
+        <v/>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -1068,19 +1068,19 @@
         <v>棕虎斑</v>
       </c>
       <c r="B15" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C15" t="str">
-        <v>assets/1785842684502-mnhr0r96eee.jpg</v>
+        <v>assets/1785842639100-82k775dhwiv.jpg</v>
       </c>
       <c r="D15" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E15" t="str">
-        <v>2026-06-06</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F15" t="str">
-        <v/>
+        <v>四川自贡</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -1112,19 +1112,19 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>纯黑色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B16" t="str">
         <v>妹妹</v>
       </c>
       <c r="C16" t="str">
-        <v>assets/1785842779532-5u1j0igrw1s.jpg</v>
+        <v>assets/1785842684502-mnhr0r96eee.jpg</v>
       </c>
       <c r="D16" t="str">
         <v>否</v>
       </c>
       <c r="E16" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F16" t="str">
         <v/>
@@ -1159,22 +1159,22 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>银虎斑</v>
+        <v>纯黑色</v>
       </c>
       <c r="B17" t="str">
         <v>妹妹</v>
       </c>
       <c r="C17" t="str">
-        <v>assets/1785842817046-6keqv4rw4yf.jpg</v>
+        <v>assets/1785842779532-5u1j0igrw1s.jpg</v>
       </c>
       <c r="D17" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E17" t="str">
         <v>2026-03-05</v>
       </c>
       <c r="F17" t="str">
-        <v>韩国</v>
+        <v/>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1206,22 +1206,22 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>浅色银虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B18" t="str">
         <v>妹妹</v>
       </c>
       <c r="C18" t="str">
-        <v>assets/1785842950972-a88lbrskpc.jpg</v>
+        <v>assets/1785842817046-6keqv4rw4yf.jpg</v>
       </c>
       <c r="D18" t="str">
         <v>是</v>
       </c>
       <c r="E18" t="str">
-        <v>2026-06-05</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F18" t="str">
-        <v>河边邢台</v>
+        <v>韩国</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1253,13 +1253,13 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>棕虎斑</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B19" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C19" t="str">
-        <v>assets/1785843011477-n3l1wi6ech.jpg</v>
+        <v>assets/1785842950972-a88lbrskpc.jpg</v>
       </c>
       <c r="D19" t="str">
         <v>是</v>
@@ -1268,7 +1268,7 @@
         <v>2026-06-05</v>
       </c>
       <c r="F19" t="str">
-        <v>四川自贡</v>
+        <v>河边邢台</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1300,22 +1300,22 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B20" t="str">
         <v>弟弟</v>
       </c>
       <c r="C20" t="str">
-        <v>assets/1785843237517-ga449iqess5.jpg</v>
+        <v>assets/1785843011477-n3l1wi6ech.jpg</v>
       </c>
       <c r="D20" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E20" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F20" t="str">
-        <v/>
+        <v>四川自贡</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1347,13 +1347,13 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>棕虎斑补丁</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B21" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C21" t="str">
-        <v>assets/1785842523893-7nwnnhwi4ns.jpg</v>
+        <v>assets/1785843237517-ga449iqess5.jpg</v>
       </c>
       <c r="D21" t="str">
         <v>否</v>
@@ -1394,19 +1394,19 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎斑补丁</v>
       </c>
       <c r="B22" t="str">
         <v>妹妹</v>
       </c>
       <c r="C22" t="str">
-        <v>assets/1785843497557-st27fk8drqi.jpg</v>
+        <v>assets/1785842523893-7nwnnhwi4ns.jpg</v>
       </c>
       <c r="D22" t="str">
         <v>否</v>
       </c>
       <c r="E22" t="str">
-        <v>2026-04-05</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F22" t="str">
         <v/>
@@ -1441,19 +1441,19 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B23" t="str">
         <v>妹妹</v>
       </c>
       <c r="C23" t="str">
-        <v>assets/1785843621923-ylhakbtw13i.jpg</v>
+        <v>assets/1785843497557-st27fk8drqi.jpg</v>
       </c>
       <c r="D23" t="str">
         <v>否</v>
       </c>
       <c r="E23" t="str">
-        <v>2026-03-05</v>
+        <v>2026-04-05</v>
       </c>
       <c r="F23" t="str">
         <v/>
@@ -1494,7 +1494,7 @@
         <v>妹妹</v>
       </c>
       <c r="C24" t="str">
-        <v>assets/1785843663884-sfxvpmiet7.jpg</v>
+        <v>assets/1785843621923-ylhakbtw13i.jpg</v>
       </c>
       <c r="D24" t="str">
         <v>否</v>
@@ -1535,96 +1535,96 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>蓝虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B25" t="str">
         <v>妹妹</v>
       </c>
       <c r="C25" t="str">
-        <v>assets/1785852601940-o236xtv7yx.jpeg</v>
+        <v>assets/1785843663884-sfxvpmiet7.jpg</v>
       </c>
       <c r="D25" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E25" t="str">
-        <v>2026-02-20</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F25" t="str">
-        <v>荷兰</v>
+        <v/>
       </c>
       <c r="G25" t="str">
-        <v>阿泽</v>
+        <v/>
       </c>
       <c r="H25" t="str">
-        <v>小辫子</v>
+        <v/>
       </c>
       <c r="I25" t="str">
-        <v>驺驺</v>
+        <v/>
       </c>
       <c r="J25" t="str">
-        <v>2026-07-02</v>
+        <v/>
       </c>
       <c r="K25" t="str">
-        <v>assets/diary/zouzou-depart.jpg</v>
+        <v/>
       </c>
       <c r="L25" t="str">
-        <v>2026-07-02</v>
+        <v/>
       </c>
       <c r="M25" t="str">
-        <v>2026-08-03</v>
+        <v/>
       </c>
       <c r="N25" t="str">
-        <v>2026-11-04</v>
+        <v/>
       </c>
       <c r="O25" t="str">
-        <v>2026-07-30 · 6.2斤 · 五个月10天了 · assets/feedback/zouzou-1.jpg</v>
+        <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>红虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B26" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C26" t="str">
-        <v>assets/1785853950207-cedor66ou2q.jpeg</v>
+        <v>assets/1785852601940-o236xtv7yx.jpeg</v>
       </c>
       <c r="D26" t="str">
         <v>是</v>
       </c>
       <c r="E26" t="str">
-        <v/>
+        <v>2026-02-20</v>
       </c>
       <c r="F26" t="str">
-        <v>广东广州</v>
+        <v>荷兰</v>
       </c>
       <c r="G26" t="str">
-        <v/>
+        <v>阿泽</v>
       </c>
       <c r="H26" t="str">
-        <v/>
+        <v>小辫子</v>
       </c>
       <c r="I26" t="str">
-        <v/>
+        <v>驺驺</v>
       </c>
       <c r="J26" t="str">
-        <v/>
+        <v>2026-07-02</v>
       </c>
       <c r="K26" t="str">
-        <v/>
+        <v>assets/diary/zouzou-depart.jpg</v>
       </c>
       <c r="L26" t="str">
-        <v/>
+        <v>2026-07-02</v>
       </c>
       <c r="M26" t="str">
-        <v/>
+        <v>2026-08-03</v>
       </c>
       <c r="N26" t="str">
-        <v/>
+        <v>2026-11-04</v>
       </c>
       <c r="O26" t="str">
-        <v/>
+        <v>2026-07-30 · 6.2斤 · 五个月10天了 · assets/feedback/zouzou-1.jpg</v>
       </c>
     </row>
     <row r="27">
@@ -1635,7 +1635,7 @@
         <v>弟弟</v>
       </c>
       <c r="C27" t="str">
-        <v>assets/1785854129383-c8qkvl537x.jpeg</v>
+        <v>assets/1785853950207-cedor66ou2q.jpeg</v>
       </c>
       <c r="D27" t="str">
         <v>是</v>
@@ -1676,13 +1676,13 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B28" t="str">
         <v>弟弟</v>
       </c>
       <c r="C28" t="str">
-        <v>assets/1785854166720-48r17hry9cd.jpeg</v>
+        <v>assets/1785854129383-c8qkvl537x.jpeg</v>
       </c>
       <c r="D28" t="str">
         <v>是</v>
@@ -1691,7 +1691,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>山西朔州</v>
+        <v>广东广州</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1726,10 +1726,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B29" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C29" t="str">
-        <v>assets/1785854224521-2cpg6xipfn6.jpeg</v>
+        <v>assets/1785854166720-48r17hry9cd.jpeg</v>
       </c>
       <c r="D29" t="str">
         <v>是</v>
@@ -1738,7 +1738,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>浙江宁波</v>
+        <v>山西朔州</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1773,10 +1773,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B30" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C30" t="str">
-        <v>assets/1785854260793-steez4s972l.jpeg</v>
+        <v>assets/1785854224521-2cpg6xipfn6.jpeg</v>
       </c>
       <c r="D30" t="str">
         <v>是</v>
@@ -1785,7 +1785,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>陕西西安</v>
+        <v>浙江宁波</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1823,7 +1823,7 @@
         <v>弟弟</v>
       </c>
       <c r="C31" t="str">
-        <v>assets/1785854319988-cohio08aod5.jpeg</v>
+        <v>assets/1785854260793-steez4s972l.jpeg</v>
       </c>
       <c r="D31" t="str">
         <v>是</v>
@@ -1832,7 +1832,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>黑龙江漠河</v>
+        <v>陕西西安</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1864,13 +1864,13 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B32" t="str">
         <v>弟弟</v>
       </c>
       <c r="C32" t="str">
-        <v>assets/1785854520974-96b8b1ekqd9.jpeg</v>
+        <v>assets/1785854319988-cohio08aod5.jpeg</v>
       </c>
       <c r="D32" t="str">
         <v>是</v>
@@ -1879,7 +1879,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>日本</v>
+        <v>黑龙江漠河</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1911,13 +1911,13 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B33" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C33" t="str">
-        <v>assets/1785854664100-haqoiu1h7hj.jpeg</v>
+        <v>assets/1785854520974-96b8b1ekqd9.jpeg</v>
       </c>
       <c r="D33" t="str">
         <v>是</v>
@@ -1926,7 +1926,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>浙江杭州</v>
+        <v>日本</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1964,7 +1964,7 @@
         <v>妹妹</v>
       </c>
       <c r="C34" t="str">
-        <v>assets/1785854690732-orrs40sx9rs.jpeg</v>
+        <v>assets/1785854664100-haqoiu1h7hj.jpeg</v>
       </c>
       <c r="D34" t="str">
         <v>是</v>
@@ -1973,7 +1973,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>贵州安顺</v>
+        <v>浙江杭州</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -2011,7 +2011,7 @@
         <v>妹妹</v>
       </c>
       <c r="C35" t="str">
-        <v>assets/1785854734122-wcpmib4m7.jpeg</v>
+        <v>assets/1785854690732-orrs40sx9rs.jpeg</v>
       </c>
       <c r="D35" t="str">
         <v>是</v>
@@ -2020,7 +2020,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>山东青岛</v>
+        <v>贵州安顺</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -2055,10 +2055,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B36" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C36" t="str">
-        <v>assets/1785854758707-1kxdkfvs6jc.jpeg</v>
+        <v>assets/1785854734122-wcpmib4m7.jpeg</v>
       </c>
       <c r="D36" t="str">
         <v>是</v>
@@ -2067,7 +2067,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>黑龙江漠河</v>
+        <v>山东青岛</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -2099,13 +2099,13 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>纯蓝色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B37" t="str">
         <v>弟弟</v>
       </c>
       <c r="C37" t="str">
-        <v>assets/1785854784780-3g0u60pdo93.jpeg</v>
+        <v>assets/1785854758707-1kxdkfvs6jc.jpeg</v>
       </c>
       <c r="D37" t="str">
         <v>是</v>
@@ -2114,7 +2114,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>河南鹤壁</v>
+        <v>黑龙江漠河</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -2146,13 +2146,13 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>银虎斑</v>
+        <v>纯蓝色</v>
       </c>
       <c r="B38" t="str">
         <v>弟弟</v>
       </c>
       <c r="C38" t="str">
-        <v>assets/1785854813179-8oyxr0h2bbu.jpeg</v>
+        <v>assets/1785854784780-3g0u60pdo93.jpeg</v>
       </c>
       <c r="D38" t="str">
         <v>是</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>陕西西安</v>
+        <v>河南鹤壁</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -2193,13 +2193,13 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B39" t="str">
         <v>弟弟</v>
       </c>
       <c r="C39" t="str">
-        <v>assets/1785854838933-uq6amircyzd.jpeg</v>
+        <v>assets/1785854813179-8oyxr0h2bbu.jpeg</v>
       </c>
       <c r="D39" t="str">
         <v>是</v>
@@ -2208,7 +2208,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>四川成都</v>
+        <v>陕西西安</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -2240,22 +2240,22 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B40" t="str">
         <v>弟弟</v>
       </c>
       <c r="C40" t="str">
-        <v>assets/1785854869973-za3p6wikqpo.jpeg</v>
+        <v>assets/1785854838933-uq6amircyzd.jpeg</v>
       </c>
       <c r="D40" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E40" t="str">
-        <v>2026-05-18</v>
+        <v/>
       </c>
       <c r="F40" t="str">
-        <v/>
+        <v>四川成都</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -2287,19 +2287,19 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B41" t="str">
         <v>弟弟</v>
       </c>
       <c r="C41" t="str">
-        <v>assets/1785854997023-mawkallt2a.jpeg</v>
+        <v>assets/1785854869973-za3p6wikqpo.jpeg</v>
       </c>
       <c r="D41" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E41" t="str">
-        <v/>
+        <v>2026-05-18</v>
       </c>
       <c r="F41" t="str">
         <v/>
@@ -2334,13 +2334,13 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>凯米尔色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B42" t="str">
         <v>弟弟</v>
       </c>
       <c r="C42" t="str">
-        <v>assets/1785855043327-wdc5pxwm34k.jpeg</v>
+        <v>assets/1785854997023-mawkallt2a.jpeg</v>
       </c>
       <c r="D42" t="str">
         <v>是</v>
@@ -2349,7 +2349,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>上海浦东</v>
+        <v/>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -2381,22 +2381,22 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>棕虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B43" t="str">
         <v>弟弟</v>
       </c>
       <c r="C43" t="str">
-        <v>assets/1785912551260-jplefm937nk.jpeg, assets/videos/02.mp4</v>
+        <v>assets/1785855043327-wdc5pxwm34k.jpeg</v>
       </c>
       <c r="D43" t="str">
         <v>是</v>
       </c>
       <c r="E43" t="str">
-        <v>2026-06-06</v>
+        <v/>
       </c>
       <c r="F43" t="str">
-        <v>浙江温州</v>
+        <v>上海浦东</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2431,19 +2431,19 @@
         <v>棕虎斑</v>
       </c>
       <c r="B44" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C44" t="str">
-        <v>assets/1785912694000-m20f5kvvrr.jpeg</v>
+        <v>assets/1785912551260-jplefm937nk.jpeg, assets/videos/02.mp4</v>
       </c>
       <c r="D44" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E44" t="str">
         <v>2026-06-06</v>
       </c>
       <c r="F44" t="str">
-        <v/>
+        <v>浙江温州</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2470,12 +2470,59 @@
         <v/>
       </c>
       <c r="O44" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>棕虎斑</v>
+      </c>
+      <c r="B45" t="str">
+        <v>妹妹</v>
+      </c>
+      <c r="C45" t="str">
+        <v>assets/1785912694000-m20f5kvvrr.jpeg</v>
+      </c>
+      <c r="D45" t="str">
+        <v>否</v>
+      </c>
+      <c r="E45" t="str">
+        <v>2026-06-06</v>
+      </c>
+      <c r="F45" t="str">
+        <v/>
+      </c>
+      <c r="G45" t="str">
+        <v/>
+      </c>
+      <c r="H45" t="str">
+        <v/>
+      </c>
+      <c r="I45" t="str">
+        <v/>
+      </c>
+      <c r="J45" t="str">
+        <v/>
+      </c>
+      <c r="K45" t="str">
+        <v/>
+      </c>
+      <c r="L45" t="str">
+        <v/>
+      </c>
+      <c r="M45" t="str">
+        <v/>
+      </c>
+      <c r="N45" t="str">
+        <v/>
+      </c>
+      <c r="O45" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O44"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O45"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O45"/>
+  <dimension ref="A1:O50"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -454,19 +454,19 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B2" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C2" t="str">
-        <v>assets/1787282064159-6b4z8c5msd.jpg</v>
+        <v>assets/1787282703381-2uakw592b4.jpg</v>
       </c>
       <c r="D2" t="str">
         <v>否</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -501,19 +501,19 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>阴影色NS11</v>
+        <v>烟灰色</v>
       </c>
       <c r="B3" t="str">
         <v>弟弟</v>
       </c>
       <c r="C3" t="str">
-        <v>assets/1787280590041-vzcwebdok1.jpg</v>
+        <v>assets/1787282649397-9hc31ncrpc.jpg</v>
       </c>
       <c r="D3" t="str">
         <v>否</v>
       </c>
       <c r="E3" t="str">
-        <v>2026-05-28</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -548,19 +548,19 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>浅色银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B4" t="str">
         <v>妹妹</v>
       </c>
       <c r="C4" t="str">
-        <v>assets/1787281786169-9ia0h837ct.jpg</v>
+        <v>assets/1787282617957-svcoyyznpg.jpg</v>
       </c>
       <c r="D4" t="str">
         <v>否</v>
       </c>
       <c r="E4" t="str">
-        <v>2026-06-15</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -595,22 +595,22 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>浅烟灰色妹妹</v>
+        <v>烟灰色</v>
       </c>
       <c r="B5" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C5" t="str">
-        <v>assets/1785843720843-63qz159daui.jpg</v>
+        <v>assets/1787282419632-78nixqjzua.jpg</v>
       </c>
       <c r="D5" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E5" t="str">
-        <v>2026-03-21</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F5" t="str">
-        <v>四川成都</v>
+        <v/>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -642,19 +642,19 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>红虎斑</v>
+        <v>纯黑色</v>
       </c>
       <c r="B6" t="str">
         <v>弟弟</v>
       </c>
       <c r="C6" t="str">
-        <v>assets/1785843763310-elg05ur61ri.jpg</v>
+        <v>assets/1787282349942-2cfuyn7xlc.jpg</v>
       </c>
       <c r="D6" t="str">
         <v>否</v>
       </c>
       <c r="E6" t="str">
-        <v>2026-02-14</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -689,19 +689,19 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>银虎斑补丁</v>
+        <v>银虎斑</v>
       </c>
       <c r="B7" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C7" t="str">
-        <v>assets/1785843820715-9kz7gy4mbr7.jpg</v>
+        <v>assets/1787282064159-6b4z8c5msd.jpg</v>
       </c>
       <c r="D7" t="str">
         <v>否</v>
       </c>
       <c r="E7" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-10</v>
       </c>
       <c r="F7" t="str">
         <v/>
@@ -736,19 +736,19 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>烟灰色</v>
+        <v>阴影色NS11</v>
       </c>
       <c r="B8" t="str">
         <v>弟弟</v>
       </c>
       <c r="C8" t="str">
-        <v>assets/1785843953805-mxl3x1982io.jpg</v>
+        <v>assets/1787280590041-vzcwebdok1.jpg</v>
       </c>
       <c r="D8" t="str">
         <v>否</v>
       </c>
       <c r="E8" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -783,19 +783,19 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>棕虎斑玳瑁</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B9" t="str">
         <v>妹妹</v>
       </c>
       <c r="C9" t="str">
-        <v>assets/1785844013835-ek4xpcje7kh.jpg</v>
+        <v>assets/1787281786169-9ia0h837ct.jpg</v>
       </c>
       <c r="D9" t="str">
         <v>否</v>
       </c>
       <c r="E9" t="str">
-        <v>2026-02-14</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -830,22 +830,22 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>银虎斑补丁</v>
+        <v>浅烟灰色妹妹</v>
       </c>
       <c r="B10" t="str">
         <v>妹妹</v>
       </c>
       <c r="C10" t="str">
-        <v>assets/1785844434338-ek5zbdgdcne.jpg</v>
+        <v>assets/1785843720843-63qz159daui.jpg</v>
       </c>
       <c r="D10" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E10" t="str">
-        <v>2026-05-24</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F10" t="str">
-        <v/>
+        <v>四川成都</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -877,22 +877,22 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B11" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C11" t="str">
-        <v>assets/1785838787730-s5f333sc3u.jpg</v>
+        <v>assets/1785843763310-elg05ur61ri.jpg</v>
       </c>
       <c r="D11" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E11" t="str">
-        <v>2026-06-05</v>
+        <v>2026-02-14</v>
       </c>
       <c r="F11" t="str">
-        <v>湖南恩施</v>
+        <v/>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -924,22 +924,22 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>银虎斑</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B12" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C12" t="str">
-        <v>assets/1785842296661-6qw3zs3as8h.jpg</v>
+        <v>assets/1785843820715-9kz7gy4mbr7.jpg</v>
       </c>
       <c r="D12" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E12" t="str">
-        <v>2026-06-05</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F12" t="str">
-        <v>湖北恩施</v>
+        <v/>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -971,22 +971,22 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B13" t="str">
         <v>弟弟</v>
       </c>
       <c r="C13" t="str">
-        <v>assets/1785842429109-porc98rel5.jpg</v>
+        <v>assets/1785843953805-mxl3x1982io.jpg</v>
       </c>
       <c r="D13" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E13" t="str">
-        <v>2025-11-05</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F13" t="str">
-        <v>韩国</v>
+        <v/>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -1018,19 +1018,19 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑玳瑁</v>
       </c>
       <c r="B14" t="str">
         <v>妹妹</v>
       </c>
       <c r="C14" t="str">
-        <v>assets/1785842594141-fcglbzjp509.jpg</v>
+        <v>assets/1785844013835-ek4xpcje7kh.jpg</v>
       </c>
       <c r="D14" t="str">
         <v>否</v>
       </c>
       <c r="E14" t="str">
-        <v>2026-05-18</v>
+        <v>2026-02-14</v>
       </c>
       <c r="F14" t="str">
         <v/>
@@ -1065,22 +1065,22 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B15" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C15" t="str">
-        <v>assets/1785842639100-82k775dhwiv.jpg</v>
+        <v>assets/1785844434338-ek5zbdgdcne.jpg</v>
       </c>
       <c r="D15" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E15" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-24</v>
       </c>
       <c r="F15" t="str">
-        <v>四川自贡</v>
+        <v/>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -1112,22 +1112,22 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B16" t="str">
         <v>妹妹</v>
       </c>
       <c r="C16" t="str">
-        <v>assets/1785842684502-mnhr0r96eee.jpg</v>
+        <v>assets/1785838787730-s5f333sc3u.jpg</v>
       </c>
       <c r="D16" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E16" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F16" t="str">
-        <v/>
+        <v>湖南恩施</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1159,22 +1159,22 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>纯黑色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B17" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C17" t="str">
-        <v>assets/1785842779532-5u1j0igrw1s.jpg</v>
+        <v>assets/1785842296661-6qw3zs3as8h.jpg</v>
       </c>
       <c r="D17" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E17" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F17" t="str">
-        <v/>
+        <v>湖北恩施</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1209,16 +1209,16 @@
         <v>银虎斑</v>
       </c>
       <c r="B18" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C18" t="str">
-        <v>assets/1785842817046-6keqv4rw4yf.jpg</v>
+        <v>assets/1785842429109-porc98rel5.jpg</v>
       </c>
       <c r="D18" t="str">
         <v>是</v>
       </c>
       <c r="E18" t="str">
-        <v>2026-03-05</v>
+        <v>2025-11-05</v>
       </c>
       <c r="F18" t="str">
         <v>韩国</v>
@@ -1253,22 +1253,22 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>浅色银虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B19" t="str">
         <v>妹妹</v>
       </c>
       <c r="C19" t="str">
-        <v>assets/1785842950972-a88lbrskpc.jpg</v>
+        <v>assets/1785842594141-fcglbzjp509.jpg</v>
       </c>
       <c r="D19" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E19" t="str">
-        <v>2026-06-05</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F19" t="str">
-        <v>河边邢台</v>
+        <v/>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1306,13 +1306,13 @@
         <v>弟弟</v>
       </c>
       <c r="C20" t="str">
-        <v>assets/1785843011477-n3l1wi6ech.jpg</v>
+        <v>assets/1785842639100-82k775dhwiv.jpg</v>
       </c>
       <c r="D20" t="str">
         <v>是</v>
       </c>
       <c r="E20" t="str">
-        <v>2026-06-05</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F20" t="str">
         <v>四川自贡</v>
@@ -1347,19 +1347,19 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B21" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C21" t="str">
-        <v>assets/1785843237517-ga449iqess5.jpg</v>
+        <v>assets/1785842684502-mnhr0r96eee.jpg</v>
       </c>
       <c r="D21" t="str">
         <v>否</v>
       </c>
       <c r="E21" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F21" t="str">
         <v/>
@@ -1394,13 +1394,13 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>棕虎斑补丁</v>
+        <v>纯黑色</v>
       </c>
       <c r="B22" t="str">
         <v>妹妹</v>
       </c>
       <c r="C22" t="str">
-        <v>assets/1785842523893-7nwnnhwi4ns.jpg</v>
+        <v>assets/1785842779532-5u1j0igrw1s.jpg</v>
       </c>
       <c r="D22" t="str">
         <v>否</v>
@@ -1441,22 +1441,22 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>蓝虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B23" t="str">
         <v>妹妹</v>
       </c>
       <c r="C23" t="str">
-        <v>assets/1785843497557-st27fk8drqi.jpg</v>
+        <v>assets/1785842817046-6keqv4rw4yf.jpg</v>
       </c>
       <c r="D23" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E23" t="str">
-        <v>2026-04-05</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F23" t="str">
-        <v/>
+        <v>韩国</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1488,22 +1488,22 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>银虎斑</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B24" t="str">
         <v>妹妹</v>
       </c>
       <c r="C24" t="str">
-        <v>assets/1785843621923-ylhakbtw13i.jpg</v>
+        <v>assets/1785842950972-a88lbrskpc.jpg</v>
       </c>
       <c r="D24" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E24" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F24" t="str">
-        <v/>
+        <v>河边邢台</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B25" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C25" t="str">
-        <v>assets/1785843663884-sfxvpmiet7.jpg</v>
+        <v>assets/1785843011477-n3l1wi6ech.jpg</v>
       </c>
       <c r="D25" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E25" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F25" t="str">
-        <v/>
+        <v>四川自贡</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1585,66 +1585,66 @@
         <v>蓝虎斑</v>
       </c>
       <c r="B26" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C26" t="str">
-        <v>assets/1785852601940-o236xtv7yx.jpeg</v>
+        <v>assets/1785843237517-ga449iqess5.jpg</v>
       </c>
       <c r="D26" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E26" t="str">
-        <v>2026-02-20</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F26" t="str">
-        <v>荷兰</v>
+        <v/>
       </c>
       <c r="G26" t="str">
-        <v>阿泽</v>
+        <v/>
       </c>
       <c r="H26" t="str">
-        <v>小辫子</v>
+        <v/>
       </c>
       <c r="I26" t="str">
-        <v>驺驺</v>
+        <v/>
       </c>
       <c r="J26" t="str">
-        <v>2026-07-02</v>
+        <v/>
       </c>
       <c r="K26" t="str">
-        <v>assets/diary/zouzou-depart.jpg</v>
+        <v/>
       </c>
       <c r="L26" t="str">
-        <v>2026-07-02</v>
+        <v/>
       </c>
       <c r="M26" t="str">
-        <v>2026-08-03</v>
+        <v/>
       </c>
       <c r="N26" t="str">
-        <v>2026-11-04</v>
+        <v/>
       </c>
       <c r="O26" t="str">
-        <v>2026-07-30 · 6.2斤 · 五个月10天了 · assets/feedback/zouzou-1.jpg</v>
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>红虎斑</v>
+        <v>棕虎斑补丁</v>
       </c>
       <c r="B27" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C27" t="str">
-        <v>assets/1785853950207-cedor66ou2q.jpeg</v>
+        <v>assets/1785842523893-7nwnnhwi4ns.jpg</v>
       </c>
       <c r="D27" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E27" t="str">
-        <v/>
+        <v>2026-03-05</v>
       </c>
       <c r="F27" t="str">
-        <v>广东广州</v>
+        <v/>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1676,22 +1676,22 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>红虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B28" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C28" t="str">
-        <v>assets/1785854129383-c8qkvl537x.jpeg</v>
+        <v>assets/1785843497557-st27fk8drqi.jpg</v>
       </c>
       <c r="D28" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E28" t="str">
-        <v/>
+        <v>2026-04-05</v>
       </c>
       <c r="F28" t="str">
-        <v>广东广州</v>
+        <v/>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1726,19 +1726,19 @@
         <v>银虎斑</v>
       </c>
       <c r="B29" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C29" t="str">
-        <v>assets/1785854166720-48r17hry9cd.jpeg</v>
+        <v>assets/1785843621923-ylhakbtw13i.jpg</v>
       </c>
       <c r="D29" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E29" t="str">
-        <v/>
+        <v>2026-03-05</v>
       </c>
       <c r="F29" t="str">
-        <v>山西朔州</v>
+        <v/>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1776,16 +1776,16 @@
         <v>妹妹</v>
       </c>
       <c r="C30" t="str">
-        <v>assets/1785854224521-2cpg6xipfn6.jpeg</v>
+        <v>assets/1785843663884-sfxvpmiet7.jpg</v>
       </c>
       <c r="D30" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E30" t="str">
-        <v/>
+        <v>2026-03-05</v>
       </c>
       <c r="F30" t="str">
-        <v>浙江宁波</v>
+        <v/>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1817,60 +1817,60 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B31" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C31" t="str">
-        <v>assets/1785854260793-steez4s972l.jpeg</v>
+        <v>assets/1785852601940-o236xtv7yx.jpeg</v>
       </c>
       <c r="D31" t="str">
         <v>是</v>
       </c>
       <c r="E31" t="str">
-        <v/>
+        <v>2026-02-20</v>
       </c>
       <c r="F31" t="str">
-        <v>陕西西安</v>
+        <v>荷兰</v>
       </c>
       <c r="G31" t="str">
-        <v/>
+        <v>阿泽</v>
       </c>
       <c r="H31" t="str">
-        <v/>
+        <v>小辫子</v>
       </c>
       <c r="I31" t="str">
-        <v/>
+        <v>驺驺</v>
       </c>
       <c r="J31" t="str">
-        <v/>
+        <v>2026-07-02</v>
       </c>
       <c r="K31" t="str">
-        <v/>
+        <v>assets/diary/zouzou-depart.jpg</v>
       </c>
       <c r="L31" t="str">
-        <v/>
+        <v>2026-07-02</v>
       </c>
       <c r="M31" t="str">
-        <v/>
+        <v>2026-08-03</v>
       </c>
       <c r="N31" t="str">
-        <v/>
+        <v>2026-11-04</v>
       </c>
       <c r="O31" t="str">
-        <v/>
+        <v>2026-07-30 · 6.2斤 · 五个月10天了 · assets/feedback/zouzou-1.jpg</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B32" t="str">
         <v>弟弟</v>
       </c>
       <c r="C32" t="str">
-        <v>assets/1785854319988-cohio08aod5.jpeg</v>
+        <v>assets/1785853950207-cedor66ou2q.jpeg</v>
       </c>
       <c r="D32" t="str">
         <v>是</v>
@@ -1879,7 +1879,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>黑龙江漠河</v>
+        <v>广东广州</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1911,13 +1911,13 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>棕虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B33" t="str">
         <v>弟弟</v>
       </c>
       <c r="C33" t="str">
-        <v>assets/1785854520974-96b8b1ekqd9.jpeg</v>
+        <v>assets/1785854129383-c8qkvl537x.jpeg</v>
       </c>
       <c r="D33" t="str">
         <v>是</v>
@@ -1926,7 +1926,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>日本</v>
+        <v>广东广州</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1961,10 +1961,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B34" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C34" t="str">
-        <v>assets/1785854664100-haqoiu1h7hj.jpeg</v>
+        <v>assets/1785854166720-48r17hry9cd.jpeg</v>
       </c>
       <c r="D34" t="str">
         <v>是</v>
@@ -1973,7 +1973,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>浙江杭州</v>
+        <v>山西朔州</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -2011,7 +2011,7 @@
         <v>妹妹</v>
       </c>
       <c r="C35" t="str">
-        <v>assets/1785854690732-orrs40sx9rs.jpeg</v>
+        <v>assets/1785854224521-2cpg6xipfn6.jpeg</v>
       </c>
       <c r="D35" t="str">
         <v>是</v>
@@ -2020,7 +2020,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>贵州安顺</v>
+        <v>浙江宁波</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -2055,10 +2055,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B36" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C36" t="str">
-        <v>assets/1785854734122-wcpmib4m7.jpeg</v>
+        <v>assets/1785854260793-steez4s972l.jpeg</v>
       </c>
       <c r="D36" t="str">
         <v>是</v>
@@ -2067,7 +2067,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>山东青岛</v>
+        <v>陕西西安</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -2105,7 +2105,7 @@
         <v>弟弟</v>
       </c>
       <c r="C37" t="str">
-        <v>assets/1785854758707-1kxdkfvs6jc.jpeg</v>
+        <v>assets/1785854319988-cohio08aod5.jpeg</v>
       </c>
       <c r="D37" t="str">
         <v>是</v>
@@ -2146,13 +2146,13 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>纯蓝色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B38" t="str">
         <v>弟弟</v>
       </c>
       <c r="C38" t="str">
-        <v>assets/1785854784780-3g0u60pdo93.jpeg</v>
+        <v>assets/1785854520974-96b8b1ekqd9.jpeg</v>
       </c>
       <c r="D38" t="str">
         <v>是</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>河南鹤壁</v>
+        <v>日本</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -2196,10 +2196,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B39" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C39" t="str">
-        <v>assets/1785854813179-8oyxr0h2bbu.jpeg</v>
+        <v>assets/1785854664100-haqoiu1h7hj.jpeg</v>
       </c>
       <c r="D39" t="str">
         <v>是</v>
@@ -2208,7 +2208,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>陕西西安</v>
+        <v>浙江杭州</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -2240,13 +2240,13 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B40" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C40" t="str">
-        <v>assets/1785854838933-uq6amircyzd.jpeg</v>
+        <v>assets/1785854690732-orrs40sx9rs.jpeg</v>
       </c>
       <c r="D40" t="str">
         <v>是</v>
@@ -2255,7 +2255,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>四川成都</v>
+        <v>贵州安顺</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -2287,22 +2287,22 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>烟灰色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B41" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C41" t="str">
-        <v>assets/1785854869973-za3p6wikqpo.jpeg</v>
+        <v>assets/1785854734122-wcpmib4m7.jpeg</v>
       </c>
       <c r="D41" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E41" t="str">
-        <v>2026-05-18</v>
+        <v/>
       </c>
       <c r="F41" t="str">
-        <v/>
+        <v>山东青岛</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -2340,7 +2340,7 @@
         <v>弟弟</v>
       </c>
       <c r="C42" t="str">
-        <v>assets/1785854997023-mawkallt2a.jpeg</v>
+        <v>assets/1785854758707-1kxdkfvs6jc.jpeg</v>
       </c>
       <c r="D42" t="str">
         <v>是</v>
@@ -2349,7 +2349,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v/>
+        <v>黑龙江漠河</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -2381,13 +2381,13 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>凯米尔色</v>
+        <v>纯蓝色</v>
       </c>
       <c r="B43" t="str">
         <v>弟弟</v>
       </c>
       <c r="C43" t="str">
-        <v>assets/1785855043327-wdc5pxwm34k.jpeg</v>
+        <v>assets/1785854784780-3g0u60pdo93.jpeg</v>
       </c>
       <c r="D43" t="str">
         <v>是</v>
@@ -2396,7 +2396,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>上海浦东</v>
+        <v>河南鹤壁</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2428,22 +2428,22 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B44" t="str">
         <v>弟弟</v>
       </c>
       <c r="C44" t="str">
-        <v>assets/1785912551260-jplefm937nk.jpeg, assets/videos/02.mp4</v>
+        <v>assets/1785854813179-8oyxr0h2bbu.jpeg</v>
       </c>
       <c r="D44" t="str">
         <v>是</v>
       </c>
       <c r="E44" t="str">
-        <v>2026-06-06</v>
+        <v/>
       </c>
       <c r="F44" t="str">
-        <v>浙江温州</v>
+        <v>陕西西安</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2478,51 +2478,286 @@
         <v>棕虎斑</v>
       </c>
       <c r="B45" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C45" t="str">
+        <v>assets/1785854838933-uq6amircyzd.jpeg</v>
+      </c>
+      <c r="D45" t="str">
+        <v>是</v>
+      </c>
+      <c r="E45" t="str">
+        <v/>
+      </c>
+      <c r="F45" t="str">
+        <v>四川成都</v>
+      </c>
+      <c r="G45" t="str">
+        <v/>
+      </c>
+      <c r="H45" t="str">
+        <v/>
+      </c>
+      <c r="I45" t="str">
+        <v/>
+      </c>
+      <c r="J45" t="str">
+        <v/>
+      </c>
+      <c r="K45" t="str">
+        <v/>
+      </c>
+      <c r="L45" t="str">
+        <v/>
+      </c>
+      <c r="M45" t="str">
+        <v/>
+      </c>
+      <c r="N45" t="str">
+        <v/>
+      </c>
+      <c r="O45" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>烟灰色</v>
+      </c>
+      <c r="B46" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C46" t="str">
+        <v>assets/1785854869973-za3p6wikqpo.jpeg</v>
+      </c>
+      <c r="D46" t="str">
+        <v>否</v>
+      </c>
+      <c r="E46" t="str">
+        <v>2026-05-18</v>
+      </c>
+      <c r="F46" t="str">
+        <v/>
+      </c>
+      <c r="G46" t="str">
+        <v/>
+      </c>
+      <c r="H46" t="str">
+        <v/>
+      </c>
+      <c r="I46" t="str">
+        <v/>
+      </c>
+      <c r="J46" t="str">
+        <v/>
+      </c>
+      <c r="K46" t="str">
+        <v/>
+      </c>
+      <c r="L46" t="str">
+        <v/>
+      </c>
+      <c r="M46" t="str">
+        <v/>
+      </c>
+      <c r="N46" t="str">
+        <v/>
+      </c>
+      <c r="O46" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>银虎斑</v>
+      </c>
+      <c r="B47" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C47" t="str">
+        <v>assets/1785854997023-mawkallt2a.jpeg</v>
+      </c>
+      <c r="D47" t="str">
+        <v>是</v>
+      </c>
+      <c r="E47" t="str">
+        <v/>
+      </c>
+      <c r="F47" t="str">
+        <v/>
+      </c>
+      <c r="G47" t="str">
+        <v/>
+      </c>
+      <c r="H47" t="str">
+        <v/>
+      </c>
+      <c r="I47" t="str">
+        <v/>
+      </c>
+      <c r="J47" t="str">
+        <v/>
+      </c>
+      <c r="K47" t="str">
+        <v/>
+      </c>
+      <c r="L47" t="str">
+        <v/>
+      </c>
+      <c r="M47" t="str">
+        <v/>
+      </c>
+      <c r="N47" t="str">
+        <v/>
+      </c>
+      <c r="O47" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>凯米尔色</v>
+      </c>
+      <c r="B48" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C48" t="str">
+        <v>assets/1785855043327-wdc5pxwm34k.jpeg</v>
+      </c>
+      <c r="D48" t="str">
+        <v>是</v>
+      </c>
+      <c r="E48" t="str">
+        <v/>
+      </c>
+      <c r="F48" t="str">
+        <v>上海浦东</v>
+      </c>
+      <c r="G48" t="str">
+        <v/>
+      </c>
+      <c r="H48" t="str">
+        <v/>
+      </c>
+      <c r="I48" t="str">
+        <v/>
+      </c>
+      <c r="J48" t="str">
+        <v/>
+      </c>
+      <c r="K48" t="str">
+        <v/>
+      </c>
+      <c r="L48" t="str">
+        <v/>
+      </c>
+      <c r="M48" t="str">
+        <v/>
+      </c>
+      <c r="N48" t="str">
+        <v/>
+      </c>
+      <c r="O48" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>棕虎斑</v>
+      </c>
+      <c r="B49" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C49" t="str">
+        <v>assets/1785912551260-jplefm937nk.jpeg, assets/videos/02.mp4</v>
+      </c>
+      <c r="D49" t="str">
+        <v>是</v>
+      </c>
+      <c r="E49" t="str">
+        <v>2026-06-06</v>
+      </c>
+      <c r="F49" t="str">
+        <v>浙江温州</v>
+      </c>
+      <c r="G49" t="str">
+        <v/>
+      </c>
+      <c r="H49" t="str">
+        <v/>
+      </c>
+      <c r="I49" t="str">
+        <v/>
+      </c>
+      <c r="J49" t="str">
+        <v/>
+      </c>
+      <c r="K49" t="str">
+        <v/>
+      </c>
+      <c r="L49" t="str">
+        <v/>
+      </c>
+      <c r="M49" t="str">
+        <v/>
+      </c>
+      <c r="N49" t="str">
+        <v/>
+      </c>
+      <c r="O49" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>棕虎斑</v>
+      </c>
+      <c r="B50" t="str">
         <v>妹妹</v>
       </c>
-      <c r="C45" t="str">
+      <c r="C50" t="str">
         <v>assets/1785912694000-m20f5kvvrr.jpeg</v>
       </c>
-      <c r="D45" t="str">
+      <c r="D50" t="str">
         <v>否</v>
       </c>
-      <c r="E45" t="str">
+      <c r="E50" t="str">
         <v>2026-06-06</v>
       </c>
-      <c r="F45" t="str">
-        <v/>
-      </c>
-      <c r="G45" t="str">
-        <v/>
-      </c>
-      <c r="H45" t="str">
-        <v/>
-      </c>
-      <c r="I45" t="str">
-        <v/>
-      </c>
-      <c r="J45" t="str">
-        <v/>
-      </c>
-      <c r="K45" t="str">
-        <v/>
-      </c>
-      <c r="L45" t="str">
-        <v/>
-      </c>
-      <c r="M45" t="str">
-        <v/>
-      </c>
-      <c r="N45" t="str">
-        <v/>
-      </c>
-      <c r="O45" t="str">
+      <c r="F50" t="str">
+        <v/>
+      </c>
+      <c r="G50" t="str">
+        <v/>
+      </c>
+      <c r="H50" t="str">
+        <v/>
+      </c>
+      <c r="I50" t="str">
+        <v/>
+      </c>
+      <c r="J50" t="str">
+        <v/>
+      </c>
+      <c r="K50" t="str">
+        <v/>
+      </c>
+      <c r="L50" t="str">
+        <v/>
+      </c>
+      <c r="M50" t="str">
+        <v/>
+      </c>
+      <c r="N50" t="str">
+        <v/>
+      </c>
+      <c r="O50" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O45"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O50"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O50"/>
+  <dimension ref="A1:O51"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -457,10 +457,10 @@
         <v>棕虎斑</v>
       </c>
       <c r="B2" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C2" t="str">
-        <v>assets/1787282703381-2uakw592b4.jpg</v>
+        <v>assets/1787282819855-7vhx3m0v40.jpg</v>
       </c>
       <c r="D2" t="str">
         <v>否</v>
@@ -501,13 +501,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B3" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C3" t="str">
-        <v>assets/1787282649397-9hc31ncrpc.jpg</v>
+        <v>assets/1787282703381-2uakw592b4.jpg</v>
       </c>
       <c r="D3" t="str">
         <v>否</v>
@@ -551,10 +551,10 @@
         <v>烟灰色</v>
       </c>
       <c r="B4" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C4" t="str">
-        <v>assets/1787282617957-svcoyyznpg.jpg</v>
+        <v>assets/1787282649397-9hc31ncrpc.jpg</v>
       </c>
       <c r="D4" t="str">
         <v>否</v>
@@ -598,10 +598,10 @@
         <v>烟灰色</v>
       </c>
       <c r="B5" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C5" t="str">
-        <v>assets/1787282419632-78nixqjzua.jpg</v>
+        <v>assets/1787282617957-svcoyyznpg.jpg</v>
       </c>
       <c r="D5" t="str">
         <v>否</v>
@@ -642,19 +642,19 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>纯黑色</v>
+        <v>烟灰色</v>
       </c>
       <c r="B6" t="str">
         <v>弟弟</v>
       </c>
       <c r="C6" t="str">
-        <v>assets/1787282349942-2cfuyn7xlc.jpg</v>
+        <v>assets/1787282419632-78nixqjzua.jpg</v>
       </c>
       <c r="D6" t="str">
         <v>否</v>
       </c>
       <c r="E6" t="str">
-        <v>2026-03-21</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -689,19 +689,19 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>银虎斑</v>
+        <v>纯黑色</v>
       </c>
       <c r="B7" t="str">
         <v>弟弟</v>
       </c>
       <c r="C7" t="str">
-        <v>assets/1787282064159-6b4z8c5msd.jpg</v>
+        <v>assets/1787282349942-2cfuyn7xlc.jpg</v>
       </c>
       <c r="D7" t="str">
         <v>否</v>
       </c>
       <c r="E7" t="str">
-        <v>2026-06-10</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F7" t="str">
         <v/>
@@ -736,19 +736,19 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>阴影色NS11</v>
+        <v>银虎斑</v>
       </c>
       <c r="B8" t="str">
         <v>弟弟</v>
       </c>
       <c r="C8" t="str">
-        <v>assets/1787280590041-vzcwebdok1.jpg</v>
+        <v>assets/1787282064159-6b4z8c5msd.jpg</v>
       </c>
       <c r="D8" t="str">
         <v>否</v>
       </c>
       <c r="E8" t="str">
-        <v>2026-05-28</v>
+        <v>2026-06-10</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -783,19 +783,19 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>浅色银虎斑</v>
+        <v>阴影色NS11</v>
       </c>
       <c r="B9" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C9" t="str">
-        <v>assets/1787281786169-9ia0h837ct.jpg</v>
+        <v>assets/1787280590041-vzcwebdok1.jpg</v>
       </c>
       <c r="D9" t="str">
         <v>否</v>
       </c>
       <c r="E9" t="str">
-        <v>2026-06-15</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -830,22 +830,22 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>浅烟灰色妹妹</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B10" t="str">
         <v>妹妹</v>
       </c>
       <c r="C10" t="str">
-        <v>assets/1785843720843-63qz159daui.jpg</v>
+        <v>assets/1787281786169-9ia0h837ct.jpg</v>
       </c>
       <c r="D10" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E10" t="str">
-        <v>2026-03-21</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F10" t="str">
-        <v>四川成都</v>
+        <v/>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -877,22 +877,22 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>红虎斑</v>
+        <v>浅烟灰色妹妹</v>
       </c>
       <c r="B11" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C11" t="str">
-        <v>assets/1785843763310-elg05ur61ri.jpg</v>
+        <v>assets/1785843720843-63qz159daui.jpg</v>
       </c>
       <c r="D11" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E11" t="str">
-        <v>2026-02-14</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F11" t="str">
-        <v/>
+        <v>四川成都</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -924,19 +924,19 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>银虎斑补丁</v>
+        <v>红虎斑</v>
       </c>
       <c r="B12" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C12" t="str">
-        <v>assets/1785843820715-9kz7gy4mbr7.jpg</v>
+        <v>assets/1785843763310-elg05ur61ri.jpg</v>
       </c>
       <c r="D12" t="str">
         <v>否</v>
       </c>
       <c r="E12" t="str">
-        <v>2026-03-05</v>
+        <v>2026-02-14</v>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -971,19 +971,19 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>烟灰色</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B13" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C13" t="str">
-        <v>assets/1785843953805-mxl3x1982io.jpg</v>
+        <v>assets/1785843820715-9kz7gy4mbr7.jpg</v>
       </c>
       <c r="D13" t="str">
         <v>否</v>
       </c>
       <c r="E13" t="str">
-        <v>2026-05-18</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F13" t="str">
         <v/>
@@ -1018,19 +1018,19 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>棕虎斑玳瑁</v>
+        <v>烟灰色</v>
       </c>
       <c r="B14" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C14" t="str">
-        <v>assets/1785844013835-ek4xpcje7kh.jpg</v>
+        <v>assets/1785843953805-mxl3x1982io.jpg</v>
       </c>
       <c r="D14" t="str">
         <v>否</v>
       </c>
       <c r="E14" t="str">
-        <v>2026-02-14</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F14" t="str">
         <v/>
@@ -1065,19 +1065,19 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>银虎斑补丁</v>
+        <v>棕虎斑玳瑁</v>
       </c>
       <c r="B15" t="str">
         <v>妹妹</v>
       </c>
       <c r="C15" t="str">
-        <v>assets/1785844434338-ek5zbdgdcne.jpg</v>
+        <v>assets/1785844013835-ek4xpcje7kh.jpg</v>
       </c>
       <c r="D15" t="str">
         <v>否</v>
       </c>
       <c r="E15" t="str">
-        <v>2026-05-24</v>
+        <v>2026-02-14</v>
       </c>
       <c r="F15" t="str">
         <v/>
@@ -1112,22 +1112,22 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>银虎斑</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B16" t="str">
         <v>妹妹</v>
       </c>
       <c r="C16" t="str">
-        <v>assets/1785838787730-s5f333sc3u.jpg</v>
+        <v>assets/1785844434338-ek5zbdgdcne.jpg</v>
       </c>
       <c r="D16" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E16" t="str">
-        <v>2026-06-05</v>
+        <v>2026-05-24</v>
       </c>
       <c r="F16" t="str">
-        <v>湖南恩施</v>
+        <v/>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1162,10 +1162,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B17" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C17" t="str">
-        <v>assets/1785842296661-6qw3zs3as8h.jpg</v>
+        <v>assets/1785838787730-s5f333sc3u.jpg</v>
       </c>
       <c r="D17" t="str">
         <v>是</v>
@@ -1174,7 +1174,7 @@
         <v>2026-06-05</v>
       </c>
       <c r="F17" t="str">
-        <v>湖北恩施</v>
+        <v>湖南恩施</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1212,16 +1212,16 @@
         <v>弟弟</v>
       </c>
       <c r="C18" t="str">
-        <v>assets/1785842429109-porc98rel5.jpg</v>
+        <v>assets/1785842296661-6qw3zs3as8h.jpg</v>
       </c>
       <c r="D18" t="str">
         <v>是</v>
       </c>
       <c r="E18" t="str">
-        <v>2025-11-05</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F18" t="str">
-        <v>韩国</v>
+        <v>湖北恩施</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1256,19 +1256,19 @@
         <v>银虎斑</v>
       </c>
       <c r="B19" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C19" t="str">
-        <v>assets/1785842594141-fcglbzjp509.jpg</v>
+        <v>assets/1785842429109-porc98rel5.jpg</v>
       </c>
       <c r="D19" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E19" t="str">
-        <v>2026-05-18</v>
+        <v>2025-11-05</v>
       </c>
       <c r="F19" t="str">
-        <v/>
+        <v>韩国</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1300,22 +1300,22 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B20" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C20" t="str">
-        <v>assets/1785842639100-82k775dhwiv.jpg</v>
+        <v>assets/1785842594141-fcglbzjp509.jpg</v>
       </c>
       <c r="D20" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E20" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F20" t="str">
-        <v>四川自贡</v>
+        <v/>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1350,19 +1350,19 @@
         <v>棕虎斑</v>
       </c>
       <c r="B21" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C21" t="str">
-        <v>assets/1785842684502-mnhr0r96eee.jpg</v>
+        <v>assets/1785842639100-82k775dhwiv.jpg</v>
       </c>
       <c r="D21" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E21" t="str">
-        <v>2026-06-06</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F21" t="str">
-        <v/>
+        <v>四川自贡</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1394,19 +1394,19 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>纯黑色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B22" t="str">
         <v>妹妹</v>
       </c>
       <c r="C22" t="str">
-        <v>assets/1785842779532-5u1j0igrw1s.jpg</v>
+        <v>assets/1785842684502-mnhr0r96eee.jpg</v>
       </c>
       <c r="D22" t="str">
         <v>否</v>
       </c>
       <c r="E22" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F22" t="str">
         <v/>
@@ -1441,22 +1441,22 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>银虎斑</v>
+        <v>纯黑色</v>
       </c>
       <c r="B23" t="str">
         <v>妹妹</v>
       </c>
       <c r="C23" t="str">
-        <v>assets/1785842817046-6keqv4rw4yf.jpg</v>
+        <v>assets/1785842779532-5u1j0igrw1s.jpg</v>
       </c>
       <c r="D23" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E23" t="str">
         <v>2026-03-05</v>
       </c>
       <c r="F23" t="str">
-        <v>韩国</v>
+        <v/>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1488,22 +1488,22 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>浅色银虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B24" t="str">
         <v>妹妹</v>
       </c>
       <c r="C24" t="str">
-        <v>assets/1785842950972-a88lbrskpc.jpg</v>
+        <v>assets/1785842817046-6keqv4rw4yf.jpg</v>
       </c>
       <c r="D24" t="str">
         <v>是</v>
       </c>
       <c r="E24" t="str">
-        <v>2026-06-05</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F24" t="str">
-        <v>河边邢台</v>
+        <v>韩国</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1535,13 +1535,13 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>棕虎斑</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B25" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C25" t="str">
-        <v>assets/1785843011477-n3l1wi6ech.jpg</v>
+        <v>assets/1785842950972-a88lbrskpc.jpg</v>
       </c>
       <c r="D25" t="str">
         <v>是</v>
@@ -1550,7 +1550,7 @@
         <v>2026-06-05</v>
       </c>
       <c r="F25" t="str">
-        <v>四川自贡</v>
+        <v>河边邢台</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1582,22 +1582,22 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B26" t="str">
         <v>弟弟</v>
       </c>
       <c r="C26" t="str">
-        <v>assets/1785843237517-ga449iqess5.jpg</v>
+        <v>assets/1785843011477-n3l1wi6ech.jpg</v>
       </c>
       <c r="D26" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E26" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F26" t="str">
-        <v/>
+        <v>四川自贡</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1629,13 +1629,13 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>棕虎斑补丁</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B27" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C27" t="str">
-        <v>assets/1785842523893-7nwnnhwi4ns.jpg</v>
+        <v>assets/1785843237517-ga449iqess5.jpg</v>
       </c>
       <c r="D27" t="str">
         <v>否</v>
@@ -1676,19 +1676,19 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎斑补丁</v>
       </c>
       <c r="B28" t="str">
         <v>妹妹</v>
       </c>
       <c r="C28" t="str">
-        <v>assets/1785843497557-st27fk8drqi.jpg</v>
+        <v>assets/1785842523893-7nwnnhwi4ns.jpg</v>
       </c>
       <c r="D28" t="str">
         <v>否</v>
       </c>
       <c r="E28" t="str">
-        <v>2026-04-05</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F28" t="str">
         <v/>
@@ -1723,19 +1723,19 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B29" t="str">
         <v>妹妹</v>
       </c>
       <c r="C29" t="str">
-        <v>assets/1785843621923-ylhakbtw13i.jpg</v>
+        <v>assets/1785843497557-st27fk8drqi.jpg</v>
       </c>
       <c r="D29" t="str">
         <v>否</v>
       </c>
       <c r="E29" t="str">
-        <v>2026-03-05</v>
+        <v>2026-04-05</v>
       </c>
       <c r="F29" t="str">
         <v/>
@@ -1776,7 +1776,7 @@
         <v>妹妹</v>
       </c>
       <c r="C30" t="str">
-        <v>assets/1785843663884-sfxvpmiet7.jpg</v>
+        <v>assets/1785843621923-ylhakbtw13i.jpg</v>
       </c>
       <c r="D30" t="str">
         <v>否</v>
@@ -1817,96 +1817,96 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>蓝虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B31" t="str">
         <v>妹妹</v>
       </c>
       <c r="C31" t="str">
-        <v>assets/1785852601940-o236xtv7yx.jpeg</v>
+        <v>assets/1785843663884-sfxvpmiet7.jpg</v>
       </c>
       <c r="D31" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E31" t="str">
-        <v>2026-02-20</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F31" t="str">
-        <v>荷兰</v>
+        <v/>
       </c>
       <c r="G31" t="str">
-        <v>阿泽</v>
+        <v/>
       </c>
       <c r="H31" t="str">
-        <v>小辫子</v>
+        <v/>
       </c>
       <c r="I31" t="str">
-        <v>驺驺</v>
+        <v/>
       </c>
       <c r="J31" t="str">
-        <v>2026-07-02</v>
+        <v/>
       </c>
       <c r="K31" t="str">
-        <v>assets/diary/zouzou-depart.jpg</v>
+        <v/>
       </c>
       <c r="L31" t="str">
-        <v>2026-07-02</v>
+        <v/>
       </c>
       <c r="M31" t="str">
-        <v>2026-08-03</v>
+        <v/>
       </c>
       <c r="N31" t="str">
-        <v>2026-11-04</v>
+        <v/>
       </c>
       <c r="O31" t="str">
-        <v>2026-07-30 · 6.2斤 · 五个月10天了 · assets/feedback/zouzou-1.jpg</v>
+        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>红虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B32" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C32" t="str">
-        <v>assets/1785853950207-cedor66ou2q.jpeg</v>
+        <v>assets/1785852601940-o236xtv7yx.jpeg</v>
       </c>
       <c r="D32" t="str">
         <v>是</v>
       </c>
       <c r="E32" t="str">
-        <v/>
+        <v>2026-02-20</v>
       </c>
       <c r="F32" t="str">
-        <v>广东广州</v>
+        <v>荷兰</v>
       </c>
       <c r="G32" t="str">
-        <v/>
+        <v>阿泽</v>
       </c>
       <c r="H32" t="str">
-        <v/>
+        <v>小辫子</v>
       </c>
       <c r="I32" t="str">
-        <v/>
+        <v>驺驺</v>
       </c>
       <c r="J32" t="str">
-        <v/>
+        <v>2026-07-02</v>
       </c>
       <c r="K32" t="str">
-        <v/>
+        <v>assets/diary/zouzou-depart.jpg</v>
       </c>
       <c r="L32" t="str">
-        <v/>
+        <v>2026-07-02</v>
       </c>
       <c r="M32" t="str">
-        <v/>
+        <v>2026-08-03</v>
       </c>
       <c r="N32" t="str">
-        <v/>
+        <v>2026-11-04</v>
       </c>
       <c r="O32" t="str">
-        <v/>
+        <v>2026-07-30 · 6.2斤 · 五个月10天了 · assets/feedback/zouzou-1.jpg</v>
       </c>
     </row>
     <row r="33">
@@ -1917,7 +1917,7 @@
         <v>弟弟</v>
       </c>
       <c r="C33" t="str">
-        <v>assets/1785854129383-c8qkvl537x.jpeg</v>
+        <v>assets/1785853950207-cedor66ou2q.jpeg</v>
       </c>
       <c r="D33" t="str">
         <v>是</v>
@@ -1958,13 +1958,13 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B34" t="str">
         <v>弟弟</v>
       </c>
       <c r="C34" t="str">
-        <v>assets/1785854166720-48r17hry9cd.jpeg</v>
+        <v>assets/1785854129383-c8qkvl537x.jpeg</v>
       </c>
       <c r="D34" t="str">
         <v>是</v>
@@ -1973,7 +1973,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>山西朔州</v>
+        <v>广东广州</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -2008,10 +2008,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B35" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C35" t="str">
-        <v>assets/1785854224521-2cpg6xipfn6.jpeg</v>
+        <v>assets/1785854166720-48r17hry9cd.jpeg</v>
       </c>
       <c r="D35" t="str">
         <v>是</v>
@@ -2020,7 +2020,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>浙江宁波</v>
+        <v>山西朔州</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -2055,10 +2055,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B36" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C36" t="str">
-        <v>assets/1785854260793-steez4s972l.jpeg</v>
+        <v>assets/1785854224521-2cpg6xipfn6.jpeg</v>
       </c>
       <c r="D36" t="str">
         <v>是</v>
@@ -2067,7 +2067,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>陕西西安</v>
+        <v>浙江宁波</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -2105,7 +2105,7 @@
         <v>弟弟</v>
       </c>
       <c r="C37" t="str">
-        <v>assets/1785854319988-cohio08aod5.jpeg</v>
+        <v>assets/1785854260793-steez4s972l.jpeg</v>
       </c>
       <c r="D37" t="str">
         <v>是</v>
@@ -2114,7 +2114,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>黑龙江漠河</v>
+        <v>陕西西安</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -2146,13 +2146,13 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B38" t="str">
         <v>弟弟</v>
       </c>
       <c r="C38" t="str">
-        <v>assets/1785854520974-96b8b1ekqd9.jpeg</v>
+        <v>assets/1785854319988-cohio08aod5.jpeg</v>
       </c>
       <c r="D38" t="str">
         <v>是</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>日本</v>
+        <v>黑龙江漠河</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -2193,13 +2193,13 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B39" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C39" t="str">
-        <v>assets/1785854664100-haqoiu1h7hj.jpeg</v>
+        <v>assets/1785854520974-96b8b1ekqd9.jpeg</v>
       </c>
       <c r="D39" t="str">
         <v>是</v>
@@ -2208,7 +2208,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>浙江杭州</v>
+        <v>日本</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -2246,7 +2246,7 @@
         <v>妹妹</v>
       </c>
       <c r="C40" t="str">
-        <v>assets/1785854690732-orrs40sx9rs.jpeg</v>
+        <v>assets/1785854664100-haqoiu1h7hj.jpeg</v>
       </c>
       <c r="D40" t="str">
         <v>是</v>
@@ -2255,7 +2255,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>贵州安顺</v>
+        <v>浙江杭州</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -2293,7 +2293,7 @@
         <v>妹妹</v>
       </c>
       <c r="C41" t="str">
-        <v>assets/1785854734122-wcpmib4m7.jpeg</v>
+        <v>assets/1785854690732-orrs40sx9rs.jpeg</v>
       </c>
       <c r="D41" t="str">
         <v>是</v>
@@ -2302,7 +2302,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>山东青岛</v>
+        <v>贵州安顺</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -2337,10 +2337,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B42" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C42" t="str">
-        <v>assets/1785854758707-1kxdkfvs6jc.jpeg</v>
+        <v>assets/1785854734122-wcpmib4m7.jpeg</v>
       </c>
       <c r="D42" t="str">
         <v>是</v>
@@ -2349,7 +2349,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>黑龙江漠河</v>
+        <v>山东青岛</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -2381,13 +2381,13 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>纯蓝色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B43" t="str">
         <v>弟弟</v>
       </c>
       <c r="C43" t="str">
-        <v>assets/1785854784780-3g0u60pdo93.jpeg</v>
+        <v>assets/1785854758707-1kxdkfvs6jc.jpeg</v>
       </c>
       <c r="D43" t="str">
         <v>是</v>
@@ -2396,7 +2396,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>河南鹤壁</v>
+        <v>黑龙江漠河</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2428,13 +2428,13 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>银虎斑</v>
+        <v>纯蓝色</v>
       </c>
       <c r="B44" t="str">
         <v>弟弟</v>
       </c>
       <c r="C44" t="str">
-        <v>assets/1785854813179-8oyxr0h2bbu.jpeg</v>
+        <v>assets/1785854784780-3g0u60pdo93.jpeg</v>
       </c>
       <c r="D44" t="str">
         <v>是</v>
@@ -2443,7 +2443,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>陕西西安</v>
+        <v>河南鹤壁</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2475,13 +2475,13 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B45" t="str">
         <v>弟弟</v>
       </c>
       <c r="C45" t="str">
-        <v>assets/1785854838933-uq6amircyzd.jpeg</v>
+        <v>assets/1785854813179-8oyxr0h2bbu.jpeg</v>
       </c>
       <c r="D45" t="str">
         <v>是</v>
@@ -2490,7 +2490,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>四川成都</v>
+        <v>陕西西安</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2522,22 +2522,22 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B46" t="str">
         <v>弟弟</v>
       </c>
       <c r="C46" t="str">
-        <v>assets/1785854869973-za3p6wikqpo.jpeg</v>
+        <v>assets/1785854838933-uq6amircyzd.jpeg</v>
       </c>
       <c r="D46" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E46" t="str">
-        <v>2026-05-18</v>
+        <v/>
       </c>
       <c r="F46" t="str">
-        <v/>
+        <v>四川成都</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2569,19 +2569,19 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B47" t="str">
         <v>弟弟</v>
       </c>
       <c r="C47" t="str">
-        <v>assets/1785854997023-mawkallt2a.jpeg</v>
+        <v>assets/1785854869973-za3p6wikqpo.jpeg</v>
       </c>
       <c r="D47" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E47" t="str">
-        <v/>
+        <v>2026-05-18</v>
       </c>
       <c r="F47" t="str">
         <v/>
@@ -2616,13 +2616,13 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>凯米尔色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B48" t="str">
         <v>弟弟</v>
       </c>
       <c r="C48" t="str">
-        <v>assets/1785855043327-wdc5pxwm34k.jpeg</v>
+        <v>assets/1785854997023-mawkallt2a.jpeg</v>
       </c>
       <c r="D48" t="str">
         <v>是</v>
@@ -2631,7 +2631,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>上海浦东</v>
+        <v/>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2663,22 +2663,22 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>棕虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B49" t="str">
         <v>弟弟</v>
       </c>
       <c r="C49" t="str">
-        <v>assets/1785912551260-jplefm937nk.jpeg, assets/videos/02.mp4</v>
+        <v>assets/1785855043327-wdc5pxwm34k.jpeg</v>
       </c>
       <c r="D49" t="str">
         <v>是</v>
       </c>
       <c r="E49" t="str">
-        <v>2026-06-06</v>
+        <v/>
       </c>
       <c r="F49" t="str">
-        <v>浙江温州</v>
+        <v>上海浦东</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2713,19 +2713,19 @@
         <v>棕虎斑</v>
       </c>
       <c r="B50" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C50" t="str">
-        <v>assets/1785912694000-m20f5kvvrr.jpeg</v>
+        <v>assets/1785912551260-jplefm937nk.jpeg, assets/videos/02.mp4</v>
       </c>
       <c r="D50" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E50" t="str">
         <v>2026-06-06</v>
       </c>
       <c r="F50" t="str">
-        <v/>
+        <v>浙江温州</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2752,12 +2752,59 @@
         <v/>
       </c>
       <c r="O50" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>棕虎斑</v>
+      </c>
+      <c r="B51" t="str">
+        <v>妹妹</v>
+      </c>
+      <c r="C51" t="str">
+        <v>assets/1785912694000-m20f5kvvrr.jpeg</v>
+      </c>
+      <c r="D51" t="str">
+        <v>否</v>
+      </c>
+      <c r="E51" t="str">
+        <v>2026-06-06</v>
+      </c>
+      <c r="F51" t="str">
+        <v/>
+      </c>
+      <c r="G51" t="str">
+        <v/>
+      </c>
+      <c r="H51" t="str">
+        <v/>
+      </c>
+      <c r="I51" t="str">
+        <v/>
+      </c>
+      <c r="J51" t="str">
+        <v/>
+      </c>
+      <c r="K51" t="str">
+        <v/>
+      </c>
+      <c r="L51" t="str">
+        <v/>
+      </c>
+      <c r="M51" t="str">
+        <v/>
+      </c>
+      <c r="N51" t="str">
+        <v/>
+      </c>
+      <c r="O51" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O51"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O51"/>
+  <dimension ref="A1:O57"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -454,19 +454,19 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>棕虎斑</v>
+        <v>阴影色NS12</v>
       </c>
       <c r="B2" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C2" t="str">
-        <v>assets/1787282819855-7vhx3m0v40.jpg</v>
+        <v>assets/1787283212708-jdnyi6ecci.jpg</v>
       </c>
       <c r="D2" t="str">
         <v>否</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-06-06</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -501,22 +501,22 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>棕虎斑</v>
+        <v>阴影色NS11</v>
       </c>
       <c r="B3" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C3" t="str">
-        <v>assets/1787282703381-2uakw592b4.jpg</v>
+        <v>assets/1787283153501-s2tjg9spwu.jpg</v>
       </c>
       <c r="D3" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E3" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>重庆</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -548,19 +548,19 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>烟灰色</v>
+        <v>浅烟灰色</v>
       </c>
       <c r="B4" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C4" t="str">
-        <v>assets/1787282649397-9hc31ncrpc.jpg</v>
+        <v>assets/1787283092677-i4d8tyrjtf.jpg</v>
       </c>
       <c r="D4" t="str">
         <v>否</v>
       </c>
       <c r="E4" t="str">
-        <v>2026-06-06</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -595,13 +595,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B5" t="str">
         <v>妹妹</v>
       </c>
       <c r="C5" t="str">
-        <v>assets/1787282617957-svcoyyznpg.jpg</v>
+        <v>assets/1787283031104-bpyq9wy2tl.jpg</v>
       </c>
       <c r="D5" t="str">
         <v>否</v>
@@ -642,13 +642,13 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B6" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C6" t="str">
-        <v>assets/1787282419632-78nixqjzua.jpg</v>
+        <v>assets/1787282991501-2fjfws0rqw.jpg</v>
       </c>
       <c r="D6" t="str">
         <v>否</v>
@@ -689,19 +689,19 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>纯黑色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B7" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C7" t="str">
-        <v>assets/1787282349942-2cfuyn7xlc.jpg</v>
+        <v>assets/1787282942262-syr48fym6c.jpg</v>
       </c>
       <c r="D7" t="str">
         <v>否</v>
       </c>
       <c r="E7" t="str">
-        <v>2026-03-21</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F7" t="str">
         <v/>
@@ -736,19 +736,19 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B8" t="str">
         <v>弟弟</v>
       </c>
       <c r="C8" t="str">
-        <v>assets/1787282064159-6b4z8c5msd.jpg</v>
+        <v>assets/1787282819855-7vhx3m0v40.jpg</v>
       </c>
       <c r="D8" t="str">
         <v>否</v>
       </c>
       <c r="E8" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -783,19 +783,19 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>阴影色NS11</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B9" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C9" t="str">
-        <v>assets/1787280590041-vzcwebdok1.jpg</v>
+        <v>assets/1787282703381-2uakw592b4.jpg</v>
       </c>
       <c r="D9" t="str">
         <v>否</v>
       </c>
       <c r="E9" t="str">
-        <v>2026-05-28</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -830,19 +830,19 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>浅色银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B10" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C10" t="str">
-        <v>assets/1787281786169-9ia0h837ct.jpg</v>
+        <v>assets/1787282649397-9hc31ncrpc.jpg</v>
       </c>
       <c r="D10" t="str">
         <v>否</v>
       </c>
       <c r="E10" t="str">
-        <v>2026-06-15</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -877,22 +877,22 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>浅烟灰色妹妹</v>
+        <v>烟灰色</v>
       </c>
       <c r="B11" t="str">
         <v>妹妹</v>
       </c>
       <c r="C11" t="str">
-        <v>assets/1785843720843-63qz159daui.jpg</v>
+        <v>assets/1787282617957-svcoyyznpg.jpg</v>
       </c>
       <c r="D11" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E11" t="str">
-        <v>2026-03-21</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F11" t="str">
-        <v>四川成都</v>
+        <v/>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -924,19 +924,19 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>红虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B12" t="str">
         <v>弟弟</v>
       </c>
       <c r="C12" t="str">
-        <v>assets/1785843763310-elg05ur61ri.jpg</v>
+        <v>assets/1787282419632-78nixqjzua.jpg</v>
       </c>
       <c r="D12" t="str">
         <v>否</v>
       </c>
       <c r="E12" t="str">
-        <v>2026-02-14</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -971,19 +971,19 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>银虎斑补丁</v>
+        <v>纯黑色</v>
       </c>
       <c r="B13" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C13" t="str">
-        <v>assets/1785843820715-9kz7gy4mbr7.jpg</v>
+        <v>assets/1787282349942-2cfuyn7xlc.jpg</v>
       </c>
       <c r="D13" t="str">
         <v>否</v>
       </c>
       <c r="E13" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F13" t="str">
         <v/>
@@ -1018,19 +1018,19 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>烟灰色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B14" t="str">
         <v>弟弟</v>
       </c>
       <c r="C14" t="str">
-        <v>assets/1785843953805-mxl3x1982io.jpg</v>
+        <v>assets/1787282064159-6b4z8c5msd.jpg</v>
       </c>
       <c r="D14" t="str">
         <v>否</v>
       </c>
       <c r="E14" t="str">
-        <v>2026-05-18</v>
+        <v>2026-06-10</v>
       </c>
       <c r="F14" t="str">
         <v/>
@@ -1065,19 +1065,19 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>棕虎斑玳瑁</v>
+        <v>阴影色NS11</v>
       </c>
       <c r="B15" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C15" t="str">
-        <v>assets/1785844013835-ek4xpcje7kh.jpg</v>
+        <v>assets/1787280590041-vzcwebdok1.jpg</v>
       </c>
       <c r="D15" t="str">
         <v>否</v>
       </c>
       <c r="E15" t="str">
-        <v>2026-02-14</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F15" t="str">
         <v/>
@@ -1112,19 +1112,19 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>银虎斑补丁</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B16" t="str">
         <v>妹妹</v>
       </c>
       <c r="C16" t="str">
-        <v>assets/1785844434338-ek5zbdgdcne.jpg</v>
+        <v>assets/1787281786169-9ia0h837ct.jpg</v>
       </c>
       <c r="D16" t="str">
         <v>否</v>
       </c>
       <c r="E16" t="str">
-        <v>2026-05-24</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F16" t="str">
         <v/>
@@ -1159,22 +1159,22 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>银虎斑</v>
+        <v>浅烟灰色妹妹</v>
       </c>
       <c r="B17" t="str">
         <v>妹妹</v>
       </c>
       <c r="C17" t="str">
-        <v>assets/1785838787730-s5f333sc3u.jpg</v>
+        <v>assets/1785843720843-63qz159daui.jpg</v>
       </c>
       <c r="D17" t="str">
         <v>是</v>
       </c>
       <c r="E17" t="str">
-        <v>2026-06-05</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F17" t="str">
-        <v>湖南恩施</v>
+        <v>四川成都</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1206,22 +1206,22 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B18" t="str">
         <v>弟弟</v>
       </c>
       <c r="C18" t="str">
-        <v>assets/1785842296661-6qw3zs3as8h.jpg</v>
+        <v>assets/1785843763310-elg05ur61ri.jpg</v>
       </c>
       <c r="D18" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E18" t="str">
-        <v>2026-06-05</v>
+        <v>2026-02-14</v>
       </c>
       <c r="F18" t="str">
-        <v>湖北恩施</v>
+        <v/>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1253,22 +1253,22 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>银虎斑</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B19" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C19" t="str">
-        <v>assets/1785842429109-porc98rel5.jpg</v>
+        <v>assets/1785843820715-9kz7gy4mbr7.jpg</v>
       </c>
       <c r="D19" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E19" t="str">
-        <v>2025-11-05</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F19" t="str">
-        <v>韩国</v>
+        <v/>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1300,13 +1300,13 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B20" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C20" t="str">
-        <v>assets/1785842594141-fcglbzjp509.jpg</v>
+        <v>assets/1785843953805-mxl3x1982io.jpg</v>
       </c>
       <c r="D20" t="str">
         <v>否</v>
@@ -1347,22 +1347,22 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>棕虎斑</v>
+        <v>棕虎斑玳瑁</v>
       </c>
       <c r="B21" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C21" t="str">
-        <v>assets/1785842639100-82k775dhwiv.jpg</v>
+        <v>assets/1785844013835-ek4xpcje7kh.jpg</v>
       </c>
       <c r="D21" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E21" t="str">
-        <v>2026-05-28</v>
+        <v>2026-02-14</v>
       </c>
       <c r="F21" t="str">
-        <v>四川自贡</v>
+        <v/>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1394,19 +1394,19 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B22" t="str">
         <v>妹妹</v>
       </c>
       <c r="C22" t="str">
-        <v>assets/1785842684502-mnhr0r96eee.jpg</v>
+        <v>assets/1785844434338-ek5zbdgdcne.jpg</v>
       </c>
       <c r="D22" t="str">
         <v>否</v>
       </c>
       <c r="E22" t="str">
-        <v>2026-06-06</v>
+        <v>2026-05-24</v>
       </c>
       <c r="F22" t="str">
         <v/>
@@ -1441,22 +1441,22 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>纯黑色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B23" t="str">
         <v>妹妹</v>
       </c>
       <c r="C23" t="str">
-        <v>assets/1785842779532-5u1j0igrw1s.jpg</v>
+        <v>assets/1785838787730-s5f333sc3u.jpg</v>
       </c>
       <c r="D23" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E23" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F23" t="str">
-        <v/>
+        <v>湖南恩施</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1491,19 +1491,19 @@
         <v>银虎斑</v>
       </c>
       <c r="B24" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C24" t="str">
-        <v>assets/1785842817046-6keqv4rw4yf.jpg</v>
+        <v>assets/1785842296661-6qw3zs3as8h.jpg</v>
       </c>
       <c r="D24" t="str">
         <v>是</v>
       </c>
       <c r="E24" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F24" t="str">
-        <v>韩国</v>
+        <v>湖北恩施</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>浅色银虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B25" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C25" t="str">
-        <v>assets/1785842950972-a88lbrskpc.jpg</v>
+        <v>assets/1785842429109-porc98rel5.jpg</v>
       </c>
       <c r="D25" t="str">
         <v>是</v>
       </c>
       <c r="E25" t="str">
-        <v>2026-06-05</v>
+        <v>2025-11-05</v>
       </c>
       <c r="F25" t="str">
-        <v>河边邢台</v>
+        <v>韩国</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1582,22 +1582,22 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B26" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C26" t="str">
-        <v>assets/1785843011477-n3l1wi6ech.jpg</v>
+        <v>assets/1785842594141-fcglbzjp509.jpg</v>
       </c>
       <c r="D26" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E26" t="str">
-        <v>2026-06-05</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F26" t="str">
-        <v>四川自贡</v>
+        <v/>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1629,22 +1629,22 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B27" t="str">
         <v>弟弟</v>
       </c>
       <c r="C27" t="str">
-        <v>assets/1785843237517-ga449iqess5.jpg</v>
+        <v>assets/1785842639100-82k775dhwiv.jpg</v>
       </c>
       <c r="D27" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E27" t="str">
-        <v>2026-03-05</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F27" t="str">
-        <v/>
+        <v>四川自贡</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1676,19 +1676,19 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>棕虎斑补丁</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B28" t="str">
         <v>妹妹</v>
       </c>
       <c r="C28" t="str">
-        <v>assets/1785842523893-7nwnnhwi4ns.jpg</v>
+        <v>assets/1785842684502-mnhr0r96eee.jpg</v>
       </c>
       <c r="D28" t="str">
         <v>否</v>
       </c>
       <c r="E28" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F28" t="str">
         <v/>
@@ -1723,19 +1723,19 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>蓝虎斑</v>
+        <v>纯黑色</v>
       </c>
       <c r="B29" t="str">
         <v>妹妹</v>
       </c>
       <c r="C29" t="str">
-        <v>assets/1785843497557-st27fk8drqi.jpg</v>
+        <v>assets/1785842779532-5u1j0igrw1s.jpg</v>
       </c>
       <c r="D29" t="str">
         <v>否</v>
       </c>
       <c r="E29" t="str">
-        <v>2026-04-05</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F29" t="str">
         <v/>
@@ -1776,16 +1776,16 @@
         <v>妹妹</v>
       </c>
       <c r="C30" t="str">
-        <v>assets/1785843621923-ylhakbtw13i.jpg</v>
+        <v>assets/1785842817046-6keqv4rw4yf.jpg</v>
       </c>
       <c r="D30" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E30" t="str">
         <v>2026-03-05</v>
       </c>
       <c r="F30" t="str">
-        <v/>
+        <v>韩国</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1817,22 +1817,22 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>银虎斑</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B31" t="str">
         <v>妹妹</v>
       </c>
       <c r="C31" t="str">
-        <v>assets/1785843663884-sfxvpmiet7.jpg</v>
+        <v>assets/1785842950972-a88lbrskpc.jpg</v>
       </c>
       <c r="D31" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E31" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F31" t="str">
-        <v/>
+        <v>河边邢台</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1864,69 +1864,69 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B32" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C32" t="str">
-        <v>assets/1785852601940-o236xtv7yx.jpeg</v>
+        <v>assets/1785843011477-n3l1wi6ech.jpg</v>
       </c>
       <c r="D32" t="str">
         <v>是</v>
       </c>
       <c r="E32" t="str">
-        <v>2026-02-20</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F32" t="str">
-        <v>荷兰</v>
+        <v>四川自贡</v>
       </c>
       <c r="G32" t="str">
-        <v>阿泽</v>
+        <v/>
       </c>
       <c r="H32" t="str">
-        <v>小辫子</v>
+        <v/>
       </c>
       <c r="I32" t="str">
-        <v>驺驺</v>
+        <v/>
       </c>
       <c r="J32" t="str">
-        <v>2026-07-02</v>
+        <v/>
       </c>
       <c r="K32" t="str">
-        <v>assets/diary/zouzou-depart.jpg</v>
+        <v/>
       </c>
       <c r="L32" t="str">
-        <v>2026-07-02</v>
+        <v/>
       </c>
       <c r="M32" t="str">
-        <v>2026-08-03</v>
+        <v/>
       </c>
       <c r="N32" t="str">
-        <v>2026-11-04</v>
+        <v/>
       </c>
       <c r="O32" t="str">
-        <v>2026-07-30 · 6.2斤 · 五个月10天了 · assets/feedback/zouzou-1.jpg</v>
+        <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>红虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B33" t="str">
         <v>弟弟</v>
       </c>
       <c r="C33" t="str">
-        <v>assets/1785853950207-cedor66ou2q.jpeg</v>
+        <v>assets/1785843237517-ga449iqess5.jpg</v>
       </c>
       <c r="D33" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E33" t="str">
-        <v/>
+        <v>2026-03-05</v>
       </c>
       <c r="F33" t="str">
-        <v>广东广州</v>
+        <v/>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1958,22 +1958,22 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>红虎斑</v>
+        <v>棕虎斑补丁</v>
       </c>
       <c r="B34" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C34" t="str">
-        <v>assets/1785854129383-c8qkvl537x.jpeg</v>
+        <v>assets/1785842523893-7nwnnhwi4ns.jpg</v>
       </c>
       <c r="D34" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E34" t="str">
-        <v/>
+        <v>2026-03-05</v>
       </c>
       <c r="F34" t="str">
-        <v>广东广州</v>
+        <v/>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -2005,22 +2005,22 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B35" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C35" t="str">
-        <v>assets/1785854166720-48r17hry9cd.jpeg</v>
+        <v>assets/1785843497557-st27fk8drqi.jpg</v>
       </c>
       <c r="D35" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E35" t="str">
-        <v/>
+        <v>2026-04-05</v>
       </c>
       <c r="F35" t="str">
-        <v>山西朔州</v>
+        <v/>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -2058,16 +2058,16 @@
         <v>妹妹</v>
       </c>
       <c r="C36" t="str">
-        <v>assets/1785854224521-2cpg6xipfn6.jpeg</v>
+        <v>assets/1785843621923-ylhakbtw13i.jpg</v>
       </c>
       <c r="D36" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E36" t="str">
-        <v/>
+        <v>2026-03-05</v>
       </c>
       <c r="F36" t="str">
-        <v>浙江宁波</v>
+        <v/>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -2102,19 +2102,19 @@
         <v>银虎斑</v>
       </c>
       <c r="B37" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C37" t="str">
-        <v>assets/1785854260793-steez4s972l.jpeg</v>
+        <v>assets/1785843663884-sfxvpmiet7.jpg</v>
       </c>
       <c r="D37" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E37" t="str">
-        <v/>
+        <v>2026-03-05</v>
       </c>
       <c r="F37" t="str">
-        <v>陕西西安</v>
+        <v/>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -2146,60 +2146,60 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B38" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C38" t="str">
-        <v>assets/1785854319988-cohio08aod5.jpeg</v>
+        <v>assets/1785852601940-o236xtv7yx.jpeg</v>
       </c>
       <c r="D38" t="str">
         <v>是</v>
       </c>
       <c r="E38" t="str">
-        <v/>
+        <v>2026-02-20</v>
       </c>
       <c r="F38" t="str">
-        <v>黑龙江漠河</v>
+        <v>荷兰</v>
       </c>
       <c r="G38" t="str">
-        <v/>
+        <v>阿泽</v>
       </c>
       <c r="H38" t="str">
-        <v/>
+        <v>小辫子</v>
       </c>
       <c r="I38" t="str">
-        <v/>
+        <v>驺驺</v>
       </c>
       <c r="J38" t="str">
-        <v/>
+        <v>2026-07-02</v>
       </c>
       <c r="K38" t="str">
-        <v/>
+        <v>assets/diary/zouzou-depart.jpg</v>
       </c>
       <c r="L38" t="str">
-        <v/>
+        <v>2026-07-02</v>
       </c>
       <c r="M38" t="str">
-        <v/>
+        <v>2026-08-03</v>
       </c>
       <c r="N38" t="str">
-        <v/>
+        <v>2026-11-04</v>
       </c>
       <c r="O38" t="str">
-        <v/>
+        <v>2026-07-30 · 6.2斤 · 五个月10天了 · assets/feedback/zouzou-1.jpg</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>棕虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B39" t="str">
         <v>弟弟</v>
       </c>
       <c r="C39" t="str">
-        <v>assets/1785854520974-96b8b1ekqd9.jpeg</v>
+        <v>assets/1785853950207-cedor66ou2q.jpeg</v>
       </c>
       <c r="D39" t="str">
         <v>是</v>
@@ -2208,7 +2208,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>日本</v>
+        <v>广东广州</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -2240,13 +2240,13 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B40" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C40" t="str">
-        <v>assets/1785854664100-haqoiu1h7hj.jpeg</v>
+        <v>assets/1785854129383-c8qkvl537x.jpeg</v>
       </c>
       <c r="D40" t="str">
         <v>是</v>
@@ -2255,7 +2255,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>浙江杭州</v>
+        <v>广东广州</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -2290,10 +2290,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B41" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C41" t="str">
-        <v>assets/1785854690732-orrs40sx9rs.jpeg</v>
+        <v>assets/1785854166720-48r17hry9cd.jpeg</v>
       </c>
       <c r="D41" t="str">
         <v>是</v>
@@ -2302,7 +2302,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>贵州安顺</v>
+        <v>山西朔州</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -2340,7 +2340,7 @@
         <v>妹妹</v>
       </c>
       <c r="C42" t="str">
-        <v>assets/1785854734122-wcpmib4m7.jpeg</v>
+        <v>assets/1785854224521-2cpg6xipfn6.jpeg</v>
       </c>
       <c r="D42" t="str">
         <v>是</v>
@@ -2349,7 +2349,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>山东青岛</v>
+        <v>浙江宁波</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -2387,7 +2387,7 @@
         <v>弟弟</v>
       </c>
       <c r="C43" t="str">
-        <v>assets/1785854758707-1kxdkfvs6jc.jpeg</v>
+        <v>assets/1785854260793-steez4s972l.jpeg</v>
       </c>
       <c r="D43" t="str">
         <v>是</v>
@@ -2396,7 +2396,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>黑龙江漠河</v>
+        <v>陕西西安</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2428,13 +2428,13 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>纯蓝色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B44" t="str">
         <v>弟弟</v>
       </c>
       <c r="C44" t="str">
-        <v>assets/1785854784780-3g0u60pdo93.jpeg</v>
+        <v>assets/1785854319988-cohio08aod5.jpeg</v>
       </c>
       <c r="D44" t="str">
         <v>是</v>
@@ -2443,7 +2443,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>河南鹤壁</v>
+        <v>黑龙江漠河</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2475,13 +2475,13 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B45" t="str">
         <v>弟弟</v>
       </c>
       <c r="C45" t="str">
-        <v>assets/1785854813179-8oyxr0h2bbu.jpeg</v>
+        <v>assets/1785854520974-96b8b1ekqd9.jpeg</v>
       </c>
       <c r="D45" t="str">
         <v>是</v>
@@ -2490,7 +2490,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>陕西西安</v>
+        <v>日本</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2522,13 +2522,13 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B46" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C46" t="str">
-        <v>assets/1785854838933-uq6amircyzd.jpeg</v>
+        <v>assets/1785854664100-haqoiu1h7hj.jpeg</v>
       </c>
       <c r="D46" t="str">
         <v>是</v>
@@ -2537,7 +2537,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>四川成都</v>
+        <v>浙江杭州</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>烟灰色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B47" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C47" t="str">
-        <v>assets/1785854869973-za3p6wikqpo.jpeg</v>
+        <v>assets/1785854690732-orrs40sx9rs.jpeg</v>
       </c>
       <c r="D47" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E47" t="str">
-        <v>2026-05-18</v>
+        <v/>
       </c>
       <c r="F47" t="str">
-        <v/>
+        <v>贵州安顺</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2619,10 +2619,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B48" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C48" t="str">
-        <v>assets/1785854997023-mawkallt2a.jpeg</v>
+        <v>assets/1785854734122-wcpmib4m7.jpeg</v>
       </c>
       <c r="D48" t="str">
         <v>是</v>
@@ -2631,7 +2631,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v/>
+        <v>山东青岛</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2663,13 +2663,13 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>凯米尔色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B49" t="str">
         <v>弟弟</v>
       </c>
       <c r="C49" t="str">
-        <v>assets/1785855043327-wdc5pxwm34k.jpeg</v>
+        <v>assets/1785854758707-1kxdkfvs6jc.jpeg</v>
       </c>
       <c r="D49" t="str">
         <v>是</v>
@@ -2678,7 +2678,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>上海浦东</v>
+        <v>黑龙江漠河</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2710,22 +2710,22 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>棕虎斑</v>
+        <v>纯蓝色</v>
       </c>
       <c r="B50" t="str">
         <v>弟弟</v>
       </c>
       <c r="C50" t="str">
-        <v>assets/1785912551260-jplefm937nk.jpeg, assets/videos/02.mp4</v>
+        <v>assets/1785854784780-3g0u60pdo93.jpeg</v>
       </c>
       <c r="D50" t="str">
         <v>是</v>
       </c>
       <c r="E50" t="str">
-        <v>2026-06-06</v>
+        <v/>
       </c>
       <c r="F50" t="str">
-        <v>浙江温州</v>
+        <v>河南鹤壁</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2757,54 +2757,336 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
+        <v>银虎斑</v>
+      </c>
+      <c r="B51" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C51" t="str">
+        <v>assets/1785854813179-8oyxr0h2bbu.jpeg</v>
+      </c>
+      <c r="D51" t="str">
+        <v>是</v>
+      </c>
+      <c r="E51" t="str">
+        <v/>
+      </c>
+      <c r="F51" t="str">
+        <v>陕西西安</v>
+      </c>
+      <c r="G51" t="str">
+        <v/>
+      </c>
+      <c r="H51" t="str">
+        <v/>
+      </c>
+      <c r="I51" t="str">
+        <v/>
+      </c>
+      <c r="J51" t="str">
+        <v/>
+      </c>
+      <c r="K51" t="str">
+        <v/>
+      </c>
+      <c r="L51" t="str">
+        <v/>
+      </c>
+      <c r="M51" t="str">
+        <v/>
+      </c>
+      <c r="N51" t="str">
+        <v/>
+      </c>
+      <c r="O51" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
         <v>棕虎斑</v>
       </c>
-      <c r="B51" t="str">
+      <c r="B52" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C52" t="str">
+        <v>assets/1785854838933-uq6amircyzd.jpeg</v>
+      </c>
+      <c r="D52" t="str">
+        <v>是</v>
+      </c>
+      <c r="E52" t="str">
+        <v/>
+      </c>
+      <c r="F52" t="str">
+        <v>四川成都</v>
+      </c>
+      <c r="G52" t="str">
+        <v/>
+      </c>
+      <c r="H52" t="str">
+        <v/>
+      </c>
+      <c r="I52" t="str">
+        <v/>
+      </c>
+      <c r="J52" t="str">
+        <v/>
+      </c>
+      <c r="K52" t="str">
+        <v/>
+      </c>
+      <c r="L52" t="str">
+        <v/>
+      </c>
+      <c r="M52" t="str">
+        <v/>
+      </c>
+      <c r="N52" t="str">
+        <v/>
+      </c>
+      <c r="O52" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>烟灰色</v>
+      </c>
+      <c r="B53" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C53" t="str">
+        <v>assets/1785854869973-za3p6wikqpo.jpeg</v>
+      </c>
+      <c r="D53" t="str">
+        <v>否</v>
+      </c>
+      <c r="E53" t="str">
+        <v>2026-05-18</v>
+      </c>
+      <c r="F53" t="str">
+        <v/>
+      </c>
+      <c r="G53" t="str">
+        <v/>
+      </c>
+      <c r="H53" t="str">
+        <v/>
+      </c>
+      <c r="I53" t="str">
+        <v/>
+      </c>
+      <c r="J53" t="str">
+        <v/>
+      </c>
+      <c r="K53" t="str">
+        <v/>
+      </c>
+      <c r="L53" t="str">
+        <v/>
+      </c>
+      <c r="M53" t="str">
+        <v/>
+      </c>
+      <c r="N53" t="str">
+        <v/>
+      </c>
+      <c r="O53" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>银虎斑</v>
+      </c>
+      <c r="B54" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C54" t="str">
+        <v>assets/1785854997023-mawkallt2a.jpeg</v>
+      </c>
+      <c r="D54" t="str">
+        <v>是</v>
+      </c>
+      <c r="E54" t="str">
+        <v/>
+      </c>
+      <c r="F54" t="str">
+        <v/>
+      </c>
+      <c r="G54" t="str">
+        <v/>
+      </c>
+      <c r="H54" t="str">
+        <v/>
+      </c>
+      <c r="I54" t="str">
+        <v/>
+      </c>
+      <c r="J54" t="str">
+        <v/>
+      </c>
+      <c r="K54" t="str">
+        <v/>
+      </c>
+      <c r="L54" t="str">
+        <v/>
+      </c>
+      <c r="M54" t="str">
+        <v/>
+      </c>
+      <c r="N54" t="str">
+        <v/>
+      </c>
+      <c r="O54" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>凯米尔色</v>
+      </c>
+      <c r="B55" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C55" t="str">
+        <v>assets/1785855043327-wdc5pxwm34k.jpeg</v>
+      </c>
+      <c r="D55" t="str">
+        <v>是</v>
+      </c>
+      <c r="E55" t="str">
+        <v/>
+      </c>
+      <c r="F55" t="str">
+        <v>上海浦东</v>
+      </c>
+      <c r="G55" t="str">
+        <v/>
+      </c>
+      <c r="H55" t="str">
+        <v/>
+      </c>
+      <c r="I55" t="str">
+        <v/>
+      </c>
+      <c r="J55" t="str">
+        <v/>
+      </c>
+      <c r="K55" t="str">
+        <v/>
+      </c>
+      <c r="L55" t="str">
+        <v/>
+      </c>
+      <c r="M55" t="str">
+        <v/>
+      </c>
+      <c r="N55" t="str">
+        <v/>
+      </c>
+      <c r="O55" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>棕虎斑</v>
+      </c>
+      <c r="B56" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C56" t="str">
+        <v>assets/1785912551260-jplefm937nk.jpeg, assets/videos/02.mp4</v>
+      </c>
+      <c r="D56" t="str">
+        <v>是</v>
+      </c>
+      <c r="E56" t="str">
+        <v>2026-06-06</v>
+      </c>
+      <c r="F56" t="str">
+        <v>浙江温州</v>
+      </c>
+      <c r="G56" t="str">
+        <v/>
+      </c>
+      <c r="H56" t="str">
+        <v/>
+      </c>
+      <c r="I56" t="str">
+        <v/>
+      </c>
+      <c r="J56" t="str">
+        <v/>
+      </c>
+      <c r="K56" t="str">
+        <v/>
+      </c>
+      <c r="L56" t="str">
+        <v/>
+      </c>
+      <c r="M56" t="str">
+        <v/>
+      </c>
+      <c r="N56" t="str">
+        <v/>
+      </c>
+      <c r="O56" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>棕虎斑</v>
+      </c>
+      <c r="B57" t="str">
         <v>妹妹</v>
       </c>
-      <c r="C51" t="str">
+      <c r="C57" t="str">
         <v>assets/1785912694000-m20f5kvvrr.jpeg</v>
       </c>
-      <c r="D51" t="str">
+      <c r="D57" t="str">
         <v>否</v>
       </c>
-      <c r="E51" t="str">
+      <c r="E57" t="str">
         <v>2026-06-06</v>
       </c>
-      <c r="F51" t="str">
-        <v/>
-      </c>
-      <c r="G51" t="str">
-        <v/>
-      </c>
-      <c r="H51" t="str">
-        <v/>
-      </c>
-      <c r="I51" t="str">
-        <v/>
-      </c>
-      <c r="J51" t="str">
-        <v/>
-      </c>
-      <c r="K51" t="str">
-        <v/>
-      </c>
-      <c r="L51" t="str">
-        <v/>
-      </c>
-      <c r="M51" t="str">
-        <v/>
-      </c>
-      <c r="N51" t="str">
-        <v/>
-      </c>
-      <c r="O51" t="str">
+      <c r="F57" t="str">
+        <v/>
+      </c>
+      <c r="G57" t="str">
+        <v/>
+      </c>
+      <c r="H57" t="str">
+        <v/>
+      </c>
+      <c r="I57" t="str">
+        <v/>
+      </c>
+      <c r="J57" t="str">
+        <v/>
+      </c>
+      <c r="K57" t="str">
+        <v/>
+      </c>
+      <c r="L57" t="str">
+        <v/>
+      </c>
+      <c r="M57" t="str">
+        <v/>
+      </c>
+      <c r="N57" t="str">
+        <v/>
+      </c>
+      <c r="O57" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O51"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O57"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O57"/>
+  <dimension ref="A1:O58"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -454,19 +454,19 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>阴影色NS12</v>
+        <v>纯黑色</v>
       </c>
       <c r="B2" t="str">
         <v>妹妹</v>
       </c>
       <c r="C2" t="str">
-        <v>assets/1787283212708-jdnyi6ecci.jpg</v>
+        <v>assets/1787283819124-4v7d1w01la.jpg</v>
       </c>
       <c r="D2" t="str">
         <v>否</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-05-28</v>
+        <v>2026-02-20</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -501,22 +501,22 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>阴影色NS11</v>
+        <v>阴影色NS12</v>
       </c>
       <c r="B3" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C3" t="str">
-        <v>assets/1787283153501-s2tjg9spwu.jpg</v>
+        <v>assets/1787283212708-jdnyi6ecci.jpg</v>
       </c>
       <c r="D3" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E3" t="str">
-        <v>2026-06-15</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F3" t="str">
-        <v>重庆</v>
+        <v/>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -548,22 +548,22 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>浅烟灰色</v>
+        <v>阴影色NS11</v>
       </c>
       <c r="B4" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C4" t="str">
-        <v>assets/1787283092677-i4d8tyrjtf.jpg</v>
+        <v>assets/1787283153501-s2tjg9spwu.jpg</v>
       </c>
       <c r="D4" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E4" t="str">
-        <v>2026-03-21</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F4" t="str">
-        <v/>
+        <v>重庆</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -595,19 +595,19 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>棕虎斑</v>
+        <v>浅烟灰色</v>
       </c>
       <c r="B5" t="str">
         <v>妹妹</v>
       </c>
       <c r="C5" t="str">
-        <v>assets/1787283031104-bpyq9wy2tl.jpg</v>
+        <v>assets/1787283092677-i4d8tyrjtf.jpg</v>
       </c>
       <c r="D5" t="str">
         <v>否</v>
       </c>
       <c r="E5" t="str">
-        <v>2026-06-06</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -648,7 +648,7 @@
         <v>妹妹</v>
       </c>
       <c r="C6" t="str">
-        <v>assets/1787282991501-2fjfws0rqw.jpg</v>
+        <v>assets/1787283031104-bpyq9wy2tl.jpg</v>
       </c>
       <c r="D6" t="str">
         <v>否</v>
@@ -695,13 +695,13 @@
         <v>妹妹</v>
       </c>
       <c r="C7" t="str">
-        <v>assets/1787282942262-syr48fym6c.jpg</v>
+        <v>assets/1787282991501-2fjfws0rqw.jpg</v>
       </c>
       <c r="D7" t="str">
         <v>否</v>
       </c>
       <c r="E7" t="str">
-        <v>2026-06-15</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F7" t="str">
         <v/>
@@ -739,16 +739,16 @@
         <v>棕虎斑</v>
       </c>
       <c r="B8" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C8" t="str">
-        <v>assets/1787282819855-7vhx3m0v40.jpg</v>
+        <v>assets/1787282942262-syr48fym6c.jpg</v>
       </c>
       <c r="D8" t="str">
         <v>否</v>
       </c>
       <c r="E8" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -786,10 +786,10 @@
         <v>棕虎斑</v>
       </c>
       <c r="B9" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C9" t="str">
-        <v>assets/1787282703381-2uakw592b4.jpg</v>
+        <v>assets/1787282819855-7vhx3m0v40.jpg</v>
       </c>
       <c r="D9" t="str">
         <v>否</v>
@@ -830,13 +830,13 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B10" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C10" t="str">
-        <v>assets/1787282649397-9hc31ncrpc.jpg</v>
+        <v>assets/1787282703381-2uakw592b4.jpg</v>
       </c>
       <c r="D10" t="str">
         <v>否</v>
@@ -880,10 +880,10 @@
         <v>烟灰色</v>
       </c>
       <c r="B11" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C11" t="str">
-        <v>assets/1787282617957-svcoyyznpg.jpg</v>
+        <v>assets/1787282649397-9hc31ncrpc.jpg</v>
       </c>
       <c r="D11" t="str">
         <v>否</v>
@@ -927,10 +927,10 @@
         <v>烟灰色</v>
       </c>
       <c r="B12" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C12" t="str">
-        <v>assets/1787282419632-78nixqjzua.jpg</v>
+        <v>assets/1787282617957-svcoyyznpg.jpg</v>
       </c>
       <c r="D12" t="str">
         <v>否</v>
@@ -971,19 +971,19 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>纯黑色</v>
+        <v>烟灰色</v>
       </c>
       <c r="B13" t="str">
         <v>弟弟</v>
       </c>
       <c r="C13" t="str">
-        <v>assets/1787282349942-2cfuyn7xlc.jpg</v>
+        <v>assets/1787282419632-78nixqjzua.jpg</v>
       </c>
       <c r="D13" t="str">
         <v>否</v>
       </c>
       <c r="E13" t="str">
-        <v>2026-03-21</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F13" t="str">
         <v/>
@@ -1018,19 +1018,19 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>银虎斑</v>
+        <v>纯黑色</v>
       </c>
       <c r="B14" t="str">
         <v>弟弟</v>
       </c>
       <c r="C14" t="str">
-        <v>assets/1787282064159-6b4z8c5msd.jpg</v>
+        <v>assets/1787282349942-2cfuyn7xlc.jpg</v>
       </c>
       <c r="D14" t="str">
         <v>否</v>
       </c>
       <c r="E14" t="str">
-        <v>2026-06-10</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F14" t="str">
         <v/>
@@ -1065,19 +1065,19 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>阴影色NS11</v>
+        <v>银虎斑</v>
       </c>
       <c r="B15" t="str">
         <v>弟弟</v>
       </c>
       <c r="C15" t="str">
-        <v>assets/1787280590041-vzcwebdok1.jpg</v>
+        <v>assets/1787282064159-6b4z8c5msd.jpg</v>
       </c>
       <c r="D15" t="str">
         <v>否</v>
       </c>
       <c r="E15" t="str">
-        <v>2026-05-28</v>
+        <v>2026-06-10</v>
       </c>
       <c r="F15" t="str">
         <v/>
@@ -1112,19 +1112,19 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>浅色银虎斑</v>
+        <v>阴影色NS11</v>
       </c>
       <c r="B16" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C16" t="str">
-        <v>assets/1787281786169-9ia0h837ct.jpg</v>
+        <v>assets/1787280590041-vzcwebdok1.jpg</v>
       </c>
       <c r="D16" t="str">
         <v>否</v>
       </c>
       <c r="E16" t="str">
-        <v>2026-06-15</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F16" t="str">
         <v/>
@@ -1159,22 +1159,22 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>浅烟灰色妹妹</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B17" t="str">
         <v>妹妹</v>
       </c>
       <c r="C17" t="str">
-        <v>assets/1785843720843-63qz159daui.jpg</v>
+        <v>assets/1787281786169-9ia0h837ct.jpg</v>
       </c>
       <c r="D17" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E17" t="str">
-        <v>2026-03-21</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F17" t="str">
-        <v>四川成都</v>
+        <v/>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1206,22 +1206,22 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>红虎斑</v>
+        <v>浅烟灰色妹妹</v>
       </c>
       <c r="B18" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C18" t="str">
-        <v>assets/1785843763310-elg05ur61ri.jpg</v>
+        <v>assets/1785843720843-63qz159daui.jpg</v>
       </c>
       <c r="D18" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E18" t="str">
-        <v>2026-02-14</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F18" t="str">
-        <v/>
+        <v>四川成都</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1253,19 +1253,19 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>银虎斑补丁</v>
+        <v>红虎斑</v>
       </c>
       <c r="B19" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C19" t="str">
-        <v>assets/1785843820715-9kz7gy4mbr7.jpg</v>
+        <v>assets/1785843763310-elg05ur61ri.jpg</v>
       </c>
       <c r="D19" t="str">
         <v>否</v>
       </c>
       <c r="E19" t="str">
-        <v>2026-03-05</v>
+        <v>2026-02-14</v>
       </c>
       <c r="F19" t="str">
         <v/>
@@ -1300,19 +1300,19 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>烟灰色</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B20" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C20" t="str">
-        <v>assets/1785843953805-mxl3x1982io.jpg</v>
+        <v>assets/1785843820715-9kz7gy4mbr7.jpg</v>
       </c>
       <c r="D20" t="str">
         <v>否</v>
       </c>
       <c r="E20" t="str">
-        <v>2026-05-18</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F20" t="str">
         <v/>
@@ -1347,19 +1347,19 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>棕虎斑玳瑁</v>
+        <v>烟灰色</v>
       </c>
       <c r="B21" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C21" t="str">
-        <v>assets/1785844013835-ek4xpcje7kh.jpg</v>
+        <v>assets/1785843953805-mxl3x1982io.jpg</v>
       </c>
       <c r="D21" t="str">
         <v>否</v>
       </c>
       <c r="E21" t="str">
-        <v>2026-02-14</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F21" t="str">
         <v/>
@@ -1394,19 +1394,19 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>银虎斑补丁</v>
+        <v>棕虎斑玳瑁</v>
       </c>
       <c r="B22" t="str">
         <v>妹妹</v>
       </c>
       <c r="C22" t="str">
-        <v>assets/1785844434338-ek5zbdgdcne.jpg</v>
+        <v>assets/1785844013835-ek4xpcje7kh.jpg</v>
       </c>
       <c r="D22" t="str">
         <v>否</v>
       </c>
       <c r="E22" t="str">
-        <v>2026-05-24</v>
+        <v>2026-02-14</v>
       </c>
       <c r="F22" t="str">
         <v/>
@@ -1441,22 +1441,22 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>银虎斑</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B23" t="str">
         <v>妹妹</v>
       </c>
       <c r="C23" t="str">
-        <v>assets/1785838787730-s5f333sc3u.jpg</v>
+        <v>assets/1785844434338-ek5zbdgdcne.jpg</v>
       </c>
       <c r="D23" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E23" t="str">
-        <v>2026-06-05</v>
+        <v>2026-05-24</v>
       </c>
       <c r="F23" t="str">
-        <v>湖南恩施</v>
+        <v/>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1491,10 +1491,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B24" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C24" t="str">
-        <v>assets/1785842296661-6qw3zs3as8h.jpg</v>
+        <v>assets/1785838787730-s5f333sc3u.jpg</v>
       </c>
       <c r="D24" t="str">
         <v>是</v>
@@ -1503,7 +1503,7 @@
         <v>2026-06-05</v>
       </c>
       <c r="F24" t="str">
-        <v>湖北恩施</v>
+        <v>湖南恩施</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1541,16 +1541,16 @@
         <v>弟弟</v>
       </c>
       <c r="C25" t="str">
-        <v>assets/1785842429109-porc98rel5.jpg</v>
+        <v>assets/1785842296661-6qw3zs3as8h.jpg</v>
       </c>
       <c r="D25" t="str">
         <v>是</v>
       </c>
       <c r="E25" t="str">
-        <v>2025-11-05</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F25" t="str">
-        <v>韩国</v>
+        <v>湖北恩施</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1585,19 +1585,19 @@
         <v>银虎斑</v>
       </c>
       <c r="B26" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C26" t="str">
-        <v>assets/1785842594141-fcglbzjp509.jpg</v>
+        <v>assets/1785842429109-porc98rel5.jpg</v>
       </c>
       <c r="D26" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E26" t="str">
-        <v>2026-05-18</v>
+        <v>2025-11-05</v>
       </c>
       <c r="F26" t="str">
-        <v/>
+        <v>韩国</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1629,22 +1629,22 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B27" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C27" t="str">
-        <v>assets/1785842639100-82k775dhwiv.jpg</v>
+        <v>assets/1785842594141-fcglbzjp509.jpg</v>
       </c>
       <c r="D27" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E27" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F27" t="str">
-        <v>四川自贡</v>
+        <v/>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1679,19 +1679,19 @@
         <v>棕虎斑</v>
       </c>
       <c r="B28" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C28" t="str">
-        <v>assets/1785842684502-mnhr0r96eee.jpg</v>
+        <v>assets/1785842639100-82k775dhwiv.jpg</v>
       </c>
       <c r="D28" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E28" t="str">
-        <v>2026-06-06</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F28" t="str">
-        <v/>
+        <v>四川自贡</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1723,19 +1723,19 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>纯黑色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B29" t="str">
         <v>妹妹</v>
       </c>
       <c r="C29" t="str">
-        <v>assets/1785842779532-5u1j0igrw1s.jpg</v>
+        <v>assets/1785842684502-mnhr0r96eee.jpg</v>
       </c>
       <c r="D29" t="str">
         <v>否</v>
       </c>
       <c r="E29" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F29" t="str">
         <v/>
@@ -1770,22 +1770,22 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>银虎斑</v>
+        <v>纯黑色</v>
       </c>
       <c r="B30" t="str">
         <v>妹妹</v>
       </c>
       <c r="C30" t="str">
-        <v>assets/1785842817046-6keqv4rw4yf.jpg</v>
+        <v>assets/1785842779532-5u1j0igrw1s.jpg</v>
       </c>
       <c r="D30" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E30" t="str">
         <v>2026-03-05</v>
       </c>
       <c r="F30" t="str">
-        <v>韩国</v>
+        <v/>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1817,22 +1817,22 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>浅色银虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B31" t="str">
         <v>妹妹</v>
       </c>
       <c r="C31" t="str">
-        <v>assets/1785842950972-a88lbrskpc.jpg</v>
+        <v>assets/1785842817046-6keqv4rw4yf.jpg</v>
       </c>
       <c r="D31" t="str">
         <v>是</v>
       </c>
       <c r="E31" t="str">
-        <v>2026-06-05</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F31" t="str">
-        <v>河边邢台</v>
+        <v>韩国</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1864,13 +1864,13 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>棕虎斑</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B32" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C32" t="str">
-        <v>assets/1785843011477-n3l1wi6ech.jpg</v>
+        <v>assets/1785842950972-a88lbrskpc.jpg</v>
       </c>
       <c r="D32" t="str">
         <v>是</v>
@@ -1879,7 +1879,7 @@
         <v>2026-06-05</v>
       </c>
       <c r="F32" t="str">
-        <v>四川自贡</v>
+        <v>河边邢台</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1911,22 +1911,22 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B33" t="str">
         <v>弟弟</v>
       </c>
       <c r="C33" t="str">
-        <v>assets/1785843237517-ga449iqess5.jpg</v>
+        <v>assets/1785843011477-n3l1wi6ech.jpg</v>
       </c>
       <c r="D33" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E33" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F33" t="str">
-        <v/>
+        <v>四川自贡</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1958,13 +1958,13 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>棕虎斑补丁</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B34" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C34" t="str">
-        <v>assets/1785842523893-7nwnnhwi4ns.jpg</v>
+        <v>assets/1785843237517-ga449iqess5.jpg</v>
       </c>
       <c r="D34" t="str">
         <v>否</v>
@@ -2005,19 +2005,19 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎斑补丁</v>
       </c>
       <c r="B35" t="str">
         <v>妹妹</v>
       </c>
       <c r="C35" t="str">
-        <v>assets/1785843497557-st27fk8drqi.jpg</v>
+        <v>assets/1785842523893-7nwnnhwi4ns.jpg</v>
       </c>
       <c r="D35" t="str">
         <v>否</v>
       </c>
       <c r="E35" t="str">
-        <v>2026-04-05</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F35" t="str">
         <v/>
@@ -2052,19 +2052,19 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B36" t="str">
         <v>妹妹</v>
       </c>
       <c r="C36" t="str">
-        <v>assets/1785843621923-ylhakbtw13i.jpg</v>
+        <v>assets/1785843497557-st27fk8drqi.jpg</v>
       </c>
       <c r="D36" t="str">
         <v>否</v>
       </c>
       <c r="E36" t="str">
-        <v>2026-03-05</v>
+        <v>2026-04-05</v>
       </c>
       <c r="F36" t="str">
         <v/>
@@ -2105,7 +2105,7 @@
         <v>妹妹</v>
       </c>
       <c r="C37" t="str">
-        <v>assets/1785843663884-sfxvpmiet7.jpg</v>
+        <v>assets/1785843621923-ylhakbtw13i.jpg</v>
       </c>
       <c r="D37" t="str">
         <v>否</v>
@@ -2146,96 +2146,96 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>蓝虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B38" t="str">
         <v>妹妹</v>
       </c>
       <c r="C38" t="str">
-        <v>assets/1785852601940-o236xtv7yx.jpeg</v>
+        <v>assets/1785843663884-sfxvpmiet7.jpg</v>
       </c>
       <c r="D38" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E38" t="str">
-        <v>2026-02-20</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F38" t="str">
-        <v>荷兰</v>
+        <v/>
       </c>
       <c r="G38" t="str">
-        <v>阿泽</v>
+        <v/>
       </c>
       <c r="H38" t="str">
-        <v>小辫子</v>
+        <v/>
       </c>
       <c r="I38" t="str">
-        <v>驺驺</v>
+        <v/>
       </c>
       <c r="J38" t="str">
-        <v>2026-07-02</v>
+        <v/>
       </c>
       <c r="K38" t="str">
-        <v>assets/diary/zouzou-depart.jpg</v>
+        <v/>
       </c>
       <c r="L38" t="str">
-        <v>2026-07-02</v>
+        <v/>
       </c>
       <c r="M38" t="str">
-        <v>2026-08-03</v>
+        <v/>
       </c>
       <c r="N38" t="str">
-        <v>2026-11-04</v>
+        <v/>
       </c>
       <c r="O38" t="str">
-        <v>2026-07-30 · 6.2斤 · 五个月10天了 · assets/feedback/zouzou-1.jpg</v>
+        <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>红虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B39" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C39" t="str">
-        <v>assets/1785853950207-cedor66ou2q.jpeg</v>
+        <v>assets/1785852601940-o236xtv7yx.jpeg</v>
       </c>
       <c r="D39" t="str">
         <v>是</v>
       </c>
       <c r="E39" t="str">
-        <v/>
+        <v>2026-02-20</v>
       </c>
       <c r="F39" t="str">
-        <v>广东广州</v>
+        <v>荷兰</v>
       </c>
       <c r="G39" t="str">
-        <v/>
+        <v>阿泽</v>
       </c>
       <c r="H39" t="str">
-        <v/>
+        <v>小辫子</v>
       </c>
       <c r="I39" t="str">
-        <v/>
+        <v>驺驺</v>
       </c>
       <c r="J39" t="str">
-        <v/>
+        <v>2026-07-02</v>
       </c>
       <c r="K39" t="str">
-        <v/>
+        <v>assets/diary/zouzou-depart.jpg</v>
       </c>
       <c r="L39" t="str">
-        <v/>
+        <v>2026-07-02</v>
       </c>
       <c r="M39" t="str">
-        <v/>
+        <v>2026-08-03</v>
       </c>
       <c r="N39" t="str">
-        <v/>
+        <v>2026-11-04</v>
       </c>
       <c r="O39" t="str">
-        <v/>
+        <v>2026-07-30 · 6.2斤 · 五个月10天了 · assets/feedback/zouzou-1.jpg</v>
       </c>
     </row>
     <row r="40">
@@ -2246,7 +2246,7 @@
         <v>弟弟</v>
       </c>
       <c r="C40" t="str">
-        <v>assets/1785854129383-c8qkvl537x.jpeg</v>
+        <v>assets/1785853950207-cedor66ou2q.jpeg</v>
       </c>
       <c r="D40" t="str">
         <v>是</v>
@@ -2287,13 +2287,13 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B41" t="str">
         <v>弟弟</v>
       </c>
       <c r="C41" t="str">
-        <v>assets/1785854166720-48r17hry9cd.jpeg</v>
+        <v>assets/1785854129383-c8qkvl537x.jpeg</v>
       </c>
       <c r="D41" t="str">
         <v>是</v>
@@ -2302,7 +2302,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>山西朔州</v>
+        <v>广东广州</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -2337,10 +2337,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B42" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C42" t="str">
-        <v>assets/1785854224521-2cpg6xipfn6.jpeg</v>
+        <v>assets/1785854166720-48r17hry9cd.jpeg</v>
       </c>
       <c r="D42" t="str">
         <v>是</v>
@@ -2349,7 +2349,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>浙江宁波</v>
+        <v>山西朔州</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -2384,10 +2384,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B43" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C43" t="str">
-        <v>assets/1785854260793-steez4s972l.jpeg</v>
+        <v>assets/1785854224521-2cpg6xipfn6.jpeg</v>
       </c>
       <c r="D43" t="str">
         <v>是</v>
@@ -2396,7 +2396,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>陕西西安</v>
+        <v>浙江宁波</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2434,7 +2434,7 @@
         <v>弟弟</v>
       </c>
       <c r="C44" t="str">
-        <v>assets/1785854319988-cohio08aod5.jpeg</v>
+        <v>assets/1785854260793-steez4s972l.jpeg</v>
       </c>
       <c r="D44" t="str">
         <v>是</v>
@@ -2443,7 +2443,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>黑龙江漠河</v>
+        <v>陕西西安</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2475,13 +2475,13 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B45" t="str">
         <v>弟弟</v>
       </c>
       <c r="C45" t="str">
-        <v>assets/1785854520974-96b8b1ekqd9.jpeg</v>
+        <v>assets/1785854319988-cohio08aod5.jpeg</v>
       </c>
       <c r="D45" t="str">
         <v>是</v>
@@ -2490,7 +2490,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>日本</v>
+        <v>黑龙江漠河</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2522,13 +2522,13 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B46" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C46" t="str">
-        <v>assets/1785854664100-haqoiu1h7hj.jpeg</v>
+        <v>assets/1785854520974-96b8b1ekqd9.jpeg</v>
       </c>
       <c r="D46" t="str">
         <v>是</v>
@@ -2537,7 +2537,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>浙江杭州</v>
+        <v>日本</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2575,7 +2575,7 @@
         <v>妹妹</v>
       </c>
       <c r="C47" t="str">
-        <v>assets/1785854690732-orrs40sx9rs.jpeg</v>
+        <v>assets/1785854664100-haqoiu1h7hj.jpeg</v>
       </c>
       <c r="D47" t="str">
         <v>是</v>
@@ -2584,7 +2584,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>贵州安顺</v>
+        <v>浙江杭州</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2622,7 +2622,7 @@
         <v>妹妹</v>
       </c>
       <c r="C48" t="str">
-        <v>assets/1785854734122-wcpmib4m7.jpeg</v>
+        <v>assets/1785854690732-orrs40sx9rs.jpeg</v>
       </c>
       <c r="D48" t="str">
         <v>是</v>
@@ -2631,7 +2631,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>山东青岛</v>
+        <v>贵州安顺</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2666,10 +2666,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B49" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C49" t="str">
-        <v>assets/1785854758707-1kxdkfvs6jc.jpeg</v>
+        <v>assets/1785854734122-wcpmib4m7.jpeg</v>
       </c>
       <c r="D49" t="str">
         <v>是</v>
@@ -2678,7 +2678,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>黑龙江漠河</v>
+        <v>山东青岛</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2710,13 +2710,13 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>纯蓝色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B50" t="str">
         <v>弟弟</v>
       </c>
       <c r="C50" t="str">
-        <v>assets/1785854784780-3g0u60pdo93.jpeg</v>
+        <v>assets/1785854758707-1kxdkfvs6jc.jpeg</v>
       </c>
       <c r="D50" t="str">
         <v>是</v>
@@ -2725,7 +2725,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>河南鹤壁</v>
+        <v>黑龙江漠河</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2757,13 +2757,13 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>银虎斑</v>
+        <v>纯蓝色</v>
       </c>
       <c r="B51" t="str">
         <v>弟弟</v>
       </c>
       <c r="C51" t="str">
-        <v>assets/1785854813179-8oyxr0h2bbu.jpeg</v>
+        <v>assets/1785854784780-3g0u60pdo93.jpeg</v>
       </c>
       <c r="D51" t="str">
         <v>是</v>
@@ -2772,7 +2772,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>陕西西安</v>
+        <v>河南鹤壁</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2804,13 +2804,13 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B52" t="str">
         <v>弟弟</v>
       </c>
       <c r="C52" t="str">
-        <v>assets/1785854838933-uq6amircyzd.jpeg</v>
+        <v>assets/1785854813179-8oyxr0h2bbu.jpeg</v>
       </c>
       <c r="D52" t="str">
         <v>是</v>
@@ -2819,7 +2819,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>四川成都</v>
+        <v>陕西西安</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2851,22 +2851,22 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B53" t="str">
         <v>弟弟</v>
       </c>
       <c r="C53" t="str">
-        <v>assets/1785854869973-za3p6wikqpo.jpeg</v>
+        <v>assets/1785854838933-uq6amircyzd.jpeg</v>
       </c>
       <c r="D53" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E53" t="str">
-        <v>2026-05-18</v>
+        <v/>
       </c>
       <c r="F53" t="str">
-        <v/>
+        <v>四川成都</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2898,19 +2898,19 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B54" t="str">
         <v>弟弟</v>
       </c>
       <c r="C54" t="str">
-        <v>assets/1785854997023-mawkallt2a.jpeg</v>
+        <v>assets/1785854869973-za3p6wikqpo.jpeg</v>
       </c>
       <c r="D54" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E54" t="str">
-        <v/>
+        <v>2026-05-18</v>
       </c>
       <c r="F54" t="str">
         <v/>
@@ -2945,13 +2945,13 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>凯米尔色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B55" t="str">
         <v>弟弟</v>
       </c>
       <c r="C55" t="str">
-        <v>assets/1785855043327-wdc5pxwm34k.jpeg</v>
+        <v>assets/1785854997023-mawkallt2a.jpeg</v>
       </c>
       <c r="D55" t="str">
         <v>是</v>
@@ -2960,7 +2960,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>上海浦东</v>
+        <v/>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2992,22 +2992,22 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>棕虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B56" t="str">
         <v>弟弟</v>
       </c>
       <c r="C56" t="str">
-        <v>assets/1785912551260-jplefm937nk.jpeg, assets/videos/02.mp4</v>
+        <v>assets/1785855043327-wdc5pxwm34k.jpeg</v>
       </c>
       <c r="D56" t="str">
         <v>是</v>
       </c>
       <c r="E56" t="str">
-        <v>2026-06-06</v>
+        <v/>
       </c>
       <c r="F56" t="str">
-        <v>浙江温州</v>
+        <v>上海浦东</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -3042,19 +3042,19 @@
         <v>棕虎斑</v>
       </c>
       <c r="B57" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C57" t="str">
-        <v>assets/1785912694000-m20f5kvvrr.jpeg</v>
+        <v>assets/1785912551260-jplefm937nk.jpeg, assets/videos/02.mp4</v>
       </c>
       <c r="D57" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E57" t="str">
         <v>2026-06-06</v>
       </c>
       <c r="F57" t="str">
-        <v/>
+        <v>浙江温州</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -3081,12 +3081,59 @@
         <v/>
       </c>
       <c r="O57" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>棕虎斑</v>
+      </c>
+      <c r="B58" t="str">
+        <v>妹妹</v>
+      </c>
+      <c r="C58" t="str">
+        <v>assets/1785912694000-m20f5kvvrr.jpeg</v>
+      </c>
+      <c r="D58" t="str">
+        <v>否</v>
+      </c>
+      <c r="E58" t="str">
+        <v>2026-06-06</v>
+      </c>
+      <c r="F58" t="str">
+        <v/>
+      </c>
+      <c r="G58" t="str">
+        <v/>
+      </c>
+      <c r="H58" t="str">
+        <v/>
+      </c>
+      <c r="I58" t="str">
+        <v/>
+      </c>
+      <c r="J58" t="str">
+        <v/>
+      </c>
+      <c r="K58" t="str">
+        <v/>
+      </c>
+      <c r="L58" t="str">
+        <v/>
+      </c>
+      <c r="M58" t="str">
+        <v/>
+      </c>
+      <c r="N58" t="str">
+        <v/>
+      </c>
+      <c r="O58" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O57"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O58"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -1163,7 +1163,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>湖南恩施</t>
+          <t>湖北恩施</t>
         </is>
       </c>
     </row>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>河边邢台</t>
+          <t>河北邢台</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2552,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -2602,7 +2601,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
@@ -2610,7 +2608,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
@@ -2653,7 +2650,6 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
@@ -2661,7 +2657,6 @@
         </is>
       </c>
     </row>
-    <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
@@ -2669,7 +2664,6 @@
         </is>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
@@ -2677,7 +2671,6 @@
         </is>
       </c>
     </row>
-    <row r="25"/>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
@@ -2727,7 +2720,6 @@
         </is>
       </c>
     </row>
-    <row r="33"/>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -2525,11 +2525,6 @@
           <t>访客地区</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>中国、荷兰、新疆</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -2525,6 +2525,11 @@
           <t>访客地区</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>新疆</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -3420,7 +3420,7 @@
         <v>新家礼包</v>
       </c>
       <c r="B3" t="str">
-        <v>日常用品、猫粮、常用药品</v>
+        <v>日常用品、过渡猫粮（半个月左右）、常用药品（驱虫药等）</v>
       </c>
     </row>
     <row r="4">

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -3007,7 +3007,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v/>
+        <v>新加坡</v>
       </c>
       <c r="G56" t="str">
         <v/>

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -2387,7 +2387,7 @@
         <v>2026-07-02</v>
       </c>
       <c r="K40" t="str">
-        <v>assets/diary/zouzou-depart.jpg</v>
+        <v/>
       </c>
       <c r="L40" t="str">
         <v>2026-07-02</v>
@@ -2399,7 +2399,7 @@
         <v>2026-11-04</v>
       </c>
       <c r="O40" t="str">
-        <v>2026-07-30 · 6.2斤 · 五个月10天了 · assets/feedback/zouzou-1.jpg</v>
+        <v>2026-08-03 · 血清检测,2026-07-02 · 打疫苗 · assets/diary/zouzou-depart.jpg,2026-07-30 · 6.2斤 · 五个月10天了 · assets/feedback/zouzou-1.jpg</v>
       </c>
       <c r="P40" t="str">
         <v>已付定金</v>

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P59"/>
+  <dimension ref="A1:S59"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -454,6 +454,15 @@
       <c r="P1" t="str">
         <v>交易阶段</v>
       </c>
+      <c r="Q1" t="str">
+        <v>价格</v>
+      </c>
+      <c r="R1" t="str">
+        <v>描述</v>
+      </c>
+      <c r="S1" t="str">
+        <v>展示描述</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -504,6 +513,15 @@
       <c r="P2" t="str">
         <v/>
       </c>
+      <c r="Q2" t="str">
+        <v/>
+      </c>
+      <c r="R2" t="str">
+        <v/>
+      </c>
+      <c r="S2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -554,6 +572,15 @@
       <c r="P3" t="str">
         <v/>
       </c>
+      <c r="Q3" t="str">
+        <v/>
+      </c>
+      <c r="R3" t="str">
+        <v/>
+      </c>
+      <c r="S3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -604,6 +631,15 @@
       <c r="P4" t="str">
         <v/>
       </c>
+      <c r="Q4" t="str">
+        <v/>
+      </c>
+      <c r="R4" t="str">
+        <v/>
+      </c>
+      <c r="S4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -654,6 +690,15 @@
       <c r="P5" t="str">
         <v/>
       </c>
+      <c r="Q5" t="str">
+        <v/>
+      </c>
+      <c r="R5" t="str">
+        <v/>
+      </c>
+      <c r="S5" t="str">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -704,6 +749,15 @@
       <c r="P6" t="str">
         <v/>
       </c>
+      <c r="Q6" t="str">
+        <v/>
+      </c>
+      <c r="R6" t="str">
+        <v/>
+      </c>
+      <c r="S6" t="str">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -754,6 +808,15 @@
       <c r="P7" t="str">
         <v/>
       </c>
+      <c r="Q7" t="str">
+        <v/>
+      </c>
+      <c r="R7" t="str">
+        <v/>
+      </c>
+      <c r="S7" t="str">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -804,6 +867,15 @@
       <c r="P8" t="str">
         <v/>
       </c>
+      <c r="Q8" t="str">
+        <v/>
+      </c>
+      <c r="R8" t="str">
+        <v/>
+      </c>
+      <c r="S8" t="str">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -854,6 +926,15 @@
       <c r="P9" t="str">
         <v/>
       </c>
+      <c r="Q9" t="str">
+        <v/>
+      </c>
+      <c r="R9" t="str">
+        <v/>
+      </c>
+      <c r="S9" t="str">
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
@@ -904,6 +985,15 @@
       <c r="P10" t="str">
         <v/>
       </c>
+      <c r="Q10" t="str">
+        <v/>
+      </c>
+      <c r="R10" t="str">
+        <v/>
+      </c>
+      <c r="S10" t="str">
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
@@ -954,6 +1044,15 @@
       <c r="P11" t="str">
         <v/>
       </c>
+      <c r="Q11" t="str">
+        <v/>
+      </c>
+      <c r="R11" t="str">
+        <v/>
+      </c>
+      <c r="S11" t="str">
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
@@ -1004,6 +1103,15 @@
       <c r="P12" t="str">
         <v/>
       </c>
+      <c r="Q12" t="str">
+        <v/>
+      </c>
+      <c r="R12" t="str">
+        <v/>
+      </c>
+      <c r="S12" t="str">
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
@@ -1054,6 +1162,15 @@
       <c r="P13" t="str">
         <v/>
       </c>
+      <c r="Q13" t="str">
+        <v/>
+      </c>
+      <c r="R13" t="str">
+        <v/>
+      </c>
+      <c r="S13" t="str">
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
@@ -1104,6 +1221,15 @@
       <c r="P14" t="str">
         <v/>
       </c>
+      <c r="Q14" t="str">
+        <v/>
+      </c>
+      <c r="R14" t="str">
+        <v/>
+      </c>
+      <c r="S14" t="str">
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
@@ -1154,6 +1280,15 @@
       <c r="P15" t="str">
         <v/>
       </c>
+      <c r="Q15" t="str">
+        <v/>
+      </c>
+      <c r="R15" t="str">
+        <v/>
+      </c>
+      <c r="S15" t="str">
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
@@ -1204,6 +1339,15 @@
       <c r="P16" t="str">
         <v/>
       </c>
+      <c r="Q16" t="str">
+        <v/>
+      </c>
+      <c r="R16" t="str">
+        <v/>
+      </c>
+      <c r="S16" t="str">
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
@@ -1254,6 +1398,15 @@
       <c r="P17" t="str">
         <v/>
       </c>
+      <c r="Q17" t="str">
+        <v/>
+      </c>
+      <c r="R17" t="str">
+        <v/>
+      </c>
+      <c r="S17" t="str">
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
@@ -1304,6 +1457,15 @@
       <c r="P18" t="str">
         <v/>
       </c>
+      <c r="Q18" t="str">
+        <v/>
+      </c>
+      <c r="R18" t="str">
+        <v/>
+      </c>
+      <c r="S18" t="str">
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
@@ -1354,6 +1516,15 @@
       <c r="P19" t="str">
         <v/>
       </c>
+      <c r="Q19" t="str">
+        <v/>
+      </c>
+      <c r="R19" t="str">
+        <v/>
+      </c>
+      <c r="S19" t="str">
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
@@ -1404,6 +1575,15 @@
       <c r="P20" t="str">
         <v/>
       </c>
+      <c r="Q20" t="str">
+        <v/>
+      </c>
+      <c r="R20" t="str">
+        <v/>
+      </c>
+      <c r="S20" t="str">
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
@@ -1454,6 +1634,15 @@
       <c r="P21" t="str">
         <v/>
       </c>
+      <c r="Q21" t="str">
+        <v/>
+      </c>
+      <c r="R21" t="str">
+        <v/>
+      </c>
+      <c r="S21" t="str">
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
@@ -1504,6 +1693,15 @@
       <c r="P22" t="str">
         <v/>
       </c>
+      <c r="Q22" t="str">
+        <v/>
+      </c>
+      <c r="R22" t="str">
+        <v/>
+      </c>
+      <c r="S22" t="str">
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
@@ -1554,6 +1752,15 @@
       <c r="P23" t="str">
         <v/>
       </c>
+      <c r="Q23" t="str">
+        <v/>
+      </c>
+      <c r="R23" t="str">
+        <v/>
+      </c>
+      <c r="S23" t="str">
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
@@ -1604,6 +1811,15 @@
       <c r="P24" t="str">
         <v/>
       </c>
+      <c r="Q24" t="str">
+        <v/>
+      </c>
+      <c r="R24" t="str">
+        <v/>
+      </c>
+      <c r="S24" t="str">
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
@@ -1654,6 +1870,15 @@
       <c r="P25" t="str">
         <v/>
       </c>
+      <c r="Q25" t="str">
+        <v/>
+      </c>
+      <c r="R25" t="str">
+        <v/>
+      </c>
+      <c r="S25" t="str">
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
@@ -1704,6 +1929,15 @@
       <c r="P26" t="str">
         <v/>
       </c>
+      <c r="Q26" t="str">
+        <v/>
+      </c>
+      <c r="R26" t="str">
+        <v/>
+      </c>
+      <c r="S26" t="str">
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
@@ -1754,6 +1988,15 @@
       <c r="P27" t="str">
         <v/>
       </c>
+      <c r="Q27" t="str">
+        <v/>
+      </c>
+      <c r="R27" t="str">
+        <v/>
+      </c>
+      <c r="S27" t="str">
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
@@ -1804,6 +2047,15 @@
       <c r="P28" t="str">
         <v/>
       </c>
+      <c r="Q28" t="str">
+        <v/>
+      </c>
+      <c r="R28" t="str">
+        <v/>
+      </c>
+      <c r="S28" t="str">
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
@@ -1854,6 +2106,15 @@
       <c r="P29" t="str">
         <v/>
       </c>
+      <c r="Q29" t="str">
+        <v/>
+      </c>
+      <c r="R29" t="str">
+        <v/>
+      </c>
+      <c r="S29" t="str">
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
@@ -1904,6 +2165,15 @@
       <c r="P30" t="str">
         <v/>
       </c>
+      <c r="Q30" t="str">
+        <v/>
+      </c>
+      <c r="R30" t="str">
+        <v/>
+      </c>
+      <c r="S30" t="str">
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
@@ -1954,6 +2224,15 @@
       <c r="P31" t="str">
         <v/>
       </c>
+      <c r="Q31" t="str">
+        <v/>
+      </c>
+      <c r="R31" t="str">
+        <v/>
+      </c>
+      <c r="S31" t="str">
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
@@ -2004,6 +2283,15 @@
       <c r="P32" t="str">
         <v/>
       </c>
+      <c r="Q32" t="str">
+        <v/>
+      </c>
+      <c r="R32" t="str">
+        <v/>
+      </c>
+      <c r="S32" t="str">
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
@@ -2054,6 +2342,15 @@
       <c r="P33" t="str">
         <v/>
       </c>
+      <c r="Q33" t="str">
+        <v/>
+      </c>
+      <c r="R33" t="str">
+        <v/>
+      </c>
+      <c r="S33" t="str">
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
@@ -2104,6 +2401,15 @@
       <c r="P34" t="str">
         <v/>
       </c>
+      <c r="Q34" t="str">
+        <v/>
+      </c>
+      <c r="R34" t="str">
+        <v/>
+      </c>
+      <c r="S34" t="str">
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
@@ -2154,6 +2460,15 @@
       <c r="P35" t="str">
         <v/>
       </c>
+      <c r="Q35" t="str">
+        <v/>
+      </c>
+      <c r="R35" t="str">
+        <v/>
+      </c>
+      <c r="S35" t="str">
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
@@ -2204,6 +2519,15 @@
       <c r="P36" t="str">
         <v/>
       </c>
+      <c r="Q36" t="str">
+        <v/>
+      </c>
+      <c r="R36" t="str">
+        <v/>
+      </c>
+      <c r="S36" t="str">
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
@@ -2254,6 +2578,15 @@
       <c r="P37" t="str">
         <v/>
       </c>
+      <c r="Q37" t="str">
+        <v/>
+      </c>
+      <c r="R37" t="str">
+        <v/>
+      </c>
+      <c r="S37" t="str">
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
@@ -2304,6 +2637,15 @@
       <c r="P38" t="str">
         <v/>
       </c>
+      <c r="Q38" t="str">
+        <v/>
+      </c>
+      <c r="R38" t="str">
+        <v/>
+      </c>
+      <c r="S38" t="str">
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
@@ -2354,6 +2696,15 @@
       <c r="P39" t="str">
         <v/>
       </c>
+      <c r="Q39" t="str">
+        <v/>
+      </c>
+      <c r="R39" t="str">
+        <v/>
+      </c>
+      <c r="S39" t="str">
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
@@ -2404,6 +2755,15 @@
       <c r="P40" t="str">
         <v>已付定金</v>
       </c>
+      <c r="Q40" t="str">
+        <v/>
+      </c>
+      <c r="R40" t="str">
+        <v>安静小猫</v>
+      </c>
+      <c r="S40" t="str">
+        <v>是</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
@@ -2454,6 +2814,15 @@
       <c r="P41" t="str">
         <v/>
       </c>
+      <c r="Q41" t="str">
+        <v/>
+      </c>
+      <c r="R41" t="str">
+        <v/>
+      </c>
+      <c r="S41" t="str">
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
@@ -2504,6 +2873,15 @@
       <c r="P42" t="str">
         <v/>
       </c>
+      <c r="Q42" t="str">
+        <v/>
+      </c>
+      <c r="R42" t="str">
+        <v/>
+      </c>
+      <c r="S42" t="str">
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
@@ -2554,6 +2932,15 @@
       <c r="P43" t="str">
         <v/>
       </c>
+      <c r="Q43" t="str">
+        <v/>
+      </c>
+      <c r="R43" t="str">
+        <v/>
+      </c>
+      <c r="S43" t="str">
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
@@ -2604,6 +2991,15 @@
       <c r="P44" t="str">
         <v/>
       </c>
+      <c r="Q44" t="str">
+        <v/>
+      </c>
+      <c r="R44" t="str">
+        <v/>
+      </c>
+      <c r="S44" t="str">
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
@@ -2654,6 +3050,15 @@
       <c r="P45" t="str">
         <v/>
       </c>
+      <c r="Q45" t="str">
+        <v/>
+      </c>
+      <c r="R45" t="str">
+        <v/>
+      </c>
+      <c r="S45" t="str">
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
@@ -2704,6 +3109,15 @@
       <c r="P46" t="str">
         <v/>
       </c>
+      <c r="Q46" t="str">
+        <v/>
+      </c>
+      <c r="R46" t="str">
+        <v/>
+      </c>
+      <c r="S46" t="str">
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
@@ -2754,6 +3168,15 @@
       <c r="P47" t="str">
         <v/>
       </c>
+      <c r="Q47" t="str">
+        <v/>
+      </c>
+      <c r="R47" t="str">
+        <v/>
+      </c>
+      <c r="S47" t="str">
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
@@ -2804,6 +3227,15 @@
       <c r="P48" t="str">
         <v/>
       </c>
+      <c r="Q48" t="str">
+        <v/>
+      </c>
+      <c r="R48" t="str">
+        <v/>
+      </c>
+      <c r="S48" t="str">
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
@@ -2854,6 +3286,15 @@
       <c r="P49" t="str">
         <v/>
       </c>
+      <c r="Q49" t="str">
+        <v/>
+      </c>
+      <c r="R49" t="str">
+        <v/>
+      </c>
+      <c r="S49" t="str">
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
@@ -2904,6 +3345,15 @@
       <c r="P50" t="str">
         <v/>
       </c>
+      <c r="Q50" t="str">
+        <v/>
+      </c>
+      <c r="R50" t="str">
+        <v/>
+      </c>
+      <c r="S50" t="str">
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
@@ -2954,6 +3404,15 @@
       <c r="P51" t="str">
         <v/>
       </c>
+      <c r="Q51" t="str">
+        <v/>
+      </c>
+      <c r="R51" t="str">
+        <v/>
+      </c>
+      <c r="S51" t="str">
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
@@ -3004,6 +3463,15 @@
       <c r="P52" t="str">
         <v/>
       </c>
+      <c r="Q52" t="str">
+        <v/>
+      </c>
+      <c r="R52" t="str">
+        <v/>
+      </c>
+      <c r="S52" t="str">
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
@@ -3054,6 +3522,15 @@
       <c r="P53" t="str">
         <v/>
       </c>
+      <c r="Q53" t="str">
+        <v/>
+      </c>
+      <c r="R53" t="str">
+        <v/>
+      </c>
+      <c r="S53" t="str">
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
@@ -3104,6 +3581,15 @@
       <c r="P54" t="str">
         <v/>
       </c>
+      <c r="Q54" t="str">
+        <v/>
+      </c>
+      <c r="R54" t="str">
+        <v/>
+      </c>
+      <c r="S54" t="str">
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
@@ -3154,6 +3640,15 @@
       <c r="P55" t="str">
         <v/>
       </c>
+      <c r="Q55" t="str">
+        <v/>
+      </c>
+      <c r="R55" t="str">
+        <v/>
+      </c>
+      <c r="S55" t="str">
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
@@ -3204,6 +3699,15 @@
       <c r="P56" t="str">
         <v/>
       </c>
+      <c r="Q56" t="str">
+        <v/>
+      </c>
+      <c r="R56" t="str">
+        <v/>
+      </c>
+      <c r="S56" t="str">
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
@@ -3254,6 +3758,15 @@
       <c r="P57" t="str">
         <v/>
       </c>
+      <c r="Q57" t="str">
+        <v/>
+      </c>
+      <c r="R57" t="str">
+        <v/>
+      </c>
+      <c r="S57" t="str">
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
@@ -3304,6 +3817,15 @@
       <c r="P58" t="str">
         <v/>
       </c>
+      <c r="Q58" t="str">
+        <v/>
+      </c>
+      <c r="R58" t="str">
+        <v/>
+      </c>
+      <c r="S58" t="str">
+        <v/>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
@@ -3354,10 +3876,19 @@
       <c r="P59" t="str">
         <v/>
       </c>
+      <c r="Q59" t="str">
+        <v/>
+      </c>
+      <c r="R59" t="str">
+        <v/>
+      </c>
+      <c r="S59" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P59"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S59"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -2762,7 +2762,7 @@
         <v>安静小猫</v>
       </c>
       <c r="S40" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
     </row>
     <row r="41">

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -2759,7 +2759,7 @@
         <v/>
       </c>
       <c r="R40" t="str">
-        <v>安静小猫</v>
+        <v/>
       </c>
       <c r="S40" t="str">
         <v>否</v>

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S59"/>
+  <dimension ref="A1:S61"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -466,22 +466,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B2" t="str">
         <v>弟弟</v>
       </c>
       <c r="C2" t="str">
-        <v>assets/1787304479674-w0trechn4p.jpg</v>
+        <v>assets/1787318365475-sj87wtsai3.jpg</v>
       </c>
       <c r="D2" t="str">
         <v>否</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-06-06</v>
+        <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>山西朔州</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -520,27 +520,27 @@
         <v/>
       </c>
       <c r="S2" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>纯黑色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B3" t="str">
         <v>妹妹</v>
       </c>
       <c r="C3" t="str">
-        <v>assets/1787283819124-4v7d1w01la.jpg</v>
+        <v>assets/1787318326155-ia4noopjhq.jpg</v>
       </c>
       <c r="D3" t="str">
         <v>否</v>
       </c>
       <c r="E3" t="str">
-        <v>2026-02-20</v>
+        <v/>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>贵州</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -579,24 +579,24 @@
         <v/>
       </c>
       <c r="S3" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>阴影色NS12</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B4" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C4" t="str">
-        <v>assets/1787283212708-jdnyi6ecci.jpg</v>
+        <v>assets/1787304479674-w0trechn4p.jpg</v>
       </c>
       <c r="D4" t="str">
         <v>否</v>
       </c>
       <c r="E4" t="str">
-        <v>2026-05-28</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -643,22 +643,22 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>阴影色NS11</v>
+        <v>纯黑色</v>
       </c>
       <c r="B5" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C5" t="str">
-        <v>assets/1787283153501-s2tjg9spwu.jpg</v>
+        <v>assets/1787283819124-4v7d1w01la.jpg</v>
       </c>
       <c r="D5" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E5" t="str">
-        <v>2026-06-15</v>
+        <v>2026-02-20</v>
       </c>
       <c r="F5" t="str">
-        <v>重庆</v>
+        <v/>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -702,19 +702,19 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>浅烟灰色</v>
+        <v>阴影色NS12</v>
       </c>
       <c r="B6" t="str">
         <v>妹妹</v>
       </c>
       <c r="C6" t="str">
-        <v>assets/1787283092677-i4d8tyrjtf.jpg</v>
+        <v>assets/1787283212708-jdnyi6ecci.jpg</v>
       </c>
       <c r="D6" t="str">
         <v>否</v>
       </c>
       <c r="E6" t="str">
-        <v>2026-03-21</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -761,22 +761,22 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>棕虎斑</v>
+        <v>阴影色NS11</v>
       </c>
       <c r="B7" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C7" t="str">
-        <v>assets/1787283031104-bpyq9wy2tl.jpg</v>
+        <v>assets/1787283153501-s2tjg9spwu.jpg</v>
       </c>
       <c r="D7" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E7" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F7" t="str">
-        <v/>
+        <v>重庆</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -820,19 +820,19 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>棕虎斑</v>
+        <v>浅烟灰色</v>
       </c>
       <c r="B8" t="str">
         <v>妹妹</v>
       </c>
       <c r="C8" t="str">
-        <v>assets/1787282991501-2fjfws0rqw.jpg</v>
+        <v>assets/1787283092677-i4d8tyrjtf.jpg</v>
       </c>
       <c r="D8" t="str">
         <v>否</v>
       </c>
       <c r="E8" t="str">
-        <v>2026-06-06</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -885,13 +885,13 @@
         <v>妹妹</v>
       </c>
       <c r="C9" t="str">
-        <v>assets/1787282942262-syr48fym6c.jpg</v>
+        <v>assets/1787283031104-bpyq9wy2tl.jpg</v>
       </c>
       <c r="D9" t="str">
         <v>否</v>
       </c>
       <c r="E9" t="str">
-        <v>2026-06-15</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -941,10 +941,10 @@
         <v>棕虎斑</v>
       </c>
       <c r="B10" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C10" t="str">
-        <v>assets/1787282819855-7vhx3m0v40.jpg</v>
+        <v>assets/1787282991501-2fjfws0rqw.jpg</v>
       </c>
       <c r="D10" t="str">
         <v>否</v>
@@ -1003,13 +1003,13 @@
         <v>妹妹</v>
       </c>
       <c r="C11" t="str">
-        <v>assets/1787282703381-2uakw592b4.jpg</v>
+        <v>assets/1787282942262-syr48fym6c.jpg</v>
       </c>
       <c r="D11" t="str">
         <v>否</v>
       </c>
       <c r="E11" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -1056,13 +1056,13 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B12" t="str">
         <v>弟弟</v>
       </c>
       <c r="C12" t="str">
-        <v>assets/1787282649397-9hc31ncrpc.jpg</v>
+        <v>assets/1787282819855-7vhx3m0v40.jpg</v>
       </c>
       <c r="D12" t="str">
         <v>否</v>
@@ -1115,13 +1115,13 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B13" t="str">
         <v>妹妹</v>
       </c>
       <c r="C13" t="str">
-        <v>assets/1787282617957-svcoyyznpg.jpg</v>
+        <v>assets/1787282703381-2uakw592b4.jpg</v>
       </c>
       <c r="D13" t="str">
         <v>否</v>
@@ -1180,7 +1180,7 @@
         <v>弟弟</v>
       </c>
       <c r="C14" t="str">
-        <v>assets/1787282419632-78nixqjzua.jpg</v>
+        <v>assets/1787282649397-9hc31ncrpc.jpg</v>
       </c>
       <c r="D14" t="str">
         <v>否</v>
@@ -1233,19 +1233,19 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>纯黑色</v>
+        <v>烟灰色</v>
       </c>
       <c r="B15" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C15" t="str">
-        <v>assets/1787282349942-2cfuyn7xlc.jpg</v>
+        <v>assets/1787282617957-svcoyyznpg.jpg</v>
       </c>
       <c r="D15" t="str">
         <v>否</v>
       </c>
       <c r="E15" t="str">
-        <v>2026-03-21</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F15" t="str">
         <v/>
@@ -1292,19 +1292,19 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B16" t="str">
         <v>弟弟</v>
       </c>
       <c r="C16" t="str">
-        <v>assets/1787282064159-6b4z8c5msd.jpg</v>
+        <v>assets/1787282419632-78nixqjzua.jpg</v>
       </c>
       <c r="D16" t="str">
         <v>否</v>
       </c>
       <c r="E16" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F16" t="str">
         <v/>
@@ -1351,19 +1351,19 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>阴影色NS11</v>
+        <v>纯黑色</v>
       </c>
       <c r="B17" t="str">
         <v>弟弟</v>
       </c>
       <c r="C17" t="str">
-        <v>assets/1787280590041-vzcwebdok1.jpg</v>
+        <v>assets/1787282349942-2cfuyn7xlc.jpg</v>
       </c>
       <c r="D17" t="str">
         <v>否</v>
       </c>
       <c r="E17" t="str">
-        <v>2026-05-28</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F17" t="str">
         <v/>
@@ -1410,19 +1410,19 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>浅色银虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B18" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C18" t="str">
-        <v>assets/1787281786169-9ia0h837ct.jpg</v>
+        <v>assets/1787282064159-6b4z8c5msd.jpg</v>
       </c>
       <c r="D18" t="str">
         <v>否</v>
       </c>
       <c r="E18" t="str">
-        <v>2026-06-15</v>
+        <v>2026-06-10</v>
       </c>
       <c r="F18" t="str">
         <v/>
@@ -1469,22 +1469,22 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>浅烟灰色</v>
+        <v>阴影色NS11</v>
       </c>
       <c r="B19" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C19" t="str">
-        <v>assets/1785843720843-63qz159daui.jpg</v>
+        <v>assets/1787280590041-vzcwebdok1.jpg</v>
       </c>
       <c r="D19" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E19" t="str">
-        <v>2026-03-21</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F19" t="str">
-        <v>四川成都</v>
+        <v/>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1528,22 +1528,22 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>凯米尔色</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B20" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C20" t="str">
-        <v>assets/1787301984056-iu6afro5z5.jpg, assets/1785843763310-elg05ur61ri.jpg</v>
+        <v>assets/1787281786169-9ia0h837ct.jpg</v>
       </c>
       <c r="D20" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E20" t="str">
-        <v>2026-02-14</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F20" t="str">
-        <v>上海浦东</v>
+        <v/>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>银虎斑补丁</v>
+        <v>浅烟灰色</v>
       </c>
       <c r="B21" t="str">
         <v>妹妹</v>
       </c>
       <c r="C21" t="str">
-        <v>assets/1785843820715-9kz7gy4mbr7.jpg</v>
+        <v>assets/1785843720843-63qz159daui.jpg</v>
       </c>
       <c r="D21" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E21" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F21" t="str">
-        <v/>
+        <v>四川成都</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1646,22 +1646,22 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>烟灰色</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B22" t="str">
         <v>弟弟</v>
       </c>
       <c r="C22" t="str">
-        <v>assets/1785843953805-mxl3x1982io.jpg</v>
+        <v>assets/1787301984056-iu6afro5z5.jpg, assets/1785843763310-elg05ur61ri.jpg</v>
       </c>
       <c r="D22" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E22" t="str">
-        <v>2026-05-18</v>
+        <v>2026-02-14</v>
       </c>
       <c r="F22" t="str">
-        <v/>
+        <v>上海浦东</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1705,19 +1705,19 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>棕虎斑玳瑁</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B23" t="str">
         <v>妹妹</v>
       </c>
       <c r="C23" t="str">
-        <v>assets/1785844013835-ek4xpcje7kh.jpg</v>
+        <v>assets/1785843820715-9kz7gy4mbr7.jpg</v>
       </c>
       <c r="D23" t="str">
         <v>否</v>
       </c>
       <c r="E23" t="str">
-        <v>2026-02-14</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F23" t="str">
         <v/>
@@ -1764,19 +1764,19 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>银虎斑补丁</v>
+        <v>烟灰色</v>
       </c>
       <c r="B24" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C24" t="str">
-        <v>assets/1785844434338-ek5zbdgdcne.jpg</v>
+        <v>assets/1785843953805-mxl3x1982io.jpg</v>
       </c>
       <c r="D24" t="str">
         <v>否</v>
       </c>
       <c r="E24" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F24" t="str">
         <v/>
@@ -1823,22 +1823,22 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑玳瑁</v>
       </c>
       <c r="B25" t="str">
         <v>妹妹</v>
       </c>
       <c r="C25" t="str">
-        <v>assets/1785838787730-s5f333sc3u.jpg</v>
+        <v>assets/1785844013835-ek4xpcje7kh.jpg</v>
       </c>
       <c r="D25" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E25" t="str">
-        <v>2026-06-05</v>
+        <v>2026-02-14</v>
       </c>
       <c r="F25" t="str">
-        <v>湖北恩施</v>
+        <v/>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1882,22 +1882,22 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>银虎斑</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B26" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C26" t="str">
-        <v>assets/1785842296661-6qw3zs3as8h.jpg</v>
+        <v>assets/1785844434338-ek5zbdgdcne.jpg</v>
       </c>
       <c r="D26" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E26" t="str">
-        <v>2026-06-05</v>
+        <v>2026-05-24</v>
       </c>
       <c r="F26" t="str">
-        <v>湖北恩施</v>
+        <v/>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1944,19 +1944,19 @@
         <v>银虎斑</v>
       </c>
       <c r="B27" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C27" t="str">
-        <v>assets/1785842429109-porc98rel5.jpg</v>
+        <v>assets/1785838787730-s5f333sc3u.jpg</v>
       </c>
       <c r="D27" t="str">
         <v>是</v>
       </c>
       <c r="E27" t="str">
-        <v>2025-11-05</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F27" t="str">
-        <v>韩国</v>
+        <v>湖北恩施</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -2003,19 +2003,19 @@
         <v>银虎斑</v>
       </c>
       <c r="B28" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C28" t="str">
-        <v>assets/1785842594141-fcglbzjp509.jpg</v>
+        <v>assets/1785842296661-6qw3zs3as8h.jpg</v>
       </c>
       <c r="D28" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E28" t="str">
-        <v>2026-05-18</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F28" t="str">
-        <v/>
+        <v>湖北恩施</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B29" t="str">
         <v>弟弟</v>
       </c>
       <c r="C29" t="str">
-        <v>assets/1785842639100-82k775dhwiv.jpg</v>
+        <v>assets/1785842429109-porc98rel5.jpg</v>
       </c>
       <c r="D29" t="str">
         <v>是</v>
       </c>
       <c r="E29" t="str">
-        <v>2026-05-28</v>
+        <v>2025-11-05</v>
       </c>
       <c r="F29" t="str">
-        <v>四川自贡</v>
+        <v>韩国</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -2118,19 +2118,19 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B30" t="str">
         <v>妹妹</v>
       </c>
       <c r="C30" t="str">
-        <v>assets/1785842684502-mnhr0r96eee.jpg</v>
+        <v>assets/1785842594141-fcglbzjp509.jpg</v>
       </c>
       <c r="D30" t="str">
         <v>否</v>
       </c>
       <c r="E30" t="str">
-        <v>2026-06-06</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F30" t="str">
         <v/>
@@ -2177,22 +2177,22 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>纯黑色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B31" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C31" t="str">
-        <v>assets/1785842779532-5u1j0igrw1s.jpg</v>
+        <v>assets/1785842639100-82k775dhwiv.jpg</v>
       </c>
       <c r="D31" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E31" t="str">
-        <v>2026-03-05</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F31" t="str">
-        <v/>
+        <v>四川自贡</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -2236,22 +2236,22 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B32" t="str">
         <v>妹妹</v>
       </c>
       <c r="C32" t="str">
-        <v>assets/1785842817046-6keqv4rw4yf.jpg</v>
+        <v>assets/1785842684502-mnhr0r96eee.jpg</v>
       </c>
       <c r="D32" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E32" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F32" t="str">
-        <v>韩国</v>
+        <v/>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -2295,22 +2295,22 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>浅色银虎斑</v>
+        <v>纯黑色</v>
       </c>
       <c r="B33" t="str">
         <v>妹妹</v>
       </c>
       <c r="C33" t="str">
-        <v>assets/1785842950972-a88lbrskpc.jpg</v>
+        <v>assets/1785842779532-5u1j0igrw1s.jpg</v>
       </c>
       <c r="D33" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E33" t="str">
-        <v>2026-06-05</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F33" t="str">
-        <v>河北邢台</v>
+        <v/>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -2354,22 +2354,22 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B34" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C34" t="str">
-        <v>assets/1785843011477-n3l1wi6ech.jpg</v>
+        <v>assets/1785842817046-6keqv4rw4yf.jpg</v>
       </c>
       <c r="D34" t="str">
         <v>是</v>
       </c>
       <c r="E34" t="str">
-        <v>2026-06-05</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F34" t="str">
-        <v>四川自贡</v>
+        <v>韩国</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -2413,22 +2413,22 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>蓝虎斑</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B35" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C35" t="str">
-        <v>assets/1785843237517-ga449iqess5.jpg</v>
+        <v>assets/1785842950972-a88lbrskpc.jpg</v>
       </c>
       <c r="D35" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E35" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F35" t="str">
-        <v/>
+        <v>河北邢台</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -2472,22 +2472,22 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>棕虎斑补丁</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B36" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C36" t="str">
-        <v>assets/1785842523893-7nwnnhwi4ns.jpg</v>
+        <v>assets/1785843011477-n3l1wi6ech.jpg</v>
       </c>
       <c r="D36" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E36" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F36" t="str">
-        <v/>
+        <v>四川自贡</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -2534,16 +2534,16 @@
         <v>蓝虎斑</v>
       </c>
       <c r="B37" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C37" t="str">
-        <v>assets/1785843497557-st27fk8drqi.jpg</v>
+        <v>assets/1785843237517-ga449iqess5.jpg</v>
       </c>
       <c r="D37" t="str">
         <v>否</v>
       </c>
       <c r="E37" t="str">
-        <v>2026-04-05</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F37" t="str">
         <v/>
@@ -2590,13 +2590,13 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑补丁</v>
       </c>
       <c r="B38" t="str">
         <v>妹妹</v>
       </c>
       <c r="C38" t="str">
-        <v>assets/1785843621923-ylhakbtw13i.jpg</v>
+        <v>assets/1785842523893-7nwnnhwi4ns.jpg</v>
       </c>
       <c r="D38" t="str">
         <v>否</v>
@@ -2649,19 +2649,19 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B39" t="str">
         <v>妹妹</v>
       </c>
       <c r="C39" t="str">
-        <v>assets/1785843663884-sfxvpmiet7.jpg</v>
+        <v>assets/1785843497557-st27fk8drqi.jpg</v>
       </c>
       <c r="D39" t="str">
         <v>否</v>
       </c>
       <c r="E39" t="str">
-        <v>2026-03-05</v>
+        <v>2026-04-05</v>
       </c>
       <c r="F39" t="str">
         <v/>
@@ -2708,52 +2708,52 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>蓝虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B40" t="str">
         <v>妹妹</v>
       </c>
       <c r="C40" t="str">
-        <v>assets/1785852601940-o236xtv7yx.jpeg</v>
+        <v>assets/1785843621923-ylhakbtw13i.jpg</v>
       </c>
       <c r="D40" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E40" t="str">
-        <v>2026-02-20</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F40" t="str">
-        <v>荷兰</v>
+        <v/>
       </c>
       <c r="G40" t="str">
-        <v>阿泽</v>
+        <v/>
       </c>
       <c r="H40" t="str">
-        <v>小辫子</v>
+        <v/>
       </c>
       <c r="I40" t="str">
-        <v>驺驺</v>
+        <v/>
       </c>
       <c r="J40" t="str">
-        <v>2026-07-02</v>
+        <v/>
       </c>
       <c r="K40" t="str">
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>2026-07-02</v>
+        <v/>
       </c>
       <c r="M40" t="str">
-        <v>2026-08-03</v>
+        <v/>
       </c>
       <c r="N40" t="str">
-        <v>2026-11-04</v>
+        <v/>
       </c>
       <c r="O40" t="str">
-        <v>2026-08-03 · 血清检测,2026-07-02 · 打疫苗 · assets/diary/zouzou-depart.jpg,2026-07-30 · 6.2斤 · 五个月10天了 · assets/feedback/zouzou-1.jpg</v>
+        <v/>
       </c>
       <c r="P40" t="str">
-        <v>已付定金</v>
+        <v/>
       </c>
       <c r="Q40" t="str">
         <v/>
@@ -2762,27 +2762,27 @@
         <v/>
       </c>
       <c r="S40" t="str">
-        <v>否</v>
+        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>红虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B41" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C41" t="str">
-        <v>assets/1785853950207-cedor66ou2q.jpeg</v>
+        <v>assets/1785843663884-sfxvpmiet7.jpg</v>
       </c>
       <c r="D41" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E41" t="str">
-        <v/>
+        <v>2026-03-05</v>
       </c>
       <c r="F41" t="str">
-        <v>广东广州</v>
+        <v/>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -2826,52 +2826,52 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>红虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B42" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C42" t="str">
-        <v>assets/1785854129383-c8qkvl537x.jpeg</v>
+        <v>assets/1785852601940-o236xtv7yx.jpeg</v>
       </c>
       <c r="D42" t="str">
         <v>是</v>
       </c>
       <c r="E42" t="str">
-        <v/>
+        <v>2026-02-20</v>
       </c>
       <c r="F42" t="str">
-        <v>广东广州</v>
+        <v>荷兰</v>
       </c>
       <c r="G42" t="str">
-        <v/>
+        <v>阿泽</v>
       </c>
       <c r="H42" t="str">
-        <v/>
+        <v>小辫子</v>
       </c>
       <c r="I42" t="str">
-        <v/>
+        <v>驺驺</v>
       </c>
       <c r="J42" t="str">
-        <v/>
+        <v>2026-07-02</v>
       </c>
       <c r="K42" t="str">
         <v/>
       </c>
       <c r="L42" t="str">
-        <v/>
+        <v>2026-07-02</v>
       </c>
       <c r="M42" t="str">
-        <v/>
+        <v>2026-08-03</v>
       </c>
       <c r="N42" t="str">
-        <v/>
+        <v>2026-11-04</v>
       </c>
       <c r="O42" t="str">
-        <v/>
+        <v>2026-08-03 · 血清检测,2026-07-02 · 打疫苗 · assets/diary/zouzou-depart.jpg,2026-07-30 · 6.2斤 · 五个月10天了 · assets/feedback/zouzou-1.jpg</v>
       </c>
       <c r="P42" t="str">
-        <v/>
+        <v>已付定金</v>
       </c>
       <c r="Q42" t="str">
         <v/>
@@ -2880,18 +2880,18 @@
         <v/>
       </c>
       <c r="S42" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B43" t="str">
         <v>弟弟</v>
       </c>
       <c r="C43" t="str">
-        <v>assets/1785854166720-48r17hry9cd.jpeg</v>
+        <v>assets/1785853950207-cedor66ou2q.jpeg</v>
       </c>
       <c r="D43" t="str">
         <v>是</v>
@@ -2900,7 +2900,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>山西朔州</v>
+        <v>广东广州</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2944,13 +2944,13 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B44" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C44" t="str">
-        <v>assets/1785854224521-2cpg6xipfn6.jpeg</v>
+        <v>assets/1785854129383-c8qkvl537x.jpeg</v>
       </c>
       <c r="D44" t="str">
         <v>是</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>浙江宁波</v>
+        <v>广东广州</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -3009,7 +3009,7 @@
         <v>弟弟</v>
       </c>
       <c r="C45" t="str">
-        <v>assets/1785854260793-steez4s972l.jpeg</v>
+        <v>assets/1785854166720-48r17hry9cd.jpeg</v>
       </c>
       <c r="D45" t="str">
         <v>是</v>
@@ -3018,7 +3018,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>陕西西安</v>
+        <v>山西朔州</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -3065,10 +3065,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B46" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C46" t="str">
-        <v>assets/1785854319988-cohio08aod5.jpeg</v>
+        <v>assets/1785854224521-2cpg6xipfn6.jpeg</v>
       </c>
       <c r="D46" t="str">
         <v>是</v>
@@ -3077,7 +3077,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>黑龙江漠河</v>
+        <v>浙江宁波</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -3121,13 +3121,13 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B47" t="str">
         <v>弟弟</v>
       </c>
       <c r="C47" t="str">
-        <v>assets/1785854520974-96b8b1ekqd9.jpeg</v>
+        <v>assets/1785854260793-steez4s972l.jpeg</v>
       </c>
       <c r="D47" t="str">
         <v>是</v>
@@ -3136,7 +3136,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>日本</v>
+        <v>陕西西安</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -3183,10 +3183,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B48" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C48" t="str">
-        <v>assets/1785854664100-haqoiu1h7hj.jpeg</v>
+        <v>assets/1785854319988-cohio08aod5.jpeg</v>
       </c>
       <c r="D48" t="str">
         <v>是</v>
@@ -3195,7 +3195,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>浙江杭州</v>
+        <v>黑龙江漠河</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -3239,13 +3239,13 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B49" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C49" t="str">
-        <v>assets/1785854690732-orrs40sx9rs.jpeg</v>
+        <v>assets/1785854520974-96b8b1ekqd9.jpeg</v>
       </c>
       <c r="D49" t="str">
         <v>是</v>
@@ -3254,7 +3254,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>贵州安顺</v>
+        <v>日本</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -3304,7 +3304,7 @@
         <v>妹妹</v>
       </c>
       <c r="C50" t="str">
-        <v>assets/1785854734122-wcpmib4m7.jpeg</v>
+        <v>assets/1785854664100-haqoiu1h7hj.jpeg</v>
       </c>
       <c r="D50" t="str">
         <v>是</v>
@@ -3313,7 +3313,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>山东青岛</v>
+        <v>浙江杭州</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -3360,10 +3360,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B51" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C51" t="str">
-        <v>assets/1785854758707-1kxdkfvs6jc.jpeg</v>
+        <v>assets/1785854690732-orrs40sx9rs.jpeg</v>
       </c>
       <c r="D51" t="str">
         <v>是</v>
@@ -3372,7 +3372,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>黑龙江漠河</v>
+        <v>贵州安顺</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -3416,13 +3416,13 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>纯蓝色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B52" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C52" t="str">
-        <v>assets/1785854784780-3g0u60pdo93.jpeg</v>
+        <v>assets/1785854734122-wcpmib4m7.jpeg</v>
       </c>
       <c r="D52" t="str">
         <v>是</v>
@@ -3431,7 +3431,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>河南鹤壁</v>
+        <v>山东青岛</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -3481,7 +3481,7 @@
         <v>弟弟</v>
       </c>
       <c r="C53" t="str">
-        <v>assets/1785854813179-8oyxr0h2bbu.jpeg</v>
+        <v>assets/1785854758707-1kxdkfvs6jc.jpeg</v>
       </c>
       <c r="D53" t="str">
         <v>是</v>
@@ -3490,7 +3490,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>陕西西安</v>
+        <v>黑龙江漠河</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -3534,13 +3534,13 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>棕虎斑</v>
+        <v>纯蓝色</v>
       </c>
       <c r="B54" t="str">
         <v>弟弟</v>
       </c>
       <c r="C54" t="str">
-        <v>assets/1785854838933-uq6amircyzd.jpeg</v>
+        <v>assets/1785854784780-3g0u60pdo93.jpeg</v>
       </c>
       <c r="D54" t="str">
         <v>是</v>
@@ -3549,7 +3549,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>四川成都</v>
+        <v>河南鹤壁</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -3593,22 +3593,22 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>烟灰色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B55" t="str">
         <v>弟弟</v>
       </c>
       <c r="C55" t="str">
-        <v>assets/1785854869973-za3p6wikqpo.jpeg</v>
+        <v>assets/1785854813179-8oyxr0h2bbu.jpeg</v>
       </c>
       <c r="D55" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E55" t="str">
-        <v>2026-05-18</v>
+        <v/>
       </c>
       <c r="F55" t="str">
-        <v/>
+        <v>陕西西安</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -3652,13 +3652,13 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B56" t="str">
         <v>弟弟</v>
       </c>
       <c r="C56" t="str">
-        <v>assets/1785854997023-mawkallt2a.jpeg</v>
+        <v>assets/1785854838933-uq6amircyzd.jpeg</v>
       </c>
       <c r="D56" t="str">
         <v>是</v>
@@ -3667,7 +3667,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>新加坡</v>
+        <v>四川成都</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>凯米尔色</v>
+        <v>烟灰色</v>
       </c>
       <c r="B57" t="str">
         <v>弟弟</v>
       </c>
       <c r="C57" t="str">
-        <v>assets/1785855043327-wdc5pxwm34k.jpeg</v>
+        <v>assets/1785854869973-za3p6wikqpo.jpeg</v>
       </c>
       <c r="D57" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E57" t="str">
-        <v/>
+        <v>2026-05-18</v>
       </c>
       <c r="F57" t="str">
-        <v>上海浦东</v>
+        <v/>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -3770,22 +3770,22 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B58" t="str">
         <v>弟弟</v>
       </c>
       <c r="C58" t="str">
-        <v>assets/1785912551260-jplefm937nk.jpeg, assets/videos/02.mp4</v>
+        <v>assets/1785854997023-mawkallt2a.jpeg</v>
       </c>
       <c r="D58" t="str">
         <v>是</v>
       </c>
       <c r="E58" t="str">
-        <v>2026-06-06</v>
+        <v/>
       </c>
       <c r="F58" t="str">
-        <v>浙江温州</v>
+        <v>新加坡</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -3829,66 +3829,184 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
+        <v>凯米尔色</v>
+      </c>
+      <c r="B59" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C59" t="str">
+        <v>assets/1785855043327-wdc5pxwm34k.jpeg</v>
+      </c>
+      <c r="D59" t="str">
+        <v>是</v>
+      </c>
+      <c r="E59" t="str">
+        <v/>
+      </c>
+      <c r="F59" t="str">
+        <v>上海浦东</v>
+      </c>
+      <c r="G59" t="str">
+        <v/>
+      </c>
+      <c r="H59" t="str">
+        <v/>
+      </c>
+      <c r="I59" t="str">
+        <v/>
+      </c>
+      <c r="J59" t="str">
+        <v/>
+      </c>
+      <c r="K59" t="str">
+        <v/>
+      </c>
+      <c r="L59" t="str">
+        <v/>
+      </c>
+      <c r="M59" t="str">
+        <v/>
+      </c>
+      <c r="N59" t="str">
+        <v/>
+      </c>
+      <c r="O59" t="str">
+        <v/>
+      </c>
+      <c r="P59" t="str">
+        <v/>
+      </c>
+      <c r="Q59" t="str">
+        <v/>
+      </c>
+      <c r="R59" t="str">
+        <v/>
+      </c>
+      <c r="S59" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
         <v>棕虎斑</v>
       </c>
-      <c r="B59" t="str">
+      <c r="B60" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C60" t="str">
+        <v>assets/1785912551260-jplefm937nk.jpeg, assets/videos/02.mp4</v>
+      </c>
+      <c r="D60" t="str">
+        <v>是</v>
+      </c>
+      <c r="E60" t="str">
+        <v>2026-06-06</v>
+      </c>
+      <c r="F60" t="str">
+        <v>浙江温州</v>
+      </c>
+      <c r="G60" t="str">
+        <v/>
+      </c>
+      <c r="H60" t="str">
+        <v/>
+      </c>
+      <c r="I60" t="str">
+        <v/>
+      </c>
+      <c r="J60" t="str">
+        <v/>
+      </c>
+      <c r="K60" t="str">
+        <v/>
+      </c>
+      <c r="L60" t="str">
+        <v/>
+      </c>
+      <c r="M60" t="str">
+        <v/>
+      </c>
+      <c r="N60" t="str">
+        <v/>
+      </c>
+      <c r="O60" t="str">
+        <v/>
+      </c>
+      <c r="P60" t="str">
+        <v/>
+      </c>
+      <c r="Q60" t="str">
+        <v/>
+      </c>
+      <c r="R60" t="str">
+        <v/>
+      </c>
+      <c r="S60" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>棕虎斑</v>
+      </c>
+      <c r="B61" t="str">
         <v>妹妹</v>
       </c>
-      <c r="C59" t="str">
+      <c r="C61" t="str">
         <v>assets/1785912694000-m20f5kvvrr.jpeg</v>
       </c>
-      <c r="D59" t="str">
+      <c r="D61" t="str">
         <v>否</v>
       </c>
-      <c r="E59" t="str">
+      <c r="E61" t="str">
         <v>2026-06-06</v>
       </c>
-      <c r="F59" t="str">
-        <v/>
-      </c>
-      <c r="G59" t="str">
-        <v/>
-      </c>
-      <c r="H59" t="str">
-        <v/>
-      </c>
-      <c r="I59" t="str">
-        <v/>
-      </c>
-      <c r="J59" t="str">
-        <v/>
-      </c>
-      <c r="K59" t="str">
-        <v/>
-      </c>
-      <c r="L59" t="str">
-        <v/>
-      </c>
-      <c r="M59" t="str">
-        <v/>
-      </c>
-      <c r="N59" t="str">
-        <v/>
-      </c>
-      <c r="O59" t="str">
-        <v/>
-      </c>
-      <c r="P59" t="str">
-        <v/>
-      </c>
-      <c r="Q59" t="str">
-        <v/>
-      </c>
-      <c r="R59" t="str">
-        <v/>
-      </c>
-      <c r="S59" t="str">
+      <c r="F61" t="str">
+        <v/>
+      </c>
+      <c r="G61" t="str">
+        <v/>
+      </c>
+      <c r="H61" t="str">
+        <v/>
+      </c>
+      <c r="I61" t="str">
+        <v/>
+      </c>
+      <c r="J61" t="str">
+        <v/>
+      </c>
+      <c r="K61" t="str">
+        <v/>
+      </c>
+      <c r="L61" t="str">
+        <v/>
+      </c>
+      <c r="M61" t="str">
+        <v/>
+      </c>
+      <c r="N61" t="str">
+        <v/>
+      </c>
+      <c r="O61" t="str">
+        <v/>
+      </c>
+      <c r="P61" t="str">
+        <v/>
+      </c>
+      <c r="Q61" t="str">
+        <v/>
+      </c>
+      <c r="R61" t="str">
+        <v/>
+      </c>
+      <c r="S61" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S59"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S61"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -475,7 +475,7 @@
         <v>assets/1787318365475-sj87wtsai3.jpg</v>
       </c>
       <c r="D2" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -511,7 +511,7 @@
         <v/>
       </c>
       <c r="P2" t="str">
-        <v/>
+        <v>已接猫</v>
       </c>
       <c r="Q2" t="str">
         <v/>
@@ -534,7 +534,7 @@
         <v>assets/1787318326155-ia4noopjhq.jpg</v>
       </c>
       <c r="D3" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E3" t="str">
         <v/>

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S61"/>
+  <dimension ref="A1:S64"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -472,7 +472,7 @@
         <v>弟弟</v>
       </c>
       <c r="C2" t="str">
-        <v>assets/1787318365475-sj87wtsai3.jpg</v>
+        <v>assets/1787318867999-3gxdddp72x.jpg</v>
       </c>
       <c r="D2" t="str">
         <v>是</v>
@@ -481,7 +481,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>山西朔州</v>
+        <v>广东广州</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -511,7 +511,7 @@
         <v/>
       </c>
       <c r="P2" t="str">
-        <v>已接猫</v>
+        <v/>
       </c>
       <c r="Q2" t="str">
         <v/>
@@ -528,10 +528,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B3" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C3" t="str">
-        <v>assets/1787318326155-ia4noopjhq.jpg</v>
+        <v>assets/1787318609722-0ojb3aikwi.jpg</v>
       </c>
       <c r="D3" t="str">
         <v>是</v>
@@ -540,7 +540,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>贵州</v>
+        <v>黑龙江鹤岗</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -584,199 +584,199 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>棕虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B4" t="str">
         <v>弟弟</v>
       </c>
       <c r="C4" t="str">
-        <v>assets/1787304479674-w0trechn4p.jpg</v>
+        <v>assets/1787318530612-779fbkfcoi.jpg</v>
       </c>
       <c r="D4" t="str">
+        <v>是</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v>天津</v>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v/>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v/>
+      </c>
+      <c r="M4" t="str">
+        <v/>
+      </c>
+      <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4" t="str">
+        <v/>
+      </c>
+      <c r="P4" t="str">
+        <v/>
+      </c>
+      <c r="Q4" t="str">
+        <v/>
+      </c>
+      <c r="R4" t="str">
+        <v/>
+      </c>
+      <c r="S4" t="str">
         <v>否</v>
-      </c>
-      <c r="E4" t="str">
-        <v>2026-06-06</v>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v/>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v/>
-      </c>
-      <c r="M4" t="str">
-        <v/>
-      </c>
-      <c r="N4" t="str">
-        <v/>
-      </c>
-      <c r="O4" t="str">
-        <v/>
-      </c>
-      <c r="P4" t="str">
-        <v/>
-      </c>
-      <c r="Q4" t="str">
-        <v/>
-      </c>
-      <c r="R4" t="str">
-        <v/>
-      </c>
-      <c r="S4" t="str">
-        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>纯黑色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B5" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C5" t="str">
-        <v>assets/1787283819124-4v7d1w01la.jpg</v>
+        <v>assets/1787318365475-sj87wtsai3.jpg</v>
       </c>
       <c r="D5" t="str">
+        <v>是</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v>山西朔州</v>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v/>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v/>
+      </c>
+      <c r="M5" t="str">
+        <v/>
+      </c>
+      <c r="N5" t="str">
+        <v/>
+      </c>
+      <c r="O5" t="str">
+        <v/>
+      </c>
+      <c r="P5" t="str">
+        <v>已接猫</v>
+      </c>
+      <c r="Q5" t="str">
+        <v/>
+      </c>
+      <c r="R5" t="str">
+        <v/>
+      </c>
+      <c r="S5" t="str">
         <v>否</v>
-      </c>
-      <c r="E5" t="str">
-        <v>2026-02-20</v>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v/>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v/>
-      </c>
-      <c r="M5" t="str">
-        <v/>
-      </c>
-      <c r="N5" t="str">
-        <v/>
-      </c>
-      <c r="O5" t="str">
-        <v/>
-      </c>
-      <c r="P5" t="str">
-        <v/>
-      </c>
-      <c r="Q5" t="str">
-        <v/>
-      </c>
-      <c r="R5" t="str">
-        <v/>
-      </c>
-      <c r="S5" t="str">
-        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>阴影色NS12</v>
+        <v>银虎斑</v>
       </c>
       <c r="B6" t="str">
         <v>妹妹</v>
       </c>
       <c r="C6" t="str">
-        <v>assets/1787283212708-jdnyi6ecci.jpg</v>
+        <v>assets/1787318326155-ia4noopjhq.jpg</v>
       </c>
       <c r="D6" t="str">
+        <v>是</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v>贵州</v>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v/>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v/>
+      </c>
+      <c r="M6" t="str">
+        <v/>
+      </c>
+      <c r="N6" t="str">
+        <v/>
+      </c>
+      <c r="O6" t="str">
+        <v/>
+      </c>
+      <c r="P6" t="str">
+        <v/>
+      </c>
+      <c r="Q6" t="str">
+        <v/>
+      </c>
+      <c r="R6" t="str">
+        <v/>
+      </c>
+      <c r="S6" t="str">
         <v>否</v>
-      </c>
-      <c r="E6" t="str">
-        <v>2026-05-28</v>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v/>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v/>
-      </c>
-      <c r="M6" t="str">
-        <v/>
-      </c>
-      <c r="N6" t="str">
-        <v/>
-      </c>
-      <c r="O6" t="str">
-        <v/>
-      </c>
-      <c r="P6" t="str">
-        <v/>
-      </c>
-      <c r="Q6" t="str">
-        <v/>
-      </c>
-      <c r="R6" t="str">
-        <v/>
-      </c>
-      <c r="S6" t="str">
-        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>阴影色NS11</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B7" t="str">
         <v>弟弟</v>
       </c>
       <c r="C7" t="str">
-        <v>assets/1787283153501-s2tjg9spwu.jpg</v>
+        <v>assets/1787304479674-w0trechn4p.jpg</v>
       </c>
       <c r="D7" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E7" t="str">
-        <v>2026-06-15</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F7" t="str">
-        <v>重庆</v>
+        <v/>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -820,19 +820,19 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>浅烟灰色</v>
+        <v>纯黑色</v>
       </c>
       <c r="B8" t="str">
         <v>妹妹</v>
       </c>
       <c r="C8" t="str">
-        <v>assets/1787283092677-i4d8tyrjtf.jpg</v>
+        <v>assets/1787283819124-4v7d1w01la.jpg</v>
       </c>
       <c r="D8" t="str">
         <v>否</v>
       </c>
       <c r="E8" t="str">
-        <v>2026-03-21</v>
+        <v>2026-02-20</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -879,19 +879,19 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>棕虎斑</v>
+        <v>阴影色NS12</v>
       </c>
       <c r="B9" t="str">
         <v>妹妹</v>
       </c>
       <c r="C9" t="str">
-        <v>assets/1787283031104-bpyq9wy2tl.jpg</v>
+        <v>assets/1787283212708-jdnyi6ecci.jpg</v>
       </c>
       <c r="D9" t="str">
         <v>否</v>
       </c>
       <c r="E9" t="str">
-        <v>2026-06-06</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -938,22 +938,22 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>棕虎斑</v>
+        <v>阴影色NS11</v>
       </c>
       <c r="B10" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C10" t="str">
-        <v>assets/1787282991501-2fjfws0rqw.jpg</v>
+        <v>assets/1787283153501-s2tjg9spwu.jpg</v>
       </c>
       <c r="D10" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E10" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F10" t="str">
-        <v/>
+        <v>重庆</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -997,19 +997,19 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>棕虎斑</v>
+        <v>浅烟灰色</v>
       </c>
       <c r="B11" t="str">
         <v>妹妹</v>
       </c>
       <c r="C11" t="str">
-        <v>assets/1787282942262-syr48fym6c.jpg</v>
+        <v>assets/1787283092677-i4d8tyrjtf.jpg</v>
       </c>
       <c r="D11" t="str">
         <v>否</v>
       </c>
       <c r="E11" t="str">
-        <v>2026-06-15</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -1059,10 +1059,10 @@
         <v>棕虎斑</v>
       </c>
       <c r="B12" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C12" t="str">
-        <v>assets/1787282819855-7vhx3m0v40.jpg</v>
+        <v>assets/1787283031104-bpyq9wy2tl.jpg</v>
       </c>
       <c r="D12" t="str">
         <v>否</v>
@@ -1121,7 +1121,7 @@
         <v>妹妹</v>
       </c>
       <c r="C13" t="str">
-        <v>assets/1787282703381-2uakw592b4.jpg</v>
+        <v>assets/1787282991501-2fjfws0rqw.jpg</v>
       </c>
       <c r="D13" t="str">
         <v>否</v>
@@ -1174,19 +1174,19 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B14" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C14" t="str">
-        <v>assets/1787282649397-9hc31ncrpc.jpg</v>
+        <v>assets/1787282942262-syr48fym6c.jpg</v>
       </c>
       <c r="D14" t="str">
         <v>否</v>
       </c>
       <c r="E14" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F14" t="str">
         <v/>
@@ -1233,13 +1233,13 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B15" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C15" t="str">
-        <v>assets/1787282617957-svcoyyznpg.jpg</v>
+        <v>assets/1787282819855-7vhx3m0v40.jpg</v>
       </c>
       <c r="D15" t="str">
         <v>否</v>
@@ -1292,13 +1292,13 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B16" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C16" t="str">
-        <v>assets/1787282419632-78nixqjzua.jpg</v>
+        <v>assets/1787282703381-2uakw592b4.jpg</v>
       </c>
       <c r="D16" t="str">
         <v>否</v>
@@ -1351,19 +1351,19 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>纯黑色</v>
+        <v>烟灰色</v>
       </c>
       <c r="B17" t="str">
         <v>弟弟</v>
       </c>
       <c r="C17" t="str">
-        <v>assets/1787282349942-2cfuyn7xlc.jpg</v>
+        <v>assets/1787282649397-9hc31ncrpc.jpg</v>
       </c>
       <c r="D17" t="str">
         <v>否</v>
       </c>
       <c r="E17" t="str">
-        <v>2026-03-21</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F17" t="str">
         <v/>
@@ -1410,19 +1410,19 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B18" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C18" t="str">
-        <v>assets/1787282064159-6b4z8c5msd.jpg</v>
+        <v>assets/1787282617957-svcoyyznpg.jpg</v>
       </c>
       <c r="D18" t="str">
         <v>否</v>
       </c>
       <c r="E18" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F18" t="str">
         <v/>
@@ -1469,19 +1469,19 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>阴影色NS11</v>
+        <v>烟灰色</v>
       </c>
       <c r="B19" t="str">
         <v>弟弟</v>
       </c>
       <c r="C19" t="str">
-        <v>assets/1787280590041-vzcwebdok1.jpg</v>
+        <v>assets/1787282419632-78nixqjzua.jpg</v>
       </c>
       <c r="D19" t="str">
         <v>否</v>
       </c>
       <c r="E19" t="str">
-        <v>2026-05-28</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F19" t="str">
         <v/>
@@ -1528,19 +1528,19 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>浅色银虎斑</v>
+        <v>纯黑色</v>
       </c>
       <c r="B20" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C20" t="str">
-        <v>assets/1787281786169-9ia0h837ct.jpg</v>
+        <v>assets/1787282349942-2cfuyn7xlc.jpg</v>
       </c>
       <c r="D20" t="str">
         <v>否</v>
       </c>
       <c r="E20" t="str">
-        <v>2026-06-15</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F20" t="str">
         <v/>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>浅烟灰色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B21" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C21" t="str">
-        <v>assets/1785843720843-63qz159daui.jpg</v>
+        <v>assets/1787282064159-6b4z8c5msd.jpg</v>
       </c>
       <c r="D21" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E21" t="str">
-        <v>2026-03-21</v>
+        <v>2026-06-10</v>
       </c>
       <c r="F21" t="str">
-        <v>四川成都</v>
+        <v/>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1646,22 +1646,22 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>凯米尔色</v>
+        <v>阴影色NS11</v>
       </c>
       <c r="B22" t="str">
         <v>弟弟</v>
       </c>
       <c r="C22" t="str">
-        <v>assets/1787301984056-iu6afro5z5.jpg, assets/1785843763310-elg05ur61ri.jpg</v>
+        <v>assets/1787280590041-vzcwebdok1.jpg</v>
       </c>
       <c r="D22" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E22" t="str">
-        <v>2026-02-14</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F22" t="str">
-        <v>上海浦东</v>
+        <v/>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1705,19 +1705,19 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>银虎斑补丁</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B23" t="str">
         <v>妹妹</v>
       </c>
       <c r="C23" t="str">
-        <v>assets/1785843820715-9kz7gy4mbr7.jpg</v>
+        <v>assets/1787281786169-9ia0h837ct.jpg</v>
       </c>
       <c r="D23" t="str">
         <v>否</v>
       </c>
       <c r="E23" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F23" t="str">
         <v/>
@@ -1764,22 +1764,22 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>烟灰色</v>
+        <v>浅烟灰色</v>
       </c>
       <c r="B24" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C24" t="str">
-        <v>assets/1785843953805-mxl3x1982io.jpg</v>
+        <v>assets/1785843720843-63qz159daui.jpg</v>
       </c>
       <c r="D24" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E24" t="str">
-        <v>2026-05-18</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F24" t="str">
-        <v/>
+        <v>四川成都</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1823,22 +1823,22 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>棕虎斑玳瑁</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B25" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C25" t="str">
-        <v>assets/1785844013835-ek4xpcje7kh.jpg</v>
+        <v>assets/1787301984056-iu6afro5z5.jpg, assets/1785843763310-elg05ur61ri.jpg</v>
       </c>
       <c r="D25" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E25" t="str">
         <v>2026-02-14</v>
       </c>
       <c r="F25" t="str">
-        <v/>
+        <v>上海浦东</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1888,13 +1888,13 @@
         <v>妹妹</v>
       </c>
       <c r="C26" t="str">
-        <v>assets/1785844434338-ek5zbdgdcne.jpg</v>
+        <v>assets/1785843820715-9kz7gy4mbr7.jpg</v>
       </c>
       <c r="D26" t="str">
         <v>否</v>
       </c>
       <c r="E26" t="str">
-        <v>2026-05-24</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F26" t="str">
         <v/>
@@ -1941,22 +1941,22 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B27" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C27" t="str">
-        <v>assets/1785838787730-s5f333sc3u.jpg</v>
+        <v>assets/1785843953805-mxl3x1982io.jpg</v>
       </c>
       <c r="D27" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E27" t="str">
-        <v>2026-06-05</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F27" t="str">
-        <v>湖北恩施</v>
+        <v/>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -2000,22 +2000,22 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑玳瑁</v>
       </c>
       <c r="B28" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C28" t="str">
-        <v>assets/1785842296661-6qw3zs3as8h.jpg</v>
+        <v>assets/1785844013835-ek4xpcje7kh.jpg</v>
       </c>
       <c r="D28" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E28" t="str">
-        <v>2026-06-05</v>
+        <v>2026-02-14</v>
       </c>
       <c r="F28" t="str">
-        <v>湖北恩施</v>
+        <v/>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>银虎斑</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B29" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C29" t="str">
-        <v>assets/1785842429109-porc98rel5.jpg</v>
+        <v>assets/1785844434338-ek5zbdgdcne.jpg</v>
       </c>
       <c r="D29" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E29" t="str">
-        <v>2025-11-05</v>
+        <v>2026-05-24</v>
       </c>
       <c r="F29" t="str">
-        <v>韩国</v>
+        <v/>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -2124,16 +2124,16 @@
         <v>妹妹</v>
       </c>
       <c r="C30" t="str">
-        <v>assets/1785842594141-fcglbzjp509.jpg</v>
+        <v>assets/1785838787730-s5f333sc3u.jpg</v>
       </c>
       <c r="D30" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E30" t="str">
-        <v>2026-05-18</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F30" t="str">
-        <v/>
+        <v>湖北恩施</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -2177,22 +2177,22 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B31" t="str">
         <v>弟弟</v>
       </c>
       <c r="C31" t="str">
-        <v>assets/1785842639100-82k775dhwiv.jpg</v>
+        <v>assets/1785842296661-6qw3zs3as8h.jpg</v>
       </c>
       <c r="D31" t="str">
         <v>是</v>
       </c>
       <c r="E31" t="str">
-        <v>2026-05-28</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F31" t="str">
-        <v>四川自贡</v>
+        <v>湖北恩施</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -2236,22 +2236,22 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B32" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C32" t="str">
-        <v>assets/1785842684502-mnhr0r96eee.jpg</v>
+        <v>assets/1785842429109-porc98rel5.jpg</v>
       </c>
       <c r="D32" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E32" t="str">
-        <v>2026-06-06</v>
+        <v>2025-11-05</v>
       </c>
       <c r="F32" t="str">
-        <v/>
+        <v>韩国</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -2295,19 +2295,19 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>纯黑色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B33" t="str">
         <v>妹妹</v>
       </c>
       <c r="C33" t="str">
-        <v>assets/1785842779532-5u1j0igrw1s.jpg</v>
+        <v>assets/1785842594141-fcglbzjp509.jpg</v>
       </c>
       <c r="D33" t="str">
         <v>否</v>
       </c>
       <c r="E33" t="str">
-        <v>2026-03-05</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F33" t="str">
         <v/>
@@ -2354,22 +2354,22 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B34" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C34" t="str">
-        <v>assets/1785842817046-6keqv4rw4yf.jpg</v>
+        <v>assets/1785842639100-82k775dhwiv.jpg</v>
       </c>
       <c r="D34" t="str">
         <v>是</v>
       </c>
       <c r="E34" t="str">
-        <v>2026-03-05</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F34" t="str">
-        <v>韩国</v>
+        <v>四川自贡</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -2413,22 +2413,22 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>浅色银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B35" t="str">
         <v>妹妹</v>
       </c>
       <c r="C35" t="str">
-        <v>assets/1785842950972-a88lbrskpc.jpg</v>
+        <v>assets/1785842684502-mnhr0r96eee.jpg</v>
       </c>
       <c r="D35" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E35" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F35" t="str">
-        <v>河北邢台</v>
+        <v/>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -2472,22 +2472,22 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>棕虎斑</v>
+        <v>纯黑色</v>
       </c>
       <c r="B36" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C36" t="str">
-        <v>assets/1785843011477-n3l1wi6ech.jpg</v>
+        <v>assets/1785842779532-5u1j0igrw1s.jpg</v>
       </c>
       <c r="D36" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E36" t="str">
-        <v>2026-06-05</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F36" t="str">
-        <v>四川自贡</v>
+        <v/>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -2531,22 +2531,22 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>蓝虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B37" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C37" t="str">
-        <v>assets/1785843237517-ga449iqess5.jpg</v>
+        <v>assets/1785842817046-6keqv4rw4yf.jpg</v>
       </c>
       <c r="D37" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E37" t="str">
         <v>2026-03-05</v>
       </c>
       <c r="F37" t="str">
-        <v/>
+        <v>韩国</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -2590,22 +2590,22 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>棕虎斑补丁</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B38" t="str">
         <v>妹妹</v>
       </c>
       <c r="C38" t="str">
-        <v>assets/1785842523893-7nwnnhwi4ns.jpg</v>
+        <v>assets/1785842950972-a88lbrskpc.jpg</v>
       </c>
       <c r="D38" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E38" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F38" t="str">
-        <v/>
+        <v>河北邢台</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -2649,22 +2649,22 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B39" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C39" t="str">
-        <v>assets/1785843497557-st27fk8drqi.jpg</v>
+        <v>assets/1785843011477-n3l1wi6ech.jpg</v>
       </c>
       <c r="D39" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E39" t="str">
-        <v>2026-04-05</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F39" t="str">
-        <v/>
+        <v>四川自贡</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -2708,13 +2708,13 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B40" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C40" t="str">
-        <v>assets/1785843621923-ylhakbtw13i.jpg</v>
+        <v>assets/1785843237517-ga449iqess5.jpg</v>
       </c>
       <c r="D40" t="str">
         <v>否</v>
@@ -2767,13 +2767,13 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑补丁</v>
       </c>
       <c r="B41" t="str">
         <v>妹妹</v>
       </c>
       <c r="C41" t="str">
-        <v>assets/1785843663884-sfxvpmiet7.jpg</v>
+        <v>assets/1785842523893-7nwnnhwi4ns.jpg</v>
       </c>
       <c r="D41" t="str">
         <v>否</v>
@@ -2832,46 +2832,46 @@
         <v>妹妹</v>
       </c>
       <c r="C42" t="str">
-        <v>assets/1785852601940-o236xtv7yx.jpeg</v>
+        <v>assets/1785843497557-st27fk8drqi.jpg</v>
       </c>
       <c r="D42" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E42" t="str">
-        <v>2026-02-20</v>
+        <v>2026-04-05</v>
       </c>
       <c r="F42" t="str">
-        <v>荷兰</v>
+        <v/>
       </c>
       <c r="G42" t="str">
-        <v>阿泽</v>
+        <v/>
       </c>
       <c r="H42" t="str">
-        <v>小辫子</v>
+        <v/>
       </c>
       <c r="I42" t="str">
-        <v>驺驺</v>
+        <v/>
       </c>
       <c r="J42" t="str">
-        <v>2026-07-02</v>
+        <v/>
       </c>
       <c r="K42" t="str">
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>2026-07-02</v>
+        <v/>
       </c>
       <c r="M42" t="str">
-        <v>2026-08-03</v>
+        <v/>
       </c>
       <c r="N42" t="str">
-        <v>2026-11-04</v>
+        <v/>
       </c>
       <c r="O42" t="str">
-        <v>2026-08-03 · 血清检测,2026-07-02 · 打疫苗 · assets/diary/zouzou-depart.jpg,2026-07-30 · 6.2斤 · 五个月10天了 · assets/feedback/zouzou-1.jpg</v>
+        <v/>
       </c>
       <c r="P42" t="str">
-        <v>已付定金</v>
+        <v/>
       </c>
       <c r="Q42" t="str">
         <v/>
@@ -2880,27 +2880,27 @@
         <v/>
       </c>
       <c r="S42" t="str">
-        <v>否</v>
+        <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>红虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B43" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C43" t="str">
-        <v>assets/1785853950207-cedor66ou2q.jpeg</v>
+        <v>assets/1785843621923-ylhakbtw13i.jpg</v>
       </c>
       <c r="D43" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E43" t="str">
-        <v/>
+        <v>2026-03-05</v>
       </c>
       <c r="F43" t="str">
-        <v>广东广州</v>
+        <v/>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2944,22 +2944,22 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>红虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B44" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C44" t="str">
-        <v>assets/1785854129383-c8qkvl537x.jpeg</v>
+        <v>assets/1785843663884-sfxvpmiet7.jpg</v>
       </c>
       <c r="D44" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E44" t="str">
-        <v/>
+        <v>2026-03-05</v>
       </c>
       <c r="F44" t="str">
-        <v>广东广州</v>
+        <v/>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -3003,52 +3003,52 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B45" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C45" t="str">
-        <v>assets/1785854166720-48r17hry9cd.jpeg</v>
+        <v>assets/1785852601940-o236xtv7yx.jpeg</v>
       </c>
       <c r="D45" t="str">
         <v>是</v>
       </c>
       <c r="E45" t="str">
-        <v/>
+        <v>2026-02-20</v>
       </c>
       <c r="F45" t="str">
-        <v>山西朔州</v>
+        <v>荷兰</v>
       </c>
       <c r="G45" t="str">
-        <v/>
+        <v>阿泽</v>
       </c>
       <c r="H45" t="str">
-        <v/>
+        <v>小辫子</v>
       </c>
       <c r="I45" t="str">
-        <v/>
+        <v>驺驺</v>
       </c>
       <c r="J45" t="str">
-        <v/>
+        <v>2026-07-02</v>
       </c>
       <c r="K45" t="str">
         <v/>
       </c>
       <c r="L45" t="str">
-        <v/>
+        <v>2026-07-02</v>
       </c>
       <c r="M45" t="str">
-        <v/>
+        <v>2026-08-03</v>
       </c>
       <c r="N45" t="str">
-        <v/>
+        <v>2026-11-04</v>
       </c>
       <c r="O45" t="str">
-        <v/>
+        <v>2026-08-03 · 血清检测,2026-07-02 · 打疫苗 · assets/diary/zouzou-depart.jpg,2026-07-30 · 6.2斤 · 五个月10天了 · assets/feedback/zouzou-1.jpg</v>
       </c>
       <c r="P45" t="str">
-        <v/>
+        <v>已付定金</v>
       </c>
       <c r="Q45" t="str">
         <v/>
@@ -3057,18 +3057,18 @@
         <v/>
       </c>
       <c r="S45" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B46" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C46" t="str">
-        <v>assets/1785854224521-2cpg6xipfn6.jpeg</v>
+        <v>assets/1785853950207-cedor66ou2q.jpeg</v>
       </c>
       <c r="D46" t="str">
         <v>是</v>
@@ -3077,7 +3077,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>浙江宁波</v>
+        <v>广东广州</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -3121,13 +3121,13 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B47" t="str">
         <v>弟弟</v>
       </c>
       <c r="C47" t="str">
-        <v>assets/1785854260793-steez4s972l.jpeg</v>
+        <v>assets/1785854129383-c8qkvl537x.jpeg</v>
       </c>
       <c r="D47" t="str">
         <v>是</v>
@@ -3136,7 +3136,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>陕西西安</v>
+        <v>广东广州</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -3186,7 +3186,7 @@
         <v>弟弟</v>
       </c>
       <c r="C48" t="str">
-        <v>assets/1785854319988-cohio08aod5.jpeg</v>
+        <v>assets/1785854166720-48r17hry9cd.jpeg</v>
       </c>
       <c r="D48" t="str">
         <v>是</v>
@@ -3195,7 +3195,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>黑龙江漠河</v>
+        <v>山西朔州</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -3239,13 +3239,13 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B49" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C49" t="str">
-        <v>assets/1785854520974-96b8b1ekqd9.jpeg</v>
+        <v>assets/1785854224521-2cpg6xipfn6.jpeg</v>
       </c>
       <c r="D49" t="str">
         <v>是</v>
@@ -3254,7 +3254,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>日本</v>
+        <v>浙江宁波</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -3301,10 +3301,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B50" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C50" t="str">
-        <v>assets/1785854664100-haqoiu1h7hj.jpeg</v>
+        <v>assets/1785854260793-steez4s972l.jpeg</v>
       </c>
       <c r="D50" t="str">
         <v>是</v>
@@ -3313,7 +3313,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>浙江杭州</v>
+        <v>陕西西安</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -3360,10 +3360,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B51" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C51" t="str">
-        <v>assets/1785854690732-orrs40sx9rs.jpeg</v>
+        <v>assets/1785854319988-cohio08aod5.jpeg</v>
       </c>
       <c r="D51" t="str">
         <v>是</v>
@@ -3372,7 +3372,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>贵州安顺</v>
+        <v>黑龙江漠河</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -3416,13 +3416,13 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B52" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C52" t="str">
-        <v>assets/1785854734122-wcpmib4m7.jpeg</v>
+        <v>assets/1785854520974-96b8b1ekqd9.jpeg</v>
       </c>
       <c r="D52" t="str">
         <v>是</v>
@@ -3431,7 +3431,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>山东青岛</v>
+        <v>日本</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -3478,10 +3478,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B53" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C53" t="str">
-        <v>assets/1785854758707-1kxdkfvs6jc.jpeg</v>
+        <v>assets/1785854664100-haqoiu1h7hj.jpeg</v>
       </c>
       <c r="D53" t="str">
         <v>是</v>
@@ -3490,7 +3490,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>黑龙江漠河</v>
+        <v>浙江杭州</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -3534,13 +3534,13 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>纯蓝色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B54" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C54" t="str">
-        <v>assets/1785854784780-3g0u60pdo93.jpeg</v>
+        <v>assets/1785854690732-orrs40sx9rs.jpeg</v>
       </c>
       <c r="D54" t="str">
         <v>是</v>
@@ -3549,7 +3549,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>河南鹤壁</v>
+        <v>贵州安顺</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -3596,10 +3596,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B55" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C55" t="str">
-        <v>assets/1785854813179-8oyxr0h2bbu.jpeg</v>
+        <v>assets/1785854734122-wcpmib4m7.jpeg</v>
       </c>
       <c r="D55" t="str">
         <v>是</v>
@@ -3608,7 +3608,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>陕西西安</v>
+        <v>山东青岛</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -3652,13 +3652,13 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B56" t="str">
         <v>弟弟</v>
       </c>
       <c r="C56" t="str">
-        <v>assets/1785854838933-uq6amircyzd.jpeg</v>
+        <v>assets/1785854758707-1kxdkfvs6jc.jpeg</v>
       </c>
       <c r="D56" t="str">
         <v>是</v>
@@ -3667,7 +3667,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>四川成都</v>
+        <v>黑龙江漠河</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>烟灰色</v>
+        <v>纯蓝色</v>
       </c>
       <c r="B57" t="str">
         <v>弟弟</v>
       </c>
       <c r="C57" t="str">
-        <v>assets/1785854869973-za3p6wikqpo.jpeg</v>
+        <v>assets/1785854784780-3g0u60pdo93.jpeg</v>
       </c>
       <c r="D57" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E57" t="str">
-        <v>2026-05-18</v>
+        <v/>
       </c>
       <c r="F57" t="str">
-        <v/>
+        <v>河南鹤壁</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -3776,7 +3776,7 @@
         <v>弟弟</v>
       </c>
       <c r="C58" t="str">
-        <v>assets/1785854997023-mawkallt2a.jpeg</v>
+        <v>assets/1785854813179-8oyxr0h2bbu.jpeg</v>
       </c>
       <c r="D58" t="str">
         <v>是</v>
@@ -3785,7 +3785,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>新加坡</v>
+        <v>陕西西安</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -3829,13 +3829,13 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>凯米尔色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B59" t="str">
         <v>弟弟</v>
       </c>
       <c r="C59" t="str">
-        <v>assets/1785855043327-wdc5pxwm34k.jpeg</v>
+        <v>assets/1785854838933-uq6amircyzd.jpeg</v>
       </c>
       <c r="D59" t="str">
         <v>是</v>
@@ -3844,7 +3844,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>上海浦东</v>
+        <v>四川成都</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -3888,22 +3888,22 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>棕虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B60" t="str">
         <v>弟弟</v>
       </c>
       <c r="C60" t="str">
-        <v>assets/1785912551260-jplefm937nk.jpeg, assets/videos/02.mp4</v>
+        <v>assets/1785854869973-za3p6wikqpo.jpeg</v>
       </c>
       <c r="D60" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E60" t="str">
-        <v>2026-06-06</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F60" t="str">
-        <v>浙江温州</v>
+        <v/>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -3947,66 +3947,243 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
+        <v>银虎斑</v>
+      </c>
+      <c r="B61" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C61" t="str">
+        <v>assets/1785854997023-mawkallt2a.jpeg</v>
+      </c>
+      <c r="D61" t="str">
+        <v>是</v>
+      </c>
+      <c r="E61" t="str">
+        <v/>
+      </c>
+      <c r="F61" t="str">
+        <v>新加坡</v>
+      </c>
+      <c r="G61" t="str">
+        <v/>
+      </c>
+      <c r="H61" t="str">
+        <v/>
+      </c>
+      <c r="I61" t="str">
+        <v/>
+      </c>
+      <c r="J61" t="str">
+        <v/>
+      </c>
+      <c r="K61" t="str">
+        <v/>
+      </c>
+      <c r="L61" t="str">
+        <v/>
+      </c>
+      <c r="M61" t="str">
+        <v/>
+      </c>
+      <c r="N61" t="str">
+        <v/>
+      </c>
+      <c r="O61" t="str">
+        <v/>
+      </c>
+      <c r="P61" t="str">
+        <v/>
+      </c>
+      <c r="Q61" t="str">
+        <v/>
+      </c>
+      <c r="R61" t="str">
+        <v/>
+      </c>
+      <c r="S61" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>凯米尔色</v>
+      </c>
+      <c r="B62" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C62" t="str">
+        <v>assets/1785855043327-wdc5pxwm34k.jpeg</v>
+      </c>
+      <c r="D62" t="str">
+        <v>是</v>
+      </c>
+      <c r="E62" t="str">
+        <v/>
+      </c>
+      <c r="F62" t="str">
+        <v>上海浦东</v>
+      </c>
+      <c r="G62" t="str">
+        <v/>
+      </c>
+      <c r="H62" t="str">
+        <v/>
+      </c>
+      <c r="I62" t="str">
+        <v/>
+      </c>
+      <c r="J62" t="str">
+        <v/>
+      </c>
+      <c r="K62" t="str">
+        <v/>
+      </c>
+      <c r="L62" t="str">
+        <v/>
+      </c>
+      <c r="M62" t="str">
+        <v/>
+      </c>
+      <c r="N62" t="str">
+        <v/>
+      </c>
+      <c r="O62" t="str">
+        <v/>
+      </c>
+      <c r="P62" t="str">
+        <v/>
+      </c>
+      <c r="Q62" t="str">
+        <v/>
+      </c>
+      <c r="R62" t="str">
+        <v/>
+      </c>
+      <c r="S62" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
         <v>棕虎斑</v>
       </c>
-      <c r="B61" t="str">
+      <c r="B63" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C63" t="str">
+        <v>assets/1785912551260-jplefm937nk.jpeg, assets/videos/02.mp4</v>
+      </c>
+      <c r="D63" t="str">
+        <v>是</v>
+      </c>
+      <c r="E63" t="str">
+        <v>2026-06-06</v>
+      </c>
+      <c r="F63" t="str">
+        <v>浙江温州</v>
+      </c>
+      <c r="G63" t="str">
+        <v/>
+      </c>
+      <c r="H63" t="str">
+        <v/>
+      </c>
+      <c r="I63" t="str">
+        <v/>
+      </c>
+      <c r="J63" t="str">
+        <v/>
+      </c>
+      <c r="K63" t="str">
+        <v/>
+      </c>
+      <c r="L63" t="str">
+        <v/>
+      </c>
+      <c r="M63" t="str">
+        <v/>
+      </c>
+      <c r="N63" t="str">
+        <v/>
+      </c>
+      <c r="O63" t="str">
+        <v/>
+      </c>
+      <c r="P63" t="str">
+        <v/>
+      </c>
+      <c r="Q63" t="str">
+        <v/>
+      </c>
+      <c r="R63" t="str">
+        <v/>
+      </c>
+      <c r="S63" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>棕虎斑</v>
+      </c>
+      <c r="B64" t="str">
         <v>妹妹</v>
       </c>
-      <c r="C61" t="str">
+      <c r="C64" t="str">
         <v>assets/1785912694000-m20f5kvvrr.jpeg</v>
       </c>
-      <c r="D61" t="str">
+      <c r="D64" t="str">
         <v>否</v>
       </c>
-      <c r="E61" t="str">
+      <c r="E64" t="str">
         <v>2026-06-06</v>
       </c>
-      <c r="F61" t="str">
-        <v/>
-      </c>
-      <c r="G61" t="str">
-        <v/>
-      </c>
-      <c r="H61" t="str">
-        <v/>
-      </c>
-      <c r="I61" t="str">
-        <v/>
-      </c>
-      <c r="J61" t="str">
-        <v/>
-      </c>
-      <c r="K61" t="str">
-        <v/>
-      </c>
-      <c r="L61" t="str">
-        <v/>
-      </c>
-      <c r="M61" t="str">
-        <v/>
-      </c>
-      <c r="N61" t="str">
-        <v/>
-      </c>
-      <c r="O61" t="str">
-        <v/>
-      </c>
-      <c r="P61" t="str">
-        <v/>
-      </c>
-      <c r="Q61" t="str">
-        <v/>
-      </c>
-      <c r="R61" t="str">
-        <v/>
-      </c>
-      <c r="S61" t="str">
+      <c r="F64" t="str">
+        <v/>
+      </c>
+      <c r="G64" t="str">
+        <v/>
+      </c>
+      <c r="H64" t="str">
+        <v/>
+      </c>
+      <c r="I64" t="str">
+        <v/>
+      </c>
+      <c r="J64" t="str">
+        <v/>
+      </c>
+      <c r="K64" t="str">
+        <v/>
+      </c>
+      <c r="L64" t="str">
+        <v/>
+      </c>
+      <c r="M64" t="str">
+        <v/>
+      </c>
+      <c r="N64" t="str">
+        <v/>
+      </c>
+      <c r="O64" t="str">
+        <v/>
+      </c>
+      <c r="P64" t="str">
+        <v/>
+      </c>
+      <c r="Q64" t="str">
+        <v/>
+      </c>
+      <c r="R64" t="str">
+        <v/>
+      </c>
+      <c r="S64" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S61"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S64"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S64"/>
+  <dimension ref="A1:S74"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -469,10 +469,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B2" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C2" t="str">
-        <v>assets/1787318867999-3gxdddp72x.jpg</v>
+        <v>assets/1787319975814-g1pfa56vfp.jpg</v>
       </c>
       <c r="D2" t="str">
         <v>是</v>
@@ -481,7 +481,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>广东广州</v>
+        <v>浙江宁波</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -528,10 +528,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B3" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C3" t="str">
-        <v>assets/1787318609722-0ojb3aikwi.jpg</v>
+        <v>assets/1787319800704-v3qeu062ak.jpg</v>
       </c>
       <c r="D3" t="str">
         <v>是</v>
@@ -540,7 +540,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>黑龙江鹤岗</v>
+        <v>河北唐山</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -584,13 +584,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>蓝虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B4" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C4" t="str">
-        <v>assets/1787318530612-779fbkfcoi.jpg</v>
+        <v>assets/1787319745369-zn66xr3bvb.jpg</v>
       </c>
       <c r="D4" t="str">
         <v>是</v>
@@ -599,7 +599,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>天津</v>
+        <v>河北石家庄</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -643,13 +643,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>银虎斑</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B5" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C5" t="str">
-        <v>assets/1787318365475-sj87wtsai3.jpg</v>
+        <v>assets/1787319547969-zqlq35fxxt.jpg</v>
       </c>
       <c r="D5" t="str">
         <v>是</v>
@@ -658,7 +658,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>山西朔州</v>
+        <v>韩国</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -688,7 +688,7 @@
         <v/>
       </c>
       <c r="P5" t="str">
-        <v>已接猫</v>
+        <v/>
       </c>
       <c r="Q5" t="str">
         <v/>
@@ -702,13 +702,13 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>银虎斑</v>
+        <v>蓝银虎斑</v>
       </c>
       <c r="B6" t="str">
         <v>妹妹</v>
       </c>
       <c r="C6" t="str">
-        <v>assets/1787318326155-ia4noopjhq.jpg</v>
+        <v>assets/1787319501376-xscwljnu1j.jpg</v>
       </c>
       <c r="D6" t="str">
         <v>是</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>贵州</v>
+        <v>美国</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -764,196 +764,196 @@
         <v>棕虎斑</v>
       </c>
       <c r="B7" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C7" t="str">
-        <v>assets/1787304479674-w0trechn4p.jpg</v>
+        <v>assets/1787319443529-4a0zqikufx.jpg</v>
       </c>
       <c r="D7" t="str">
+        <v>是</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v>中国台湾</v>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v/>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v/>
+      </c>
+      <c r="M7" t="str">
+        <v/>
+      </c>
+      <c r="N7" t="str">
+        <v/>
+      </c>
+      <c r="O7" t="str">
+        <v/>
+      </c>
+      <c r="P7" t="str">
+        <v/>
+      </c>
+      <c r="Q7" t="str">
+        <v/>
+      </c>
+      <c r="R7" t="str">
+        <v/>
+      </c>
+      <c r="S7" t="str">
         <v>否</v>
-      </c>
-      <c r="E7" t="str">
-        <v>2026-06-06</v>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v/>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v/>
-      </c>
-      <c r="M7" t="str">
-        <v/>
-      </c>
-      <c r="N7" t="str">
-        <v/>
-      </c>
-      <c r="O7" t="str">
-        <v/>
-      </c>
-      <c r="P7" t="str">
-        <v/>
-      </c>
-      <c r="Q7" t="str">
-        <v/>
-      </c>
-      <c r="R7" t="str">
-        <v/>
-      </c>
-      <c r="S7" t="str">
-        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>纯黑色</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B8" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C8" t="str">
-        <v>assets/1787283819124-4v7d1w01la.jpg</v>
+        <v>assets/1787319356194-lr2d5680i9.jpg</v>
       </c>
       <c r="D8" t="str">
+        <v>是</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v>中国台湾</v>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v/>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v/>
+      </c>
+      <c r="M8" t="str">
+        <v/>
+      </c>
+      <c r="N8" t="str">
+        <v/>
+      </c>
+      <c r="O8" t="str">
+        <v/>
+      </c>
+      <c r="P8" t="str">
+        <v/>
+      </c>
+      <c r="Q8" t="str">
+        <v/>
+      </c>
+      <c r="R8" t="str">
+        <v/>
+      </c>
+      <c r="S8" t="str">
         <v>否</v>
-      </c>
-      <c r="E8" t="str">
-        <v>2026-02-20</v>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v/>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v/>
-      </c>
-      <c r="M8" t="str">
-        <v/>
-      </c>
-      <c r="N8" t="str">
-        <v/>
-      </c>
-      <c r="O8" t="str">
-        <v/>
-      </c>
-      <c r="P8" t="str">
-        <v/>
-      </c>
-      <c r="Q8" t="str">
-        <v/>
-      </c>
-      <c r="R8" t="str">
-        <v/>
-      </c>
-      <c r="S8" t="str">
-        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>阴影色NS12</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B9" t="str">
         <v>妹妹</v>
       </c>
       <c r="C9" t="str">
-        <v>assets/1787283212708-jdnyi6ecci.jpg</v>
+        <v>assets/1787319208828-aizqo4blcv.jpg</v>
       </c>
       <c r="D9" t="str">
+        <v>是</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v>山东淄博</v>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v/>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v/>
+      </c>
+      <c r="M9" t="str">
+        <v/>
+      </c>
+      <c r="N9" t="str">
+        <v/>
+      </c>
+      <c r="O9" t="str">
+        <v/>
+      </c>
+      <c r="P9" t="str">
+        <v/>
+      </c>
+      <c r="Q9" t="str">
+        <v/>
+      </c>
+      <c r="R9" t="str">
+        <v/>
+      </c>
+      <c r="S9" t="str">
         <v>否</v>
-      </c>
-      <c r="E9" t="str">
-        <v>2026-05-28</v>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v/>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v/>
-      </c>
-      <c r="M9" t="str">
-        <v/>
-      </c>
-      <c r="N9" t="str">
-        <v/>
-      </c>
-      <c r="O9" t="str">
-        <v/>
-      </c>
-      <c r="P9" t="str">
-        <v/>
-      </c>
-      <c r="Q9" t="str">
-        <v/>
-      </c>
-      <c r="R9" t="str">
-        <v/>
-      </c>
-      <c r="S9" t="str">
-        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>阴影色NS11</v>
+        <v>银虎斑</v>
       </c>
       <c r="B10" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C10" t="str">
-        <v>assets/1787283153501-s2tjg9spwu.jpg</v>
+        <v>assets/1787319162970-cc2v8ovnni.jpg</v>
       </c>
       <c r="D10" t="str">
         <v>是</v>
       </c>
       <c r="E10" t="str">
-        <v>2026-06-15</v>
+        <v/>
       </c>
       <c r="F10" t="str">
-        <v>重庆</v>
+        <v>韩国</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -992,372 +992,372 @@
         <v/>
       </c>
       <c r="S10" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>浅烟灰色</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B11" t="str">
         <v>妹妹</v>
       </c>
       <c r="C11" t="str">
-        <v>assets/1787283092677-i4d8tyrjtf.jpg</v>
+        <v>assets/1787319098214-8pwa9yx2wc.jpg</v>
       </c>
       <c r="D11" t="str">
+        <v>是</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v>四川成都</v>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v/>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v/>
+      </c>
+      <c r="M11" t="str">
+        <v/>
+      </c>
+      <c r="N11" t="str">
+        <v/>
+      </c>
+      <c r="O11" t="str">
+        <v/>
+      </c>
+      <c r="P11" t="str">
+        <v/>
+      </c>
+      <c r="Q11" t="str">
+        <v/>
+      </c>
+      <c r="R11" t="str">
+        <v/>
+      </c>
+      <c r="S11" t="str">
         <v>否</v>
-      </c>
-      <c r="E11" t="str">
-        <v>2026-03-21</v>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <v/>
-      </c>
-      <c r="J11" t="str">
-        <v/>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str">
-        <v/>
-      </c>
-      <c r="M11" t="str">
-        <v/>
-      </c>
-      <c r="N11" t="str">
-        <v/>
-      </c>
-      <c r="O11" t="str">
-        <v/>
-      </c>
-      <c r="P11" t="str">
-        <v/>
-      </c>
-      <c r="Q11" t="str">
-        <v/>
-      </c>
-      <c r="R11" t="str">
-        <v/>
-      </c>
-      <c r="S11" t="str">
-        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B12" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C12" t="str">
-        <v>assets/1787283031104-bpyq9wy2tl.jpg</v>
+        <v>assets/1787318867999-3gxdddp72x.jpg</v>
       </c>
       <c r="D12" t="str">
+        <v>是</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v>广东广州</v>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v/>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v/>
+      </c>
+      <c r="M12" t="str">
+        <v/>
+      </c>
+      <c r="N12" t="str">
+        <v/>
+      </c>
+      <c r="O12" t="str">
+        <v/>
+      </c>
+      <c r="P12" t="str">
+        <v/>
+      </c>
+      <c r="Q12" t="str">
+        <v/>
+      </c>
+      <c r="R12" t="str">
+        <v/>
+      </c>
+      <c r="S12" t="str">
         <v>否</v>
-      </c>
-      <c r="E12" t="str">
-        <v>2026-06-06</v>
-      </c>
-      <c r="F12" t="str">
-        <v/>
-      </c>
-      <c r="G12" t="str">
-        <v/>
-      </c>
-      <c r="H12" t="str">
-        <v/>
-      </c>
-      <c r="I12" t="str">
-        <v/>
-      </c>
-      <c r="J12" t="str">
-        <v/>
-      </c>
-      <c r="K12" t="str">
-        <v/>
-      </c>
-      <c r="L12" t="str">
-        <v/>
-      </c>
-      <c r="M12" t="str">
-        <v/>
-      </c>
-      <c r="N12" t="str">
-        <v/>
-      </c>
-      <c r="O12" t="str">
-        <v/>
-      </c>
-      <c r="P12" t="str">
-        <v/>
-      </c>
-      <c r="Q12" t="str">
-        <v/>
-      </c>
-      <c r="R12" t="str">
-        <v/>
-      </c>
-      <c r="S12" t="str">
-        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B13" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C13" t="str">
-        <v>assets/1787282991501-2fjfws0rqw.jpg</v>
+        <v>assets/1787318609722-0ojb3aikwi.jpg</v>
       </c>
       <c r="D13" t="str">
+        <v>是</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v>黑龙江鹤岗</v>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v/>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v/>
+      </c>
+      <c r="M13" t="str">
+        <v/>
+      </c>
+      <c r="N13" t="str">
+        <v/>
+      </c>
+      <c r="O13" t="str">
+        <v/>
+      </c>
+      <c r="P13" t="str">
+        <v/>
+      </c>
+      <c r="Q13" t="str">
+        <v/>
+      </c>
+      <c r="R13" t="str">
+        <v/>
+      </c>
+      <c r="S13" t="str">
         <v>否</v>
-      </c>
-      <c r="E13" t="str">
-        <v>2026-06-06</v>
-      </c>
-      <c r="F13" t="str">
-        <v/>
-      </c>
-      <c r="G13" t="str">
-        <v/>
-      </c>
-      <c r="H13" t="str">
-        <v/>
-      </c>
-      <c r="I13" t="str">
-        <v/>
-      </c>
-      <c r="J13" t="str">
-        <v/>
-      </c>
-      <c r="K13" t="str">
-        <v/>
-      </c>
-      <c r="L13" t="str">
-        <v/>
-      </c>
-      <c r="M13" t="str">
-        <v/>
-      </c>
-      <c r="N13" t="str">
-        <v/>
-      </c>
-      <c r="O13" t="str">
-        <v/>
-      </c>
-      <c r="P13" t="str">
-        <v/>
-      </c>
-      <c r="Q13" t="str">
-        <v/>
-      </c>
-      <c r="R13" t="str">
-        <v/>
-      </c>
-      <c r="S13" t="str">
-        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>棕虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B14" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C14" t="str">
-        <v>assets/1787282942262-syr48fym6c.jpg</v>
+        <v>assets/1787318530612-779fbkfcoi.jpg</v>
       </c>
       <c r="D14" t="str">
+        <v>是</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v>天津</v>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v/>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v/>
+      </c>
+      <c r="M14" t="str">
+        <v/>
+      </c>
+      <c r="N14" t="str">
+        <v/>
+      </c>
+      <c r="O14" t="str">
+        <v/>
+      </c>
+      <c r="P14" t="str">
+        <v/>
+      </c>
+      <c r="Q14" t="str">
+        <v/>
+      </c>
+      <c r="R14" t="str">
+        <v/>
+      </c>
+      <c r="S14" t="str">
         <v>否</v>
-      </c>
-      <c r="E14" t="str">
-        <v>2026-06-15</v>
-      </c>
-      <c r="F14" t="str">
-        <v/>
-      </c>
-      <c r="G14" t="str">
-        <v/>
-      </c>
-      <c r="H14" t="str">
-        <v/>
-      </c>
-      <c r="I14" t="str">
-        <v/>
-      </c>
-      <c r="J14" t="str">
-        <v/>
-      </c>
-      <c r="K14" t="str">
-        <v/>
-      </c>
-      <c r="L14" t="str">
-        <v/>
-      </c>
-      <c r="M14" t="str">
-        <v/>
-      </c>
-      <c r="N14" t="str">
-        <v/>
-      </c>
-      <c r="O14" t="str">
-        <v/>
-      </c>
-      <c r="P14" t="str">
-        <v/>
-      </c>
-      <c r="Q14" t="str">
-        <v/>
-      </c>
-      <c r="R14" t="str">
-        <v/>
-      </c>
-      <c r="S14" t="str">
-        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B15" t="str">
         <v>弟弟</v>
       </c>
       <c r="C15" t="str">
-        <v>assets/1787282819855-7vhx3m0v40.jpg</v>
+        <v>assets/1787318365475-sj87wtsai3.jpg</v>
       </c>
       <c r="D15" t="str">
+        <v>是</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v>山西朔州</v>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v/>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v/>
+      </c>
+      <c r="M15" t="str">
+        <v/>
+      </c>
+      <c r="N15" t="str">
+        <v/>
+      </c>
+      <c r="O15" t="str">
+        <v/>
+      </c>
+      <c r="P15" t="str">
+        <v>已接猫</v>
+      </c>
+      <c r="Q15" t="str">
+        <v/>
+      </c>
+      <c r="R15" t="str">
+        <v/>
+      </c>
+      <c r="S15" t="str">
         <v>否</v>
-      </c>
-      <c r="E15" t="str">
-        <v>2026-06-06</v>
-      </c>
-      <c r="F15" t="str">
-        <v/>
-      </c>
-      <c r="G15" t="str">
-        <v/>
-      </c>
-      <c r="H15" t="str">
-        <v/>
-      </c>
-      <c r="I15" t="str">
-        <v/>
-      </c>
-      <c r="J15" t="str">
-        <v/>
-      </c>
-      <c r="K15" t="str">
-        <v/>
-      </c>
-      <c r="L15" t="str">
-        <v/>
-      </c>
-      <c r="M15" t="str">
-        <v/>
-      </c>
-      <c r="N15" t="str">
-        <v/>
-      </c>
-      <c r="O15" t="str">
-        <v/>
-      </c>
-      <c r="P15" t="str">
-        <v/>
-      </c>
-      <c r="Q15" t="str">
-        <v/>
-      </c>
-      <c r="R15" t="str">
-        <v/>
-      </c>
-      <c r="S15" t="str">
-        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B16" t="str">
         <v>妹妹</v>
       </c>
       <c r="C16" t="str">
-        <v>assets/1787282703381-2uakw592b4.jpg</v>
+        <v>assets/1787318326155-ia4noopjhq.jpg</v>
       </c>
       <c r="D16" t="str">
+        <v>是</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v>贵州</v>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v/>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
+        <v/>
+      </c>
+      <c r="M16" t="str">
+        <v/>
+      </c>
+      <c r="N16" t="str">
+        <v/>
+      </c>
+      <c r="O16" t="str">
+        <v/>
+      </c>
+      <c r="P16" t="str">
+        <v/>
+      </c>
+      <c r="Q16" t="str">
+        <v/>
+      </c>
+      <c r="R16" t="str">
+        <v/>
+      </c>
+      <c r="S16" t="str">
         <v>否</v>
-      </c>
-      <c r="E16" t="str">
-        <v>2026-06-06</v>
-      </c>
-      <c r="F16" t="str">
-        <v/>
-      </c>
-      <c r="G16" t="str">
-        <v/>
-      </c>
-      <c r="H16" t="str">
-        <v/>
-      </c>
-      <c r="I16" t="str">
-        <v/>
-      </c>
-      <c r="J16" t="str">
-        <v/>
-      </c>
-      <c r="K16" t="str">
-        <v/>
-      </c>
-      <c r="L16" t="str">
-        <v/>
-      </c>
-      <c r="M16" t="str">
-        <v/>
-      </c>
-      <c r="N16" t="str">
-        <v/>
-      </c>
-      <c r="O16" t="str">
-        <v/>
-      </c>
-      <c r="P16" t="str">
-        <v/>
-      </c>
-      <c r="Q16" t="str">
-        <v/>
-      </c>
-      <c r="R16" t="str">
-        <v/>
-      </c>
-      <c r="S16" t="str">
-        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B17" t="str">
         <v>弟弟</v>
       </c>
       <c r="C17" t="str">
-        <v>assets/1787282649397-9hc31ncrpc.jpg</v>
+        <v>assets/1787304479674-w0trechn4p.jpg</v>
       </c>
       <c r="D17" t="str">
         <v>否</v>
@@ -1410,19 +1410,19 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>烟灰色</v>
+        <v>纯黑色</v>
       </c>
       <c r="B18" t="str">
         <v>妹妹</v>
       </c>
       <c r="C18" t="str">
-        <v>assets/1787282617957-svcoyyznpg.jpg</v>
+        <v>assets/1787283819124-4v7d1w01la.jpg</v>
       </c>
       <c r="D18" t="str">
         <v>否</v>
       </c>
       <c r="E18" t="str">
-        <v>2026-06-06</v>
+        <v>2026-02-20</v>
       </c>
       <c r="F18" t="str">
         <v/>
@@ -1469,19 +1469,19 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>烟灰色</v>
+        <v>阴影色NS12</v>
       </c>
       <c r="B19" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C19" t="str">
-        <v>assets/1787282419632-78nixqjzua.jpg</v>
+        <v>assets/1787283212708-jdnyi6ecci.jpg</v>
       </c>
       <c r="D19" t="str">
         <v>否</v>
       </c>
       <c r="E19" t="str">
-        <v>2026-06-06</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F19" t="str">
         <v/>
@@ -1528,22 +1528,22 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>纯黑色</v>
+        <v>阴影色NS11</v>
       </c>
       <c r="B20" t="str">
         <v>弟弟</v>
       </c>
       <c r="C20" t="str">
-        <v>assets/1787282349942-2cfuyn7xlc.jpg</v>
+        <v>assets/1787283153501-s2tjg9spwu.jpg</v>
       </c>
       <c r="D20" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E20" t="str">
-        <v>2026-03-21</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F20" t="str">
-        <v/>
+        <v>重庆</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1587,19 +1587,19 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>银虎斑</v>
+        <v>浅烟灰色</v>
       </c>
       <c r="B21" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C21" t="str">
-        <v>assets/1787282064159-6b4z8c5msd.jpg</v>
+        <v>assets/1787283092677-i4d8tyrjtf.jpg</v>
       </c>
       <c r="D21" t="str">
         <v>否</v>
       </c>
       <c r="E21" t="str">
-        <v>2026-06-10</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F21" t="str">
         <v/>
@@ -1646,19 +1646,19 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>阴影色NS11</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B22" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C22" t="str">
-        <v>assets/1787280590041-vzcwebdok1.jpg</v>
+        <v>assets/1787283031104-bpyq9wy2tl.jpg</v>
       </c>
       <c r="D22" t="str">
         <v>否</v>
       </c>
       <c r="E22" t="str">
-        <v>2026-05-28</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F22" t="str">
         <v/>
@@ -1705,19 +1705,19 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>浅色银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B23" t="str">
         <v>妹妹</v>
       </c>
       <c r="C23" t="str">
-        <v>assets/1787281786169-9ia0h837ct.jpg</v>
+        <v>assets/1787282991501-2fjfws0rqw.jpg</v>
       </c>
       <c r="D23" t="str">
         <v>否</v>
       </c>
       <c r="E23" t="str">
-        <v>2026-06-15</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F23" t="str">
         <v/>
@@ -1764,22 +1764,22 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>浅烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B24" t="str">
         <v>妹妹</v>
       </c>
       <c r="C24" t="str">
-        <v>assets/1785843720843-63qz159daui.jpg</v>
+        <v>assets/1787282942262-syr48fym6c.jpg</v>
       </c>
       <c r="D24" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E24" t="str">
-        <v>2026-03-21</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F24" t="str">
-        <v>四川成都</v>
+        <v/>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1823,22 +1823,22 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>凯米尔色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B25" t="str">
         <v>弟弟</v>
       </c>
       <c r="C25" t="str">
-        <v>assets/1787301984056-iu6afro5z5.jpg, assets/1785843763310-elg05ur61ri.jpg</v>
+        <v>assets/1787282819855-7vhx3m0v40.jpg</v>
       </c>
       <c r="D25" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E25" t="str">
-        <v>2026-02-14</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F25" t="str">
-        <v>上海浦东</v>
+        <v/>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1882,19 +1882,19 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>银虎斑补丁</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B26" t="str">
         <v>妹妹</v>
       </c>
       <c r="C26" t="str">
-        <v>assets/1785843820715-9kz7gy4mbr7.jpg</v>
+        <v>assets/1787282703381-2uakw592b4.jpg</v>
       </c>
       <c r="D26" t="str">
         <v>否</v>
       </c>
       <c r="E26" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F26" t="str">
         <v/>
@@ -1947,13 +1947,13 @@
         <v>弟弟</v>
       </c>
       <c r="C27" t="str">
-        <v>assets/1785843953805-mxl3x1982io.jpg</v>
+        <v>assets/1787282649397-9hc31ncrpc.jpg</v>
       </c>
       <c r="D27" t="str">
         <v>否</v>
       </c>
       <c r="E27" t="str">
-        <v>2026-05-18</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F27" t="str">
         <v/>
@@ -2000,19 +2000,19 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>棕虎斑玳瑁</v>
+        <v>烟灰色</v>
       </c>
       <c r="B28" t="str">
         <v>妹妹</v>
       </c>
       <c r="C28" t="str">
-        <v>assets/1785844013835-ek4xpcje7kh.jpg</v>
+        <v>assets/1787282617957-svcoyyznpg.jpg</v>
       </c>
       <c r="D28" t="str">
         <v>否</v>
       </c>
       <c r="E28" t="str">
-        <v>2026-02-14</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F28" t="str">
         <v/>
@@ -2059,19 +2059,19 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>银虎斑补丁</v>
+        <v>烟灰色</v>
       </c>
       <c r="B29" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C29" t="str">
-        <v>assets/1785844434338-ek5zbdgdcne.jpg</v>
+        <v>assets/1787282419632-78nixqjzua.jpg</v>
       </c>
       <c r="D29" t="str">
         <v>否</v>
       </c>
       <c r="E29" t="str">
-        <v>2026-05-24</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F29" t="str">
         <v/>
@@ -2118,22 +2118,22 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>银虎斑</v>
+        <v>纯黑色</v>
       </c>
       <c r="B30" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C30" t="str">
-        <v>assets/1785838787730-s5f333sc3u.jpg</v>
+        <v>assets/1787282349942-2cfuyn7xlc.jpg</v>
       </c>
       <c r="D30" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E30" t="str">
-        <v>2026-06-05</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F30" t="str">
-        <v>湖北恩施</v>
+        <v/>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -2183,16 +2183,16 @@
         <v>弟弟</v>
       </c>
       <c r="C31" t="str">
-        <v>assets/1785842296661-6qw3zs3as8h.jpg</v>
+        <v>assets/1787282064159-6b4z8c5msd.jpg</v>
       </c>
       <c r="D31" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E31" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-10</v>
       </c>
       <c r="F31" t="str">
-        <v>湖北恩施</v>
+        <v/>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -2236,22 +2236,22 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>银虎斑</v>
+        <v>阴影色NS11</v>
       </c>
       <c r="B32" t="str">
         <v>弟弟</v>
       </c>
       <c r="C32" t="str">
-        <v>assets/1785842429109-porc98rel5.jpg</v>
+        <v>assets/1787280590041-vzcwebdok1.jpg</v>
       </c>
       <c r="D32" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E32" t="str">
-        <v>2025-11-05</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F32" t="str">
-        <v>韩国</v>
+        <v/>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -2295,19 +2295,19 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>银虎斑</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B33" t="str">
         <v>妹妹</v>
       </c>
       <c r="C33" t="str">
-        <v>assets/1785842594141-fcglbzjp509.jpg</v>
+        <v>assets/1787281786169-9ia0h837ct.jpg</v>
       </c>
       <c r="D33" t="str">
         <v>否</v>
       </c>
       <c r="E33" t="str">
-        <v>2026-05-18</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F33" t="str">
         <v/>
@@ -2354,22 +2354,22 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>棕虎斑</v>
+        <v>浅烟灰色</v>
       </c>
       <c r="B34" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C34" t="str">
-        <v>assets/1785842639100-82k775dhwiv.jpg</v>
+        <v>assets/1785843720843-63qz159daui.jpg</v>
       </c>
       <c r="D34" t="str">
         <v>是</v>
       </c>
       <c r="E34" t="str">
-        <v>2026-05-28</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F34" t="str">
-        <v>四川自贡</v>
+        <v>四川成都</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -2413,22 +2413,22 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>棕虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B35" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C35" t="str">
-        <v>assets/1785842684502-mnhr0r96eee.jpg</v>
+        <v>assets/1787301984056-iu6afro5z5.jpg, assets/1785843763310-elg05ur61ri.jpg</v>
       </c>
       <c r="D35" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E35" t="str">
-        <v>2026-06-06</v>
+        <v>2026-02-14</v>
       </c>
       <c r="F35" t="str">
-        <v/>
+        <v>上海浦东</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -2472,13 +2472,13 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>纯黑色</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B36" t="str">
         <v>妹妹</v>
       </c>
       <c r="C36" t="str">
-        <v>assets/1785842779532-5u1j0igrw1s.jpg</v>
+        <v>assets/1785843820715-9kz7gy4mbr7.jpg</v>
       </c>
       <c r="D36" t="str">
         <v>否</v>
@@ -2531,22 +2531,22 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B37" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C37" t="str">
-        <v>assets/1785842817046-6keqv4rw4yf.jpg</v>
+        <v>assets/1785843953805-mxl3x1982io.jpg</v>
       </c>
       <c r="D37" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E37" t="str">
-        <v>2026-03-05</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F37" t="str">
-        <v>韩国</v>
+        <v/>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -2590,22 +2590,22 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>浅色银虎斑</v>
+        <v>棕虎斑玳瑁</v>
       </c>
       <c r="B38" t="str">
         <v>妹妹</v>
       </c>
       <c r="C38" t="str">
-        <v>assets/1785842950972-a88lbrskpc.jpg</v>
+        <v>assets/1785844013835-ek4xpcje7kh.jpg</v>
       </c>
       <c r="D38" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E38" t="str">
-        <v>2026-06-05</v>
+        <v>2026-02-14</v>
       </c>
       <c r="F38" t="str">
-        <v>河北邢台</v>
+        <v/>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -2649,22 +2649,22 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B39" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C39" t="str">
-        <v>assets/1785843011477-n3l1wi6ech.jpg</v>
+        <v>assets/1785844434338-ek5zbdgdcne.jpg</v>
       </c>
       <c r="D39" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E39" t="str">
-        <v>2026-06-05</v>
+        <v>2026-05-24</v>
       </c>
       <c r="F39" t="str">
-        <v>四川自贡</v>
+        <v/>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -2708,22 +2708,22 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>蓝虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B40" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C40" t="str">
-        <v>assets/1785843237517-ga449iqess5.jpg</v>
+        <v>assets/1785838787730-s5f333sc3u.jpg</v>
       </c>
       <c r="D40" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E40" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F40" t="str">
-        <v/>
+        <v>湖北恩施</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -2767,22 +2767,22 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>棕虎斑补丁</v>
+        <v>银虎斑</v>
       </c>
       <c r="B41" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C41" t="str">
-        <v>assets/1785842523893-7nwnnhwi4ns.jpg</v>
+        <v>assets/1785842296661-6qw3zs3as8h.jpg</v>
       </c>
       <c r="D41" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E41" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F41" t="str">
-        <v/>
+        <v>湖北恩施</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -2826,22 +2826,22 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>蓝虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B42" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C42" t="str">
-        <v>assets/1785843497557-st27fk8drqi.jpg</v>
+        <v>assets/1785842429109-porc98rel5.jpg</v>
       </c>
       <c r="D42" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E42" t="str">
-        <v>2026-04-05</v>
+        <v>2025-11-05</v>
       </c>
       <c r="F42" t="str">
-        <v/>
+        <v>韩国</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -2891,13 +2891,13 @@
         <v>妹妹</v>
       </c>
       <c r="C43" t="str">
-        <v>assets/1785843621923-ylhakbtw13i.jpg</v>
+        <v>assets/1785842594141-fcglbzjp509.jpg</v>
       </c>
       <c r="D43" t="str">
         <v>否</v>
       </c>
       <c r="E43" t="str">
-        <v>2026-03-05</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F43" t="str">
         <v/>
@@ -2944,22 +2944,22 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B44" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C44" t="str">
-        <v>assets/1785843663884-sfxvpmiet7.jpg</v>
+        <v>assets/1785842639100-82k775dhwiv.jpg</v>
       </c>
       <c r="D44" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E44" t="str">
-        <v>2026-03-05</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F44" t="str">
-        <v/>
+        <v>四川自贡</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -3003,52 +3003,52 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B45" t="str">
         <v>妹妹</v>
       </c>
       <c r="C45" t="str">
-        <v>assets/1785852601940-o236xtv7yx.jpeg</v>
+        <v>assets/1785842684502-mnhr0r96eee.jpg</v>
       </c>
       <c r="D45" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E45" t="str">
-        <v>2026-02-20</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F45" t="str">
-        <v>荷兰</v>
+        <v/>
       </c>
       <c r="G45" t="str">
-        <v>阿泽</v>
+        <v/>
       </c>
       <c r="H45" t="str">
-        <v>小辫子</v>
+        <v/>
       </c>
       <c r="I45" t="str">
-        <v>驺驺</v>
+        <v/>
       </c>
       <c r="J45" t="str">
-        <v>2026-07-02</v>
+        <v/>
       </c>
       <c r="K45" t="str">
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>2026-07-02</v>
+        <v/>
       </c>
       <c r="M45" t="str">
-        <v>2026-08-03</v>
+        <v/>
       </c>
       <c r="N45" t="str">
-        <v>2026-11-04</v>
+        <v/>
       </c>
       <c r="O45" t="str">
-        <v>2026-08-03 · 血清检测,2026-07-02 · 打疫苗 · assets/diary/zouzou-depart.jpg,2026-07-30 · 6.2斤 · 五个月10天了 · assets/feedback/zouzou-1.jpg</v>
+        <v/>
       </c>
       <c r="P45" t="str">
-        <v>已付定金</v>
+        <v/>
       </c>
       <c r="Q45" t="str">
         <v/>
@@ -3057,27 +3057,27 @@
         <v/>
       </c>
       <c r="S45" t="str">
-        <v>否</v>
+        <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>红虎斑</v>
+        <v>纯黑色</v>
       </c>
       <c r="B46" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C46" t="str">
-        <v>assets/1785853950207-cedor66ou2q.jpeg</v>
+        <v>assets/1785842779532-5u1j0igrw1s.jpg</v>
       </c>
       <c r="D46" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E46" t="str">
-        <v/>
+        <v>2026-03-05</v>
       </c>
       <c r="F46" t="str">
-        <v>广东广州</v>
+        <v/>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>红虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B47" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C47" t="str">
-        <v>assets/1785854129383-c8qkvl537x.jpeg</v>
+        <v>assets/1785842817046-6keqv4rw4yf.jpg</v>
       </c>
       <c r="D47" t="str">
         <v>是</v>
       </c>
       <c r="E47" t="str">
-        <v/>
+        <v>2026-03-05</v>
       </c>
       <c r="F47" t="str">
-        <v>广东广州</v>
+        <v>韩国</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -3180,22 +3180,22 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>银虎斑</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B48" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C48" t="str">
-        <v>assets/1785854166720-48r17hry9cd.jpeg</v>
+        <v>assets/1785842950972-a88lbrskpc.jpg</v>
       </c>
       <c r="D48" t="str">
         <v>是</v>
       </c>
       <c r="E48" t="str">
-        <v/>
+        <v>2026-06-05</v>
       </c>
       <c r="F48" t="str">
-        <v>山西朔州</v>
+        <v>河北邢台</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -3239,22 +3239,22 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B49" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C49" t="str">
-        <v>assets/1785854224521-2cpg6xipfn6.jpeg</v>
+        <v>assets/1785843011477-n3l1wi6ech.jpg</v>
       </c>
       <c r="D49" t="str">
         <v>是</v>
       </c>
       <c r="E49" t="str">
-        <v/>
+        <v>2026-06-05</v>
       </c>
       <c r="F49" t="str">
-        <v>浙江宁波</v>
+        <v>四川自贡</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -3298,22 +3298,22 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B50" t="str">
         <v>弟弟</v>
       </c>
       <c r="C50" t="str">
-        <v>assets/1785854260793-steez4s972l.jpeg</v>
+        <v>assets/1785843237517-ga449iqess5.jpg</v>
       </c>
       <c r="D50" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E50" t="str">
-        <v/>
+        <v>2026-03-05</v>
       </c>
       <c r="F50" t="str">
-        <v>陕西西安</v>
+        <v/>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -3357,22 +3357,22 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑补丁</v>
       </c>
       <c r="B51" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C51" t="str">
-        <v>assets/1785854319988-cohio08aod5.jpeg</v>
+        <v>assets/1785842523893-7nwnnhwi4ns.jpg</v>
       </c>
       <c r="D51" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E51" t="str">
-        <v/>
+        <v>2026-03-05</v>
       </c>
       <c r="F51" t="str">
-        <v>黑龙江漠河</v>
+        <v/>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -3416,22 +3416,22 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>棕虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B52" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C52" t="str">
-        <v>assets/1785854520974-96b8b1ekqd9.jpeg</v>
+        <v>assets/1785843497557-st27fk8drqi.jpg</v>
       </c>
       <c r="D52" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E52" t="str">
-        <v/>
+        <v>2026-04-05</v>
       </c>
       <c r="F52" t="str">
-        <v>日本</v>
+        <v/>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -3481,16 +3481,16 @@
         <v>妹妹</v>
       </c>
       <c r="C53" t="str">
-        <v>assets/1785854664100-haqoiu1h7hj.jpeg</v>
+        <v>assets/1785843621923-ylhakbtw13i.jpg</v>
       </c>
       <c r="D53" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E53" t="str">
-        <v/>
+        <v>2026-03-05</v>
       </c>
       <c r="F53" t="str">
-        <v>浙江杭州</v>
+        <v/>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -3540,16 +3540,16 @@
         <v>妹妹</v>
       </c>
       <c r="C54" t="str">
-        <v>assets/1785854690732-orrs40sx9rs.jpeg</v>
+        <v>assets/1785843663884-sfxvpmiet7.jpg</v>
       </c>
       <c r="D54" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E54" t="str">
-        <v/>
+        <v>2026-03-05</v>
       </c>
       <c r="F54" t="str">
-        <v>贵州安顺</v>
+        <v/>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -3593,52 +3593,52 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B55" t="str">
         <v>妹妹</v>
       </c>
       <c r="C55" t="str">
-        <v>assets/1785854734122-wcpmib4m7.jpeg</v>
+        <v>assets/1785852601940-o236xtv7yx.jpeg</v>
       </c>
       <c r="D55" t="str">
         <v>是</v>
       </c>
       <c r="E55" t="str">
-        <v/>
+        <v>2026-02-20</v>
       </c>
       <c r="F55" t="str">
-        <v>山东青岛</v>
+        <v>荷兰</v>
       </c>
       <c r="G55" t="str">
-        <v/>
+        <v>阿泽</v>
       </c>
       <c r="H55" t="str">
-        <v/>
+        <v>小辫子</v>
       </c>
       <c r="I55" t="str">
-        <v/>
+        <v>驺驺</v>
       </c>
       <c r="J55" t="str">
-        <v/>
+        <v>2026-07-02</v>
       </c>
       <c r="K55" t="str">
         <v/>
       </c>
       <c r="L55" t="str">
-        <v/>
+        <v>2026-07-02</v>
       </c>
       <c r="M55" t="str">
-        <v/>
+        <v>2026-08-03</v>
       </c>
       <c r="N55" t="str">
-        <v/>
+        <v>2026-11-04</v>
       </c>
       <c r="O55" t="str">
-        <v/>
+        <v>2026-08-03 · 血清检测,2026-07-02 · 打疫苗 · assets/diary/zouzou-depart.jpg,2026-07-30 · 6.2斤 · 五个月10天了 · assets/feedback/zouzou-1.jpg</v>
       </c>
       <c r="P55" t="str">
-        <v/>
+        <v>已付定金</v>
       </c>
       <c r="Q55" t="str">
         <v/>
@@ -3647,18 +3647,18 @@
         <v/>
       </c>
       <c r="S55" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B56" t="str">
         <v>弟弟</v>
       </c>
       <c r="C56" t="str">
-        <v>assets/1785854758707-1kxdkfvs6jc.jpeg</v>
+        <v>assets/1785853950207-cedor66ou2q.jpeg</v>
       </c>
       <c r="D56" t="str">
         <v>是</v>
@@ -3667,7 +3667,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>黑龙江漠河</v>
+        <v>广东广州</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -3711,13 +3711,13 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>纯蓝色</v>
+        <v>红虎斑</v>
       </c>
       <c r="B57" t="str">
         <v>弟弟</v>
       </c>
       <c r="C57" t="str">
-        <v>assets/1785854784780-3g0u60pdo93.jpeg</v>
+        <v>assets/1785854129383-c8qkvl537x.jpeg</v>
       </c>
       <c r="D57" t="str">
         <v>是</v>
@@ -3726,7 +3726,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>河南鹤壁</v>
+        <v>广东广州</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -3776,7 +3776,7 @@
         <v>弟弟</v>
       </c>
       <c r="C58" t="str">
-        <v>assets/1785854813179-8oyxr0h2bbu.jpeg</v>
+        <v>assets/1785854166720-48r17hry9cd.jpeg</v>
       </c>
       <c r="D58" t="str">
         <v>是</v>
@@ -3785,7 +3785,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>陕西西安</v>
+        <v>山西朔州</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -3829,13 +3829,13 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B59" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C59" t="str">
-        <v>assets/1785854838933-uq6amircyzd.jpeg</v>
+        <v>assets/1785854224521-2cpg6xipfn6.jpeg</v>
       </c>
       <c r="D59" t="str">
         <v>是</v>
@@ -3844,7 +3844,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>四川成都</v>
+        <v>浙江宁波</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -3888,22 +3888,22 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>烟灰色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B60" t="str">
         <v>弟弟</v>
       </c>
       <c r="C60" t="str">
-        <v>assets/1785854869973-za3p6wikqpo.jpeg</v>
+        <v>assets/1785854260793-steez4s972l.jpeg</v>
       </c>
       <c r="D60" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E60" t="str">
-        <v>2026-05-18</v>
+        <v/>
       </c>
       <c r="F60" t="str">
-        <v/>
+        <v>陕西西安</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -3953,7 +3953,7 @@
         <v>弟弟</v>
       </c>
       <c r="C61" t="str">
-        <v>assets/1785854997023-mawkallt2a.jpeg</v>
+        <v>assets/1785854319988-cohio08aod5.jpeg</v>
       </c>
       <c r="D61" t="str">
         <v>是</v>
@@ -3962,7 +3962,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>新加坡</v>
+        <v>黑龙江漠河</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -4006,13 +4006,13 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>凯米尔色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B62" t="str">
         <v>弟弟</v>
       </c>
       <c r="C62" t="str">
-        <v>assets/1785855043327-wdc5pxwm34k.jpeg</v>
+        <v>assets/1785854520974-96b8b1ekqd9.jpeg</v>
       </c>
       <c r="D62" t="str">
         <v>是</v>
@@ -4021,7 +4021,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>上海浦东</v>
+        <v>日本</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -4065,22 +4065,22 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B63" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C63" t="str">
-        <v>assets/1785912551260-jplefm937nk.jpeg, assets/videos/02.mp4</v>
+        <v>assets/1785854664100-haqoiu1h7hj.jpeg</v>
       </c>
       <c r="D63" t="str">
         <v>是</v>
       </c>
       <c r="E63" t="str">
-        <v>2026-06-06</v>
+        <v/>
       </c>
       <c r="F63" t="str">
-        <v>浙江温州</v>
+        <v>浙江杭州</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -4124,66 +4124,656 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B64" t="str">
         <v>妹妹</v>
       </c>
       <c r="C64" t="str">
+        <v>assets/1785854690732-orrs40sx9rs.jpeg</v>
+      </c>
+      <c r="D64" t="str">
+        <v>是</v>
+      </c>
+      <c r="E64" t="str">
+        <v/>
+      </c>
+      <c r="F64" t="str">
+        <v>贵州安顺</v>
+      </c>
+      <c r="G64" t="str">
+        <v/>
+      </c>
+      <c r="H64" t="str">
+        <v/>
+      </c>
+      <c r="I64" t="str">
+        <v/>
+      </c>
+      <c r="J64" t="str">
+        <v/>
+      </c>
+      <c r="K64" t="str">
+        <v/>
+      </c>
+      <c r="L64" t="str">
+        <v/>
+      </c>
+      <c r="M64" t="str">
+        <v/>
+      </c>
+      <c r="N64" t="str">
+        <v/>
+      </c>
+      <c r="O64" t="str">
+        <v/>
+      </c>
+      <c r="P64" t="str">
+        <v/>
+      </c>
+      <c r="Q64" t="str">
+        <v/>
+      </c>
+      <c r="R64" t="str">
+        <v/>
+      </c>
+      <c r="S64" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>银虎斑</v>
+      </c>
+      <c r="B65" t="str">
+        <v>妹妹</v>
+      </c>
+      <c r="C65" t="str">
+        <v>assets/1785854734122-wcpmib4m7.jpeg</v>
+      </c>
+      <c r="D65" t="str">
+        <v>是</v>
+      </c>
+      <c r="E65" t="str">
+        <v/>
+      </c>
+      <c r="F65" t="str">
+        <v>山东青岛</v>
+      </c>
+      <c r="G65" t="str">
+        <v/>
+      </c>
+      <c r="H65" t="str">
+        <v/>
+      </c>
+      <c r="I65" t="str">
+        <v/>
+      </c>
+      <c r="J65" t="str">
+        <v/>
+      </c>
+      <c r="K65" t="str">
+        <v/>
+      </c>
+      <c r="L65" t="str">
+        <v/>
+      </c>
+      <c r="M65" t="str">
+        <v/>
+      </c>
+      <c r="N65" t="str">
+        <v/>
+      </c>
+      <c r="O65" t="str">
+        <v/>
+      </c>
+      <c r="P65" t="str">
+        <v/>
+      </c>
+      <c r="Q65" t="str">
+        <v/>
+      </c>
+      <c r="R65" t="str">
+        <v/>
+      </c>
+      <c r="S65" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>银虎斑</v>
+      </c>
+      <c r="B66" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C66" t="str">
+        <v>assets/1785854758707-1kxdkfvs6jc.jpeg</v>
+      </c>
+      <c r="D66" t="str">
+        <v>是</v>
+      </c>
+      <c r="E66" t="str">
+        <v/>
+      </c>
+      <c r="F66" t="str">
+        <v>黑龙江漠河</v>
+      </c>
+      <c r="G66" t="str">
+        <v/>
+      </c>
+      <c r="H66" t="str">
+        <v/>
+      </c>
+      <c r="I66" t="str">
+        <v/>
+      </c>
+      <c r="J66" t="str">
+        <v/>
+      </c>
+      <c r="K66" t="str">
+        <v/>
+      </c>
+      <c r="L66" t="str">
+        <v/>
+      </c>
+      <c r="M66" t="str">
+        <v/>
+      </c>
+      <c r="N66" t="str">
+        <v/>
+      </c>
+      <c r="O66" t="str">
+        <v/>
+      </c>
+      <c r="P66" t="str">
+        <v/>
+      </c>
+      <c r="Q66" t="str">
+        <v/>
+      </c>
+      <c r="R66" t="str">
+        <v/>
+      </c>
+      <c r="S66" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>纯蓝色</v>
+      </c>
+      <c r="B67" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C67" t="str">
+        <v>assets/1785854784780-3g0u60pdo93.jpeg</v>
+      </c>
+      <c r="D67" t="str">
+        <v>是</v>
+      </c>
+      <c r="E67" t="str">
+        <v/>
+      </c>
+      <c r="F67" t="str">
+        <v>河南鹤壁</v>
+      </c>
+      <c r="G67" t="str">
+        <v/>
+      </c>
+      <c r="H67" t="str">
+        <v/>
+      </c>
+      <c r="I67" t="str">
+        <v/>
+      </c>
+      <c r="J67" t="str">
+        <v/>
+      </c>
+      <c r="K67" t="str">
+        <v/>
+      </c>
+      <c r="L67" t="str">
+        <v/>
+      </c>
+      <c r="M67" t="str">
+        <v/>
+      </c>
+      <c r="N67" t="str">
+        <v/>
+      </c>
+      <c r="O67" t="str">
+        <v/>
+      </c>
+      <c r="P67" t="str">
+        <v/>
+      </c>
+      <c r="Q67" t="str">
+        <v/>
+      </c>
+      <c r="R67" t="str">
+        <v/>
+      </c>
+      <c r="S67" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>银虎斑</v>
+      </c>
+      <c r="B68" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C68" t="str">
+        <v>assets/1785854813179-8oyxr0h2bbu.jpeg</v>
+      </c>
+      <c r="D68" t="str">
+        <v>是</v>
+      </c>
+      <c r="E68" t="str">
+        <v/>
+      </c>
+      <c r="F68" t="str">
+        <v>陕西西安</v>
+      </c>
+      <c r="G68" t="str">
+        <v/>
+      </c>
+      <c r="H68" t="str">
+        <v/>
+      </c>
+      <c r="I68" t="str">
+        <v/>
+      </c>
+      <c r="J68" t="str">
+        <v/>
+      </c>
+      <c r="K68" t="str">
+        <v/>
+      </c>
+      <c r="L68" t="str">
+        <v/>
+      </c>
+      <c r="M68" t="str">
+        <v/>
+      </c>
+      <c r="N68" t="str">
+        <v/>
+      </c>
+      <c r="O68" t="str">
+        <v/>
+      </c>
+      <c r="P68" t="str">
+        <v/>
+      </c>
+      <c r="Q68" t="str">
+        <v/>
+      </c>
+      <c r="R68" t="str">
+        <v/>
+      </c>
+      <c r="S68" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>棕虎斑</v>
+      </c>
+      <c r="B69" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C69" t="str">
+        <v>assets/1785854838933-uq6amircyzd.jpeg</v>
+      </c>
+      <c r="D69" t="str">
+        <v>是</v>
+      </c>
+      <c r="E69" t="str">
+        <v/>
+      </c>
+      <c r="F69" t="str">
+        <v>四川成都</v>
+      </c>
+      <c r="G69" t="str">
+        <v/>
+      </c>
+      <c r="H69" t="str">
+        <v/>
+      </c>
+      <c r="I69" t="str">
+        <v/>
+      </c>
+      <c r="J69" t="str">
+        <v/>
+      </c>
+      <c r="K69" t="str">
+        <v/>
+      </c>
+      <c r="L69" t="str">
+        <v/>
+      </c>
+      <c r="M69" t="str">
+        <v/>
+      </c>
+      <c r="N69" t="str">
+        <v/>
+      </c>
+      <c r="O69" t="str">
+        <v/>
+      </c>
+      <c r="P69" t="str">
+        <v/>
+      </c>
+      <c r="Q69" t="str">
+        <v/>
+      </c>
+      <c r="R69" t="str">
+        <v/>
+      </c>
+      <c r="S69" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>烟灰色</v>
+      </c>
+      <c r="B70" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C70" t="str">
+        <v>assets/1785854869973-za3p6wikqpo.jpeg</v>
+      </c>
+      <c r="D70" t="str">
+        <v>否</v>
+      </c>
+      <c r="E70" t="str">
+        <v>2026-05-18</v>
+      </c>
+      <c r="F70" t="str">
+        <v/>
+      </c>
+      <c r="G70" t="str">
+        <v/>
+      </c>
+      <c r="H70" t="str">
+        <v/>
+      </c>
+      <c r="I70" t="str">
+        <v/>
+      </c>
+      <c r="J70" t="str">
+        <v/>
+      </c>
+      <c r="K70" t="str">
+        <v/>
+      </c>
+      <c r="L70" t="str">
+        <v/>
+      </c>
+      <c r="M70" t="str">
+        <v/>
+      </c>
+      <c r="N70" t="str">
+        <v/>
+      </c>
+      <c r="O70" t="str">
+        <v/>
+      </c>
+      <c r="P70" t="str">
+        <v/>
+      </c>
+      <c r="Q70" t="str">
+        <v/>
+      </c>
+      <c r="R70" t="str">
+        <v/>
+      </c>
+      <c r="S70" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>银虎斑</v>
+      </c>
+      <c r="B71" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C71" t="str">
+        <v>assets/1785854997023-mawkallt2a.jpeg</v>
+      </c>
+      <c r="D71" t="str">
+        <v>是</v>
+      </c>
+      <c r="E71" t="str">
+        <v/>
+      </c>
+      <c r="F71" t="str">
+        <v>新加坡</v>
+      </c>
+      <c r="G71" t="str">
+        <v/>
+      </c>
+      <c r="H71" t="str">
+        <v/>
+      </c>
+      <c r="I71" t="str">
+        <v/>
+      </c>
+      <c r="J71" t="str">
+        <v/>
+      </c>
+      <c r="K71" t="str">
+        <v/>
+      </c>
+      <c r="L71" t="str">
+        <v/>
+      </c>
+      <c r="M71" t="str">
+        <v/>
+      </c>
+      <c r="N71" t="str">
+        <v/>
+      </c>
+      <c r="O71" t="str">
+        <v/>
+      </c>
+      <c r="P71" t="str">
+        <v/>
+      </c>
+      <c r="Q71" t="str">
+        <v/>
+      </c>
+      <c r="R71" t="str">
+        <v/>
+      </c>
+      <c r="S71" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>凯米尔色</v>
+      </c>
+      <c r="B72" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C72" t="str">
+        <v>assets/1785855043327-wdc5pxwm34k.jpeg</v>
+      </c>
+      <c r="D72" t="str">
+        <v>是</v>
+      </c>
+      <c r="E72" t="str">
+        <v/>
+      </c>
+      <c r="F72" t="str">
+        <v>上海浦东</v>
+      </c>
+      <c r="G72" t="str">
+        <v/>
+      </c>
+      <c r="H72" t="str">
+        <v/>
+      </c>
+      <c r="I72" t="str">
+        <v/>
+      </c>
+      <c r="J72" t="str">
+        <v/>
+      </c>
+      <c r="K72" t="str">
+        <v/>
+      </c>
+      <c r="L72" t="str">
+        <v/>
+      </c>
+      <c r="M72" t="str">
+        <v/>
+      </c>
+      <c r="N72" t="str">
+        <v/>
+      </c>
+      <c r="O72" t="str">
+        <v/>
+      </c>
+      <c r="P72" t="str">
+        <v/>
+      </c>
+      <c r="Q72" t="str">
+        <v/>
+      </c>
+      <c r="R72" t="str">
+        <v/>
+      </c>
+      <c r="S72" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>棕虎斑</v>
+      </c>
+      <c r="B73" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C73" t="str">
+        <v>assets/1785912551260-jplefm937nk.jpeg, assets/videos/02.mp4</v>
+      </c>
+      <c r="D73" t="str">
+        <v>是</v>
+      </c>
+      <c r="E73" t="str">
+        <v>2026-06-06</v>
+      </c>
+      <c r="F73" t="str">
+        <v>浙江温州</v>
+      </c>
+      <c r="G73" t="str">
+        <v/>
+      </c>
+      <c r="H73" t="str">
+        <v/>
+      </c>
+      <c r="I73" t="str">
+        <v/>
+      </c>
+      <c r="J73" t="str">
+        <v/>
+      </c>
+      <c r="K73" t="str">
+        <v/>
+      </c>
+      <c r="L73" t="str">
+        <v/>
+      </c>
+      <c r="M73" t="str">
+        <v/>
+      </c>
+      <c r="N73" t="str">
+        <v/>
+      </c>
+      <c r="O73" t="str">
+        <v/>
+      </c>
+      <c r="P73" t="str">
+        <v/>
+      </c>
+      <c r="Q73" t="str">
+        <v/>
+      </c>
+      <c r="R73" t="str">
+        <v/>
+      </c>
+      <c r="S73" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>棕虎斑</v>
+      </c>
+      <c r="B74" t="str">
+        <v>妹妹</v>
+      </c>
+      <c r="C74" t="str">
         <v>assets/1785912694000-m20f5kvvrr.jpeg</v>
       </c>
-      <c r="D64" t="str">
+      <c r="D74" t="str">
         <v>否</v>
       </c>
-      <c r="E64" t="str">
+      <c r="E74" t="str">
         <v>2026-06-06</v>
       </c>
-      <c r="F64" t="str">
-        <v/>
-      </c>
-      <c r="G64" t="str">
-        <v/>
-      </c>
-      <c r="H64" t="str">
-        <v/>
-      </c>
-      <c r="I64" t="str">
-        <v/>
-      </c>
-      <c r="J64" t="str">
-        <v/>
-      </c>
-      <c r="K64" t="str">
-        <v/>
-      </c>
-      <c r="L64" t="str">
-        <v/>
-      </c>
-      <c r="M64" t="str">
-        <v/>
-      </c>
-      <c r="N64" t="str">
-        <v/>
-      </c>
-      <c r="O64" t="str">
-        <v/>
-      </c>
-      <c r="P64" t="str">
-        <v/>
-      </c>
-      <c r="Q64" t="str">
-        <v/>
-      </c>
-      <c r="R64" t="str">
-        <v/>
-      </c>
-      <c r="S64" t="str">
+      <c r="F74" t="str">
+        <v/>
+      </c>
+      <c r="G74" t="str">
+        <v/>
+      </c>
+      <c r="H74" t="str">
+        <v/>
+      </c>
+      <c r="I74" t="str">
+        <v/>
+      </c>
+      <c r="J74" t="str">
+        <v/>
+      </c>
+      <c r="K74" t="str">
+        <v/>
+      </c>
+      <c r="L74" t="str">
+        <v/>
+      </c>
+      <c r="M74" t="str">
+        <v/>
+      </c>
+      <c r="N74" t="str">
+        <v/>
+      </c>
+      <c r="O74" t="str">
+        <v/>
+      </c>
+      <c r="P74" t="str">
+        <v/>
+      </c>
+      <c r="Q74" t="str">
+        <v/>
+      </c>
+      <c r="R74" t="str">
+        <v/>
+      </c>
+      <c r="S74" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S64"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S74"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S74"/>
+  <dimension ref="A1:S84"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -469,10 +469,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B2" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C2" t="str">
-        <v>assets/1787319975814-g1pfa56vfp.jpg</v>
+        <v>assets/1787321989528-7d6liuhuk9.jpg</v>
       </c>
       <c r="D2" t="str">
         <v>是</v>
@@ -481,7 +481,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>浙江宁波</v>
+        <v>陕西西安</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -528,10 +528,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B3" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C3" t="str">
-        <v>assets/1787319800704-v3qeu062ak.jpg</v>
+        <v>assets/1787321941642-xlrc1no2ua.jpg</v>
       </c>
       <c r="D3" t="str">
         <v>是</v>
@@ -540,7 +540,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>河北唐山</v>
+        <v>山东东营</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -584,13 +584,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>银虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B4" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C4" t="str">
-        <v>assets/1787319745369-zn66xr3bvb.jpg</v>
+        <v>assets/1787321903535-6orj7qcgzn.jpg</v>
       </c>
       <c r="D4" t="str">
         <v>是</v>
@@ -599,7 +599,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>河北石家庄</v>
+        <v>中国台湾</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -643,13 +643,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>棕虎补丁</v>
+        <v>烟灰色</v>
       </c>
       <c r="B5" t="str">
         <v>妹妹</v>
       </c>
       <c r="C5" t="str">
-        <v>assets/1787319547969-zqlq35fxxt.jpg</v>
+        <v>assets/1787321858985-v4qej7cq7g.jpg</v>
       </c>
       <c r="D5" t="str">
         <v>是</v>
@@ -658,7 +658,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>韩国</v>
+        <v>中国台湾</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -702,13 +702,13 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>蓝银虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B6" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C6" t="str">
-        <v>assets/1787319501376-xscwljnu1j.jpg</v>
+        <v>assets/1787321834306-efgnyhujon.jpg</v>
       </c>
       <c r="D6" t="str">
         <v>是</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>美国</v>
+        <v>北京</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -761,13 +761,13 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B7" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C7" t="str">
-        <v>assets/1787319443529-4a0zqikufx.jpg</v>
+        <v>assets/1787321439916-uttgpbkogb.jpg</v>
       </c>
       <c r="D7" t="str">
         <v>是</v>
@@ -776,7 +776,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>中国台湾</v>
+        <v>安徽合肥</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -820,13 +820,13 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>蓝虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B8" t="str">
         <v>弟弟</v>
       </c>
       <c r="C8" t="str">
-        <v>assets/1787319356194-lr2d5680i9.jpg</v>
+        <v>assets/1787321419210-51hhgurygq.jpg</v>
       </c>
       <c r="D8" t="str">
         <v>是</v>
@@ -835,7 +835,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>中国台湾</v>
+        <v>上海</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -879,13 +879,13 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>棕虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B9" t="str">
         <v>妹妹</v>
       </c>
       <c r="C9" t="str">
-        <v>assets/1787319208828-aizqo4blcv.jpg</v>
+        <v>assets/1787321363369-bzjn51j5il.jpg</v>
       </c>
       <c r="D9" t="str">
         <v>是</v>
@@ -894,7 +894,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>山东淄博</v>
+        <v>中国台湾</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -938,13 +938,13 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B10" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C10" t="str">
-        <v>assets/1787319162970-cc2v8ovnni.jpg</v>
+        <v>assets/1787321332559-87p6spuch3.jpg</v>
       </c>
       <c r="D10" t="str">
         <v>是</v>
@@ -953,7 +953,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>韩国</v>
+        <v>中国台湾</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -997,13 +997,13 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>棕虎补丁</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B11" t="str">
         <v>妹妹</v>
       </c>
       <c r="C11" t="str">
-        <v>assets/1787319098214-8pwa9yx2wc.jpg</v>
+        <v>assets/1787321232531-59lnzv8y98.jpg</v>
       </c>
       <c r="D11" t="str">
         <v>是</v>
@@ -1012,7 +1012,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>四川成都</v>
+        <v>北京</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -1059,10 +1059,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B12" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C12" t="str">
-        <v>assets/1787318867999-3gxdddp72x.jpg</v>
+        <v>assets/1787319975814-g1pfa56vfp.jpg</v>
       </c>
       <c r="D12" t="str">
         <v>是</v>
@@ -1071,7 +1071,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>广东广州</v>
+        <v>浙江宁波</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -1118,10 +1118,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B13" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C13" t="str">
-        <v>assets/1787318609722-0ojb3aikwi.jpg</v>
+        <v>assets/1787319800704-v3qeu062ak.jpg</v>
       </c>
       <c r="D13" t="str">
         <v>是</v>
@@ -1130,7 +1130,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>黑龙江鹤岗</v>
+        <v>河北唐山</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -1174,13 +1174,13 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>蓝虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B14" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C14" t="str">
-        <v>assets/1787318530612-779fbkfcoi.jpg</v>
+        <v>assets/1787319745369-zn66xr3bvb.jpg</v>
       </c>
       <c r="D14" t="str">
         <v>是</v>
@@ -1189,7 +1189,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>天津</v>
+        <v>河北石家庄</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -1233,13 +1233,13 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>银虎斑</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B15" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C15" t="str">
-        <v>assets/1787318365475-sj87wtsai3.jpg</v>
+        <v>assets/1787319547969-zqlq35fxxt.jpg</v>
       </c>
       <c r="D15" t="str">
         <v>是</v>
@@ -1248,7 +1248,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>山西朔州</v>
+        <v>韩国</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -1278,7 +1278,7 @@
         <v/>
       </c>
       <c r="P15" t="str">
-        <v>已接猫</v>
+        <v/>
       </c>
       <c r="Q15" t="str">
         <v/>
@@ -1292,13 +1292,13 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>银虎斑</v>
+        <v>蓝银虎斑</v>
       </c>
       <c r="B16" t="str">
         <v>妹妹</v>
       </c>
       <c r="C16" t="str">
-        <v>assets/1787318326155-ia4noopjhq.jpg</v>
+        <v>assets/1787319501376-xscwljnu1j.jpg</v>
       </c>
       <c r="D16" t="str">
         <v>是</v>
@@ -1307,7 +1307,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>贵州</v>
+        <v>美国</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1354,196 +1354,196 @@
         <v>棕虎斑</v>
       </c>
       <c r="B17" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C17" t="str">
-        <v>assets/1787304479674-w0trechn4p.jpg</v>
+        <v>assets/1787319443529-4a0zqikufx.jpg</v>
       </c>
       <c r="D17" t="str">
+        <v>是</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v>中国台湾</v>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v/>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17" t="str">
+        <v/>
+      </c>
+      <c r="M17" t="str">
+        <v/>
+      </c>
+      <c r="N17" t="str">
+        <v/>
+      </c>
+      <c r="O17" t="str">
+        <v/>
+      </c>
+      <c r="P17" t="str">
+        <v/>
+      </c>
+      <c r="Q17" t="str">
+        <v/>
+      </c>
+      <c r="R17" t="str">
+        <v/>
+      </c>
+      <c r="S17" t="str">
         <v>否</v>
-      </c>
-      <c r="E17" t="str">
-        <v>2026-06-06</v>
-      </c>
-      <c r="F17" t="str">
-        <v/>
-      </c>
-      <c r="G17" t="str">
-        <v/>
-      </c>
-      <c r="H17" t="str">
-        <v/>
-      </c>
-      <c r="I17" t="str">
-        <v/>
-      </c>
-      <c r="J17" t="str">
-        <v/>
-      </c>
-      <c r="K17" t="str">
-        <v/>
-      </c>
-      <c r="L17" t="str">
-        <v/>
-      </c>
-      <c r="M17" t="str">
-        <v/>
-      </c>
-      <c r="N17" t="str">
-        <v/>
-      </c>
-      <c r="O17" t="str">
-        <v/>
-      </c>
-      <c r="P17" t="str">
-        <v/>
-      </c>
-      <c r="Q17" t="str">
-        <v/>
-      </c>
-      <c r="R17" t="str">
-        <v/>
-      </c>
-      <c r="S17" t="str">
-        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>纯黑色</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B18" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C18" t="str">
-        <v>assets/1787283819124-4v7d1w01la.jpg</v>
+        <v>assets/1787319356194-lr2d5680i9.jpg</v>
       </c>
       <c r="D18" t="str">
+        <v>是</v>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v>中国台湾</v>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v/>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <v/>
+      </c>
+      <c r="L18" t="str">
+        <v/>
+      </c>
+      <c r="M18" t="str">
+        <v/>
+      </c>
+      <c r="N18" t="str">
+        <v/>
+      </c>
+      <c r="O18" t="str">
+        <v/>
+      </c>
+      <c r="P18" t="str">
+        <v/>
+      </c>
+      <c r="Q18" t="str">
+        <v/>
+      </c>
+      <c r="R18" t="str">
+        <v/>
+      </c>
+      <c r="S18" t="str">
         <v>否</v>
-      </c>
-      <c r="E18" t="str">
-        <v>2026-02-20</v>
-      </c>
-      <c r="F18" t="str">
-        <v/>
-      </c>
-      <c r="G18" t="str">
-        <v/>
-      </c>
-      <c r="H18" t="str">
-        <v/>
-      </c>
-      <c r="I18" t="str">
-        <v/>
-      </c>
-      <c r="J18" t="str">
-        <v/>
-      </c>
-      <c r="K18" t="str">
-        <v/>
-      </c>
-      <c r="L18" t="str">
-        <v/>
-      </c>
-      <c r="M18" t="str">
-        <v/>
-      </c>
-      <c r="N18" t="str">
-        <v/>
-      </c>
-      <c r="O18" t="str">
-        <v/>
-      </c>
-      <c r="P18" t="str">
-        <v/>
-      </c>
-      <c r="Q18" t="str">
-        <v/>
-      </c>
-      <c r="R18" t="str">
-        <v/>
-      </c>
-      <c r="S18" t="str">
-        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>阴影色NS12</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B19" t="str">
         <v>妹妹</v>
       </c>
       <c r="C19" t="str">
-        <v>assets/1787283212708-jdnyi6ecci.jpg</v>
+        <v>assets/1787319208828-aizqo4blcv.jpg</v>
       </c>
       <c r="D19" t="str">
+        <v>是</v>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <v>山东淄博</v>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
+        <v/>
+      </c>
+      <c r="J19" t="str">
+        <v/>
+      </c>
+      <c r="K19" t="str">
+        <v/>
+      </c>
+      <c r="L19" t="str">
+        <v/>
+      </c>
+      <c r="M19" t="str">
+        <v/>
+      </c>
+      <c r="N19" t="str">
+        <v/>
+      </c>
+      <c r="O19" t="str">
+        <v/>
+      </c>
+      <c r="P19" t="str">
+        <v/>
+      </c>
+      <c r="Q19" t="str">
+        <v/>
+      </c>
+      <c r="R19" t="str">
+        <v/>
+      </c>
+      <c r="S19" t="str">
         <v>否</v>
-      </c>
-      <c r="E19" t="str">
-        <v>2026-05-28</v>
-      </c>
-      <c r="F19" t="str">
-        <v/>
-      </c>
-      <c r="G19" t="str">
-        <v/>
-      </c>
-      <c r="H19" t="str">
-        <v/>
-      </c>
-      <c r="I19" t="str">
-        <v/>
-      </c>
-      <c r="J19" t="str">
-        <v/>
-      </c>
-      <c r="K19" t="str">
-        <v/>
-      </c>
-      <c r="L19" t="str">
-        <v/>
-      </c>
-      <c r="M19" t="str">
-        <v/>
-      </c>
-      <c r="N19" t="str">
-        <v/>
-      </c>
-      <c r="O19" t="str">
-        <v/>
-      </c>
-      <c r="P19" t="str">
-        <v/>
-      </c>
-      <c r="Q19" t="str">
-        <v/>
-      </c>
-      <c r="R19" t="str">
-        <v/>
-      </c>
-      <c r="S19" t="str">
-        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>阴影色NS11</v>
+        <v>银虎斑</v>
       </c>
       <c r="B20" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C20" t="str">
-        <v>assets/1787283153501-s2tjg9spwu.jpg</v>
+        <v>assets/1787319162970-cc2v8ovnni.jpg</v>
       </c>
       <c r="D20" t="str">
         <v>是</v>
       </c>
       <c r="E20" t="str">
-        <v>2026-06-15</v>
+        <v/>
       </c>
       <c r="F20" t="str">
-        <v>重庆</v>
+        <v>韩国</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1582,372 +1582,372 @@
         <v/>
       </c>
       <c r="S20" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>浅烟灰色</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B21" t="str">
         <v>妹妹</v>
       </c>
       <c r="C21" t="str">
-        <v>assets/1787283092677-i4d8tyrjtf.jpg</v>
+        <v>assets/1787319098214-8pwa9yx2wc.jpg</v>
       </c>
       <c r="D21" t="str">
+        <v>是</v>
+      </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
+        <v>四川成都</v>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
+        <v/>
+      </c>
+      <c r="J21" t="str">
+        <v/>
+      </c>
+      <c r="K21" t="str">
+        <v/>
+      </c>
+      <c r="L21" t="str">
+        <v/>
+      </c>
+      <c r="M21" t="str">
+        <v/>
+      </c>
+      <c r="N21" t="str">
+        <v/>
+      </c>
+      <c r="O21" t="str">
+        <v/>
+      </c>
+      <c r="P21" t="str">
+        <v/>
+      </c>
+      <c r="Q21" t="str">
+        <v/>
+      </c>
+      <c r="R21" t="str">
+        <v/>
+      </c>
+      <c r="S21" t="str">
         <v>否</v>
-      </c>
-      <c r="E21" t="str">
-        <v>2026-03-21</v>
-      </c>
-      <c r="F21" t="str">
-        <v/>
-      </c>
-      <c r="G21" t="str">
-        <v/>
-      </c>
-      <c r="H21" t="str">
-        <v/>
-      </c>
-      <c r="I21" t="str">
-        <v/>
-      </c>
-      <c r="J21" t="str">
-        <v/>
-      </c>
-      <c r="K21" t="str">
-        <v/>
-      </c>
-      <c r="L21" t="str">
-        <v/>
-      </c>
-      <c r="M21" t="str">
-        <v/>
-      </c>
-      <c r="N21" t="str">
-        <v/>
-      </c>
-      <c r="O21" t="str">
-        <v/>
-      </c>
-      <c r="P21" t="str">
-        <v/>
-      </c>
-      <c r="Q21" t="str">
-        <v/>
-      </c>
-      <c r="R21" t="str">
-        <v/>
-      </c>
-      <c r="S21" t="str">
-        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B22" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C22" t="str">
-        <v>assets/1787283031104-bpyq9wy2tl.jpg</v>
+        <v>assets/1787318867999-3gxdddp72x.jpg</v>
       </c>
       <c r="D22" t="str">
+        <v>是</v>
+      </c>
+      <c r="E22" t="str">
+        <v/>
+      </c>
+      <c r="F22" t="str">
+        <v>广东广州</v>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
+      <c r="I22" t="str">
+        <v/>
+      </c>
+      <c r="J22" t="str">
+        <v/>
+      </c>
+      <c r="K22" t="str">
+        <v/>
+      </c>
+      <c r="L22" t="str">
+        <v/>
+      </c>
+      <c r="M22" t="str">
+        <v/>
+      </c>
+      <c r="N22" t="str">
+        <v/>
+      </c>
+      <c r="O22" t="str">
+        <v/>
+      </c>
+      <c r="P22" t="str">
+        <v/>
+      </c>
+      <c r="Q22" t="str">
+        <v/>
+      </c>
+      <c r="R22" t="str">
+        <v/>
+      </c>
+      <c r="S22" t="str">
         <v>否</v>
-      </c>
-      <c r="E22" t="str">
-        <v>2026-06-06</v>
-      </c>
-      <c r="F22" t="str">
-        <v/>
-      </c>
-      <c r="G22" t="str">
-        <v/>
-      </c>
-      <c r="H22" t="str">
-        <v/>
-      </c>
-      <c r="I22" t="str">
-        <v/>
-      </c>
-      <c r="J22" t="str">
-        <v/>
-      </c>
-      <c r="K22" t="str">
-        <v/>
-      </c>
-      <c r="L22" t="str">
-        <v/>
-      </c>
-      <c r="M22" t="str">
-        <v/>
-      </c>
-      <c r="N22" t="str">
-        <v/>
-      </c>
-      <c r="O22" t="str">
-        <v/>
-      </c>
-      <c r="P22" t="str">
-        <v/>
-      </c>
-      <c r="Q22" t="str">
-        <v/>
-      </c>
-      <c r="R22" t="str">
-        <v/>
-      </c>
-      <c r="S22" t="str">
-        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B23" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C23" t="str">
-        <v>assets/1787282991501-2fjfws0rqw.jpg</v>
+        <v>assets/1787318609722-0ojb3aikwi.jpg</v>
       </c>
       <c r="D23" t="str">
+        <v>是</v>
+      </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
+      <c r="F23" t="str">
+        <v>黑龙江鹤岗</v>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <v/>
+      </c>
+      <c r="I23" t="str">
+        <v/>
+      </c>
+      <c r="J23" t="str">
+        <v/>
+      </c>
+      <c r="K23" t="str">
+        <v/>
+      </c>
+      <c r="L23" t="str">
+        <v/>
+      </c>
+      <c r="M23" t="str">
+        <v/>
+      </c>
+      <c r="N23" t="str">
+        <v/>
+      </c>
+      <c r="O23" t="str">
+        <v/>
+      </c>
+      <c r="P23" t="str">
+        <v/>
+      </c>
+      <c r="Q23" t="str">
+        <v/>
+      </c>
+      <c r="R23" t="str">
+        <v/>
+      </c>
+      <c r="S23" t="str">
         <v>否</v>
-      </c>
-      <c r="E23" t="str">
-        <v>2026-06-06</v>
-      </c>
-      <c r="F23" t="str">
-        <v/>
-      </c>
-      <c r="G23" t="str">
-        <v/>
-      </c>
-      <c r="H23" t="str">
-        <v/>
-      </c>
-      <c r="I23" t="str">
-        <v/>
-      </c>
-      <c r="J23" t="str">
-        <v/>
-      </c>
-      <c r="K23" t="str">
-        <v/>
-      </c>
-      <c r="L23" t="str">
-        <v/>
-      </c>
-      <c r="M23" t="str">
-        <v/>
-      </c>
-      <c r="N23" t="str">
-        <v/>
-      </c>
-      <c r="O23" t="str">
-        <v/>
-      </c>
-      <c r="P23" t="str">
-        <v/>
-      </c>
-      <c r="Q23" t="str">
-        <v/>
-      </c>
-      <c r="R23" t="str">
-        <v/>
-      </c>
-      <c r="S23" t="str">
-        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>棕虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B24" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C24" t="str">
-        <v>assets/1787282942262-syr48fym6c.jpg</v>
+        <v>assets/1787318530612-779fbkfcoi.jpg</v>
       </c>
       <c r="D24" t="str">
+        <v>是</v>
+      </c>
+      <c r="E24" t="str">
+        <v/>
+      </c>
+      <c r="F24" t="str">
+        <v>天津</v>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
+      <c r="I24" t="str">
+        <v/>
+      </c>
+      <c r="J24" t="str">
+        <v/>
+      </c>
+      <c r="K24" t="str">
+        <v/>
+      </c>
+      <c r="L24" t="str">
+        <v/>
+      </c>
+      <c r="M24" t="str">
+        <v/>
+      </c>
+      <c r="N24" t="str">
+        <v/>
+      </c>
+      <c r="O24" t="str">
+        <v/>
+      </c>
+      <c r="P24" t="str">
+        <v/>
+      </c>
+      <c r="Q24" t="str">
+        <v/>
+      </c>
+      <c r="R24" t="str">
+        <v/>
+      </c>
+      <c r="S24" t="str">
         <v>否</v>
-      </c>
-      <c r="E24" t="str">
-        <v>2026-06-15</v>
-      </c>
-      <c r="F24" t="str">
-        <v/>
-      </c>
-      <c r="G24" t="str">
-        <v/>
-      </c>
-      <c r="H24" t="str">
-        <v/>
-      </c>
-      <c r="I24" t="str">
-        <v/>
-      </c>
-      <c r="J24" t="str">
-        <v/>
-      </c>
-      <c r="K24" t="str">
-        <v/>
-      </c>
-      <c r="L24" t="str">
-        <v/>
-      </c>
-      <c r="M24" t="str">
-        <v/>
-      </c>
-      <c r="N24" t="str">
-        <v/>
-      </c>
-      <c r="O24" t="str">
-        <v/>
-      </c>
-      <c r="P24" t="str">
-        <v/>
-      </c>
-      <c r="Q24" t="str">
-        <v/>
-      </c>
-      <c r="R24" t="str">
-        <v/>
-      </c>
-      <c r="S24" t="str">
-        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B25" t="str">
         <v>弟弟</v>
       </c>
       <c r="C25" t="str">
-        <v>assets/1787282819855-7vhx3m0v40.jpg</v>
+        <v>assets/1787318365475-sj87wtsai3.jpg</v>
       </c>
       <c r="D25" t="str">
+        <v>是</v>
+      </c>
+      <c r="E25" t="str">
+        <v/>
+      </c>
+      <c r="F25" t="str">
+        <v>山西朔州</v>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+      <c r="H25" t="str">
+        <v/>
+      </c>
+      <c r="I25" t="str">
+        <v/>
+      </c>
+      <c r="J25" t="str">
+        <v/>
+      </c>
+      <c r="K25" t="str">
+        <v/>
+      </c>
+      <c r="L25" t="str">
+        <v/>
+      </c>
+      <c r="M25" t="str">
+        <v/>
+      </c>
+      <c r="N25" t="str">
+        <v/>
+      </c>
+      <c r="O25" t="str">
+        <v/>
+      </c>
+      <c r="P25" t="str">
+        <v>已接猫</v>
+      </c>
+      <c r="Q25" t="str">
+        <v/>
+      </c>
+      <c r="R25" t="str">
+        <v/>
+      </c>
+      <c r="S25" t="str">
         <v>否</v>
-      </c>
-      <c r="E25" t="str">
-        <v>2026-06-06</v>
-      </c>
-      <c r="F25" t="str">
-        <v/>
-      </c>
-      <c r="G25" t="str">
-        <v/>
-      </c>
-      <c r="H25" t="str">
-        <v/>
-      </c>
-      <c r="I25" t="str">
-        <v/>
-      </c>
-      <c r="J25" t="str">
-        <v/>
-      </c>
-      <c r="K25" t="str">
-        <v/>
-      </c>
-      <c r="L25" t="str">
-        <v/>
-      </c>
-      <c r="M25" t="str">
-        <v/>
-      </c>
-      <c r="N25" t="str">
-        <v/>
-      </c>
-      <c r="O25" t="str">
-        <v/>
-      </c>
-      <c r="P25" t="str">
-        <v/>
-      </c>
-      <c r="Q25" t="str">
-        <v/>
-      </c>
-      <c r="R25" t="str">
-        <v/>
-      </c>
-      <c r="S25" t="str">
-        <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B26" t="str">
         <v>妹妹</v>
       </c>
       <c r="C26" t="str">
-        <v>assets/1787282703381-2uakw592b4.jpg</v>
+        <v>assets/1787318326155-ia4noopjhq.jpg</v>
       </c>
       <c r="D26" t="str">
+        <v>是</v>
+      </c>
+      <c r="E26" t="str">
+        <v/>
+      </c>
+      <c r="F26" t="str">
+        <v>贵州</v>
+      </c>
+      <c r="G26" t="str">
+        <v/>
+      </c>
+      <c r="H26" t="str">
+        <v/>
+      </c>
+      <c r="I26" t="str">
+        <v/>
+      </c>
+      <c r="J26" t="str">
+        <v/>
+      </c>
+      <c r="K26" t="str">
+        <v/>
+      </c>
+      <c r="L26" t="str">
+        <v/>
+      </c>
+      <c r="M26" t="str">
+        <v/>
+      </c>
+      <c r="N26" t="str">
+        <v/>
+      </c>
+      <c r="O26" t="str">
+        <v/>
+      </c>
+      <c r="P26" t="str">
+        <v/>
+      </c>
+      <c r="Q26" t="str">
+        <v/>
+      </c>
+      <c r="R26" t="str">
+        <v/>
+      </c>
+      <c r="S26" t="str">
         <v>否</v>
-      </c>
-      <c r="E26" t="str">
-        <v>2026-06-06</v>
-      </c>
-      <c r="F26" t="str">
-        <v/>
-      </c>
-      <c r="G26" t="str">
-        <v/>
-      </c>
-      <c r="H26" t="str">
-        <v/>
-      </c>
-      <c r="I26" t="str">
-        <v/>
-      </c>
-      <c r="J26" t="str">
-        <v/>
-      </c>
-      <c r="K26" t="str">
-        <v/>
-      </c>
-      <c r="L26" t="str">
-        <v/>
-      </c>
-      <c r="M26" t="str">
-        <v/>
-      </c>
-      <c r="N26" t="str">
-        <v/>
-      </c>
-      <c r="O26" t="str">
-        <v/>
-      </c>
-      <c r="P26" t="str">
-        <v/>
-      </c>
-      <c r="Q26" t="str">
-        <v/>
-      </c>
-      <c r="R26" t="str">
-        <v/>
-      </c>
-      <c r="S26" t="str">
-        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B27" t="str">
         <v>弟弟</v>
       </c>
       <c r="C27" t="str">
-        <v>assets/1787282649397-9hc31ncrpc.jpg</v>
+        <v>assets/1787304479674-w0trechn4p.jpg</v>
       </c>
       <c r="D27" t="str">
         <v>否</v>
@@ -2000,19 +2000,19 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>烟灰色</v>
+        <v>纯黑色</v>
       </c>
       <c r="B28" t="str">
         <v>妹妹</v>
       </c>
       <c r="C28" t="str">
-        <v>assets/1787282617957-svcoyyznpg.jpg</v>
+        <v>assets/1787283819124-4v7d1w01la.jpg</v>
       </c>
       <c r="D28" t="str">
         <v>否</v>
       </c>
       <c r="E28" t="str">
-        <v>2026-06-06</v>
+        <v>2026-02-20</v>
       </c>
       <c r="F28" t="str">
         <v/>
@@ -2059,19 +2059,19 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>烟灰色</v>
+        <v>阴影色NS12</v>
       </c>
       <c r="B29" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C29" t="str">
-        <v>assets/1787282419632-78nixqjzua.jpg</v>
+        <v>assets/1787283212708-jdnyi6ecci.jpg</v>
       </c>
       <c r="D29" t="str">
         <v>否</v>
       </c>
       <c r="E29" t="str">
-        <v>2026-06-06</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F29" t="str">
         <v/>
@@ -2118,22 +2118,22 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>纯黑色</v>
+        <v>阴影色NS11</v>
       </c>
       <c r="B30" t="str">
         <v>弟弟</v>
       </c>
       <c r="C30" t="str">
-        <v>assets/1787282349942-2cfuyn7xlc.jpg</v>
+        <v>assets/1787283153501-s2tjg9spwu.jpg</v>
       </c>
       <c r="D30" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E30" t="str">
-        <v>2026-03-21</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F30" t="str">
-        <v/>
+        <v>重庆</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -2177,19 +2177,19 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>银虎斑</v>
+        <v>浅烟灰色</v>
       </c>
       <c r="B31" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C31" t="str">
-        <v>assets/1787282064159-6b4z8c5msd.jpg</v>
+        <v>assets/1787283092677-i4d8tyrjtf.jpg</v>
       </c>
       <c r="D31" t="str">
         <v>否</v>
       </c>
       <c r="E31" t="str">
-        <v>2026-06-10</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F31" t="str">
         <v/>
@@ -2236,19 +2236,19 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>阴影色NS11</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B32" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C32" t="str">
-        <v>assets/1787280590041-vzcwebdok1.jpg</v>
+        <v>assets/1787283031104-bpyq9wy2tl.jpg</v>
       </c>
       <c r="D32" t="str">
         <v>否</v>
       </c>
       <c r="E32" t="str">
-        <v>2026-05-28</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F32" t="str">
         <v/>
@@ -2295,19 +2295,19 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>浅色银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B33" t="str">
         <v>妹妹</v>
       </c>
       <c r="C33" t="str">
-        <v>assets/1787281786169-9ia0h837ct.jpg</v>
+        <v>assets/1787282991501-2fjfws0rqw.jpg</v>
       </c>
       <c r="D33" t="str">
         <v>否</v>
       </c>
       <c r="E33" t="str">
-        <v>2026-06-15</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F33" t="str">
         <v/>
@@ -2354,22 +2354,22 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>浅烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B34" t="str">
         <v>妹妹</v>
       </c>
       <c r="C34" t="str">
-        <v>assets/1785843720843-63qz159daui.jpg</v>
+        <v>assets/1787282942262-syr48fym6c.jpg</v>
       </c>
       <c r="D34" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E34" t="str">
-        <v>2026-03-21</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F34" t="str">
-        <v>四川成都</v>
+        <v/>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -2413,22 +2413,22 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>凯米尔色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B35" t="str">
         <v>弟弟</v>
       </c>
       <c r="C35" t="str">
-        <v>assets/1787301984056-iu6afro5z5.jpg, assets/1785843763310-elg05ur61ri.jpg</v>
+        <v>assets/1787282819855-7vhx3m0v40.jpg</v>
       </c>
       <c r="D35" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E35" t="str">
-        <v>2026-02-14</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F35" t="str">
-        <v>上海浦东</v>
+        <v/>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -2472,19 +2472,19 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>银虎斑补丁</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B36" t="str">
         <v>妹妹</v>
       </c>
       <c r="C36" t="str">
-        <v>assets/1785843820715-9kz7gy4mbr7.jpg</v>
+        <v>assets/1787282703381-2uakw592b4.jpg</v>
       </c>
       <c r="D36" t="str">
         <v>否</v>
       </c>
       <c r="E36" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F36" t="str">
         <v/>
@@ -2537,13 +2537,13 @@
         <v>弟弟</v>
       </c>
       <c r="C37" t="str">
-        <v>assets/1785843953805-mxl3x1982io.jpg</v>
+        <v>assets/1787282649397-9hc31ncrpc.jpg</v>
       </c>
       <c r="D37" t="str">
         <v>否</v>
       </c>
       <c r="E37" t="str">
-        <v>2026-05-18</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F37" t="str">
         <v/>
@@ -2590,19 +2590,19 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>棕虎斑玳瑁</v>
+        <v>烟灰色</v>
       </c>
       <c r="B38" t="str">
         <v>妹妹</v>
       </c>
       <c r="C38" t="str">
-        <v>assets/1785844013835-ek4xpcje7kh.jpg</v>
+        <v>assets/1787282617957-svcoyyznpg.jpg</v>
       </c>
       <c r="D38" t="str">
         <v>否</v>
       </c>
       <c r="E38" t="str">
-        <v>2026-02-14</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F38" t="str">
         <v/>
@@ -2649,19 +2649,19 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>银虎斑补丁</v>
+        <v>烟灰色</v>
       </c>
       <c r="B39" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C39" t="str">
-        <v>assets/1785844434338-ek5zbdgdcne.jpg</v>
+        <v>assets/1787282419632-78nixqjzua.jpg</v>
       </c>
       <c r="D39" t="str">
         <v>否</v>
       </c>
       <c r="E39" t="str">
-        <v>2026-05-24</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F39" t="str">
         <v/>
@@ -2708,22 +2708,22 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>银虎斑</v>
+        <v>纯黑色</v>
       </c>
       <c r="B40" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C40" t="str">
-        <v>assets/1785838787730-s5f333sc3u.jpg</v>
+        <v>assets/1787282349942-2cfuyn7xlc.jpg</v>
       </c>
       <c r="D40" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E40" t="str">
-        <v>2026-06-05</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F40" t="str">
-        <v>湖北恩施</v>
+        <v/>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -2773,16 +2773,16 @@
         <v>弟弟</v>
       </c>
       <c r="C41" t="str">
-        <v>assets/1785842296661-6qw3zs3as8h.jpg</v>
+        <v>assets/1787282064159-6b4z8c5msd.jpg</v>
       </c>
       <c r="D41" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E41" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-10</v>
       </c>
       <c r="F41" t="str">
-        <v>湖北恩施</v>
+        <v/>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -2826,22 +2826,22 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>银虎斑</v>
+        <v>阴影色NS11</v>
       </c>
       <c r="B42" t="str">
         <v>弟弟</v>
       </c>
       <c r="C42" t="str">
-        <v>assets/1785842429109-porc98rel5.jpg</v>
+        <v>assets/1787280590041-vzcwebdok1.jpg</v>
       </c>
       <c r="D42" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E42" t="str">
-        <v>2025-11-05</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F42" t="str">
-        <v>韩国</v>
+        <v/>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -2885,19 +2885,19 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>银虎斑</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B43" t="str">
         <v>妹妹</v>
       </c>
       <c r="C43" t="str">
-        <v>assets/1785842594141-fcglbzjp509.jpg</v>
+        <v>assets/1787281786169-9ia0h837ct.jpg</v>
       </c>
       <c r="D43" t="str">
         <v>否</v>
       </c>
       <c r="E43" t="str">
-        <v>2026-05-18</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F43" t="str">
         <v/>
@@ -2944,22 +2944,22 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>棕虎斑</v>
+        <v>浅烟灰色</v>
       </c>
       <c r="B44" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C44" t="str">
-        <v>assets/1785842639100-82k775dhwiv.jpg</v>
+        <v>assets/1785843720843-63qz159daui.jpg</v>
       </c>
       <c r="D44" t="str">
         <v>是</v>
       </c>
       <c r="E44" t="str">
-        <v>2026-05-28</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F44" t="str">
-        <v>四川自贡</v>
+        <v>四川成都</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -3003,22 +3003,22 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>棕虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B45" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C45" t="str">
-        <v>assets/1785842684502-mnhr0r96eee.jpg</v>
+        <v>assets/1787301984056-iu6afro5z5.jpg, assets/1785843763310-elg05ur61ri.jpg</v>
       </c>
       <c r="D45" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E45" t="str">
-        <v>2026-06-06</v>
+        <v>2026-02-14</v>
       </c>
       <c r="F45" t="str">
-        <v/>
+        <v>上海浦东</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -3062,13 +3062,13 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>纯黑色</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B46" t="str">
         <v>妹妹</v>
       </c>
       <c r="C46" t="str">
-        <v>assets/1785842779532-5u1j0igrw1s.jpg</v>
+        <v>assets/1785843820715-9kz7gy4mbr7.jpg</v>
       </c>
       <c r="D46" t="str">
         <v>否</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B47" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C47" t="str">
-        <v>assets/1785842817046-6keqv4rw4yf.jpg</v>
+        <v>assets/1785843953805-mxl3x1982io.jpg</v>
       </c>
       <c r="D47" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E47" t="str">
-        <v>2026-03-05</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F47" t="str">
-        <v>韩国</v>
+        <v/>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -3180,22 +3180,22 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>浅色银虎斑</v>
+        <v>棕虎斑玳瑁</v>
       </c>
       <c r="B48" t="str">
         <v>妹妹</v>
       </c>
       <c r="C48" t="str">
-        <v>assets/1785842950972-a88lbrskpc.jpg</v>
+        <v>assets/1785844013835-ek4xpcje7kh.jpg</v>
       </c>
       <c r="D48" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E48" t="str">
-        <v>2026-06-05</v>
+        <v>2026-02-14</v>
       </c>
       <c r="F48" t="str">
-        <v>河北邢台</v>
+        <v/>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -3239,22 +3239,22 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B49" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C49" t="str">
-        <v>assets/1785843011477-n3l1wi6ech.jpg</v>
+        <v>assets/1785844434338-ek5zbdgdcne.jpg</v>
       </c>
       <c r="D49" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E49" t="str">
-        <v>2026-06-05</v>
+        <v>2026-05-24</v>
       </c>
       <c r="F49" t="str">
-        <v>四川自贡</v>
+        <v/>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -3298,22 +3298,22 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>蓝虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B50" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C50" t="str">
-        <v>assets/1785843237517-ga449iqess5.jpg</v>
+        <v>assets/1785838787730-s5f333sc3u.jpg</v>
       </c>
       <c r="D50" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E50" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F50" t="str">
-        <v/>
+        <v>湖北恩施</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -3357,22 +3357,22 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>棕虎斑补丁</v>
+        <v>银虎斑</v>
       </c>
       <c r="B51" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C51" t="str">
-        <v>assets/1785842523893-7nwnnhwi4ns.jpg</v>
+        <v>assets/1785842296661-6qw3zs3as8h.jpg</v>
       </c>
       <c r="D51" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E51" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F51" t="str">
-        <v/>
+        <v>湖北恩施</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -3416,22 +3416,22 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>蓝虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B52" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C52" t="str">
-        <v>assets/1785843497557-st27fk8drqi.jpg</v>
+        <v>assets/1785842429109-porc98rel5.jpg</v>
       </c>
       <c r="D52" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E52" t="str">
-        <v>2026-04-05</v>
+        <v>2025-11-05</v>
       </c>
       <c r="F52" t="str">
-        <v/>
+        <v>韩国</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -3481,13 +3481,13 @@
         <v>妹妹</v>
       </c>
       <c r="C53" t="str">
-        <v>assets/1785843621923-ylhakbtw13i.jpg</v>
+        <v>assets/1785842594141-fcglbzjp509.jpg</v>
       </c>
       <c r="D53" t="str">
         <v>否</v>
       </c>
       <c r="E53" t="str">
-        <v>2026-03-05</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F53" t="str">
         <v/>
@@ -3534,22 +3534,22 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B54" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C54" t="str">
-        <v>assets/1785843663884-sfxvpmiet7.jpg</v>
+        <v>assets/1785842639100-82k775dhwiv.jpg</v>
       </c>
       <c r="D54" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E54" t="str">
-        <v>2026-03-05</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F54" t="str">
-        <v/>
+        <v>四川自贡</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -3593,52 +3593,52 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B55" t="str">
         <v>妹妹</v>
       </c>
       <c r="C55" t="str">
-        <v>assets/1785852601940-o236xtv7yx.jpeg</v>
+        <v>assets/1785842684502-mnhr0r96eee.jpg</v>
       </c>
       <c r="D55" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E55" t="str">
-        <v>2026-02-20</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F55" t="str">
-        <v>荷兰</v>
+        <v/>
       </c>
       <c r="G55" t="str">
-        <v>阿泽</v>
+        <v/>
       </c>
       <c r="H55" t="str">
-        <v>小辫子</v>
+        <v/>
       </c>
       <c r="I55" t="str">
-        <v>驺驺</v>
+        <v/>
       </c>
       <c r="J55" t="str">
-        <v>2026-07-02</v>
+        <v/>
       </c>
       <c r="K55" t="str">
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>2026-07-02</v>
+        <v/>
       </c>
       <c r="M55" t="str">
-        <v>2026-08-03</v>
+        <v/>
       </c>
       <c r="N55" t="str">
-        <v>2026-11-04</v>
+        <v/>
       </c>
       <c r="O55" t="str">
-        <v>2026-08-03 · 血清检测,2026-07-02 · 打疫苗 · assets/diary/zouzou-depart.jpg,2026-07-30 · 6.2斤 · 五个月10天了 · assets/feedback/zouzou-1.jpg</v>
+        <v/>
       </c>
       <c r="P55" t="str">
-        <v>已付定金</v>
+        <v/>
       </c>
       <c r="Q55" t="str">
         <v/>
@@ -3647,27 +3647,27 @@
         <v/>
       </c>
       <c r="S55" t="str">
-        <v>否</v>
+        <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>红虎斑</v>
+        <v>纯黑色</v>
       </c>
       <c r="B56" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C56" t="str">
-        <v>assets/1785853950207-cedor66ou2q.jpeg</v>
+        <v>assets/1785842779532-5u1j0igrw1s.jpg</v>
       </c>
       <c r="D56" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E56" t="str">
-        <v/>
+        <v>2026-03-05</v>
       </c>
       <c r="F56" t="str">
-        <v>广东广州</v>
+        <v/>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>红虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B57" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C57" t="str">
-        <v>assets/1785854129383-c8qkvl537x.jpeg</v>
+        <v>assets/1785842817046-6keqv4rw4yf.jpg</v>
       </c>
       <c r="D57" t="str">
         <v>是</v>
       </c>
       <c r="E57" t="str">
-        <v/>
+        <v>2026-03-05</v>
       </c>
       <c r="F57" t="str">
-        <v>广东广州</v>
+        <v>韩国</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -3770,22 +3770,22 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>银虎斑</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B58" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C58" t="str">
-        <v>assets/1785854166720-48r17hry9cd.jpeg</v>
+        <v>assets/1785842950972-a88lbrskpc.jpg</v>
       </c>
       <c r="D58" t="str">
         <v>是</v>
       </c>
       <c r="E58" t="str">
-        <v/>
+        <v>2026-06-05</v>
       </c>
       <c r="F58" t="str">
-        <v>山西朔州</v>
+        <v>河北邢台</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -3829,22 +3829,22 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B59" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C59" t="str">
-        <v>assets/1785854224521-2cpg6xipfn6.jpeg</v>
+        <v>assets/1785843011477-n3l1wi6ech.jpg</v>
       </c>
       <c r="D59" t="str">
         <v>是</v>
       </c>
       <c r="E59" t="str">
-        <v/>
+        <v>2026-06-05</v>
       </c>
       <c r="F59" t="str">
-        <v>浙江宁波</v>
+        <v>四川自贡</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -3888,22 +3888,22 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B60" t="str">
         <v>弟弟</v>
       </c>
       <c r="C60" t="str">
-        <v>assets/1785854260793-steez4s972l.jpeg</v>
+        <v>assets/1785843237517-ga449iqess5.jpg</v>
       </c>
       <c r="D60" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E60" t="str">
-        <v/>
+        <v>2026-03-05</v>
       </c>
       <c r="F60" t="str">
-        <v>陕西西安</v>
+        <v/>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -3947,22 +3947,22 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑补丁</v>
       </c>
       <c r="B61" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C61" t="str">
-        <v>assets/1785854319988-cohio08aod5.jpeg</v>
+        <v>assets/1785842523893-7nwnnhwi4ns.jpg</v>
       </c>
       <c r="D61" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E61" t="str">
-        <v/>
+        <v>2026-03-05</v>
       </c>
       <c r="F61" t="str">
-        <v>黑龙江漠河</v>
+        <v/>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -4006,22 +4006,22 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>棕虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B62" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C62" t="str">
-        <v>assets/1785854520974-96b8b1ekqd9.jpeg</v>
+        <v>assets/1785843497557-st27fk8drqi.jpg</v>
       </c>
       <c r="D62" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E62" t="str">
-        <v/>
+        <v>2026-04-05</v>
       </c>
       <c r="F62" t="str">
-        <v>日本</v>
+        <v/>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -4071,16 +4071,16 @@
         <v>妹妹</v>
       </c>
       <c r="C63" t="str">
-        <v>assets/1785854664100-haqoiu1h7hj.jpeg</v>
+        <v>assets/1785843621923-ylhakbtw13i.jpg</v>
       </c>
       <c r="D63" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E63" t="str">
-        <v/>
+        <v>2026-03-05</v>
       </c>
       <c r="F63" t="str">
-        <v>浙江杭州</v>
+        <v/>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -4130,16 +4130,16 @@
         <v>妹妹</v>
       </c>
       <c r="C64" t="str">
-        <v>assets/1785854690732-orrs40sx9rs.jpeg</v>
+        <v>assets/1785843663884-sfxvpmiet7.jpg</v>
       </c>
       <c r="D64" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E64" t="str">
-        <v/>
+        <v>2026-03-05</v>
       </c>
       <c r="F64" t="str">
-        <v>贵州安顺</v>
+        <v/>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -4183,52 +4183,52 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B65" t="str">
         <v>妹妹</v>
       </c>
       <c r="C65" t="str">
-        <v>assets/1785854734122-wcpmib4m7.jpeg</v>
+        <v>assets/1785852601940-o236xtv7yx.jpeg</v>
       </c>
       <c r="D65" t="str">
         <v>是</v>
       </c>
       <c r="E65" t="str">
-        <v/>
+        <v>2026-02-20</v>
       </c>
       <c r="F65" t="str">
-        <v>山东青岛</v>
+        <v>荷兰</v>
       </c>
       <c r="G65" t="str">
-        <v/>
+        <v>阿泽</v>
       </c>
       <c r="H65" t="str">
-        <v/>
+        <v>小辫子</v>
       </c>
       <c r="I65" t="str">
-        <v/>
+        <v>驺驺</v>
       </c>
       <c r="J65" t="str">
-        <v/>
+        <v>2026-07-02</v>
       </c>
       <c r="K65" t="str">
         <v/>
       </c>
       <c r="L65" t="str">
-        <v/>
+        <v>2026-07-02</v>
       </c>
       <c r="M65" t="str">
-        <v/>
+        <v>2026-08-03</v>
       </c>
       <c r="N65" t="str">
-        <v/>
+        <v>2026-11-04</v>
       </c>
       <c r="O65" t="str">
-        <v/>
+        <v>2026-08-03 · 血清检测,2026-07-02 · 打疫苗 · assets/diary/zouzou-depart.jpg,2026-07-30 · 6.2斤 · 五个月10天了 · assets/feedback/zouzou-1.jpg</v>
       </c>
       <c r="P65" t="str">
-        <v/>
+        <v>已付定金</v>
       </c>
       <c r="Q65" t="str">
         <v/>
@@ -4237,18 +4237,18 @@
         <v/>
       </c>
       <c r="S65" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B66" t="str">
         <v>弟弟</v>
       </c>
       <c r="C66" t="str">
-        <v>assets/1785854758707-1kxdkfvs6jc.jpeg</v>
+        <v>assets/1785853950207-cedor66ou2q.jpeg</v>
       </c>
       <c r="D66" t="str">
         <v>是</v>
@@ -4257,7 +4257,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>黑龙江漠河</v>
+        <v>广东广州</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -4301,13 +4301,13 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>纯蓝色</v>
+        <v>红虎斑</v>
       </c>
       <c r="B67" t="str">
         <v>弟弟</v>
       </c>
       <c r="C67" t="str">
-        <v>assets/1785854784780-3g0u60pdo93.jpeg</v>
+        <v>assets/1785854129383-c8qkvl537x.jpeg</v>
       </c>
       <c r="D67" t="str">
         <v>是</v>
@@ -4316,7 +4316,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>河南鹤壁</v>
+        <v>广东广州</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -4366,7 +4366,7 @@
         <v>弟弟</v>
       </c>
       <c r="C68" t="str">
-        <v>assets/1785854813179-8oyxr0h2bbu.jpeg</v>
+        <v>assets/1785854166720-48r17hry9cd.jpeg</v>
       </c>
       <c r="D68" t="str">
         <v>是</v>
@@ -4375,7 +4375,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>陕西西安</v>
+        <v>山西朔州</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -4419,13 +4419,13 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B69" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C69" t="str">
-        <v>assets/1785854838933-uq6amircyzd.jpeg</v>
+        <v>assets/1785854224521-2cpg6xipfn6.jpeg</v>
       </c>
       <c r="D69" t="str">
         <v>是</v>
@@ -4434,7 +4434,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>四川成都</v>
+        <v>浙江宁波</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -4478,22 +4478,22 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>烟灰色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B70" t="str">
         <v>弟弟</v>
       </c>
       <c r="C70" t="str">
-        <v>assets/1785854869973-za3p6wikqpo.jpeg</v>
+        <v>assets/1785854260793-steez4s972l.jpeg</v>
       </c>
       <c r="D70" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E70" t="str">
-        <v>2026-05-18</v>
+        <v/>
       </c>
       <c r="F70" t="str">
-        <v/>
+        <v>陕西西安</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -4543,7 +4543,7 @@
         <v>弟弟</v>
       </c>
       <c r="C71" t="str">
-        <v>assets/1785854997023-mawkallt2a.jpeg</v>
+        <v>assets/1785854319988-cohio08aod5.jpeg</v>
       </c>
       <c r="D71" t="str">
         <v>是</v>
@@ -4552,7 +4552,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>新加坡</v>
+        <v>黑龙江漠河</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -4596,13 +4596,13 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>凯米尔色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B72" t="str">
         <v>弟弟</v>
       </c>
       <c r="C72" t="str">
-        <v>assets/1785855043327-wdc5pxwm34k.jpeg</v>
+        <v>assets/1785854520974-96b8b1ekqd9.jpeg</v>
       </c>
       <c r="D72" t="str">
         <v>是</v>
@@ -4611,7 +4611,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>上海浦东</v>
+        <v>日本</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B73" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C73" t="str">
-        <v>assets/1785912551260-jplefm937nk.jpeg, assets/videos/02.mp4</v>
+        <v>assets/1785854664100-haqoiu1h7hj.jpeg</v>
       </c>
       <c r="D73" t="str">
         <v>是</v>
       </c>
       <c r="E73" t="str">
-        <v>2026-06-06</v>
+        <v/>
       </c>
       <c r="F73" t="str">
-        <v>浙江温州</v>
+        <v>浙江杭州</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -4714,66 +4714,656 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B74" t="str">
         <v>妹妹</v>
       </c>
       <c r="C74" t="str">
+        <v>assets/1785854690732-orrs40sx9rs.jpeg</v>
+      </c>
+      <c r="D74" t="str">
+        <v>是</v>
+      </c>
+      <c r="E74" t="str">
+        <v/>
+      </c>
+      <c r="F74" t="str">
+        <v>贵州安顺</v>
+      </c>
+      <c r="G74" t="str">
+        <v/>
+      </c>
+      <c r="H74" t="str">
+        <v/>
+      </c>
+      <c r="I74" t="str">
+        <v/>
+      </c>
+      <c r="J74" t="str">
+        <v/>
+      </c>
+      <c r="K74" t="str">
+        <v/>
+      </c>
+      <c r="L74" t="str">
+        <v/>
+      </c>
+      <c r="M74" t="str">
+        <v/>
+      </c>
+      <c r="N74" t="str">
+        <v/>
+      </c>
+      <c r="O74" t="str">
+        <v/>
+      </c>
+      <c r="P74" t="str">
+        <v/>
+      </c>
+      <c r="Q74" t="str">
+        <v/>
+      </c>
+      <c r="R74" t="str">
+        <v/>
+      </c>
+      <c r="S74" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>银虎斑</v>
+      </c>
+      <c r="B75" t="str">
+        <v>妹妹</v>
+      </c>
+      <c r="C75" t="str">
+        <v>assets/1785854734122-wcpmib4m7.jpeg</v>
+      </c>
+      <c r="D75" t="str">
+        <v>是</v>
+      </c>
+      <c r="E75" t="str">
+        <v/>
+      </c>
+      <c r="F75" t="str">
+        <v>山东青岛</v>
+      </c>
+      <c r="G75" t="str">
+        <v/>
+      </c>
+      <c r="H75" t="str">
+        <v/>
+      </c>
+      <c r="I75" t="str">
+        <v/>
+      </c>
+      <c r="J75" t="str">
+        <v/>
+      </c>
+      <c r="K75" t="str">
+        <v/>
+      </c>
+      <c r="L75" t="str">
+        <v/>
+      </c>
+      <c r="M75" t="str">
+        <v/>
+      </c>
+      <c r="N75" t="str">
+        <v/>
+      </c>
+      <c r="O75" t="str">
+        <v/>
+      </c>
+      <c r="P75" t="str">
+        <v/>
+      </c>
+      <c r="Q75" t="str">
+        <v/>
+      </c>
+      <c r="R75" t="str">
+        <v/>
+      </c>
+      <c r="S75" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>银虎斑</v>
+      </c>
+      <c r="B76" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C76" t="str">
+        <v>assets/1785854758707-1kxdkfvs6jc.jpeg</v>
+      </c>
+      <c r="D76" t="str">
+        <v>是</v>
+      </c>
+      <c r="E76" t="str">
+        <v/>
+      </c>
+      <c r="F76" t="str">
+        <v>黑龙江漠河</v>
+      </c>
+      <c r="G76" t="str">
+        <v/>
+      </c>
+      <c r="H76" t="str">
+        <v/>
+      </c>
+      <c r="I76" t="str">
+        <v/>
+      </c>
+      <c r="J76" t="str">
+        <v/>
+      </c>
+      <c r="K76" t="str">
+        <v/>
+      </c>
+      <c r="L76" t="str">
+        <v/>
+      </c>
+      <c r="M76" t="str">
+        <v/>
+      </c>
+      <c r="N76" t="str">
+        <v/>
+      </c>
+      <c r="O76" t="str">
+        <v/>
+      </c>
+      <c r="P76" t="str">
+        <v/>
+      </c>
+      <c r="Q76" t="str">
+        <v/>
+      </c>
+      <c r="R76" t="str">
+        <v/>
+      </c>
+      <c r="S76" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>纯蓝色</v>
+      </c>
+      <c r="B77" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C77" t="str">
+        <v>assets/1785854784780-3g0u60pdo93.jpeg</v>
+      </c>
+      <c r="D77" t="str">
+        <v>是</v>
+      </c>
+      <c r="E77" t="str">
+        <v/>
+      </c>
+      <c r="F77" t="str">
+        <v>河南鹤壁</v>
+      </c>
+      <c r="G77" t="str">
+        <v/>
+      </c>
+      <c r="H77" t="str">
+        <v/>
+      </c>
+      <c r="I77" t="str">
+        <v/>
+      </c>
+      <c r="J77" t="str">
+        <v/>
+      </c>
+      <c r="K77" t="str">
+        <v/>
+      </c>
+      <c r="L77" t="str">
+        <v/>
+      </c>
+      <c r="M77" t="str">
+        <v/>
+      </c>
+      <c r="N77" t="str">
+        <v/>
+      </c>
+      <c r="O77" t="str">
+        <v/>
+      </c>
+      <c r="P77" t="str">
+        <v/>
+      </c>
+      <c r="Q77" t="str">
+        <v/>
+      </c>
+      <c r="R77" t="str">
+        <v/>
+      </c>
+      <c r="S77" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>银虎斑</v>
+      </c>
+      <c r="B78" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C78" t="str">
+        <v>assets/1785854813179-8oyxr0h2bbu.jpeg</v>
+      </c>
+      <c r="D78" t="str">
+        <v>是</v>
+      </c>
+      <c r="E78" t="str">
+        <v/>
+      </c>
+      <c r="F78" t="str">
+        <v>陕西西安</v>
+      </c>
+      <c r="G78" t="str">
+        <v/>
+      </c>
+      <c r="H78" t="str">
+        <v/>
+      </c>
+      <c r="I78" t="str">
+        <v/>
+      </c>
+      <c r="J78" t="str">
+        <v/>
+      </c>
+      <c r="K78" t="str">
+        <v/>
+      </c>
+      <c r="L78" t="str">
+        <v/>
+      </c>
+      <c r="M78" t="str">
+        <v/>
+      </c>
+      <c r="N78" t="str">
+        <v/>
+      </c>
+      <c r="O78" t="str">
+        <v/>
+      </c>
+      <c r="P78" t="str">
+        <v/>
+      </c>
+      <c r="Q78" t="str">
+        <v/>
+      </c>
+      <c r="R78" t="str">
+        <v/>
+      </c>
+      <c r="S78" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>棕虎斑</v>
+      </c>
+      <c r="B79" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C79" t="str">
+        <v>assets/1785854838933-uq6amircyzd.jpeg</v>
+      </c>
+      <c r="D79" t="str">
+        <v>是</v>
+      </c>
+      <c r="E79" t="str">
+        <v/>
+      </c>
+      <c r="F79" t="str">
+        <v>四川成都</v>
+      </c>
+      <c r="G79" t="str">
+        <v/>
+      </c>
+      <c r="H79" t="str">
+        <v/>
+      </c>
+      <c r="I79" t="str">
+        <v/>
+      </c>
+      <c r="J79" t="str">
+        <v/>
+      </c>
+      <c r="K79" t="str">
+        <v/>
+      </c>
+      <c r="L79" t="str">
+        <v/>
+      </c>
+      <c r="M79" t="str">
+        <v/>
+      </c>
+      <c r="N79" t="str">
+        <v/>
+      </c>
+      <c r="O79" t="str">
+        <v/>
+      </c>
+      <c r="P79" t="str">
+        <v/>
+      </c>
+      <c r="Q79" t="str">
+        <v/>
+      </c>
+      <c r="R79" t="str">
+        <v/>
+      </c>
+      <c r="S79" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>烟灰色</v>
+      </c>
+      <c r="B80" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C80" t="str">
+        <v>assets/1785854869973-za3p6wikqpo.jpeg</v>
+      </c>
+      <c r="D80" t="str">
+        <v>否</v>
+      </c>
+      <c r="E80" t="str">
+        <v>2026-05-18</v>
+      </c>
+      <c r="F80" t="str">
+        <v/>
+      </c>
+      <c r="G80" t="str">
+        <v/>
+      </c>
+      <c r="H80" t="str">
+        <v/>
+      </c>
+      <c r="I80" t="str">
+        <v/>
+      </c>
+      <c r="J80" t="str">
+        <v/>
+      </c>
+      <c r="K80" t="str">
+        <v/>
+      </c>
+      <c r="L80" t="str">
+        <v/>
+      </c>
+      <c r="M80" t="str">
+        <v/>
+      </c>
+      <c r="N80" t="str">
+        <v/>
+      </c>
+      <c r="O80" t="str">
+        <v/>
+      </c>
+      <c r="P80" t="str">
+        <v/>
+      </c>
+      <c r="Q80" t="str">
+        <v/>
+      </c>
+      <c r="R80" t="str">
+        <v/>
+      </c>
+      <c r="S80" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>银虎斑</v>
+      </c>
+      <c r="B81" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C81" t="str">
+        <v>assets/1785854997023-mawkallt2a.jpeg</v>
+      </c>
+      <c r="D81" t="str">
+        <v>是</v>
+      </c>
+      <c r="E81" t="str">
+        <v/>
+      </c>
+      <c r="F81" t="str">
+        <v>新加坡</v>
+      </c>
+      <c r="G81" t="str">
+        <v/>
+      </c>
+      <c r="H81" t="str">
+        <v/>
+      </c>
+      <c r="I81" t="str">
+        <v/>
+      </c>
+      <c r="J81" t="str">
+        <v/>
+      </c>
+      <c r="K81" t="str">
+        <v/>
+      </c>
+      <c r="L81" t="str">
+        <v/>
+      </c>
+      <c r="M81" t="str">
+        <v/>
+      </c>
+      <c r="N81" t="str">
+        <v/>
+      </c>
+      <c r="O81" t="str">
+        <v/>
+      </c>
+      <c r="P81" t="str">
+        <v/>
+      </c>
+      <c r="Q81" t="str">
+        <v/>
+      </c>
+      <c r="R81" t="str">
+        <v/>
+      </c>
+      <c r="S81" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>凯米尔色</v>
+      </c>
+      <c r="B82" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C82" t="str">
+        <v>assets/1785855043327-wdc5pxwm34k.jpeg</v>
+      </c>
+      <c r="D82" t="str">
+        <v>是</v>
+      </c>
+      <c r="E82" t="str">
+        <v/>
+      </c>
+      <c r="F82" t="str">
+        <v>上海浦东</v>
+      </c>
+      <c r="G82" t="str">
+        <v/>
+      </c>
+      <c r="H82" t="str">
+        <v/>
+      </c>
+      <c r="I82" t="str">
+        <v/>
+      </c>
+      <c r="J82" t="str">
+        <v/>
+      </c>
+      <c r="K82" t="str">
+        <v/>
+      </c>
+      <c r="L82" t="str">
+        <v/>
+      </c>
+      <c r="M82" t="str">
+        <v/>
+      </c>
+      <c r="N82" t="str">
+        <v/>
+      </c>
+      <c r="O82" t="str">
+        <v/>
+      </c>
+      <c r="P82" t="str">
+        <v/>
+      </c>
+      <c r="Q82" t="str">
+        <v/>
+      </c>
+      <c r="R82" t="str">
+        <v/>
+      </c>
+      <c r="S82" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>棕虎斑</v>
+      </c>
+      <c r="B83" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C83" t="str">
+        <v>assets/1785912551260-jplefm937nk.jpeg, assets/videos/02.mp4</v>
+      </c>
+      <c r="D83" t="str">
+        <v>是</v>
+      </c>
+      <c r="E83" t="str">
+        <v>2026-06-06</v>
+      </c>
+      <c r="F83" t="str">
+        <v>浙江温州</v>
+      </c>
+      <c r="G83" t="str">
+        <v/>
+      </c>
+      <c r="H83" t="str">
+        <v/>
+      </c>
+      <c r="I83" t="str">
+        <v/>
+      </c>
+      <c r="J83" t="str">
+        <v/>
+      </c>
+      <c r="K83" t="str">
+        <v/>
+      </c>
+      <c r="L83" t="str">
+        <v/>
+      </c>
+      <c r="M83" t="str">
+        <v/>
+      </c>
+      <c r="N83" t="str">
+        <v/>
+      </c>
+      <c r="O83" t="str">
+        <v/>
+      </c>
+      <c r="P83" t="str">
+        <v/>
+      </c>
+      <c r="Q83" t="str">
+        <v/>
+      </c>
+      <c r="R83" t="str">
+        <v/>
+      </c>
+      <c r="S83" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>棕虎斑</v>
+      </c>
+      <c r="B84" t="str">
+        <v>妹妹</v>
+      </c>
+      <c r="C84" t="str">
         <v>assets/1785912694000-m20f5kvvrr.jpeg</v>
       </c>
-      <c r="D74" t="str">
+      <c r="D84" t="str">
         <v>否</v>
       </c>
-      <c r="E74" t="str">
+      <c r="E84" t="str">
         <v>2026-06-06</v>
       </c>
-      <c r="F74" t="str">
-        <v/>
-      </c>
-      <c r="G74" t="str">
-        <v/>
-      </c>
-      <c r="H74" t="str">
-        <v/>
-      </c>
-      <c r="I74" t="str">
-        <v/>
-      </c>
-      <c r="J74" t="str">
-        <v/>
-      </c>
-      <c r="K74" t="str">
-        <v/>
-      </c>
-      <c r="L74" t="str">
-        <v/>
-      </c>
-      <c r="M74" t="str">
-        <v/>
-      </c>
-      <c r="N74" t="str">
-        <v/>
-      </c>
-      <c r="O74" t="str">
-        <v/>
-      </c>
-      <c r="P74" t="str">
-        <v/>
-      </c>
-      <c r="Q74" t="str">
-        <v/>
-      </c>
-      <c r="R74" t="str">
-        <v/>
-      </c>
-      <c r="S74" t="str">
+      <c r="F84" t="str">
+        <v/>
+      </c>
+      <c r="G84" t="str">
+        <v/>
+      </c>
+      <c r="H84" t="str">
+        <v/>
+      </c>
+      <c r="I84" t="str">
+        <v/>
+      </c>
+      <c r="J84" t="str">
+        <v/>
+      </c>
+      <c r="K84" t="str">
+        <v/>
+      </c>
+      <c r="L84" t="str">
+        <v/>
+      </c>
+      <c r="M84" t="str">
+        <v/>
+      </c>
+      <c r="N84" t="str">
+        <v/>
+      </c>
+      <c r="O84" t="str">
+        <v/>
+      </c>
+      <c r="P84" t="str">
+        <v/>
+      </c>
+      <c r="Q84" t="str">
+        <v/>
+      </c>
+      <c r="R84" t="str">
+        <v/>
+      </c>
+      <c r="S84" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S74"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S84"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S84"/>
+  <dimension ref="A1:S94"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -469,10 +469,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B2" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C2" t="str">
-        <v>assets/1787321989528-7d6liuhuk9.jpg</v>
+        <v>assets/1787322988096-6e2f54q7vo.jpg</v>
       </c>
       <c r="D2" t="str">
         <v>是</v>
@@ -481,7 +481,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>陕西西安</v>
+        <v>浙江宁波</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -525,13 +525,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>银虎斑</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B3" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C3" t="str">
-        <v>assets/1787321941642-xlrc1no2ua.jpg</v>
+        <v>assets/1787322938518-85ev8bs2k5.jpg</v>
       </c>
       <c r="D3" t="str">
         <v>是</v>
@@ -540,7 +540,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>山东东营</v>
+        <v>马来西亚</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -584,13 +584,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>凯米尔色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B4" t="str">
         <v>弟弟</v>
       </c>
       <c r="C4" t="str">
-        <v>assets/1787321903535-6orj7qcgzn.jpg</v>
+        <v>assets/1787322881183-tzu9xtw2sg.jpg</v>
       </c>
       <c r="D4" t="str">
         <v>是</v>
@@ -599,7 +599,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>中国台湾</v>
+        <v>陕西西安</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -643,13 +643,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>烟灰色</v>
+        <v>纯黑色</v>
       </c>
       <c r="B5" t="str">
         <v>妹妹</v>
       </c>
       <c r="C5" t="str">
-        <v>assets/1787321858985-v4qej7cq7g.jpg</v>
+        <v>assets/1787322840098-nhy4jjyx7k.jpg</v>
       </c>
       <c r="D5" t="str">
         <v>是</v>
@@ -658,7 +658,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>中国台湾</v>
+        <v>广西南宁</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -702,13 +702,13 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B6" t="str">
         <v>弟弟</v>
       </c>
       <c r="C6" t="str">
-        <v>assets/1787321834306-efgnyhujon.jpg</v>
+        <v>assets/1787322760950-gn3qgego4s.jpg</v>
       </c>
       <c r="D6" t="str">
         <v>是</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>北京</v>
+        <v>广西南宁</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -761,13 +761,13 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B7" t="str">
         <v>弟弟</v>
       </c>
       <c r="C7" t="str">
-        <v>assets/1787321439916-uttgpbkogb.jpg</v>
+        <v>assets/1787322605982-04n50xegt2.jpg</v>
       </c>
       <c r="D7" t="str">
         <v>是</v>
@@ -776,7 +776,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>安徽合肥</v>
+        <v>上海</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -820,13 +820,13 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B8" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C8" t="str">
-        <v>assets/1787321419210-51hhgurygq.jpg</v>
+        <v>assets/1787322490045-kog3ru43dy.jpg</v>
       </c>
       <c r="D8" t="str">
         <v>是</v>
@@ -879,13 +879,13 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>凯米尔色</v>
+        <v>红虎斑</v>
       </c>
       <c r="B9" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C9" t="str">
-        <v>assets/1787321363369-bzjn51j5il.jpg</v>
+        <v>assets/1787322419996-0m33yx89nm.jpg</v>
       </c>
       <c r="D9" t="str">
         <v>是</v>
@@ -894,7 +894,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>中国台湾</v>
+        <v>广东广州</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -938,13 +938,13 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>棕虎斑</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B10" t="str">
         <v>弟弟</v>
       </c>
       <c r="C10" t="str">
-        <v>assets/1787321332559-87p6spuch3.jpg</v>
+        <v>assets/1787322377730-vj5csj2mll.jpg</v>
       </c>
       <c r="D10" t="str">
         <v>是</v>
@@ -953,7 +953,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>中国台湾</v>
+        <v>柬埔寨</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -997,13 +997,13 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>棕虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B11" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C11" t="str">
-        <v>assets/1787321232531-59lnzv8y98.jpg</v>
+        <v>assets/1787322269611-53yaj5ideu.jpg</v>
       </c>
       <c r="D11" t="str">
         <v>是</v>
@@ -1012,7 +1012,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>北京</v>
+        <v>山东枣庄</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -1059,10 +1059,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B12" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C12" t="str">
-        <v>assets/1787319975814-g1pfa56vfp.jpg</v>
+        <v>assets/1787321989528-7d6liuhuk9.jpg</v>
       </c>
       <c r="D12" t="str">
         <v>是</v>
@@ -1071,7 +1071,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>浙江宁波</v>
+        <v>陕西西安</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -1118,10 +1118,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B13" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C13" t="str">
-        <v>assets/1787319800704-v3qeu062ak.jpg</v>
+        <v>assets/1787321941642-xlrc1no2ua.jpg</v>
       </c>
       <c r="D13" t="str">
         <v>是</v>
@@ -1130,7 +1130,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>河北唐山</v>
+        <v>山东东营</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -1174,13 +1174,13 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>银虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B14" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C14" t="str">
-        <v>assets/1787319745369-zn66xr3bvb.jpg</v>
+        <v>assets/1787321903535-6orj7qcgzn.jpg</v>
       </c>
       <c r="D14" t="str">
         <v>是</v>
@@ -1189,7 +1189,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>河北石家庄</v>
+        <v>中国台湾</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -1233,13 +1233,13 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>棕虎补丁</v>
+        <v>烟灰色</v>
       </c>
       <c r="B15" t="str">
         <v>妹妹</v>
       </c>
       <c r="C15" t="str">
-        <v>assets/1787319547969-zqlq35fxxt.jpg</v>
+        <v>assets/1787321858985-v4qej7cq7g.jpg</v>
       </c>
       <c r="D15" t="str">
         <v>是</v>
@@ -1248,7 +1248,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>韩国</v>
+        <v>中国台湾</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -1292,13 +1292,13 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>蓝银虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B16" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C16" t="str">
-        <v>assets/1787319501376-xscwljnu1j.jpg</v>
+        <v>assets/1787321834306-efgnyhujon.jpg</v>
       </c>
       <c r="D16" t="str">
         <v>是</v>
@@ -1307,7 +1307,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>美国</v>
+        <v>北京</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1351,13 +1351,13 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B17" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C17" t="str">
-        <v>assets/1787319443529-4a0zqikufx.jpg</v>
+        <v>assets/1787321439916-uttgpbkogb.jpg</v>
       </c>
       <c r="D17" t="str">
         <v>是</v>
@@ -1366,7 +1366,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>中国台湾</v>
+        <v>安徽合肥</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1410,13 +1410,13 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>蓝虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B18" t="str">
         <v>弟弟</v>
       </c>
       <c r="C18" t="str">
-        <v>assets/1787319356194-lr2d5680i9.jpg</v>
+        <v>assets/1787321419210-51hhgurygq.jpg</v>
       </c>
       <c r="D18" t="str">
         <v>是</v>
@@ -1425,7 +1425,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>中国台湾</v>
+        <v>上海</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1469,13 +1469,13 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>棕虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B19" t="str">
         <v>妹妹</v>
       </c>
       <c r="C19" t="str">
-        <v>assets/1787319208828-aizqo4blcv.jpg</v>
+        <v>assets/1787321363369-bzjn51j5il.jpg</v>
       </c>
       <c r="D19" t="str">
         <v>是</v>
@@ -1484,7 +1484,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>山东淄博</v>
+        <v>中国台湾</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1528,13 +1528,13 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B20" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C20" t="str">
-        <v>assets/1787319162970-cc2v8ovnni.jpg</v>
+        <v>assets/1787321332559-87p6spuch3.jpg</v>
       </c>
       <c r="D20" t="str">
         <v>是</v>
@@ -1543,7 +1543,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>韩国</v>
+        <v>中国台湾</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1587,13 +1587,13 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>棕虎补丁</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B21" t="str">
         <v>妹妹</v>
       </c>
       <c r="C21" t="str">
-        <v>assets/1787319098214-8pwa9yx2wc.jpg</v>
+        <v>assets/1787321232531-59lnzv8y98.jpg</v>
       </c>
       <c r="D21" t="str">
         <v>是</v>
@@ -1602,7 +1602,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>四川成都</v>
+        <v>北京</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1649,10 +1649,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B22" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C22" t="str">
-        <v>assets/1787318867999-3gxdddp72x.jpg</v>
+        <v>assets/1787319975814-g1pfa56vfp.jpg</v>
       </c>
       <c r="D22" t="str">
         <v>是</v>
@@ -1661,7 +1661,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>广东广州</v>
+        <v>浙江宁波</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1708,10 +1708,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B23" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C23" t="str">
-        <v>assets/1787318609722-0ojb3aikwi.jpg</v>
+        <v>assets/1787319800704-v3qeu062ak.jpg</v>
       </c>
       <c r="D23" t="str">
         <v>是</v>
@@ -1720,7 +1720,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>黑龙江鹤岗</v>
+        <v>河北唐山</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1764,13 +1764,13 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>蓝虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B24" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C24" t="str">
-        <v>assets/1787318530612-779fbkfcoi.jpg</v>
+        <v>assets/1787319745369-zn66xr3bvb.jpg</v>
       </c>
       <c r="D24" t="str">
         <v>是</v>
@@ -1779,7 +1779,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>天津</v>
+        <v>河北石家庄</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1823,13 +1823,13 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>银虎斑</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B25" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C25" t="str">
-        <v>assets/1787318365475-sj87wtsai3.jpg</v>
+        <v>assets/1787319547969-zqlq35fxxt.jpg</v>
       </c>
       <c r="D25" t="str">
         <v>是</v>
@@ -1838,7 +1838,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>山西朔州</v>
+        <v>韩国</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1868,7 +1868,7 @@
         <v/>
       </c>
       <c r="P25" t="str">
-        <v>已接猫</v>
+        <v/>
       </c>
       <c r="Q25" t="str">
         <v/>
@@ -1882,13 +1882,13 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>银虎斑</v>
+        <v>蓝银虎斑</v>
       </c>
       <c r="B26" t="str">
         <v>妹妹</v>
       </c>
       <c r="C26" t="str">
-        <v>assets/1787318326155-ia4noopjhq.jpg</v>
+        <v>assets/1787319501376-xscwljnu1j.jpg</v>
       </c>
       <c r="D26" t="str">
         <v>是</v>
@@ -1897,7 +1897,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>贵州</v>
+        <v>美国</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1944,19 +1944,19 @@
         <v>棕虎斑</v>
       </c>
       <c r="B27" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C27" t="str">
-        <v>assets/1787304479674-w0trechn4p.jpg</v>
+        <v>assets/1787319443529-4a0zqikufx.jpg</v>
       </c>
       <c r="D27" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E27" t="str">
-        <v>2026-06-06</v>
+        <v/>
       </c>
       <c r="F27" t="str">
-        <v/>
+        <v>中国台湾</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1995,27 +1995,27 @@
         <v/>
       </c>
       <c r="S27" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>纯黑色</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B28" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C28" t="str">
-        <v>assets/1787283819124-4v7d1w01la.jpg</v>
+        <v>assets/1787319356194-lr2d5680i9.jpg</v>
       </c>
       <c r="D28" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E28" t="str">
-        <v>2026-02-20</v>
+        <v/>
       </c>
       <c r="F28" t="str">
-        <v/>
+        <v>中国台湾</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -2054,27 +2054,27 @@
         <v/>
       </c>
       <c r="S28" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>阴影色NS12</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B29" t="str">
         <v>妹妹</v>
       </c>
       <c r="C29" t="str">
-        <v>assets/1787283212708-jdnyi6ecci.jpg</v>
+        <v>assets/1787319208828-aizqo4blcv.jpg</v>
       </c>
       <c r="D29" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E29" t="str">
-        <v>2026-05-28</v>
+        <v/>
       </c>
       <c r="F29" t="str">
-        <v/>
+        <v>山东淄博</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -2113,27 +2113,27 @@
         <v/>
       </c>
       <c r="S29" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>阴影色NS11</v>
+        <v>银虎斑</v>
       </c>
       <c r="B30" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C30" t="str">
-        <v>assets/1787283153501-s2tjg9spwu.jpg</v>
+        <v>assets/1787319162970-cc2v8ovnni.jpg</v>
       </c>
       <c r="D30" t="str">
         <v>是</v>
       </c>
       <c r="E30" t="str">
-        <v>2026-06-15</v>
+        <v/>
       </c>
       <c r="F30" t="str">
-        <v>重庆</v>
+        <v>韩国</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -2172,27 +2172,27 @@
         <v/>
       </c>
       <c r="S30" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>浅烟灰色</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B31" t="str">
         <v>妹妹</v>
       </c>
       <c r="C31" t="str">
-        <v>assets/1787283092677-i4d8tyrjtf.jpg</v>
+        <v>assets/1787319098214-8pwa9yx2wc.jpg</v>
       </c>
       <c r="D31" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E31" t="str">
-        <v>2026-03-21</v>
+        <v/>
       </c>
       <c r="F31" t="str">
-        <v/>
+        <v>四川成都</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -2231,27 +2231,27 @@
         <v/>
       </c>
       <c r="S31" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B32" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C32" t="str">
-        <v>assets/1787283031104-bpyq9wy2tl.jpg</v>
+        <v>assets/1787318867999-3gxdddp72x.jpg</v>
       </c>
       <c r="D32" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E32" t="str">
-        <v>2026-06-06</v>
+        <v/>
       </c>
       <c r="F32" t="str">
-        <v/>
+        <v>广东广州</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -2290,27 +2290,27 @@
         <v/>
       </c>
       <c r="S32" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B33" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C33" t="str">
-        <v>assets/1787282991501-2fjfws0rqw.jpg</v>
+        <v>assets/1787318609722-0ojb3aikwi.jpg</v>
       </c>
       <c r="D33" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E33" t="str">
-        <v>2026-06-06</v>
+        <v/>
       </c>
       <c r="F33" t="str">
-        <v/>
+        <v>黑龙江鹤岗</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -2349,27 +2349,27 @@
         <v/>
       </c>
       <c r="S33" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>棕虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B34" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C34" t="str">
-        <v>assets/1787282942262-syr48fym6c.jpg</v>
+        <v>assets/1787318530612-779fbkfcoi.jpg</v>
       </c>
       <c r="D34" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E34" t="str">
-        <v>2026-06-15</v>
+        <v/>
       </c>
       <c r="F34" t="str">
-        <v/>
+        <v>天津</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -2408,27 +2408,27 @@
         <v/>
       </c>
       <c r="S34" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B35" t="str">
         <v>弟弟</v>
       </c>
       <c r="C35" t="str">
-        <v>assets/1787282819855-7vhx3m0v40.jpg</v>
+        <v>assets/1787318365475-sj87wtsai3.jpg</v>
       </c>
       <c r="D35" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E35" t="str">
-        <v>2026-06-06</v>
+        <v/>
       </c>
       <c r="F35" t="str">
-        <v/>
+        <v>山西朔州</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -2458,7 +2458,7 @@
         <v/>
       </c>
       <c r="P35" t="str">
-        <v/>
+        <v>已接猫</v>
       </c>
       <c r="Q35" t="str">
         <v/>
@@ -2467,27 +2467,27 @@
         <v/>
       </c>
       <c r="S35" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B36" t="str">
         <v>妹妹</v>
       </c>
       <c r="C36" t="str">
-        <v>assets/1787282703381-2uakw592b4.jpg</v>
+        <v>assets/1787318326155-ia4noopjhq.jpg</v>
       </c>
       <c r="D36" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E36" t="str">
-        <v>2026-06-06</v>
+        <v/>
       </c>
       <c r="F36" t="str">
-        <v/>
+        <v>贵州</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -2526,18 +2526,18 @@
         <v/>
       </c>
       <c r="S36" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B37" t="str">
         <v>弟弟</v>
       </c>
       <c r="C37" t="str">
-        <v>assets/1787282649397-9hc31ncrpc.jpg</v>
+        <v>assets/1787304479674-w0trechn4p.jpg</v>
       </c>
       <c r="D37" t="str">
         <v>否</v>
@@ -2590,19 +2590,19 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>烟灰色</v>
+        <v>纯黑色</v>
       </c>
       <c r="B38" t="str">
         <v>妹妹</v>
       </c>
       <c r="C38" t="str">
-        <v>assets/1787282617957-svcoyyznpg.jpg</v>
+        <v>assets/1787283819124-4v7d1w01la.jpg</v>
       </c>
       <c r="D38" t="str">
         <v>否</v>
       </c>
       <c r="E38" t="str">
-        <v>2026-06-06</v>
+        <v>2026-02-20</v>
       </c>
       <c r="F38" t="str">
         <v/>
@@ -2649,19 +2649,19 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>烟灰色</v>
+        <v>阴影色NS12</v>
       </c>
       <c r="B39" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C39" t="str">
-        <v>assets/1787282419632-78nixqjzua.jpg</v>
+        <v>assets/1787283212708-jdnyi6ecci.jpg</v>
       </c>
       <c r="D39" t="str">
         <v>否</v>
       </c>
       <c r="E39" t="str">
-        <v>2026-06-06</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F39" t="str">
         <v/>
@@ -2708,22 +2708,22 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>纯黑色</v>
+        <v>阴影色NS11</v>
       </c>
       <c r="B40" t="str">
         <v>弟弟</v>
       </c>
       <c r="C40" t="str">
-        <v>assets/1787282349942-2cfuyn7xlc.jpg</v>
+        <v>assets/1787283153501-s2tjg9spwu.jpg</v>
       </c>
       <c r="D40" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E40" t="str">
-        <v>2026-03-21</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F40" t="str">
-        <v/>
+        <v>重庆</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -2767,19 +2767,19 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>银虎斑</v>
+        <v>浅烟灰色</v>
       </c>
       <c r="B41" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C41" t="str">
-        <v>assets/1787282064159-6b4z8c5msd.jpg</v>
+        <v>assets/1787283092677-i4d8tyrjtf.jpg</v>
       </c>
       <c r="D41" t="str">
         <v>否</v>
       </c>
       <c r="E41" t="str">
-        <v>2026-06-10</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F41" t="str">
         <v/>
@@ -2826,19 +2826,19 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>阴影色NS11</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B42" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C42" t="str">
-        <v>assets/1787280590041-vzcwebdok1.jpg</v>
+        <v>assets/1787283031104-bpyq9wy2tl.jpg</v>
       </c>
       <c r="D42" t="str">
         <v>否</v>
       </c>
       <c r="E42" t="str">
-        <v>2026-05-28</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F42" t="str">
         <v/>
@@ -2885,19 +2885,19 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>浅色银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B43" t="str">
         <v>妹妹</v>
       </c>
       <c r="C43" t="str">
-        <v>assets/1787281786169-9ia0h837ct.jpg</v>
+        <v>assets/1787282991501-2fjfws0rqw.jpg</v>
       </c>
       <c r="D43" t="str">
         <v>否</v>
       </c>
       <c r="E43" t="str">
-        <v>2026-06-15</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F43" t="str">
         <v/>
@@ -2944,22 +2944,22 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>浅烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B44" t="str">
         <v>妹妹</v>
       </c>
       <c r="C44" t="str">
-        <v>assets/1785843720843-63qz159daui.jpg</v>
+        <v>assets/1787282942262-syr48fym6c.jpg</v>
       </c>
       <c r="D44" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E44" t="str">
-        <v>2026-03-21</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F44" t="str">
-        <v>四川成都</v>
+        <v/>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -3003,22 +3003,22 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>凯米尔色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B45" t="str">
         <v>弟弟</v>
       </c>
       <c r="C45" t="str">
-        <v>assets/1787301984056-iu6afro5z5.jpg, assets/1785843763310-elg05ur61ri.jpg</v>
+        <v>assets/1787282819855-7vhx3m0v40.jpg</v>
       </c>
       <c r="D45" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E45" t="str">
-        <v>2026-02-14</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F45" t="str">
-        <v>上海浦东</v>
+        <v/>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -3062,19 +3062,19 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>银虎斑补丁</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B46" t="str">
         <v>妹妹</v>
       </c>
       <c r="C46" t="str">
-        <v>assets/1785843820715-9kz7gy4mbr7.jpg</v>
+        <v>assets/1787282703381-2uakw592b4.jpg</v>
       </c>
       <c r="D46" t="str">
         <v>否</v>
       </c>
       <c r="E46" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F46" t="str">
         <v/>
@@ -3127,13 +3127,13 @@
         <v>弟弟</v>
       </c>
       <c r="C47" t="str">
-        <v>assets/1785843953805-mxl3x1982io.jpg</v>
+        <v>assets/1787282649397-9hc31ncrpc.jpg</v>
       </c>
       <c r="D47" t="str">
         <v>否</v>
       </c>
       <c r="E47" t="str">
-        <v>2026-05-18</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F47" t="str">
         <v/>
@@ -3180,19 +3180,19 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>棕虎斑玳瑁</v>
+        <v>烟灰色</v>
       </c>
       <c r="B48" t="str">
         <v>妹妹</v>
       </c>
       <c r="C48" t="str">
-        <v>assets/1785844013835-ek4xpcje7kh.jpg</v>
+        <v>assets/1787282617957-svcoyyznpg.jpg</v>
       </c>
       <c r="D48" t="str">
         <v>否</v>
       </c>
       <c r="E48" t="str">
-        <v>2026-02-14</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F48" t="str">
         <v/>
@@ -3239,19 +3239,19 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>银虎斑补丁</v>
+        <v>烟灰色</v>
       </c>
       <c r="B49" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C49" t="str">
-        <v>assets/1785844434338-ek5zbdgdcne.jpg</v>
+        <v>assets/1787282419632-78nixqjzua.jpg</v>
       </c>
       <c r="D49" t="str">
         <v>否</v>
       </c>
       <c r="E49" t="str">
-        <v>2026-05-24</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F49" t="str">
         <v/>
@@ -3298,22 +3298,22 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>银虎斑</v>
+        <v>纯黑色</v>
       </c>
       <c r="B50" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C50" t="str">
-        <v>assets/1785838787730-s5f333sc3u.jpg</v>
+        <v>assets/1787282349942-2cfuyn7xlc.jpg</v>
       </c>
       <c r="D50" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E50" t="str">
-        <v>2026-06-05</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F50" t="str">
-        <v>湖北恩施</v>
+        <v/>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -3363,16 +3363,16 @@
         <v>弟弟</v>
       </c>
       <c r="C51" t="str">
-        <v>assets/1785842296661-6qw3zs3as8h.jpg</v>
+        <v>assets/1787282064159-6b4z8c5msd.jpg</v>
       </c>
       <c r="D51" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E51" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-10</v>
       </c>
       <c r="F51" t="str">
-        <v>湖北恩施</v>
+        <v/>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -3416,22 +3416,22 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>银虎斑</v>
+        <v>阴影色NS11</v>
       </c>
       <c r="B52" t="str">
         <v>弟弟</v>
       </c>
       <c r="C52" t="str">
-        <v>assets/1785842429109-porc98rel5.jpg</v>
+        <v>assets/1787280590041-vzcwebdok1.jpg</v>
       </c>
       <c r="D52" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E52" t="str">
-        <v>2025-11-05</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F52" t="str">
-        <v>韩国</v>
+        <v/>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -3475,19 +3475,19 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>银虎斑</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B53" t="str">
         <v>妹妹</v>
       </c>
       <c r="C53" t="str">
-        <v>assets/1785842594141-fcglbzjp509.jpg</v>
+        <v>assets/1787281786169-9ia0h837ct.jpg</v>
       </c>
       <c r="D53" t="str">
         <v>否</v>
       </c>
       <c r="E53" t="str">
-        <v>2026-05-18</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F53" t="str">
         <v/>
@@ -3534,22 +3534,22 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>棕虎斑</v>
+        <v>浅烟灰色</v>
       </c>
       <c r="B54" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C54" t="str">
-        <v>assets/1785842639100-82k775dhwiv.jpg</v>
+        <v>assets/1785843720843-63qz159daui.jpg</v>
       </c>
       <c r="D54" t="str">
         <v>是</v>
       </c>
       <c r="E54" t="str">
-        <v>2026-05-28</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F54" t="str">
-        <v>四川自贡</v>
+        <v>四川成都</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -3593,22 +3593,22 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>棕虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B55" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C55" t="str">
-        <v>assets/1785842684502-mnhr0r96eee.jpg</v>
+        <v>assets/1787301984056-iu6afro5z5.jpg, assets/1785843763310-elg05ur61ri.jpg</v>
       </c>
       <c r="D55" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E55" t="str">
-        <v>2026-06-06</v>
+        <v>2026-02-14</v>
       </c>
       <c r="F55" t="str">
-        <v/>
+        <v>上海浦东</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -3652,13 +3652,13 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>纯黑色</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B56" t="str">
         <v>妹妹</v>
       </c>
       <c r="C56" t="str">
-        <v>assets/1785842779532-5u1j0igrw1s.jpg</v>
+        <v>assets/1785843820715-9kz7gy4mbr7.jpg</v>
       </c>
       <c r="D56" t="str">
         <v>否</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B57" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C57" t="str">
-        <v>assets/1785842817046-6keqv4rw4yf.jpg</v>
+        <v>assets/1785843953805-mxl3x1982io.jpg</v>
       </c>
       <c r="D57" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E57" t="str">
-        <v>2026-03-05</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F57" t="str">
-        <v>韩国</v>
+        <v/>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -3770,22 +3770,22 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>浅色银虎斑</v>
+        <v>棕虎斑玳瑁</v>
       </c>
       <c r="B58" t="str">
         <v>妹妹</v>
       </c>
       <c r="C58" t="str">
-        <v>assets/1785842950972-a88lbrskpc.jpg</v>
+        <v>assets/1785844013835-ek4xpcje7kh.jpg</v>
       </c>
       <c r="D58" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E58" t="str">
-        <v>2026-06-05</v>
+        <v>2026-02-14</v>
       </c>
       <c r="F58" t="str">
-        <v>河北邢台</v>
+        <v/>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -3829,22 +3829,22 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B59" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C59" t="str">
-        <v>assets/1785843011477-n3l1wi6ech.jpg</v>
+        <v>assets/1785844434338-ek5zbdgdcne.jpg</v>
       </c>
       <c r="D59" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E59" t="str">
-        <v>2026-06-05</v>
+        <v>2026-05-24</v>
       </c>
       <c r="F59" t="str">
-        <v>四川自贡</v>
+        <v/>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -3888,22 +3888,22 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>蓝虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B60" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C60" t="str">
-        <v>assets/1785843237517-ga449iqess5.jpg</v>
+        <v>assets/1785838787730-s5f333sc3u.jpg</v>
       </c>
       <c r="D60" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E60" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F60" t="str">
-        <v/>
+        <v>湖北恩施</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -3947,22 +3947,22 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>棕虎斑补丁</v>
+        <v>银虎斑</v>
       </c>
       <c r="B61" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C61" t="str">
-        <v>assets/1785842523893-7nwnnhwi4ns.jpg</v>
+        <v>assets/1785842296661-6qw3zs3as8h.jpg</v>
       </c>
       <c r="D61" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E61" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F61" t="str">
-        <v/>
+        <v>湖北恩施</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -4006,22 +4006,22 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>蓝虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B62" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C62" t="str">
-        <v>assets/1785843497557-st27fk8drqi.jpg</v>
+        <v>assets/1785842429109-porc98rel5.jpg</v>
       </c>
       <c r="D62" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E62" t="str">
-        <v>2026-04-05</v>
+        <v>2025-11-05</v>
       </c>
       <c r="F62" t="str">
-        <v/>
+        <v>韩国</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -4071,13 +4071,13 @@
         <v>妹妹</v>
       </c>
       <c r="C63" t="str">
-        <v>assets/1785843621923-ylhakbtw13i.jpg</v>
+        <v>assets/1785842594141-fcglbzjp509.jpg</v>
       </c>
       <c r="D63" t="str">
         <v>否</v>
       </c>
       <c r="E63" t="str">
-        <v>2026-03-05</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F63" t="str">
         <v/>
@@ -4124,22 +4124,22 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B64" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C64" t="str">
-        <v>assets/1785843663884-sfxvpmiet7.jpg</v>
+        <v>assets/1785842639100-82k775dhwiv.jpg</v>
       </c>
       <c r="D64" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E64" t="str">
-        <v>2026-03-05</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F64" t="str">
-        <v/>
+        <v>四川自贡</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -4183,52 +4183,52 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B65" t="str">
         <v>妹妹</v>
       </c>
       <c r="C65" t="str">
-        <v>assets/1785852601940-o236xtv7yx.jpeg</v>
+        <v>assets/1785842684502-mnhr0r96eee.jpg</v>
       </c>
       <c r="D65" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E65" t="str">
-        <v>2026-02-20</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F65" t="str">
-        <v>荷兰</v>
+        <v/>
       </c>
       <c r="G65" t="str">
-        <v>阿泽</v>
+        <v/>
       </c>
       <c r="H65" t="str">
-        <v>小辫子</v>
+        <v/>
       </c>
       <c r="I65" t="str">
-        <v>驺驺</v>
+        <v/>
       </c>
       <c r="J65" t="str">
-        <v>2026-07-02</v>
+        <v/>
       </c>
       <c r="K65" t="str">
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>2026-07-02</v>
+        <v/>
       </c>
       <c r="M65" t="str">
-        <v>2026-08-03</v>
+        <v/>
       </c>
       <c r="N65" t="str">
-        <v>2026-11-04</v>
+        <v/>
       </c>
       <c r="O65" t="str">
-        <v>2026-08-03 · 血清检测,2026-07-02 · 打疫苗 · assets/diary/zouzou-depart.jpg,2026-07-30 · 6.2斤 · 五个月10天了 · assets/feedback/zouzou-1.jpg</v>
+        <v/>
       </c>
       <c r="P65" t="str">
-        <v>已付定金</v>
+        <v/>
       </c>
       <c r="Q65" t="str">
         <v/>
@@ -4237,27 +4237,27 @@
         <v/>
       </c>
       <c r="S65" t="str">
-        <v>否</v>
+        <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>红虎斑</v>
+        <v>纯黑色</v>
       </c>
       <c r="B66" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C66" t="str">
-        <v>assets/1785853950207-cedor66ou2q.jpeg</v>
+        <v>assets/1785842779532-5u1j0igrw1s.jpg</v>
       </c>
       <c r="D66" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E66" t="str">
-        <v/>
+        <v>2026-03-05</v>
       </c>
       <c r="F66" t="str">
-        <v>广东广州</v>
+        <v/>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -4301,22 +4301,22 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>红虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B67" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C67" t="str">
-        <v>assets/1785854129383-c8qkvl537x.jpeg</v>
+        <v>assets/1785842817046-6keqv4rw4yf.jpg</v>
       </c>
       <c r="D67" t="str">
         <v>是</v>
       </c>
       <c r="E67" t="str">
-        <v/>
+        <v>2026-03-05</v>
       </c>
       <c r="F67" t="str">
-        <v>广东广州</v>
+        <v>韩国</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -4360,22 +4360,22 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>银虎斑</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B68" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C68" t="str">
-        <v>assets/1785854166720-48r17hry9cd.jpeg</v>
+        <v>assets/1785842950972-a88lbrskpc.jpg</v>
       </c>
       <c r="D68" t="str">
         <v>是</v>
       </c>
       <c r="E68" t="str">
-        <v/>
+        <v>2026-06-05</v>
       </c>
       <c r="F68" t="str">
-        <v>山西朔州</v>
+        <v>河北邢台</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -4419,22 +4419,22 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B69" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C69" t="str">
-        <v>assets/1785854224521-2cpg6xipfn6.jpeg</v>
+        <v>assets/1785843011477-n3l1wi6ech.jpg</v>
       </c>
       <c r="D69" t="str">
         <v>是</v>
       </c>
       <c r="E69" t="str">
-        <v/>
+        <v>2026-06-05</v>
       </c>
       <c r="F69" t="str">
-        <v>浙江宁波</v>
+        <v>四川自贡</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -4478,22 +4478,22 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B70" t="str">
         <v>弟弟</v>
       </c>
       <c r="C70" t="str">
-        <v>assets/1785854260793-steez4s972l.jpeg</v>
+        <v>assets/1785843237517-ga449iqess5.jpg</v>
       </c>
       <c r="D70" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E70" t="str">
-        <v/>
+        <v>2026-03-05</v>
       </c>
       <c r="F70" t="str">
-        <v>陕西西安</v>
+        <v/>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑补丁</v>
       </c>
       <c r="B71" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C71" t="str">
-        <v>assets/1785854319988-cohio08aod5.jpeg</v>
+        <v>assets/1785842523893-7nwnnhwi4ns.jpg</v>
       </c>
       <c r="D71" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E71" t="str">
-        <v/>
+        <v>2026-03-05</v>
       </c>
       <c r="F71" t="str">
-        <v>黑龙江漠河</v>
+        <v/>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -4596,22 +4596,22 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>棕虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B72" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C72" t="str">
-        <v>assets/1785854520974-96b8b1ekqd9.jpeg</v>
+        <v>assets/1785843497557-st27fk8drqi.jpg</v>
       </c>
       <c r="D72" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E72" t="str">
-        <v/>
+        <v>2026-04-05</v>
       </c>
       <c r="F72" t="str">
-        <v>日本</v>
+        <v/>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -4661,16 +4661,16 @@
         <v>妹妹</v>
       </c>
       <c r="C73" t="str">
-        <v>assets/1785854664100-haqoiu1h7hj.jpeg</v>
+        <v>assets/1785843621923-ylhakbtw13i.jpg</v>
       </c>
       <c r="D73" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E73" t="str">
-        <v/>
+        <v>2026-03-05</v>
       </c>
       <c r="F73" t="str">
-        <v>浙江杭州</v>
+        <v/>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -4720,16 +4720,16 @@
         <v>妹妹</v>
       </c>
       <c r="C74" t="str">
-        <v>assets/1785854690732-orrs40sx9rs.jpeg</v>
+        <v>assets/1785843663884-sfxvpmiet7.jpg</v>
       </c>
       <c r="D74" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E74" t="str">
-        <v/>
+        <v>2026-03-05</v>
       </c>
       <c r="F74" t="str">
-        <v>贵州安顺</v>
+        <v/>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -4773,52 +4773,52 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B75" t="str">
         <v>妹妹</v>
       </c>
       <c r="C75" t="str">
-        <v>assets/1785854734122-wcpmib4m7.jpeg</v>
+        <v>assets/1785852601940-o236xtv7yx.jpeg</v>
       </c>
       <c r="D75" t="str">
         <v>是</v>
       </c>
       <c r="E75" t="str">
-        <v/>
+        <v>2026-02-20</v>
       </c>
       <c r="F75" t="str">
-        <v>山东青岛</v>
+        <v>荷兰</v>
       </c>
       <c r="G75" t="str">
-        <v/>
+        <v>阿泽</v>
       </c>
       <c r="H75" t="str">
-        <v/>
+        <v>小辫子</v>
       </c>
       <c r="I75" t="str">
-        <v/>
+        <v>驺驺</v>
       </c>
       <c r="J75" t="str">
-        <v/>
+        <v>2026-07-02</v>
       </c>
       <c r="K75" t="str">
         <v/>
       </c>
       <c r="L75" t="str">
-        <v/>
+        <v>2026-07-02</v>
       </c>
       <c r="M75" t="str">
-        <v/>
+        <v>2026-08-03</v>
       </c>
       <c r="N75" t="str">
-        <v/>
+        <v>2026-11-04</v>
       </c>
       <c r="O75" t="str">
-        <v/>
+        <v>2026-08-03 · 血清检测,2026-07-02 · 打疫苗 · assets/diary/zouzou-depart.jpg,2026-07-30 · 6.2斤 · 五个月10天了 · assets/feedback/zouzou-1.jpg</v>
       </c>
       <c r="P75" t="str">
-        <v/>
+        <v>已付定金</v>
       </c>
       <c r="Q75" t="str">
         <v/>
@@ -4827,18 +4827,18 @@
         <v/>
       </c>
       <c r="S75" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B76" t="str">
         <v>弟弟</v>
       </c>
       <c r="C76" t="str">
-        <v>assets/1785854758707-1kxdkfvs6jc.jpeg</v>
+        <v>assets/1785853950207-cedor66ou2q.jpeg</v>
       </c>
       <c r="D76" t="str">
         <v>是</v>
@@ -4847,7 +4847,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>黑龙江漠河</v>
+        <v>广东广州</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -4891,13 +4891,13 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>纯蓝色</v>
+        <v>红虎斑</v>
       </c>
       <c r="B77" t="str">
         <v>弟弟</v>
       </c>
       <c r="C77" t="str">
-        <v>assets/1785854784780-3g0u60pdo93.jpeg</v>
+        <v>assets/1785854129383-c8qkvl537x.jpeg</v>
       </c>
       <c r="D77" t="str">
         <v>是</v>
@@ -4906,7 +4906,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>河南鹤壁</v>
+        <v>广东广州</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -4956,7 +4956,7 @@
         <v>弟弟</v>
       </c>
       <c r="C78" t="str">
-        <v>assets/1785854813179-8oyxr0h2bbu.jpeg</v>
+        <v>assets/1785854166720-48r17hry9cd.jpeg</v>
       </c>
       <c r="D78" t="str">
         <v>是</v>
@@ -4965,7 +4965,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>陕西西安</v>
+        <v>山西朔州</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -5009,13 +5009,13 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B79" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C79" t="str">
-        <v>assets/1785854838933-uq6amircyzd.jpeg</v>
+        <v>assets/1785854224521-2cpg6xipfn6.jpeg</v>
       </c>
       <c r="D79" t="str">
         <v>是</v>
@@ -5024,7 +5024,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>四川成都</v>
+        <v>浙江宁波</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -5068,22 +5068,22 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>烟灰色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B80" t="str">
         <v>弟弟</v>
       </c>
       <c r="C80" t="str">
-        <v>assets/1785854869973-za3p6wikqpo.jpeg</v>
+        <v>assets/1785854260793-steez4s972l.jpeg</v>
       </c>
       <c r="D80" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E80" t="str">
-        <v>2026-05-18</v>
+        <v/>
       </c>
       <c r="F80" t="str">
-        <v/>
+        <v>陕西西安</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -5133,7 +5133,7 @@
         <v>弟弟</v>
       </c>
       <c r="C81" t="str">
-        <v>assets/1785854997023-mawkallt2a.jpeg</v>
+        <v>assets/1785854319988-cohio08aod5.jpeg</v>
       </c>
       <c r="D81" t="str">
         <v>是</v>
@@ -5142,7 +5142,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>新加坡</v>
+        <v>黑龙江漠河</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -5186,13 +5186,13 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>凯米尔色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B82" t="str">
         <v>弟弟</v>
       </c>
       <c r="C82" t="str">
-        <v>assets/1785855043327-wdc5pxwm34k.jpeg</v>
+        <v>assets/1785854520974-96b8b1ekqd9.jpeg</v>
       </c>
       <c r="D82" t="str">
         <v>是</v>
@@ -5201,7 +5201,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>上海浦东</v>
+        <v>日本</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -5245,22 +5245,22 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B83" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C83" t="str">
-        <v>assets/1785912551260-jplefm937nk.jpeg, assets/videos/02.mp4</v>
+        <v>assets/1785854664100-haqoiu1h7hj.jpeg</v>
       </c>
       <c r="D83" t="str">
         <v>是</v>
       </c>
       <c r="E83" t="str">
-        <v>2026-06-06</v>
+        <v/>
       </c>
       <c r="F83" t="str">
-        <v>浙江温州</v>
+        <v>浙江杭州</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -5304,66 +5304,656 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B84" t="str">
         <v>妹妹</v>
       </c>
       <c r="C84" t="str">
+        <v>assets/1785854690732-orrs40sx9rs.jpeg</v>
+      </c>
+      <c r="D84" t="str">
+        <v>是</v>
+      </c>
+      <c r="E84" t="str">
+        <v/>
+      </c>
+      <c r="F84" t="str">
+        <v>贵州安顺</v>
+      </c>
+      <c r="G84" t="str">
+        <v/>
+      </c>
+      <c r="H84" t="str">
+        <v/>
+      </c>
+      <c r="I84" t="str">
+        <v/>
+      </c>
+      <c r="J84" t="str">
+        <v/>
+      </c>
+      <c r="K84" t="str">
+        <v/>
+      </c>
+      <c r="L84" t="str">
+        <v/>
+      </c>
+      <c r="M84" t="str">
+        <v/>
+      </c>
+      <c r="N84" t="str">
+        <v/>
+      </c>
+      <c r="O84" t="str">
+        <v/>
+      </c>
+      <c r="P84" t="str">
+        <v/>
+      </c>
+      <c r="Q84" t="str">
+        <v/>
+      </c>
+      <c r="R84" t="str">
+        <v/>
+      </c>
+      <c r="S84" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>银虎斑</v>
+      </c>
+      <c r="B85" t="str">
+        <v>妹妹</v>
+      </c>
+      <c r="C85" t="str">
+        <v>assets/1785854734122-wcpmib4m7.jpeg</v>
+      </c>
+      <c r="D85" t="str">
+        <v>是</v>
+      </c>
+      <c r="E85" t="str">
+        <v/>
+      </c>
+      <c r="F85" t="str">
+        <v>山东青岛</v>
+      </c>
+      <c r="G85" t="str">
+        <v/>
+      </c>
+      <c r="H85" t="str">
+        <v/>
+      </c>
+      <c r="I85" t="str">
+        <v/>
+      </c>
+      <c r="J85" t="str">
+        <v/>
+      </c>
+      <c r="K85" t="str">
+        <v/>
+      </c>
+      <c r="L85" t="str">
+        <v/>
+      </c>
+      <c r="M85" t="str">
+        <v/>
+      </c>
+      <c r="N85" t="str">
+        <v/>
+      </c>
+      <c r="O85" t="str">
+        <v/>
+      </c>
+      <c r="P85" t="str">
+        <v/>
+      </c>
+      <c r="Q85" t="str">
+        <v/>
+      </c>
+      <c r="R85" t="str">
+        <v/>
+      </c>
+      <c r="S85" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>银虎斑</v>
+      </c>
+      <c r="B86" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C86" t="str">
+        <v>assets/1785854758707-1kxdkfvs6jc.jpeg</v>
+      </c>
+      <c r="D86" t="str">
+        <v>是</v>
+      </c>
+      <c r="E86" t="str">
+        <v/>
+      </c>
+      <c r="F86" t="str">
+        <v>黑龙江漠河</v>
+      </c>
+      <c r="G86" t="str">
+        <v/>
+      </c>
+      <c r="H86" t="str">
+        <v/>
+      </c>
+      <c r="I86" t="str">
+        <v/>
+      </c>
+      <c r="J86" t="str">
+        <v/>
+      </c>
+      <c r="K86" t="str">
+        <v/>
+      </c>
+      <c r="L86" t="str">
+        <v/>
+      </c>
+      <c r="M86" t="str">
+        <v/>
+      </c>
+      <c r="N86" t="str">
+        <v/>
+      </c>
+      <c r="O86" t="str">
+        <v/>
+      </c>
+      <c r="P86" t="str">
+        <v/>
+      </c>
+      <c r="Q86" t="str">
+        <v/>
+      </c>
+      <c r="R86" t="str">
+        <v/>
+      </c>
+      <c r="S86" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>纯蓝色</v>
+      </c>
+      <c r="B87" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C87" t="str">
+        <v>assets/1785854784780-3g0u60pdo93.jpeg</v>
+      </c>
+      <c r="D87" t="str">
+        <v>是</v>
+      </c>
+      <c r="E87" t="str">
+        <v/>
+      </c>
+      <c r="F87" t="str">
+        <v>河南鹤壁</v>
+      </c>
+      <c r="G87" t="str">
+        <v/>
+      </c>
+      <c r="H87" t="str">
+        <v/>
+      </c>
+      <c r="I87" t="str">
+        <v/>
+      </c>
+      <c r="J87" t="str">
+        <v/>
+      </c>
+      <c r="K87" t="str">
+        <v/>
+      </c>
+      <c r="L87" t="str">
+        <v/>
+      </c>
+      <c r="M87" t="str">
+        <v/>
+      </c>
+      <c r="N87" t="str">
+        <v/>
+      </c>
+      <c r="O87" t="str">
+        <v/>
+      </c>
+      <c r="P87" t="str">
+        <v/>
+      </c>
+      <c r="Q87" t="str">
+        <v/>
+      </c>
+      <c r="R87" t="str">
+        <v/>
+      </c>
+      <c r="S87" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>银虎斑</v>
+      </c>
+      <c r="B88" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C88" t="str">
+        <v>assets/1785854813179-8oyxr0h2bbu.jpeg</v>
+      </c>
+      <c r="D88" t="str">
+        <v>是</v>
+      </c>
+      <c r="E88" t="str">
+        <v/>
+      </c>
+      <c r="F88" t="str">
+        <v>陕西西安</v>
+      </c>
+      <c r="G88" t="str">
+        <v/>
+      </c>
+      <c r="H88" t="str">
+        <v/>
+      </c>
+      <c r="I88" t="str">
+        <v/>
+      </c>
+      <c r="J88" t="str">
+        <v/>
+      </c>
+      <c r="K88" t="str">
+        <v/>
+      </c>
+      <c r="L88" t="str">
+        <v/>
+      </c>
+      <c r="M88" t="str">
+        <v/>
+      </c>
+      <c r="N88" t="str">
+        <v/>
+      </c>
+      <c r="O88" t="str">
+        <v/>
+      </c>
+      <c r="P88" t="str">
+        <v/>
+      </c>
+      <c r="Q88" t="str">
+        <v/>
+      </c>
+      <c r="R88" t="str">
+        <v/>
+      </c>
+      <c r="S88" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>棕虎斑</v>
+      </c>
+      <c r="B89" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C89" t="str">
+        <v>assets/1785854838933-uq6amircyzd.jpeg</v>
+      </c>
+      <c r="D89" t="str">
+        <v>是</v>
+      </c>
+      <c r="E89" t="str">
+        <v/>
+      </c>
+      <c r="F89" t="str">
+        <v>四川成都</v>
+      </c>
+      <c r="G89" t="str">
+        <v/>
+      </c>
+      <c r="H89" t="str">
+        <v/>
+      </c>
+      <c r="I89" t="str">
+        <v/>
+      </c>
+      <c r="J89" t="str">
+        <v/>
+      </c>
+      <c r="K89" t="str">
+        <v/>
+      </c>
+      <c r="L89" t="str">
+        <v/>
+      </c>
+      <c r="M89" t="str">
+        <v/>
+      </c>
+      <c r="N89" t="str">
+        <v/>
+      </c>
+      <c r="O89" t="str">
+        <v/>
+      </c>
+      <c r="P89" t="str">
+        <v/>
+      </c>
+      <c r="Q89" t="str">
+        <v/>
+      </c>
+      <c r="R89" t="str">
+        <v/>
+      </c>
+      <c r="S89" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>烟灰色</v>
+      </c>
+      <c r="B90" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C90" t="str">
+        <v>assets/1785854869973-za3p6wikqpo.jpeg</v>
+      </c>
+      <c r="D90" t="str">
+        <v>否</v>
+      </c>
+      <c r="E90" t="str">
+        <v>2026-05-18</v>
+      </c>
+      <c r="F90" t="str">
+        <v/>
+      </c>
+      <c r="G90" t="str">
+        <v/>
+      </c>
+      <c r="H90" t="str">
+        <v/>
+      </c>
+      <c r="I90" t="str">
+        <v/>
+      </c>
+      <c r="J90" t="str">
+        <v/>
+      </c>
+      <c r="K90" t="str">
+        <v/>
+      </c>
+      <c r="L90" t="str">
+        <v/>
+      </c>
+      <c r="M90" t="str">
+        <v/>
+      </c>
+      <c r="N90" t="str">
+        <v/>
+      </c>
+      <c r="O90" t="str">
+        <v/>
+      </c>
+      <c r="P90" t="str">
+        <v/>
+      </c>
+      <c r="Q90" t="str">
+        <v/>
+      </c>
+      <c r="R90" t="str">
+        <v/>
+      </c>
+      <c r="S90" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>银虎斑</v>
+      </c>
+      <c r="B91" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C91" t="str">
+        <v>assets/1785854997023-mawkallt2a.jpeg</v>
+      </c>
+      <c r="D91" t="str">
+        <v>是</v>
+      </c>
+      <c r="E91" t="str">
+        <v/>
+      </c>
+      <c r="F91" t="str">
+        <v>新加坡</v>
+      </c>
+      <c r="G91" t="str">
+        <v/>
+      </c>
+      <c r="H91" t="str">
+        <v/>
+      </c>
+      <c r="I91" t="str">
+        <v/>
+      </c>
+      <c r="J91" t="str">
+        <v/>
+      </c>
+      <c r="K91" t="str">
+        <v/>
+      </c>
+      <c r="L91" t="str">
+        <v/>
+      </c>
+      <c r="M91" t="str">
+        <v/>
+      </c>
+      <c r="N91" t="str">
+        <v/>
+      </c>
+      <c r="O91" t="str">
+        <v/>
+      </c>
+      <c r="P91" t="str">
+        <v/>
+      </c>
+      <c r="Q91" t="str">
+        <v/>
+      </c>
+      <c r="R91" t="str">
+        <v/>
+      </c>
+      <c r="S91" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>凯米尔色</v>
+      </c>
+      <c r="B92" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C92" t="str">
+        <v>assets/1785855043327-wdc5pxwm34k.jpeg</v>
+      </c>
+      <c r="D92" t="str">
+        <v>是</v>
+      </c>
+      <c r="E92" t="str">
+        <v/>
+      </c>
+      <c r="F92" t="str">
+        <v>上海浦东</v>
+      </c>
+      <c r="G92" t="str">
+        <v/>
+      </c>
+      <c r="H92" t="str">
+        <v/>
+      </c>
+      <c r="I92" t="str">
+        <v/>
+      </c>
+      <c r="J92" t="str">
+        <v/>
+      </c>
+      <c r="K92" t="str">
+        <v/>
+      </c>
+      <c r="L92" t="str">
+        <v/>
+      </c>
+      <c r="M92" t="str">
+        <v/>
+      </c>
+      <c r="N92" t="str">
+        <v/>
+      </c>
+      <c r="O92" t="str">
+        <v/>
+      </c>
+      <c r="P92" t="str">
+        <v/>
+      </c>
+      <c r="Q92" t="str">
+        <v/>
+      </c>
+      <c r="R92" t="str">
+        <v/>
+      </c>
+      <c r="S92" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>棕虎斑</v>
+      </c>
+      <c r="B93" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C93" t="str">
+        <v>assets/1785912551260-jplefm937nk.jpeg, assets/videos/02.mp4</v>
+      </c>
+      <c r="D93" t="str">
+        <v>是</v>
+      </c>
+      <c r="E93" t="str">
+        <v>2026-06-06</v>
+      </c>
+      <c r="F93" t="str">
+        <v>浙江温州</v>
+      </c>
+      <c r="G93" t="str">
+        <v/>
+      </c>
+      <c r="H93" t="str">
+        <v/>
+      </c>
+      <c r="I93" t="str">
+        <v/>
+      </c>
+      <c r="J93" t="str">
+        <v/>
+      </c>
+      <c r="K93" t="str">
+        <v/>
+      </c>
+      <c r="L93" t="str">
+        <v/>
+      </c>
+      <c r="M93" t="str">
+        <v/>
+      </c>
+      <c r="N93" t="str">
+        <v/>
+      </c>
+      <c r="O93" t="str">
+        <v/>
+      </c>
+      <c r="P93" t="str">
+        <v/>
+      </c>
+      <c r="Q93" t="str">
+        <v/>
+      </c>
+      <c r="R93" t="str">
+        <v/>
+      </c>
+      <c r="S93" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>棕虎斑</v>
+      </c>
+      <c r="B94" t="str">
+        <v>妹妹</v>
+      </c>
+      <c r="C94" t="str">
         <v>assets/1785912694000-m20f5kvvrr.jpeg</v>
       </c>
-      <c r="D84" t="str">
-        <v>否</v>
-      </c>
-      <c r="E84" t="str">
+      <c r="D94" t="str">
+        <v>否</v>
+      </c>
+      <c r="E94" t="str">
         <v>2026-06-06</v>
       </c>
-      <c r="F84" t="str">
-        <v/>
-      </c>
-      <c r="G84" t="str">
-        <v/>
-      </c>
-      <c r="H84" t="str">
-        <v/>
-      </c>
-      <c r="I84" t="str">
-        <v/>
-      </c>
-      <c r="J84" t="str">
-        <v/>
-      </c>
-      <c r="K84" t="str">
-        <v/>
-      </c>
-      <c r="L84" t="str">
-        <v/>
-      </c>
-      <c r="M84" t="str">
-        <v/>
-      </c>
-      <c r="N84" t="str">
-        <v/>
-      </c>
-      <c r="O84" t="str">
-        <v/>
-      </c>
-      <c r="P84" t="str">
-        <v/>
-      </c>
-      <c r="Q84" t="str">
-        <v/>
-      </c>
-      <c r="R84" t="str">
-        <v/>
-      </c>
-      <c r="S84" t="str">
+      <c r="F94" t="str">
+        <v/>
+      </c>
+      <c r="G94" t="str">
+        <v/>
+      </c>
+      <c r="H94" t="str">
+        <v/>
+      </c>
+      <c r="I94" t="str">
+        <v/>
+      </c>
+      <c r="J94" t="str">
+        <v/>
+      </c>
+      <c r="K94" t="str">
+        <v/>
+      </c>
+      <c r="L94" t="str">
+        <v/>
+      </c>
+      <c r="M94" t="str">
+        <v/>
+      </c>
+      <c r="N94" t="str">
+        <v/>
+      </c>
+      <c r="O94" t="str">
+        <v/>
+      </c>
+      <c r="P94" t="str">
+        <v/>
+      </c>
+      <c r="Q94" t="str">
+        <v/>
+      </c>
+      <c r="R94" t="str">
+        <v/>
+      </c>
+      <c r="S94" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S84"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S94"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S94"/>
+  <dimension ref="A1:S122"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -466,13 +466,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>银虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B2" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C2" t="str">
-        <v>assets/1787322988096-6e2f54q7vo.jpg</v>
+        <v>assets/1787325862706-wq18k3ej56.jpg</v>
       </c>
       <c r="D2" t="str">
         <v>是</v>
@@ -481,7 +481,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>浙江宁波</v>
+        <v>江苏苏州</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -525,13 +525,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>银虎斑补丁</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B3" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C3" t="str">
-        <v>assets/1787322938518-85ev8bs2k5.jpg</v>
+        <v>assets/1787325743258-a7oac7hzlo.jpg</v>
       </c>
       <c r="D3" t="str">
         <v>是</v>
@@ -540,7 +540,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>马来西亚</v>
+        <v>江苏苏州</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -590,7 +590,7 @@
         <v>弟弟</v>
       </c>
       <c r="C4" t="str">
-        <v>assets/1787322881183-tzu9xtw2sg.jpg</v>
+        <v>assets/1787325706797-kgk81ghccy.jpg</v>
       </c>
       <c r="D4" t="str">
         <v>是</v>
@@ -599,7 +599,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>陕西西安</v>
+        <v>北京</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -643,13 +643,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>纯黑色</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B5" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C5" t="str">
-        <v>assets/1787322840098-nhy4jjyx7k.jpg</v>
+        <v>assets/1787325603704-lahzgrm7fa.jpg,assets/1787325690106-wgu3spujit.jpg</v>
       </c>
       <c r="D5" t="str">
         <v>是</v>
@@ -658,7 +658,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>广西南宁</v>
+        <v>上海</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -705,10 +705,10 @@
         <v>棕虎斑</v>
       </c>
       <c r="B6" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C6" t="str">
-        <v>assets/1787322760950-gn3qgego4s.jpg</v>
+        <v>assets/1787325554341-608thexrne.jpg</v>
       </c>
       <c r="D6" t="str">
         <v>是</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>广西南宁</v>
+        <v>江苏苏州</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -761,13 +761,13 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>红虎斑</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B7" t="str">
         <v>弟弟</v>
       </c>
       <c r="C7" t="str">
-        <v>assets/1787322605982-04n50xegt2.jpg</v>
+        <v>assets/1787325480828-q90pskoiw3.jpg</v>
       </c>
       <c r="D7" t="str">
         <v>是</v>
@@ -776,7 +776,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>上海</v>
+        <v>四川成都</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -820,13 +820,13 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>蓝虎斑</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B8" t="str">
         <v>妹妹</v>
       </c>
       <c r="C8" t="str">
-        <v>assets/1787322490045-kog3ru43dy.jpg</v>
+        <v>assets/1787325448999-a2pg8176fu.jpg</v>
       </c>
       <c r="D8" t="str">
         <v>是</v>
@@ -835,7 +835,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>上海</v>
+        <v>中国台湾</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -879,13 +879,13 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>红虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B9" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C9" t="str">
-        <v>assets/1787322419996-0m33yx89nm.jpg</v>
+        <v>assets/1787325357634-k55zlfhmqj.jpg</v>
       </c>
       <c r="D9" t="str">
         <v>是</v>
@@ -894,7 +894,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>广东广州</v>
+        <v>浙江杭州</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -938,13 +938,13 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>浅色银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B10" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C10" t="str">
-        <v>assets/1787322377730-vj5csj2mll.jpg</v>
+        <v>assets/1787325237876-t19isaq5gu.jpg</v>
       </c>
       <c r="D10" t="str">
         <v>是</v>
@@ -953,7 +953,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>柬埔寨</v>
+        <v>辽宁沈阳</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -997,13 +997,13 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>蓝虎斑</v>
+        <v>金棕虎斑</v>
       </c>
       <c r="B11" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C11" t="str">
-        <v>assets/1787322269611-53yaj5ideu.jpg</v>
+        <v>assets/1787325199931-e7wms9qtya.jpg</v>
       </c>
       <c r="D11" t="str">
         <v>是</v>
@@ -1012,7 +1012,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>山东枣庄</v>
+        <v>四川成都</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -1056,13 +1056,13 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B12" t="str">
         <v>弟弟</v>
       </c>
       <c r="C12" t="str">
-        <v>assets/1787321989528-7d6liuhuk9.jpg</v>
+        <v>assets/1787325172354-4sa8uzaey2.jpg</v>
       </c>
       <c r="D12" t="str">
         <v>是</v>
@@ -1071,7 +1071,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>陕西西安</v>
+        <v>中国香港</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -1115,13 +1115,13 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B13" t="str">
         <v>弟弟</v>
       </c>
       <c r="C13" t="str">
-        <v>assets/1787321941642-xlrc1no2ua.jpg</v>
+        <v>assets/1787325109283-y7mvkk6qg4.jpg</v>
       </c>
       <c r="D13" t="str">
         <v>是</v>
@@ -1130,7 +1130,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>山东东营</v>
+        <v>中国澳门</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -1174,13 +1174,13 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>凯米尔色</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B14" t="str">
         <v>弟弟</v>
       </c>
       <c r="C14" t="str">
-        <v>assets/1787321903535-6orj7qcgzn.jpg</v>
+        <v>assets/1787325033629-y3ygps3zaj.jpg</v>
       </c>
       <c r="D14" t="str">
         <v>是</v>
@@ -1189,7 +1189,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>中国台湾</v>
+        <v>山东青岛</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -1236,10 +1236,10 @@
         <v>烟灰色</v>
       </c>
       <c r="B15" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C15" t="str">
-        <v>assets/1787321858985-v4qej7cq7g.jpg</v>
+        <v>assets/1787324954998-w5m5jox439.jpg</v>
       </c>
       <c r="D15" t="str">
         <v>是</v>
@@ -1248,7 +1248,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>中国台湾</v>
+        <v>海南海口</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -1292,13 +1292,13 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B16" t="str">
         <v>弟弟</v>
       </c>
       <c r="C16" t="str">
-        <v>assets/1787321834306-efgnyhujon.jpg</v>
+        <v>assets/1787324905909-zrz8o79kdf.jpg</v>
       </c>
       <c r="D16" t="str">
         <v>是</v>
@@ -1307,7 +1307,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>北京</v>
+        <v>内蒙古</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1351,13 +1351,13 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B17" t="str">
         <v>弟弟</v>
       </c>
       <c r="C17" t="str">
-        <v>assets/1787321439916-uttgpbkogb.jpg</v>
+        <v>assets/1787324880505-gbh0sn7b6j.jpg</v>
       </c>
       <c r="D17" t="str">
         <v>是</v>
@@ -1366,7 +1366,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>安徽合肥</v>
+        <v>中国香港</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1410,13 +1410,13 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B18" t="str">
         <v>弟弟</v>
       </c>
       <c r="C18" t="str">
-        <v>assets/1787321419210-51hhgurygq.jpg</v>
+        <v>assets/1787324806613-31yyz14tsf.jpg</v>
       </c>
       <c r="D18" t="str">
         <v>是</v>
@@ -1425,7 +1425,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>上海</v>
+        <v>四川成都</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1469,13 +1469,13 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>凯米尔色</v>
+        <v>红虎斑</v>
       </c>
       <c r="B19" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C19" t="str">
-        <v>assets/1787321363369-bzjn51j5il.jpg</v>
+        <v>assets/1787324789658-uz6ephkdsh.jpg</v>
       </c>
       <c r="D19" t="str">
         <v>是</v>
@@ -1484,7 +1484,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>中国台湾</v>
+        <v>湖北武汉</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1528,13 +1528,13 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>棕虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B20" t="str">
         <v>弟弟</v>
       </c>
       <c r="C20" t="str">
-        <v>assets/1787321332559-87p6spuch3.jpg</v>
+        <v>assets/1787324522658-smn44crast.jpg</v>
       </c>
       <c r="D20" t="str">
         <v>是</v>
@@ -1543,7 +1543,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>中国台湾</v>
+        <v>湖北武汉</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1590,10 +1590,10 @@
         <v>棕虎斑</v>
       </c>
       <c r="B21" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C21" t="str">
-        <v>assets/1787321232531-59lnzv8y98.jpg</v>
+        <v>assets/1787324365608-6xtrjp7euz.jpg</v>
       </c>
       <c r="D21" t="str">
         <v>是</v>
@@ -1602,7 +1602,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>北京</v>
+        <v>新疆</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1646,13 +1646,13 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>银虎斑</v>
+        <v>浅凯米尔</v>
       </c>
       <c r="B22" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C22" t="str">
-        <v>assets/1787319975814-g1pfa56vfp.jpg</v>
+        <v>assets/1787324331029-d74lcuycf6.jpg</v>
       </c>
       <c r="D22" t="str">
         <v>是</v>
@@ -1661,7 +1661,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>浙江宁波</v>
+        <v>四川成都</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1705,13 +1705,13 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B23" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C23" t="str">
-        <v>assets/1787319800704-v3qeu062ak.jpg</v>
+        <v>assets/1787324297469-ans1lse2l5.jpg</v>
       </c>
       <c r="D23" t="str">
         <v>是</v>
@@ -1720,7 +1720,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>河北唐山</v>
+        <v>四川乐山</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1764,13 +1764,13 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B24" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C24" t="str">
-        <v>assets/1787319745369-zn66xr3bvb.jpg</v>
+        <v>assets/1787324256827-7w383z4bg1.jpg</v>
       </c>
       <c r="D24" t="str">
         <v>是</v>
@@ -1779,7 +1779,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>河北石家庄</v>
+        <v>中国台湾</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1823,13 +1823,13 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>棕虎补丁</v>
+        <v>银虎斑</v>
       </c>
       <c r="B25" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C25" t="str">
-        <v>assets/1787319547969-zqlq35fxxt.jpg</v>
+        <v>assets/1787324228262-y3vwn6i4zk.jpg</v>
       </c>
       <c r="D25" t="str">
         <v>是</v>
@@ -1838,7 +1838,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>韩国</v>
+        <v>四川成都</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1882,13 +1882,13 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>蓝银虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B26" t="str">
         <v>妹妹</v>
       </c>
       <c r="C26" t="str">
-        <v>assets/1787319501376-xscwljnu1j.jpg</v>
+        <v>assets/1787324201418-9tk4ik75mo.jpg</v>
       </c>
       <c r="D26" t="str">
         <v>是</v>
@@ -1897,7 +1897,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>美国</v>
+        <v>江苏南京</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1944,10 +1944,10 @@
         <v>棕虎斑</v>
       </c>
       <c r="B27" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C27" t="str">
-        <v>assets/1787319443529-4a0zqikufx.jpg</v>
+        <v>assets/1787324092513-jpa2rmkci2.jpg</v>
       </c>
       <c r="D27" t="str">
         <v>是</v>
@@ -1956,7 +1956,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>中国台湾</v>
+        <v>江苏南京</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -2000,13 +2000,13 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>蓝虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B28" t="str">
         <v>弟弟</v>
       </c>
       <c r="C28" t="str">
-        <v>assets/1787319356194-lr2d5680i9.jpg</v>
+        <v>assets/1787323318612-soge38hpsf.jpg</v>
       </c>
       <c r="D28" t="str">
         <v>是</v>
@@ -2015,7 +2015,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>中国台湾</v>
+        <v>上海</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -2062,10 +2062,10 @@
         <v>棕虎斑</v>
       </c>
       <c r="B29" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C29" t="str">
-        <v>assets/1787319208828-aizqo4blcv.jpg</v>
+        <v>assets/1787323235892-7yq8ioq01e.jpg</v>
       </c>
       <c r="D29" t="str">
         <v>是</v>
@@ -2074,7 +2074,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>山东淄博</v>
+        <v>四川成都</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -2124,7 +2124,7 @@
         <v>妹妹</v>
       </c>
       <c r="C30" t="str">
-        <v>assets/1787319162970-cc2v8ovnni.jpg</v>
+        <v>assets/1787322988096-6e2f54q7vo.jpg</v>
       </c>
       <c r="D30" t="str">
         <v>是</v>
@@ -2133,7 +2133,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>韩国</v>
+        <v>浙江宁波</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -2177,13 +2177,13 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>棕虎补丁</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B31" t="str">
         <v>妹妹</v>
       </c>
       <c r="C31" t="str">
-        <v>assets/1787319098214-8pwa9yx2wc.jpg</v>
+        <v>assets/1787322938518-85ev8bs2k5.jpg</v>
       </c>
       <c r="D31" t="str">
         <v>是</v>
@@ -2192,7 +2192,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>四川成都</v>
+        <v>马来西亚</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -2242,7 +2242,7 @@
         <v>弟弟</v>
       </c>
       <c r="C32" t="str">
-        <v>assets/1787318867999-3gxdddp72x.jpg</v>
+        <v>assets/1787322881183-tzu9xtw2sg.jpg</v>
       </c>
       <c r="D32" t="str">
         <v>是</v>
@@ -2251,7 +2251,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>广东广州</v>
+        <v>陕西西安</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -2295,13 +2295,13 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>银虎斑</v>
+        <v>纯黑色</v>
       </c>
       <c r="B33" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C33" t="str">
-        <v>assets/1787318609722-0ojb3aikwi.jpg</v>
+        <v>assets/1787322840098-nhy4jjyx7k.jpg</v>
       </c>
       <c r="D33" t="str">
         <v>是</v>
@@ -2310,7 +2310,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>黑龙江鹤岗</v>
+        <v>广西南宁</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -2354,13 +2354,13 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B34" t="str">
         <v>弟弟</v>
       </c>
       <c r="C34" t="str">
-        <v>assets/1787318530612-779fbkfcoi.jpg</v>
+        <v>assets/1787322760950-gn3qgego4s.jpg</v>
       </c>
       <c r="D34" t="str">
         <v>是</v>
@@ -2369,7 +2369,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>天津</v>
+        <v>广西南宁</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -2413,13 +2413,13 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B35" t="str">
         <v>弟弟</v>
       </c>
       <c r="C35" t="str">
-        <v>assets/1787318365475-sj87wtsai3.jpg</v>
+        <v>assets/1787322605982-04n50xegt2.jpg</v>
       </c>
       <c r="D35" t="str">
         <v>是</v>
@@ -2428,7 +2428,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>山西朔州</v>
+        <v>上海</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -2458,7 +2458,7 @@
         <v/>
       </c>
       <c r="P35" t="str">
-        <v>已接猫</v>
+        <v/>
       </c>
       <c r="Q35" t="str">
         <v/>
@@ -2472,13 +2472,13 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B36" t="str">
         <v>妹妹</v>
       </c>
       <c r="C36" t="str">
-        <v>assets/1787318326155-ia4noopjhq.jpg</v>
+        <v>assets/1787322490045-kog3ru43dy.jpg</v>
       </c>
       <c r="D36" t="str">
         <v>是</v>
@@ -2487,7 +2487,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>贵州</v>
+        <v>上海</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -2531,22 +2531,22 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>棕虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B37" t="str">
         <v>弟弟</v>
       </c>
       <c r="C37" t="str">
-        <v>assets/1787304479674-w0trechn4p.jpg</v>
+        <v>assets/1787322419996-0m33yx89nm.jpg</v>
       </c>
       <c r="D37" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E37" t="str">
-        <v>2026-06-06</v>
+        <v/>
       </c>
       <c r="F37" t="str">
-        <v/>
+        <v>广东广州</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -2585,27 +2585,27 @@
         <v/>
       </c>
       <c r="S37" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>纯黑色</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B38" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C38" t="str">
-        <v>assets/1787283819124-4v7d1w01la.jpg</v>
+        <v>assets/1787322377730-vj5csj2mll.jpg</v>
       </c>
       <c r="D38" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E38" t="str">
-        <v>2026-02-20</v>
+        <v/>
       </c>
       <c r="F38" t="str">
-        <v/>
+        <v>柬埔寨</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -2644,27 +2644,27 @@
         <v/>
       </c>
       <c r="S38" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>阴影色NS12</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B39" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C39" t="str">
-        <v>assets/1787283212708-jdnyi6ecci.jpg</v>
+        <v>assets/1787322269611-53yaj5ideu.jpg</v>
       </c>
       <c r="D39" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E39" t="str">
-        <v>2026-05-28</v>
+        <v/>
       </c>
       <c r="F39" t="str">
-        <v/>
+        <v>山东枣庄</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -2703,27 +2703,27 @@
         <v/>
       </c>
       <c r="S39" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>阴影色NS11</v>
+        <v>银虎斑</v>
       </c>
       <c r="B40" t="str">
         <v>弟弟</v>
       </c>
       <c r="C40" t="str">
-        <v>assets/1787283153501-s2tjg9spwu.jpg</v>
+        <v>assets/1787321989528-7d6liuhuk9.jpg</v>
       </c>
       <c r="D40" t="str">
         <v>是</v>
       </c>
       <c r="E40" t="str">
-        <v>2026-06-15</v>
+        <v/>
       </c>
       <c r="F40" t="str">
-        <v>重庆</v>
+        <v>陕西西安</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -2762,27 +2762,27 @@
         <v/>
       </c>
       <c r="S40" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>浅烟灰色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B41" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C41" t="str">
-        <v>assets/1787283092677-i4d8tyrjtf.jpg</v>
+        <v>assets/1787321941642-xlrc1no2ua.jpg</v>
       </c>
       <c r="D41" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E41" t="str">
-        <v>2026-03-21</v>
+        <v/>
       </c>
       <c r="F41" t="str">
-        <v/>
+        <v>山东东营</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -2821,27 +2821,27 @@
         <v/>
       </c>
       <c r="S41" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>棕虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B42" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C42" t="str">
-        <v>assets/1787283031104-bpyq9wy2tl.jpg</v>
+        <v>assets/1787321903535-6orj7qcgzn.jpg</v>
       </c>
       <c r="D42" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E42" t="str">
-        <v>2026-06-06</v>
+        <v/>
       </c>
       <c r="F42" t="str">
-        <v/>
+        <v>中国台湾</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -2880,27 +2880,27 @@
         <v/>
       </c>
       <c r="S42" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>棕虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B43" t="str">
         <v>妹妹</v>
       </c>
       <c r="C43" t="str">
-        <v>assets/1787282991501-2fjfws0rqw.jpg</v>
+        <v>assets/1787321858985-v4qej7cq7g.jpg</v>
       </c>
       <c r="D43" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E43" t="str">
-        <v>2026-06-06</v>
+        <v/>
       </c>
       <c r="F43" t="str">
-        <v/>
+        <v>中国台湾</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2939,27 +2939,27 @@
         <v/>
       </c>
       <c r="S43" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B44" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C44" t="str">
-        <v>assets/1787282942262-syr48fym6c.jpg</v>
+        <v>assets/1787321834306-efgnyhujon.jpg</v>
       </c>
       <c r="D44" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E44" t="str">
-        <v>2026-06-15</v>
+        <v/>
       </c>
       <c r="F44" t="str">
-        <v/>
+        <v>北京</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2998,27 +2998,27 @@
         <v/>
       </c>
       <c r="S44" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B45" t="str">
         <v>弟弟</v>
       </c>
       <c r="C45" t="str">
-        <v>assets/1787282819855-7vhx3m0v40.jpg</v>
+        <v>assets/1787321439916-uttgpbkogb.jpg</v>
       </c>
       <c r="D45" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E45" t="str">
-        <v>2026-06-06</v>
+        <v/>
       </c>
       <c r="F45" t="str">
-        <v/>
+        <v>安徽合肥</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -3057,27 +3057,27 @@
         <v/>
       </c>
       <c r="S45" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B46" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C46" t="str">
-        <v>assets/1787282703381-2uakw592b4.jpg</v>
+        <v>assets/1787321419210-51hhgurygq.jpg</v>
       </c>
       <c r="D46" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E46" t="str">
-        <v>2026-06-06</v>
+        <v/>
       </c>
       <c r="F46" t="str">
-        <v/>
+        <v>上海</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -3116,27 +3116,27 @@
         <v/>
       </c>
       <c r="S46" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>烟灰色</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B47" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C47" t="str">
-        <v>assets/1787282649397-9hc31ncrpc.jpg</v>
+        <v>assets/1787321363369-bzjn51j5il.jpg</v>
       </c>
       <c r="D47" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E47" t="str">
-        <v>2026-06-06</v>
+        <v/>
       </c>
       <c r="F47" t="str">
-        <v/>
+        <v>中国台湾</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -3175,27 +3175,27 @@
         <v/>
       </c>
       <c r="S47" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B48" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C48" t="str">
-        <v>assets/1787282617957-svcoyyznpg.jpg</v>
+        <v>assets/1787321332559-87p6spuch3.jpg</v>
       </c>
       <c r="D48" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E48" t="str">
-        <v>2026-06-06</v>
+        <v/>
       </c>
       <c r="F48" t="str">
-        <v/>
+        <v>中国台湾</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -3234,27 +3234,27 @@
         <v/>
       </c>
       <c r="S48" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B49" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C49" t="str">
-        <v>assets/1787282419632-78nixqjzua.jpg</v>
+        <v>assets/1787321232531-59lnzv8y98.jpg</v>
       </c>
       <c r="D49" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E49" t="str">
-        <v>2026-06-06</v>
+        <v/>
       </c>
       <c r="F49" t="str">
-        <v/>
+        <v>北京</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -3293,27 +3293,27 @@
         <v/>
       </c>
       <c r="S49" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>纯黑色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B50" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C50" t="str">
-        <v>assets/1787282349942-2cfuyn7xlc.jpg</v>
+        <v>assets/1787319975814-g1pfa56vfp.jpg</v>
       </c>
       <c r="D50" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E50" t="str">
-        <v>2026-03-21</v>
+        <v/>
       </c>
       <c r="F50" t="str">
-        <v/>
+        <v>浙江宁波</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -3352,7 +3352,7 @@
         <v/>
       </c>
       <c r="S50" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="51">
@@ -3360,19 +3360,19 @@
         <v>银虎斑</v>
       </c>
       <c r="B51" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C51" t="str">
-        <v>assets/1787282064159-6b4z8c5msd.jpg</v>
+        <v>assets/1787319800704-v3qeu062ak.jpg</v>
       </c>
       <c r="D51" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E51" t="str">
-        <v>2026-06-10</v>
+        <v/>
       </c>
       <c r="F51" t="str">
-        <v/>
+        <v>河北唐山</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -3411,27 +3411,27 @@
         <v/>
       </c>
       <c r="S51" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>阴影色NS11</v>
+        <v>银虎斑</v>
       </c>
       <c r="B52" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C52" t="str">
-        <v>assets/1787280590041-vzcwebdok1.jpg</v>
+        <v>assets/1787319745369-zn66xr3bvb.jpg</v>
       </c>
       <c r="D52" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E52" t="str">
-        <v>2026-05-28</v>
+        <v/>
       </c>
       <c r="F52" t="str">
-        <v/>
+        <v>河北石家庄</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -3470,27 +3470,27 @@
         <v/>
       </c>
       <c r="S52" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>浅色银虎斑</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B53" t="str">
         <v>妹妹</v>
       </c>
       <c r="C53" t="str">
-        <v>assets/1787281786169-9ia0h837ct.jpg</v>
+        <v>assets/1787319547969-zqlq35fxxt.jpg</v>
       </c>
       <c r="D53" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E53" t="str">
-        <v>2026-06-15</v>
+        <v/>
       </c>
       <c r="F53" t="str">
-        <v/>
+        <v>韩国</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -3529,27 +3529,27 @@
         <v/>
       </c>
       <c r="S53" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>浅烟灰色</v>
+        <v>蓝银虎斑</v>
       </c>
       <c r="B54" t="str">
         <v>妹妹</v>
       </c>
       <c r="C54" t="str">
-        <v>assets/1785843720843-63qz159daui.jpg</v>
+        <v>assets/1787319501376-xscwljnu1j.jpg</v>
       </c>
       <c r="D54" t="str">
         <v>是</v>
       </c>
       <c r="E54" t="str">
-        <v>2026-03-21</v>
+        <v/>
       </c>
       <c r="F54" t="str">
-        <v>四川成都</v>
+        <v>美国</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -3588,27 +3588,27 @@
         <v/>
       </c>
       <c r="S54" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>凯米尔色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B55" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C55" t="str">
-        <v>assets/1787301984056-iu6afro5z5.jpg, assets/1785843763310-elg05ur61ri.jpg</v>
+        <v>assets/1787319443529-4a0zqikufx.jpg</v>
       </c>
       <c r="D55" t="str">
         <v>是</v>
       </c>
       <c r="E55" t="str">
-        <v>2026-02-14</v>
+        <v/>
       </c>
       <c r="F55" t="str">
-        <v>上海浦东</v>
+        <v>中国台湾</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -3647,27 +3647,27 @@
         <v/>
       </c>
       <c r="S55" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>银虎斑补丁</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B56" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C56" t="str">
-        <v>assets/1785843820715-9kz7gy4mbr7.jpg</v>
+        <v>assets/1787319356194-lr2d5680i9.jpg</v>
       </c>
       <c r="D56" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E56" t="str">
-        <v>2026-03-05</v>
+        <v/>
       </c>
       <c r="F56" t="str">
-        <v/>
+        <v>中国台湾</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -3706,27 +3706,27 @@
         <v/>
       </c>
       <c r="S56" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B57" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C57" t="str">
-        <v>assets/1785843953805-mxl3x1982io.jpg</v>
+        <v>assets/1787319208828-aizqo4blcv.jpg</v>
       </c>
       <c r="D57" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E57" t="str">
-        <v>2026-05-18</v>
+        <v/>
       </c>
       <c r="F57" t="str">
-        <v/>
+        <v>山东淄博</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -3765,27 +3765,27 @@
         <v/>
       </c>
       <c r="S57" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>棕虎斑玳瑁</v>
+        <v>银虎斑</v>
       </c>
       <c r="B58" t="str">
         <v>妹妹</v>
       </c>
       <c r="C58" t="str">
-        <v>assets/1785844013835-ek4xpcje7kh.jpg</v>
+        <v>assets/1787319162970-cc2v8ovnni.jpg</v>
       </c>
       <c r="D58" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E58" t="str">
-        <v>2026-02-14</v>
+        <v/>
       </c>
       <c r="F58" t="str">
-        <v/>
+        <v>韩国</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -3824,27 +3824,27 @@
         <v/>
       </c>
       <c r="S58" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>银虎斑补丁</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B59" t="str">
         <v>妹妹</v>
       </c>
       <c r="C59" t="str">
-        <v>assets/1785844434338-ek5zbdgdcne.jpg</v>
+        <v>assets/1787319098214-8pwa9yx2wc.jpg</v>
       </c>
       <c r="D59" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E59" t="str">
-        <v>2026-05-24</v>
+        <v/>
       </c>
       <c r="F59" t="str">
-        <v/>
+        <v>四川成都</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -3883,7 +3883,7 @@
         <v/>
       </c>
       <c r="S59" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="60">
@@ -3891,19 +3891,19 @@
         <v>银虎斑</v>
       </c>
       <c r="B60" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C60" t="str">
-        <v>assets/1785838787730-s5f333sc3u.jpg</v>
+        <v>assets/1787318867999-3gxdddp72x.jpg</v>
       </c>
       <c r="D60" t="str">
         <v>是</v>
       </c>
       <c r="E60" t="str">
-        <v>2026-06-05</v>
+        <v/>
       </c>
       <c r="F60" t="str">
-        <v>湖北恩施</v>
+        <v>广东广州</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -3942,7 +3942,7 @@
         <v/>
       </c>
       <c r="S60" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="61">
@@ -3953,16 +3953,16 @@
         <v>弟弟</v>
       </c>
       <c r="C61" t="str">
-        <v>assets/1785842296661-6qw3zs3as8h.jpg</v>
+        <v>assets/1787318609722-0ojb3aikwi.jpg</v>
       </c>
       <c r="D61" t="str">
         <v>是</v>
       </c>
       <c r="E61" t="str">
-        <v>2026-06-05</v>
+        <v/>
       </c>
       <c r="F61" t="str">
-        <v>湖北恩施</v>
+        <v>黑龙江鹤岗</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -4001,27 +4001,27 @@
         <v/>
       </c>
       <c r="S61" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B62" t="str">
         <v>弟弟</v>
       </c>
       <c r="C62" t="str">
-        <v>assets/1785842429109-porc98rel5.jpg</v>
+        <v>assets/1787318530612-779fbkfcoi.jpg</v>
       </c>
       <c r="D62" t="str">
         <v>是</v>
       </c>
       <c r="E62" t="str">
-        <v>2025-11-05</v>
+        <v/>
       </c>
       <c r="F62" t="str">
-        <v>韩国</v>
+        <v>天津</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -4060,7 +4060,7 @@
         <v/>
       </c>
       <c r="S62" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="63">
@@ -4068,19 +4068,19 @@
         <v>银虎斑</v>
       </c>
       <c r="B63" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C63" t="str">
-        <v>assets/1785842594141-fcglbzjp509.jpg</v>
+        <v>assets/1787318365475-sj87wtsai3.jpg</v>
       </c>
       <c r="D63" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E63" t="str">
-        <v>2026-05-18</v>
+        <v/>
       </c>
       <c r="F63" t="str">
-        <v/>
+        <v>山西朔州</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -4110,7 +4110,7 @@
         <v/>
       </c>
       <c r="P63" t="str">
-        <v/>
+        <v>已接猫</v>
       </c>
       <c r="Q63" t="str">
         <v/>
@@ -4119,27 +4119,27 @@
         <v/>
       </c>
       <c r="S63" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B64" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C64" t="str">
-        <v>assets/1785842639100-82k775dhwiv.jpg</v>
+        <v>assets/1787318326155-ia4noopjhq.jpg</v>
       </c>
       <c r="D64" t="str">
         <v>是</v>
       </c>
       <c r="E64" t="str">
-        <v>2026-05-28</v>
+        <v/>
       </c>
       <c r="F64" t="str">
-        <v>四川自贡</v>
+        <v>贵州</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -4178,7 +4178,7 @@
         <v/>
       </c>
       <c r="S64" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="65">
@@ -4186,10 +4186,10 @@
         <v>棕虎斑</v>
       </c>
       <c r="B65" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C65" t="str">
-        <v>assets/1785842684502-mnhr0r96eee.jpg</v>
+        <v>assets/1787304479674-w0trechn4p.jpg</v>
       </c>
       <c r="D65" t="str">
         <v>否</v>
@@ -4248,13 +4248,13 @@
         <v>妹妹</v>
       </c>
       <c r="C66" t="str">
-        <v>assets/1785842779532-5u1j0igrw1s.jpg</v>
+        <v>assets/1787283819124-4v7d1w01la.jpg</v>
       </c>
       <c r="D66" t="str">
         <v>否</v>
       </c>
       <c r="E66" t="str">
-        <v>2026-03-05</v>
+        <v>2026-02-20</v>
       </c>
       <c r="F66" t="str">
         <v/>
@@ -4301,22 +4301,22 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>银虎斑</v>
+        <v>阴影色NS12</v>
       </c>
       <c r="B67" t="str">
         <v>妹妹</v>
       </c>
       <c r="C67" t="str">
-        <v>assets/1785842817046-6keqv4rw4yf.jpg</v>
+        <v>assets/1787283212708-jdnyi6ecci.jpg</v>
       </c>
       <c r="D67" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E67" t="str">
-        <v>2026-03-05</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F67" t="str">
-        <v>韩国</v>
+        <v/>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -4360,22 +4360,22 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>浅色银虎斑</v>
+        <v>阴影色NS11</v>
       </c>
       <c r="B68" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C68" t="str">
-        <v>assets/1785842950972-a88lbrskpc.jpg</v>
+        <v>assets/1787283153501-s2tjg9spwu.jpg</v>
       </c>
       <c r="D68" t="str">
         <v>是</v>
       </c>
       <c r="E68" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F68" t="str">
-        <v>河北邢台</v>
+        <v>重庆</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -4419,22 +4419,22 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>棕虎斑</v>
+        <v>浅烟灰色</v>
       </c>
       <c r="B69" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C69" t="str">
-        <v>assets/1785843011477-n3l1wi6ech.jpg</v>
+        <v>assets/1787283092677-i4d8tyrjtf.jpg</v>
       </c>
       <c r="D69" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E69" t="str">
-        <v>2026-06-05</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F69" t="str">
-        <v>四川自贡</v>
+        <v/>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -4478,19 +4478,19 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B70" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C70" t="str">
-        <v>assets/1785843237517-ga449iqess5.jpg</v>
+        <v>assets/1787283031104-bpyq9wy2tl.jpg</v>
       </c>
       <c r="D70" t="str">
         <v>否</v>
       </c>
       <c r="E70" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F70" t="str">
         <v/>
@@ -4537,19 +4537,19 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>棕虎斑补丁</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B71" t="str">
         <v>妹妹</v>
       </c>
       <c r="C71" t="str">
-        <v>assets/1785842523893-7nwnnhwi4ns.jpg</v>
+        <v>assets/1787282991501-2fjfws0rqw.jpg</v>
       </c>
       <c r="D71" t="str">
         <v>否</v>
       </c>
       <c r="E71" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F71" t="str">
         <v/>
@@ -4596,19 +4596,19 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B72" t="str">
         <v>妹妹</v>
       </c>
       <c r="C72" t="str">
-        <v>assets/1785843497557-st27fk8drqi.jpg</v>
+        <v>assets/1787282942262-syr48fym6c.jpg</v>
       </c>
       <c r="D72" t="str">
         <v>否</v>
       </c>
       <c r="E72" t="str">
-        <v>2026-04-05</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F72" t="str">
         <v/>
@@ -4655,19 +4655,19 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B73" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C73" t="str">
-        <v>assets/1785843621923-ylhakbtw13i.jpg</v>
+        <v>assets/1787282819855-7vhx3m0v40.jpg</v>
       </c>
       <c r="D73" t="str">
         <v>否</v>
       </c>
       <c r="E73" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F73" t="str">
         <v/>
@@ -4714,19 +4714,19 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B74" t="str">
         <v>妹妹</v>
       </c>
       <c r="C74" t="str">
-        <v>assets/1785843663884-sfxvpmiet7.jpg</v>
+        <v>assets/1787282703381-2uakw592b4.jpg</v>
       </c>
       <c r="D74" t="str">
         <v>否</v>
       </c>
       <c r="E74" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F74" t="str">
         <v/>
@@ -4773,52 +4773,52 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>蓝虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B75" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C75" t="str">
-        <v>assets/1785852601940-o236xtv7yx.jpeg</v>
+        <v>assets/1787282649397-9hc31ncrpc.jpg</v>
       </c>
       <c r="D75" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E75" t="str">
-        <v>2026-02-20</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F75" t="str">
-        <v>荷兰</v>
+        <v/>
       </c>
       <c r="G75" t="str">
-        <v>阿泽</v>
+        <v/>
       </c>
       <c r="H75" t="str">
-        <v>小辫子</v>
+        <v/>
       </c>
       <c r="I75" t="str">
-        <v>驺驺</v>
+        <v/>
       </c>
       <c r="J75" t="str">
-        <v>2026-07-02</v>
+        <v/>
       </c>
       <c r="K75" t="str">
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>2026-07-02</v>
+        <v/>
       </c>
       <c r="M75" t="str">
-        <v>2026-08-03</v>
+        <v/>
       </c>
       <c r="N75" t="str">
-        <v>2026-11-04</v>
+        <v/>
       </c>
       <c r="O75" t="str">
-        <v>2026-08-03 · 血清检测,2026-07-02 · 打疫苗 · assets/diary/zouzou-depart.jpg,2026-07-30 · 6.2斤 · 五个月10天了 · assets/feedback/zouzou-1.jpg</v>
+        <v/>
       </c>
       <c r="P75" t="str">
-        <v>已付定金</v>
+        <v/>
       </c>
       <c r="Q75" t="str">
         <v/>
@@ -4827,27 +4827,27 @@
         <v/>
       </c>
       <c r="S75" t="str">
-        <v>否</v>
+        <v/>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>红虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B76" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C76" t="str">
-        <v>assets/1785853950207-cedor66ou2q.jpeg</v>
+        <v>assets/1787282617957-svcoyyznpg.jpg</v>
       </c>
       <c r="D76" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E76" t="str">
-        <v/>
+        <v>2026-06-06</v>
       </c>
       <c r="F76" t="str">
-        <v>广东广州</v>
+        <v/>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -4891,22 +4891,22 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>红虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B77" t="str">
         <v>弟弟</v>
       </c>
       <c r="C77" t="str">
-        <v>assets/1785854129383-c8qkvl537x.jpeg</v>
+        <v>assets/1787282419632-78nixqjzua.jpg</v>
       </c>
       <c r="D77" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E77" t="str">
-        <v/>
+        <v>2026-06-06</v>
       </c>
       <c r="F77" t="str">
-        <v>广东广州</v>
+        <v/>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -4950,22 +4950,22 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>银虎斑</v>
+        <v>纯黑色</v>
       </c>
       <c r="B78" t="str">
         <v>弟弟</v>
       </c>
       <c r="C78" t="str">
-        <v>assets/1785854166720-48r17hry9cd.jpeg</v>
+        <v>assets/1787282349942-2cfuyn7xlc.jpg</v>
       </c>
       <c r="D78" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E78" t="str">
-        <v/>
+        <v>2026-03-21</v>
       </c>
       <c r="F78" t="str">
-        <v>山西朔州</v>
+        <v/>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -5012,19 +5012,19 @@
         <v>银虎斑</v>
       </c>
       <c r="B79" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C79" t="str">
-        <v>assets/1785854224521-2cpg6xipfn6.jpeg</v>
+        <v>assets/1787282064159-6b4z8c5msd.jpg</v>
       </c>
       <c r="D79" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E79" t="str">
-        <v/>
+        <v>2026-06-10</v>
       </c>
       <c r="F79" t="str">
-        <v>浙江宁波</v>
+        <v/>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -5068,22 +5068,22 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>银虎斑</v>
+        <v>阴影色NS11</v>
       </c>
       <c r="B80" t="str">
         <v>弟弟</v>
       </c>
       <c r="C80" t="str">
-        <v>assets/1785854260793-steez4s972l.jpeg</v>
+        <v>assets/1787280590041-vzcwebdok1.jpg</v>
       </c>
       <c r="D80" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E80" t="str">
-        <v/>
+        <v>2026-05-28</v>
       </c>
       <c r="F80" t="str">
-        <v>陕西西安</v>
+        <v/>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -5127,22 +5127,22 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>银虎斑</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B81" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C81" t="str">
-        <v>assets/1785854319988-cohio08aod5.jpeg</v>
+        <v>assets/1787281786169-9ia0h837ct.jpg</v>
       </c>
       <c r="D81" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E81" t="str">
-        <v/>
+        <v>2026-06-15</v>
       </c>
       <c r="F81" t="str">
-        <v>黑龙江漠河</v>
+        <v/>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -5186,22 +5186,22 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>棕虎斑</v>
+        <v>浅烟灰色</v>
       </c>
       <c r="B82" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C82" t="str">
-        <v>assets/1785854520974-96b8b1ekqd9.jpeg</v>
+        <v>assets/1785843720843-63qz159daui.jpg</v>
       </c>
       <c r="D82" t="str">
         <v>是</v>
       </c>
       <c r="E82" t="str">
-        <v/>
+        <v>2026-03-21</v>
       </c>
       <c r="F82" t="str">
-        <v>日本</v>
+        <v>四川成都</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -5245,22 +5245,22 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>银虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B83" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C83" t="str">
-        <v>assets/1785854664100-haqoiu1h7hj.jpeg</v>
+        <v>assets/1787301984056-iu6afro5z5.jpg, assets/1785843763310-elg05ur61ri.jpg</v>
       </c>
       <c r="D83" t="str">
         <v>是</v>
       </c>
       <c r="E83" t="str">
-        <v/>
+        <v>2026-02-14</v>
       </c>
       <c r="F83" t="str">
-        <v>浙江杭州</v>
+        <v>上海浦东</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -5304,22 +5304,22 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>银虎斑</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B84" t="str">
         <v>妹妹</v>
       </c>
       <c r="C84" t="str">
-        <v>assets/1785854690732-orrs40sx9rs.jpeg</v>
+        <v>assets/1785843820715-9kz7gy4mbr7.jpg</v>
       </c>
       <c r="D84" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E84" t="str">
-        <v/>
+        <v>2026-03-05</v>
       </c>
       <c r="F84" t="str">
-        <v>贵州安顺</v>
+        <v/>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -5363,22 +5363,22 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B85" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C85" t="str">
-        <v>assets/1785854734122-wcpmib4m7.jpeg</v>
+        <v>assets/1785843953805-mxl3x1982io.jpg</v>
       </c>
       <c r="D85" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E85" t="str">
-        <v/>
+        <v>2026-05-18</v>
       </c>
       <c r="F85" t="str">
-        <v>山东青岛</v>
+        <v/>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -5422,22 +5422,22 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑玳瑁</v>
       </c>
       <c r="B86" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C86" t="str">
-        <v>assets/1785854758707-1kxdkfvs6jc.jpeg</v>
+        <v>assets/1785844013835-ek4xpcje7kh.jpg</v>
       </c>
       <c r="D86" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E86" t="str">
-        <v/>
+        <v>2026-02-14</v>
       </c>
       <c r="F86" t="str">
-        <v>黑龙江漠河</v>
+        <v/>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -5481,22 +5481,22 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>纯蓝色</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B87" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C87" t="str">
-        <v>assets/1785854784780-3g0u60pdo93.jpeg</v>
+        <v>assets/1785844434338-ek5zbdgdcne.jpg</v>
       </c>
       <c r="D87" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E87" t="str">
-        <v/>
+        <v>2026-05-24</v>
       </c>
       <c r="F87" t="str">
-        <v>河南鹤壁</v>
+        <v/>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -5543,19 +5543,19 @@
         <v>银虎斑</v>
       </c>
       <c r="B88" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C88" t="str">
-        <v>assets/1785854813179-8oyxr0h2bbu.jpeg</v>
+        <v>assets/1785838787730-s5f333sc3u.jpg</v>
       </c>
       <c r="D88" t="str">
         <v>是</v>
       </c>
       <c r="E88" t="str">
-        <v/>
+        <v>2026-06-05</v>
       </c>
       <c r="F88" t="str">
-        <v>陕西西安</v>
+        <v>湖北恩施</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -5599,22 +5599,22 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B89" t="str">
         <v>弟弟</v>
       </c>
       <c r="C89" t="str">
-        <v>assets/1785854838933-uq6amircyzd.jpeg</v>
+        <v>assets/1785842296661-6qw3zs3as8h.jpg</v>
       </c>
       <c r="D89" t="str">
         <v>是</v>
       </c>
       <c r="E89" t="str">
-        <v/>
+        <v>2026-06-05</v>
       </c>
       <c r="F89" t="str">
-        <v>四川成都</v>
+        <v>湖北恩施</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -5658,22 +5658,22 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>烟灰色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B90" t="str">
         <v>弟弟</v>
       </c>
       <c r="C90" t="str">
-        <v>assets/1785854869973-za3p6wikqpo.jpeg</v>
+        <v>assets/1785842429109-porc98rel5.jpg</v>
       </c>
       <c r="D90" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E90" t="str">
-        <v>2026-05-18</v>
+        <v>2025-11-05</v>
       </c>
       <c r="F90" t="str">
-        <v/>
+        <v>韩国</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -5720,19 +5720,19 @@
         <v>银虎斑</v>
       </c>
       <c r="B91" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C91" t="str">
-        <v>assets/1785854997023-mawkallt2a.jpeg</v>
+        <v>assets/1785842594141-fcglbzjp509.jpg</v>
       </c>
       <c r="D91" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E91" t="str">
-        <v/>
+        <v>2026-05-18</v>
       </c>
       <c r="F91" t="str">
-        <v>新加坡</v>
+        <v/>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -5776,22 +5776,22 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>凯米尔色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B92" t="str">
         <v>弟弟</v>
       </c>
       <c r="C92" t="str">
-        <v>assets/1785855043327-wdc5pxwm34k.jpeg</v>
+        <v>assets/1785842639100-82k775dhwiv.jpg</v>
       </c>
       <c r="D92" t="str">
         <v>是</v>
       </c>
       <c r="E92" t="str">
-        <v/>
+        <v>2026-05-28</v>
       </c>
       <c r="F92" t="str">
-        <v>上海浦东</v>
+        <v>四川自贡</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -5838,19 +5838,19 @@
         <v>棕虎斑</v>
       </c>
       <c r="B93" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C93" t="str">
-        <v>assets/1785912551260-jplefm937nk.jpeg, assets/videos/02.mp4</v>
+        <v>assets/1785842684502-mnhr0r96eee.jpg</v>
       </c>
       <c r="D93" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E93" t="str">
         <v>2026-06-06</v>
       </c>
       <c r="F93" t="str">
-        <v>浙江温州</v>
+        <v/>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -5894,66 +5894,1718 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>棕虎斑</v>
+        <v>纯黑色</v>
       </c>
       <c r="B94" t="str">
         <v>妹妹</v>
       </c>
       <c r="C94" t="str">
+        <v>assets/1785842779532-5u1j0igrw1s.jpg</v>
+      </c>
+      <c r="D94" t="str">
+        <v>否</v>
+      </c>
+      <c r="E94" t="str">
+        <v>2026-03-05</v>
+      </c>
+      <c r="F94" t="str">
+        <v/>
+      </c>
+      <c r="G94" t="str">
+        <v/>
+      </c>
+      <c r="H94" t="str">
+        <v/>
+      </c>
+      <c r="I94" t="str">
+        <v/>
+      </c>
+      <c r="J94" t="str">
+        <v/>
+      </c>
+      <c r="K94" t="str">
+        <v/>
+      </c>
+      <c r="L94" t="str">
+        <v/>
+      </c>
+      <c r="M94" t="str">
+        <v/>
+      </c>
+      <c r="N94" t="str">
+        <v/>
+      </c>
+      <c r="O94" t="str">
+        <v/>
+      </c>
+      <c r="P94" t="str">
+        <v/>
+      </c>
+      <c r="Q94" t="str">
+        <v/>
+      </c>
+      <c r="R94" t="str">
+        <v/>
+      </c>
+      <c r="S94" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>银虎斑</v>
+      </c>
+      <c r="B95" t="str">
+        <v>妹妹</v>
+      </c>
+      <c r="C95" t="str">
+        <v>assets/1785842817046-6keqv4rw4yf.jpg</v>
+      </c>
+      <c r="D95" t="str">
+        <v>是</v>
+      </c>
+      <c r="E95" t="str">
+        <v>2026-03-05</v>
+      </c>
+      <c r="F95" t="str">
+        <v>韩国</v>
+      </c>
+      <c r="G95" t="str">
+        <v/>
+      </c>
+      <c r="H95" t="str">
+        <v/>
+      </c>
+      <c r="I95" t="str">
+        <v/>
+      </c>
+      <c r="J95" t="str">
+        <v/>
+      </c>
+      <c r="K95" t="str">
+        <v/>
+      </c>
+      <c r="L95" t="str">
+        <v/>
+      </c>
+      <c r="M95" t="str">
+        <v/>
+      </c>
+      <c r="N95" t="str">
+        <v/>
+      </c>
+      <c r="O95" t="str">
+        <v/>
+      </c>
+      <c r="P95" t="str">
+        <v/>
+      </c>
+      <c r="Q95" t="str">
+        <v/>
+      </c>
+      <c r="R95" t="str">
+        <v/>
+      </c>
+      <c r="S95" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>浅色银虎斑</v>
+      </c>
+      <c r="B96" t="str">
+        <v>妹妹</v>
+      </c>
+      <c r="C96" t="str">
+        <v>assets/1785842950972-a88lbrskpc.jpg</v>
+      </c>
+      <c r="D96" t="str">
+        <v>是</v>
+      </c>
+      <c r="E96" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="F96" t="str">
+        <v>河北邢台</v>
+      </c>
+      <c r="G96" t="str">
+        <v/>
+      </c>
+      <c r="H96" t="str">
+        <v/>
+      </c>
+      <c r="I96" t="str">
+        <v/>
+      </c>
+      <c r="J96" t="str">
+        <v/>
+      </c>
+      <c r="K96" t="str">
+        <v/>
+      </c>
+      <c r="L96" t="str">
+        <v/>
+      </c>
+      <c r="M96" t="str">
+        <v/>
+      </c>
+      <c r="N96" t="str">
+        <v/>
+      </c>
+      <c r="O96" t="str">
+        <v/>
+      </c>
+      <c r="P96" t="str">
+        <v/>
+      </c>
+      <c r="Q96" t="str">
+        <v/>
+      </c>
+      <c r="R96" t="str">
+        <v/>
+      </c>
+      <c r="S96" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>棕虎斑</v>
+      </c>
+      <c r="B97" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C97" t="str">
+        <v>assets/1785843011477-n3l1wi6ech.jpg</v>
+      </c>
+      <c r="D97" t="str">
+        <v>是</v>
+      </c>
+      <c r="E97" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="F97" t="str">
+        <v>四川自贡</v>
+      </c>
+      <c r="G97" t="str">
+        <v/>
+      </c>
+      <c r="H97" t="str">
+        <v/>
+      </c>
+      <c r="I97" t="str">
+        <v/>
+      </c>
+      <c r="J97" t="str">
+        <v/>
+      </c>
+      <c r="K97" t="str">
+        <v/>
+      </c>
+      <c r="L97" t="str">
+        <v/>
+      </c>
+      <c r="M97" t="str">
+        <v/>
+      </c>
+      <c r="N97" t="str">
+        <v/>
+      </c>
+      <c r="O97" t="str">
+        <v/>
+      </c>
+      <c r="P97" t="str">
+        <v/>
+      </c>
+      <c r="Q97" t="str">
+        <v/>
+      </c>
+      <c r="R97" t="str">
+        <v/>
+      </c>
+      <c r="S97" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>蓝虎斑</v>
+      </c>
+      <c r="B98" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C98" t="str">
+        <v>assets/1785843237517-ga449iqess5.jpg</v>
+      </c>
+      <c r="D98" t="str">
+        <v>否</v>
+      </c>
+      <c r="E98" t="str">
+        <v>2026-03-05</v>
+      </c>
+      <c r="F98" t="str">
+        <v/>
+      </c>
+      <c r="G98" t="str">
+        <v/>
+      </c>
+      <c r="H98" t="str">
+        <v/>
+      </c>
+      <c r="I98" t="str">
+        <v/>
+      </c>
+      <c r="J98" t="str">
+        <v/>
+      </c>
+      <c r="K98" t="str">
+        <v/>
+      </c>
+      <c r="L98" t="str">
+        <v/>
+      </c>
+      <c r="M98" t="str">
+        <v/>
+      </c>
+      <c r="N98" t="str">
+        <v/>
+      </c>
+      <c r="O98" t="str">
+        <v/>
+      </c>
+      <c r="P98" t="str">
+        <v/>
+      </c>
+      <c r="Q98" t="str">
+        <v/>
+      </c>
+      <c r="R98" t="str">
+        <v/>
+      </c>
+      <c r="S98" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>棕虎斑补丁</v>
+      </c>
+      <c r="B99" t="str">
+        <v>妹妹</v>
+      </c>
+      <c r="C99" t="str">
+        <v>assets/1785842523893-7nwnnhwi4ns.jpg</v>
+      </c>
+      <c r="D99" t="str">
+        <v>否</v>
+      </c>
+      <c r="E99" t="str">
+        <v>2026-03-05</v>
+      </c>
+      <c r="F99" t="str">
+        <v/>
+      </c>
+      <c r="G99" t="str">
+        <v/>
+      </c>
+      <c r="H99" t="str">
+        <v/>
+      </c>
+      <c r="I99" t="str">
+        <v/>
+      </c>
+      <c r="J99" t="str">
+        <v/>
+      </c>
+      <c r="K99" t="str">
+        <v/>
+      </c>
+      <c r="L99" t="str">
+        <v/>
+      </c>
+      <c r="M99" t="str">
+        <v/>
+      </c>
+      <c r="N99" t="str">
+        <v/>
+      </c>
+      <c r="O99" t="str">
+        <v/>
+      </c>
+      <c r="P99" t="str">
+        <v/>
+      </c>
+      <c r="Q99" t="str">
+        <v/>
+      </c>
+      <c r="R99" t="str">
+        <v/>
+      </c>
+      <c r="S99" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>蓝虎斑</v>
+      </c>
+      <c r="B100" t="str">
+        <v>妹妹</v>
+      </c>
+      <c r="C100" t="str">
+        <v>assets/1785843497557-st27fk8drqi.jpg</v>
+      </c>
+      <c r="D100" t="str">
+        <v>否</v>
+      </c>
+      <c r="E100" t="str">
+        <v>2026-04-05</v>
+      </c>
+      <c r="F100" t="str">
+        <v/>
+      </c>
+      <c r="G100" t="str">
+        <v/>
+      </c>
+      <c r="H100" t="str">
+        <v/>
+      </c>
+      <c r="I100" t="str">
+        <v/>
+      </c>
+      <c r="J100" t="str">
+        <v/>
+      </c>
+      <c r="K100" t="str">
+        <v/>
+      </c>
+      <c r="L100" t="str">
+        <v/>
+      </c>
+      <c r="M100" t="str">
+        <v/>
+      </c>
+      <c r="N100" t="str">
+        <v/>
+      </c>
+      <c r="O100" t="str">
+        <v/>
+      </c>
+      <c r="P100" t="str">
+        <v/>
+      </c>
+      <c r="Q100" t="str">
+        <v/>
+      </c>
+      <c r="R100" t="str">
+        <v/>
+      </c>
+      <c r="S100" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>银虎斑</v>
+      </c>
+      <c r="B101" t="str">
+        <v>妹妹</v>
+      </c>
+      <c r="C101" t="str">
+        <v>assets/1785843621923-ylhakbtw13i.jpg</v>
+      </c>
+      <c r="D101" t="str">
+        <v>否</v>
+      </c>
+      <c r="E101" t="str">
+        <v>2026-03-05</v>
+      </c>
+      <c r="F101" t="str">
+        <v/>
+      </c>
+      <c r="G101" t="str">
+        <v/>
+      </c>
+      <c r="H101" t="str">
+        <v/>
+      </c>
+      <c r="I101" t="str">
+        <v/>
+      </c>
+      <c r="J101" t="str">
+        <v/>
+      </c>
+      <c r="K101" t="str">
+        <v/>
+      </c>
+      <c r="L101" t="str">
+        <v/>
+      </c>
+      <c r="M101" t="str">
+        <v/>
+      </c>
+      <c r="N101" t="str">
+        <v/>
+      </c>
+      <c r="O101" t="str">
+        <v/>
+      </c>
+      <c r="P101" t="str">
+        <v/>
+      </c>
+      <c r="Q101" t="str">
+        <v/>
+      </c>
+      <c r="R101" t="str">
+        <v/>
+      </c>
+      <c r="S101" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>银虎斑</v>
+      </c>
+      <c r="B102" t="str">
+        <v>妹妹</v>
+      </c>
+      <c r="C102" t="str">
+        <v>assets/1785843663884-sfxvpmiet7.jpg</v>
+      </c>
+      <c r="D102" t="str">
+        <v>否</v>
+      </c>
+      <c r="E102" t="str">
+        <v>2026-03-05</v>
+      </c>
+      <c r="F102" t="str">
+        <v/>
+      </c>
+      <c r="G102" t="str">
+        <v/>
+      </c>
+      <c r="H102" t="str">
+        <v/>
+      </c>
+      <c r="I102" t="str">
+        <v/>
+      </c>
+      <c r="J102" t="str">
+        <v/>
+      </c>
+      <c r="K102" t="str">
+        <v/>
+      </c>
+      <c r="L102" t="str">
+        <v/>
+      </c>
+      <c r="M102" t="str">
+        <v/>
+      </c>
+      <c r="N102" t="str">
+        <v/>
+      </c>
+      <c r="O102" t="str">
+        <v/>
+      </c>
+      <c r="P102" t="str">
+        <v/>
+      </c>
+      <c r="Q102" t="str">
+        <v/>
+      </c>
+      <c r="R102" t="str">
+        <v/>
+      </c>
+      <c r="S102" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>蓝虎斑</v>
+      </c>
+      <c r="B103" t="str">
+        <v>妹妹</v>
+      </c>
+      <c r="C103" t="str">
+        <v>assets/1785852601940-o236xtv7yx.jpeg</v>
+      </c>
+      <c r="D103" t="str">
+        <v>是</v>
+      </c>
+      <c r="E103" t="str">
+        <v>2026-02-20</v>
+      </c>
+      <c r="F103" t="str">
+        <v>荷兰</v>
+      </c>
+      <c r="G103" t="str">
+        <v>阿泽</v>
+      </c>
+      <c r="H103" t="str">
+        <v>小辫子</v>
+      </c>
+      <c r="I103" t="str">
+        <v>驺驺</v>
+      </c>
+      <c r="J103" t="str">
+        <v>2026-07-02</v>
+      </c>
+      <c r="K103" t="str">
+        <v/>
+      </c>
+      <c r="L103" t="str">
+        <v>2026-07-02</v>
+      </c>
+      <c r="M103" t="str">
+        <v>2026-08-03</v>
+      </c>
+      <c r="N103" t="str">
+        <v>2026-11-04</v>
+      </c>
+      <c r="O103" t="str">
+        <v>2026-08-03 · 血清检测,2026-07-02 · 打疫苗 · assets/diary/zouzou-depart.jpg,2026-07-30 · 6.2斤 · 五个月10天了 · assets/feedback/zouzou-1.jpg</v>
+      </c>
+      <c r="P103" t="str">
+        <v>已付定金</v>
+      </c>
+      <c r="Q103" t="str">
+        <v/>
+      </c>
+      <c r="R103" t="str">
+        <v/>
+      </c>
+      <c r="S103" t="str">
+        <v>否</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>红虎斑</v>
+      </c>
+      <c r="B104" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C104" t="str">
+        <v>assets/1785853950207-cedor66ou2q.jpeg</v>
+      </c>
+      <c r="D104" t="str">
+        <v>是</v>
+      </c>
+      <c r="E104" t="str">
+        <v/>
+      </c>
+      <c r="F104" t="str">
+        <v>广东广州</v>
+      </c>
+      <c r="G104" t="str">
+        <v/>
+      </c>
+      <c r="H104" t="str">
+        <v/>
+      </c>
+      <c r="I104" t="str">
+        <v/>
+      </c>
+      <c r="J104" t="str">
+        <v/>
+      </c>
+      <c r="K104" t="str">
+        <v/>
+      </c>
+      <c r="L104" t="str">
+        <v/>
+      </c>
+      <c r="M104" t="str">
+        <v/>
+      </c>
+      <c r="N104" t="str">
+        <v/>
+      </c>
+      <c r="O104" t="str">
+        <v/>
+      </c>
+      <c r="P104" t="str">
+        <v/>
+      </c>
+      <c r="Q104" t="str">
+        <v/>
+      </c>
+      <c r="R104" t="str">
+        <v/>
+      </c>
+      <c r="S104" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>红虎斑</v>
+      </c>
+      <c r="B105" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C105" t="str">
+        <v>assets/1785854129383-c8qkvl537x.jpeg</v>
+      </c>
+      <c r="D105" t="str">
+        <v>是</v>
+      </c>
+      <c r="E105" t="str">
+        <v/>
+      </c>
+      <c r="F105" t="str">
+        <v>广东广州</v>
+      </c>
+      <c r="G105" t="str">
+        <v/>
+      </c>
+      <c r="H105" t="str">
+        <v/>
+      </c>
+      <c r="I105" t="str">
+        <v/>
+      </c>
+      <c r="J105" t="str">
+        <v/>
+      </c>
+      <c r="K105" t="str">
+        <v/>
+      </c>
+      <c r="L105" t="str">
+        <v/>
+      </c>
+      <c r="M105" t="str">
+        <v/>
+      </c>
+      <c r="N105" t="str">
+        <v/>
+      </c>
+      <c r="O105" t="str">
+        <v/>
+      </c>
+      <c r="P105" t="str">
+        <v/>
+      </c>
+      <c r="Q105" t="str">
+        <v/>
+      </c>
+      <c r="R105" t="str">
+        <v/>
+      </c>
+      <c r="S105" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>银虎斑</v>
+      </c>
+      <c r="B106" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C106" t="str">
+        <v>assets/1785854166720-48r17hry9cd.jpeg</v>
+      </c>
+      <c r="D106" t="str">
+        <v>是</v>
+      </c>
+      <c r="E106" t="str">
+        <v/>
+      </c>
+      <c r="F106" t="str">
+        <v>山西朔州</v>
+      </c>
+      <c r="G106" t="str">
+        <v/>
+      </c>
+      <c r="H106" t="str">
+        <v/>
+      </c>
+      <c r="I106" t="str">
+        <v/>
+      </c>
+      <c r="J106" t="str">
+        <v/>
+      </c>
+      <c r="K106" t="str">
+        <v/>
+      </c>
+      <c r="L106" t="str">
+        <v/>
+      </c>
+      <c r="M106" t="str">
+        <v/>
+      </c>
+      <c r="N106" t="str">
+        <v/>
+      </c>
+      <c r="O106" t="str">
+        <v/>
+      </c>
+      <c r="P106" t="str">
+        <v/>
+      </c>
+      <c r="Q106" t="str">
+        <v/>
+      </c>
+      <c r="R106" t="str">
+        <v/>
+      </c>
+      <c r="S106" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>银虎斑</v>
+      </c>
+      <c r="B107" t="str">
+        <v>妹妹</v>
+      </c>
+      <c r="C107" t="str">
+        <v>assets/1785854224521-2cpg6xipfn6.jpeg</v>
+      </c>
+      <c r="D107" t="str">
+        <v>是</v>
+      </c>
+      <c r="E107" t="str">
+        <v/>
+      </c>
+      <c r="F107" t="str">
+        <v>浙江宁波</v>
+      </c>
+      <c r="G107" t="str">
+        <v/>
+      </c>
+      <c r="H107" t="str">
+        <v/>
+      </c>
+      <c r="I107" t="str">
+        <v/>
+      </c>
+      <c r="J107" t="str">
+        <v/>
+      </c>
+      <c r="K107" t="str">
+        <v/>
+      </c>
+      <c r="L107" t="str">
+        <v/>
+      </c>
+      <c r="M107" t="str">
+        <v/>
+      </c>
+      <c r="N107" t="str">
+        <v/>
+      </c>
+      <c r="O107" t="str">
+        <v/>
+      </c>
+      <c r="P107" t="str">
+        <v/>
+      </c>
+      <c r="Q107" t="str">
+        <v/>
+      </c>
+      <c r="R107" t="str">
+        <v/>
+      </c>
+      <c r="S107" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>银虎斑</v>
+      </c>
+      <c r="B108" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C108" t="str">
+        <v>assets/1785854260793-steez4s972l.jpeg</v>
+      </c>
+      <c r="D108" t="str">
+        <v>是</v>
+      </c>
+      <c r="E108" t="str">
+        <v/>
+      </c>
+      <c r="F108" t="str">
+        <v>陕西西安</v>
+      </c>
+      <c r="G108" t="str">
+        <v/>
+      </c>
+      <c r="H108" t="str">
+        <v/>
+      </c>
+      <c r="I108" t="str">
+        <v/>
+      </c>
+      <c r="J108" t="str">
+        <v/>
+      </c>
+      <c r="K108" t="str">
+        <v/>
+      </c>
+      <c r="L108" t="str">
+        <v/>
+      </c>
+      <c r="M108" t="str">
+        <v/>
+      </c>
+      <c r="N108" t="str">
+        <v/>
+      </c>
+      <c r="O108" t="str">
+        <v/>
+      </c>
+      <c r="P108" t="str">
+        <v/>
+      </c>
+      <c r="Q108" t="str">
+        <v/>
+      </c>
+      <c r="R108" t="str">
+        <v/>
+      </c>
+      <c r="S108" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>银虎斑</v>
+      </c>
+      <c r="B109" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C109" t="str">
+        <v>assets/1785854319988-cohio08aod5.jpeg</v>
+      </c>
+      <c r="D109" t="str">
+        <v>是</v>
+      </c>
+      <c r="E109" t="str">
+        <v/>
+      </c>
+      <c r="F109" t="str">
+        <v>黑龙江漠河</v>
+      </c>
+      <c r="G109" t="str">
+        <v/>
+      </c>
+      <c r="H109" t="str">
+        <v/>
+      </c>
+      <c r="I109" t="str">
+        <v/>
+      </c>
+      <c r="J109" t="str">
+        <v/>
+      </c>
+      <c r="K109" t="str">
+        <v/>
+      </c>
+      <c r="L109" t="str">
+        <v/>
+      </c>
+      <c r="M109" t="str">
+        <v/>
+      </c>
+      <c r="N109" t="str">
+        <v/>
+      </c>
+      <c r="O109" t="str">
+        <v/>
+      </c>
+      <c r="P109" t="str">
+        <v/>
+      </c>
+      <c r="Q109" t="str">
+        <v/>
+      </c>
+      <c r="R109" t="str">
+        <v/>
+      </c>
+      <c r="S109" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>棕虎斑</v>
+      </c>
+      <c r="B110" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C110" t="str">
+        <v>assets/1785854520974-96b8b1ekqd9.jpeg</v>
+      </c>
+      <c r="D110" t="str">
+        <v>是</v>
+      </c>
+      <c r="E110" t="str">
+        <v/>
+      </c>
+      <c r="F110" t="str">
+        <v>日本</v>
+      </c>
+      <c r="G110" t="str">
+        <v/>
+      </c>
+      <c r="H110" t="str">
+        <v/>
+      </c>
+      <c r="I110" t="str">
+        <v/>
+      </c>
+      <c r="J110" t="str">
+        <v/>
+      </c>
+      <c r="K110" t="str">
+        <v/>
+      </c>
+      <c r="L110" t="str">
+        <v/>
+      </c>
+      <c r="M110" t="str">
+        <v/>
+      </c>
+      <c r="N110" t="str">
+        <v/>
+      </c>
+      <c r="O110" t="str">
+        <v/>
+      </c>
+      <c r="P110" t="str">
+        <v/>
+      </c>
+      <c r="Q110" t="str">
+        <v/>
+      </c>
+      <c r="R110" t="str">
+        <v/>
+      </c>
+      <c r="S110" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>银虎斑</v>
+      </c>
+      <c r="B111" t="str">
+        <v>妹妹</v>
+      </c>
+      <c r="C111" t="str">
+        <v>assets/1785854664100-haqoiu1h7hj.jpeg</v>
+      </c>
+      <c r="D111" t="str">
+        <v>是</v>
+      </c>
+      <c r="E111" t="str">
+        <v/>
+      </c>
+      <c r="F111" t="str">
+        <v>浙江杭州</v>
+      </c>
+      <c r="G111" t="str">
+        <v/>
+      </c>
+      <c r="H111" t="str">
+        <v/>
+      </c>
+      <c r="I111" t="str">
+        <v/>
+      </c>
+      <c r="J111" t="str">
+        <v/>
+      </c>
+      <c r="K111" t="str">
+        <v/>
+      </c>
+      <c r="L111" t="str">
+        <v/>
+      </c>
+      <c r="M111" t="str">
+        <v/>
+      </c>
+      <c r="N111" t="str">
+        <v/>
+      </c>
+      <c r="O111" t="str">
+        <v/>
+      </c>
+      <c r="P111" t="str">
+        <v/>
+      </c>
+      <c r="Q111" t="str">
+        <v/>
+      </c>
+      <c r="R111" t="str">
+        <v/>
+      </c>
+      <c r="S111" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>银虎斑</v>
+      </c>
+      <c r="B112" t="str">
+        <v>妹妹</v>
+      </c>
+      <c r="C112" t="str">
+        <v>assets/1785854690732-orrs40sx9rs.jpeg</v>
+      </c>
+      <c r="D112" t="str">
+        <v>是</v>
+      </c>
+      <c r="E112" t="str">
+        <v/>
+      </c>
+      <c r="F112" t="str">
+        <v>贵州安顺</v>
+      </c>
+      <c r="G112" t="str">
+        <v/>
+      </c>
+      <c r="H112" t="str">
+        <v/>
+      </c>
+      <c r="I112" t="str">
+        <v/>
+      </c>
+      <c r="J112" t="str">
+        <v/>
+      </c>
+      <c r="K112" t="str">
+        <v/>
+      </c>
+      <c r="L112" t="str">
+        <v/>
+      </c>
+      <c r="M112" t="str">
+        <v/>
+      </c>
+      <c r="N112" t="str">
+        <v/>
+      </c>
+      <c r="O112" t="str">
+        <v/>
+      </c>
+      <c r="P112" t="str">
+        <v/>
+      </c>
+      <c r="Q112" t="str">
+        <v/>
+      </c>
+      <c r="R112" t="str">
+        <v/>
+      </c>
+      <c r="S112" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>银虎斑</v>
+      </c>
+      <c r="B113" t="str">
+        <v>妹妹</v>
+      </c>
+      <c r="C113" t="str">
+        <v>assets/1785854734122-wcpmib4m7.jpeg</v>
+      </c>
+      <c r="D113" t="str">
+        <v>是</v>
+      </c>
+      <c r="E113" t="str">
+        <v/>
+      </c>
+      <c r="F113" t="str">
+        <v>山东青岛</v>
+      </c>
+      <c r="G113" t="str">
+        <v/>
+      </c>
+      <c r="H113" t="str">
+        <v/>
+      </c>
+      <c r="I113" t="str">
+        <v/>
+      </c>
+      <c r="J113" t="str">
+        <v/>
+      </c>
+      <c r="K113" t="str">
+        <v/>
+      </c>
+      <c r="L113" t="str">
+        <v/>
+      </c>
+      <c r="M113" t="str">
+        <v/>
+      </c>
+      <c r="N113" t="str">
+        <v/>
+      </c>
+      <c r="O113" t="str">
+        <v/>
+      </c>
+      <c r="P113" t="str">
+        <v/>
+      </c>
+      <c r="Q113" t="str">
+        <v/>
+      </c>
+      <c r="R113" t="str">
+        <v/>
+      </c>
+      <c r="S113" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>银虎斑</v>
+      </c>
+      <c r="B114" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C114" t="str">
+        <v>assets/1785854758707-1kxdkfvs6jc.jpeg</v>
+      </c>
+      <c r="D114" t="str">
+        <v>是</v>
+      </c>
+      <c r="E114" t="str">
+        <v/>
+      </c>
+      <c r="F114" t="str">
+        <v>黑龙江漠河</v>
+      </c>
+      <c r="G114" t="str">
+        <v/>
+      </c>
+      <c r="H114" t="str">
+        <v/>
+      </c>
+      <c r="I114" t="str">
+        <v/>
+      </c>
+      <c r="J114" t="str">
+        <v/>
+      </c>
+      <c r="K114" t="str">
+        <v/>
+      </c>
+      <c r="L114" t="str">
+        <v/>
+      </c>
+      <c r="M114" t="str">
+        <v/>
+      </c>
+      <c r="N114" t="str">
+        <v/>
+      </c>
+      <c r="O114" t="str">
+        <v/>
+      </c>
+      <c r="P114" t="str">
+        <v/>
+      </c>
+      <c r="Q114" t="str">
+        <v/>
+      </c>
+      <c r="R114" t="str">
+        <v/>
+      </c>
+      <c r="S114" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>纯蓝色</v>
+      </c>
+      <c r="B115" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C115" t="str">
+        <v>assets/1785854784780-3g0u60pdo93.jpeg</v>
+      </c>
+      <c r="D115" t="str">
+        <v>是</v>
+      </c>
+      <c r="E115" t="str">
+        <v/>
+      </c>
+      <c r="F115" t="str">
+        <v>河南鹤壁</v>
+      </c>
+      <c r="G115" t="str">
+        <v/>
+      </c>
+      <c r="H115" t="str">
+        <v/>
+      </c>
+      <c r="I115" t="str">
+        <v/>
+      </c>
+      <c r="J115" t="str">
+        <v/>
+      </c>
+      <c r="K115" t="str">
+        <v/>
+      </c>
+      <c r="L115" t="str">
+        <v/>
+      </c>
+      <c r="M115" t="str">
+        <v/>
+      </c>
+      <c r="N115" t="str">
+        <v/>
+      </c>
+      <c r="O115" t="str">
+        <v/>
+      </c>
+      <c r="P115" t="str">
+        <v/>
+      </c>
+      <c r="Q115" t="str">
+        <v/>
+      </c>
+      <c r="R115" t="str">
+        <v/>
+      </c>
+      <c r="S115" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>银虎斑</v>
+      </c>
+      <c r="B116" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C116" t="str">
+        <v>assets/1785854813179-8oyxr0h2bbu.jpeg</v>
+      </c>
+      <c r="D116" t="str">
+        <v>是</v>
+      </c>
+      <c r="E116" t="str">
+        <v/>
+      </c>
+      <c r="F116" t="str">
+        <v>陕西西安</v>
+      </c>
+      <c r="G116" t="str">
+        <v/>
+      </c>
+      <c r="H116" t="str">
+        <v/>
+      </c>
+      <c r="I116" t="str">
+        <v/>
+      </c>
+      <c r="J116" t="str">
+        <v/>
+      </c>
+      <c r="K116" t="str">
+        <v/>
+      </c>
+      <c r="L116" t="str">
+        <v/>
+      </c>
+      <c r="M116" t="str">
+        <v/>
+      </c>
+      <c r="N116" t="str">
+        <v/>
+      </c>
+      <c r="O116" t="str">
+        <v/>
+      </c>
+      <c r="P116" t="str">
+        <v/>
+      </c>
+      <c r="Q116" t="str">
+        <v/>
+      </c>
+      <c r="R116" t="str">
+        <v/>
+      </c>
+      <c r="S116" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>棕虎斑</v>
+      </c>
+      <c r="B117" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C117" t="str">
+        <v>assets/1785854838933-uq6amircyzd.jpeg</v>
+      </c>
+      <c r="D117" t="str">
+        <v>是</v>
+      </c>
+      <c r="E117" t="str">
+        <v/>
+      </c>
+      <c r="F117" t="str">
+        <v>四川成都</v>
+      </c>
+      <c r="G117" t="str">
+        <v/>
+      </c>
+      <c r="H117" t="str">
+        <v/>
+      </c>
+      <c r="I117" t="str">
+        <v/>
+      </c>
+      <c r="J117" t="str">
+        <v/>
+      </c>
+      <c r="K117" t="str">
+        <v/>
+      </c>
+      <c r="L117" t="str">
+        <v/>
+      </c>
+      <c r="M117" t="str">
+        <v/>
+      </c>
+      <c r="N117" t="str">
+        <v/>
+      </c>
+      <c r="O117" t="str">
+        <v/>
+      </c>
+      <c r="P117" t="str">
+        <v/>
+      </c>
+      <c r="Q117" t="str">
+        <v/>
+      </c>
+      <c r="R117" t="str">
+        <v/>
+      </c>
+      <c r="S117" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>烟灰色</v>
+      </c>
+      <c r="B118" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C118" t="str">
+        <v>assets/1785854869973-za3p6wikqpo.jpeg</v>
+      </c>
+      <c r="D118" t="str">
+        <v>否</v>
+      </c>
+      <c r="E118" t="str">
+        <v>2026-05-18</v>
+      </c>
+      <c r="F118" t="str">
+        <v/>
+      </c>
+      <c r="G118" t="str">
+        <v/>
+      </c>
+      <c r="H118" t="str">
+        <v/>
+      </c>
+      <c r="I118" t="str">
+        <v/>
+      </c>
+      <c r="J118" t="str">
+        <v/>
+      </c>
+      <c r="K118" t="str">
+        <v/>
+      </c>
+      <c r="L118" t="str">
+        <v/>
+      </c>
+      <c r="M118" t="str">
+        <v/>
+      </c>
+      <c r="N118" t="str">
+        <v/>
+      </c>
+      <c r="O118" t="str">
+        <v/>
+      </c>
+      <c r="P118" t="str">
+        <v/>
+      </c>
+      <c r="Q118" t="str">
+        <v/>
+      </c>
+      <c r="R118" t="str">
+        <v/>
+      </c>
+      <c r="S118" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>银虎斑</v>
+      </c>
+      <c r="B119" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C119" t="str">
+        <v>assets/1785854997023-mawkallt2a.jpeg</v>
+      </c>
+      <c r="D119" t="str">
+        <v>是</v>
+      </c>
+      <c r="E119" t="str">
+        <v/>
+      </c>
+      <c r="F119" t="str">
+        <v>新加坡</v>
+      </c>
+      <c r="G119" t="str">
+        <v/>
+      </c>
+      <c r="H119" t="str">
+        <v/>
+      </c>
+      <c r="I119" t="str">
+        <v/>
+      </c>
+      <c r="J119" t="str">
+        <v/>
+      </c>
+      <c r="K119" t="str">
+        <v/>
+      </c>
+      <c r="L119" t="str">
+        <v/>
+      </c>
+      <c r="M119" t="str">
+        <v/>
+      </c>
+      <c r="N119" t="str">
+        <v/>
+      </c>
+      <c r="O119" t="str">
+        <v/>
+      </c>
+      <c r="P119" t="str">
+        <v/>
+      </c>
+      <c r="Q119" t="str">
+        <v/>
+      </c>
+      <c r="R119" t="str">
+        <v/>
+      </c>
+      <c r="S119" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>凯米尔色</v>
+      </c>
+      <c r="B120" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C120" t="str">
+        <v>assets/1785855043327-wdc5pxwm34k.jpeg</v>
+      </c>
+      <c r="D120" t="str">
+        <v>是</v>
+      </c>
+      <c r="E120" t="str">
+        <v/>
+      </c>
+      <c r="F120" t="str">
+        <v>上海浦东</v>
+      </c>
+      <c r="G120" t="str">
+        <v/>
+      </c>
+      <c r="H120" t="str">
+        <v/>
+      </c>
+      <c r="I120" t="str">
+        <v/>
+      </c>
+      <c r="J120" t="str">
+        <v/>
+      </c>
+      <c r="K120" t="str">
+        <v/>
+      </c>
+      <c r="L120" t="str">
+        <v/>
+      </c>
+      <c r="M120" t="str">
+        <v/>
+      </c>
+      <c r="N120" t="str">
+        <v/>
+      </c>
+      <c r="O120" t="str">
+        <v/>
+      </c>
+      <c r="P120" t="str">
+        <v/>
+      </c>
+      <c r="Q120" t="str">
+        <v/>
+      </c>
+      <c r="R120" t="str">
+        <v/>
+      </c>
+      <c r="S120" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>棕虎斑</v>
+      </c>
+      <c r="B121" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C121" t="str">
+        <v>assets/1785912551260-jplefm937nk.jpeg, assets/videos/02.mp4</v>
+      </c>
+      <c r="D121" t="str">
+        <v>是</v>
+      </c>
+      <c r="E121" t="str">
+        <v>2026-06-06</v>
+      </c>
+      <c r="F121" t="str">
+        <v>浙江温州</v>
+      </c>
+      <c r="G121" t="str">
+        <v/>
+      </c>
+      <c r="H121" t="str">
+        <v/>
+      </c>
+      <c r="I121" t="str">
+        <v/>
+      </c>
+      <c r="J121" t="str">
+        <v/>
+      </c>
+      <c r="K121" t="str">
+        <v/>
+      </c>
+      <c r="L121" t="str">
+        <v/>
+      </c>
+      <c r="M121" t="str">
+        <v/>
+      </c>
+      <c r="N121" t="str">
+        <v/>
+      </c>
+      <c r="O121" t="str">
+        <v/>
+      </c>
+      <c r="P121" t="str">
+        <v/>
+      </c>
+      <c r="Q121" t="str">
+        <v/>
+      </c>
+      <c r="R121" t="str">
+        <v/>
+      </c>
+      <c r="S121" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>棕虎斑</v>
+      </c>
+      <c r="B122" t="str">
+        <v>妹妹</v>
+      </c>
+      <c r="C122" t="str">
         <v>assets/1785912694000-m20f5kvvrr.jpeg</v>
       </c>
-      <c r="D94" t="str">
-        <v>否</v>
-      </c>
-      <c r="E94" t="str">
+      <c r="D122" t="str">
+        <v>否</v>
+      </c>
+      <c r="E122" t="str">
         <v>2026-06-06</v>
       </c>
-      <c r="F94" t="str">
-        <v/>
-      </c>
-      <c r="G94" t="str">
-        <v/>
-      </c>
-      <c r="H94" t="str">
-        <v/>
-      </c>
-      <c r="I94" t="str">
-        <v/>
-      </c>
-      <c r="J94" t="str">
-        <v/>
-      </c>
-      <c r="K94" t="str">
-        <v/>
-      </c>
-      <c r="L94" t="str">
-        <v/>
-      </c>
-      <c r="M94" t="str">
-        <v/>
-      </c>
-      <c r="N94" t="str">
-        <v/>
-      </c>
-      <c r="O94" t="str">
-        <v/>
-      </c>
-      <c r="P94" t="str">
-        <v/>
-      </c>
-      <c r="Q94" t="str">
-        <v/>
-      </c>
-      <c r="R94" t="str">
-        <v/>
-      </c>
-      <c r="S94" t="str">
+      <c r="F122" t="str">
+        <v/>
+      </c>
+      <c r="G122" t="str">
+        <v/>
+      </c>
+      <c r="H122" t="str">
+        <v/>
+      </c>
+      <c r="I122" t="str">
+        <v/>
+      </c>
+      <c r="J122" t="str">
+        <v/>
+      </c>
+      <c r="K122" t="str">
+        <v/>
+      </c>
+      <c r="L122" t="str">
+        <v/>
+      </c>
+      <c r="M122" t="str">
+        <v/>
+      </c>
+      <c r="N122" t="str">
+        <v/>
+      </c>
+      <c r="O122" t="str">
+        <v/>
+      </c>
+      <c r="P122" t="str">
+        <v/>
+      </c>
+      <c r="Q122" t="str">
+        <v/>
+      </c>
+      <c r="R122" t="str">
+        <v/>
+      </c>
+      <c r="S122" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S94"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S122"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S122"/>
+  <dimension ref="A1:S150"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -466,13 +466,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>凯米尔色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B2" t="str">
         <v>弟弟</v>
       </c>
       <c r="C2" t="str">
-        <v>assets/1787325862706-wq18k3ej56.jpg</v>
+        <v>assets/1787327967245-m62ohievcl.jpg</v>
       </c>
       <c r="D2" t="str">
         <v>是</v>
@@ -481,7 +481,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>江苏苏州</v>
+        <v>福建福州</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -525,13 +525,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>凯米尔色</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B3" t="str">
         <v>弟弟</v>
       </c>
       <c r="C3" t="str">
-        <v>assets/1787325743258-a7oac7hzlo.jpg</v>
+        <v>assets/1787327853521-js8ljh3ulj.jpg</v>
       </c>
       <c r="D3" t="str">
         <v>是</v>
@@ -540,7 +540,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>江苏苏州</v>
+        <v>上海</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -584,13 +584,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>银虎斑</v>
+        <v>纯蓝色</v>
       </c>
       <c r="B4" t="str">
         <v>弟弟</v>
       </c>
       <c r="C4" t="str">
-        <v>assets/1787325706797-kgk81ghccy.jpg</v>
+        <v>assets/1787327793837-znk2knoo6p.jpg</v>
       </c>
       <c r="D4" t="str">
         <v>是</v>
@@ -599,7 +599,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>北京</v>
+        <v>河南鹤壁</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -643,13 +643,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>蓝虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B5" t="str">
         <v>弟弟</v>
       </c>
       <c r="C5" t="str">
-        <v>assets/1787325603704-lahzgrm7fa.jpg,assets/1787325690106-wgu3spujit.jpg</v>
+        <v>assets/1787327752832-kkpmp21os3.jpg</v>
       </c>
       <c r="D5" t="str">
         <v>是</v>
@@ -658,7 +658,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>上海</v>
+        <v>陕西西安</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -702,13 +702,13 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B6" t="str">
         <v>妹妹</v>
       </c>
       <c r="C6" t="str">
-        <v>assets/1787325554341-608thexrne.jpg</v>
+        <v>assets/1787327605711-4o2f6v6ybp.jpg</v>
       </c>
       <c r="D6" t="str">
         <v>是</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>江苏苏州</v>
+        <v>陕西西安</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -761,13 +761,13 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>浅色银虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B7" t="str">
         <v>弟弟</v>
       </c>
       <c r="C7" t="str">
-        <v>assets/1787325480828-q90pskoiw3.jpg</v>
+        <v>assets/1787327573762-h23cux94p2.jpg</v>
       </c>
       <c r="D7" t="str">
         <v>是</v>
@@ -776,7 +776,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>四川成都</v>
+        <v>北京</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -820,13 +820,13 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>浅色银虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B8" t="str">
         <v>妹妹</v>
       </c>
       <c r="C8" t="str">
-        <v>assets/1787325448999-a2pg8176fu.jpg</v>
+        <v>assets/1787327496557-9daggljg4g.jpg</v>
       </c>
       <c r="D8" t="str">
         <v>是</v>
@@ -835,7 +835,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>中国台湾</v>
+        <v>黑龙江哈尔滨</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -879,13 +879,13 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>棕虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B9" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C9" t="str">
-        <v>assets/1787325357634-k55zlfhmqj.jpg</v>
+        <v>assets/1787327456560-p4yhq4qvrv.jpg</v>
       </c>
       <c r="D9" t="str">
         <v>是</v>
@@ -894,7 +894,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>浙江杭州</v>
+        <v>甘肃嘉峪关</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -938,13 +938,13 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>烟灰色</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B10" t="str">
         <v>妹妹</v>
       </c>
       <c r="C10" t="str">
-        <v>assets/1787325237876-t19isaq5gu.jpg</v>
+        <v>assets/1787327421713-zg7np4yzkc.jpg</v>
       </c>
       <c r="D10" t="str">
         <v>是</v>
@@ -953,7 +953,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>辽宁沈阳</v>
+        <v>安徽合肥</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -997,13 +997,13 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>金棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B11" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C11" t="str">
-        <v>assets/1787325199931-e7wms9qtya.jpg</v>
+        <v>assets/1787327337811-u5u2pdew3.jpg</v>
       </c>
       <c r="D11" t="str">
         <v>是</v>
@@ -1012,7 +1012,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>四川成都</v>
+        <v>安徽合肥</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -1056,13 +1056,13 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B12" t="str">
         <v>弟弟</v>
       </c>
       <c r="C12" t="str">
-        <v>assets/1787325172354-4sa8uzaey2.jpg</v>
+        <v>assets/1787327309143-6c1dan1sev.jpg</v>
       </c>
       <c r="D12" t="str">
         <v>是</v>
@@ -1071,7 +1071,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>中国香港</v>
+        <v>四川成都</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -1115,13 +1115,13 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>烟灰色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B13" t="str">
         <v>弟弟</v>
       </c>
       <c r="C13" t="str">
-        <v>assets/1787325109283-y7mvkk6qg4.jpg</v>
+        <v>assets/1787327277453-w89ujg69fm.jpg</v>
       </c>
       <c r="D13" t="str">
         <v>是</v>
@@ -1130,7 +1130,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>中国澳门</v>
+        <v>四川成都</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -1174,13 +1174,13 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>蓝虎斑</v>
+        <v>蓝银虎斑</v>
       </c>
       <c r="B14" t="str">
         <v>弟弟</v>
       </c>
       <c r="C14" t="str">
-        <v>assets/1787325033629-y3ygps3zaj.jpg</v>
+        <v>assets/1787327232159-lkrcl588a5.jpg</v>
       </c>
       <c r="D14" t="str">
         <v>是</v>
@@ -1189,7 +1189,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>山东青岛</v>
+        <v>四川成都</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -1233,13 +1233,13 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>烟灰色</v>
+        <v>玳瑁色</v>
       </c>
       <c r="B15" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C15" t="str">
-        <v>assets/1787324954998-w5m5jox439.jpg</v>
+        <v>assets/1787327182347-3az0z7sys2.jpg</v>
       </c>
       <c r="D15" t="str">
         <v>是</v>
@@ -1248,7 +1248,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>海南海口</v>
+        <v>四川内江</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -1292,13 +1292,13 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>棕虎斑</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B16" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C16" t="str">
-        <v>assets/1787324905909-zrz8o79kdf.jpg</v>
+        <v>assets/1787327143756-4xtgfy5ozu.jpg</v>
       </c>
       <c r="D16" t="str">
         <v>是</v>
@@ -1307,7 +1307,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>内蒙古</v>
+        <v>贵州贵阳</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1351,13 +1351,13 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>烟灰色</v>
+        <v>黑烟色</v>
       </c>
       <c r="B17" t="str">
         <v>弟弟</v>
       </c>
       <c r="C17" t="str">
-        <v>assets/1787324880505-gbh0sn7b6j.jpg</v>
+        <v>assets/1787327101790-tqjlseog5y.jpg</v>
       </c>
       <c r="D17" t="str">
         <v>是</v>
@@ -1366,7 +1366,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>中国香港</v>
+        <v>浙江杭州</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1416,7 +1416,7 @@
         <v>弟弟</v>
       </c>
       <c r="C18" t="str">
-        <v>assets/1787324806613-31yyz14tsf.jpg</v>
+        <v>assets/1787327019632-l1780lu2hj.jpg</v>
       </c>
       <c r="D18" t="str">
         <v>是</v>
@@ -1425,7 +1425,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>四川成都</v>
+        <v>山东威海</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1469,13 +1469,13 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>红虎斑</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B19" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C19" t="str">
-        <v>assets/1787324789658-uz6ephkdsh.jpg</v>
+        <v>assets/1787326905275-plz3fpgo97.jpg</v>
       </c>
       <c r="D19" t="str">
         <v>是</v>
@@ -1484,7 +1484,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>湖北武汉</v>
+        <v>浙江杭州</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1528,13 +1528,13 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>烟灰色</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B20" t="str">
         <v>弟弟</v>
       </c>
       <c r="C20" t="str">
-        <v>assets/1787324522658-smn44crast.jpg</v>
+        <v>assets/1787326874462-z9rzs7wg17.jpg</v>
       </c>
       <c r="D20" t="str">
         <v>是</v>
@@ -1543,7 +1543,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>湖北武汉</v>
+        <v>四川成都</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1587,13 +1587,13 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>棕虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B21" t="str">
         <v>弟弟</v>
       </c>
       <c r="C21" t="str">
-        <v>assets/1787324365608-6xtrjp7euz.jpg</v>
+        <v>assets/1787326843271-0uhv7b9p89.jpg</v>
       </c>
       <c r="D21" t="str">
         <v>是</v>
@@ -1602,7 +1602,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>新疆</v>
+        <v>四川成都</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1646,13 +1646,13 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>浅凯米尔</v>
+        <v>凯米尔</v>
       </c>
       <c r="B22" t="str">
         <v>弟弟</v>
       </c>
       <c r="C22" t="str">
-        <v>assets/1787324331029-d74lcuycf6.jpg</v>
+        <v>assets/1787326814713-p5oavnlulg.jpg</v>
       </c>
       <c r="D22" t="str">
         <v>是</v>
@@ -1705,13 +1705,13 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>红虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B23" t="str">
         <v>弟弟</v>
       </c>
       <c r="C23" t="str">
-        <v>assets/1787324297469-ans1lse2l5.jpg</v>
+        <v>assets/1787326773577-13q5out2d0.jpg</v>
       </c>
       <c r="D23" t="str">
         <v>是</v>
@@ -1720,7 +1720,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>四川乐山</v>
+        <v>四川宜宾</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1764,13 +1764,13 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>红虎斑</v>
+        <v>金棕虎斑</v>
       </c>
       <c r="B24" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C24" t="str">
-        <v>assets/1787324256827-7w383z4bg1.jpg</v>
+        <v>assets/1787326548993-89s929m2hg.jpg</v>
       </c>
       <c r="D24" t="str">
         <v>是</v>
@@ -1779,7 +1779,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>中国台湾</v>
+        <v>上海</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1823,13 +1823,13 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>银虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B25" t="str">
         <v>弟弟</v>
       </c>
       <c r="C25" t="str">
-        <v>assets/1787324228262-y3vwn6i4zk.jpg</v>
+        <v>assets/1787326449218-09s9ucram4.jpg</v>
       </c>
       <c r="D25" t="str">
         <v>是</v>
@@ -1838,7 +1838,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>四川成都</v>
+        <v>德国</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1882,13 +1882,13 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>凯米尔色</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B26" t="str">
         <v>妹妹</v>
       </c>
       <c r="C26" t="str">
-        <v>assets/1787324201418-9tk4ik75mo.jpg</v>
+        <v>assets/1787326277374-8ti107m5ki.jpg</v>
       </c>
       <c r="D26" t="str">
         <v>是</v>
@@ -1897,7 +1897,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>江苏南京</v>
+        <v>广东深圳</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1941,13 +1941,13 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>棕虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B27" t="str">
         <v>弟弟</v>
       </c>
       <c r="C27" t="str">
-        <v>assets/1787324092513-jpa2rmkci2.jpg</v>
+        <v>assets/1787326236952-2pmwche4t3.jpg</v>
       </c>
       <c r="D27" t="str">
         <v>是</v>
@@ -1956,7 +1956,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>江苏南京</v>
+        <v>福建泉州</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -2006,7 +2006,7 @@
         <v>弟弟</v>
       </c>
       <c r="C28" t="str">
-        <v>assets/1787323318612-soge38hpsf.jpg</v>
+        <v>assets/1787326184557-90v6clkwen.jpg</v>
       </c>
       <c r="D28" t="str">
         <v>是</v>
@@ -2015,7 +2015,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>上海</v>
+        <v>福建福州</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -2062,10 +2062,10 @@
         <v>棕虎斑</v>
       </c>
       <c r="B29" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C29" t="str">
-        <v>assets/1787323235892-7yq8ioq01e.jpg</v>
+        <v>assets/1787326046155-4tk23nq4dj.jpg</v>
       </c>
       <c r="D29" t="str">
         <v>是</v>
@@ -2074,7 +2074,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>四川成都</v>
+        <v>广西贵港</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -2118,13 +2118,13 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>银虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B30" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C30" t="str">
-        <v>assets/1787322988096-6e2f54q7vo.jpg</v>
+        <v>assets/1787325862706-wq18k3ej56.jpg</v>
       </c>
       <c r="D30" t="str">
         <v>是</v>
@@ -2133,7 +2133,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>浙江宁波</v>
+        <v>江苏苏州</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -2177,13 +2177,13 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>银虎斑补丁</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B31" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C31" t="str">
-        <v>assets/1787322938518-85ev8bs2k5.jpg</v>
+        <v>assets/1787325743258-a7oac7hzlo.jpg</v>
       </c>
       <c r="D31" t="str">
         <v>是</v>
@@ -2192,7 +2192,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>马来西亚</v>
+        <v>江苏苏州</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -2242,7 +2242,7 @@
         <v>弟弟</v>
       </c>
       <c r="C32" t="str">
-        <v>assets/1787322881183-tzu9xtw2sg.jpg</v>
+        <v>assets/1787325706797-kgk81ghccy.jpg</v>
       </c>
       <c r="D32" t="str">
         <v>是</v>
@@ -2251,7 +2251,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>陕西西安</v>
+        <v>北京</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -2295,13 +2295,13 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>纯黑色</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B33" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C33" t="str">
-        <v>assets/1787322840098-nhy4jjyx7k.jpg</v>
+        <v>assets/1787325603704-lahzgrm7fa.jpg,assets/1787325690106-wgu3spujit.jpg</v>
       </c>
       <c r="D33" t="str">
         <v>是</v>
@@ -2310,7 +2310,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>广西南宁</v>
+        <v>上海</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -2357,10 +2357,10 @@
         <v>棕虎斑</v>
       </c>
       <c r="B34" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C34" t="str">
-        <v>assets/1787322760950-gn3qgego4s.jpg</v>
+        <v>assets/1787325554341-608thexrne.jpg</v>
       </c>
       <c r="D34" t="str">
         <v>是</v>
@@ -2369,7 +2369,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>广西南宁</v>
+        <v>江苏苏州</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -2413,13 +2413,13 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>红虎斑</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B35" t="str">
         <v>弟弟</v>
       </c>
       <c r="C35" t="str">
-        <v>assets/1787322605982-04n50xegt2.jpg</v>
+        <v>assets/1787325480828-q90pskoiw3.jpg</v>
       </c>
       <c r="D35" t="str">
         <v>是</v>
@@ -2428,7 +2428,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>上海</v>
+        <v>四川成都</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -2472,13 +2472,13 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>蓝虎斑</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B36" t="str">
         <v>妹妹</v>
       </c>
       <c r="C36" t="str">
-        <v>assets/1787322490045-kog3ru43dy.jpg</v>
+        <v>assets/1787325448999-a2pg8176fu.jpg</v>
       </c>
       <c r="D36" t="str">
         <v>是</v>
@@ -2487,7 +2487,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>上海</v>
+        <v>中国台湾</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -2531,13 +2531,13 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>红虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B37" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C37" t="str">
-        <v>assets/1787322419996-0m33yx89nm.jpg</v>
+        <v>assets/1787325357634-k55zlfhmqj.jpg</v>
       </c>
       <c r="D37" t="str">
         <v>是</v>
@@ -2546,7 +2546,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>广东广州</v>
+        <v>浙江杭州</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -2590,13 +2590,13 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>浅色银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B38" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C38" t="str">
-        <v>assets/1787322377730-vj5csj2mll.jpg</v>
+        <v>assets/1787325237876-t19isaq5gu.jpg</v>
       </c>
       <c r="D38" t="str">
         <v>是</v>
@@ -2605,7 +2605,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>柬埔寨</v>
+        <v>辽宁沈阳</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -2649,13 +2649,13 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>蓝虎斑</v>
+        <v>金棕虎斑</v>
       </c>
       <c r="B39" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C39" t="str">
-        <v>assets/1787322269611-53yaj5ideu.jpg</v>
+        <v>assets/1787325199931-e7wms9qtya.jpg</v>
       </c>
       <c r="D39" t="str">
         <v>是</v>
@@ -2664,7 +2664,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>山东枣庄</v>
+        <v>四川成都</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -2708,13 +2708,13 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B40" t="str">
         <v>弟弟</v>
       </c>
       <c r="C40" t="str">
-        <v>assets/1787321989528-7d6liuhuk9.jpg</v>
+        <v>assets/1787325172354-4sa8uzaey2.jpg</v>
       </c>
       <c r="D40" t="str">
         <v>是</v>
@@ -2723,7 +2723,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>陕西西安</v>
+        <v>中国香港</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -2767,13 +2767,13 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B41" t="str">
         <v>弟弟</v>
       </c>
       <c r="C41" t="str">
-        <v>assets/1787321941642-xlrc1no2ua.jpg</v>
+        <v>assets/1787325109283-y7mvkk6qg4.jpg</v>
       </c>
       <c r="D41" t="str">
         <v>是</v>
@@ -2782,7 +2782,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>山东东营</v>
+        <v>中国澳门</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -2826,13 +2826,13 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>凯米尔色</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B42" t="str">
         <v>弟弟</v>
       </c>
       <c r="C42" t="str">
-        <v>assets/1787321903535-6orj7qcgzn.jpg</v>
+        <v>assets/1787325033629-y3ygps3zaj.jpg</v>
       </c>
       <c r="D42" t="str">
         <v>是</v>
@@ -2841,7 +2841,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>中国台湾</v>
+        <v>山东青岛</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -2888,10 +2888,10 @@
         <v>烟灰色</v>
       </c>
       <c r="B43" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C43" t="str">
-        <v>assets/1787321858985-v4qej7cq7g.jpg</v>
+        <v>assets/1787324954998-w5m5jox439.jpg</v>
       </c>
       <c r="D43" t="str">
         <v>是</v>
@@ -2900,7 +2900,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>中国台湾</v>
+        <v>海南海口</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2944,13 +2944,13 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B44" t="str">
         <v>弟弟</v>
       </c>
       <c r="C44" t="str">
-        <v>assets/1787321834306-efgnyhujon.jpg</v>
+        <v>assets/1787324905909-zrz8o79kdf.jpg</v>
       </c>
       <c r="D44" t="str">
         <v>是</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>北京</v>
+        <v>内蒙古</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -3003,13 +3003,13 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B45" t="str">
         <v>弟弟</v>
       </c>
       <c r="C45" t="str">
-        <v>assets/1787321439916-uttgpbkogb.jpg</v>
+        <v>assets/1787324880505-gbh0sn7b6j.jpg</v>
       </c>
       <c r="D45" t="str">
         <v>是</v>
@@ -3018,7 +3018,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>安徽合肥</v>
+        <v>中国香港</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -3062,13 +3062,13 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B46" t="str">
         <v>弟弟</v>
       </c>
       <c r="C46" t="str">
-        <v>assets/1787321419210-51hhgurygq.jpg</v>
+        <v>assets/1787324806613-31yyz14tsf.jpg</v>
       </c>
       <c r="D46" t="str">
         <v>是</v>
@@ -3077,7 +3077,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>上海</v>
+        <v>四川成都</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -3121,13 +3121,13 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>凯米尔色</v>
+        <v>红虎斑</v>
       </c>
       <c r="B47" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C47" t="str">
-        <v>assets/1787321363369-bzjn51j5il.jpg</v>
+        <v>assets/1787324789658-uz6ephkdsh.jpg</v>
       </c>
       <c r="D47" t="str">
         <v>是</v>
@@ -3136,7 +3136,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>中国台湾</v>
+        <v>湖北武汉</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -3180,13 +3180,13 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>棕虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B48" t="str">
         <v>弟弟</v>
       </c>
       <c r="C48" t="str">
-        <v>assets/1787321332559-87p6spuch3.jpg</v>
+        <v>assets/1787324522658-smn44crast.jpg</v>
       </c>
       <c r="D48" t="str">
         <v>是</v>
@@ -3195,7 +3195,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>中国台湾</v>
+        <v>湖北武汉</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -3242,10 +3242,10 @@
         <v>棕虎斑</v>
       </c>
       <c r="B49" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C49" t="str">
-        <v>assets/1787321232531-59lnzv8y98.jpg</v>
+        <v>assets/1787324365608-6xtrjp7euz.jpg</v>
       </c>
       <c r="D49" t="str">
         <v>是</v>
@@ -3254,7 +3254,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>北京</v>
+        <v>新疆</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -3298,13 +3298,13 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>银虎斑</v>
+        <v>浅凯米尔</v>
       </c>
       <c r="B50" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C50" t="str">
-        <v>assets/1787319975814-g1pfa56vfp.jpg</v>
+        <v>assets/1787324331029-d74lcuycf6.jpg</v>
       </c>
       <c r="D50" t="str">
         <v>是</v>
@@ -3313,7 +3313,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>浙江宁波</v>
+        <v>四川成都</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -3357,13 +3357,13 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B51" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C51" t="str">
-        <v>assets/1787319800704-v3qeu062ak.jpg</v>
+        <v>assets/1787324297469-ans1lse2l5.jpg</v>
       </c>
       <c r="D51" t="str">
         <v>是</v>
@@ -3372,7 +3372,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>河北唐山</v>
+        <v>四川乐山</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -3416,13 +3416,13 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B52" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C52" t="str">
-        <v>assets/1787319745369-zn66xr3bvb.jpg</v>
+        <v>assets/1787324256827-7w383z4bg1.jpg</v>
       </c>
       <c r="D52" t="str">
         <v>是</v>
@@ -3431,7 +3431,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>河北石家庄</v>
+        <v>中国台湾</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -3475,13 +3475,13 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>棕虎补丁</v>
+        <v>银虎斑</v>
       </c>
       <c r="B53" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C53" t="str">
-        <v>assets/1787319547969-zqlq35fxxt.jpg</v>
+        <v>assets/1787324228262-y3vwn6i4zk.jpg</v>
       </c>
       <c r="D53" t="str">
         <v>是</v>
@@ -3490,7 +3490,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>韩国</v>
+        <v>四川成都</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -3534,13 +3534,13 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>蓝银虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B54" t="str">
         <v>妹妹</v>
       </c>
       <c r="C54" t="str">
-        <v>assets/1787319501376-xscwljnu1j.jpg</v>
+        <v>assets/1787324201418-9tk4ik75mo.jpg</v>
       </c>
       <c r="D54" t="str">
         <v>是</v>
@@ -3549,7 +3549,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>美国</v>
+        <v>江苏南京</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -3596,10 +3596,10 @@
         <v>棕虎斑</v>
       </c>
       <c r="B55" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C55" t="str">
-        <v>assets/1787319443529-4a0zqikufx.jpg</v>
+        <v>assets/1787324092513-jpa2rmkci2.jpg</v>
       </c>
       <c r="D55" t="str">
         <v>是</v>
@@ -3608,7 +3608,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>中国台湾</v>
+        <v>江苏南京</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -3652,13 +3652,13 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>蓝虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B56" t="str">
         <v>弟弟</v>
       </c>
       <c r="C56" t="str">
-        <v>assets/1787319356194-lr2d5680i9.jpg</v>
+        <v>assets/1787323318612-soge38hpsf.jpg</v>
       </c>
       <c r="D56" t="str">
         <v>是</v>
@@ -3667,7 +3667,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>中国台湾</v>
+        <v>上海</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -3714,10 +3714,10 @@
         <v>棕虎斑</v>
       </c>
       <c r="B57" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C57" t="str">
-        <v>assets/1787319208828-aizqo4blcv.jpg</v>
+        <v>assets/1787323235892-7yq8ioq01e.jpg</v>
       </c>
       <c r="D57" t="str">
         <v>是</v>
@@ -3726,7 +3726,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>山东淄博</v>
+        <v>四川成都</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -3776,7 +3776,7 @@
         <v>妹妹</v>
       </c>
       <c r="C58" t="str">
-        <v>assets/1787319162970-cc2v8ovnni.jpg</v>
+        <v>assets/1787322988096-6e2f54q7vo.jpg</v>
       </c>
       <c r="D58" t="str">
         <v>是</v>
@@ -3785,7 +3785,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>韩国</v>
+        <v>浙江宁波</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -3829,13 +3829,13 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>棕虎补丁</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B59" t="str">
         <v>妹妹</v>
       </c>
       <c r="C59" t="str">
-        <v>assets/1787319098214-8pwa9yx2wc.jpg</v>
+        <v>assets/1787322938518-85ev8bs2k5.jpg</v>
       </c>
       <c r="D59" t="str">
         <v>是</v>
@@ -3844,7 +3844,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>四川成都</v>
+        <v>马来西亚</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -3894,7 +3894,7 @@
         <v>弟弟</v>
       </c>
       <c r="C60" t="str">
-        <v>assets/1787318867999-3gxdddp72x.jpg</v>
+        <v>assets/1787322881183-tzu9xtw2sg.jpg</v>
       </c>
       <c r="D60" t="str">
         <v>是</v>
@@ -3903,7 +3903,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>广东广州</v>
+        <v>陕西西安</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -3947,13 +3947,13 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>银虎斑</v>
+        <v>纯黑色</v>
       </c>
       <c r="B61" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C61" t="str">
-        <v>assets/1787318609722-0ojb3aikwi.jpg</v>
+        <v>assets/1787322840098-nhy4jjyx7k.jpg</v>
       </c>
       <c r="D61" t="str">
         <v>是</v>
@@ -3962,7 +3962,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>黑龙江鹤岗</v>
+        <v>广西南宁</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -4006,13 +4006,13 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B62" t="str">
         <v>弟弟</v>
       </c>
       <c r="C62" t="str">
-        <v>assets/1787318530612-779fbkfcoi.jpg</v>
+        <v>assets/1787322760950-gn3qgego4s.jpg</v>
       </c>
       <c r="D62" t="str">
         <v>是</v>
@@ -4021,7 +4021,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>天津</v>
+        <v>广西南宁</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -4065,13 +4065,13 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B63" t="str">
         <v>弟弟</v>
       </c>
       <c r="C63" t="str">
-        <v>assets/1787318365475-sj87wtsai3.jpg</v>
+        <v>assets/1787322605982-04n50xegt2.jpg</v>
       </c>
       <c r="D63" t="str">
         <v>是</v>
@@ -4080,7 +4080,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>山西朔州</v>
+        <v>上海</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -4110,7 +4110,7 @@
         <v/>
       </c>
       <c r="P63" t="str">
-        <v>已接猫</v>
+        <v/>
       </c>
       <c r="Q63" t="str">
         <v/>
@@ -4124,13 +4124,13 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B64" t="str">
         <v>妹妹</v>
       </c>
       <c r="C64" t="str">
-        <v>assets/1787318326155-ia4noopjhq.jpg</v>
+        <v>assets/1787322490045-kog3ru43dy.jpg</v>
       </c>
       <c r="D64" t="str">
         <v>是</v>
@@ -4139,7 +4139,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>贵州</v>
+        <v>上海</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -4183,22 +4183,22 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>棕虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B65" t="str">
         <v>弟弟</v>
       </c>
       <c r="C65" t="str">
-        <v>assets/1787304479674-w0trechn4p.jpg</v>
+        <v>assets/1787322419996-0m33yx89nm.jpg</v>
       </c>
       <c r="D65" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E65" t="str">
-        <v>2026-06-06</v>
+        <v/>
       </c>
       <c r="F65" t="str">
-        <v/>
+        <v>广东广州</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -4237,27 +4237,27 @@
         <v/>
       </c>
       <c r="S65" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>纯黑色</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B66" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C66" t="str">
-        <v>assets/1787283819124-4v7d1w01la.jpg</v>
+        <v>assets/1787322377730-vj5csj2mll.jpg</v>
       </c>
       <c r="D66" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E66" t="str">
-        <v>2026-02-20</v>
+        <v/>
       </c>
       <c r="F66" t="str">
-        <v/>
+        <v>柬埔寨</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -4296,27 +4296,27 @@
         <v/>
       </c>
       <c r="S66" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>阴影色NS12</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B67" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C67" t="str">
-        <v>assets/1787283212708-jdnyi6ecci.jpg</v>
+        <v>assets/1787322269611-53yaj5ideu.jpg</v>
       </c>
       <c r="D67" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E67" t="str">
-        <v>2026-05-28</v>
+        <v/>
       </c>
       <c r="F67" t="str">
-        <v/>
+        <v>山东枣庄</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -4355,27 +4355,27 @@
         <v/>
       </c>
       <c r="S67" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>阴影色NS11</v>
+        <v>银虎斑</v>
       </c>
       <c r="B68" t="str">
         <v>弟弟</v>
       </c>
       <c r="C68" t="str">
-        <v>assets/1787283153501-s2tjg9spwu.jpg</v>
+        <v>assets/1787321989528-7d6liuhuk9.jpg</v>
       </c>
       <c r="D68" t="str">
         <v>是</v>
       </c>
       <c r="E68" t="str">
-        <v>2026-06-15</v>
+        <v/>
       </c>
       <c r="F68" t="str">
-        <v>重庆</v>
+        <v>陕西西安</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -4414,27 +4414,27 @@
         <v/>
       </c>
       <c r="S68" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>浅烟灰色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B69" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C69" t="str">
-        <v>assets/1787283092677-i4d8tyrjtf.jpg</v>
+        <v>assets/1787321941642-xlrc1no2ua.jpg</v>
       </c>
       <c r="D69" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E69" t="str">
-        <v>2026-03-21</v>
+        <v/>
       </c>
       <c r="F69" t="str">
-        <v/>
+        <v>山东东营</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -4473,27 +4473,27 @@
         <v/>
       </c>
       <c r="S69" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>棕虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B70" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C70" t="str">
-        <v>assets/1787283031104-bpyq9wy2tl.jpg</v>
+        <v>assets/1787321903535-6orj7qcgzn.jpg</v>
       </c>
       <c r="D70" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E70" t="str">
-        <v>2026-06-06</v>
+        <v/>
       </c>
       <c r="F70" t="str">
-        <v/>
+        <v>中国台湾</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -4532,27 +4532,27 @@
         <v/>
       </c>
       <c r="S70" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>棕虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B71" t="str">
         <v>妹妹</v>
       </c>
       <c r="C71" t="str">
-        <v>assets/1787282991501-2fjfws0rqw.jpg</v>
+        <v>assets/1787321858985-v4qej7cq7g.jpg</v>
       </c>
       <c r="D71" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E71" t="str">
-        <v>2026-06-06</v>
+        <v/>
       </c>
       <c r="F71" t="str">
-        <v/>
+        <v>中国台湾</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -4591,27 +4591,27 @@
         <v/>
       </c>
       <c r="S71" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B72" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C72" t="str">
-        <v>assets/1787282942262-syr48fym6c.jpg</v>
+        <v>assets/1787321834306-efgnyhujon.jpg</v>
       </c>
       <c r="D72" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E72" t="str">
-        <v>2026-06-15</v>
+        <v/>
       </c>
       <c r="F72" t="str">
-        <v/>
+        <v>北京</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -4650,27 +4650,27 @@
         <v/>
       </c>
       <c r="S72" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B73" t="str">
         <v>弟弟</v>
       </c>
       <c r="C73" t="str">
-        <v>assets/1787282819855-7vhx3m0v40.jpg</v>
+        <v>assets/1787321439916-uttgpbkogb.jpg</v>
       </c>
       <c r="D73" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E73" t="str">
-        <v>2026-06-06</v>
+        <v/>
       </c>
       <c r="F73" t="str">
-        <v/>
+        <v>安徽合肥</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -4709,27 +4709,27 @@
         <v/>
       </c>
       <c r="S73" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B74" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C74" t="str">
-        <v>assets/1787282703381-2uakw592b4.jpg</v>
+        <v>assets/1787321419210-51hhgurygq.jpg</v>
       </c>
       <c r="D74" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E74" t="str">
-        <v>2026-06-06</v>
+        <v/>
       </c>
       <c r="F74" t="str">
-        <v/>
+        <v>上海</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -4768,27 +4768,27 @@
         <v/>
       </c>
       <c r="S74" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>烟灰色</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B75" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C75" t="str">
-        <v>assets/1787282649397-9hc31ncrpc.jpg</v>
+        <v>assets/1787321363369-bzjn51j5il.jpg</v>
       </c>
       <c r="D75" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E75" t="str">
-        <v>2026-06-06</v>
+        <v/>
       </c>
       <c r="F75" t="str">
-        <v/>
+        <v>中国台湾</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -4827,27 +4827,27 @@
         <v/>
       </c>
       <c r="S75" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B76" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C76" t="str">
-        <v>assets/1787282617957-svcoyyznpg.jpg</v>
+        <v>assets/1787321332559-87p6spuch3.jpg</v>
       </c>
       <c r="D76" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E76" t="str">
-        <v>2026-06-06</v>
+        <v/>
       </c>
       <c r="F76" t="str">
-        <v/>
+        <v>中国台湾</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -4886,27 +4886,27 @@
         <v/>
       </c>
       <c r="S76" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B77" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C77" t="str">
-        <v>assets/1787282419632-78nixqjzua.jpg</v>
+        <v>assets/1787321232531-59lnzv8y98.jpg</v>
       </c>
       <c r="D77" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E77" t="str">
-        <v>2026-06-06</v>
+        <v/>
       </c>
       <c r="F77" t="str">
-        <v/>
+        <v>北京</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -4945,27 +4945,27 @@
         <v/>
       </c>
       <c r="S77" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>纯黑色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B78" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C78" t="str">
-        <v>assets/1787282349942-2cfuyn7xlc.jpg</v>
+        <v>assets/1787319975814-g1pfa56vfp.jpg</v>
       </c>
       <c r="D78" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E78" t="str">
-        <v>2026-03-21</v>
+        <v/>
       </c>
       <c r="F78" t="str">
-        <v/>
+        <v>浙江宁波</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -5004,7 +5004,7 @@
         <v/>
       </c>
       <c r="S78" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="79">
@@ -5012,19 +5012,19 @@
         <v>银虎斑</v>
       </c>
       <c r="B79" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C79" t="str">
-        <v>assets/1787282064159-6b4z8c5msd.jpg</v>
+        <v>assets/1787319800704-v3qeu062ak.jpg</v>
       </c>
       <c r="D79" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E79" t="str">
-        <v>2026-06-10</v>
+        <v/>
       </c>
       <c r="F79" t="str">
-        <v/>
+        <v>河北唐山</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -5063,27 +5063,27 @@
         <v/>
       </c>
       <c r="S79" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>阴影色NS11</v>
+        <v>银虎斑</v>
       </c>
       <c r="B80" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C80" t="str">
-        <v>assets/1787280590041-vzcwebdok1.jpg</v>
+        <v>assets/1787319745369-zn66xr3bvb.jpg</v>
       </c>
       <c r="D80" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E80" t="str">
-        <v>2026-05-28</v>
+        <v/>
       </c>
       <c r="F80" t="str">
-        <v/>
+        <v>河北石家庄</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -5122,27 +5122,27 @@
         <v/>
       </c>
       <c r="S80" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>浅色银虎斑</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B81" t="str">
         <v>妹妹</v>
       </c>
       <c r="C81" t="str">
-        <v>assets/1787281786169-9ia0h837ct.jpg</v>
+        <v>assets/1787319547969-zqlq35fxxt.jpg</v>
       </c>
       <c r="D81" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E81" t="str">
-        <v>2026-06-15</v>
+        <v/>
       </c>
       <c r="F81" t="str">
-        <v/>
+        <v>韩国</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -5181,27 +5181,27 @@
         <v/>
       </c>
       <c r="S81" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>浅烟灰色</v>
+        <v>蓝银虎斑</v>
       </c>
       <c r="B82" t="str">
         <v>妹妹</v>
       </c>
       <c r="C82" t="str">
-        <v>assets/1785843720843-63qz159daui.jpg</v>
+        <v>assets/1787319501376-xscwljnu1j.jpg</v>
       </c>
       <c r="D82" t="str">
         <v>是</v>
       </c>
       <c r="E82" t="str">
-        <v>2026-03-21</v>
+        <v/>
       </c>
       <c r="F82" t="str">
-        <v>四川成都</v>
+        <v>美国</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -5240,27 +5240,27 @@
         <v/>
       </c>
       <c r="S82" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>凯米尔色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B83" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C83" t="str">
-        <v>assets/1787301984056-iu6afro5z5.jpg, assets/1785843763310-elg05ur61ri.jpg</v>
+        <v>assets/1787319443529-4a0zqikufx.jpg</v>
       </c>
       <c r="D83" t="str">
         <v>是</v>
       </c>
       <c r="E83" t="str">
-        <v>2026-02-14</v>
+        <v/>
       </c>
       <c r="F83" t="str">
-        <v>上海浦东</v>
+        <v>中国台湾</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -5299,27 +5299,27 @@
         <v/>
       </c>
       <c r="S83" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>银虎斑补丁</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B84" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C84" t="str">
-        <v>assets/1785843820715-9kz7gy4mbr7.jpg</v>
+        <v>assets/1787319356194-lr2d5680i9.jpg</v>
       </c>
       <c r="D84" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E84" t="str">
-        <v>2026-03-05</v>
+        <v/>
       </c>
       <c r="F84" t="str">
-        <v/>
+        <v>中国台湾</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -5358,27 +5358,27 @@
         <v/>
       </c>
       <c r="S84" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B85" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C85" t="str">
-        <v>assets/1785843953805-mxl3x1982io.jpg</v>
+        <v>assets/1787319208828-aizqo4blcv.jpg</v>
       </c>
       <c r="D85" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E85" t="str">
-        <v>2026-05-18</v>
+        <v/>
       </c>
       <c r="F85" t="str">
-        <v/>
+        <v>山东淄博</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -5417,27 +5417,27 @@
         <v/>
       </c>
       <c r="S85" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>棕虎斑玳瑁</v>
+        <v>银虎斑</v>
       </c>
       <c r="B86" t="str">
         <v>妹妹</v>
       </c>
       <c r="C86" t="str">
-        <v>assets/1785844013835-ek4xpcje7kh.jpg</v>
+        <v>assets/1787319162970-cc2v8ovnni.jpg</v>
       </c>
       <c r="D86" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E86" t="str">
-        <v>2026-02-14</v>
+        <v/>
       </c>
       <c r="F86" t="str">
-        <v/>
+        <v>韩国</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -5476,27 +5476,27 @@
         <v/>
       </c>
       <c r="S86" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>银虎斑补丁</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B87" t="str">
         <v>妹妹</v>
       </c>
       <c r="C87" t="str">
-        <v>assets/1785844434338-ek5zbdgdcne.jpg</v>
+        <v>assets/1787319098214-8pwa9yx2wc.jpg</v>
       </c>
       <c r="D87" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E87" t="str">
-        <v>2026-05-24</v>
+        <v/>
       </c>
       <c r="F87" t="str">
-        <v/>
+        <v>四川成都</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -5535,7 +5535,7 @@
         <v/>
       </c>
       <c r="S87" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="88">
@@ -5543,19 +5543,19 @@
         <v>银虎斑</v>
       </c>
       <c r="B88" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C88" t="str">
-        <v>assets/1785838787730-s5f333sc3u.jpg</v>
+        <v>assets/1787318867999-3gxdddp72x.jpg</v>
       </c>
       <c r="D88" t="str">
         <v>是</v>
       </c>
       <c r="E88" t="str">
-        <v>2026-06-05</v>
+        <v/>
       </c>
       <c r="F88" t="str">
-        <v>湖北恩施</v>
+        <v>广东广州</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -5594,7 +5594,7 @@
         <v/>
       </c>
       <c r="S88" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="89">
@@ -5605,16 +5605,16 @@
         <v>弟弟</v>
       </c>
       <c r="C89" t="str">
-        <v>assets/1785842296661-6qw3zs3as8h.jpg</v>
+        <v>assets/1787318609722-0ojb3aikwi.jpg</v>
       </c>
       <c r="D89" t="str">
         <v>是</v>
       </c>
       <c r="E89" t="str">
-        <v>2026-06-05</v>
+        <v/>
       </c>
       <c r="F89" t="str">
-        <v>湖北恩施</v>
+        <v>黑龙江鹤岗</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -5653,27 +5653,27 @@
         <v/>
       </c>
       <c r="S89" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B90" t="str">
         <v>弟弟</v>
       </c>
       <c r="C90" t="str">
-        <v>assets/1785842429109-porc98rel5.jpg</v>
+        <v>assets/1787318530612-779fbkfcoi.jpg</v>
       </c>
       <c r="D90" t="str">
         <v>是</v>
       </c>
       <c r="E90" t="str">
-        <v>2025-11-05</v>
+        <v/>
       </c>
       <c r="F90" t="str">
-        <v>韩国</v>
+        <v>天津</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -5712,7 +5712,7 @@
         <v/>
       </c>
       <c r="S90" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="91">
@@ -5720,19 +5720,19 @@
         <v>银虎斑</v>
       </c>
       <c r="B91" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C91" t="str">
-        <v>assets/1785842594141-fcglbzjp509.jpg</v>
+        <v>assets/1787318365475-sj87wtsai3.jpg</v>
       </c>
       <c r="D91" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E91" t="str">
-        <v>2026-05-18</v>
+        <v/>
       </c>
       <c r="F91" t="str">
-        <v/>
+        <v>山西朔州</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -5762,7 +5762,7 @@
         <v/>
       </c>
       <c r="P91" t="str">
-        <v/>
+        <v>已接猫</v>
       </c>
       <c r="Q91" t="str">
         <v/>
@@ -5771,27 +5771,27 @@
         <v/>
       </c>
       <c r="S91" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B92" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C92" t="str">
-        <v>assets/1785842639100-82k775dhwiv.jpg</v>
+        <v>assets/1787318326155-ia4noopjhq.jpg</v>
       </c>
       <c r="D92" t="str">
         <v>是</v>
       </c>
       <c r="E92" t="str">
-        <v>2026-05-28</v>
+        <v/>
       </c>
       <c r="F92" t="str">
-        <v>四川自贡</v>
+        <v>贵州</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -5830,7 +5830,7 @@
         <v/>
       </c>
       <c r="S92" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="93">
@@ -5838,10 +5838,10 @@
         <v>棕虎斑</v>
       </c>
       <c r="B93" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C93" t="str">
-        <v>assets/1785842684502-mnhr0r96eee.jpg</v>
+        <v>assets/1787304479674-w0trechn4p.jpg</v>
       </c>
       <c r="D93" t="str">
         <v>否</v>
@@ -5900,13 +5900,13 @@
         <v>妹妹</v>
       </c>
       <c r="C94" t="str">
-        <v>assets/1785842779532-5u1j0igrw1s.jpg</v>
+        <v>assets/1787283819124-4v7d1w01la.jpg</v>
       </c>
       <c r="D94" t="str">
         <v>否</v>
       </c>
       <c r="E94" t="str">
-        <v>2026-03-05</v>
+        <v>2026-02-20</v>
       </c>
       <c r="F94" t="str">
         <v/>
@@ -5953,22 +5953,22 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>银虎斑</v>
+        <v>阴影色NS12</v>
       </c>
       <c r="B95" t="str">
         <v>妹妹</v>
       </c>
       <c r="C95" t="str">
-        <v>assets/1785842817046-6keqv4rw4yf.jpg</v>
+        <v>assets/1787283212708-jdnyi6ecci.jpg</v>
       </c>
       <c r="D95" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E95" t="str">
-        <v>2026-03-05</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F95" t="str">
-        <v>韩国</v>
+        <v/>
       </c>
       <c r="G95" t="str">
         <v/>
@@ -6012,22 +6012,22 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>浅色银虎斑</v>
+        <v>阴影色NS11</v>
       </c>
       <c r="B96" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C96" t="str">
-        <v>assets/1785842950972-a88lbrskpc.jpg</v>
+        <v>assets/1787283153501-s2tjg9spwu.jpg</v>
       </c>
       <c r="D96" t="str">
         <v>是</v>
       </c>
       <c r="E96" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F96" t="str">
-        <v>河北邢台</v>
+        <v>重庆</v>
       </c>
       <c r="G96" t="str">
         <v/>
@@ -6071,22 +6071,22 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>棕虎斑</v>
+        <v>浅烟灰色</v>
       </c>
       <c r="B97" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C97" t="str">
-        <v>assets/1785843011477-n3l1wi6ech.jpg</v>
+        <v>assets/1787283092677-i4d8tyrjtf.jpg</v>
       </c>
       <c r="D97" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E97" t="str">
-        <v>2026-06-05</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F97" t="str">
-        <v>四川自贡</v>
+        <v/>
       </c>
       <c r="G97" t="str">
         <v/>
@@ -6130,19 +6130,19 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B98" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C98" t="str">
-        <v>assets/1785843237517-ga449iqess5.jpg</v>
+        <v>assets/1787283031104-bpyq9wy2tl.jpg</v>
       </c>
       <c r="D98" t="str">
         <v>否</v>
       </c>
       <c r="E98" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F98" t="str">
         <v/>
@@ -6189,19 +6189,19 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>棕虎斑补丁</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B99" t="str">
         <v>妹妹</v>
       </c>
       <c r="C99" t="str">
-        <v>assets/1785842523893-7nwnnhwi4ns.jpg</v>
+        <v>assets/1787282991501-2fjfws0rqw.jpg</v>
       </c>
       <c r="D99" t="str">
         <v>否</v>
       </c>
       <c r="E99" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F99" t="str">
         <v/>
@@ -6248,19 +6248,19 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B100" t="str">
         <v>妹妹</v>
       </c>
       <c r="C100" t="str">
-        <v>assets/1785843497557-st27fk8drqi.jpg</v>
+        <v>assets/1787282942262-syr48fym6c.jpg</v>
       </c>
       <c r="D100" t="str">
         <v>否</v>
       </c>
       <c r="E100" t="str">
-        <v>2026-04-05</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F100" t="str">
         <v/>
@@ -6307,19 +6307,19 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B101" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C101" t="str">
-        <v>assets/1785843621923-ylhakbtw13i.jpg</v>
+        <v>assets/1787282819855-7vhx3m0v40.jpg</v>
       </c>
       <c r="D101" t="str">
         <v>否</v>
       </c>
       <c r="E101" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F101" t="str">
         <v/>
@@ -6366,19 +6366,19 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B102" t="str">
         <v>妹妹</v>
       </c>
       <c r="C102" t="str">
-        <v>assets/1785843663884-sfxvpmiet7.jpg</v>
+        <v>assets/1787282703381-2uakw592b4.jpg</v>
       </c>
       <c r="D102" t="str">
         <v>否</v>
       </c>
       <c r="E102" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F102" t="str">
         <v/>
@@ -6425,52 +6425,52 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>蓝虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B103" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C103" t="str">
-        <v>assets/1785852601940-o236xtv7yx.jpeg</v>
+        <v>assets/1787282649397-9hc31ncrpc.jpg</v>
       </c>
       <c r="D103" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E103" t="str">
-        <v>2026-02-20</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F103" t="str">
-        <v>荷兰</v>
+        <v/>
       </c>
       <c r="G103" t="str">
-        <v>阿泽</v>
+        <v/>
       </c>
       <c r="H103" t="str">
-        <v>小辫子</v>
+        <v/>
       </c>
       <c r="I103" t="str">
-        <v>驺驺</v>
+        <v/>
       </c>
       <c r="J103" t="str">
-        <v>2026-07-02</v>
+        <v/>
       </c>
       <c r="K103" t="str">
         <v/>
       </c>
       <c r="L103" t="str">
-        <v>2026-07-02</v>
+        <v/>
       </c>
       <c r="M103" t="str">
-        <v>2026-08-03</v>
+        <v/>
       </c>
       <c r="N103" t="str">
-        <v>2026-11-04</v>
+        <v/>
       </c>
       <c r="O103" t="str">
-        <v>2026-08-03 · 血清检测,2026-07-02 · 打疫苗 · assets/diary/zouzou-depart.jpg,2026-07-30 · 6.2斤 · 五个月10天了 · assets/feedback/zouzou-1.jpg</v>
+        <v/>
       </c>
       <c r="P103" t="str">
-        <v>已付定金</v>
+        <v/>
       </c>
       <c r="Q103" t="str">
         <v/>
@@ -6479,27 +6479,27 @@
         <v/>
       </c>
       <c r="S103" t="str">
-        <v>否</v>
+        <v/>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>红虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B104" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C104" t="str">
-        <v>assets/1785853950207-cedor66ou2q.jpeg</v>
+        <v>assets/1787282617957-svcoyyznpg.jpg</v>
       </c>
       <c r="D104" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E104" t="str">
-        <v/>
+        <v>2026-06-06</v>
       </c>
       <c r="F104" t="str">
-        <v>广东广州</v>
+        <v/>
       </c>
       <c r="G104" t="str">
         <v/>
@@ -6543,22 +6543,22 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>红虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B105" t="str">
         <v>弟弟</v>
       </c>
       <c r="C105" t="str">
-        <v>assets/1785854129383-c8qkvl537x.jpeg</v>
+        <v>assets/1787282419632-78nixqjzua.jpg</v>
       </c>
       <c r="D105" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E105" t="str">
-        <v/>
+        <v>2026-06-06</v>
       </c>
       <c r="F105" t="str">
-        <v>广东广州</v>
+        <v/>
       </c>
       <c r="G105" t="str">
         <v/>
@@ -6602,22 +6602,22 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>银虎斑</v>
+        <v>纯黑色</v>
       </c>
       <c r="B106" t="str">
         <v>弟弟</v>
       </c>
       <c r="C106" t="str">
-        <v>assets/1785854166720-48r17hry9cd.jpeg</v>
+        <v>assets/1787282349942-2cfuyn7xlc.jpg</v>
       </c>
       <c r="D106" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E106" t="str">
-        <v/>
+        <v>2026-03-21</v>
       </c>
       <c r="F106" t="str">
-        <v>山西朔州</v>
+        <v/>
       </c>
       <c r="G106" t="str">
         <v/>
@@ -6664,19 +6664,19 @@
         <v>银虎斑</v>
       </c>
       <c r="B107" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C107" t="str">
-        <v>assets/1785854224521-2cpg6xipfn6.jpeg</v>
+        <v>assets/1787282064159-6b4z8c5msd.jpg</v>
       </c>
       <c r="D107" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E107" t="str">
-        <v/>
+        <v>2026-06-10</v>
       </c>
       <c r="F107" t="str">
-        <v>浙江宁波</v>
+        <v/>
       </c>
       <c r="G107" t="str">
         <v/>
@@ -6720,22 +6720,22 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>银虎斑</v>
+        <v>阴影色NS11</v>
       </c>
       <c r="B108" t="str">
         <v>弟弟</v>
       </c>
       <c r="C108" t="str">
-        <v>assets/1785854260793-steez4s972l.jpeg</v>
+        <v>assets/1787280590041-vzcwebdok1.jpg</v>
       </c>
       <c r="D108" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E108" t="str">
-        <v/>
+        <v>2026-05-28</v>
       </c>
       <c r="F108" t="str">
-        <v>陕西西安</v>
+        <v/>
       </c>
       <c r="G108" t="str">
         <v/>
@@ -6779,22 +6779,22 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>银虎斑</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B109" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C109" t="str">
-        <v>assets/1785854319988-cohio08aod5.jpeg</v>
+        <v>assets/1787281786169-9ia0h837ct.jpg</v>
       </c>
       <c r="D109" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E109" t="str">
-        <v/>
+        <v>2026-06-15</v>
       </c>
       <c r="F109" t="str">
-        <v>黑龙江漠河</v>
+        <v/>
       </c>
       <c r="G109" t="str">
         <v/>
@@ -6838,22 +6838,22 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>棕虎斑</v>
+        <v>浅烟灰色</v>
       </c>
       <c r="B110" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C110" t="str">
-        <v>assets/1785854520974-96b8b1ekqd9.jpeg</v>
+        <v>assets/1785843720843-63qz159daui.jpg</v>
       </c>
       <c r="D110" t="str">
         <v>是</v>
       </c>
       <c r="E110" t="str">
-        <v/>
+        <v>2026-03-21</v>
       </c>
       <c r="F110" t="str">
-        <v>日本</v>
+        <v>四川成都</v>
       </c>
       <c r="G110" t="str">
         <v/>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>银虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B111" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C111" t="str">
-        <v>assets/1785854664100-haqoiu1h7hj.jpeg</v>
+        <v>assets/1787301984056-iu6afro5z5.jpg, assets/1785843763310-elg05ur61ri.jpg</v>
       </c>
       <c r="D111" t="str">
         <v>是</v>
       </c>
       <c r="E111" t="str">
-        <v/>
+        <v>2026-02-14</v>
       </c>
       <c r="F111" t="str">
-        <v>浙江杭州</v>
+        <v>上海浦东</v>
       </c>
       <c r="G111" t="str">
         <v/>
@@ -6956,22 +6956,22 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>银虎斑</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B112" t="str">
         <v>妹妹</v>
       </c>
       <c r="C112" t="str">
-        <v>assets/1785854690732-orrs40sx9rs.jpeg</v>
+        <v>assets/1785843820715-9kz7gy4mbr7.jpg</v>
       </c>
       <c r="D112" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E112" t="str">
-        <v/>
+        <v>2026-03-05</v>
       </c>
       <c r="F112" t="str">
-        <v>贵州安顺</v>
+        <v/>
       </c>
       <c r="G112" t="str">
         <v/>
@@ -7015,22 +7015,22 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B113" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C113" t="str">
-        <v>assets/1785854734122-wcpmib4m7.jpeg</v>
+        <v>assets/1785843953805-mxl3x1982io.jpg</v>
       </c>
       <c r="D113" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E113" t="str">
-        <v/>
+        <v>2026-05-18</v>
       </c>
       <c r="F113" t="str">
-        <v>山东青岛</v>
+        <v/>
       </c>
       <c r="G113" t="str">
         <v/>
@@ -7074,22 +7074,22 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑玳瑁</v>
       </c>
       <c r="B114" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C114" t="str">
-        <v>assets/1785854758707-1kxdkfvs6jc.jpeg</v>
+        <v>assets/1785844013835-ek4xpcje7kh.jpg</v>
       </c>
       <c r="D114" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E114" t="str">
-        <v/>
+        <v>2026-02-14</v>
       </c>
       <c r="F114" t="str">
-        <v>黑龙江漠河</v>
+        <v/>
       </c>
       <c r="G114" t="str">
         <v/>
@@ -7133,22 +7133,22 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>纯蓝色</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B115" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C115" t="str">
-        <v>assets/1785854784780-3g0u60pdo93.jpeg</v>
+        <v>assets/1785844434338-ek5zbdgdcne.jpg</v>
       </c>
       <c r="D115" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E115" t="str">
-        <v/>
+        <v>2026-05-24</v>
       </c>
       <c r="F115" t="str">
-        <v>河南鹤壁</v>
+        <v/>
       </c>
       <c r="G115" t="str">
         <v/>
@@ -7195,19 +7195,19 @@
         <v>银虎斑</v>
       </c>
       <c r="B116" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C116" t="str">
-        <v>assets/1785854813179-8oyxr0h2bbu.jpeg</v>
+        <v>assets/1785838787730-s5f333sc3u.jpg</v>
       </c>
       <c r="D116" t="str">
         <v>是</v>
       </c>
       <c r="E116" t="str">
-        <v/>
+        <v>2026-06-05</v>
       </c>
       <c r="F116" t="str">
-        <v>陕西西安</v>
+        <v>湖北恩施</v>
       </c>
       <c r="G116" t="str">
         <v/>
@@ -7251,22 +7251,22 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B117" t="str">
         <v>弟弟</v>
       </c>
       <c r="C117" t="str">
-        <v>assets/1785854838933-uq6amircyzd.jpeg</v>
+        <v>assets/1785842296661-6qw3zs3as8h.jpg</v>
       </c>
       <c r="D117" t="str">
         <v>是</v>
       </c>
       <c r="E117" t="str">
-        <v/>
+        <v>2026-06-05</v>
       </c>
       <c r="F117" t="str">
-        <v>四川成都</v>
+        <v>湖北恩施</v>
       </c>
       <c r="G117" t="str">
         <v/>
@@ -7310,22 +7310,22 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>烟灰色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B118" t="str">
         <v>弟弟</v>
       </c>
       <c r="C118" t="str">
-        <v>assets/1785854869973-za3p6wikqpo.jpeg</v>
+        <v>assets/1785842429109-porc98rel5.jpg</v>
       </c>
       <c r="D118" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E118" t="str">
-        <v>2026-05-18</v>
+        <v>2025-11-05</v>
       </c>
       <c r="F118" t="str">
-        <v/>
+        <v>韩国</v>
       </c>
       <c r="G118" t="str">
         <v/>
@@ -7372,19 +7372,19 @@
         <v>银虎斑</v>
       </c>
       <c r="B119" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C119" t="str">
-        <v>assets/1785854997023-mawkallt2a.jpeg</v>
+        <v>assets/1785842594141-fcglbzjp509.jpg</v>
       </c>
       <c r="D119" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E119" t="str">
-        <v/>
+        <v>2026-05-18</v>
       </c>
       <c r="F119" t="str">
-        <v>新加坡</v>
+        <v/>
       </c>
       <c r="G119" t="str">
         <v/>
@@ -7428,22 +7428,22 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>凯米尔色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B120" t="str">
         <v>弟弟</v>
       </c>
       <c r="C120" t="str">
-        <v>assets/1785855043327-wdc5pxwm34k.jpeg</v>
+        <v>assets/1785842639100-82k775dhwiv.jpg</v>
       </c>
       <c r="D120" t="str">
         <v>是</v>
       </c>
       <c r="E120" t="str">
-        <v/>
+        <v>2026-05-28</v>
       </c>
       <c r="F120" t="str">
-        <v>上海浦东</v>
+        <v>四川自贡</v>
       </c>
       <c r="G120" t="str">
         <v/>
@@ -7490,19 +7490,19 @@
         <v>棕虎斑</v>
       </c>
       <c r="B121" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C121" t="str">
-        <v>assets/1785912551260-jplefm937nk.jpeg, assets/videos/02.mp4</v>
+        <v>assets/1785842684502-mnhr0r96eee.jpg</v>
       </c>
       <c r="D121" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E121" t="str">
         <v>2026-06-06</v>
       </c>
       <c r="F121" t="str">
-        <v>浙江温州</v>
+        <v/>
       </c>
       <c r="G121" t="str">
         <v/>
@@ -7546,66 +7546,1718 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>棕虎斑</v>
+        <v>纯黑色</v>
       </c>
       <c r="B122" t="str">
         <v>妹妹</v>
       </c>
       <c r="C122" t="str">
+        <v>assets/1785842779532-5u1j0igrw1s.jpg</v>
+      </c>
+      <c r="D122" t="str">
+        <v>否</v>
+      </c>
+      <c r="E122" t="str">
+        <v>2026-03-05</v>
+      </c>
+      <c r="F122" t="str">
+        <v/>
+      </c>
+      <c r="G122" t="str">
+        <v/>
+      </c>
+      <c r="H122" t="str">
+        <v/>
+      </c>
+      <c r="I122" t="str">
+        <v/>
+      </c>
+      <c r="J122" t="str">
+        <v/>
+      </c>
+      <c r="K122" t="str">
+        <v/>
+      </c>
+      <c r="L122" t="str">
+        <v/>
+      </c>
+      <c r="M122" t="str">
+        <v/>
+      </c>
+      <c r="N122" t="str">
+        <v/>
+      </c>
+      <c r="O122" t="str">
+        <v/>
+      </c>
+      <c r="P122" t="str">
+        <v/>
+      </c>
+      <c r="Q122" t="str">
+        <v/>
+      </c>
+      <c r="R122" t="str">
+        <v/>
+      </c>
+      <c r="S122" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>银虎斑</v>
+      </c>
+      <c r="B123" t="str">
+        <v>妹妹</v>
+      </c>
+      <c r="C123" t="str">
+        <v>assets/1785842817046-6keqv4rw4yf.jpg</v>
+      </c>
+      <c r="D123" t="str">
+        <v>是</v>
+      </c>
+      <c r="E123" t="str">
+        <v>2026-03-05</v>
+      </c>
+      <c r="F123" t="str">
+        <v>韩国</v>
+      </c>
+      <c r="G123" t="str">
+        <v/>
+      </c>
+      <c r="H123" t="str">
+        <v/>
+      </c>
+      <c r="I123" t="str">
+        <v/>
+      </c>
+      <c r="J123" t="str">
+        <v/>
+      </c>
+      <c r="K123" t="str">
+        <v/>
+      </c>
+      <c r="L123" t="str">
+        <v/>
+      </c>
+      <c r="M123" t="str">
+        <v/>
+      </c>
+      <c r="N123" t="str">
+        <v/>
+      </c>
+      <c r="O123" t="str">
+        <v/>
+      </c>
+      <c r="P123" t="str">
+        <v/>
+      </c>
+      <c r="Q123" t="str">
+        <v/>
+      </c>
+      <c r="R123" t="str">
+        <v/>
+      </c>
+      <c r="S123" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>浅色银虎斑</v>
+      </c>
+      <c r="B124" t="str">
+        <v>妹妹</v>
+      </c>
+      <c r="C124" t="str">
+        <v>assets/1785842950972-a88lbrskpc.jpg</v>
+      </c>
+      <c r="D124" t="str">
+        <v>是</v>
+      </c>
+      <c r="E124" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="F124" t="str">
+        <v>河北邢台</v>
+      </c>
+      <c r="G124" t="str">
+        <v/>
+      </c>
+      <c r="H124" t="str">
+        <v/>
+      </c>
+      <c r="I124" t="str">
+        <v/>
+      </c>
+      <c r="J124" t="str">
+        <v/>
+      </c>
+      <c r="K124" t="str">
+        <v/>
+      </c>
+      <c r="L124" t="str">
+        <v/>
+      </c>
+      <c r="M124" t="str">
+        <v/>
+      </c>
+      <c r="N124" t="str">
+        <v/>
+      </c>
+      <c r="O124" t="str">
+        <v/>
+      </c>
+      <c r="P124" t="str">
+        <v/>
+      </c>
+      <c r="Q124" t="str">
+        <v/>
+      </c>
+      <c r="R124" t="str">
+        <v/>
+      </c>
+      <c r="S124" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>棕虎斑</v>
+      </c>
+      <c r="B125" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C125" t="str">
+        <v>assets/1785843011477-n3l1wi6ech.jpg</v>
+      </c>
+      <c r="D125" t="str">
+        <v>是</v>
+      </c>
+      <c r="E125" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="F125" t="str">
+        <v>四川自贡</v>
+      </c>
+      <c r="G125" t="str">
+        <v/>
+      </c>
+      <c r="H125" t="str">
+        <v/>
+      </c>
+      <c r="I125" t="str">
+        <v/>
+      </c>
+      <c r="J125" t="str">
+        <v/>
+      </c>
+      <c r="K125" t="str">
+        <v/>
+      </c>
+      <c r="L125" t="str">
+        <v/>
+      </c>
+      <c r="M125" t="str">
+        <v/>
+      </c>
+      <c r="N125" t="str">
+        <v/>
+      </c>
+      <c r="O125" t="str">
+        <v/>
+      </c>
+      <c r="P125" t="str">
+        <v/>
+      </c>
+      <c r="Q125" t="str">
+        <v/>
+      </c>
+      <c r="R125" t="str">
+        <v/>
+      </c>
+      <c r="S125" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>蓝虎斑</v>
+      </c>
+      <c r="B126" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C126" t="str">
+        <v>assets/1785843237517-ga449iqess5.jpg</v>
+      </c>
+      <c r="D126" t="str">
+        <v>否</v>
+      </c>
+      <c r="E126" t="str">
+        <v>2026-03-05</v>
+      </c>
+      <c r="F126" t="str">
+        <v/>
+      </c>
+      <c r="G126" t="str">
+        <v/>
+      </c>
+      <c r="H126" t="str">
+        <v/>
+      </c>
+      <c r="I126" t="str">
+        <v/>
+      </c>
+      <c r="J126" t="str">
+        <v/>
+      </c>
+      <c r="K126" t="str">
+        <v/>
+      </c>
+      <c r="L126" t="str">
+        <v/>
+      </c>
+      <c r="M126" t="str">
+        <v/>
+      </c>
+      <c r="N126" t="str">
+        <v/>
+      </c>
+      <c r="O126" t="str">
+        <v/>
+      </c>
+      <c r="P126" t="str">
+        <v/>
+      </c>
+      <c r="Q126" t="str">
+        <v/>
+      </c>
+      <c r="R126" t="str">
+        <v/>
+      </c>
+      <c r="S126" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>棕虎斑补丁</v>
+      </c>
+      <c r="B127" t="str">
+        <v>妹妹</v>
+      </c>
+      <c r="C127" t="str">
+        <v>assets/1785842523893-7nwnnhwi4ns.jpg</v>
+      </c>
+      <c r="D127" t="str">
+        <v>否</v>
+      </c>
+      <c r="E127" t="str">
+        <v>2026-03-05</v>
+      </c>
+      <c r="F127" t="str">
+        <v/>
+      </c>
+      <c r="G127" t="str">
+        <v/>
+      </c>
+      <c r="H127" t="str">
+        <v/>
+      </c>
+      <c r="I127" t="str">
+        <v/>
+      </c>
+      <c r="J127" t="str">
+        <v/>
+      </c>
+      <c r="K127" t="str">
+        <v/>
+      </c>
+      <c r="L127" t="str">
+        <v/>
+      </c>
+      <c r="M127" t="str">
+        <v/>
+      </c>
+      <c r="N127" t="str">
+        <v/>
+      </c>
+      <c r="O127" t="str">
+        <v/>
+      </c>
+      <c r="P127" t="str">
+        <v/>
+      </c>
+      <c r="Q127" t="str">
+        <v/>
+      </c>
+      <c r="R127" t="str">
+        <v/>
+      </c>
+      <c r="S127" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>蓝虎斑</v>
+      </c>
+      <c r="B128" t="str">
+        <v>妹妹</v>
+      </c>
+      <c r="C128" t="str">
+        <v>assets/1785843497557-st27fk8drqi.jpg</v>
+      </c>
+      <c r="D128" t="str">
+        <v>否</v>
+      </c>
+      <c r="E128" t="str">
+        <v>2026-04-05</v>
+      </c>
+      <c r="F128" t="str">
+        <v/>
+      </c>
+      <c r="G128" t="str">
+        <v/>
+      </c>
+      <c r="H128" t="str">
+        <v/>
+      </c>
+      <c r="I128" t="str">
+        <v/>
+      </c>
+      <c r="J128" t="str">
+        <v/>
+      </c>
+      <c r="K128" t="str">
+        <v/>
+      </c>
+      <c r="L128" t="str">
+        <v/>
+      </c>
+      <c r="M128" t="str">
+        <v/>
+      </c>
+      <c r="N128" t="str">
+        <v/>
+      </c>
+      <c r="O128" t="str">
+        <v/>
+      </c>
+      <c r="P128" t="str">
+        <v/>
+      </c>
+      <c r="Q128" t="str">
+        <v/>
+      </c>
+      <c r="R128" t="str">
+        <v/>
+      </c>
+      <c r="S128" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>银虎斑</v>
+      </c>
+      <c r="B129" t="str">
+        <v>妹妹</v>
+      </c>
+      <c r="C129" t="str">
+        <v>assets/1785843621923-ylhakbtw13i.jpg</v>
+      </c>
+      <c r="D129" t="str">
+        <v>否</v>
+      </c>
+      <c r="E129" t="str">
+        <v>2026-03-05</v>
+      </c>
+      <c r="F129" t="str">
+        <v/>
+      </c>
+      <c r="G129" t="str">
+        <v/>
+      </c>
+      <c r="H129" t="str">
+        <v/>
+      </c>
+      <c r="I129" t="str">
+        <v/>
+      </c>
+      <c r="J129" t="str">
+        <v/>
+      </c>
+      <c r="K129" t="str">
+        <v/>
+      </c>
+      <c r="L129" t="str">
+        <v/>
+      </c>
+      <c r="M129" t="str">
+        <v/>
+      </c>
+      <c r="N129" t="str">
+        <v/>
+      </c>
+      <c r="O129" t="str">
+        <v/>
+      </c>
+      <c r="P129" t="str">
+        <v/>
+      </c>
+      <c r="Q129" t="str">
+        <v/>
+      </c>
+      <c r="R129" t="str">
+        <v/>
+      </c>
+      <c r="S129" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>银虎斑</v>
+      </c>
+      <c r="B130" t="str">
+        <v>妹妹</v>
+      </c>
+      <c r="C130" t="str">
+        <v>assets/1785843663884-sfxvpmiet7.jpg</v>
+      </c>
+      <c r="D130" t="str">
+        <v>否</v>
+      </c>
+      <c r="E130" t="str">
+        <v>2026-03-05</v>
+      </c>
+      <c r="F130" t="str">
+        <v/>
+      </c>
+      <c r="G130" t="str">
+        <v/>
+      </c>
+      <c r="H130" t="str">
+        <v/>
+      </c>
+      <c r="I130" t="str">
+        <v/>
+      </c>
+      <c r="J130" t="str">
+        <v/>
+      </c>
+      <c r="K130" t="str">
+        <v/>
+      </c>
+      <c r="L130" t="str">
+        <v/>
+      </c>
+      <c r="M130" t="str">
+        <v/>
+      </c>
+      <c r="N130" t="str">
+        <v/>
+      </c>
+      <c r="O130" t="str">
+        <v/>
+      </c>
+      <c r="P130" t="str">
+        <v/>
+      </c>
+      <c r="Q130" t="str">
+        <v/>
+      </c>
+      <c r="R130" t="str">
+        <v/>
+      </c>
+      <c r="S130" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>蓝虎斑</v>
+      </c>
+      <c r="B131" t="str">
+        <v>妹妹</v>
+      </c>
+      <c r="C131" t="str">
+        <v>assets/1785852601940-o236xtv7yx.jpeg</v>
+      </c>
+      <c r="D131" t="str">
+        <v>是</v>
+      </c>
+      <c r="E131" t="str">
+        <v>2026-02-20</v>
+      </c>
+      <c r="F131" t="str">
+        <v>荷兰</v>
+      </c>
+      <c r="G131" t="str">
+        <v>阿泽</v>
+      </c>
+      <c r="H131" t="str">
+        <v>小辫子</v>
+      </c>
+      <c r="I131" t="str">
+        <v>驺驺</v>
+      </c>
+      <c r="J131" t="str">
+        <v>2026-07-02</v>
+      </c>
+      <c r="K131" t="str">
+        <v/>
+      </c>
+      <c r="L131" t="str">
+        <v>2026-07-02</v>
+      </c>
+      <c r="M131" t="str">
+        <v>2026-08-03</v>
+      </c>
+      <c r="N131" t="str">
+        <v>2026-11-04</v>
+      </c>
+      <c r="O131" t="str">
+        <v>2026-08-03 · 血清检测,2026-07-02 · 打疫苗 · assets/diary/zouzou-depart.jpg,2026-07-30 · 6.2斤 · 五个月10天了 · assets/feedback/zouzou-1.jpg</v>
+      </c>
+      <c r="P131" t="str">
+        <v>已付定金</v>
+      </c>
+      <c r="Q131" t="str">
+        <v/>
+      </c>
+      <c r="R131" t="str">
+        <v/>
+      </c>
+      <c r="S131" t="str">
+        <v>否</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>红虎斑</v>
+      </c>
+      <c r="B132" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C132" t="str">
+        <v>assets/1785853950207-cedor66ou2q.jpeg</v>
+      </c>
+      <c r="D132" t="str">
+        <v>是</v>
+      </c>
+      <c r="E132" t="str">
+        <v/>
+      </c>
+      <c r="F132" t="str">
+        <v>广东广州</v>
+      </c>
+      <c r="G132" t="str">
+        <v/>
+      </c>
+      <c r="H132" t="str">
+        <v/>
+      </c>
+      <c r="I132" t="str">
+        <v/>
+      </c>
+      <c r="J132" t="str">
+        <v/>
+      </c>
+      <c r="K132" t="str">
+        <v/>
+      </c>
+      <c r="L132" t="str">
+        <v/>
+      </c>
+      <c r="M132" t="str">
+        <v/>
+      </c>
+      <c r="N132" t="str">
+        <v/>
+      </c>
+      <c r="O132" t="str">
+        <v/>
+      </c>
+      <c r="P132" t="str">
+        <v/>
+      </c>
+      <c r="Q132" t="str">
+        <v/>
+      </c>
+      <c r="R132" t="str">
+        <v/>
+      </c>
+      <c r="S132" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>红虎斑</v>
+      </c>
+      <c r="B133" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C133" t="str">
+        <v>assets/1785854129383-c8qkvl537x.jpeg</v>
+      </c>
+      <c r="D133" t="str">
+        <v>是</v>
+      </c>
+      <c r="E133" t="str">
+        <v/>
+      </c>
+      <c r="F133" t="str">
+        <v>广东广州</v>
+      </c>
+      <c r="G133" t="str">
+        <v/>
+      </c>
+      <c r="H133" t="str">
+        <v/>
+      </c>
+      <c r="I133" t="str">
+        <v/>
+      </c>
+      <c r="J133" t="str">
+        <v/>
+      </c>
+      <c r="K133" t="str">
+        <v/>
+      </c>
+      <c r="L133" t="str">
+        <v/>
+      </c>
+      <c r="M133" t="str">
+        <v/>
+      </c>
+      <c r="N133" t="str">
+        <v/>
+      </c>
+      <c r="O133" t="str">
+        <v/>
+      </c>
+      <c r="P133" t="str">
+        <v/>
+      </c>
+      <c r="Q133" t="str">
+        <v/>
+      </c>
+      <c r="R133" t="str">
+        <v/>
+      </c>
+      <c r="S133" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>银虎斑</v>
+      </c>
+      <c r="B134" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C134" t="str">
+        <v>assets/1785854166720-48r17hry9cd.jpeg</v>
+      </c>
+      <c r="D134" t="str">
+        <v>是</v>
+      </c>
+      <c r="E134" t="str">
+        <v/>
+      </c>
+      <c r="F134" t="str">
+        <v>山西朔州</v>
+      </c>
+      <c r="G134" t="str">
+        <v/>
+      </c>
+      <c r="H134" t="str">
+        <v/>
+      </c>
+      <c r="I134" t="str">
+        <v/>
+      </c>
+      <c r="J134" t="str">
+        <v/>
+      </c>
+      <c r="K134" t="str">
+        <v/>
+      </c>
+      <c r="L134" t="str">
+        <v/>
+      </c>
+      <c r="M134" t="str">
+        <v/>
+      </c>
+      <c r="N134" t="str">
+        <v/>
+      </c>
+      <c r="O134" t="str">
+        <v/>
+      </c>
+      <c r="P134" t="str">
+        <v/>
+      </c>
+      <c r="Q134" t="str">
+        <v/>
+      </c>
+      <c r="R134" t="str">
+        <v/>
+      </c>
+      <c r="S134" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>银虎斑</v>
+      </c>
+      <c r="B135" t="str">
+        <v>妹妹</v>
+      </c>
+      <c r="C135" t="str">
+        <v>assets/1785854224521-2cpg6xipfn6.jpeg</v>
+      </c>
+      <c r="D135" t="str">
+        <v>是</v>
+      </c>
+      <c r="E135" t="str">
+        <v/>
+      </c>
+      <c r="F135" t="str">
+        <v>浙江宁波</v>
+      </c>
+      <c r="G135" t="str">
+        <v/>
+      </c>
+      <c r="H135" t="str">
+        <v/>
+      </c>
+      <c r="I135" t="str">
+        <v/>
+      </c>
+      <c r="J135" t="str">
+        <v/>
+      </c>
+      <c r="K135" t="str">
+        <v/>
+      </c>
+      <c r="L135" t="str">
+        <v/>
+      </c>
+      <c r="M135" t="str">
+        <v/>
+      </c>
+      <c r="N135" t="str">
+        <v/>
+      </c>
+      <c r="O135" t="str">
+        <v/>
+      </c>
+      <c r="P135" t="str">
+        <v/>
+      </c>
+      <c r="Q135" t="str">
+        <v/>
+      </c>
+      <c r="R135" t="str">
+        <v/>
+      </c>
+      <c r="S135" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>银虎斑</v>
+      </c>
+      <c r="B136" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C136" t="str">
+        <v>assets/1785854260793-steez4s972l.jpeg</v>
+      </c>
+      <c r="D136" t="str">
+        <v>是</v>
+      </c>
+      <c r="E136" t="str">
+        <v/>
+      </c>
+      <c r="F136" t="str">
+        <v>陕西西安</v>
+      </c>
+      <c r="G136" t="str">
+        <v/>
+      </c>
+      <c r="H136" t="str">
+        <v/>
+      </c>
+      <c r="I136" t="str">
+        <v/>
+      </c>
+      <c r="J136" t="str">
+        <v/>
+      </c>
+      <c r="K136" t="str">
+        <v/>
+      </c>
+      <c r="L136" t="str">
+        <v/>
+      </c>
+      <c r="M136" t="str">
+        <v/>
+      </c>
+      <c r="N136" t="str">
+        <v/>
+      </c>
+      <c r="O136" t="str">
+        <v/>
+      </c>
+      <c r="P136" t="str">
+        <v/>
+      </c>
+      <c r="Q136" t="str">
+        <v/>
+      </c>
+      <c r="R136" t="str">
+        <v/>
+      </c>
+      <c r="S136" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>银虎斑</v>
+      </c>
+      <c r="B137" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C137" t="str">
+        <v>assets/1785854319988-cohio08aod5.jpeg</v>
+      </c>
+      <c r="D137" t="str">
+        <v>是</v>
+      </c>
+      <c r="E137" t="str">
+        <v/>
+      </c>
+      <c r="F137" t="str">
+        <v>黑龙江漠河</v>
+      </c>
+      <c r="G137" t="str">
+        <v/>
+      </c>
+      <c r="H137" t="str">
+        <v/>
+      </c>
+      <c r="I137" t="str">
+        <v/>
+      </c>
+      <c r="J137" t="str">
+        <v/>
+      </c>
+      <c r="K137" t="str">
+        <v/>
+      </c>
+      <c r="L137" t="str">
+        <v/>
+      </c>
+      <c r="M137" t="str">
+        <v/>
+      </c>
+      <c r="N137" t="str">
+        <v/>
+      </c>
+      <c r="O137" t="str">
+        <v/>
+      </c>
+      <c r="P137" t="str">
+        <v/>
+      </c>
+      <c r="Q137" t="str">
+        <v/>
+      </c>
+      <c r="R137" t="str">
+        <v/>
+      </c>
+      <c r="S137" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>棕虎斑</v>
+      </c>
+      <c r="B138" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C138" t="str">
+        <v>assets/1785854520974-96b8b1ekqd9.jpeg</v>
+      </c>
+      <c r="D138" t="str">
+        <v>是</v>
+      </c>
+      <c r="E138" t="str">
+        <v/>
+      </c>
+      <c r="F138" t="str">
+        <v>日本</v>
+      </c>
+      <c r="G138" t="str">
+        <v/>
+      </c>
+      <c r="H138" t="str">
+        <v/>
+      </c>
+      <c r="I138" t="str">
+        <v/>
+      </c>
+      <c r="J138" t="str">
+        <v/>
+      </c>
+      <c r="K138" t="str">
+        <v/>
+      </c>
+      <c r="L138" t="str">
+        <v/>
+      </c>
+      <c r="M138" t="str">
+        <v/>
+      </c>
+      <c r="N138" t="str">
+        <v/>
+      </c>
+      <c r="O138" t="str">
+        <v/>
+      </c>
+      <c r="P138" t="str">
+        <v/>
+      </c>
+      <c r="Q138" t="str">
+        <v/>
+      </c>
+      <c r="R138" t="str">
+        <v/>
+      </c>
+      <c r="S138" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>银虎斑</v>
+      </c>
+      <c r="B139" t="str">
+        <v>妹妹</v>
+      </c>
+      <c r="C139" t="str">
+        <v>assets/1785854664100-haqoiu1h7hj.jpeg</v>
+      </c>
+      <c r="D139" t="str">
+        <v>是</v>
+      </c>
+      <c r="E139" t="str">
+        <v/>
+      </c>
+      <c r="F139" t="str">
+        <v>浙江杭州</v>
+      </c>
+      <c r="G139" t="str">
+        <v/>
+      </c>
+      <c r="H139" t="str">
+        <v/>
+      </c>
+      <c r="I139" t="str">
+        <v/>
+      </c>
+      <c r="J139" t="str">
+        <v/>
+      </c>
+      <c r="K139" t="str">
+        <v/>
+      </c>
+      <c r="L139" t="str">
+        <v/>
+      </c>
+      <c r="M139" t="str">
+        <v/>
+      </c>
+      <c r="N139" t="str">
+        <v/>
+      </c>
+      <c r="O139" t="str">
+        <v/>
+      </c>
+      <c r="P139" t="str">
+        <v/>
+      </c>
+      <c r="Q139" t="str">
+        <v/>
+      </c>
+      <c r="R139" t="str">
+        <v/>
+      </c>
+      <c r="S139" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>银虎斑</v>
+      </c>
+      <c r="B140" t="str">
+        <v>妹妹</v>
+      </c>
+      <c r="C140" t="str">
+        <v>assets/1785854690732-orrs40sx9rs.jpeg</v>
+      </c>
+      <c r="D140" t="str">
+        <v>是</v>
+      </c>
+      <c r="E140" t="str">
+        <v/>
+      </c>
+      <c r="F140" t="str">
+        <v>贵州安顺</v>
+      </c>
+      <c r="G140" t="str">
+        <v/>
+      </c>
+      <c r="H140" t="str">
+        <v/>
+      </c>
+      <c r="I140" t="str">
+        <v/>
+      </c>
+      <c r="J140" t="str">
+        <v/>
+      </c>
+      <c r="K140" t="str">
+        <v/>
+      </c>
+      <c r="L140" t="str">
+        <v/>
+      </c>
+      <c r="M140" t="str">
+        <v/>
+      </c>
+      <c r="N140" t="str">
+        <v/>
+      </c>
+      <c r="O140" t="str">
+        <v/>
+      </c>
+      <c r="P140" t="str">
+        <v/>
+      </c>
+      <c r="Q140" t="str">
+        <v/>
+      </c>
+      <c r="R140" t="str">
+        <v/>
+      </c>
+      <c r="S140" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>银虎斑</v>
+      </c>
+      <c r="B141" t="str">
+        <v>妹妹</v>
+      </c>
+      <c r="C141" t="str">
+        <v>assets/1785854734122-wcpmib4m7.jpeg</v>
+      </c>
+      <c r="D141" t="str">
+        <v>是</v>
+      </c>
+      <c r="E141" t="str">
+        <v/>
+      </c>
+      <c r="F141" t="str">
+        <v>山东青岛</v>
+      </c>
+      <c r="G141" t="str">
+        <v/>
+      </c>
+      <c r="H141" t="str">
+        <v/>
+      </c>
+      <c r="I141" t="str">
+        <v/>
+      </c>
+      <c r="J141" t="str">
+        <v/>
+      </c>
+      <c r="K141" t="str">
+        <v/>
+      </c>
+      <c r="L141" t="str">
+        <v/>
+      </c>
+      <c r="M141" t="str">
+        <v/>
+      </c>
+      <c r="N141" t="str">
+        <v/>
+      </c>
+      <c r="O141" t="str">
+        <v/>
+      </c>
+      <c r="P141" t="str">
+        <v/>
+      </c>
+      <c r="Q141" t="str">
+        <v/>
+      </c>
+      <c r="R141" t="str">
+        <v/>
+      </c>
+      <c r="S141" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>银虎斑</v>
+      </c>
+      <c r="B142" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C142" t="str">
+        <v>assets/1785854758707-1kxdkfvs6jc.jpeg</v>
+      </c>
+      <c r="D142" t="str">
+        <v>是</v>
+      </c>
+      <c r="E142" t="str">
+        <v/>
+      </c>
+      <c r="F142" t="str">
+        <v>黑龙江漠河</v>
+      </c>
+      <c r="G142" t="str">
+        <v/>
+      </c>
+      <c r="H142" t="str">
+        <v/>
+      </c>
+      <c r="I142" t="str">
+        <v/>
+      </c>
+      <c r="J142" t="str">
+        <v/>
+      </c>
+      <c r="K142" t="str">
+        <v/>
+      </c>
+      <c r="L142" t="str">
+        <v/>
+      </c>
+      <c r="M142" t="str">
+        <v/>
+      </c>
+      <c r="N142" t="str">
+        <v/>
+      </c>
+      <c r="O142" t="str">
+        <v/>
+      </c>
+      <c r="P142" t="str">
+        <v/>
+      </c>
+      <c r="Q142" t="str">
+        <v/>
+      </c>
+      <c r="R142" t="str">
+        <v/>
+      </c>
+      <c r="S142" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>纯蓝色</v>
+      </c>
+      <c r="B143" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C143" t="str">
+        <v>assets/1785854784780-3g0u60pdo93.jpeg</v>
+      </c>
+      <c r="D143" t="str">
+        <v>是</v>
+      </c>
+      <c r="E143" t="str">
+        <v/>
+      </c>
+      <c r="F143" t="str">
+        <v>河南鹤壁</v>
+      </c>
+      <c r="G143" t="str">
+        <v/>
+      </c>
+      <c r="H143" t="str">
+        <v/>
+      </c>
+      <c r="I143" t="str">
+        <v/>
+      </c>
+      <c r="J143" t="str">
+        <v/>
+      </c>
+      <c r="K143" t="str">
+        <v/>
+      </c>
+      <c r="L143" t="str">
+        <v/>
+      </c>
+      <c r="M143" t="str">
+        <v/>
+      </c>
+      <c r="N143" t="str">
+        <v/>
+      </c>
+      <c r="O143" t="str">
+        <v/>
+      </c>
+      <c r="P143" t="str">
+        <v/>
+      </c>
+      <c r="Q143" t="str">
+        <v/>
+      </c>
+      <c r="R143" t="str">
+        <v/>
+      </c>
+      <c r="S143" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>银虎斑</v>
+      </c>
+      <c r="B144" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C144" t="str">
+        <v>assets/1785854813179-8oyxr0h2bbu.jpeg</v>
+      </c>
+      <c r="D144" t="str">
+        <v>是</v>
+      </c>
+      <c r="E144" t="str">
+        <v/>
+      </c>
+      <c r="F144" t="str">
+        <v>陕西西安</v>
+      </c>
+      <c r="G144" t="str">
+        <v/>
+      </c>
+      <c r="H144" t="str">
+        <v/>
+      </c>
+      <c r="I144" t="str">
+        <v/>
+      </c>
+      <c r="J144" t="str">
+        <v/>
+      </c>
+      <c r="K144" t="str">
+        <v/>
+      </c>
+      <c r="L144" t="str">
+        <v/>
+      </c>
+      <c r="M144" t="str">
+        <v/>
+      </c>
+      <c r="N144" t="str">
+        <v/>
+      </c>
+      <c r="O144" t="str">
+        <v/>
+      </c>
+      <c r="P144" t="str">
+        <v/>
+      </c>
+      <c r="Q144" t="str">
+        <v/>
+      </c>
+      <c r="R144" t="str">
+        <v/>
+      </c>
+      <c r="S144" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>棕虎斑</v>
+      </c>
+      <c r="B145" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C145" t="str">
+        <v>assets/1785854838933-uq6amircyzd.jpeg</v>
+      </c>
+      <c r="D145" t="str">
+        <v>是</v>
+      </c>
+      <c r="E145" t="str">
+        <v/>
+      </c>
+      <c r="F145" t="str">
+        <v>四川成都</v>
+      </c>
+      <c r="G145" t="str">
+        <v/>
+      </c>
+      <c r="H145" t="str">
+        <v/>
+      </c>
+      <c r="I145" t="str">
+        <v/>
+      </c>
+      <c r="J145" t="str">
+        <v/>
+      </c>
+      <c r="K145" t="str">
+        <v/>
+      </c>
+      <c r="L145" t="str">
+        <v/>
+      </c>
+      <c r="M145" t="str">
+        <v/>
+      </c>
+      <c r="N145" t="str">
+        <v/>
+      </c>
+      <c r="O145" t="str">
+        <v/>
+      </c>
+      <c r="P145" t="str">
+        <v/>
+      </c>
+      <c r="Q145" t="str">
+        <v/>
+      </c>
+      <c r="R145" t="str">
+        <v/>
+      </c>
+      <c r="S145" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>烟灰色</v>
+      </c>
+      <c r="B146" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C146" t="str">
+        <v>assets/1785854869973-za3p6wikqpo.jpeg</v>
+      </c>
+      <c r="D146" t="str">
+        <v>否</v>
+      </c>
+      <c r="E146" t="str">
+        <v>2026-05-18</v>
+      </c>
+      <c r="F146" t="str">
+        <v/>
+      </c>
+      <c r="G146" t="str">
+        <v/>
+      </c>
+      <c r="H146" t="str">
+        <v/>
+      </c>
+      <c r="I146" t="str">
+        <v/>
+      </c>
+      <c r="J146" t="str">
+        <v/>
+      </c>
+      <c r="K146" t="str">
+        <v/>
+      </c>
+      <c r="L146" t="str">
+        <v/>
+      </c>
+      <c r="M146" t="str">
+        <v/>
+      </c>
+      <c r="N146" t="str">
+        <v/>
+      </c>
+      <c r="O146" t="str">
+        <v/>
+      </c>
+      <c r="P146" t="str">
+        <v/>
+      </c>
+      <c r="Q146" t="str">
+        <v/>
+      </c>
+      <c r="R146" t="str">
+        <v/>
+      </c>
+      <c r="S146" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>银虎斑</v>
+      </c>
+      <c r="B147" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C147" t="str">
+        <v>assets/1785854997023-mawkallt2a.jpeg</v>
+      </c>
+      <c r="D147" t="str">
+        <v>是</v>
+      </c>
+      <c r="E147" t="str">
+        <v/>
+      </c>
+      <c r="F147" t="str">
+        <v>新加坡</v>
+      </c>
+      <c r="G147" t="str">
+        <v/>
+      </c>
+      <c r="H147" t="str">
+        <v/>
+      </c>
+      <c r="I147" t="str">
+        <v/>
+      </c>
+      <c r="J147" t="str">
+        <v/>
+      </c>
+      <c r="K147" t="str">
+        <v/>
+      </c>
+      <c r="L147" t="str">
+        <v/>
+      </c>
+      <c r="M147" t="str">
+        <v/>
+      </c>
+      <c r="N147" t="str">
+        <v/>
+      </c>
+      <c r="O147" t="str">
+        <v/>
+      </c>
+      <c r="P147" t="str">
+        <v/>
+      </c>
+      <c r="Q147" t="str">
+        <v/>
+      </c>
+      <c r="R147" t="str">
+        <v/>
+      </c>
+      <c r="S147" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>凯米尔色</v>
+      </c>
+      <c r="B148" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C148" t="str">
+        <v>assets/1785855043327-wdc5pxwm34k.jpeg</v>
+      </c>
+      <c r="D148" t="str">
+        <v>是</v>
+      </c>
+      <c r="E148" t="str">
+        <v/>
+      </c>
+      <c r="F148" t="str">
+        <v>上海浦东</v>
+      </c>
+      <c r="G148" t="str">
+        <v/>
+      </c>
+      <c r="H148" t="str">
+        <v/>
+      </c>
+      <c r="I148" t="str">
+        <v/>
+      </c>
+      <c r="J148" t="str">
+        <v/>
+      </c>
+      <c r="K148" t="str">
+        <v/>
+      </c>
+      <c r="L148" t="str">
+        <v/>
+      </c>
+      <c r="M148" t="str">
+        <v/>
+      </c>
+      <c r="N148" t="str">
+        <v/>
+      </c>
+      <c r="O148" t="str">
+        <v/>
+      </c>
+      <c r="P148" t="str">
+        <v/>
+      </c>
+      <c r="Q148" t="str">
+        <v/>
+      </c>
+      <c r="R148" t="str">
+        <v/>
+      </c>
+      <c r="S148" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>棕虎斑</v>
+      </c>
+      <c r="B149" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C149" t="str">
+        <v>assets/1785912551260-jplefm937nk.jpeg, assets/videos/02.mp4</v>
+      </c>
+      <c r="D149" t="str">
+        <v>是</v>
+      </c>
+      <c r="E149" t="str">
+        <v>2026-06-06</v>
+      </c>
+      <c r="F149" t="str">
+        <v>浙江温州</v>
+      </c>
+      <c r="G149" t="str">
+        <v/>
+      </c>
+      <c r="H149" t="str">
+        <v/>
+      </c>
+      <c r="I149" t="str">
+        <v/>
+      </c>
+      <c r="J149" t="str">
+        <v/>
+      </c>
+      <c r="K149" t="str">
+        <v/>
+      </c>
+      <c r="L149" t="str">
+        <v/>
+      </c>
+      <c r="M149" t="str">
+        <v/>
+      </c>
+      <c r="N149" t="str">
+        <v/>
+      </c>
+      <c r="O149" t="str">
+        <v/>
+      </c>
+      <c r="P149" t="str">
+        <v/>
+      </c>
+      <c r="Q149" t="str">
+        <v/>
+      </c>
+      <c r="R149" t="str">
+        <v/>
+      </c>
+      <c r="S149" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>棕虎斑</v>
+      </c>
+      <c r="B150" t="str">
+        <v>妹妹</v>
+      </c>
+      <c r="C150" t="str">
         <v>assets/1785912694000-m20f5kvvrr.jpeg</v>
       </c>
-      <c r="D122" t="str">
-        <v>否</v>
-      </c>
-      <c r="E122" t="str">
+      <c r="D150" t="str">
+        <v>否</v>
+      </c>
+      <c r="E150" t="str">
         <v>2026-06-06</v>
       </c>
-      <c r="F122" t="str">
-        <v/>
-      </c>
-      <c r="G122" t="str">
-        <v/>
-      </c>
-      <c r="H122" t="str">
-        <v/>
-      </c>
-      <c r="I122" t="str">
-        <v/>
-      </c>
-      <c r="J122" t="str">
-        <v/>
-      </c>
-      <c r="K122" t="str">
-        <v/>
-      </c>
-      <c r="L122" t="str">
-        <v/>
-      </c>
-      <c r="M122" t="str">
-        <v/>
-      </c>
-      <c r="N122" t="str">
-        <v/>
-      </c>
-      <c r="O122" t="str">
-        <v/>
-      </c>
-      <c r="P122" t="str">
-        <v/>
-      </c>
-      <c r="Q122" t="str">
-        <v/>
-      </c>
-      <c r="R122" t="str">
-        <v/>
-      </c>
-      <c r="S122" t="str">
+      <c r="F150" t="str">
+        <v/>
+      </c>
+      <c r="G150" t="str">
+        <v/>
+      </c>
+      <c r="H150" t="str">
+        <v/>
+      </c>
+      <c r="I150" t="str">
+        <v/>
+      </c>
+      <c r="J150" t="str">
+        <v/>
+      </c>
+      <c r="K150" t="str">
+        <v/>
+      </c>
+      <c r="L150" t="str">
+        <v/>
+      </c>
+      <c r="M150" t="str">
+        <v/>
+      </c>
+      <c r="N150" t="str">
+        <v/>
+      </c>
+      <c r="O150" t="str">
+        <v/>
+      </c>
+      <c r="P150" t="str">
+        <v/>
+      </c>
+      <c r="Q150" t="str">
+        <v/>
+      </c>
+      <c r="R150" t="str">
+        <v/>
+      </c>
+      <c r="S150" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S122"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S150"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S150"/>
+  <dimension ref="A1:S152"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -466,13 +466,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B2" t="str">
         <v>弟弟</v>
       </c>
       <c r="C2" t="str">
-        <v>assets/1787327967245-m62ohievcl.jpg</v>
+        <v>assets/1787328436957-x30od0gw28.jpg</v>
       </c>
       <c r="D2" t="str">
         <v>是</v>
@@ -481,7 +481,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>福建福州</v>
+        <v>江苏苏州</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -531,7 +531,7 @@
         <v>弟弟</v>
       </c>
       <c r="C3" t="str">
-        <v>assets/1787327853521-js8ljh3ulj.jpg</v>
+        <v>assets/1787328420967-viv9v8nbjn.jpg</v>
       </c>
       <c r="D3" t="str">
         <v>是</v>
@@ -540,7 +540,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>上海</v>
+        <v>辽宁东港</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -584,13 +584,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>纯蓝色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B4" t="str">
         <v>弟弟</v>
       </c>
       <c r="C4" t="str">
-        <v>assets/1787327793837-znk2knoo6p.jpg</v>
+        <v>assets/1787327967245-m62ohievcl.jpg</v>
       </c>
       <c r="D4" t="str">
         <v>是</v>
@@ -599,7 +599,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>河南鹤壁</v>
+        <v>福建福州</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -643,13 +643,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B5" t="str">
         <v>弟弟</v>
       </c>
       <c r="C5" t="str">
-        <v>assets/1787327752832-kkpmp21os3.jpg</v>
+        <v>assets/1787327853521-js8ljh3ulj.jpg</v>
       </c>
       <c r="D5" t="str">
         <v>是</v>
@@ -658,7 +658,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>陕西西安</v>
+        <v>上海</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -702,13 +702,13 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>银虎斑</v>
+        <v>纯蓝色</v>
       </c>
       <c r="B6" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C6" t="str">
-        <v>assets/1787327605711-4o2f6v6ybp.jpg</v>
+        <v>assets/1787327793837-znk2knoo6p.jpg</v>
       </c>
       <c r="D6" t="str">
         <v>是</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>陕西西安</v>
+        <v>河南鹤壁</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -767,7 +767,7 @@
         <v>弟弟</v>
       </c>
       <c r="C7" t="str">
-        <v>assets/1787327573762-h23cux94p2.jpg</v>
+        <v>assets/1787327752832-kkpmp21os3.jpg</v>
       </c>
       <c r="D7" t="str">
         <v>是</v>
@@ -776,7 +776,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>北京</v>
+        <v>陕西西安</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -826,7 +826,7 @@
         <v>妹妹</v>
       </c>
       <c r="C8" t="str">
-        <v>assets/1787327496557-9daggljg4g.jpg</v>
+        <v>assets/1787327605711-4o2f6v6ybp.jpg</v>
       </c>
       <c r="D8" t="str">
         <v>是</v>
@@ -835,7 +835,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>黑龙江哈尔滨</v>
+        <v>陕西西安</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -879,13 +879,13 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>烟灰色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B9" t="str">
         <v>弟弟</v>
       </c>
       <c r="C9" t="str">
-        <v>assets/1787327456560-p4yhq4qvrv.jpg</v>
+        <v>assets/1787327573762-h23cux94p2.jpg</v>
       </c>
       <c r="D9" t="str">
         <v>是</v>
@@ -894,7 +894,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>甘肃嘉峪关</v>
+        <v>北京</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -938,13 +938,13 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>蓝虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B10" t="str">
         <v>妹妹</v>
       </c>
       <c r="C10" t="str">
-        <v>assets/1787327421713-zg7np4yzkc.jpg</v>
+        <v>assets/1787327496557-9daggljg4g.jpg</v>
       </c>
       <c r="D10" t="str">
         <v>是</v>
@@ -953,7 +953,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>安徽合肥</v>
+        <v>黑龙江哈尔滨</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -997,13 +997,13 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B11" t="str">
         <v>弟弟</v>
       </c>
       <c r="C11" t="str">
-        <v>assets/1787327337811-u5u2pdew3.jpg</v>
+        <v>assets/1787327456560-p4yhq4qvrv.jpg</v>
       </c>
       <c r="D11" t="str">
         <v>是</v>
@@ -1012,7 +1012,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>安徽合肥</v>
+        <v>甘肃嘉峪关</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -1056,13 +1056,13 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>棕虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B12" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C12" t="str">
-        <v>assets/1787327309143-6c1dan1sev.jpg</v>
+        <v>assets/1787327421713-zg7np4yzkc.jpg</v>
       </c>
       <c r="D12" t="str">
         <v>是</v>
@@ -1071,7 +1071,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>四川成都</v>
+        <v>安徽合肥</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -1121,7 +1121,7 @@
         <v>弟弟</v>
       </c>
       <c r="C13" t="str">
-        <v>assets/1787327277453-w89ujg69fm.jpg</v>
+        <v>assets/1787327337811-u5u2pdew3.jpg</v>
       </c>
       <c r="D13" t="str">
         <v>是</v>
@@ -1130,7 +1130,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>四川成都</v>
+        <v>安徽合肥</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -1174,13 +1174,13 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>蓝银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B14" t="str">
         <v>弟弟</v>
       </c>
       <c r="C14" t="str">
-        <v>assets/1787327232159-lkrcl588a5.jpg</v>
+        <v>assets/1787327309143-6c1dan1sev.jpg</v>
       </c>
       <c r="D14" t="str">
         <v>是</v>
@@ -1233,13 +1233,13 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>玳瑁色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B15" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C15" t="str">
-        <v>assets/1787327182347-3az0z7sys2.jpg</v>
+        <v>assets/1787327277453-w89ujg69fm.jpg</v>
       </c>
       <c r="D15" t="str">
         <v>是</v>
@@ -1248,7 +1248,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>四川内江</v>
+        <v>四川成都</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -1292,13 +1292,13 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>棕虎补丁</v>
+        <v>蓝银虎斑</v>
       </c>
       <c r="B16" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C16" t="str">
-        <v>assets/1787327143756-4xtgfy5ozu.jpg</v>
+        <v>assets/1787327232159-lkrcl588a5.jpg</v>
       </c>
       <c r="D16" t="str">
         <v>是</v>
@@ -1307,7 +1307,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>贵州贵阳</v>
+        <v>四川成都</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1351,13 +1351,13 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>黑烟色</v>
+        <v>玳瑁色</v>
       </c>
       <c r="B17" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C17" t="str">
-        <v>assets/1787327101790-tqjlseog5y.jpg</v>
+        <v>assets/1787327182347-3az0z7sys2.jpg</v>
       </c>
       <c r="D17" t="str">
         <v>是</v>
@@ -1366,7 +1366,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>浙江杭州</v>
+        <v>四川内江</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1410,13 +1410,13 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>烟灰色</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B18" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C18" t="str">
-        <v>assets/1787327019632-l1780lu2hj.jpg</v>
+        <v>assets/1787327143756-4xtgfy5ozu.jpg</v>
       </c>
       <c r="D18" t="str">
         <v>是</v>
@@ -1425,7 +1425,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>山东威海</v>
+        <v>贵州贵阳</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1469,13 +1469,13 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>棕虎补丁</v>
+        <v>黑烟色</v>
       </c>
       <c r="B19" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C19" t="str">
-        <v>assets/1787326905275-plz3fpgo97.jpg</v>
+        <v>assets/1787327101790-tqjlseog5y.jpg</v>
       </c>
       <c r="D19" t="str">
         <v>是</v>
@@ -1528,13 +1528,13 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>蓝虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B20" t="str">
         <v>弟弟</v>
       </c>
       <c r="C20" t="str">
-        <v>assets/1787326874462-z9rzs7wg17.jpg</v>
+        <v>assets/1787327019632-l1780lu2hj.jpg</v>
       </c>
       <c r="D20" t="str">
         <v>是</v>
@@ -1543,7 +1543,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>四川成都</v>
+        <v>山东威海</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1587,13 +1587,13 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>凯米尔色</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B21" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C21" t="str">
-        <v>assets/1787326843271-0uhv7b9p89.jpg</v>
+        <v>assets/1787326905275-plz3fpgo97.jpg</v>
       </c>
       <c r="D21" t="str">
         <v>是</v>
@@ -1602,7 +1602,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>四川成都</v>
+        <v>浙江杭州</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1646,13 +1646,13 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>凯米尔</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B22" t="str">
         <v>弟弟</v>
       </c>
       <c r="C22" t="str">
-        <v>assets/1787326814713-p5oavnlulg.jpg</v>
+        <v>assets/1787326874462-z9rzs7wg17.jpg</v>
       </c>
       <c r="D22" t="str">
         <v>是</v>
@@ -1705,13 +1705,13 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>棕虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B23" t="str">
         <v>弟弟</v>
       </c>
       <c r="C23" t="str">
-        <v>assets/1787326773577-13q5out2d0.jpg</v>
+        <v>assets/1787326843271-0uhv7b9p89.jpg</v>
       </c>
       <c r="D23" t="str">
         <v>是</v>
@@ -1720,7 +1720,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>四川宜宾</v>
+        <v>四川成都</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1764,13 +1764,13 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>金棕虎斑</v>
+        <v>凯米尔</v>
       </c>
       <c r="B24" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C24" t="str">
-        <v>assets/1787326548993-89s929m2hg.jpg</v>
+        <v>assets/1787326814713-p5oavnlulg.jpg</v>
       </c>
       <c r="D24" t="str">
         <v>是</v>
@@ -1779,7 +1779,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>上海</v>
+        <v>四川成都</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1823,13 +1823,13 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>凯米尔色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B25" t="str">
         <v>弟弟</v>
       </c>
       <c r="C25" t="str">
-        <v>assets/1787326449218-09s9ucram4.jpg</v>
+        <v>assets/1787326773577-13q5out2d0.jpg</v>
       </c>
       <c r="D25" t="str">
         <v>是</v>
@@ -1838,7 +1838,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>德国</v>
+        <v>四川宜宾</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1882,13 +1882,13 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>棕虎补丁</v>
+        <v>金棕虎斑</v>
       </c>
       <c r="B26" t="str">
         <v>妹妹</v>
       </c>
       <c r="C26" t="str">
-        <v>assets/1787326277374-8ti107m5ki.jpg</v>
+        <v>assets/1787326548993-89s929m2hg.jpg</v>
       </c>
       <c r="D26" t="str">
         <v>是</v>
@@ -1897,7 +1897,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>广东深圳</v>
+        <v>上海</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1941,13 +1941,13 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>烟灰色</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B27" t="str">
         <v>弟弟</v>
       </c>
       <c r="C27" t="str">
-        <v>assets/1787326236952-2pmwche4t3.jpg</v>
+        <v>assets/1787326449218-09s9ucram4.jpg</v>
       </c>
       <c r="D27" t="str">
         <v>是</v>
@@ -1956,7 +1956,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>福建泉州</v>
+        <v>德国</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -2000,13 +2000,13 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>银虎斑</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B28" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C28" t="str">
-        <v>assets/1787326184557-90v6clkwen.jpg</v>
+        <v>assets/1787326277374-8ti107m5ki.jpg</v>
       </c>
       <c r="D28" t="str">
         <v>是</v>
@@ -2015,7 +2015,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>福建福州</v>
+        <v>广东深圳</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -2059,13 +2059,13 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>棕虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B29" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C29" t="str">
-        <v>assets/1787326046155-4tk23nq4dj.jpg</v>
+        <v>assets/1787326236952-2pmwche4t3.jpg</v>
       </c>
       <c r="D29" t="str">
         <v>是</v>
@@ -2074,7 +2074,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>广西贵港</v>
+        <v>福建泉州</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -2118,13 +2118,13 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>凯米尔色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B30" t="str">
         <v>弟弟</v>
       </c>
       <c r="C30" t="str">
-        <v>assets/1787325862706-wq18k3ej56.jpg</v>
+        <v>assets/1787326184557-90v6clkwen.jpg</v>
       </c>
       <c r="D30" t="str">
         <v>是</v>
@@ -2133,7 +2133,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>江苏苏州</v>
+        <v>福建福州</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -2177,13 +2177,13 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>凯米尔色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B31" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C31" t="str">
-        <v>assets/1787325743258-a7oac7hzlo.jpg</v>
+        <v>assets/1787326046155-4tk23nq4dj.jpg</v>
       </c>
       <c r="D31" t="str">
         <v>是</v>
@@ -2192,7 +2192,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>江苏苏州</v>
+        <v>广西贵港</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -2236,13 +2236,13 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>银虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B32" t="str">
         <v>弟弟</v>
       </c>
       <c r="C32" t="str">
-        <v>assets/1787325706797-kgk81ghccy.jpg</v>
+        <v>assets/1787325862706-wq18k3ej56.jpg</v>
       </c>
       <c r="D32" t="str">
         <v>是</v>
@@ -2251,7 +2251,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>北京</v>
+        <v>江苏苏州</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -2295,13 +2295,13 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>蓝虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B33" t="str">
         <v>弟弟</v>
       </c>
       <c r="C33" t="str">
-        <v>assets/1787325603704-lahzgrm7fa.jpg,assets/1787325690106-wgu3spujit.jpg</v>
+        <v>assets/1787325743258-a7oac7hzlo.jpg</v>
       </c>
       <c r="D33" t="str">
         <v>是</v>
@@ -2310,7 +2310,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>上海</v>
+        <v>江苏苏州</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -2354,13 +2354,13 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B34" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C34" t="str">
-        <v>assets/1787325554341-608thexrne.jpg</v>
+        <v>assets/1787325706797-kgk81ghccy.jpg</v>
       </c>
       <c r="D34" t="str">
         <v>是</v>
@@ -2369,7 +2369,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>江苏苏州</v>
+        <v>北京</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -2413,13 +2413,13 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>浅色银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B35" t="str">
         <v>弟弟</v>
       </c>
       <c r="C35" t="str">
-        <v>assets/1787325480828-q90pskoiw3.jpg</v>
+        <v>assets/1787325603704-lahzgrm7fa.jpg,assets/1787325690106-wgu3spujit.jpg</v>
       </c>
       <c r="D35" t="str">
         <v>是</v>
@@ -2428,7 +2428,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>四川成都</v>
+        <v>上海</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -2472,13 +2472,13 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>浅色银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B36" t="str">
         <v>妹妹</v>
       </c>
       <c r="C36" t="str">
-        <v>assets/1787325448999-a2pg8176fu.jpg</v>
+        <v>assets/1787325554341-608thexrne.jpg</v>
       </c>
       <c r="D36" t="str">
         <v>是</v>
@@ -2487,7 +2487,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>中国台湾</v>
+        <v>江苏苏州</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -2531,13 +2531,13 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>棕虎斑</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B37" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C37" t="str">
-        <v>assets/1787325357634-k55zlfhmqj.jpg</v>
+        <v>assets/1787325480828-q90pskoiw3.jpg</v>
       </c>
       <c r="D37" t="str">
         <v>是</v>
@@ -2546,7 +2546,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>浙江杭州</v>
+        <v>四川成都</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -2590,13 +2590,13 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>烟灰色</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B38" t="str">
         <v>妹妹</v>
       </c>
       <c r="C38" t="str">
-        <v>assets/1787325237876-t19isaq5gu.jpg</v>
+        <v>assets/1787325448999-a2pg8176fu.jpg</v>
       </c>
       <c r="D38" t="str">
         <v>是</v>
@@ -2605,7 +2605,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>辽宁沈阳</v>
+        <v>中国台湾</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -2649,13 +2649,13 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>金棕虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B39" t="str">
         <v>妹妹</v>
       </c>
       <c r="C39" t="str">
-        <v>assets/1787325199931-e7wms9qtya.jpg</v>
+        <v>assets/1787325357634-k55zlfhmqj.jpg</v>
       </c>
       <c r="D39" t="str">
         <v>是</v>
@@ -2664,7 +2664,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>四川成都</v>
+        <v>浙江杭州</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -2708,13 +2708,13 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>蓝虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B40" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C40" t="str">
-        <v>assets/1787325172354-4sa8uzaey2.jpg</v>
+        <v>assets/1787325237876-t19isaq5gu.jpg</v>
       </c>
       <c r="D40" t="str">
         <v>是</v>
@@ -2723,7 +2723,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>中国香港</v>
+        <v>辽宁沈阳</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -2767,13 +2767,13 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>烟灰色</v>
+        <v>金棕虎斑</v>
       </c>
       <c r="B41" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C41" t="str">
-        <v>assets/1787325109283-y7mvkk6qg4.jpg</v>
+        <v>assets/1787325199931-e7wms9qtya.jpg</v>
       </c>
       <c r="D41" t="str">
         <v>是</v>
@@ -2782,7 +2782,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>中国澳门</v>
+        <v>四川成都</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -2832,7 +2832,7 @@
         <v>弟弟</v>
       </c>
       <c r="C42" t="str">
-        <v>assets/1787325033629-y3ygps3zaj.jpg</v>
+        <v>assets/1787325172354-4sa8uzaey2.jpg</v>
       </c>
       <c r="D42" t="str">
         <v>是</v>
@@ -2841,7 +2841,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>山东青岛</v>
+        <v>中国香港</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -2891,7 +2891,7 @@
         <v>弟弟</v>
       </c>
       <c r="C43" t="str">
-        <v>assets/1787324954998-w5m5jox439.jpg</v>
+        <v>assets/1787325109283-y7mvkk6qg4.jpg</v>
       </c>
       <c r="D43" t="str">
         <v>是</v>
@@ -2900,7 +2900,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>海南海口</v>
+        <v>中国澳门</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2944,13 +2944,13 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>棕虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B44" t="str">
         <v>弟弟</v>
       </c>
       <c r="C44" t="str">
-        <v>assets/1787324905909-zrz8o79kdf.jpg</v>
+        <v>assets/1787325033629-y3ygps3zaj.jpg</v>
       </c>
       <c r="D44" t="str">
         <v>是</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>内蒙古</v>
+        <v>山东青岛</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -3009,7 +3009,7 @@
         <v>弟弟</v>
       </c>
       <c r="C45" t="str">
-        <v>assets/1787324880505-gbh0sn7b6j.jpg</v>
+        <v>assets/1787324954998-w5m5jox439.jpg</v>
       </c>
       <c r="D45" t="str">
         <v>是</v>
@@ -3018,7 +3018,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>中国香港</v>
+        <v>海南海口</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -3062,13 +3062,13 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B46" t="str">
         <v>弟弟</v>
       </c>
       <c r="C46" t="str">
-        <v>assets/1787324806613-31yyz14tsf.jpg</v>
+        <v>assets/1787324905909-zrz8o79kdf.jpg</v>
       </c>
       <c r="D46" t="str">
         <v>是</v>
@@ -3077,7 +3077,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>四川成都</v>
+        <v>内蒙古</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -3121,13 +3121,13 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>红虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B47" t="str">
         <v>弟弟</v>
       </c>
       <c r="C47" t="str">
-        <v>assets/1787324789658-uz6ephkdsh.jpg</v>
+        <v>assets/1787324880505-gbh0sn7b6j.jpg</v>
       </c>
       <c r="D47" t="str">
         <v>是</v>
@@ -3136,7 +3136,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>湖北武汉</v>
+        <v>中国香港</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -3186,7 +3186,7 @@
         <v>弟弟</v>
       </c>
       <c r="C48" t="str">
-        <v>assets/1787324522658-smn44crast.jpg</v>
+        <v>assets/1787324806613-31yyz14tsf.jpg</v>
       </c>
       <c r="D48" t="str">
         <v>是</v>
@@ -3195,7 +3195,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>湖北武汉</v>
+        <v>四川成都</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -3239,13 +3239,13 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>棕虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B49" t="str">
         <v>弟弟</v>
       </c>
       <c r="C49" t="str">
-        <v>assets/1787324365608-6xtrjp7euz.jpg</v>
+        <v>assets/1787324789658-uz6ephkdsh.jpg</v>
       </c>
       <c r="D49" t="str">
         <v>是</v>
@@ -3254,7 +3254,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>新疆</v>
+        <v>湖北武汉</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -3298,13 +3298,13 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>浅凯米尔</v>
+        <v>烟灰色</v>
       </c>
       <c r="B50" t="str">
         <v>弟弟</v>
       </c>
       <c r="C50" t="str">
-        <v>assets/1787324331029-d74lcuycf6.jpg</v>
+        <v>assets/1787324522658-smn44crast.jpg</v>
       </c>
       <c r="D50" t="str">
         <v>是</v>
@@ -3313,7 +3313,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>四川成都</v>
+        <v>湖北武汉</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -3357,13 +3357,13 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>红虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B51" t="str">
         <v>弟弟</v>
       </c>
       <c r="C51" t="str">
-        <v>assets/1787324297469-ans1lse2l5.jpg</v>
+        <v>assets/1787324365608-6xtrjp7euz.jpg</v>
       </c>
       <c r="D51" t="str">
         <v>是</v>
@@ -3372,7 +3372,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>四川乐山</v>
+        <v>新疆</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -3416,13 +3416,13 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>红虎斑</v>
+        <v>浅凯米尔</v>
       </c>
       <c r="B52" t="str">
         <v>弟弟</v>
       </c>
       <c r="C52" t="str">
-        <v>assets/1787324256827-7w383z4bg1.jpg</v>
+        <v>assets/1787324331029-d74lcuycf6.jpg</v>
       </c>
       <c r="D52" t="str">
         <v>是</v>
@@ -3431,7 +3431,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>中国台湾</v>
+        <v>四川成都</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -3475,13 +3475,13 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B53" t="str">
         <v>弟弟</v>
       </c>
       <c r="C53" t="str">
-        <v>assets/1787324228262-y3vwn6i4zk.jpg</v>
+        <v>assets/1787324297469-ans1lse2l5.jpg</v>
       </c>
       <c r="D53" t="str">
         <v>是</v>
@@ -3490,7 +3490,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>四川成都</v>
+        <v>四川乐山</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -3534,13 +3534,13 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>凯米尔色</v>
+        <v>红虎斑</v>
       </c>
       <c r="B54" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C54" t="str">
-        <v>assets/1787324201418-9tk4ik75mo.jpg</v>
+        <v>assets/1787324256827-7w383z4bg1.jpg</v>
       </c>
       <c r="D54" t="str">
         <v>是</v>
@@ -3549,7 +3549,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>江苏南京</v>
+        <v>中国台湾</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -3593,13 +3593,13 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B55" t="str">
         <v>弟弟</v>
       </c>
       <c r="C55" t="str">
-        <v>assets/1787324092513-jpa2rmkci2.jpg</v>
+        <v>assets/1787324228262-y3vwn6i4zk.jpg</v>
       </c>
       <c r="D55" t="str">
         <v>是</v>
@@ -3608,7 +3608,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>江苏南京</v>
+        <v>四川成都</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -3652,13 +3652,13 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>银虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B56" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C56" t="str">
-        <v>assets/1787323318612-soge38hpsf.jpg</v>
+        <v>assets/1787324201418-9tk4ik75mo.jpg</v>
       </c>
       <c r="D56" t="str">
         <v>是</v>
@@ -3667,7 +3667,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>上海</v>
+        <v>江苏南京</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -3717,7 +3717,7 @@
         <v>弟弟</v>
       </c>
       <c r="C57" t="str">
-        <v>assets/1787323235892-7yq8ioq01e.jpg</v>
+        <v>assets/1787324092513-jpa2rmkci2.jpg</v>
       </c>
       <c r="D57" t="str">
         <v>是</v>
@@ -3726,7 +3726,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>四川成都</v>
+        <v>江苏南京</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -3773,10 +3773,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B58" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C58" t="str">
-        <v>assets/1787322988096-6e2f54q7vo.jpg</v>
+        <v>assets/1787323318612-soge38hpsf.jpg</v>
       </c>
       <c r="D58" t="str">
         <v>是</v>
@@ -3785,7 +3785,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>浙江宁波</v>
+        <v>上海</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -3829,13 +3829,13 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>银虎斑补丁</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B59" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C59" t="str">
-        <v>assets/1787322938518-85ev8bs2k5.jpg</v>
+        <v>assets/1787323235892-7yq8ioq01e.jpg</v>
       </c>
       <c r="D59" t="str">
         <v>是</v>
@@ -3844,7 +3844,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>马来西亚</v>
+        <v>四川成都</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -3891,10 +3891,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B60" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C60" t="str">
-        <v>assets/1787322881183-tzu9xtw2sg.jpg</v>
+        <v>assets/1787322988096-6e2f54q7vo.jpg</v>
       </c>
       <c r="D60" t="str">
         <v>是</v>
@@ -3903,7 +3903,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>陕西西安</v>
+        <v>浙江宁波</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -3947,13 +3947,13 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>纯黑色</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B61" t="str">
         <v>妹妹</v>
       </c>
       <c r="C61" t="str">
-        <v>assets/1787322840098-nhy4jjyx7k.jpg</v>
+        <v>assets/1787322938518-85ev8bs2k5.jpg</v>
       </c>
       <c r="D61" t="str">
         <v>是</v>
@@ -3962,7 +3962,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>广西南宁</v>
+        <v>马来西亚</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -4006,13 +4006,13 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B62" t="str">
         <v>弟弟</v>
       </c>
       <c r="C62" t="str">
-        <v>assets/1787322760950-gn3qgego4s.jpg</v>
+        <v>assets/1787322881183-tzu9xtw2sg.jpg</v>
       </c>
       <c r="D62" t="str">
         <v>是</v>
@@ -4021,7 +4021,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>广西南宁</v>
+        <v>陕西西安</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -4065,13 +4065,13 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>红虎斑</v>
+        <v>纯黑色</v>
       </c>
       <c r="B63" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C63" t="str">
-        <v>assets/1787322605982-04n50xegt2.jpg</v>
+        <v>assets/1787322840098-nhy4jjyx7k.jpg</v>
       </c>
       <c r="D63" t="str">
         <v>是</v>
@@ -4080,7 +4080,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>上海</v>
+        <v>广西南宁</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -4124,13 +4124,13 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B64" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C64" t="str">
-        <v>assets/1787322490045-kog3ru43dy.jpg</v>
+        <v>assets/1787322760950-gn3qgego4s.jpg</v>
       </c>
       <c r="D64" t="str">
         <v>是</v>
@@ -4139,7 +4139,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>上海</v>
+        <v>广西南宁</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -4189,7 +4189,7 @@
         <v>弟弟</v>
       </c>
       <c r="C65" t="str">
-        <v>assets/1787322419996-0m33yx89nm.jpg</v>
+        <v>assets/1787322605982-04n50xegt2.jpg</v>
       </c>
       <c r="D65" t="str">
         <v>是</v>
@@ -4198,7 +4198,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>广东广州</v>
+        <v>上海</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -4242,13 +4242,13 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>浅色银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B66" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C66" t="str">
-        <v>assets/1787322377730-vj5csj2mll.jpg</v>
+        <v>assets/1787322490045-kog3ru43dy.jpg</v>
       </c>
       <c r="D66" t="str">
         <v>是</v>
@@ -4257,7 +4257,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>柬埔寨</v>
+        <v>上海</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -4301,13 +4301,13 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>蓝虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B67" t="str">
         <v>弟弟</v>
       </c>
       <c r="C67" t="str">
-        <v>assets/1787322269611-53yaj5ideu.jpg</v>
+        <v>assets/1787322419996-0m33yx89nm.jpg</v>
       </c>
       <c r="D67" t="str">
         <v>是</v>
@@ -4316,7 +4316,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>山东枣庄</v>
+        <v>广东广州</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -4360,13 +4360,13 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>银虎斑</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B68" t="str">
         <v>弟弟</v>
       </c>
       <c r="C68" t="str">
-        <v>assets/1787321989528-7d6liuhuk9.jpg</v>
+        <v>assets/1787322377730-vj5csj2mll.jpg</v>
       </c>
       <c r="D68" t="str">
         <v>是</v>
@@ -4375,7 +4375,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>陕西西安</v>
+        <v>柬埔寨</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -4419,13 +4419,13 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B69" t="str">
         <v>弟弟</v>
       </c>
       <c r="C69" t="str">
-        <v>assets/1787321941642-xlrc1no2ua.jpg</v>
+        <v>assets/1787322269611-53yaj5ideu.jpg</v>
       </c>
       <c r="D69" t="str">
         <v>是</v>
@@ -4434,7 +4434,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>山东东营</v>
+        <v>山东枣庄</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -4478,13 +4478,13 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>凯米尔色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B70" t="str">
         <v>弟弟</v>
       </c>
       <c r="C70" t="str">
-        <v>assets/1787321903535-6orj7qcgzn.jpg</v>
+        <v>assets/1787321989528-7d6liuhuk9.jpg</v>
       </c>
       <c r="D70" t="str">
         <v>是</v>
@@ -4493,7 +4493,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>中国台湾</v>
+        <v>陕西西安</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -4537,13 +4537,13 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>烟灰色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B71" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C71" t="str">
-        <v>assets/1787321858985-v4qej7cq7g.jpg</v>
+        <v>assets/1787321941642-xlrc1no2ua.jpg</v>
       </c>
       <c r="D71" t="str">
         <v>是</v>
@@ -4552,7 +4552,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>中国台湾</v>
+        <v>山东东营</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -4596,13 +4596,13 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>银虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B72" t="str">
         <v>弟弟</v>
       </c>
       <c r="C72" t="str">
-        <v>assets/1787321834306-efgnyhujon.jpg</v>
+        <v>assets/1787321903535-6orj7qcgzn.jpg</v>
       </c>
       <c r="D72" t="str">
         <v>是</v>
@@ -4611,7 +4611,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>北京</v>
+        <v>中国台湾</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -4655,13 +4655,13 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B73" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C73" t="str">
-        <v>assets/1787321439916-uttgpbkogb.jpg</v>
+        <v>assets/1787321858985-v4qej7cq7g.jpg</v>
       </c>
       <c r="D73" t="str">
         <v>是</v>
@@ -4670,7 +4670,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>安徽合肥</v>
+        <v>中国台湾</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -4720,7 +4720,7 @@
         <v>弟弟</v>
       </c>
       <c r="C74" t="str">
-        <v>assets/1787321419210-51hhgurygq.jpg</v>
+        <v>assets/1787321834306-efgnyhujon.jpg</v>
       </c>
       <c r="D74" t="str">
         <v>是</v>
@@ -4729,7 +4729,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>上海</v>
+        <v>北京</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -4773,13 +4773,13 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>凯米尔色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B75" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C75" t="str">
-        <v>assets/1787321363369-bzjn51j5il.jpg</v>
+        <v>assets/1787321439916-uttgpbkogb.jpg</v>
       </c>
       <c r="D75" t="str">
         <v>是</v>
@@ -4788,7 +4788,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>中国台湾</v>
+        <v>安徽合肥</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -4832,13 +4832,13 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B76" t="str">
         <v>弟弟</v>
       </c>
       <c r="C76" t="str">
-        <v>assets/1787321332559-87p6spuch3.jpg</v>
+        <v>assets/1787321419210-51hhgurygq.jpg</v>
       </c>
       <c r="D76" t="str">
         <v>是</v>
@@ -4847,7 +4847,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>中国台湾</v>
+        <v>上海</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -4891,13 +4891,13 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>棕虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B77" t="str">
         <v>妹妹</v>
       </c>
       <c r="C77" t="str">
-        <v>assets/1787321232531-59lnzv8y98.jpg</v>
+        <v>assets/1787321363369-bzjn51j5il.jpg</v>
       </c>
       <c r="D77" t="str">
         <v>是</v>
@@ -4906,7 +4906,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>北京</v>
+        <v>中国台湾</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -4950,13 +4950,13 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B78" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C78" t="str">
-        <v>assets/1787319975814-g1pfa56vfp.jpg</v>
+        <v>assets/1787321332559-87p6spuch3.jpg</v>
       </c>
       <c r="D78" t="str">
         <v>是</v>
@@ -4965,7 +4965,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>浙江宁波</v>
+        <v>中国台湾</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -5009,13 +5009,13 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B79" t="str">
         <v>妹妹</v>
       </c>
       <c r="C79" t="str">
-        <v>assets/1787319800704-v3qeu062ak.jpg</v>
+        <v>assets/1787321232531-59lnzv8y98.jpg</v>
       </c>
       <c r="D79" t="str">
         <v>是</v>
@@ -5024,7 +5024,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>河北唐山</v>
+        <v>北京</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -5074,7 +5074,7 @@
         <v>妹妹</v>
       </c>
       <c r="C80" t="str">
-        <v>assets/1787319745369-zn66xr3bvb.jpg</v>
+        <v>assets/1787319975814-g1pfa56vfp.jpg</v>
       </c>
       <c r="D80" t="str">
         <v>是</v>
@@ -5083,7 +5083,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>河北石家庄</v>
+        <v>浙江宁波</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -5127,13 +5127,13 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>棕虎补丁</v>
+        <v>银虎斑</v>
       </c>
       <c r="B81" t="str">
         <v>妹妹</v>
       </c>
       <c r="C81" t="str">
-        <v>assets/1787319547969-zqlq35fxxt.jpg</v>
+        <v>assets/1787319800704-v3qeu062ak.jpg</v>
       </c>
       <c r="D81" t="str">
         <v>是</v>
@@ -5142,7 +5142,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>韩国</v>
+        <v>河北唐山</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -5186,13 +5186,13 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>蓝银虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B82" t="str">
         <v>妹妹</v>
       </c>
       <c r="C82" t="str">
-        <v>assets/1787319501376-xscwljnu1j.jpg</v>
+        <v>assets/1787319745369-zn66xr3bvb.jpg</v>
       </c>
       <c r="D82" t="str">
         <v>是</v>
@@ -5201,7 +5201,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>美国</v>
+        <v>河北石家庄</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -5245,13 +5245,13 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>棕虎斑</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B83" t="str">
         <v>妹妹</v>
       </c>
       <c r="C83" t="str">
-        <v>assets/1787319443529-4a0zqikufx.jpg</v>
+        <v>assets/1787319547969-zqlq35fxxt.jpg</v>
       </c>
       <c r="D83" t="str">
         <v>是</v>
@@ -5260,7 +5260,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>中国台湾</v>
+        <v>韩国</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -5304,13 +5304,13 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>蓝虎斑</v>
+        <v>蓝银虎斑</v>
       </c>
       <c r="B84" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C84" t="str">
-        <v>assets/1787319356194-lr2d5680i9.jpg</v>
+        <v>assets/1787319501376-xscwljnu1j.jpg</v>
       </c>
       <c r="D84" t="str">
         <v>是</v>
@@ -5319,7 +5319,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>中国台湾</v>
+        <v>美国</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -5369,7 +5369,7 @@
         <v>妹妹</v>
       </c>
       <c r="C85" t="str">
-        <v>assets/1787319208828-aizqo4blcv.jpg</v>
+        <v>assets/1787319443529-4a0zqikufx.jpg</v>
       </c>
       <c r="D85" t="str">
         <v>是</v>
@@ -5378,7 +5378,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>山东淄博</v>
+        <v>中国台湾</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -5422,13 +5422,13 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B86" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C86" t="str">
-        <v>assets/1787319162970-cc2v8ovnni.jpg</v>
+        <v>assets/1787319356194-lr2d5680i9.jpg</v>
       </c>
       <c r="D86" t="str">
         <v>是</v>
@@ -5437,7 +5437,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>韩国</v>
+        <v>中国台湾</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -5481,13 +5481,13 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>棕虎补丁</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B87" t="str">
         <v>妹妹</v>
       </c>
       <c r="C87" t="str">
-        <v>assets/1787319098214-8pwa9yx2wc.jpg</v>
+        <v>assets/1787319208828-aizqo4blcv.jpg</v>
       </c>
       <c r="D87" t="str">
         <v>是</v>
@@ -5496,7 +5496,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>四川成都</v>
+        <v>山东淄博</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -5543,10 +5543,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B88" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C88" t="str">
-        <v>assets/1787318867999-3gxdddp72x.jpg</v>
+        <v>assets/1787319162970-cc2v8ovnni.jpg</v>
       </c>
       <c r="D88" t="str">
         <v>是</v>
@@ -5555,7 +5555,7 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>广东广州</v>
+        <v>韩国</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -5599,13 +5599,13 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>银虎斑</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B89" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C89" t="str">
-        <v>assets/1787318609722-0ojb3aikwi.jpg</v>
+        <v>assets/1787319098214-8pwa9yx2wc.jpg</v>
       </c>
       <c r="D89" t="str">
         <v>是</v>
@@ -5614,7 +5614,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>黑龙江鹤岗</v>
+        <v>四川成都</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -5658,13 +5658,13 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>蓝虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B90" t="str">
         <v>弟弟</v>
       </c>
       <c r="C90" t="str">
-        <v>assets/1787318530612-779fbkfcoi.jpg</v>
+        <v>assets/1787318867999-3gxdddp72x.jpg</v>
       </c>
       <c r="D90" t="str">
         <v>是</v>
@@ -5673,7 +5673,7 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>天津</v>
+        <v>广东广州</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -5723,7 +5723,7 @@
         <v>弟弟</v>
       </c>
       <c r="C91" t="str">
-        <v>assets/1787318365475-sj87wtsai3.jpg</v>
+        <v>assets/1787318609722-0ojb3aikwi.jpg</v>
       </c>
       <c r="D91" t="str">
         <v>是</v>
@@ -5732,7 +5732,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>山西朔州</v>
+        <v>黑龙江鹤岗</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -5762,7 +5762,7 @@
         <v/>
       </c>
       <c r="P91" t="str">
-        <v>已接猫</v>
+        <v/>
       </c>
       <c r="Q91" t="str">
         <v/>
@@ -5776,13 +5776,13 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B92" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C92" t="str">
-        <v>assets/1787318326155-ia4noopjhq.jpg</v>
+        <v>assets/1787318530612-779fbkfcoi.jpg</v>
       </c>
       <c r="D92" t="str">
         <v>是</v>
@@ -5791,7 +5791,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>贵州</v>
+        <v>天津</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -5835,22 +5835,22 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B93" t="str">
         <v>弟弟</v>
       </c>
       <c r="C93" t="str">
-        <v>assets/1787304479674-w0trechn4p.jpg</v>
+        <v>assets/1787318365475-sj87wtsai3.jpg</v>
       </c>
       <c r="D93" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E93" t="str">
-        <v>2026-06-06</v>
+        <v/>
       </c>
       <c r="F93" t="str">
-        <v/>
+        <v>山西朔州</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -5880,7 +5880,7 @@
         <v/>
       </c>
       <c r="P93" t="str">
-        <v/>
+        <v>已接猫</v>
       </c>
       <c r="Q93" t="str">
         <v/>
@@ -5889,27 +5889,27 @@
         <v/>
       </c>
       <c r="S93" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>纯黑色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B94" t="str">
         <v>妹妹</v>
       </c>
       <c r="C94" t="str">
-        <v>assets/1787283819124-4v7d1w01la.jpg</v>
+        <v>assets/1787318326155-ia4noopjhq.jpg</v>
       </c>
       <c r="D94" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E94" t="str">
-        <v>2026-02-20</v>
+        <v/>
       </c>
       <c r="F94" t="str">
-        <v/>
+        <v>贵州</v>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -5948,24 +5948,24 @@
         <v/>
       </c>
       <c r="S94" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>阴影色NS12</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B95" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C95" t="str">
-        <v>assets/1787283212708-jdnyi6ecci.jpg</v>
+        <v>assets/1787304479674-w0trechn4p.jpg</v>
       </c>
       <c r="D95" t="str">
         <v>否</v>
       </c>
       <c r="E95" t="str">
-        <v>2026-05-28</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F95" t="str">
         <v/>
@@ -6012,22 +6012,22 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>阴影色NS11</v>
+        <v>纯黑色</v>
       </c>
       <c r="B96" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C96" t="str">
-        <v>assets/1787283153501-s2tjg9spwu.jpg</v>
+        <v>assets/1787283819124-4v7d1w01la.jpg</v>
       </c>
       <c r="D96" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E96" t="str">
-        <v>2026-06-15</v>
+        <v>2026-02-20</v>
       </c>
       <c r="F96" t="str">
-        <v>重庆</v>
+        <v/>
       </c>
       <c r="G96" t="str">
         <v/>
@@ -6071,19 +6071,19 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>浅烟灰色</v>
+        <v>阴影色NS12</v>
       </c>
       <c r="B97" t="str">
         <v>妹妹</v>
       </c>
       <c r="C97" t="str">
-        <v>assets/1787283092677-i4d8tyrjtf.jpg</v>
+        <v>assets/1787283212708-jdnyi6ecci.jpg</v>
       </c>
       <c r="D97" t="str">
         <v>否</v>
       </c>
       <c r="E97" t="str">
-        <v>2026-03-21</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F97" t="str">
         <v/>
@@ -6130,22 +6130,22 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>棕虎斑</v>
+        <v>阴影色NS11</v>
       </c>
       <c r="B98" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C98" t="str">
-        <v>assets/1787283031104-bpyq9wy2tl.jpg</v>
+        <v>assets/1787283153501-s2tjg9spwu.jpg</v>
       </c>
       <c r="D98" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E98" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F98" t="str">
-        <v/>
+        <v>重庆</v>
       </c>
       <c r="G98" t="str">
         <v/>
@@ -6189,19 +6189,19 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>棕虎斑</v>
+        <v>浅烟灰色</v>
       </c>
       <c r="B99" t="str">
         <v>妹妹</v>
       </c>
       <c r="C99" t="str">
-        <v>assets/1787282991501-2fjfws0rqw.jpg</v>
+        <v>assets/1787283092677-i4d8tyrjtf.jpg</v>
       </c>
       <c r="D99" t="str">
         <v>否</v>
       </c>
       <c r="E99" t="str">
-        <v>2026-06-06</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F99" t="str">
         <v/>
@@ -6254,13 +6254,13 @@
         <v>妹妹</v>
       </c>
       <c r="C100" t="str">
-        <v>assets/1787282942262-syr48fym6c.jpg</v>
+        <v>assets/1787283031104-bpyq9wy2tl.jpg</v>
       </c>
       <c r="D100" t="str">
         <v>否</v>
       </c>
       <c r="E100" t="str">
-        <v>2026-06-15</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F100" t="str">
         <v/>
@@ -6310,10 +6310,10 @@
         <v>棕虎斑</v>
       </c>
       <c r="B101" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C101" t="str">
-        <v>assets/1787282819855-7vhx3m0v40.jpg</v>
+        <v>assets/1787282991501-2fjfws0rqw.jpg</v>
       </c>
       <c r="D101" t="str">
         <v>否</v>
@@ -6372,13 +6372,13 @@
         <v>妹妹</v>
       </c>
       <c r="C102" t="str">
-        <v>assets/1787282703381-2uakw592b4.jpg</v>
+        <v>assets/1787282942262-syr48fym6c.jpg</v>
       </c>
       <c r="D102" t="str">
         <v>否</v>
       </c>
       <c r="E102" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F102" t="str">
         <v/>
@@ -6425,13 +6425,13 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B103" t="str">
         <v>弟弟</v>
       </c>
       <c r="C103" t="str">
-        <v>assets/1787282649397-9hc31ncrpc.jpg</v>
+        <v>assets/1787282819855-7vhx3m0v40.jpg</v>
       </c>
       <c r="D103" t="str">
         <v>否</v>
@@ -6484,13 +6484,13 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B104" t="str">
         <v>妹妹</v>
       </c>
       <c r="C104" t="str">
-        <v>assets/1787282617957-svcoyyznpg.jpg</v>
+        <v>assets/1787282703381-2uakw592b4.jpg</v>
       </c>
       <c r="D104" t="str">
         <v>否</v>
@@ -6549,7 +6549,7 @@
         <v>弟弟</v>
       </c>
       <c r="C105" t="str">
-        <v>assets/1787282419632-78nixqjzua.jpg</v>
+        <v>assets/1787282649397-9hc31ncrpc.jpg</v>
       </c>
       <c r="D105" t="str">
         <v>否</v>
@@ -6602,19 +6602,19 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>纯黑色</v>
+        <v>烟灰色</v>
       </c>
       <c r="B106" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C106" t="str">
-        <v>assets/1787282349942-2cfuyn7xlc.jpg</v>
+        <v>assets/1787282617957-svcoyyznpg.jpg</v>
       </c>
       <c r="D106" t="str">
         <v>否</v>
       </c>
       <c r="E106" t="str">
-        <v>2026-03-21</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F106" t="str">
         <v/>
@@ -6661,19 +6661,19 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B107" t="str">
         <v>弟弟</v>
       </c>
       <c r="C107" t="str">
-        <v>assets/1787282064159-6b4z8c5msd.jpg</v>
+        <v>assets/1787282419632-78nixqjzua.jpg</v>
       </c>
       <c r="D107" t="str">
         <v>否</v>
       </c>
       <c r="E107" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F107" t="str">
         <v/>
@@ -6720,19 +6720,19 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>阴影色NS11</v>
+        <v>纯黑色</v>
       </c>
       <c r="B108" t="str">
         <v>弟弟</v>
       </c>
       <c r="C108" t="str">
-        <v>assets/1787280590041-vzcwebdok1.jpg</v>
+        <v>assets/1787282349942-2cfuyn7xlc.jpg</v>
       </c>
       <c r="D108" t="str">
         <v>否</v>
       </c>
       <c r="E108" t="str">
-        <v>2026-05-28</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F108" t="str">
         <v/>
@@ -6779,19 +6779,19 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>浅色银虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B109" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C109" t="str">
-        <v>assets/1787281786169-9ia0h837ct.jpg</v>
+        <v>assets/1787282064159-6b4z8c5msd.jpg</v>
       </c>
       <c r="D109" t="str">
         <v>否</v>
       </c>
       <c r="E109" t="str">
-        <v>2026-06-15</v>
+        <v>2026-06-10</v>
       </c>
       <c r="F109" t="str">
         <v/>
@@ -6838,22 +6838,22 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>浅烟灰色</v>
+        <v>阴影色NS11</v>
       </c>
       <c r="B110" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C110" t="str">
-        <v>assets/1785843720843-63qz159daui.jpg</v>
+        <v>assets/1787280590041-vzcwebdok1.jpg</v>
       </c>
       <c r="D110" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E110" t="str">
-        <v>2026-03-21</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F110" t="str">
-        <v>四川成都</v>
+        <v/>
       </c>
       <c r="G110" t="str">
         <v/>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>凯米尔色</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B111" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C111" t="str">
-        <v>assets/1787301984056-iu6afro5z5.jpg, assets/1785843763310-elg05ur61ri.jpg</v>
+        <v>assets/1787281786169-9ia0h837ct.jpg</v>
       </c>
       <c r="D111" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E111" t="str">
-        <v>2026-02-14</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F111" t="str">
-        <v>上海浦东</v>
+        <v/>
       </c>
       <c r="G111" t="str">
         <v/>
@@ -6956,22 +6956,22 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>银虎斑补丁</v>
+        <v>浅烟灰色</v>
       </c>
       <c r="B112" t="str">
         <v>妹妹</v>
       </c>
       <c r="C112" t="str">
-        <v>assets/1785843820715-9kz7gy4mbr7.jpg</v>
+        <v>assets/1785843720843-63qz159daui.jpg</v>
       </c>
       <c r="D112" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E112" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F112" t="str">
-        <v/>
+        <v>四川成都</v>
       </c>
       <c r="G112" t="str">
         <v/>
@@ -7015,22 +7015,22 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>烟灰色</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B113" t="str">
         <v>弟弟</v>
       </c>
       <c r="C113" t="str">
-        <v>assets/1785843953805-mxl3x1982io.jpg</v>
+        <v>assets/1787301984056-iu6afro5z5.jpg, assets/1785843763310-elg05ur61ri.jpg</v>
       </c>
       <c r="D113" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E113" t="str">
-        <v>2026-05-18</v>
+        <v>2026-02-14</v>
       </c>
       <c r="F113" t="str">
-        <v/>
+        <v>上海浦东</v>
       </c>
       <c r="G113" t="str">
         <v/>
@@ -7074,19 +7074,19 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>棕虎斑玳瑁</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B114" t="str">
         <v>妹妹</v>
       </c>
       <c r="C114" t="str">
-        <v>assets/1785844013835-ek4xpcje7kh.jpg</v>
+        <v>assets/1785843820715-9kz7gy4mbr7.jpg</v>
       </c>
       <c r="D114" t="str">
         <v>否</v>
       </c>
       <c r="E114" t="str">
-        <v>2026-02-14</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F114" t="str">
         <v/>
@@ -7133,19 +7133,19 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>银虎斑补丁</v>
+        <v>烟灰色</v>
       </c>
       <c r="B115" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C115" t="str">
-        <v>assets/1785844434338-ek5zbdgdcne.jpg</v>
+        <v>assets/1785843953805-mxl3x1982io.jpg</v>
       </c>
       <c r="D115" t="str">
         <v>否</v>
       </c>
       <c r="E115" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F115" t="str">
         <v/>
@@ -7192,22 +7192,22 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑玳瑁</v>
       </c>
       <c r="B116" t="str">
         <v>妹妹</v>
       </c>
       <c r="C116" t="str">
-        <v>assets/1785838787730-s5f333sc3u.jpg</v>
+        <v>assets/1785844013835-ek4xpcje7kh.jpg</v>
       </c>
       <c r="D116" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E116" t="str">
-        <v>2026-06-05</v>
+        <v>2026-02-14</v>
       </c>
       <c r="F116" t="str">
-        <v>湖北恩施</v>
+        <v/>
       </c>
       <c r="G116" t="str">
         <v/>
@@ -7251,22 +7251,22 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>银虎斑</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B117" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C117" t="str">
-        <v>assets/1785842296661-6qw3zs3as8h.jpg</v>
+        <v>assets/1785844434338-ek5zbdgdcne.jpg</v>
       </c>
       <c r="D117" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E117" t="str">
-        <v>2026-06-05</v>
+        <v>2026-05-24</v>
       </c>
       <c r="F117" t="str">
-        <v>湖北恩施</v>
+        <v/>
       </c>
       <c r="G117" t="str">
         <v/>
@@ -7313,19 +7313,19 @@
         <v>银虎斑</v>
       </c>
       <c r="B118" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C118" t="str">
-        <v>assets/1785842429109-porc98rel5.jpg</v>
+        <v>assets/1785838787730-s5f333sc3u.jpg</v>
       </c>
       <c r="D118" t="str">
         <v>是</v>
       </c>
       <c r="E118" t="str">
-        <v>2025-11-05</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F118" t="str">
-        <v>韩国</v>
+        <v>湖北恩施</v>
       </c>
       <c r="G118" t="str">
         <v/>
@@ -7372,19 +7372,19 @@
         <v>银虎斑</v>
       </c>
       <c r="B119" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C119" t="str">
-        <v>assets/1785842594141-fcglbzjp509.jpg</v>
+        <v>assets/1785842296661-6qw3zs3as8h.jpg</v>
       </c>
       <c r="D119" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E119" t="str">
-        <v>2026-05-18</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F119" t="str">
-        <v/>
+        <v>湖北恩施</v>
       </c>
       <c r="G119" t="str">
         <v/>
@@ -7428,22 +7428,22 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B120" t="str">
         <v>弟弟</v>
       </c>
       <c r="C120" t="str">
-        <v>assets/1785842639100-82k775dhwiv.jpg</v>
+        <v>assets/1785842429109-porc98rel5.jpg</v>
       </c>
       <c r="D120" t="str">
         <v>是</v>
       </c>
       <c r="E120" t="str">
-        <v>2026-05-28</v>
+        <v>2025-11-05</v>
       </c>
       <c r="F120" t="str">
-        <v>四川自贡</v>
+        <v>韩国</v>
       </c>
       <c r="G120" t="str">
         <v/>
@@ -7487,19 +7487,19 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B121" t="str">
         <v>妹妹</v>
       </c>
       <c r="C121" t="str">
-        <v>assets/1785842684502-mnhr0r96eee.jpg</v>
+        <v>assets/1785842594141-fcglbzjp509.jpg</v>
       </c>
       <c r="D121" t="str">
         <v>否</v>
       </c>
       <c r="E121" t="str">
-        <v>2026-06-06</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F121" t="str">
         <v/>
@@ -7546,22 +7546,22 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>纯黑色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B122" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C122" t="str">
-        <v>assets/1785842779532-5u1j0igrw1s.jpg</v>
+        <v>assets/1785842639100-82k775dhwiv.jpg</v>
       </c>
       <c r="D122" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E122" t="str">
-        <v>2026-03-05</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F122" t="str">
-        <v/>
+        <v>四川自贡</v>
       </c>
       <c r="G122" t="str">
         <v/>
@@ -7605,22 +7605,22 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B123" t="str">
         <v>妹妹</v>
       </c>
       <c r="C123" t="str">
-        <v>assets/1785842817046-6keqv4rw4yf.jpg</v>
+        <v>assets/1785842684502-mnhr0r96eee.jpg</v>
       </c>
       <c r="D123" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E123" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F123" t="str">
-        <v>韩国</v>
+        <v/>
       </c>
       <c r="G123" t="str">
         <v/>
@@ -7664,22 +7664,22 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>浅色银虎斑</v>
+        <v>纯黑色</v>
       </c>
       <c r="B124" t="str">
         <v>妹妹</v>
       </c>
       <c r="C124" t="str">
-        <v>assets/1785842950972-a88lbrskpc.jpg</v>
+        <v>assets/1785842779532-5u1j0igrw1s.jpg</v>
       </c>
       <c r="D124" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E124" t="str">
-        <v>2026-06-05</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F124" t="str">
-        <v>河北邢台</v>
+        <v/>
       </c>
       <c r="G124" t="str">
         <v/>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B125" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C125" t="str">
-        <v>assets/1785843011477-n3l1wi6ech.jpg</v>
+        <v>assets/1785842817046-6keqv4rw4yf.jpg</v>
       </c>
       <c r="D125" t="str">
         <v>是</v>
       </c>
       <c r="E125" t="str">
-        <v>2026-06-05</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F125" t="str">
-        <v>四川自贡</v>
+        <v>韩国</v>
       </c>
       <c r="G125" t="str">
         <v/>
@@ -7782,22 +7782,22 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>蓝虎斑</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B126" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C126" t="str">
-        <v>assets/1785843237517-ga449iqess5.jpg</v>
+        <v>assets/1785842950972-a88lbrskpc.jpg</v>
       </c>
       <c r="D126" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E126" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F126" t="str">
-        <v/>
+        <v>河北邢台</v>
       </c>
       <c r="G126" t="str">
         <v/>
@@ -7841,22 +7841,22 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>棕虎斑补丁</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B127" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C127" t="str">
-        <v>assets/1785842523893-7nwnnhwi4ns.jpg</v>
+        <v>assets/1785843011477-n3l1wi6ech.jpg</v>
       </c>
       <c r="D127" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E127" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F127" t="str">
-        <v/>
+        <v>四川自贡</v>
       </c>
       <c r="G127" t="str">
         <v/>
@@ -7903,16 +7903,16 @@
         <v>蓝虎斑</v>
       </c>
       <c r="B128" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C128" t="str">
-        <v>assets/1785843497557-st27fk8drqi.jpg</v>
+        <v>assets/1785843237517-ga449iqess5.jpg</v>
       </c>
       <c r="D128" t="str">
         <v>否</v>
       </c>
       <c r="E128" t="str">
-        <v>2026-04-05</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F128" t="str">
         <v/>
@@ -7959,13 +7959,13 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑补丁</v>
       </c>
       <c r="B129" t="str">
         <v>妹妹</v>
       </c>
       <c r="C129" t="str">
-        <v>assets/1785843621923-ylhakbtw13i.jpg</v>
+        <v>assets/1785842523893-7nwnnhwi4ns.jpg</v>
       </c>
       <c r="D129" t="str">
         <v>否</v>
@@ -8018,19 +8018,19 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B130" t="str">
         <v>妹妹</v>
       </c>
       <c r="C130" t="str">
-        <v>assets/1785843663884-sfxvpmiet7.jpg</v>
+        <v>assets/1785843497557-st27fk8drqi.jpg</v>
       </c>
       <c r="D130" t="str">
         <v>否</v>
       </c>
       <c r="E130" t="str">
-        <v>2026-03-05</v>
+        <v>2026-04-05</v>
       </c>
       <c r="F130" t="str">
         <v/>
@@ -8077,52 +8077,52 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>蓝虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B131" t="str">
         <v>妹妹</v>
       </c>
       <c r="C131" t="str">
-        <v>assets/1785852601940-o236xtv7yx.jpeg</v>
+        <v>assets/1785843621923-ylhakbtw13i.jpg</v>
       </c>
       <c r="D131" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E131" t="str">
-        <v>2026-02-20</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F131" t="str">
-        <v>荷兰</v>
+        <v/>
       </c>
       <c r="G131" t="str">
-        <v>阿泽</v>
+        <v/>
       </c>
       <c r="H131" t="str">
-        <v>小辫子</v>
+        <v/>
       </c>
       <c r="I131" t="str">
-        <v>驺驺</v>
+        <v/>
       </c>
       <c r="J131" t="str">
-        <v>2026-07-02</v>
+        <v/>
       </c>
       <c r="K131" t="str">
         <v/>
       </c>
       <c r="L131" t="str">
-        <v>2026-07-02</v>
+        <v/>
       </c>
       <c r="M131" t="str">
-        <v>2026-08-03</v>
+        <v/>
       </c>
       <c r="N131" t="str">
-        <v>2026-11-04</v>
+        <v/>
       </c>
       <c r="O131" t="str">
-        <v>2026-08-03 · 血清检测,2026-07-02 · 打疫苗 · assets/diary/zouzou-depart.jpg,2026-07-30 · 6.2斤 · 五个月10天了 · assets/feedback/zouzou-1.jpg</v>
+        <v/>
       </c>
       <c r="P131" t="str">
-        <v>已付定金</v>
+        <v/>
       </c>
       <c r="Q131" t="str">
         <v/>
@@ -8131,27 +8131,27 @@
         <v/>
       </c>
       <c r="S131" t="str">
-        <v>否</v>
+        <v/>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>红虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B132" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C132" t="str">
-        <v>assets/1785853950207-cedor66ou2q.jpeg</v>
+        <v>assets/1785843663884-sfxvpmiet7.jpg</v>
       </c>
       <c r="D132" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E132" t="str">
-        <v/>
+        <v>2026-03-05</v>
       </c>
       <c r="F132" t="str">
-        <v>广东广州</v>
+        <v/>
       </c>
       <c r="G132" t="str">
         <v/>
@@ -8195,52 +8195,52 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>红虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B133" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C133" t="str">
-        <v>assets/1785854129383-c8qkvl537x.jpeg</v>
+        <v>assets/1785852601940-o236xtv7yx.jpeg</v>
       </c>
       <c r="D133" t="str">
         <v>是</v>
       </c>
       <c r="E133" t="str">
-        <v/>
+        <v>2026-02-20</v>
       </c>
       <c r="F133" t="str">
-        <v>广东广州</v>
+        <v>荷兰</v>
       </c>
       <c r="G133" t="str">
-        <v/>
+        <v>阿泽</v>
       </c>
       <c r="H133" t="str">
-        <v/>
+        <v>小辫子</v>
       </c>
       <c r="I133" t="str">
-        <v/>
+        <v>驺驺</v>
       </c>
       <c r="J133" t="str">
-        <v/>
+        <v>2026-07-02</v>
       </c>
       <c r="K133" t="str">
         <v/>
       </c>
       <c r="L133" t="str">
-        <v/>
+        <v>2026-07-02</v>
       </c>
       <c r="M133" t="str">
-        <v/>
+        <v>2026-08-03</v>
       </c>
       <c r="N133" t="str">
-        <v/>
+        <v>2026-11-04</v>
       </c>
       <c r="O133" t="str">
-        <v/>
+        <v>2026-08-03 · 血清检测,2026-07-02 · 打疫苗 · assets/diary/zouzou-depart.jpg,2026-07-30 · 6.2斤 · 五个月10天了 · assets/feedback/zouzou-1.jpg</v>
       </c>
       <c r="P133" t="str">
-        <v/>
+        <v>已付定金</v>
       </c>
       <c r="Q133" t="str">
         <v/>
@@ -8249,18 +8249,18 @@
         <v/>
       </c>
       <c r="S133" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B134" t="str">
         <v>弟弟</v>
       </c>
       <c r="C134" t="str">
-        <v>assets/1785854166720-48r17hry9cd.jpeg</v>
+        <v>assets/1785853950207-cedor66ou2q.jpeg</v>
       </c>
       <c r="D134" t="str">
         <v>是</v>
@@ -8269,7 +8269,7 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>山西朔州</v>
+        <v>广东广州</v>
       </c>
       <c r="G134" t="str">
         <v/>
@@ -8313,13 +8313,13 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B135" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C135" t="str">
-        <v>assets/1785854224521-2cpg6xipfn6.jpeg</v>
+        <v>assets/1785854129383-c8qkvl537x.jpeg</v>
       </c>
       <c r="D135" t="str">
         <v>是</v>
@@ -8328,7 +8328,7 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>浙江宁波</v>
+        <v>广东广州</v>
       </c>
       <c r="G135" t="str">
         <v/>
@@ -8378,7 +8378,7 @@
         <v>弟弟</v>
       </c>
       <c r="C136" t="str">
-        <v>assets/1785854260793-steez4s972l.jpeg</v>
+        <v>assets/1785854166720-48r17hry9cd.jpeg</v>
       </c>
       <c r="D136" t="str">
         <v>是</v>
@@ -8387,7 +8387,7 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>陕西西安</v>
+        <v>山西朔州</v>
       </c>
       <c r="G136" t="str">
         <v/>
@@ -8434,10 +8434,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B137" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C137" t="str">
-        <v>assets/1785854319988-cohio08aod5.jpeg</v>
+        <v>assets/1785854224521-2cpg6xipfn6.jpeg</v>
       </c>
       <c r="D137" t="str">
         <v>是</v>
@@ -8446,7 +8446,7 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>黑龙江漠河</v>
+        <v>浙江宁波</v>
       </c>
       <c r="G137" t="str">
         <v/>
@@ -8490,13 +8490,13 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B138" t="str">
         <v>弟弟</v>
       </c>
       <c r="C138" t="str">
-        <v>assets/1785854520974-96b8b1ekqd9.jpeg</v>
+        <v>assets/1785854260793-steez4s972l.jpeg</v>
       </c>
       <c r="D138" t="str">
         <v>是</v>
@@ -8505,7 +8505,7 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>日本</v>
+        <v>陕西西安</v>
       </c>
       <c r="G138" t="str">
         <v/>
@@ -8552,10 +8552,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B139" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C139" t="str">
-        <v>assets/1785854664100-haqoiu1h7hj.jpeg</v>
+        <v>assets/1785854319988-cohio08aod5.jpeg</v>
       </c>
       <c r="D139" t="str">
         <v>是</v>
@@ -8564,7 +8564,7 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>浙江杭州</v>
+        <v>黑龙江漠河</v>
       </c>
       <c r="G139" t="str">
         <v/>
@@ -8608,13 +8608,13 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B140" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C140" t="str">
-        <v>assets/1785854690732-orrs40sx9rs.jpeg</v>
+        <v>assets/1785854520974-96b8b1ekqd9.jpeg</v>
       </c>
       <c r="D140" t="str">
         <v>是</v>
@@ -8623,7 +8623,7 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>贵州安顺</v>
+        <v>日本</v>
       </c>
       <c r="G140" t="str">
         <v/>
@@ -8673,7 +8673,7 @@
         <v>妹妹</v>
       </c>
       <c r="C141" t="str">
-        <v>assets/1785854734122-wcpmib4m7.jpeg</v>
+        <v>assets/1785854664100-haqoiu1h7hj.jpeg</v>
       </c>
       <c r="D141" t="str">
         <v>是</v>
@@ -8682,7 +8682,7 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>山东青岛</v>
+        <v>浙江杭州</v>
       </c>
       <c r="G141" t="str">
         <v/>
@@ -8729,10 +8729,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B142" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C142" t="str">
-        <v>assets/1785854758707-1kxdkfvs6jc.jpeg</v>
+        <v>assets/1785854690732-orrs40sx9rs.jpeg</v>
       </c>
       <c r="D142" t="str">
         <v>是</v>
@@ -8741,7 +8741,7 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>黑龙江漠河</v>
+        <v>贵州安顺</v>
       </c>
       <c r="G142" t="str">
         <v/>
@@ -8785,13 +8785,13 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>纯蓝色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B143" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C143" t="str">
-        <v>assets/1785854784780-3g0u60pdo93.jpeg</v>
+        <v>assets/1785854734122-wcpmib4m7.jpeg</v>
       </c>
       <c r="D143" t="str">
         <v>是</v>
@@ -8800,7 +8800,7 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>河南鹤壁</v>
+        <v>山东青岛</v>
       </c>
       <c r="G143" t="str">
         <v/>
@@ -8850,7 +8850,7 @@
         <v>弟弟</v>
       </c>
       <c r="C144" t="str">
-        <v>assets/1785854813179-8oyxr0h2bbu.jpeg</v>
+        <v>assets/1785854758707-1kxdkfvs6jc.jpeg</v>
       </c>
       <c r="D144" t="str">
         <v>是</v>
@@ -8859,7 +8859,7 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>陕西西安</v>
+        <v>黑龙江漠河</v>
       </c>
       <c r="G144" t="str">
         <v/>
@@ -8903,13 +8903,13 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>棕虎斑</v>
+        <v>纯蓝色</v>
       </c>
       <c r="B145" t="str">
         <v>弟弟</v>
       </c>
       <c r="C145" t="str">
-        <v>assets/1785854838933-uq6amircyzd.jpeg</v>
+        <v>assets/1785854784780-3g0u60pdo93.jpeg</v>
       </c>
       <c r="D145" t="str">
         <v>是</v>
@@ -8918,7 +8918,7 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>四川成都</v>
+        <v>河南鹤壁</v>
       </c>
       <c r="G145" t="str">
         <v/>
@@ -8962,22 +8962,22 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>烟灰色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B146" t="str">
         <v>弟弟</v>
       </c>
       <c r="C146" t="str">
-        <v>assets/1785854869973-za3p6wikqpo.jpeg</v>
+        <v>assets/1785854813179-8oyxr0h2bbu.jpeg</v>
       </c>
       <c r="D146" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E146" t="str">
-        <v>2026-05-18</v>
+        <v/>
       </c>
       <c r="F146" t="str">
-        <v/>
+        <v>陕西西安</v>
       </c>
       <c r="G146" t="str">
         <v/>
@@ -9021,13 +9021,13 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B147" t="str">
         <v>弟弟</v>
       </c>
       <c r="C147" t="str">
-        <v>assets/1785854997023-mawkallt2a.jpeg</v>
+        <v>assets/1785854838933-uq6amircyzd.jpeg</v>
       </c>
       <c r="D147" t="str">
         <v>是</v>
@@ -9036,7 +9036,7 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>新加坡</v>
+        <v>四川成都</v>
       </c>
       <c r="G147" t="str">
         <v/>
@@ -9080,22 +9080,22 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>凯米尔色</v>
+        <v>烟灰色</v>
       </c>
       <c r="B148" t="str">
         <v>弟弟</v>
       </c>
       <c r="C148" t="str">
-        <v>assets/1785855043327-wdc5pxwm34k.jpeg</v>
+        <v>assets/1785854869973-za3p6wikqpo.jpeg</v>
       </c>
       <c r="D148" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E148" t="str">
-        <v/>
+        <v>2026-05-18</v>
       </c>
       <c r="F148" t="str">
-        <v>上海浦东</v>
+        <v/>
       </c>
       <c r="G148" t="str">
         <v/>
@@ -9139,22 +9139,22 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B149" t="str">
         <v>弟弟</v>
       </c>
       <c r="C149" t="str">
-        <v>assets/1785912551260-jplefm937nk.jpeg, assets/videos/02.mp4</v>
+        <v>assets/1785854997023-mawkallt2a.jpeg</v>
       </c>
       <c r="D149" t="str">
         <v>是</v>
       </c>
       <c r="E149" t="str">
-        <v>2026-06-06</v>
+        <v/>
       </c>
       <c r="F149" t="str">
-        <v>浙江温州</v>
+        <v>新加坡</v>
       </c>
       <c r="G149" t="str">
         <v/>
@@ -9198,66 +9198,184 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
+        <v>凯米尔色</v>
+      </c>
+      <c r="B150" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C150" t="str">
+        <v>assets/1785855043327-wdc5pxwm34k.jpeg</v>
+      </c>
+      <c r="D150" t="str">
+        <v>是</v>
+      </c>
+      <c r="E150" t="str">
+        <v/>
+      </c>
+      <c r="F150" t="str">
+        <v>上海浦东</v>
+      </c>
+      <c r="G150" t="str">
+        <v/>
+      </c>
+      <c r="H150" t="str">
+        <v/>
+      </c>
+      <c r="I150" t="str">
+        <v/>
+      </c>
+      <c r="J150" t="str">
+        <v/>
+      </c>
+      <c r="K150" t="str">
+        <v/>
+      </c>
+      <c r="L150" t="str">
+        <v/>
+      </c>
+      <c r="M150" t="str">
+        <v/>
+      </c>
+      <c r="N150" t="str">
+        <v/>
+      </c>
+      <c r="O150" t="str">
+        <v/>
+      </c>
+      <c r="P150" t="str">
+        <v/>
+      </c>
+      <c r="Q150" t="str">
+        <v/>
+      </c>
+      <c r="R150" t="str">
+        <v/>
+      </c>
+      <c r="S150" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
         <v>棕虎斑</v>
       </c>
-      <c r="B150" t="str">
+      <c r="B151" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C151" t="str">
+        <v>assets/1785912551260-jplefm937nk.jpeg, assets/videos/02.mp4</v>
+      </c>
+      <c r="D151" t="str">
+        <v>是</v>
+      </c>
+      <c r="E151" t="str">
+        <v>2026-06-06</v>
+      </c>
+      <c r="F151" t="str">
+        <v>浙江温州</v>
+      </c>
+      <c r="G151" t="str">
+        <v/>
+      </c>
+      <c r="H151" t="str">
+        <v/>
+      </c>
+      <c r="I151" t="str">
+        <v/>
+      </c>
+      <c r="J151" t="str">
+        <v/>
+      </c>
+      <c r="K151" t="str">
+        <v/>
+      </c>
+      <c r="L151" t="str">
+        <v/>
+      </c>
+      <c r="M151" t="str">
+        <v/>
+      </c>
+      <c r="N151" t="str">
+        <v/>
+      </c>
+      <c r="O151" t="str">
+        <v/>
+      </c>
+      <c r="P151" t="str">
+        <v/>
+      </c>
+      <c r="Q151" t="str">
+        <v/>
+      </c>
+      <c r="R151" t="str">
+        <v/>
+      </c>
+      <c r="S151" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>棕虎斑</v>
+      </c>
+      <c r="B152" t="str">
         <v>妹妹</v>
       </c>
-      <c r="C150" t="str">
+      <c r="C152" t="str">
         <v>assets/1785912694000-m20f5kvvrr.jpeg</v>
       </c>
-      <c r="D150" t="str">
-        <v>否</v>
-      </c>
-      <c r="E150" t="str">
+      <c r="D152" t="str">
+        <v>否</v>
+      </c>
+      <c r="E152" t="str">
         <v>2026-06-06</v>
       </c>
-      <c r="F150" t="str">
-        <v/>
-      </c>
-      <c r="G150" t="str">
-        <v/>
-      </c>
-      <c r="H150" t="str">
-        <v/>
-      </c>
-      <c r="I150" t="str">
-        <v/>
-      </c>
-      <c r="J150" t="str">
-        <v/>
-      </c>
-      <c r="K150" t="str">
-        <v/>
-      </c>
-      <c r="L150" t="str">
-        <v/>
-      </c>
-      <c r="M150" t="str">
-        <v/>
-      </c>
-      <c r="N150" t="str">
-        <v/>
-      </c>
-      <c r="O150" t="str">
-        <v/>
-      </c>
-      <c r="P150" t="str">
-        <v/>
-      </c>
-      <c r="Q150" t="str">
-        <v/>
-      </c>
-      <c r="R150" t="str">
-        <v/>
-      </c>
-      <c r="S150" t="str">
+      <c r="F152" t="str">
+        <v/>
+      </c>
+      <c r="G152" t="str">
+        <v/>
+      </c>
+      <c r="H152" t="str">
+        <v/>
+      </c>
+      <c r="I152" t="str">
+        <v/>
+      </c>
+      <c r="J152" t="str">
+        <v/>
+      </c>
+      <c r="K152" t="str">
+        <v/>
+      </c>
+      <c r="L152" t="str">
+        <v/>
+      </c>
+      <c r="M152" t="str">
+        <v/>
+      </c>
+      <c r="N152" t="str">
+        <v/>
+      </c>
+      <c r="O152" t="str">
+        <v/>
+      </c>
+      <c r="P152" t="str">
+        <v/>
+      </c>
+      <c r="Q152" t="str">
+        <v/>
+      </c>
+      <c r="R152" t="str">
+        <v/>
+      </c>
+      <c r="S152" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S150"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S152"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -9528,42 +9528,42 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>如何预订心仪的小猫？</v>
+        <v>小猫的价格范围？</v>
       </c>
       <c r="B2" t="str">
-        <v>通过微信沟通确认小猫后，支付 30% 定金并签订电子合同即完成预订；接猫前一天付清尾款。</v>
+        <v>5000–30000 元不等，具体取决于脸版品相、骨量结构与毛量毛色等综合品相，欢迎微信咨询心仪的小猫。</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>小猫接回家时会附带什么？</v>
+        <v>如何预订心仪的小猫？</v>
       </c>
       <c r="B3" t="str">
-        <v>新家礼包会随小猫一同快递寄出，内含日常用品、猫粮和常用药品；同时提供疫苗与驱虫记录。</v>
+        <v>通过微信沟通确认小猫后，支付 30% 定金并签订电子合同即完成预订；接猫前一天付清尾款。</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>猫舍做了哪些健康保障？</v>
+        <v>小猫接回家时会附带什么？</v>
       </c>
       <c r="B4" t="str">
-        <v>种猫均进行 HCM（肥厚型心肌病）与 PKD（多囊肾）基因检测，幼猫按月龄完成疫苗和驱虫，并提供终身饲养指导。</v>
+        <v>新家礼包会随小猫一同快递寄出，内含日常用品、猫粮和常用药品；同时提供疫苗与驱虫记录。</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>小猫多大可以接回家？</v>
+        <v>猫舍做了哪些健康保障？</v>
       </c>
       <c r="B5" t="str">
-        <v>一般满 3 个月、完成基础疫苗后交付，具体以每只小猫的状态为准。</v>
+        <v>种猫均进行 HCM（肥厚型心肌病）与 PKD（多囊肾）基因检测，幼猫按月龄完成疫苗和驱虫，并提供终身饲养指导。</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>小猫的价格范围？</v>
+        <v>小猫多大可以接回家？</v>
       </c>
       <c r="B6" t="str">
-        <v>5000–30000 元不等，具体取决于脸版品相、骨量结构与毛量毛色，欢迎微信咨询心仪的小猫。</v>
+        <v>一般满 3 个月、完成基础疫苗后交付，具体以每只小猫的状态为准。</v>
       </c>
     </row>
     <row r="7" xml:space="preserve">

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S152"/>
+  <dimension ref="A1:S154"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -466,22 +466,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B2" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C2" t="str">
-        <v>assets/1787328436957-x30od0gw28.jpg</v>
+        <v>assets/1787388322060-uj8bkwqgnv.jpg</v>
       </c>
       <c r="D2" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E2" t="str">
-        <v/>
+        <v>2026-06-06</v>
       </c>
       <c r="F2" t="str">
-        <v>江苏苏州</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -525,22 +525,22 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B3" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C3" t="str">
-        <v>assets/1787328420967-viv9v8nbjn.jpg</v>
+        <v>assets/1787388277490-e6u506cx0r.jpg</v>
       </c>
       <c r="D3" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E3" t="str">
-        <v/>
+        <v>2026-06-06</v>
       </c>
       <c r="F3" t="str">
-        <v>辽宁东港</v>
+        <v/>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -584,13 +584,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B4" t="str">
         <v>弟弟</v>
       </c>
       <c r="C4" t="str">
-        <v>assets/1787327967245-m62ohievcl.jpg</v>
+        <v>assets/1787328436957-x30od0gw28.jpg</v>
       </c>
       <c r="D4" t="str">
         <v>是</v>
@@ -599,7 +599,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>福建福州</v>
+        <v>江苏苏州</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -649,7 +649,7 @@
         <v>弟弟</v>
       </c>
       <c r="C5" t="str">
-        <v>assets/1787327853521-js8ljh3ulj.jpg</v>
+        <v>assets/1787328420967-viv9v8nbjn.jpg</v>
       </c>
       <c r="D5" t="str">
         <v>是</v>
@@ -658,7 +658,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>上海</v>
+        <v>辽宁东港</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -702,13 +702,13 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>纯蓝色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B6" t="str">
         <v>弟弟</v>
       </c>
       <c r="C6" t="str">
-        <v>assets/1787327793837-znk2knoo6p.jpg</v>
+        <v>assets/1787327967245-m62ohievcl.jpg</v>
       </c>
       <c r="D6" t="str">
         <v>是</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>河南鹤壁</v>
+        <v>福建福州</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -761,13 +761,13 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B7" t="str">
         <v>弟弟</v>
       </c>
       <c r="C7" t="str">
-        <v>assets/1787327752832-kkpmp21os3.jpg</v>
+        <v>assets/1787327853521-js8ljh3ulj.jpg</v>
       </c>
       <c r="D7" t="str">
         <v>是</v>
@@ -776,7 +776,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>陕西西安</v>
+        <v>上海</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -820,13 +820,13 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>银虎斑</v>
+        <v>纯蓝色</v>
       </c>
       <c r="B8" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C8" t="str">
-        <v>assets/1787327605711-4o2f6v6ybp.jpg</v>
+        <v>assets/1787327793837-znk2knoo6p.jpg</v>
       </c>
       <c r="D8" t="str">
         <v>是</v>
@@ -835,7 +835,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>陕西西安</v>
+        <v>河南鹤壁</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -885,7 +885,7 @@
         <v>弟弟</v>
       </c>
       <c r="C9" t="str">
-        <v>assets/1787327573762-h23cux94p2.jpg</v>
+        <v>assets/1787327752832-kkpmp21os3.jpg</v>
       </c>
       <c r="D9" t="str">
         <v>是</v>
@@ -894,7 +894,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>北京</v>
+        <v>陕西西安</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -944,7 +944,7 @@
         <v>妹妹</v>
       </c>
       <c r="C10" t="str">
-        <v>assets/1787327496557-9daggljg4g.jpg</v>
+        <v>assets/1787327605711-4o2f6v6ybp.jpg</v>
       </c>
       <c r="D10" t="str">
         <v>是</v>
@@ -953,7 +953,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>黑龙江哈尔滨</v>
+        <v>陕西西安</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -997,13 +997,13 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>烟灰色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B11" t="str">
         <v>弟弟</v>
       </c>
       <c r="C11" t="str">
-        <v>assets/1787327456560-p4yhq4qvrv.jpg</v>
+        <v>assets/1787327573762-h23cux94p2.jpg</v>
       </c>
       <c r="D11" t="str">
         <v>是</v>
@@ -1012,7 +1012,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>甘肃嘉峪关</v>
+        <v>北京</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -1056,13 +1056,13 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>蓝虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B12" t="str">
         <v>妹妹</v>
       </c>
       <c r="C12" t="str">
-        <v>assets/1787327421713-zg7np4yzkc.jpg</v>
+        <v>assets/1787327496557-9daggljg4g.jpg</v>
       </c>
       <c r="D12" t="str">
         <v>是</v>
@@ -1071,7 +1071,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>安徽合肥</v>
+        <v>黑龙江哈尔滨</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -1115,13 +1115,13 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B13" t="str">
         <v>弟弟</v>
       </c>
       <c r="C13" t="str">
-        <v>assets/1787327337811-u5u2pdew3.jpg</v>
+        <v>assets/1787327456560-p4yhq4qvrv.jpg</v>
       </c>
       <c r="D13" t="str">
         <v>是</v>
@@ -1130,7 +1130,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>安徽合肥</v>
+        <v>甘肃嘉峪关</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -1174,13 +1174,13 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>棕虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B14" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C14" t="str">
-        <v>assets/1787327309143-6c1dan1sev.jpg</v>
+        <v>assets/1787327421713-zg7np4yzkc.jpg</v>
       </c>
       <c r="D14" t="str">
         <v>是</v>
@@ -1189,7 +1189,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>四川成都</v>
+        <v>安徽合肥</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -1239,7 +1239,7 @@
         <v>弟弟</v>
       </c>
       <c r="C15" t="str">
-        <v>assets/1787327277453-w89ujg69fm.jpg</v>
+        <v>assets/1787327337811-u5u2pdew3.jpg</v>
       </c>
       <c r="D15" t="str">
         <v>是</v>
@@ -1248,7 +1248,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>四川成都</v>
+        <v>安徽合肥</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -1292,13 +1292,13 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>蓝银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B16" t="str">
         <v>弟弟</v>
       </c>
       <c r="C16" t="str">
-        <v>assets/1787327232159-lkrcl588a5.jpg</v>
+        <v>assets/1787327309143-6c1dan1sev.jpg</v>
       </c>
       <c r="D16" t="str">
         <v>是</v>
@@ -1351,13 +1351,13 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>玳瑁色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B17" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C17" t="str">
-        <v>assets/1787327182347-3az0z7sys2.jpg</v>
+        <v>assets/1787327277453-w89ujg69fm.jpg</v>
       </c>
       <c r="D17" t="str">
         <v>是</v>
@@ -1366,7 +1366,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>四川内江</v>
+        <v>四川成都</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1410,13 +1410,13 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>棕虎补丁</v>
+        <v>蓝银虎斑</v>
       </c>
       <c r="B18" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C18" t="str">
-        <v>assets/1787327143756-4xtgfy5ozu.jpg</v>
+        <v>assets/1787327232159-lkrcl588a5.jpg</v>
       </c>
       <c r="D18" t="str">
         <v>是</v>
@@ -1425,7 +1425,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>贵州贵阳</v>
+        <v>四川成都</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1469,13 +1469,13 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>黑烟色</v>
+        <v>玳瑁色</v>
       </c>
       <c r="B19" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C19" t="str">
-        <v>assets/1787327101790-tqjlseog5y.jpg</v>
+        <v>assets/1787327182347-3az0z7sys2.jpg</v>
       </c>
       <c r="D19" t="str">
         <v>是</v>
@@ -1484,7 +1484,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>浙江杭州</v>
+        <v>四川内江</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1528,13 +1528,13 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>烟灰色</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B20" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C20" t="str">
-        <v>assets/1787327019632-l1780lu2hj.jpg</v>
+        <v>assets/1787327143756-4xtgfy5ozu.jpg</v>
       </c>
       <c r="D20" t="str">
         <v>是</v>
@@ -1543,7 +1543,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>山东威海</v>
+        <v>贵州贵阳</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1587,13 +1587,13 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>棕虎补丁</v>
+        <v>黑烟色</v>
       </c>
       <c r="B21" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C21" t="str">
-        <v>assets/1787326905275-plz3fpgo97.jpg</v>
+        <v>assets/1787327101790-tqjlseog5y.jpg</v>
       </c>
       <c r="D21" t="str">
         <v>是</v>
@@ -1646,13 +1646,13 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>蓝虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B22" t="str">
         <v>弟弟</v>
       </c>
       <c r="C22" t="str">
-        <v>assets/1787326874462-z9rzs7wg17.jpg</v>
+        <v>assets/1787327019632-l1780lu2hj.jpg</v>
       </c>
       <c r="D22" t="str">
         <v>是</v>
@@ -1661,7 +1661,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>四川成都</v>
+        <v>山东威海</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1705,13 +1705,13 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>凯米尔色</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B23" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C23" t="str">
-        <v>assets/1787326843271-0uhv7b9p89.jpg</v>
+        <v>assets/1787326905275-plz3fpgo97.jpg</v>
       </c>
       <c r="D23" t="str">
         <v>是</v>
@@ -1720,7 +1720,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>四川成都</v>
+        <v>浙江杭州</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1764,13 +1764,13 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>凯米尔</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B24" t="str">
         <v>弟弟</v>
       </c>
       <c r="C24" t="str">
-        <v>assets/1787326814713-p5oavnlulg.jpg</v>
+        <v>assets/1787326874462-z9rzs7wg17.jpg</v>
       </c>
       <c r="D24" t="str">
         <v>是</v>
@@ -1823,13 +1823,13 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>棕虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B25" t="str">
         <v>弟弟</v>
       </c>
       <c r="C25" t="str">
-        <v>assets/1787326773577-13q5out2d0.jpg</v>
+        <v>assets/1787326843271-0uhv7b9p89.jpg</v>
       </c>
       <c r="D25" t="str">
         <v>是</v>
@@ -1838,7 +1838,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>四川宜宾</v>
+        <v>四川成都</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1882,13 +1882,13 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>金棕虎斑</v>
+        <v>凯米尔</v>
       </c>
       <c r="B26" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C26" t="str">
-        <v>assets/1787326548993-89s929m2hg.jpg</v>
+        <v>assets/1787326814713-p5oavnlulg.jpg</v>
       </c>
       <c r="D26" t="str">
         <v>是</v>
@@ -1897,7 +1897,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>上海</v>
+        <v>四川成都</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1941,13 +1941,13 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>凯米尔色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B27" t="str">
         <v>弟弟</v>
       </c>
       <c r="C27" t="str">
-        <v>assets/1787326449218-09s9ucram4.jpg</v>
+        <v>assets/1787326773577-13q5out2d0.jpg</v>
       </c>
       <c r="D27" t="str">
         <v>是</v>
@@ -1956,7 +1956,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>德国</v>
+        <v>四川宜宾</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -2000,13 +2000,13 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>棕虎补丁</v>
+        <v>金棕虎斑</v>
       </c>
       <c r="B28" t="str">
         <v>妹妹</v>
       </c>
       <c r="C28" t="str">
-        <v>assets/1787326277374-8ti107m5ki.jpg</v>
+        <v>assets/1787326548993-89s929m2hg.jpg</v>
       </c>
       <c r="D28" t="str">
         <v>是</v>
@@ -2015,7 +2015,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>广东深圳</v>
+        <v>上海</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -2059,13 +2059,13 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>烟灰色</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B29" t="str">
         <v>弟弟</v>
       </c>
       <c r="C29" t="str">
-        <v>assets/1787326236952-2pmwche4t3.jpg</v>
+        <v>assets/1787326449218-09s9ucram4.jpg</v>
       </c>
       <c r="D29" t="str">
         <v>是</v>
@@ -2074,7 +2074,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>福建泉州</v>
+        <v>德国</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -2118,13 +2118,13 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>银虎斑</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B30" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C30" t="str">
-        <v>assets/1787326184557-90v6clkwen.jpg</v>
+        <v>assets/1787326277374-8ti107m5ki.jpg</v>
       </c>
       <c r="D30" t="str">
         <v>是</v>
@@ -2133,7 +2133,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>福建福州</v>
+        <v>广东深圳</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -2177,13 +2177,13 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>棕虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B31" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C31" t="str">
-        <v>assets/1787326046155-4tk23nq4dj.jpg</v>
+        <v>assets/1787326236952-2pmwche4t3.jpg</v>
       </c>
       <c r="D31" t="str">
         <v>是</v>
@@ -2192,7 +2192,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>广西贵港</v>
+        <v>福建泉州</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -2236,13 +2236,13 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>凯米尔色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B32" t="str">
         <v>弟弟</v>
       </c>
       <c r="C32" t="str">
-        <v>assets/1787325862706-wq18k3ej56.jpg</v>
+        <v>assets/1787326184557-90v6clkwen.jpg</v>
       </c>
       <c r="D32" t="str">
         <v>是</v>
@@ -2251,7 +2251,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>江苏苏州</v>
+        <v>福建福州</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -2295,13 +2295,13 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>凯米尔色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B33" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C33" t="str">
-        <v>assets/1787325743258-a7oac7hzlo.jpg</v>
+        <v>assets/1787326046155-4tk23nq4dj.jpg</v>
       </c>
       <c r="D33" t="str">
         <v>是</v>
@@ -2310,7 +2310,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>江苏苏州</v>
+        <v>广西贵港</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -2354,13 +2354,13 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>银虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B34" t="str">
         <v>弟弟</v>
       </c>
       <c r="C34" t="str">
-        <v>assets/1787325706797-kgk81ghccy.jpg</v>
+        <v>assets/1787325862706-wq18k3ej56.jpg</v>
       </c>
       <c r="D34" t="str">
         <v>是</v>
@@ -2369,7 +2369,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>北京</v>
+        <v>江苏苏州</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -2413,13 +2413,13 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>蓝虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B35" t="str">
         <v>弟弟</v>
       </c>
       <c r="C35" t="str">
-        <v>assets/1787325603704-lahzgrm7fa.jpg,assets/1787325690106-wgu3spujit.jpg</v>
+        <v>assets/1787325743258-a7oac7hzlo.jpg</v>
       </c>
       <c r="D35" t="str">
         <v>是</v>
@@ -2428,7 +2428,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>上海</v>
+        <v>江苏苏州</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -2472,13 +2472,13 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B36" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C36" t="str">
-        <v>assets/1787325554341-608thexrne.jpg</v>
+        <v>assets/1787325706797-kgk81ghccy.jpg</v>
       </c>
       <c r="D36" t="str">
         <v>是</v>
@@ -2487,7 +2487,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>江苏苏州</v>
+        <v>北京</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -2531,13 +2531,13 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>浅色银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B37" t="str">
         <v>弟弟</v>
       </c>
       <c r="C37" t="str">
-        <v>assets/1787325480828-q90pskoiw3.jpg</v>
+        <v>assets/1787325603704-lahzgrm7fa.jpg,assets/1787325690106-wgu3spujit.jpg</v>
       </c>
       <c r="D37" t="str">
         <v>是</v>
@@ -2546,7 +2546,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>四川成都</v>
+        <v>上海</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -2590,13 +2590,13 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>浅色银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B38" t="str">
         <v>妹妹</v>
       </c>
       <c r="C38" t="str">
-        <v>assets/1787325448999-a2pg8176fu.jpg</v>
+        <v>assets/1787325554341-608thexrne.jpg</v>
       </c>
       <c r="D38" t="str">
         <v>是</v>
@@ -2605,7 +2605,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>中国台湾</v>
+        <v>江苏苏州</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -2649,13 +2649,13 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>棕虎斑</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B39" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C39" t="str">
-        <v>assets/1787325357634-k55zlfhmqj.jpg</v>
+        <v>assets/1787325480828-q90pskoiw3.jpg</v>
       </c>
       <c r="D39" t="str">
         <v>是</v>
@@ -2664,7 +2664,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>浙江杭州</v>
+        <v>四川成都</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -2708,13 +2708,13 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>烟灰色</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B40" t="str">
         <v>妹妹</v>
       </c>
       <c r="C40" t="str">
-        <v>assets/1787325237876-t19isaq5gu.jpg</v>
+        <v>assets/1787325448999-a2pg8176fu.jpg</v>
       </c>
       <c r="D40" t="str">
         <v>是</v>
@@ -2723,7 +2723,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>辽宁沈阳</v>
+        <v>中国台湾</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -2767,13 +2767,13 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>金棕虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B41" t="str">
         <v>妹妹</v>
       </c>
       <c r="C41" t="str">
-        <v>assets/1787325199931-e7wms9qtya.jpg</v>
+        <v>assets/1787325357634-k55zlfhmqj.jpg</v>
       </c>
       <c r="D41" t="str">
         <v>是</v>
@@ -2782,7 +2782,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>四川成都</v>
+        <v>浙江杭州</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -2826,13 +2826,13 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>蓝虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B42" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C42" t="str">
-        <v>assets/1787325172354-4sa8uzaey2.jpg</v>
+        <v>assets/1787325237876-t19isaq5gu.jpg</v>
       </c>
       <c r="D42" t="str">
         <v>是</v>
@@ -2841,7 +2841,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>中国香港</v>
+        <v>辽宁沈阳</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -2885,13 +2885,13 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>烟灰色</v>
+        <v>金棕虎斑</v>
       </c>
       <c r="B43" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C43" t="str">
-        <v>assets/1787325109283-y7mvkk6qg4.jpg</v>
+        <v>assets/1787325199931-e7wms9qtya.jpg</v>
       </c>
       <c r="D43" t="str">
         <v>是</v>
@@ -2900,7 +2900,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>中国澳门</v>
+        <v>四川成都</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2950,7 +2950,7 @@
         <v>弟弟</v>
       </c>
       <c r="C44" t="str">
-        <v>assets/1787325033629-y3ygps3zaj.jpg</v>
+        <v>assets/1787325172354-4sa8uzaey2.jpg</v>
       </c>
       <c r="D44" t="str">
         <v>是</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>山东青岛</v>
+        <v>中国香港</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -3009,7 +3009,7 @@
         <v>弟弟</v>
       </c>
       <c r="C45" t="str">
-        <v>assets/1787324954998-w5m5jox439.jpg</v>
+        <v>assets/1787325109283-y7mvkk6qg4.jpg</v>
       </c>
       <c r="D45" t="str">
         <v>是</v>
@@ -3018,7 +3018,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>海南海口</v>
+        <v>中国澳门</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -3062,13 +3062,13 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>棕虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B46" t="str">
         <v>弟弟</v>
       </c>
       <c r="C46" t="str">
-        <v>assets/1787324905909-zrz8o79kdf.jpg</v>
+        <v>assets/1787325033629-y3ygps3zaj.jpg</v>
       </c>
       <c r="D46" t="str">
         <v>是</v>
@@ -3077,7 +3077,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>内蒙古</v>
+        <v>山东青岛</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -3127,7 +3127,7 @@
         <v>弟弟</v>
       </c>
       <c r="C47" t="str">
-        <v>assets/1787324880505-gbh0sn7b6j.jpg</v>
+        <v>assets/1787324954998-w5m5jox439.jpg</v>
       </c>
       <c r="D47" t="str">
         <v>是</v>
@@ -3136,7 +3136,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>中国香港</v>
+        <v>海南海口</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -3180,13 +3180,13 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B48" t="str">
         <v>弟弟</v>
       </c>
       <c r="C48" t="str">
-        <v>assets/1787324806613-31yyz14tsf.jpg</v>
+        <v>assets/1787324905909-zrz8o79kdf.jpg</v>
       </c>
       <c r="D48" t="str">
         <v>是</v>
@@ -3195,7 +3195,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>四川成都</v>
+        <v>内蒙古</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -3239,13 +3239,13 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>红虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B49" t="str">
         <v>弟弟</v>
       </c>
       <c r="C49" t="str">
-        <v>assets/1787324789658-uz6ephkdsh.jpg</v>
+        <v>assets/1787324880505-gbh0sn7b6j.jpg</v>
       </c>
       <c r="D49" t="str">
         <v>是</v>
@@ -3254,7 +3254,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>湖北武汉</v>
+        <v>中国香港</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -3304,7 +3304,7 @@
         <v>弟弟</v>
       </c>
       <c r="C50" t="str">
-        <v>assets/1787324522658-smn44crast.jpg</v>
+        <v>assets/1787324806613-31yyz14tsf.jpg</v>
       </c>
       <c r="D50" t="str">
         <v>是</v>
@@ -3313,7 +3313,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>湖北武汉</v>
+        <v>四川成都</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -3357,13 +3357,13 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>棕虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B51" t="str">
         <v>弟弟</v>
       </c>
       <c r="C51" t="str">
-        <v>assets/1787324365608-6xtrjp7euz.jpg</v>
+        <v>assets/1787324789658-uz6ephkdsh.jpg</v>
       </c>
       <c r="D51" t="str">
         <v>是</v>
@@ -3372,7 +3372,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>新疆</v>
+        <v>湖北武汉</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -3416,13 +3416,13 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>浅凯米尔</v>
+        <v>烟灰色</v>
       </c>
       <c r="B52" t="str">
         <v>弟弟</v>
       </c>
       <c r="C52" t="str">
-        <v>assets/1787324331029-d74lcuycf6.jpg</v>
+        <v>assets/1787324522658-smn44crast.jpg</v>
       </c>
       <c r="D52" t="str">
         <v>是</v>
@@ -3431,7 +3431,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>四川成都</v>
+        <v>湖北武汉</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -3475,13 +3475,13 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>红虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B53" t="str">
         <v>弟弟</v>
       </c>
       <c r="C53" t="str">
-        <v>assets/1787324297469-ans1lse2l5.jpg</v>
+        <v>assets/1787324365608-6xtrjp7euz.jpg</v>
       </c>
       <c r="D53" t="str">
         <v>是</v>
@@ -3490,7 +3490,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>四川乐山</v>
+        <v>新疆</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -3534,13 +3534,13 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>红虎斑</v>
+        <v>浅凯米尔</v>
       </c>
       <c r="B54" t="str">
         <v>弟弟</v>
       </c>
       <c r="C54" t="str">
-        <v>assets/1787324256827-7w383z4bg1.jpg</v>
+        <v>assets/1787324331029-d74lcuycf6.jpg</v>
       </c>
       <c r="D54" t="str">
         <v>是</v>
@@ -3549,7 +3549,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>中国台湾</v>
+        <v>四川成都</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -3593,13 +3593,13 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B55" t="str">
         <v>弟弟</v>
       </c>
       <c r="C55" t="str">
-        <v>assets/1787324228262-y3vwn6i4zk.jpg</v>
+        <v>assets/1787324297469-ans1lse2l5.jpg</v>
       </c>
       <c r="D55" t="str">
         <v>是</v>
@@ -3608,7 +3608,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>四川成都</v>
+        <v>四川乐山</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -3652,13 +3652,13 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>凯米尔色</v>
+        <v>红虎斑</v>
       </c>
       <c r="B56" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C56" t="str">
-        <v>assets/1787324201418-9tk4ik75mo.jpg</v>
+        <v>assets/1787324256827-7w383z4bg1.jpg</v>
       </c>
       <c r="D56" t="str">
         <v>是</v>
@@ -3667,7 +3667,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>江苏南京</v>
+        <v>中国台湾</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -3711,13 +3711,13 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B57" t="str">
         <v>弟弟</v>
       </c>
       <c r="C57" t="str">
-        <v>assets/1787324092513-jpa2rmkci2.jpg</v>
+        <v>assets/1787324228262-y3vwn6i4zk.jpg</v>
       </c>
       <c r="D57" t="str">
         <v>是</v>
@@ -3726,7 +3726,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>江苏南京</v>
+        <v>四川成都</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -3770,13 +3770,13 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>银虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B58" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C58" t="str">
-        <v>assets/1787323318612-soge38hpsf.jpg</v>
+        <v>assets/1787324201418-9tk4ik75mo.jpg</v>
       </c>
       <c r="D58" t="str">
         <v>是</v>
@@ -3785,7 +3785,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>上海</v>
+        <v>江苏南京</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -3835,7 +3835,7 @@
         <v>弟弟</v>
       </c>
       <c r="C59" t="str">
-        <v>assets/1787323235892-7yq8ioq01e.jpg</v>
+        <v>assets/1787324092513-jpa2rmkci2.jpg</v>
       </c>
       <c r="D59" t="str">
         <v>是</v>
@@ -3844,7 +3844,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>四川成都</v>
+        <v>江苏南京</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -3891,10 +3891,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B60" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C60" t="str">
-        <v>assets/1787322988096-6e2f54q7vo.jpg</v>
+        <v>assets/1787323318612-soge38hpsf.jpg</v>
       </c>
       <c r="D60" t="str">
         <v>是</v>
@@ -3903,7 +3903,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>浙江宁波</v>
+        <v>上海</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -3947,13 +3947,13 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>银虎斑补丁</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B61" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C61" t="str">
-        <v>assets/1787322938518-85ev8bs2k5.jpg</v>
+        <v>assets/1787323235892-7yq8ioq01e.jpg</v>
       </c>
       <c r="D61" t="str">
         <v>是</v>
@@ -3962,7 +3962,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>马来西亚</v>
+        <v>四川成都</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -4009,10 +4009,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B62" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C62" t="str">
-        <v>assets/1787322881183-tzu9xtw2sg.jpg</v>
+        <v>assets/1787322988096-6e2f54q7vo.jpg</v>
       </c>
       <c r="D62" t="str">
         <v>是</v>
@@ -4021,7 +4021,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>陕西西安</v>
+        <v>浙江宁波</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -4065,13 +4065,13 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>纯黑色</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B63" t="str">
         <v>妹妹</v>
       </c>
       <c r="C63" t="str">
-        <v>assets/1787322840098-nhy4jjyx7k.jpg</v>
+        <v>assets/1787322938518-85ev8bs2k5.jpg</v>
       </c>
       <c r="D63" t="str">
         <v>是</v>
@@ -4080,7 +4080,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>广西南宁</v>
+        <v>马来西亚</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -4124,13 +4124,13 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B64" t="str">
         <v>弟弟</v>
       </c>
       <c r="C64" t="str">
-        <v>assets/1787322760950-gn3qgego4s.jpg</v>
+        <v>assets/1787322881183-tzu9xtw2sg.jpg</v>
       </c>
       <c r="D64" t="str">
         <v>是</v>
@@ -4139,7 +4139,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>广西南宁</v>
+        <v>陕西西安</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -4183,13 +4183,13 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>红虎斑</v>
+        <v>纯黑色</v>
       </c>
       <c r="B65" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C65" t="str">
-        <v>assets/1787322605982-04n50xegt2.jpg</v>
+        <v>assets/1787322840098-nhy4jjyx7k.jpg</v>
       </c>
       <c r="D65" t="str">
         <v>是</v>
@@ -4198,7 +4198,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>上海</v>
+        <v>广西南宁</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -4242,13 +4242,13 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B66" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C66" t="str">
-        <v>assets/1787322490045-kog3ru43dy.jpg</v>
+        <v>assets/1787322760950-gn3qgego4s.jpg</v>
       </c>
       <c r="D66" t="str">
         <v>是</v>
@@ -4257,7 +4257,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>上海</v>
+        <v>广西南宁</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -4307,7 +4307,7 @@
         <v>弟弟</v>
       </c>
       <c r="C67" t="str">
-        <v>assets/1787322419996-0m33yx89nm.jpg</v>
+        <v>assets/1787322605982-04n50xegt2.jpg</v>
       </c>
       <c r="D67" t="str">
         <v>是</v>
@@ -4316,7 +4316,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>广东广州</v>
+        <v>上海</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -4360,13 +4360,13 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>浅色银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B68" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C68" t="str">
-        <v>assets/1787322377730-vj5csj2mll.jpg</v>
+        <v>assets/1787322490045-kog3ru43dy.jpg</v>
       </c>
       <c r="D68" t="str">
         <v>是</v>
@@ -4375,7 +4375,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>柬埔寨</v>
+        <v>上海</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -4419,13 +4419,13 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>蓝虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B69" t="str">
         <v>弟弟</v>
       </c>
       <c r="C69" t="str">
-        <v>assets/1787322269611-53yaj5ideu.jpg</v>
+        <v>assets/1787322419996-0m33yx89nm.jpg</v>
       </c>
       <c r="D69" t="str">
         <v>是</v>
@@ -4434,7 +4434,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>山东枣庄</v>
+        <v>广东广州</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -4478,13 +4478,13 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>银虎斑</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B70" t="str">
         <v>弟弟</v>
       </c>
       <c r="C70" t="str">
-        <v>assets/1787321989528-7d6liuhuk9.jpg</v>
+        <v>assets/1787322377730-vj5csj2mll.jpg</v>
       </c>
       <c r="D70" t="str">
         <v>是</v>
@@ -4493,7 +4493,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>陕西西安</v>
+        <v>柬埔寨</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -4537,13 +4537,13 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B71" t="str">
         <v>弟弟</v>
       </c>
       <c r="C71" t="str">
-        <v>assets/1787321941642-xlrc1no2ua.jpg</v>
+        <v>assets/1787322269611-53yaj5ideu.jpg</v>
       </c>
       <c r="D71" t="str">
         <v>是</v>
@@ -4552,7 +4552,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>山东东营</v>
+        <v>山东枣庄</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -4596,13 +4596,13 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>凯米尔色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B72" t="str">
         <v>弟弟</v>
       </c>
       <c r="C72" t="str">
-        <v>assets/1787321903535-6orj7qcgzn.jpg</v>
+        <v>assets/1787321989528-7d6liuhuk9.jpg</v>
       </c>
       <c r="D72" t="str">
         <v>是</v>
@@ -4611,7 +4611,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>中国台湾</v>
+        <v>陕西西安</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -4655,13 +4655,13 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>烟灰色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B73" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C73" t="str">
-        <v>assets/1787321858985-v4qej7cq7g.jpg</v>
+        <v>assets/1787321941642-xlrc1no2ua.jpg</v>
       </c>
       <c r="D73" t="str">
         <v>是</v>
@@ -4670,7 +4670,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>中国台湾</v>
+        <v>山东东营</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -4714,13 +4714,13 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>银虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B74" t="str">
         <v>弟弟</v>
       </c>
       <c r="C74" t="str">
-        <v>assets/1787321834306-efgnyhujon.jpg</v>
+        <v>assets/1787321903535-6orj7qcgzn.jpg</v>
       </c>
       <c r="D74" t="str">
         <v>是</v>
@@ -4729,7 +4729,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>北京</v>
+        <v>中国台湾</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -4773,13 +4773,13 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B75" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C75" t="str">
-        <v>assets/1787321439916-uttgpbkogb.jpg</v>
+        <v>assets/1787321858985-v4qej7cq7g.jpg</v>
       </c>
       <c r="D75" t="str">
         <v>是</v>
@@ -4788,7 +4788,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>安徽合肥</v>
+        <v>中国台湾</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -4838,7 +4838,7 @@
         <v>弟弟</v>
       </c>
       <c r="C76" t="str">
-        <v>assets/1787321419210-51hhgurygq.jpg</v>
+        <v>assets/1787321834306-efgnyhujon.jpg</v>
       </c>
       <c r="D76" t="str">
         <v>是</v>
@@ -4847,7 +4847,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>上海</v>
+        <v>北京</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -4891,13 +4891,13 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>凯米尔色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B77" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C77" t="str">
-        <v>assets/1787321363369-bzjn51j5il.jpg</v>
+        <v>assets/1787321439916-uttgpbkogb.jpg</v>
       </c>
       <c r="D77" t="str">
         <v>是</v>
@@ -4906,7 +4906,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>中国台湾</v>
+        <v>安徽合肥</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -4950,13 +4950,13 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B78" t="str">
         <v>弟弟</v>
       </c>
       <c r="C78" t="str">
-        <v>assets/1787321332559-87p6spuch3.jpg</v>
+        <v>assets/1787321419210-51hhgurygq.jpg</v>
       </c>
       <c r="D78" t="str">
         <v>是</v>
@@ -4965,7 +4965,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>中国台湾</v>
+        <v>上海</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -5009,13 +5009,13 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>棕虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B79" t="str">
         <v>妹妹</v>
       </c>
       <c r="C79" t="str">
-        <v>assets/1787321232531-59lnzv8y98.jpg</v>
+        <v>assets/1787321363369-bzjn51j5il.jpg</v>
       </c>
       <c r="D79" t="str">
         <v>是</v>
@@ -5024,7 +5024,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>北京</v>
+        <v>中国台湾</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -5068,13 +5068,13 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B80" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C80" t="str">
-        <v>assets/1787319975814-g1pfa56vfp.jpg</v>
+        <v>assets/1787321332559-87p6spuch3.jpg</v>
       </c>
       <c r="D80" t="str">
         <v>是</v>
@@ -5083,7 +5083,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>浙江宁波</v>
+        <v>中国台湾</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -5127,13 +5127,13 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B81" t="str">
         <v>妹妹</v>
       </c>
       <c r="C81" t="str">
-        <v>assets/1787319800704-v3qeu062ak.jpg</v>
+        <v>assets/1787321232531-59lnzv8y98.jpg</v>
       </c>
       <c r="D81" t="str">
         <v>是</v>
@@ -5142,7 +5142,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>河北唐山</v>
+        <v>北京</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -5192,7 +5192,7 @@
         <v>妹妹</v>
       </c>
       <c r="C82" t="str">
-        <v>assets/1787319745369-zn66xr3bvb.jpg</v>
+        <v>assets/1787319975814-g1pfa56vfp.jpg</v>
       </c>
       <c r="D82" t="str">
         <v>是</v>
@@ -5201,7 +5201,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>河北石家庄</v>
+        <v>浙江宁波</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -5245,13 +5245,13 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>棕虎补丁</v>
+        <v>银虎斑</v>
       </c>
       <c r="B83" t="str">
         <v>妹妹</v>
       </c>
       <c r="C83" t="str">
-        <v>assets/1787319547969-zqlq35fxxt.jpg</v>
+        <v>assets/1787319800704-v3qeu062ak.jpg</v>
       </c>
       <c r="D83" t="str">
         <v>是</v>
@@ -5260,7 +5260,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>韩国</v>
+        <v>河北唐山</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -5304,13 +5304,13 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>蓝银虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B84" t="str">
         <v>妹妹</v>
       </c>
       <c r="C84" t="str">
-        <v>assets/1787319501376-xscwljnu1j.jpg</v>
+        <v>assets/1787319745369-zn66xr3bvb.jpg</v>
       </c>
       <c r="D84" t="str">
         <v>是</v>
@@ -5319,7 +5319,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>美国</v>
+        <v>河北石家庄</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -5363,13 +5363,13 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>棕虎斑</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B85" t="str">
         <v>妹妹</v>
       </c>
       <c r="C85" t="str">
-        <v>assets/1787319443529-4a0zqikufx.jpg</v>
+        <v>assets/1787319547969-zqlq35fxxt.jpg</v>
       </c>
       <c r="D85" t="str">
         <v>是</v>
@@ -5378,7 +5378,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>中国台湾</v>
+        <v>韩国</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -5422,13 +5422,13 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>蓝虎斑</v>
+        <v>蓝银虎斑</v>
       </c>
       <c r="B86" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C86" t="str">
-        <v>assets/1787319356194-lr2d5680i9.jpg</v>
+        <v>assets/1787319501376-xscwljnu1j.jpg</v>
       </c>
       <c r="D86" t="str">
         <v>是</v>
@@ -5437,7 +5437,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>中国台湾</v>
+        <v>美国</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -5487,7 +5487,7 @@
         <v>妹妹</v>
       </c>
       <c r="C87" t="str">
-        <v>assets/1787319208828-aizqo4blcv.jpg</v>
+        <v>assets/1787319443529-4a0zqikufx.jpg</v>
       </c>
       <c r="D87" t="str">
         <v>是</v>
@@ -5496,7 +5496,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>山东淄博</v>
+        <v>中国台湾</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -5540,13 +5540,13 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B88" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C88" t="str">
-        <v>assets/1787319162970-cc2v8ovnni.jpg</v>
+        <v>assets/1787319356194-lr2d5680i9.jpg</v>
       </c>
       <c r="D88" t="str">
         <v>是</v>
@@ -5555,7 +5555,7 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>韩国</v>
+        <v>中国台湾</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -5599,13 +5599,13 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>棕虎补丁</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B89" t="str">
         <v>妹妹</v>
       </c>
       <c r="C89" t="str">
-        <v>assets/1787319098214-8pwa9yx2wc.jpg</v>
+        <v>assets/1787319208828-aizqo4blcv.jpg</v>
       </c>
       <c r="D89" t="str">
         <v>是</v>
@@ -5614,7 +5614,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>四川成都</v>
+        <v>山东淄博</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -5661,10 +5661,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B90" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C90" t="str">
-        <v>assets/1787318867999-3gxdddp72x.jpg</v>
+        <v>assets/1787319162970-cc2v8ovnni.jpg</v>
       </c>
       <c r="D90" t="str">
         <v>是</v>
@@ -5673,7 +5673,7 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>广东广州</v>
+        <v>韩国</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -5717,13 +5717,13 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>银虎斑</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B91" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C91" t="str">
-        <v>assets/1787318609722-0ojb3aikwi.jpg</v>
+        <v>assets/1787319098214-8pwa9yx2wc.jpg</v>
       </c>
       <c r="D91" t="str">
         <v>是</v>
@@ -5732,7 +5732,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>黑龙江鹤岗</v>
+        <v>四川成都</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -5776,13 +5776,13 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>蓝虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B92" t="str">
         <v>弟弟</v>
       </c>
       <c r="C92" t="str">
-        <v>assets/1787318530612-779fbkfcoi.jpg</v>
+        <v>assets/1787318867999-3gxdddp72x.jpg</v>
       </c>
       <c r="D92" t="str">
         <v>是</v>
@@ -5791,7 +5791,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>天津</v>
+        <v>广东广州</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -5841,7 +5841,7 @@
         <v>弟弟</v>
       </c>
       <c r="C93" t="str">
-        <v>assets/1787318365475-sj87wtsai3.jpg</v>
+        <v>assets/1787318609722-0ojb3aikwi.jpg</v>
       </c>
       <c r="D93" t="str">
         <v>是</v>
@@ -5850,7 +5850,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>山西朔州</v>
+        <v>黑龙江鹤岗</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -5880,7 +5880,7 @@
         <v/>
       </c>
       <c r="P93" t="str">
-        <v>已接猫</v>
+        <v/>
       </c>
       <c r="Q93" t="str">
         <v/>
@@ -5894,13 +5894,13 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B94" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C94" t="str">
-        <v>assets/1787318326155-ia4noopjhq.jpg</v>
+        <v>assets/1787318530612-779fbkfcoi.jpg</v>
       </c>
       <c r="D94" t="str">
         <v>是</v>
@@ -5909,7 +5909,7 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>贵州</v>
+        <v>天津</v>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -5953,22 +5953,22 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B95" t="str">
         <v>弟弟</v>
       </c>
       <c r="C95" t="str">
-        <v>assets/1787304479674-w0trechn4p.jpg</v>
+        <v>assets/1787318365475-sj87wtsai3.jpg</v>
       </c>
       <c r="D95" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E95" t="str">
-        <v>2026-06-06</v>
+        <v/>
       </c>
       <c r="F95" t="str">
-        <v/>
+        <v>山西朔州</v>
       </c>
       <c r="G95" t="str">
         <v/>
@@ -5998,7 +5998,7 @@
         <v/>
       </c>
       <c r="P95" t="str">
-        <v/>
+        <v>已接猫</v>
       </c>
       <c r="Q95" t="str">
         <v/>
@@ -6007,27 +6007,27 @@
         <v/>
       </c>
       <c r="S95" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>纯黑色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B96" t="str">
         <v>妹妹</v>
       </c>
       <c r="C96" t="str">
-        <v>assets/1787283819124-4v7d1w01la.jpg</v>
+        <v>assets/1787318326155-ia4noopjhq.jpg</v>
       </c>
       <c r="D96" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E96" t="str">
-        <v>2026-02-20</v>
+        <v/>
       </c>
       <c r="F96" t="str">
-        <v/>
+        <v>贵州</v>
       </c>
       <c r="G96" t="str">
         <v/>
@@ -6066,24 +6066,24 @@
         <v/>
       </c>
       <c r="S96" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>阴影色NS12</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B97" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C97" t="str">
-        <v>assets/1787283212708-jdnyi6ecci.jpg</v>
+        <v>assets/1787304479674-w0trechn4p.jpg</v>
       </c>
       <c r="D97" t="str">
         <v>否</v>
       </c>
       <c r="E97" t="str">
-        <v>2026-05-28</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F97" t="str">
         <v/>
@@ -6130,22 +6130,22 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>阴影色NS11</v>
+        <v>纯黑色</v>
       </c>
       <c r="B98" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C98" t="str">
-        <v>assets/1787283153501-s2tjg9spwu.jpg</v>
+        <v>assets/1787283819124-4v7d1w01la.jpg</v>
       </c>
       <c r="D98" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E98" t="str">
-        <v>2026-06-15</v>
+        <v>2026-02-20</v>
       </c>
       <c r="F98" t="str">
-        <v>重庆</v>
+        <v/>
       </c>
       <c r="G98" t="str">
         <v/>
@@ -6189,19 +6189,19 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>浅烟灰色</v>
+        <v>阴影色NS12</v>
       </c>
       <c r="B99" t="str">
         <v>妹妹</v>
       </c>
       <c r="C99" t="str">
-        <v>assets/1787283092677-i4d8tyrjtf.jpg</v>
+        <v>assets/1787283212708-jdnyi6ecci.jpg</v>
       </c>
       <c r="D99" t="str">
         <v>否</v>
       </c>
       <c r="E99" t="str">
-        <v>2026-03-21</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F99" t="str">
         <v/>
@@ -6248,22 +6248,22 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>棕虎斑</v>
+        <v>阴影色NS11</v>
       </c>
       <c r="B100" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C100" t="str">
-        <v>assets/1787283031104-bpyq9wy2tl.jpg</v>
+        <v>assets/1787283153501-s2tjg9spwu.jpg</v>
       </c>
       <c r="D100" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E100" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F100" t="str">
-        <v/>
+        <v>重庆</v>
       </c>
       <c r="G100" t="str">
         <v/>
@@ -6307,19 +6307,19 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>棕虎斑</v>
+        <v>浅烟灰色</v>
       </c>
       <c r="B101" t="str">
         <v>妹妹</v>
       </c>
       <c r="C101" t="str">
-        <v>assets/1787282991501-2fjfws0rqw.jpg</v>
+        <v>assets/1787283092677-i4d8tyrjtf.jpg</v>
       </c>
       <c r="D101" t="str">
         <v>否</v>
       </c>
       <c r="E101" t="str">
-        <v>2026-06-06</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F101" t="str">
         <v/>
@@ -6372,13 +6372,13 @@
         <v>妹妹</v>
       </c>
       <c r="C102" t="str">
-        <v>assets/1787282942262-syr48fym6c.jpg</v>
+        <v>assets/1787283031104-bpyq9wy2tl.jpg</v>
       </c>
       <c r="D102" t="str">
         <v>否</v>
       </c>
       <c r="E102" t="str">
-        <v>2026-06-15</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F102" t="str">
         <v/>
@@ -6428,10 +6428,10 @@
         <v>棕虎斑</v>
       </c>
       <c r="B103" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C103" t="str">
-        <v>assets/1787282819855-7vhx3m0v40.jpg</v>
+        <v>assets/1787282991501-2fjfws0rqw.jpg</v>
       </c>
       <c r="D103" t="str">
         <v>否</v>
@@ -6490,13 +6490,13 @@
         <v>妹妹</v>
       </c>
       <c r="C104" t="str">
-        <v>assets/1787282703381-2uakw592b4.jpg</v>
+        <v>assets/1787282942262-syr48fym6c.jpg</v>
       </c>
       <c r="D104" t="str">
         <v>否</v>
       </c>
       <c r="E104" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F104" t="str">
         <v/>
@@ -6543,13 +6543,13 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B105" t="str">
         <v>弟弟</v>
       </c>
       <c r="C105" t="str">
-        <v>assets/1787282649397-9hc31ncrpc.jpg</v>
+        <v>assets/1787282819855-7vhx3m0v40.jpg</v>
       </c>
       <c r="D105" t="str">
         <v>否</v>
@@ -6602,13 +6602,13 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B106" t="str">
         <v>妹妹</v>
       </c>
       <c r="C106" t="str">
-        <v>assets/1787282617957-svcoyyznpg.jpg</v>
+        <v>assets/1787282703381-2uakw592b4.jpg</v>
       </c>
       <c r="D106" t="str">
         <v>否</v>
@@ -6667,7 +6667,7 @@
         <v>弟弟</v>
       </c>
       <c r="C107" t="str">
-        <v>assets/1787282419632-78nixqjzua.jpg</v>
+        <v>assets/1787282649397-9hc31ncrpc.jpg</v>
       </c>
       <c r="D107" t="str">
         <v>否</v>
@@ -6720,19 +6720,19 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>纯黑色</v>
+        <v>烟灰色</v>
       </c>
       <c r="B108" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C108" t="str">
-        <v>assets/1787282349942-2cfuyn7xlc.jpg</v>
+        <v>assets/1787282617957-svcoyyznpg.jpg</v>
       </c>
       <c r="D108" t="str">
         <v>否</v>
       </c>
       <c r="E108" t="str">
-        <v>2026-03-21</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F108" t="str">
         <v/>
@@ -6779,19 +6779,19 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B109" t="str">
         <v>弟弟</v>
       </c>
       <c r="C109" t="str">
-        <v>assets/1787282064159-6b4z8c5msd.jpg</v>
+        <v>assets/1787282419632-78nixqjzua.jpg</v>
       </c>
       <c r="D109" t="str">
         <v>否</v>
       </c>
       <c r="E109" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F109" t="str">
         <v/>
@@ -6838,19 +6838,19 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>阴影色NS11</v>
+        <v>纯黑色</v>
       </c>
       <c r="B110" t="str">
         <v>弟弟</v>
       </c>
       <c r="C110" t="str">
-        <v>assets/1787280590041-vzcwebdok1.jpg</v>
+        <v>assets/1787282349942-2cfuyn7xlc.jpg</v>
       </c>
       <c r="D110" t="str">
         <v>否</v>
       </c>
       <c r="E110" t="str">
-        <v>2026-05-28</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F110" t="str">
         <v/>
@@ -6897,19 +6897,19 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>浅色银虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B111" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C111" t="str">
-        <v>assets/1787281786169-9ia0h837ct.jpg</v>
+        <v>assets/1787282064159-6b4z8c5msd.jpg</v>
       </c>
       <c r="D111" t="str">
         <v>否</v>
       </c>
       <c r="E111" t="str">
-        <v>2026-06-15</v>
+        <v>2026-06-10</v>
       </c>
       <c r="F111" t="str">
         <v/>
@@ -6956,22 +6956,22 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>浅烟灰色</v>
+        <v>阴影色NS11</v>
       </c>
       <c r="B112" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C112" t="str">
-        <v>assets/1785843720843-63qz159daui.jpg</v>
+        <v>assets/1787280590041-vzcwebdok1.jpg</v>
       </c>
       <c r="D112" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E112" t="str">
-        <v>2026-03-21</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F112" t="str">
-        <v>四川成都</v>
+        <v/>
       </c>
       <c r="G112" t="str">
         <v/>
@@ -7015,22 +7015,22 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>凯米尔色</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B113" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C113" t="str">
-        <v>assets/1787301984056-iu6afro5z5.jpg, assets/1785843763310-elg05ur61ri.jpg</v>
+        <v>assets/1787281786169-9ia0h837ct.jpg</v>
       </c>
       <c r="D113" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E113" t="str">
-        <v>2026-02-14</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F113" t="str">
-        <v>上海浦东</v>
+        <v/>
       </c>
       <c r="G113" t="str">
         <v/>
@@ -7074,22 +7074,22 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>银虎斑补丁</v>
+        <v>浅烟灰色</v>
       </c>
       <c r="B114" t="str">
         <v>妹妹</v>
       </c>
       <c r="C114" t="str">
-        <v>assets/1785843820715-9kz7gy4mbr7.jpg</v>
+        <v>assets/1785843720843-63qz159daui.jpg</v>
       </c>
       <c r="D114" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E114" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F114" t="str">
-        <v/>
+        <v>四川成都</v>
       </c>
       <c r="G114" t="str">
         <v/>
@@ -7133,22 +7133,22 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>烟灰色</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B115" t="str">
         <v>弟弟</v>
       </c>
       <c r="C115" t="str">
-        <v>assets/1785843953805-mxl3x1982io.jpg</v>
+        <v>assets/1787301984056-iu6afro5z5.jpg, assets/1785843763310-elg05ur61ri.jpg</v>
       </c>
       <c r="D115" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E115" t="str">
-        <v>2026-05-18</v>
+        <v>2026-02-14</v>
       </c>
       <c r="F115" t="str">
-        <v/>
+        <v>上海浦东</v>
       </c>
       <c r="G115" t="str">
         <v/>
@@ -7192,19 +7192,19 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>棕虎斑玳瑁</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B116" t="str">
         <v>妹妹</v>
       </c>
       <c r="C116" t="str">
-        <v>assets/1785844013835-ek4xpcje7kh.jpg</v>
+        <v>assets/1785843820715-9kz7gy4mbr7.jpg</v>
       </c>
       <c r="D116" t="str">
         <v>否</v>
       </c>
       <c r="E116" t="str">
-        <v>2026-02-14</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F116" t="str">
         <v/>
@@ -7251,19 +7251,19 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>银虎斑补丁</v>
+        <v>烟灰色</v>
       </c>
       <c r="B117" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C117" t="str">
-        <v>assets/1785844434338-ek5zbdgdcne.jpg</v>
+        <v>assets/1785843953805-mxl3x1982io.jpg</v>
       </c>
       <c r="D117" t="str">
         <v>否</v>
       </c>
       <c r="E117" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F117" t="str">
         <v/>
@@ -7310,22 +7310,22 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑玳瑁</v>
       </c>
       <c r="B118" t="str">
         <v>妹妹</v>
       </c>
       <c r="C118" t="str">
-        <v>assets/1785838787730-s5f333sc3u.jpg</v>
+        <v>assets/1785844013835-ek4xpcje7kh.jpg</v>
       </c>
       <c r="D118" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E118" t="str">
-        <v>2026-06-05</v>
+        <v>2026-02-14</v>
       </c>
       <c r="F118" t="str">
-        <v>湖北恩施</v>
+        <v/>
       </c>
       <c r="G118" t="str">
         <v/>
@@ -7369,22 +7369,22 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>银虎斑</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B119" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C119" t="str">
-        <v>assets/1785842296661-6qw3zs3as8h.jpg</v>
+        <v>assets/1785844434338-ek5zbdgdcne.jpg</v>
       </c>
       <c r="D119" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E119" t="str">
-        <v>2026-06-05</v>
+        <v>2026-05-24</v>
       </c>
       <c r="F119" t="str">
-        <v>湖北恩施</v>
+        <v/>
       </c>
       <c r="G119" t="str">
         <v/>
@@ -7431,19 +7431,19 @@
         <v>银虎斑</v>
       </c>
       <c r="B120" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C120" t="str">
-        <v>assets/1785842429109-porc98rel5.jpg</v>
+        <v>assets/1785838787730-s5f333sc3u.jpg</v>
       </c>
       <c r="D120" t="str">
         <v>是</v>
       </c>
       <c r="E120" t="str">
-        <v>2025-11-05</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F120" t="str">
-        <v>韩国</v>
+        <v>湖北恩施</v>
       </c>
       <c r="G120" t="str">
         <v/>
@@ -7490,19 +7490,19 @@
         <v>银虎斑</v>
       </c>
       <c r="B121" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C121" t="str">
-        <v>assets/1785842594141-fcglbzjp509.jpg</v>
+        <v>assets/1785842296661-6qw3zs3as8h.jpg</v>
       </c>
       <c r="D121" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E121" t="str">
-        <v>2026-05-18</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F121" t="str">
-        <v/>
+        <v>湖北恩施</v>
       </c>
       <c r="G121" t="str">
         <v/>
@@ -7546,22 +7546,22 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B122" t="str">
         <v>弟弟</v>
       </c>
       <c r="C122" t="str">
-        <v>assets/1785842639100-82k775dhwiv.jpg</v>
+        <v>assets/1785842429109-porc98rel5.jpg</v>
       </c>
       <c r="D122" t="str">
         <v>是</v>
       </c>
       <c r="E122" t="str">
-        <v>2026-05-28</v>
+        <v>2025-11-05</v>
       </c>
       <c r="F122" t="str">
-        <v>四川自贡</v>
+        <v>韩国</v>
       </c>
       <c r="G122" t="str">
         <v/>
@@ -7605,19 +7605,19 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B123" t="str">
         <v>妹妹</v>
       </c>
       <c r="C123" t="str">
-        <v>assets/1785842684502-mnhr0r96eee.jpg</v>
+        <v>assets/1785842594141-fcglbzjp509.jpg</v>
       </c>
       <c r="D123" t="str">
         <v>否</v>
       </c>
       <c r="E123" t="str">
-        <v>2026-06-06</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F123" t="str">
         <v/>
@@ -7664,22 +7664,22 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>纯黑色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B124" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C124" t="str">
-        <v>assets/1785842779532-5u1j0igrw1s.jpg</v>
+        <v>assets/1785842639100-82k775dhwiv.jpg</v>
       </c>
       <c r="D124" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E124" t="str">
-        <v>2026-03-05</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F124" t="str">
-        <v/>
+        <v>四川自贡</v>
       </c>
       <c r="G124" t="str">
         <v/>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B125" t="str">
         <v>妹妹</v>
       </c>
       <c r="C125" t="str">
-        <v>assets/1785842817046-6keqv4rw4yf.jpg</v>
+        <v>assets/1785842684502-mnhr0r96eee.jpg</v>
       </c>
       <c r="D125" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E125" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F125" t="str">
-        <v>韩国</v>
+        <v/>
       </c>
       <c r="G125" t="str">
         <v/>
@@ -7782,22 +7782,22 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>浅色银虎斑</v>
+        <v>纯黑色</v>
       </c>
       <c r="B126" t="str">
         <v>妹妹</v>
       </c>
       <c r="C126" t="str">
-        <v>assets/1785842950972-a88lbrskpc.jpg</v>
+        <v>assets/1785842779532-5u1j0igrw1s.jpg</v>
       </c>
       <c r="D126" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E126" t="str">
-        <v>2026-06-05</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F126" t="str">
-        <v>河北邢台</v>
+        <v/>
       </c>
       <c r="G126" t="str">
         <v/>
@@ -7841,22 +7841,22 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B127" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C127" t="str">
-        <v>assets/1785843011477-n3l1wi6ech.jpg</v>
+        <v>assets/1785842817046-6keqv4rw4yf.jpg</v>
       </c>
       <c r="D127" t="str">
         <v>是</v>
       </c>
       <c r="E127" t="str">
-        <v>2026-06-05</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F127" t="str">
-        <v>四川自贡</v>
+        <v>韩国</v>
       </c>
       <c r="G127" t="str">
         <v/>
@@ -7900,22 +7900,22 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>蓝虎斑</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B128" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C128" t="str">
-        <v>assets/1785843237517-ga449iqess5.jpg</v>
+        <v>assets/1785842950972-a88lbrskpc.jpg</v>
       </c>
       <c r="D128" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E128" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F128" t="str">
-        <v/>
+        <v>河北邢台</v>
       </c>
       <c r="G128" t="str">
         <v/>
@@ -7959,22 +7959,22 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>棕虎斑补丁</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B129" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C129" t="str">
-        <v>assets/1785842523893-7nwnnhwi4ns.jpg</v>
+        <v>assets/1785843011477-n3l1wi6ech.jpg</v>
       </c>
       <c r="D129" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E129" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F129" t="str">
-        <v/>
+        <v>四川自贡</v>
       </c>
       <c r="G129" t="str">
         <v/>
@@ -8021,16 +8021,16 @@
         <v>蓝虎斑</v>
       </c>
       <c r="B130" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C130" t="str">
-        <v>assets/1785843497557-st27fk8drqi.jpg</v>
+        <v>assets/1785843237517-ga449iqess5.jpg</v>
       </c>
       <c r="D130" t="str">
         <v>否</v>
       </c>
       <c r="E130" t="str">
-        <v>2026-04-05</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F130" t="str">
         <v/>
@@ -8077,13 +8077,13 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑补丁</v>
       </c>
       <c r="B131" t="str">
         <v>妹妹</v>
       </c>
       <c r="C131" t="str">
-        <v>assets/1785843621923-ylhakbtw13i.jpg</v>
+        <v>assets/1785842523893-7nwnnhwi4ns.jpg</v>
       </c>
       <c r="D131" t="str">
         <v>否</v>
@@ -8136,19 +8136,19 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B132" t="str">
         <v>妹妹</v>
       </c>
       <c r="C132" t="str">
-        <v>assets/1785843663884-sfxvpmiet7.jpg</v>
+        <v>assets/1785843497557-st27fk8drqi.jpg</v>
       </c>
       <c r="D132" t="str">
         <v>否</v>
       </c>
       <c r="E132" t="str">
-        <v>2026-03-05</v>
+        <v>2026-04-05</v>
       </c>
       <c r="F132" t="str">
         <v/>
@@ -8195,52 +8195,52 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>蓝虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B133" t="str">
         <v>妹妹</v>
       </c>
       <c r="C133" t="str">
-        <v>assets/1785852601940-o236xtv7yx.jpeg</v>
+        <v>assets/1785843621923-ylhakbtw13i.jpg</v>
       </c>
       <c r="D133" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E133" t="str">
-        <v>2026-02-20</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F133" t="str">
-        <v>荷兰</v>
+        <v/>
       </c>
       <c r="G133" t="str">
-        <v>阿泽</v>
+        <v/>
       </c>
       <c r="H133" t="str">
-        <v>小辫子</v>
+        <v/>
       </c>
       <c r="I133" t="str">
-        <v>驺驺</v>
+        <v/>
       </c>
       <c r="J133" t="str">
-        <v>2026-07-02</v>
+        <v/>
       </c>
       <c r="K133" t="str">
         <v/>
       </c>
       <c r="L133" t="str">
-        <v>2026-07-02</v>
+        <v/>
       </c>
       <c r="M133" t="str">
-        <v>2026-08-03</v>
+        <v/>
       </c>
       <c r="N133" t="str">
-        <v>2026-11-04</v>
+        <v/>
       </c>
       <c r="O133" t="str">
-        <v>2026-08-03 · 血清检测,2026-07-02 · 打疫苗 · assets/diary/zouzou-depart.jpg,2026-07-30 · 6.2斤 · 五个月10天了 · assets/feedback/zouzou-1.jpg</v>
+        <v/>
       </c>
       <c r="P133" t="str">
-        <v>已付定金</v>
+        <v/>
       </c>
       <c r="Q133" t="str">
         <v/>
@@ -8249,27 +8249,27 @@
         <v/>
       </c>
       <c r="S133" t="str">
-        <v>否</v>
+        <v/>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>红虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B134" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C134" t="str">
-        <v>assets/1785853950207-cedor66ou2q.jpeg</v>
+        <v>assets/1785843663884-sfxvpmiet7.jpg</v>
       </c>
       <c r="D134" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E134" t="str">
-        <v/>
+        <v>2026-03-05</v>
       </c>
       <c r="F134" t="str">
-        <v>广东广州</v>
+        <v/>
       </c>
       <c r="G134" t="str">
         <v/>
@@ -8313,52 +8313,52 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>红虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B135" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C135" t="str">
-        <v>assets/1785854129383-c8qkvl537x.jpeg</v>
+        <v>assets/1785852601940-o236xtv7yx.jpeg</v>
       </c>
       <c r="D135" t="str">
         <v>是</v>
       </c>
       <c r="E135" t="str">
-        <v/>
+        <v>2026-02-20</v>
       </c>
       <c r="F135" t="str">
-        <v>广东广州</v>
+        <v>荷兰</v>
       </c>
       <c r="G135" t="str">
-        <v/>
+        <v>阿泽</v>
       </c>
       <c r="H135" t="str">
-        <v/>
+        <v>小辫子</v>
       </c>
       <c r="I135" t="str">
-        <v/>
+        <v>驺驺</v>
       </c>
       <c r="J135" t="str">
-        <v/>
+        <v>2026-07-02</v>
       </c>
       <c r="K135" t="str">
         <v/>
       </c>
       <c r="L135" t="str">
-        <v/>
+        <v>2026-07-02</v>
       </c>
       <c r="M135" t="str">
-        <v/>
+        <v>2026-08-03</v>
       </c>
       <c r="N135" t="str">
-        <v/>
+        <v>2026-11-04</v>
       </c>
       <c r="O135" t="str">
-        <v/>
+        <v>2026-08-03 · 血清检测,2026-07-02 · 打疫苗 · assets/diary/zouzou-depart.jpg,2026-07-30 · 6.2斤 · 五个月10天了 · assets/feedback/zouzou-1.jpg</v>
       </c>
       <c r="P135" t="str">
-        <v/>
+        <v>已付定金</v>
       </c>
       <c r="Q135" t="str">
         <v/>
@@ -8367,18 +8367,18 @@
         <v/>
       </c>
       <c r="S135" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B136" t="str">
         <v>弟弟</v>
       </c>
       <c r="C136" t="str">
-        <v>assets/1785854166720-48r17hry9cd.jpeg</v>
+        <v>assets/1785853950207-cedor66ou2q.jpeg</v>
       </c>
       <c r="D136" t="str">
         <v>是</v>
@@ -8387,7 +8387,7 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>山西朔州</v>
+        <v>广东广州</v>
       </c>
       <c r="G136" t="str">
         <v/>
@@ -8431,13 +8431,13 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B137" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C137" t="str">
-        <v>assets/1785854224521-2cpg6xipfn6.jpeg</v>
+        <v>assets/1785854129383-c8qkvl537x.jpeg</v>
       </c>
       <c r="D137" t="str">
         <v>是</v>
@@ -8446,7 +8446,7 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>浙江宁波</v>
+        <v>广东广州</v>
       </c>
       <c r="G137" t="str">
         <v/>
@@ -8496,7 +8496,7 @@
         <v>弟弟</v>
       </c>
       <c r="C138" t="str">
-        <v>assets/1785854260793-steez4s972l.jpeg</v>
+        <v>assets/1785854166720-48r17hry9cd.jpeg</v>
       </c>
       <c r="D138" t="str">
         <v>是</v>
@@ -8505,7 +8505,7 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>陕西西安</v>
+        <v>山西朔州</v>
       </c>
       <c r="G138" t="str">
         <v/>
@@ -8552,10 +8552,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B139" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C139" t="str">
-        <v>assets/1785854319988-cohio08aod5.jpeg</v>
+        <v>assets/1785854224521-2cpg6xipfn6.jpeg</v>
       </c>
       <c r="D139" t="str">
         <v>是</v>
@@ -8564,7 +8564,7 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>黑龙江漠河</v>
+        <v>浙江宁波</v>
       </c>
       <c r="G139" t="str">
         <v/>
@@ -8608,13 +8608,13 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B140" t="str">
         <v>弟弟</v>
       </c>
       <c r="C140" t="str">
-        <v>assets/1785854520974-96b8b1ekqd9.jpeg</v>
+        <v>assets/1785854260793-steez4s972l.jpeg</v>
       </c>
       <c r="D140" t="str">
         <v>是</v>
@@ -8623,7 +8623,7 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>日本</v>
+        <v>陕西西安</v>
       </c>
       <c r="G140" t="str">
         <v/>
@@ -8670,10 +8670,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B141" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C141" t="str">
-        <v>assets/1785854664100-haqoiu1h7hj.jpeg</v>
+        <v>assets/1785854319988-cohio08aod5.jpeg</v>
       </c>
       <c r="D141" t="str">
         <v>是</v>
@@ -8682,7 +8682,7 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>浙江杭州</v>
+        <v>黑龙江漠河</v>
       </c>
       <c r="G141" t="str">
         <v/>
@@ -8726,13 +8726,13 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B142" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C142" t="str">
-        <v>assets/1785854690732-orrs40sx9rs.jpeg</v>
+        <v>assets/1785854520974-96b8b1ekqd9.jpeg</v>
       </c>
       <c r="D142" t="str">
         <v>是</v>
@@ -8741,7 +8741,7 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>贵州安顺</v>
+        <v>日本</v>
       </c>
       <c r="G142" t="str">
         <v/>
@@ -8791,7 +8791,7 @@
         <v>妹妹</v>
       </c>
       <c r="C143" t="str">
-        <v>assets/1785854734122-wcpmib4m7.jpeg</v>
+        <v>assets/1785854664100-haqoiu1h7hj.jpeg</v>
       </c>
       <c r="D143" t="str">
         <v>是</v>
@@ -8800,7 +8800,7 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>山东青岛</v>
+        <v>浙江杭州</v>
       </c>
       <c r="G143" t="str">
         <v/>
@@ -8847,10 +8847,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B144" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C144" t="str">
-        <v>assets/1785854758707-1kxdkfvs6jc.jpeg</v>
+        <v>assets/1785854690732-orrs40sx9rs.jpeg</v>
       </c>
       <c r="D144" t="str">
         <v>是</v>
@@ -8859,7 +8859,7 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>黑龙江漠河</v>
+        <v>贵州安顺</v>
       </c>
       <c r="G144" t="str">
         <v/>
@@ -8903,13 +8903,13 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>纯蓝色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B145" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C145" t="str">
-        <v>assets/1785854784780-3g0u60pdo93.jpeg</v>
+        <v>assets/1785854734122-wcpmib4m7.jpeg</v>
       </c>
       <c r="D145" t="str">
         <v>是</v>
@@ -8918,7 +8918,7 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>河南鹤壁</v>
+        <v>山东青岛</v>
       </c>
       <c r="G145" t="str">
         <v/>
@@ -8968,7 +8968,7 @@
         <v>弟弟</v>
       </c>
       <c r="C146" t="str">
-        <v>assets/1785854813179-8oyxr0h2bbu.jpeg</v>
+        <v>assets/1785854758707-1kxdkfvs6jc.jpeg</v>
       </c>
       <c r="D146" t="str">
         <v>是</v>
@@ -8977,7 +8977,7 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>陕西西安</v>
+        <v>黑龙江漠河</v>
       </c>
       <c r="G146" t="str">
         <v/>
@@ -9021,13 +9021,13 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>棕虎斑</v>
+        <v>纯蓝色</v>
       </c>
       <c r="B147" t="str">
         <v>弟弟</v>
       </c>
       <c r="C147" t="str">
-        <v>assets/1785854838933-uq6amircyzd.jpeg</v>
+        <v>assets/1785854784780-3g0u60pdo93.jpeg</v>
       </c>
       <c r="D147" t="str">
         <v>是</v>
@@ -9036,7 +9036,7 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>四川成都</v>
+        <v>河南鹤壁</v>
       </c>
       <c r="G147" t="str">
         <v/>
@@ -9080,22 +9080,22 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>烟灰色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B148" t="str">
         <v>弟弟</v>
       </c>
       <c r="C148" t="str">
-        <v>assets/1785854869973-za3p6wikqpo.jpeg</v>
+        <v>assets/1785854813179-8oyxr0h2bbu.jpeg</v>
       </c>
       <c r="D148" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E148" t="str">
-        <v>2026-05-18</v>
+        <v/>
       </c>
       <c r="F148" t="str">
-        <v/>
+        <v>陕西西安</v>
       </c>
       <c r="G148" t="str">
         <v/>
@@ -9139,13 +9139,13 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B149" t="str">
         <v>弟弟</v>
       </c>
       <c r="C149" t="str">
-        <v>assets/1785854997023-mawkallt2a.jpeg</v>
+        <v>assets/1785854838933-uq6amircyzd.jpeg</v>
       </c>
       <c r="D149" t="str">
         <v>是</v>
@@ -9154,7 +9154,7 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>新加坡</v>
+        <v>四川成都</v>
       </c>
       <c r="G149" t="str">
         <v/>
@@ -9198,22 +9198,22 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>凯米尔色</v>
+        <v>烟灰色</v>
       </c>
       <c r="B150" t="str">
         <v>弟弟</v>
       </c>
       <c r="C150" t="str">
-        <v>assets/1785855043327-wdc5pxwm34k.jpeg</v>
+        <v>assets/1785854869973-za3p6wikqpo.jpeg</v>
       </c>
       <c r="D150" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E150" t="str">
-        <v/>
+        <v>2026-05-18</v>
       </c>
       <c r="F150" t="str">
-        <v>上海浦东</v>
+        <v/>
       </c>
       <c r="G150" t="str">
         <v/>
@@ -9257,22 +9257,22 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B151" t="str">
         <v>弟弟</v>
       </c>
       <c r="C151" t="str">
-        <v>assets/1785912551260-jplefm937nk.jpeg, assets/videos/02.mp4</v>
+        <v>assets/1785854997023-mawkallt2a.jpeg</v>
       </c>
       <c r="D151" t="str">
         <v>是</v>
       </c>
       <c r="E151" t="str">
-        <v>2026-06-06</v>
+        <v/>
       </c>
       <c r="F151" t="str">
-        <v>浙江温州</v>
+        <v>新加坡</v>
       </c>
       <c r="G151" t="str">
         <v/>
@@ -9316,66 +9316,184 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
+        <v>凯米尔色</v>
+      </c>
+      <c r="B152" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C152" t="str">
+        <v>assets/1785855043327-wdc5pxwm34k.jpeg</v>
+      </c>
+      <c r="D152" t="str">
+        <v>是</v>
+      </c>
+      <c r="E152" t="str">
+        <v/>
+      </c>
+      <c r="F152" t="str">
+        <v>上海浦东</v>
+      </c>
+      <c r="G152" t="str">
+        <v/>
+      </c>
+      <c r="H152" t="str">
+        <v/>
+      </c>
+      <c r="I152" t="str">
+        <v/>
+      </c>
+      <c r="J152" t="str">
+        <v/>
+      </c>
+      <c r="K152" t="str">
+        <v/>
+      </c>
+      <c r="L152" t="str">
+        <v/>
+      </c>
+      <c r="M152" t="str">
+        <v/>
+      </c>
+      <c r="N152" t="str">
+        <v/>
+      </c>
+      <c r="O152" t="str">
+        <v/>
+      </c>
+      <c r="P152" t="str">
+        <v/>
+      </c>
+      <c r="Q152" t="str">
+        <v/>
+      </c>
+      <c r="R152" t="str">
+        <v/>
+      </c>
+      <c r="S152" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
         <v>棕虎斑</v>
       </c>
-      <c r="B152" t="str">
+      <c r="B153" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C153" t="str">
+        <v>assets/1785912551260-jplefm937nk.jpeg, assets/videos/02.mp4</v>
+      </c>
+      <c r="D153" t="str">
+        <v>是</v>
+      </c>
+      <c r="E153" t="str">
+        <v>2026-06-06</v>
+      </c>
+      <c r="F153" t="str">
+        <v>浙江温州</v>
+      </c>
+      <c r="G153" t="str">
+        <v/>
+      </c>
+      <c r="H153" t="str">
+        <v/>
+      </c>
+      <c r="I153" t="str">
+        <v/>
+      </c>
+      <c r="J153" t="str">
+        <v/>
+      </c>
+      <c r="K153" t="str">
+        <v/>
+      </c>
+      <c r="L153" t="str">
+        <v/>
+      </c>
+      <c r="M153" t="str">
+        <v/>
+      </c>
+      <c r="N153" t="str">
+        <v/>
+      </c>
+      <c r="O153" t="str">
+        <v/>
+      </c>
+      <c r="P153" t="str">
+        <v/>
+      </c>
+      <c r="Q153" t="str">
+        <v/>
+      </c>
+      <c r="R153" t="str">
+        <v/>
+      </c>
+      <c r="S153" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>棕虎斑</v>
+      </c>
+      <c r="B154" t="str">
         <v>妹妹</v>
       </c>
-      <c r="C152" t="str">
+      <c r="C154" t="str">
         <v>assets/1785912694000-m20f5kvvrr.jpeg</v>
       </c>
-      <c r="D152" t="str">
-        <v>否</v>
-      </c>
-      <c r="E152" t="str">
+      <c r="D154" t="str">
+        <v>否</v>
+      </c>
+      <c r="E154" t="str">
         <v>2026-06-06</v>
       </c>
-      <c r="F152" t="str">
-        <v/>
-      </c>
-      <c r="G152" t="str">
-        <v/>
-      </c>
-      <c r="H152" t="str">
-        <v/>
-      </c>
-      <c r="I152" t="str">
-        <v/>
-      </c>
-      <c r="J152" t="str">
-        <v/>
-      </c>
-      <c r="K152" t="str">
-        <v/>
-      </c>
-      <c r="L152" t="str">
-        <v/>
-      </c>
-      <c r="M152" t="str">
-        <v/>
-      </c>
-      <c r="N152" t="str">
-        <v/>
-      </c>
-      <c r="O152" t="str">
-        <v/>
-      </c>
-      <c r="P152" t="str">
-        <v/>
-      </c>
-      <c r="Q152" t="str">
-        <v/>
-      </c>
-      <c r="R152" t="str">
-        <v/>
-      </c>
-      <c r="S152" t="str">
+      <c r="F154" t="str">
+        <v/>
+      </c>
+      <c r="G154" t="str">
+        <v/>
+      </c>
+      <c r="H154" t="str">
+        <v/>
+      </c>
+      <c r="I154" t="str">
+        <v/>
+      </c>
+      <c r="J154" t="str">
+        <v/>
+      </c>
+      <c r="K154" t="str">
+        <v/>
+      </c>
+      <c r="L154" t="str">
+        <v/>
+      </c>
+      <c r="M154" t="str">
+        <v/>
+      </c>
+      <c r="N154" t="str">
+        <v/>
+      </c>
+      <c r="O154" t="str">
+        <v/>
+      </c>
+      <c r="P154" t="str">
+        <v/>
+      </c>
+      <c r="Q154" t="str">
+        <v/>
+      </c>
+      <c r="R154" t="str">
+        <v/>
+      </c>
+      <c r="S154" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S152"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S154"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S154"/>
+  <dimension ref="A1:S155"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -466,22 +466,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B2" t="str">
         <v>妹妹</v>
       </c>
       <c r="C2" t="str">
-        <v>assets/1787388322060-uj8bkwqgnv.jpg</v>
+        <v>assets/1787466121255-21jto2cugv.jpg</v>
       </c>
       <c r="D2" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-06-06</v>
+        <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>四川广安</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -525,13 +525,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>棕虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B3" t="str">
         <v>妹妹</v>
       </c>
       <c r="C3" t="str">
-        <v>assets/1787388277490-e6u506cx0r.jpg</v>
+        <v>assets/1787388322060-uj8bkwqgnv.jpg</v>
       </c>
       <c r="D3" t="str">
         <v>否</v>
@@ -584,22 +584,22 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B4" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C4" t="str">
-        <v>assets/1787328436957-x30od0gw28.jpg</v>
+        <v>assets/1787388277490-e6u506cx0r.jpg</v>
       </c>
       <c r="D4" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E4" t="str">
-        <v/>
+        <v>2026-06-06</v>
       </c>
       <c r="F4" t="str">
-        <v>江苏苏州</v>
+        <v/>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -643,13 +643,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>蓝虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B5" t="str">
         <v>弟弟</v>
       </c>
       <c r="C5" t="str">
-        <v>assets/1787328420967-viv9v8nbjn.jpg</v>
+        <v>assets/1787328436957-x30od0gw28.jpg</v>
       </c>
       <c r="D5" t="str">
         <v>是</v>
@@ -658,7 +658,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>辽宁东港</v>
+        <v>江苏苏州</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -702,13 +702,13 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>棕虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B6" t="str">
         <v>弟弟</v>
       </c>
       <c r="C6" t="str">
-        <v>assets/1787327967245-m62ohievcl.jpg</v>
+        <v>assets/1787328420967-viv9v8nbjn.jpg</v>
       </c>
       <c r="D6" t="str">
         <v>是</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>福建福州</v>
+        <v>辽宁东港</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -761,13 +761,13 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B7" t="str">
         <v>弟弟</v>
       </c>
       <c r="C7" t="str">
-        <v>assets/1787327853521-js8ljh3ulj.jpg</v>
+        <v>assets/1787327967245-m62ohievcl.jpg</v>
       </c>
       <c r="D7" t="str">
         <v>是</v>
@@ -776,7 +776,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>上海</v>
+        <v>福建福州</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -820,13 +820,13 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>纯蓝色</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B8" t="str">
         <v>弟弟</v>
       </c>
       <c r="C8" t="str">
-        <v>assets/1787327793837-znk2knoo6p.jpg</v>
+        <v>assets/1787327853521-js8ljh3ulj.jpg</v>
       </c>
       <c r="D8" t="str">
         <v>是</v>
@@ -835,7 +835,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>河南鹤壁</v>
+        <v>上海</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -879,13 +879,13 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>银虎斑</v>
+        <v>纯蓝色</v>
       </c>
       <c r="B9" t="str">
         <v>弟弟</v>
       </c>
       <c r="C9" t="str">
-        <v>assets/1787327752832-kkpmp21os3.jpg</v>
+        <v>assets/1787327793837-znk2knoo6p.jpg</v>
       </c>
       <c r="D9" t="str">
         <v>是</v>
@@ -894,7 +894,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>陕西西安</v>
+        <v>河南鹤壁</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -941,10 +941,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B10" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C10" t="str">
-        <v>assets/1787327605711-4o2f6v6ybp.jpg</v>
+        <v>assets/1787327752832-kkpmp21os3.jpg</v>
       </c>
       <c r="D10" t="str">
         <v>是</v>
@@ -1000,10 +1000,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B11" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C11" t="str">
-        <v>assets/1787327573762-h23cux94p2.jpg</v>
+        <v>assets/1787327605711-4o2f6v6ybp.jpg</v>
       </c>
       <c r="D11" t="str">
         <v>是</v>
@@ -1012,7 +1012,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>北京</v>
+        <v>陕西西安</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -1059,10 +1059,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B12" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C12" t="str">
-        <v>assets/1787327496557-9daggljg4g.jpg</v>
+        <v>assets/1787327573762-h23cux94p2.jpg</v>
       </c>
       <c r="D12" t="str">
         <v>是</v>
@@ -1071,7 +1071,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>黑龙江哈尔滨</v>
+        <v>北京</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -1115,13 +1115,13 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>烟灰色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B13" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C13" t="str">
-        <v>assets/1787327456560-p4yhq4qvrv.jpg</v>
+        <v>assets/1787327496557-9daggljg4g.jpg</v>
       </c>
       <c r="D13" t="str">
         <v>是</v>
@@ -1130,7 +1130,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>甘肃嘉峪关</v>
+        <v>黑龙江哈尔滨</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -1174,13 +1174,13 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>蓝虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B14" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C14" t="str">
-        <v>assets/1787327421713-zg7np4yzkc.jpg</v>
+        <v>assets/1787327456560-p4yhq4qvrv.jpg</v>
       </c>
       <c r="D14" t="str">
         <v>是</v>
@@ -1189,7 +1189,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>安徽合肥</v>
+        <v>甘肃嘉峪关</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -1233,13 +1233,13 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B15" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C15" t="str">
-        <v>assets/1787327337811-u5u2pdew3.jpg</v>
+        <v>assets/1787327421713-zg7np4yzkc.jpg</v>
       </c>
       <c r="D15" t="str">
         <v>是</v>
@@ -1292,13 +1292,13 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B16" t="str">
         <v>弟弟</v>
       </c>
       <c r="C16" t="str">
-        <v>assets/1787327309143-6c1dan1sev.jpg</v>
+        <v>assets/1787327337811-u5u2pdew3.jpg</v>
       </c>
       <c r="D16" t="str">
         <v>是</v>
@@ -1307,7 +1307,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>四川成都</v>
+        <v>安徽合肥</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1351,13 +1351,13 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B17" t="str">
         <v>弟弟</v>
       </c>
       <c r="C17" t="str">
-        <v>assets/1787327277453-w89ujg69fm.jpg</v>
+        <v>assets/1787327309143-6c1dan1sev.jpg</v>
       </c>
       <c r="D17" t="str">
         <v>是</v>
@@ -1410,13 +1410,13 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>蓝银虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B18" t="str">
         <v>弟弟</v>
       </c>
       <c r="C18" t="str">
-        <v>assets/1787327232159-lkrcl588a5.jpg</v>
+        <v>assets/1787327277453-w89ujg69fm.jpg</v>
       </c>
       <c r="D18" t="str">
         <v>是</v>
@@ -1469,13 +1469,13 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>玳瑁色</v>
+        <v>蓝银虎斑</v>
       </c>
       <c r="B19" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C19" t="str">
-        <v>assets/1787327182347-3az0z7sys2.jpg</v>
+        <v>assets/1787327232159-lkrcl588a5.jpg</v>
       </c>
       <c r="D19" t="str">
         <v>是</v>
@@ -1484,7 +1484,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>四川内江</v>
+        <v>四川成都</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1528,13 +1528,13 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>棕虎补丁</v>
+        <v>玳瑁色</v>
       </c>
       <c r="B20" t="str">
         <v>妹妹</v>
       </c>
       <c r="C20" t="str">
-        <v>assets/1787327143756-4xtgfy5ozu.jpg</v>
+        <v>assets/1787327182347-3az0z7sys2.jpg</v>
       </c>
       <c r="D20" t="str">
         <v>是</v>
@@ -1543,7 +1543,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>贵州贵阳</v>
+        <v>四川内江</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1587,13 +1587,13 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>黑烟色</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B21" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C21" t="str">
-        <v>assets/1787327101790-tqjlseog5y.jpg</v>
+        <v>assets/1787327143756-4xtgfy5ozu.jpg</v>
       </c>
       <c r="D21" t="str">
         <v>是</v>
@@ -1602,7 +1602,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>浙江杭州</v>
+        <v>贵州贵阳</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1646,13 +1646,13 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>烟灰色</v>
+        <v>黑烟色</v>
       </c>
       <c r="B22" t="str">
         <v>弟弟</v>
       </c>
       <c r="C22" t="str">
-        <v>assets/1787327019632-l1780lu2hj.jpg</v>
+        <v>assets/1787327101790-tqjlseog5y.jpg</v>
       </c>
       <c r="D22" t="str">
         <v>是</v>
@@ -1661,7 +1661,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>山东威海</v>
+        <v>浙江杭州</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1705,13 +1705,13 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>棕虎补丁</v>
+        <v>烟灰色</v>
       </c>
       <c r="B23" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C23" t="str">
-        <v>assets/1787326905275-plz3fpgo97.jpg</v>
+        <v>assets/1787327019632-l1780lu2hj.jpg</v>
       </c>
       <c r="D23" t="str">
         <v>是</v>
@@ -1720,7 +1720,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>浙江杭州</v>
+        <v>山东威海</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1764,13 +1764,13 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B24" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C24" t="str">
-        <v>assets/1787326874462-z9rzs7wg17.jpg</v>
+        <v>assets/1787326905275-plz3fpgo97.jpg</v>
       </c>
       <c r="D24" t="str">
         <v>是</v>
@@ -1779,7 +1779,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>四川成都</v>
+        <v>浙江杭州</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1823,13 +1823,13 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>凯米尔色</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B25" t="str">
         <v>弟弟</v>
       </c>
       <c r="C25" t="str">
-        <v>assets/1787326843271-0uhv7b9p89.jpg</v>
+        <v>assets/1787326874462-z9rzs7wg17.jpg</v>
       </c>
       <c r="D25" t="str">
         <v>是</v>
@@ -1882,13 +1882,13 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>凯米尔</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B26" t="str">
         <v>弟弟</v>
       </c>
       <c r="C26" t="str">
-        <v>assets/1787326814713-p5oavnlulg.jpg</v>
+        <v>assets/1787326843271-0uhv7b9p89.jpg</v>
       </c>
       <c r="D26" t="str">
         <v>是</v>
@@ -1941,13 +1941,13 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>棕虎斑</v>
+        <v>凯米尔</v>
       </c>
       <c r="B27" t="str">
         <v>弟弟</v>
       </c>
       <c r="C27" t="str">
-        <v>assets/1787326773577-13q5out2d0.jpg</v>
+        <v>assets/1787326814713-p5oavnlulg.jpg</v>
       </c>
       <c r="D27" t="str">
         <v>是</v>
@@ -1956,7 +1956,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>四川宜宾</v>
+        <v>四川成都</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -2000,13 +2000,13 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>金棕虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B28" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C28" t="str">
-        <v>assets/1787326548993-89s929m2hg.jpg</v>
+        <v>assets/1787326773577-13q5out2d0.jpg</v>
       </c>
       <c r="D28" t="str">
         <v>是</v>
@@ -2015,7 +2015,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>上海</v>
+        <v>四川宜宾</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -2059,13 +2059,13 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>凯米尔色</v>
+        <v>金棕虎斑</v>
       </c>
       <c r="B29" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C29" t="str">
-        <v>assets/1787326449218-09s9ucram4.jpg</v>
+        <v>assets/1787326548993-89s929m2hg.jpg</v>
       </c>
       <c r="D29" t="str">
         <v>是</v>
@@ -2074,7 +2074,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>德国</v>
+        <v>上海</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -2118,13 +2118,13 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>棕虎补丁</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B30" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C30" t="str">
-        <v>assets/1787326277374-8ti107m5ki.jpg</v>
+        <v>assets/1787326449218-09s9ucram4.jpg</v>
       </c>
       <c r="D30" t="str">
         <v>是</v>
@@ -2133,7 +2133,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>广东深圳</v>
+        <v>德国</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -2177,13 +2177,13 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>烟灰色</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B31" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C31" t="str">
-        <v>assets/1787326236952-2pmwche4t3.jpg</v>
+        <v>assets/1787326277374-8ti107m5ki.jpg</v>
       </c>
       <c r="D31" t="str">
         <v>是</v>
@@ -2192,7 +2192,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>福建泉州</v>
+        <v>广东深圳</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -2236,13 +2236,13 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B32" t="str">
         <v>弟弟</v>
       </c>
       <c r="C32" t="str">
-        <v>assets/1787326184557-90v6clkwen.jpg</v>
+        <v>assets/1787326236952-2pmwche4t3.jpg</v>
       </c>
       <c r="D32" t="str">
         <v>是</v>
@@ -2251,7 +2251,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>福建福州</v>
+        <v>福建泉州</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -2295,13 +2295,13 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B33" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C33" t="str">
-        <v>assets/1787326046155-4tk23nq4dj.jpg</v>
+        <v>assets/1787326184557-90v6clkwen.jpg</v>
       </c>
       <c r="D33" t="str">
         <v>是</v>
@@ -2310,7 +2310,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>广西贵港</v>
+        <v>福建福州</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -2354,13 +2354,13 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>凯米尔色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B34" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C34" t="str">
-        <v>assets/1787325862706-wq18k3ej56.jpg</v>
+        <v>assets/1787326046155-4tk23nq4dj.jpg</v>
       </c>
       <c r="D34" t="str">
         <v>是</v>
@@ -2369,7 +2369,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>江苏苏州</v>
+        <v>广西贵港</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -2419,7 +2419,7 @@
         <v>弟弟</v>
       </c>
       <c r="C35" t="str">
-        <v>assets/1787325743258-a7oac7hzlo.jpg</v>
+        <v>assets/1787325862706-wq18k3ej56.jpg</v>
       </c>
       <c r="D35" t="str">
         <v>是</v>
@@ -2472,13 +2472,13 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>银虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B36" t="str">
         <v>弟弟</v>
       </c>
       <c r="C36" t="str">
-        <v>assets/1787325706797-kgk81ghccy.jpg</v>
+        <v>assets/1787325743258-a7oac7hzlo.jpg</v>
       </c>
       <c r="D36" t="str">
         <v>是</v>
@@ -2487,7 +2487,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>北京</v>
+        <v>江苏苏州</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -2531,13 +2531,13 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>蓝虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B37" t="str">
         <v>弟弟</v>
       </c>
       <c r="C37" t="str">
-        <v>assets/1787325603704-lahzgrm7fa.jpg,assets/1787325690106-wgu3spujit.jpg</v>
+        <v>assets/1787325706797-kgk81ghccy.jpg</v>
       </c>
       <c r="D37" t="str">
         <v>是</v>
@@ -2546,7 +2546,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>上海</v>
+        <v>北京</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -2590,13 +2590,13 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>棕虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B38" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C38" t="str">
-        <v>assets/1787325554341-608thexrne.jpg</v>
+        <v>assets/1787325603704-lahzgrm7fa.jpg,assets/1787325690106-wgu3spujit.jpg</v>
       </c>
       <c r="D38" t="str">
         <v>是</v>
@@ -2605,7 +2605,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>江苏苏州</v>
+        <v>上海</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -2649,13 +2649,13 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>浅色银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B39" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C39" t="str">
-        <v>assets/1787325480828-q90pskoiw3.jpg</v>
+        <v>assets/1787325554341-608thexrne.jpg</v>
       </c>
       <c r="D39" t="str">
         <v>是</v>
@@ -2664,7 +2664,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>四川成都</v>
+        <v>江苏苏州</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -2711,10 +2711,10 @@
         <v>浅色银虎斑</v>
       </c>
       <c r="B40" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C40" t="str">
-        <v>assets/1787325448999-a2pg8176fu.jpg</v>
+        <v>assets/1787325480828-q90pskoiw3.jpg</v>
       </c>
       <c r="D40" t="str">
         <v>是</v>
@@ -2723,7 +2723,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>中国台湾</v>
+        <v>四川成都</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -2767,13 +2767,13 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>棕虎斑</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B41" t="str">
         <v>妹妹</v>
       </c>
       <c r="C41" t="str">
-        <v>assets/1787325357634-k55zlfhmqj.jpg</v>
+        <v>assets/1787325448999-a2pg8176fu.jpg</v>
       </c>
       <c r="D41" t="str">
         <v>是</v>
@@ -2782,7 +2782,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>浙江杭州</v>
+        <v>中国台湾</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -2826,13 +2826,13 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B42" t="str">
         <v>妹妹</v>
       </c>
       <c r="C42" t="str">
-        <v>assets/1787325237876-t19isaq5gu.jpg</v>
+        <v>assets/1787325357634-k55zlfhmqj.jpg</v>
       </c>
       <c r="D42" t="str">
         <v>是</v>
@@ -2841,7 +2841,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>辽宁沈阳</v>
+        <v>浙江杭州</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -2885,13 +2885,13 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>金棕虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B43" t="str">
         <v>妹妹</v>
       </c>
       <c r="C43" t="str">
-        <v>assets/1787325199931-e7wms9qtya.jpg</v>
+        <v>assets/1787325237876-t19isaq5gu.jpg</v>
       </c>
       <c r="D43" t="str">
         <v>是</v>
@@ -2900,7 +2900,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>四川成都</v>
+        <v>辽宁沈阳</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2944,13 +2944,13 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>蓝虎斑</v>
+        <v>金棕虎斑</v>
       </c>
       <c r="B44" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C44" t="str">
-        <v>assets/1787325172354-4sa8uzaey2.jpg</v>
+        <v>assets/1787325199931-e7wms9qtya.jpg</v>
       </c>
       <c r="D44" t="str">
         <v>是</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>中国香港</v>
+        <v>四川成都</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -3003,13 +3003,13 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>烟灰色</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B45" t="str">
         <v>弟弟</v>
       </c>
       <c r="C45" t="str">
-        <v>assets/1787325109283-y7mvkk6qg4.jpg</v>
+        <v>assets/1787325172354-4sa8uzaey2.jpg</v>
       </c>
       <c r="D45" t="str">
         <v>是</v>
@@ -3018,7 +3018,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>中国澳门</v>
+        <v>中国香港</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -3062,13 +3062,13 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>蓝虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B46" t="str">
         <v>弟弟</v>
       </c>
       <c r="C46" t="str">
-        <v>assets/1787325033629-y3ygps3zaj.jpg</v>
+        <v>assets/1787325109283-y7mvkk6qg4.jpg</v>
       </c>
       <c r="D46" t="str">
         <v>是</v>
@@ -3077,7 +3077,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>山东青岛</v>
+        <v>中国澳门</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -3121,13 +3121,13 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>烟灰色</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B47" t="str">
         <v>弟弟</v>
       </c>
       <c r="C47" t="str">
-        <v>assets/1787324954998-w5m5jox439.jpg</v>
+        <v>assets/1787325033629-y3ygps3zaj.jpg</v>
       </c>
       <c r="D47" t="str">
         <v>是</v>
@@ -3136,7 +3136,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>海南海口</v>
+        <v>山东青岛</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -3180,13 +3180,13 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>棕虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B48" t="str">
         <v>弟弟</v>
       </c>
       <c r="C48" t="str">
-        <v>assets/1787324905909-zrz8o79kdf.jpg</v>
+        <v>assets/1787324954998-w5m5jox439.jpg</v>
       </c>
       <c r="D48" t="str">
         <v>是</v>
@@ -3195,7 +3195,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>内蒙古</v>
+        <v>海南海口</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -3239,13 +3239,13 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B49" t="str">
         <v>弟弟</v>
       </c>
       <c r="C49" t="str">
-        <v>assets/1787324880505-gbh0sn7b6j.jpg</v>
+        <v>assets/1787324905909-zrz8o79kdf.jpg</v>
       </c>
       <c r="D49" t="str">
         <v>是</v>
@@ -3254,7 +3254,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>中国香港</v>
+        <v>内蒙古</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -3304,7 +3304,7 @@
         <v>弟弟</v>
       </c>
       <c r="C50" t="str">
-        <v>assets/1787324806613-31yyz14tsf.jpg</v>
+        <v>assets/1787324880505-gbh0sn7b6j.jpg</v>
       </c>
       <c r="D50" t="str">
         <v>是</v>
@@ -3313,7 +3313,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>四川成都</v>
+        <v>中国香港</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -3357,13 +3357,13 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>红虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B51" t="str">
         <v>弟弟</v>
       </c>
       <c r="C51" t="str">
-        <v>assets/1787324789658-uz6ephkdsh.jpg</v>
+        <v>assets/1787324806613-31yyz14tsf.jpg</v>
       </c>
       <c r="D51" t="str">
         <v>是</v>
@@ -3372,7 +3372,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>湖北武汉</v>
+        <v>四川成都</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -3416,13 +3416,13 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>烟灰色</v>
+        <v>红虎斑</v>
       </c>
       <c r="B52" t="str">
         <v>弟弟</v>
       </c>
       <c r="C52" t="str">
-        <v>assets/1787324522658-smn44crast.jpg</v>
+        <v>assets/1787324789658-uz6ephkdsh.jpg</v>
       </c>
       <c r="D52" t="str">
         <v>是</v>
@@ -3475,13 +3475,13 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>棕虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B53" t="str">
         <v>弟弟</v>
       </c>
       <c r="C53" t="str">
-        <v>assets/1787324365608-6xtrjp7euz.jpg</v>
+        <v>assets/1787324522658-smn44crast.jpg</v>
       </c>
       <c r="D53" t="str">
         <v>是</v>
@@ -3490,7 +3490,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>新疆</v>
+        <v>湖北武汉</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -3534,13 +3534,13 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>浅凯米尔</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B54" t="str">
         <v>弟弟</v>
       </c>
       <c r="C54" t="str">
-        <v>assets/1787324331029-d74lcuycf6.jpg</v>
+        <v>assets/1787324365608-6xtrjp7euz.jpg</v>
       </c>
       <c r="D54" t="str">
         <v>是</v>
@@ -3549,7 +3549,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>四川成都</v>
+        <v>新疆</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -3593,13 +3593,13 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>红虎斑</v>
+        <v>浅凯米尔</v>
       </c>
       <c r="B55" t="str">
         <v>弟弟</v>
       </c>
       <c r="C55" t="str">
-        <v>assets/1787324297469-ans1lse2l5.jpg</v>
+        <v>assets/1787324331029-d74lcuycf6.jpg</v>
       </c>
       <c r="D55" t="str">
         <v>是</v>
@@ -3608,7 +3608,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>四川乐山</v>
+        <v>四川成都</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -3658,7 +3658,7 @@
         <v>弟弟</v>
       </c>
       <c r="C56" t="str">
-        <v>assets/1787324256827-7w383z4bg1.jpg</v>
+        <v>assets/1787324297469-ans1lse2l5.jpg</v>
       </c>
       <c r="D56" t="str">
         <v>是</v>
@@ -3667,7 +3667,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>中国台湾</v>
+        <v>四川乐山</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -3711,13 +3711,13 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B57" t="str">
         <v>弟弟</v>
       </c>
       <c r="C57" t="str">
-        <v>assets/1787324228262-y3vwn6i4zk.jpg</v>
+        <v>assets/1787324256827-7w383z4bg1.jpg</v>
       </c>
       <c r="D57" t="str">
         <v>是</v>
@@ -3726,7 +3726,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>四川成都</v>
+        <v>中国台湾</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -3770,13 +3770,13 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>凯米尔色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B58" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C58" t="str">
-        <v>assets/1787324201418-9tk4ik75mo.jpg</v>
+        <v>assets/1787324228262-y3vwn6i4zk.jpg</v>
       </c>
       <c r="D58" t="str">
         <v>是</v>
@@ -3785,7 +3785,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>江苏南京</v>
+        <v>四川成都</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -3829,13 +3829,13 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>棕虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B59" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C59" t="str">
-        <v>assets/1787324092513-jpa2rmkci2.jpg</v>
+        <v>assets/1787324201418-9tk4ik75mo.jpg</v>
       </c>
       <c r="D59" t="str">
         <v>是</v>
@@ -3888,13 +3888,13 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B60" t="str">
         <v>弟弟</v>
       </c>
       <c r="C60" t="str">
-        <v>assets/1787323318612-soge38hpsf.jpg</v>
+        <v>assets/1787324092513-jpa2rmkci2.jpg</v>
       </c>
       <c r="D60" t="str">
         <v>是</v>
@@ -3903,7 +3903,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>上海</v>
+        <v>江苏南京</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -3947,13 +3947,13 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B61" t="str">
         <v>弟弟</v>
       </c>
       <c r="C61" t="str">
-        <v>assets/1787323235892-7yq8ioq01e.jpg</v>
+        <v>assets/1787323318612-soge38hpsf.jpg</v>
       </c>
       <c r="D61" t="str">
         <v>是</v>
@@ -3962,7 +3962,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>四川成都</v>
+        <v>上海</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -4006,13 +4006,13 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B62" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C62" t="str">
-        <v>assets/1787322988096-6e2f54q7vo.jpg</v>
+        <v>assets/1787323235892-7yq8ioq01e.jpg</v>
       </c>
       <c r="D62" t="str">
         <v>是</v>
@@ -4021,7 +4021,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>浙江宁波</v>
+        <v>四川成都</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -4065,13 +4065,13 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>银虎斑补丁</v>
+        <v>银虎斑</v>
       </c>
       <c r="B63" t="str">
         <v>妹妹</v>
       </c>
       <c r="C63" t="str">
-        <v>assets/1787322938518-85ev8bs2k5.jpg</v>
+        <v>assets/1787322988096-6e2f54q7vo.jpg</v>
       </c>
       <c r="D63" t="str">
         <v>是</v>
@@ -4080,7 +4080,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>马来西亚</v>
+        <v>浙江宁波</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -4124,13 +4124,13 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>银虎斑</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B64" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C64" t="str">
-        <v>assets/1787322881183-tzu9xtw2sg.jpg</v>
+        <v>assets/1787322938518-85ev8bs2k5.jpg</v>
       </c>
       <c r="D64" t="str">
         <v>是</v>
@@ -4139,7 +4139,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>陕西西安</v>
+        <v>马来西亚</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -4183,13 +4183,13 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>纯黑色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B65" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C65" t="str">
-        <v>assets/1787322840098-nhy4jjyx7k.jpg</v>
+        <v>assets/1787322881183-tzu9xtw2sg.jpg</v>
       </c>
       <c r="D65" t="str">
         <v>是</v>
@@ -4198,7 +4198,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>广西南宁</v>
+        <v>陕西西安</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -4242,13 +4242,13 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>棕虎斑</v>
+        <v>纯黑色</v>
       </c>
       <c r="B66" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C66" t="str">
-        <v>assets/1787322760950-gn3qgego4s.jpg</v>
+        <v>assets/1787322840098-nhy4jjyx7k.jpg</v>
       </c>
       <c r="D66" t="str">
         <v>是</v>
@@ -4301,13 +4301,13 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>红虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B67" t="str">
         <v>弟弟</v>
       </c>
       <c r="C67" t="str">
-        <v>assets/1787322605982-04n50xegt2.jpg</v>
+        <v>assets/1787322760950-gn3qgego4s.jpg</v>
       </c>
       <c r="D67" t="str">
         <v>是</v>
@@ -4316,7 +4316,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>上海</v>
+        <v>广西南宁</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -4360,13 +4360,13 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>蓝虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B68" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C68" t="str">
-        <v>assets/1787322490045-kog3ru43dy.jpg</v>
+        <v>assets/1787322605982-04n50xegt2.jpg</v>
       </c>
       <c r="D68" t="str">
         <v>是</v>
@@ -4419,13 +4419,13 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>红虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B69" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C69" t="str">
-        <v>assets/1787322419996-0m33yx89nm.jpg</v>
+        <v>assets/1787322490045-kog3ru43dy.jpg</v>
       </c>
       <c r="D69" t="str">
         <v>是</v>
@@ -4434,7 +4434,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>广东广州</v>
+        <v>上海</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -4478,13 +4478,13 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>浅色银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B70" t="str">
         <v>弟弟</v>
       </c>
       <c r="C70" t="str">
-        <v>assets/1787322377730-vj5csj2mll.jpg</v>
+        <v>assets/1787322419996-0m33yx89nm.jpg</v>
       </c>
       <c r="D70" t="str">
         <v>是</v>
@@ -4493,7 +4493,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>柬埔寨</v>
+        <v>广东广州</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -4537,13 +4537,13 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>蓝虎斑</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B71" t="str">
         <v>弟弟</v>
       </c>
       <c r="C71" t="str">
-        <v>assets/1787322269611-53yaj5ideu.jpg</v>
+        <v>assets/1787322377730-vj5csj2mll.jpg</v>
       </c>
       <c r="D71" t="str">
         <v>是</v>
@@ -4552,7 +4552,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>山东枣庄</v>
+        <v>柬埔寨</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -4596,13 +4596,13 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B72" t="str">
         <v>弟弟</v>
       </c>
       <c r="C72" t="str">
-        <v>assets/1787321989528-7d6liuhuk9.jpg</v>
+        <v>assets/1787322269611-53yaj5ideu.jpg</v>
       </c>
       <c r="D72" t="str">
         <v>是</v>
@@ -4611,7 +4611,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>陕西西安</v>
+        <v>山东枣庄</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -4661,7 +4661,7 @@
         <v>弟弟</v>
       </c>
       <c r="C73" t="str">
-        <v>assets/1787321941642-xlrc1no2ua.jpg</v>
+        <v>assets/1787321989528-7d6liuhuk9.jpg</v>
       </c>
       <c r="D73" t="str">
         <v>是</v>
@@ -4670,7 +4670,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>山东东营</v>
+        <v>陕西西安</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -4714,13 +4714,13 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>凯米尔色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B74" t="str">
         <v>弟弟</v>
       </c>
       <c r="C74" t="str">
-        <v>assets/1787321903535-6orj7qcgzn.jpg</v>
+        <v>assets/1787321941642-xlrc1no2ua.jpg</v>
       </c>
       <c r="D74" t="str">
         <v>是</v>
@@ -4729,7 +4729,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>中国台湾</v>
+        <v>山东东营</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -4773,13 +4773,13 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>烟灰色</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B75" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C75" t="str">
-        <v>assets/1787321858985-v4qej7cq7g.jpg</v>
+        <v>assets/1787321903535-6orj7qcgzn.jpg</v>
       </c>
       <c r="D75" t="str">
         <v>是</v>
@@ -4832,13 +4832,13 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B76" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C76" t="str">
-        <v>assets/1787321834306-efgnyhujon.jpg</v>
+        <v>assets/1787321858985-v4qej7cq7g.jpg</v>
       </c>
       <c r="D76" t="str">
         <v>是</v>
@@ -4847,7 +4847,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>北京</v>
+        <v>中国台湾</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -4897,7 +4897,7 @@
         <v>弟弟</v>
       </c>
       <c r="C77" t="str">
-        <v>assets/1787321439916-uttgpbkogb.jpg</v>
+        <v>assets/1787321834306-efgnyhujon.jpg</v>
       </c>
       <c r="D77" t="str">
         <v>是</v>
@@ -4906,7 +4906,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>安徽合肥</v>
+        <v>北京</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -4956,7 +4956,7 @@
         <v>弟弟</v>
       </c>
       <c r="C78" t="str">
-        <v>assets/1787321419210-51hhgurygq.jpg</v>
+        <v>assets/1787321439916-uttgpbkogb.jpg</v>
       </c>
       <c r="D78" t="str">
         <v>是</v>
@@ -4965,7 +4965,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>上海</v>
+        <v>安徽合肥</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -5009,13 +5009,13 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>凯米尔色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B79" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C79" t="str">
-        <v>assets/1787321363369-bzjn51j5il.jpg</v>
+        <v>assets/1787321419210-51hhgurygq.jpg</v>
       </c>
       <c r="D79" t="str">
         <v>是</v>
@@ -5024,7 +5024,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>中国台湾</v>
+        <v>上海</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -5068,13 +5068,13 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>棕虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B80" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C80" t="str">
-        <v>assets/1787321332559-87p6spuch3.jpg</v>
+        <v>assets/1787321363369-bzjn51j5il.jpg</v>
       </c>
       <c r="D80" t="str">
         <v>是</v>
@@ -5130,10 +5130,10 @@
         <v>棕虎斑</v>
       </c>
       <c r="B81" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C81" t="str">
-        <v>assets/1787321232531-59lnzv8y98.jpg</v>
+        <v>assets/1787321332559-87p6spuch3.jpg</v>
       </c>
       <c r="D81" t="str">
         <v>是</v>
@@ -5142,7 +5142,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>北京</v>
+        <v>中国台湾</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -5186,13 +5186,13 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B82" t="str">
         <v>妹妹</v>
       </c>
       <c r="C82" t="str">
-        <v>assets/1787319975814-g1pfa56vfp.jpg</v>
+        <v>assets/1787321232531-59lnzv8y98.jpg</v>
       </c>
       <c r="D82" t="str">
         <v>是</v>
@@ -5201,7 +5201,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>浙江宁波</v>
+        <v>北京</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -5251,7 +5251,7 @@
         <v>妹妹</v>
       </c>
       <c r="C83" t="str">
-        <v>assets/1787319800704-v3qeu062ak.jpg</v>
+        <v>assets/1787319975814-g1pfa56vfp.jpg</v>
       </c>
       <c r="D83" t="str">
         <v>是</v>
@@ -5260,7 +5260,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>河北唐山</v>
+        <v>浙江宁波</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -5310,7 +5310,7 @@
         <v>妹妹</v>
       </c>
       <c r="C84" t="str">
-        <v>assets/1787319745369-zn66xr3bvb.jpg</v>
+        <v>assets/1787319800704-v3qeu062ak.jpg</v>
       </c>
       <c r="D84" t="str">
         <v>是</v>
@@ -5319,7 +5319,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>河北石家庄</v>
+        <v>河北唐山</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -5363,13 +5363,13 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>棕虎补丁</v>
+        <v>银虎斑</v>
       </c>
       <c r="B85" t="str">
         <v>妹妹</v>
       </c>
       <c r="C85" t="str">
-        <v>assets/1787319547969-zqlq35fxxt.jpg</v>
+        <v>assets/1787319745369-zn66xr3bvb.jpg</v>
       </c>
       <c r="D85" t="str">
         <v>是</v>
@@ -5378,7 +5378,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>韩国</v>
+        <v>河北石家庄</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -5422,13 +5422,13 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>蓝银虎斑</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B86" t="str">
         <v>妹妹</v>
       </c>
       <c r="C86" t="str">
-        <v>assets/1787319501376-xscwljnu1j.jpg</v>
+        <v>assets/1787319547969-zqlq35fxxt.jpg</v>
       </c>
       <c r="D86" t="str">
         <v>是</v>
@@ -5437,7 +5437,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>美国</v>
+        <v>韩国</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -5481,13 +5481,13 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>棕虎斑</v>
+        <v>蓝银虎斑</v>
       </c>
       <c r="B87" t="str">
         <v>妹妹</v>
       </c>
       <c r="C87" t="str">
-        <v>assets/1787319443529-4a0zqikufx.jpg</v>
+        <v>assets/1787319501376-xscwljnu1j.jpg</v>
       </c>
       <c r="D87" t="str">
         <v>是</v>
@@ -5496,7 +5496,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>中国台湾</v>
+        <v>美国</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -5540,13 +5540,13 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B88" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C88" t="str">
-        <v>assets/1787319356194-lr2d5680i9.jpg</v>
+        <v>assets/1787319443529-4a0zqikufx.jpg</v>
       </c>
       <c r="D88" t="str">
         <v>是</v>
@@ -5599,13 +5599,13 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>棕虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B89" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C89" t="str">
-        <v>assets/1787319208828-aizqo4blcv.jpg</v>
+        <v>assets/1787319356194-lr2d5680i9.jpg</v>
       </c>
       <c r="D89" t="str">
         <v>是</v>
@@ -5614,7 +5614,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>山东淄博</v>
+        <v>中国台湾</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -5658,13 +5658,13 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B90" t="str">
         <v>妹妹</v>
       </c>
       <c r="C90" t="str">
-        <v>assets/1787319162970-cc2v8ovnni.jpg</v>
+        <v>assets/1787319208828-aizqo4blcv.jpg</v>
       </c>
       <c r="D90" t="str">
         <v>是</v>
@@ -5673,7 +5673,7 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>韩国</v>
+        <v>山东淄博</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -5717,13 +5717,13 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>棕虎补丁</v>
+        <v>银虎斑</v>
       </c>
       <c r="B91" t="str">
         <v>妹妹</v>
       </c>
       <c r="C91" t="str">
-        <v>assets/1787319098214-8pwa9yx2wc.jpg</v>
+        <v>assets/1787319162970-cc2v8ovnni.jpg</v>
       </c>
       <c r="D91" t="str">
         <v>是</v>
@@ -5732,7 +5732,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>四川成都</v>
+        <v>韩国</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -5776,13 +5776,13 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>银虎斑</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B92" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C92" t="str">
-        <v>assets/1787318867999-3gxdddp72x.jpg</v>
+        <v>assets/1787319098214-8pwa9yx2wc.jpg</v>
       </c>
       <c r="D92" t="str">
         <v>是</v>
@@ -5791,7 +5791,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>广东广州</v>
+        <v>四川成都</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -5841,7 +5841,7 @@
         <v>弟弟</v>
       </c>
       <c r="C93" t="str">
-        <v>assets/1787318609722-0ojb3aikwi.jpg</v>
+        <v>assets/1787318867999-3gxdddp72x.jpg</v>
       </c>
       <c r="D93" t="str">
         <v>是</v>
@@ -5850,7 +5850,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>黑龙江鹤岗</v>
+        <v>广东广州</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -5894,13 +5894,13 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>蓝虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B94" t="str">
         <v>弟弟</v>
       </c>
       <c r="C94" t="str">
-        <v>assets/1787318530612-779fbkfcoi.jpg</v>
+        <v>assets/1787318609722-0ojb3aikwi.jpg</v>
       </c>
       <c r="D94" t="str">
         <v>是</v>
@@ -5909,7 +5909,7 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>天津</v>
+        <v>黑龙江鹤岗</v>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -5953,13 +5953,13 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B95" t="str">
         <v>弟弟</v>
       </c>
       <c r="C95" t="str">
-        <v>assets/1787318365475-sj87wtsai3.jpg</v>
+        <v>assets/1787318530612-779fbkfcoi.jpg</v>
       </c>
       <c r="D95" t="str">
         <v>是</v>
@@ -5968,7 +5968,7 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>山西朔州</v>
+        <v>天津</v>
       </c>
       <c r="G95" t="str">
         <v/>
@@ -5998,7 +5998,7 @@
         <v/>
       </c>
       <c r="P95" t="str">
-        <v>已接猫</v>
+        <v/>
       </c>
       <c r="Q95" t="str">
         <v/>
@@ -6015,10 +6015,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B96" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C96" t="str">
-        <v>assets/1787318326155-ia4noopjhq.jpg</v>
+        <v>assets/1787318365475-sj87wtsai3.jpg</v>
       </c>
       <c r="D96" t="str">
         <v>是</v>
@@ -6027,7 +6027,7 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>贵州</v>
+        <v>山西朔州</v>
       </c>
       <c r="G96" t="str">
         <v/>
@@ -6057,7 +6057,7 @@
         <v/>
       </c>
       <c r="P96" t="str">
-        <v/>
+        <v>已接猫</v>
       </c>
       <c r="Q96" t="str">
         <v/>
@@ -6071,22 +6071,22 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B97" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C97" t="str">
-        <v>assets/1787304479674-w0trechn4p.jpg</v>
+        <v>assets/1787318326155-ia4noopjhq.jpg</v>
       </c>
       <c r="D97" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E97" t="str">
-        <v>2026-06-06</v>
+        <v/>
       </c>
       <c r="F97" t="str">
-        <v/>
+        <v>贵州</v>
       </c>
       <c r="G97" t="str">
         <v/>
@@ -6125,24 +6125,24 @@
         <v/>
       </c>
       <c r="S97" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>纯黑色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B98" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C98" t="str">
-        <v>assets/1787283819124-4v7d1w01la.jpg</v>
+        <v>assets/1787304479674-w0trechn4p.jpg</v>
       </c>
       <c r="D98" t="str">
         <v>否</v>
       </c>
       <c r="E98" t="str">
-        <v>2026-02-20</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F98" t="str">
         <v/>
@@ -6189,19 +6189,19 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>阴影色NS12</v>
+        <v>纯黑色</v>
       </c>
       <c r="B99" t="str">
         <v>妹妹</v>
       </c>
       <c r="C99" t="str">
-        <v>assets/1787283212708-jdnyi6ecci.jpg</v>
+        <v>assets/1787283819124-4v7d1w01la.jpg</v>
       </c>
       <c r="D99" t="str">
         <v>否</v>
       </c>
       <c r="E99" t="str">
-        <v>2026-05-28</v>
+        <v>2026-02-20</v>
       </c>
       <c r="F99" t="str">
         <v/>
@@ -6248,22 +6248,22 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>阴影色NS11</v>
+        <v>阴影色NS12</v>
       </c>
       <c r="B100" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C100" t="str">
-        <v>assets/1787283153501-s2tjg9spwu.jpg</v>
+        <v>assets/1787283212708-jdnyi6ecci.jpg</v>
       </c>
       <c r="D100" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E100" t="str">
-        <v>2026-06-15</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F100" t="str">
-        <v>重庆</v>
+        <v/>
       </c>
       <c r="G100" t="str">
         <v/>
@@ -6307,22 +6307,22 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>浅烟灰色</v>
+        <v>阴影色NS11</v>
       </c>
       <c r="B101" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C101" t="str">
-        <v>assets/1787283092677-i4d8tyrjtf.jpg</v>
+        <v>assets/1787283153501-s2tjg9spwu.jpg</v>
       </c>
       <c r="D101" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E101" t="str">
-        <v>2026-03-21</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F101" t="str">
-        <v/>
+        <v>重庆</v>
       </c>
       <c r="G101" t="str">
         <v/>
@@ -6366,19 +6366,19 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>棕虎斑</v>
+        <v>浅烟灰色</v>
       </c>
       <c r="B102" t="str">
         <v>妹妹</v>
       </c>
       <c r="C102" t="str">
-        <v>assets/1787283031104-bpyq9wy2tl.jpg</v>
+        <v>assets/1787283092677-i4d8tyrjtf.jpg</v>
       </c>
       <c r="D102" t="str">
         <v>否</v>
       </c>
       <c r="E102" t="str">
-        <v>2026-06-06</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F102" t="str">
         <v/>
@@ -6431,7 +6431,7 @@
         <v>妹妹</v>
       </c>
       <c r="C103" t="str">
-        <v>assets/1787282991501-2fjfws0rqw.jpg</v>
+        <v>assets/1787283031104-bpyq9wy2tl.jpg</v>
       </c>
       <c r="D103" t="str">
         <v>否</v>
@@ -6490,13 +6490,13 @@
         <v>妹妹</v>
       </c>
       <c r="C104" t="str">
-        <v>assets/1787282942262-syr48fym6c.jpg</v>
+        <v>assets/1787282991501-2fjfws0rqw.jpg</v>
       </c>
       <c r="D104" t="str">
         <v>否</v>
       </c>
       <c r="E104" t="str">
-        <v>2026-06-15</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F104" t="str">
         <v/>
@@ -6546,16 +6546,16 @@
         <v>棕虎斑</v>
       </c>
       <c r="B105" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C105" t="str">
-        <v>assets/1787282819855-7vhx3m0v40.jpg</v>
+        <v>assets/1787282942262-syr48fym6c.jpg</v>
       </c>
       <c r="D105" t="str">
         <v>否</v>
       </c>
       <c r="E105" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F105" t="str">
         <v/>
@@ -6605,10 +6605,10 @@
         <v>棕虎斑</v>
       </c>
       <c r="B106" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C106" t="str">
-        <v>assets/1787282703381-2uakw592b4.jpg</v>
+        <v>assets/1787282819855-7vhx3m0v40.jpg</v>
       </c>
       <c r="D106" t="str">
         <v>否</v>
@@ -6661,13 +6661,13 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B107" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C107" t="str">
-        <v>assets/1787282649397-9hc31ncrpc.jpg</v>
+        <v>assets/1787282703381-2uakw592b4.jpg</v>
       </c>
       <c r="D107" t="str">
         <v>否</v>
@@ -6723,10 +6723,10 @@
         <v>烟灰色</v>
       </c>
       <c r="B108" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C108" t="str">
-        <v>assets/1787282617957-svcoyyznpg.jpg</v>
+        <v>assets/1787282649397-9hc31ncrpc.jpg</v>
       </c>
       <c r="D108" t="str">
         <v>否</v>
@@ -6782,10 +6782,10 @@
         <v>烟灰色</v>
       </c>
       <c r="B109" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C109" t="str">
-        <v>assets/1787282419632-78nixqjzua.jpg</v>
+        <v>assets/1787282617957-svcoyyznpg.jpg</v>
       </c>
       <c r="D109" t="str">
         <v>否</v>
@@ -6838,19 +6838,19 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>纯黑色</v>
+        <v>烟灰色</v>
       </c>
       <c r="B110" t="str">
         <v>弟弟</v>
       </c>
       <c r="C110" t="str">
-        <v>assets/1787282349942-2cfuyn7xlc.jpg</v>
+        <v>assets/1787282419632-78nixqjzua.jpg</v>
       </c>
       <c r="D110" t="str">
         <v>否</v>
       </c>
       <c r="E110" t="str">
-        <v>2026-03-21</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F110" t="str">
         <v/>
@@ -6897,19 +6897,19 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>银虎斑</v>
+        <v>纯黑色</v>
       </c>
       <c r="B111" t="str">
         <v>弟弟</v>
       </c>
       <c r="C111" t="str">
-        <v>assets/1787282064159-6b4z8c5msd.jpg</v>
+        <v>assets/1787282349942-2cfuyn7xlc.jpg</v>
       </c>
       <c r="D111" t="str">
         <v>否</v>
       </c>
       <c r="E111" t="str">
-        <v>2026-06-10</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F111" t="str">
         <v/>
@@ -6956,19 +6956,19 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>阴影色NS11</v>
+        <v>银虎斑</v>
       </c>
       <c r="B112" t="str">
         <v>弟弟</v>
       </c>
       <c r="C112" t="str">
-        <v>assets/1787280590041-vzcwebdok1.jpg</v>
+        <v>assets/1787282064159-6b4z8c5msd.jpg</v>
       </c>
       <c r="D112" t="str">
         <v>否</v>
       </c>
       <c r="E112" t="str">
-        <v>2026-05-28</v>
+        <v>2026-06-10</v>
       </c>
       <c r="F112" t="str">
         <v/>
@@ -7015,19 +7015,19 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>浅色银虎斑</v>
+        <v>阴影色NS11</v>
       </c>
       <c r="B113" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C113" t="str">
-        <v>assets/1787281786169-9ia0h837ct.jpg</v>
+        <v>assets/1787280590041-vzcwebdok1.jpg</v>
       </c>
       <c r="D113" t="str">
         <v>否</v>
       </c>
       <c r="E113" t="str">
-        <v>2026-06-15</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F113" t="str">
         <v/>
@@ -7074,22 +7074,22 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>浅烟灰色</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B114" t="str">
         <v>妹妹</v>
       </c>
       <c r="C114" t="str">
-        <v>assets/1785843720843-63qz159daui.jpg</v>
+        <v>assets/1787281786169-9ia0h837ct.jpg</v>
       </c>
       <c r="D114" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E114" t="str">
-        <v>2026-03-21</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F114" t="str">
-        <v>四川成都</v>
+        <v/>
       </c>
       <c r="G114" t="str">
         <v/>
@@ -7133,22 +7133,22 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>凯米尔色</v>
+        <v>浅烟灰色</v>
       </c>
       <c r="B115" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C115" t="str">
-        <v>assets/1787301984056-iu6afro5z5.jpg, assets/1785843763310-elg05ur61ri.jpg</v>
+        <v>assets/1785843720843-63qz159daui.jpg</v>
       </c>
       <c r="D115" t="str">
         <v>是</v>
       </c>
       <c r="E115" t="str">
-        <v>2026-02-14</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F115" t="str">
-        <v>上海浦东</v>
+        <v>四川成都</v>
       </c>
       <c r="G115" t="str">
         <v/>
@@ -7192,22 +7192,22 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>银虎斑补丁</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B116" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C116" t="str">
-        <v>assets/1785843820715-9kz7gy4mbr7.jpg</v>
+        <v>assets/1787301984056-iu6afro5z5.jpg, assets/1785843763310-elg05ur61ri.jpg</v>
       </c>
       <c r="D116" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E116" t="str">
-        <v>2026-03-05</v>
+        <v>2026-02-14</v>
       </c>
       <c r="F116" t="str">
-        <v/>
+        <v>上海浦东</v>
       </c>
       <c r="G116" t="str">
         <v/>
@@ -7251,19 +7251,19 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>烟灰色</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B117" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C117" t="str">
-        <v>assets/1785843953805-mxl3x1982io.jpg</v>
+        <v>assets/1785843820715-9kz7gy4mbr7.jpg</v>
       </c>
       <c r="D117" t="str">
         <v>否</v>
       </c>
       <c r="E117" t="str">
-        <v>2026-05-18</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F117" t="str">
         <v/>
@@ -7310,19 +7310,19 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>棕虎斑玳瑁</v>
+        <v>烟灰色</v>
       </c>
       <c r="B118" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C118" t="str">
-        <v>assets/1785844013835-ek4xpcje7kh.jpg</v>
+        <v>assets/1785843953805-mxl3x1982io.jpg</v>
       </c>
       <c r="D118" t="str">
         <v>否</v>
       </c>
       <c r="E118" t="str">
-        <v>2026-02-14</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F118" t="str">
         <v/>
@@ -7369,19 +7369,19 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>银虎斑补丁</v>
+        <v>棕虎斑玳瑁</v>
       </c>
       <c r="B119" t="str">
         <v>妹妹</v>
       </c>
       <c r="C119" t="str">
-        <v>assets/1785844434338-ek5zbdgdcne.jpg</v>
+        <v>assets/1785844013835-ek4xpcje7kh.jpg</v>
       </c>
       <c r="D119" t="str">
         <v>否</v>
       </c>
       <c r="E119" t="str">
-        <v>2026-05-24</v>
+        <v>2026-02-14</v>
       </c>
       <c r="F119" t="str">
         <v/>
@@ -7428,22 +7428,22 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>银虎斑</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B120" t="str">
         <v>妹妹</v>
       </c>
       <c r="C120" t="str">
-        <v>assets/1785838787730-s5f333sc3u.jpg</v>
+        <v>assets/1785844434338-ek5zbdgdcne.jpg</v>
       </c>
       <c r="D120" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E120" t="str">
-        <v>2026-06-05</v>
+        <v>2026-05-24</v>
       </c>
       <c r="F120" t="str">
-        <v>湖北恩施</v>
+        <v/>
       </c>
       <c r="G120" t="str">
         <v/>
@@ -7490,10 +7490,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B121" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C121" t="str">
-        <v>assets/1785842296661-6qw3zs3as8h.jpg</v>
+        <v>assets/1785838787730-s5f333sc3u.jpg</v>
       </c>
       <c r="D121" t="str">
         <v>是</v>
@@ -7552,16 +7552,16 @@
         <v>弟弟</v>
       </c>
       <c r="C122" t="str">
-        <v>assets/1785842429109-porc98rel5.jpg</v>
+        <v>assets/1785842296661-6qw3zs3as8h.jpg</v>
       </c>
       <c r="D122" t="str">
         <v>是</v>
       </c>
       <c r="E122" t="str">
-        <v>2025-11-05</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F122" t="str">
-        <v>韩国</v>
+        <v>湖北恩施</v>
       </c>
       <c r="G122" t="str">
         <v/>
@@ -7608,19 +7608,19 @@
         <v>银虎斑</v>
       </c>
       <c r="B123" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C123" t="str">
-        <v>assets/1785842594141-fcglbzjp509.jpg</v>
+        <v>assets/1785842429109-porc98rel5.jpg</v>
       </c>
       <c r="D123" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E123" t="str">
-        <v>2026-05-18</v>
+        <v>2025-11-05</v>
       </c>
       <c r="F123" t="str">
-        <v/>
+        <v>韩国</v>
       </c>
       <c r="G123" t="str">
         <v/>
@@ -7664,22 +7664,22 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B124" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C124" t="str">
-        <v>assets/1785842639100-82k775dhwiv.jpg</v>
+        <v>assets/1785842594141-fcglbzjp509.jpg</v>
       </c>
       <c r="D124" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E124" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F124" t="str">
-        <v>四川自贡</v>
+        <v/>
       </c>
       <c r="G124" t="str">
         <v/>
@@ -7726,19 +7726,19 @@
         <v>棕虎斑</v>
       </c>
       <c r="B125" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C125" t="str">
-        <v>assets/1785842684502-mnhr0r96eee.jpg</v>
+        <v>assets/1785842639100-82k775dhwiv.jpg</v>
       </c>
       <c r="D125" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E125" t="str">
-        <v>2026-06-06</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F125" t="str">
-        <v/>
+        <v>四川自贡</v>
       </c>
       <c r="G125" t="str">
         <v/>
@@ -7782,19 +7782,19 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>纯黑色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B126" t="str">
         <v>妹妹</v>
       </c>
       <c r="C126" t="str">
-        <v>assets/1785842779532-5u1j0igrw1s.jpg</v>
+        <v>assets/1785842684502-mnhr0r96eee.jpg</v>
       </c>
       <c r="D126" t="str">
         <v>否</v>
       </c>
       <c r="E126" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F126" t="str">
         <v/>
@@ -7841,22 +7841,22 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>银虎斑</v>
+        <v>纯黑色</v>
       </c>
       <c r="B127" t="str">
         <v>妹妹</v>
       </c>
       <c r="C127" t="str">
-        <v>assets/1785842817046-6keqv4rw4yf.jpg</v>
+        <v>assets/1785842779532-5u1j0igrw1s.jpg</v>
       </c>
       <c r="D127" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E127" t="str">
         <v>2026-03-05</v>
       </c>
       <c r="F127" t="str">
-        <v>韩国</v>
+        <v/>
       </c>
       <c r="G127" t="str">
         <v/>
@@ -7900,22 +7900,22 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>浅色银虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B128" t="str">
         <v>妹妹</v>
       </c>
       <c r="C128" t="str">
-        <v>assets/1785842950972-a88lbrskpc.jpg</v>
+        <v>assets/1785842817046-6keqv4rw4yf.jpg</v>
       </c>
       <c r="D128" t="str">
         <v>是</v>
       </c>
       <c r="E128" t="str">
-        <v>2026-06-05</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F128" t="str">
-        <v>河北邢台</v>
+        <v>韩国</v>
       </c>
       <c r="G128" t="str">
         <v/>
@@ -7959,13 +7959,13 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>棕虎斑</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B129" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C129" t="str">
-        <v>assets/1785843011477-n3l1wi6ech.jpg</v>
+        <v>assets/1785842950972-a88lbrskpc.jpg</v>
       </c>
       <c r="D129" t="str">
         <v>是</v>
@@ -7974,7 +7974,7 @@
         <v>2026-06-05</v>
       </c>
       <c r="F129" t="str">
-        <v>四川自贡</v>
+        <v>河北邢台</v>
       </c>
       <c r="G129" t="str">
         <v/>
@@ -8018,22 +8018,22 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B130" t="str">
         <v>弟弟</v>
       </c>
       <c r="C130" t="str">
-        <v>assets/1785843237517-ga449iqess5.jpg</v>
+        <v>assets/1785843011477-n3l1wi6ech.jpg</v>
       </c>
       <c r="D130" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E130" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F130" t="str">
-        <v/>
+        <v>四川自贡</v>
       </c>
       <c r="G130" t="str">
         <v/>
@@ -8077,13 +8077,13 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>棕虎斑补丁</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B131" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C131" t="str">
-        <v>assets/1785842523893-7nwnnhwi4ns.jpg</v>
+        <v>assets/1785843237517-ga449iqess5.jpg</v>
       </c>
       <c r="D131" t="str">
         <v>否</v>
@@ -8136,19 +8136,19 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎斑补丁</v>
       </c>
       <c r="B132" t="str">
         <v>妹妹</v>
       </c>
       <c r="C132" t="str">
-        <v>assets/1785843497557-st27fk8drqi.jpg</v>
+        <v>assets/1785842523893-7nwnnhwi4ns.jpg</v>
       </c>
       <c r="D132" t="str">
         <v>否</v>
       </c>
       <c r="E132" t="str">
-        <v>2026-04-05</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F132" t="str">
         <v/>
@@ -8195,19 +8195,19 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B133" t="str">
         <v>妹妹</v>
       </c>
       <c r="C133" t="str">
-        <v>assets/1785843621923-ylhakbtw13i.jpg</v>
+        <v>assets/1785843497557-st27fk8drqi.jpg</v>
       </c>
       <c r="D133" t="str">
         <v>否</v>
       </c>
       <c r="E133" t="str">
-        <v>2026-03-05</v>
+        <v>2026-04-05</v>
       </c>
       <c r="F133" t="str">
         <v/>
@@ -8260,7 +8260,7 @@
         <v>妹妹</v>
       </c>
       <c r="C134" t="str">
-        <v>assets/1785843663884-sfxvpmiet7.jpg</v>
+        <v>assets/1785843621923-ylhakbtw13i.jpg</v>
       </c>
       <c r="D134" t="str">
         <v>否</v>
@@ -8313,52 +8313,52 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>蓝虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B135" t="str">
         <v>妹妹</v>
       </c>
       <c r="C135" t="str">
-        <v>assets/1785852601940-o236xtv7yx.jpeg</v>
+        <v>assets/1785843663884-sfxvpmiet7.jpg</v>
       </c>
       <c r="D135" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E135" t="str">
-        <v>2026-02-20</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F135" t="str">
-        <v>荷兰</v>
+        <v/>
       </c>
       <c r="G135" t="str">
-        <v>阿泽</v>
+        <v/>
       </c>
       <c r="H135" t="str">
-        <v>小辫子</v>
+        <v/>
       </c>
       <c r="I135" t="str">
-        <v>驺驺</v>
+        <v/>
       </c>
       <c r="J135" t="str">
-        <v>2026-07-02</v>
+        <v/>
       </c>
       <c r="K135" t="str">
         <v/>
       </c>
       <c r="L135" t="str">
-        <v>2026-07-02</v>
+        <v/>
       </c>
       <c r="M135" t="str">
-        <v>2026-08-03</v>
+        <v/>
       </c>
       <c r="N135" t="str">
-        <v>2026-11-04</v>
+        <v/>
       </c>
       <c r="O135" t="str">
-        <v>2026-08-03 · 血清检测,2026-07-02 · 打疫苗 · assets/diary/zouzou-depart.jpg,2026-07-30 · 6.2斤 · 五个月10天了 · assets/feedback/zouzou-1.jpg</v>
+        <v/>
       </c>
       <c r="P135" t="str">
-        <v>已付定金</v>
+        <v/>
       </c>
       <c r="Q135" t="str">
         <v/>
@@ -8367,57 +8367,57 @@
         <v/>
       </c>
       <c r="S135" t="str">
-        <v>否</v>
+        <v/>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>红虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B136" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C136" t="str">
-        <v>assets/1785853950207-cedor66ou2q.jpeg</v>
+        <v>assets/1785852601940-o236xtv7yx.jpeg</v>
       </c>
       <c r="D136" t="str">
         <v>是</v>
       </c>
       <c r="E136" t="str">
-        <v/>
+        <v>2026-02-20</v>
       </c>
       <c r="F136" t="str">
-        <v>广东广州</v>
+        <v>荷兰</v>
       </c>
       <c r="G136" t="str">
-        <v/>
+        <v>阿泽</v>
       </c>
       <c r="H136" t="str">
-        <v/>
+        <v>小辫子</v>
       </c>
       <c r="I136" t="str">
-        <v/>
+        <v>驺驺</v>
       </c>
       <c r="J136" t="str">
-        <v/>
+        <v>2026-07-02</v>
       </c>
       <c r="K136" t="str">
         <v/>
       </c>
       <c r="L136" t="str">
-        <v/>
+        <v>2026-07-02</v>
       </c>
       <c r="M136" t="str">
-        <v/>
+        <v>2026-08-03</v>
       </c>
       <c r="N136" t="str">
-        <v/>
+        <v>2026-11-04</v>
       </c>
       <c r="O136" t="str">
-        <v/>
+        <v>2026-08-03 · 血清检测,2026-07-02 · 打疫苗 · assets/diary/zouzou-depart.jpg,2026-07-30 · 6.2斤 · 五个月10天了 · assets/feedback/zouzou-1.jpg</v>
       </c>
       <c r="P136" t="str">
-        <v/>
+        <v>已付定金</v>
       </c>
       <c r="Q136" t="str">
         <v/>
@@ -8426,7 +8426,7 @@
         <v/>
       </c>
       <c r="S136" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="137">
@@ -8437,7 +8437,7 @@
         <v>弟弟</v>
       </c>
       <c r="C137" t="str">
-        <v>assets/1785854129383-c8qkvl537x.jpeg</v>
+        <v>assets/1785853950207-cedor66ou2q.jpeg</v>
       </c>
       <c r="D137" t="str">
         <v>是</v>
@@ -8490,13 +8490,13 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B138" t="str">
         <v>弟弟</v>
       </c>
       <c r="C138" t="str">
-        <v>assets/1785854166720-48r17hry9cd.jpeg</v>
+        <v>assets/1785854129383-c8qkvl537x.jpeg</v>
       </c>
       <c r="D138" t="str">
         <v>是</v>
@@ -8505,7 +8505,7 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>山西朔州</v>
+        <v>广东广州</v>
       </c>
       <c r="G138" t="str">
         <v/>
@@ -8552,10 +8552,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B139" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C139" t="str">
-        <v>assets/1785854224521-2cpg6xipfn6.jpeg</v>
+        <v>assets/1785854166720-48r17hry9cd.jpeg</v>
       </c>
       <c r="D139" t="str">
         <v>是</v>
@@ -8564,7 +8564,7 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>浙江宁波</v>
+        <v>山西朔州</v>
       </c>
       <c r="G139" t="str">
         <v/>
@@ -8611,10 +8611,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B140" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C140" t="str">
-        <v>assets/1785854260793-steez4s972l.jpeg</v>
+        <v>assets/1785854224521-2cpg6xipfn6.jpeg</v>
       </c>
       <c r="D140" t="str">
         <v>是</v>
@@ -8623,7 +8623,7 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>陕西西安</v>
+        <v>浙江宁波</v>
       </c>
       <c r="G140" t="str">
         <v/>
@@ -8673,7 +8673,7 @@
         <v>弟弟</v>
       </c>
       <c r="C141" t="str">
-        <v>assets/1785854319988-cohio08aod5.jpeg</v>
+        <v>assets/1785854260793-steez4s972l.jpeg</v>
       </c>
       <c r="D141" t="str">
         <v>是</v>
@@ -8682,7 +8682,7 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>黑龙江漠河</v>
+        <v>陕西西安</v>
       </c>
       <c r="G141" t="str">
         <v/>
@@ -8726,13 +8726,13 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B142" t="str">
         <v>弟弟</v>
       </c>
       <c r="C142" t="str">
-        <v>assets/1785854520974-96b8b1ekqd9.jpeg</v>
+        <v>assets/1785854319988-cohio08aod5.jpeg</v>
       </c>
       <c r="D142" t="str">
         <v>是</v>
@@ -8741,7 +8741,7 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>日本</v>
+        <v>黑龙江漠河</v>
       </c>
       <c r="G142" t="str">
         <v/>
@@ -8785,13 +8785,13 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B143" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C143" t="str">
-        <v>assets/1785854664100-haqoiu1h7hj.jpeg</v>
+        <v>assets/1785854520974-96b8b1ekqd9.jpeg</v>
       </c>
       <c r="D143" t="str">
         <v>是</v>
@@ -8800,7 +8800,7 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>浙江杭州</v>
+        <v>日本</v>
       </c>
       <c r="G143" t="str">
         <v/>
@@ -8850,7 +8850,7 @@
         <v>妹妹</v>
       </c>
       <c r="C144" t="str">
-        <v>assets/1785854690732-orrs40sx9rs.jpeg</v>
+        <v>assets/1785854664100-haqoiu1h7hj.jpeg</v>
       </c>
       <c r="D144" t="str">
         <v>是</v>
@@ -8859,7 +8859,7 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>贵州安顺</v>
+        <v>浙江杭州</v>
       </c>
       <c r="G144" t="str">
         <v/>
@@ -8909,7 +8909,7 @@
         <v>妹妹</v>
       </c>
       <c r="C145" t="str">
-        <v>assets/1785854734122-wcpmib4m7.jpeg</v>
+        <v>assets/1785854690732-orrs40sx9rs.jpeg</v>
       </c>
       <c r="D145" t="str">
         <v>是</v>
@@ -8918,7 +8918,7 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>山东青岛</v>
+        <v>贵州安顺</v>
       </c>
       <c r="G145" t="str">
         <v/>
@@ -8965,10 +8965,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B146" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C146" t="str">
-        <v>assets/1785854758707-1kxdkfvs6jc.jpeg</v>
+        <v>assets/1785854734122-wcpmib4m7.jpeg</v>
       </c>
       <c r="D146" t="str">
         <v>是</v>
@@ -8977,7 +8977,7 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>黑龙江漠河</v>
+        <v>山东青岛</v>
       </c>
       <c r="G146" t="str">
         <v/>
@@ -9021,13 +9021,13 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>纯蓝色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B147" t="str">
         <v>弟弟</v>
       </c>
       <c r="C147" t="str">
-        <v>assets/1785854784780-3g0u60pdo93.jpeg</v>
+        <v>assets/1785854758707-1kxdkfvs6jc.jpeg</v>
       </c>
       <c r="D147" t="str">
         <v>是</v>
@@ -9036,7 +9036,7 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>河南鹤壁</v>
+        <v>黑龙江漠河</v>
       </c>
       <c r="G147" t="str">
         <v/>
@@ -9080,13 +9080,13 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>银虎斑</v>
+        <v>纯蓝色</v>
       </c>
       <c r="B148" t="str">
         <v>弟弟</v>
       </c>
       <c r="C148" t="str">
-        <v>assets/1785854813179-8oyxr0h2bbu.jpeg</v>
+        <v>assets/1785854784780-3g0u60pdo93.jpeg</v>
       </c>
       <c r="D148" t="str">
         <v>是</v>
@@ -9095,7 +9095,7 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>陕西西安</v>
+        <v>河南鹤壁</v>
       </c>
       <c r="G148" t="str">
         <v/>
@@ -9139,13 +9139,13 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B149" t="str">
         <v>弟弟</v>
       </c>
       <c r="C149" t="str">
-        <v>assets/1785854838933-uq6amircyzd.jpeg</v>
+        <v>assets/1785854813179-8oyxr0h2bbu.jpeg</v>
       </c>
       <c r="D149" t="str">
         <v>是</v>
@@ -9154,7 +9154,7 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>四川成都</v>
+        <v>陕西西安</v>
       </c>
       <c r="G149" t="str">
         <v/>
@@ -9198,22 +9198,22 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B150" t="str">
         <v>弟弟</v>
       </c>
       <c r="C150" t="str">
-        <v>assets/1785854869973-za3p6wikqpo.jpeg</v>
+        <v>assets/1785854838933-uq6amircyzd.jpeg</v>
       </c>
       <c r="D150" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E150" t="str">
-        <v>2026-05-18</v>
+        <v/>
       </c>
       <c r="F150" t="str">
-        <v/>
+        <v>四川成都</v>
       </c>
       <c r="G150" t="str">
         <v/>
@@ -9257,22 +9257,22 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B151" t="str">
         <v>弟弟</v>
       </c>
       <c r="C151" t="str">
-        <v>assets/1785854997023-mawkallt2a.jpeg</v>
+        <v>assets/1785854869973-za3p6wikqpo.jpeg</v>
       </c>
       <c r="D151" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E151" t="str">
-        <v/>
+        <v>2026-05-18</v>
       </c>
       <c r="F151" t="str">
-        <v>新加坡</v>
+        <v/>
       </c>
       <c r="G151" t="str">
         <v/>
@@ -9316,13 +9316,13 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>凯米尔色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B152" t="str">
         <v>弟弟</v>
       </c>
       <c r="C152" t="str">
-        <v>assets/1785855043327-wdc5pxwm34k.jpeg</v>
+        <v>assets/1785854997023-mawkallt2a.jpeg</v>
       </c>
       <c r="D152" t="str">
         <v>是</v>
@@ -9331,7 +9331,7 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>上海浦东</v>
+        <v>新加坡</v>
       </c>
       <c r="G152" t="str">
         <v/>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>棕虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B153" t="str">
         <v>弟弟</v>
       </c>
       <c r="C153" t="str">
-        <v>assets/1785912551260-jplefm937nk.jpeg, assets/videos/02.mp4</v>
+        <v>assets/1785855043327-wdc5pxwm34k.jpeg</v>
       </c>
       <c r="D153" t="str">
         <v>是</v>
       </c>
       <c r="E153" t="str">
-        <v>2026-06-06</v>
+        <v/>
       </c>
       <c r="F153" t="str">
-        <v>浙江温州</v>
+        <v>上海浦东</v>
       </c>
       <c r="G153" t="str">
         <v/>
@@ -9437,19 +9437,19 @@
         <v>棕虎斑</v>
       </c>
       <c r="B154" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C154" t="str">
-        <v>assets/1785912694000-m20f5kvvrr.jpeg</v>
+        <v>assets/1785912551260-jplefm937nk.jpeg, assets/videos/02.mp4</v>
       </c>
       <c r="D154" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E154" t="str">
         <v>2026-06-06</v>
       </c>
       <c r="F154" t="str">
-        <v/>
+        <v>浙江温州</v>
       </c>
       <c r="G154" t="str">
         <v/>
@@ -9488,12 +9488,71 @@
         <v/>
       </c>
       <c r="S154" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>棕虎斑</v>
+      </c>
+      <c r="B155" t="str">
+        <v>妹妹</v>
+      </c>
+      <c r="C155" t="str">
+        <v>assets/1785912694000-m20f5kvvrr.jpeg</v>
+      </c>
+      <c r="D155" t="str">
+        <v>否</v>
+      </c>
+      <c r="E155" t="str">
+        <v>2026-06-06</v>
+      </c>
+      <c r="F155" t="str">
+        <v/>
+      </c>
+      <c r="G155" t="str">
+        <v/>
+      </c>
+      <c r="H155" t="str">
+        <v/>
+      </c>
+      <c r="I155" t="str">
+        <v/>
+      </c>
+      <c r="J155" t="str">
+        <v/>
+      </c>
+      <c r="K155" t="str">
+        <v/>
+      </c>
+      <c r="L155" t="str">
+        <v/>
+      </c>
+      <c r="M155" t="str">
+        <v/>
+      </c>
+      <c r="N155" t="str">
+        <v/>
+      </c>
+      <c r="O155" t="str">
+        <v/>
+      </c>
+      <c r="P155" t="str">
+        <v/>
+      </c>
+      <c r="Q155" t="str">
+        <v/>
+      </c>
+      <c r="R155" t="str">
+        <v/>
+      </c>
+      <c r="S155" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S154"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S155"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S155"/>
+  <dimension ref="A1:S157"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -469,19 +469,19 @@
         <v>棕虎斑</v>
       </c>
       <c r="B2" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C2" t="str">
-        <v>assets/1787466121255-21jto2cugv.jpg</v>
+        <v>assets/1787479268842-7en9nzy302.jpg</v>
       </c>
       <c r="D2" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E2" t="str">
-        <v/>
+        <v>2026-06-10</v>
       </c>
       <c r="F2" t="str">
-        <v>四川广安</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -493,7 +493,7 @@
         <v/>
       </c>
       <c r="J2" t="str">
-        <v/>
+        <v>2026-06-10</v>
       </c>
       <c r="K2" t="str">
         <v/>
@@ -525,19 +525,19 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>烟灰色</v>
+        <v>纯黑色</v>
       </c>
       <c r="B3" t="str">
         <v>妹妹</v>
       </c>
       <c r="C3" t="str">
-        <v>assets/1787388322060-uj8bkwqgnv.jpg</v>
+        <v>assets/1787479242639-32zuh5lham.jpg</v>
       </c>
       <c r="D3" t="str">
         <v>否</v>
       </c>
       <c r="E3" t="str">
-        <v>2026-06-06</v>
+        <v/>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -552,7 +552,7 @@
         <v/>
       </c>
       <c r="J3" t="str">
-        <v/>
+        <v>2026-06-10</v>
       </c>
       <c r="K3" t="str">
         <v/>
@@ -590,16 +590,16 @@
         <v>妹妹</v>
       </c>
       <c r="C4" t="str">
-        <v>assets/1787388277490-e6u506cx0r.jpg</v>
+        <v>assets/1787466121255-21jto2cugv.jpg</v>
       </c>
       <c r="D4" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E4" t="str">
-        <v>2026-06-06</v>
+        <v/>
       </c>
       <c r="F4" t="str">
-        <v/>
+        <v>四川广安</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -643,22 +643,22 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B5" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C5" t="str">
-        <v>assets/1787328436957-x30od0gw28.jpg</v>
+        <v>assets/1787388322060-uj8bkwqgnv.jpg</v>
       </c>
       <c r="D5" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E5" t="str">
-        <v/>
+        <v>2026-06-06</v>
       </c>
       <c r="F5" t="str">
-        <v>江苏苏州</v>
+        <v/>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -702,22 +702,22 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B6" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C6" t="str">
-        <v>assets/1787328420967-viv9v8nbjn.jpg</v>
+        <v>assets/1787388277490-e6u506cx0r.jpg</v>
       </c>
       <c r="D6" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E6" t="str">
-        <v/>
+        <v>2026-06-06</v>
       </c>
       <c r="F6" t="str">
-        <v>辽宁东港</v>
+        <v/>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -761,13 +761,13 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B7" t="str">
         <v>弟弟</v>
       </c>
       <c r="C7" t="str">
-        <v>assets/1787327967245-m62ohievcl.jpg</v>
+        <v>assets/1787328436957-x30od0gw28.jpg</v>
       </c>
       <c r="D7" t="str">
         <v>是</v>
@@ -776,7 +776,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>福建福州</v>
+        <v>江苏苏州</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -826,7 +826,7 @@
         <v>弟弟</v>
       </c>
       <c r="C8" t="str">
-        <v>assets/1787327853521-js8ljh3ulj.jpg</v>
+        <v>assets/1787328420967-viv9v8nbjn.jpg</v>
       </c>
       <c r="D8" t="str">
         <v>是</v>
@@ -835,7 +835,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>上海</v>
+        <v>辽宁东港</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -879,13 +879,13 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>纯蓝色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B9" t="str">
         <v>弟弟</v>
       </c>
       <c r="C9" t="str">
-        <v>assets/1787327793837-znk2knoo6p.jpg</v>
+        <v>assets/1787327967245-m62ohievcl.jpg</v>
       </c>
       <c r="D9" t="str">
         <v>是</v>
@@ -894,7 +894,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>河南鹤壁</v>
+        <v>福建福州</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -938,13 +938,13 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B10" t="str">
         <v>弟弟</v>
       </c>
       <c r="C10" t="str">
-        <v>assets/1787327752832-kkpmp21os3.jpg</v>
+        <v>assets/1787327853521-js8ljh3ulj.jpg</v>
       </c>
       <c r="D10" t="str">
         <v>是</v>
@@ -953,7 +953,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>陕西西安</v>
+        <v>上海</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -997,13 +997,13 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>银虎斑</v>
+        <v>纯蓝色</v>
       </c>
       <c r="B11" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C11" t="str">
-        <v>assets/1787327605711-4o2f6v6ybp.jpg</v>
+        <v>assets/1787327793837-znk2knoo6p.jpg</v>
       </c>
       <c r="D11" t="str">
         <v>是</v>
@@ -1012,7 +1012,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>陕西西安</v>
+        <v>河南鹤壁</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -1062,7 +1062,7 @@
         <v>弟弟</v>
       </c>
       <c r="C12" t="str">
-        <v>assets/1787327573762-h23cux94p2.jpg</v>
+        <v>assets/1787327752832-kkpmp21os3.jpg</v>
       </c>
       <c r="D12" t="str">
         <v>是</v>
@@ -1071,7 +1071,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>北京</v>
+        <v>陕西西安</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -1121,7 +1121,7 @@
         <v>妹妹</v>
       </c>
       <c r="C13" t="str">
-        <v>assets/1787327496557-9daggljg4g.jpg</v>
+        <v>assets/1787327605711-4o2f6v6ybp.jpg</v>
       </c>
       <c r="D13" t="str">
         <v>是</v>
@@ -1130,7 +1130,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>黑龙江哈尔滨</v>
+        <v>陕西西安</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -1174,13 +1174,13 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>烟灰色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B14" t="str">
         <v>弟弟</v>
       </c>
       <c r="C14" t="str">
-        <v>assets/1787327456560-p4yhq4qvrv.jpg</v>
+        <v>assets/1787327573762-h23cux94p2.jpg</v>
       </c>
       <c r="D14" t="str">
         <v>是</v>
@@ -1189,7 +1189,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>甘肃嘉峪关</v>
+        <v>北京</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -1233,13 +1233,13 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>蓝虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B15" t="str">
         <v>妹妹</v>
       </c>
       <c r="C15" t="str">
-        <v>assets/1787327421713-zg7np4yzkc.jpg</v>
+        <v>assets/1787327496557-9daggljg4g.jpg</v>
       </c>
       <c r="D15" t="str">
         <v>是</v>
@@ -1248,7 +1248,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>安徽合肥</v>
+        <v>黑龙江哈尔滨</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -1292,13 +1292,13 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B16" t="str">
         <v>弟弟</v>
       </c>
       <c r="C16" t="str">
-        <v>assets/1787327337811-u5u2pdew3.jpg</v>
+        <v>assets/1787327456560-p4yhq4qvrv.jpg</v>
       </c>
       <c r="D16" t="str">
         <v>是</v>
@@ -1307,7 +1307,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>安徽合肥</v>
+        <v>甘肃嘉峪关</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1351,13 +1351,13 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>棕虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B17" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C17" t="str">
-        <v>assets/1787327309143-6c1dan1sev.jpg</v>
+        <v>assets/1787327421713-zg7np4yzkc.jpg</v>
       </c>
       <c r="D17" t="str">
         <v>是</v>
@@ -1366,7 +1366,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>四川成都</v>
+        <v>安徽合肥</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1416,7 +1416,7 @@
         <v>弟弟</v>
       </c>
       <c r="C18" t="str">
-        <v>assets/1787327277453-w89ujg69fm.jpg</v>
+        <v>assets/1787327337811-u5u2pdew3.jpg</v>
       </c>
       <c r="D18" t="str">
         <v>是</v>
@@ -1425,7 +1425,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>四川成都</v>
+        <v>安徽合肥</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1469,13 +1469,13 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>蓝银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B19" t="str">
         <v>弟弟</v>
       </c>
       <c r="C19" t="str">
-        <v>assets/1787327232159-lkrcl588a5.jpg</v>
+        <v>assets/1787327309143-6c1dan1sev.jpg</v>
       </c>
       <c r="D19" t="str">
         <v>是</v>
@@ -1528,13 +1528,13 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>玳瑁色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B20" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C20" t="str">
-        <v>assets/1787327182347-3az0z7sys2.jpg</v>
+        <v>assets/1787327277453-w89ujg69fm.jpg</v>
       </c>
       <c r="D20" t="str">
         <v>是</v>
@@ -1543,7 +1543,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>四川内江</v>
+        <v>四川成都</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1587,13 +1587,13 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>棕虎补丁</v>
+        <v>蓝银虎斑</v>
       </c>
       <c r="B21" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C21" t="str">
-        <v>assets/1787327143756-4xtgfy5ozu.jpg</v>
+        <v>assets/1787327232159-lkrcl588a5.jpg</v>
       </c>
       <c r="D21" t="str">
         <v>是</v>
@@ -1602,7 +1602,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>贵州贵阳</v>
+        <v>四川成都</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1646,13 +1646,13 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>黑烟色</v>
+        <v>玳瑁色</v>
       </c>
       <c r="B22" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C22" t="str">
-        <v>assets/1787327101790-tqjlseog5y.jpg</v>
+        <v>assets/1787327182347-3az0z7sys2.jpg</v>
       </c>
       <c r="D22" t="str">
         <v>是</v>
@@ -1661,7 +1661,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>浙江杭州</v>
+        <v>四川内江</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1705,13 +1705,13 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>烟灰色</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B23" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C23" t="str">
-        <v>assets/1787327019632-l1780lu2hj.jpg</v>
+        <v>assets/1787327143756-4xtgfy5ozu.jpg</v>
       </c>
       <c r="D23" t="str">
         <v>是</v>
@@ -1720,7 +1720,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>山东威海</v>
+        <v>贵州贵阳</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1764,13 +1764,13 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>棕虎补丁</v>
+        <v>黑烟色</v>
       </c>
       <c r="B24" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C24" t="str">
-        <v>assets/1787326905275-plz3fpgo97.jpg</v>
+        <v>assets/1787327101790-tqjlseog5y.jpg</v>
       </c>
       <c r="D24" t="str">
         <v>是</v>
@@ -1823,13 +1823,13 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>蓝虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B25" t="str">
         <v>弟弟</v>
       </c>
       <c r="C25" t="str">
-        <v>assets/1787326874462-z9rzs7wg17.jpg</v>
+        <v>assets/1787327019632-l1780lu2hj.jpg</v>
       </c>
       <c r="D25" t="str">
         <v>是</v>
@@ -1838,7 +1838,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>四川成都</v>
+        <v>山东威海</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1882,13 +1882,13 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>凯米尔色</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B26" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C26" t="str">
-        <v>assets/1787326843271-0uhv7b9p89.jpg</v>
+        <v>assets/1787326905275-plz3fpgo97.jpg</v>
       </c>
       <c r="D26" t="str">
         <v>是</v>
@@ -1897,7 +1897,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>四川成都</v>
+        <v>浙江杭州</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1941,13 +1941,13 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>凯米尔</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B27" t="str">
         <v>弟弟</v>
       </c>
       <c r="C27" t="str">
-        <v>assets/1787326814713-p5oavnlulg.jpg</v>
+        <v>assets/1787326874462-z9rzs7wg17.jpg</v>
       </c>
       <c r="D27" t="str">
         <v>是</v>
@@ -2000,13 +2000,13 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>棕虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B28" t="str">
         <v>弟弟</v>
       </c>
       <c r="C28" t="str">
-        <v>assets/1787326773577-13q5out2d0.jpg</v>
+        <v>assets/1787326843271-0uhv7b9p89.jpg</v>
       </c>
       <c r="D28" t="str">
         <v>是</v>
@@ -2015,7 +2015,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>四川宜宾</v>
+        <v>四川成都</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -2059,13 +2059,13 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>金棕虎斑</v>
+        <v>凯米尔</v>
       </c>
       <c r="B29" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C29" t="str">
-        <v>assets/1787326548993-89s929m2hg.jpg</v>
+        <v>assets/1787326814713-p5oavnlulg.jpg</v>
       </c>
       <c r="D29" t="str">
         <v>是</v>
@@ -2074,7 +2074,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>上海</v>
+        <v>四川成都</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -2118,13 +2118,13 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>凯米尔色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B30" t="str">
         <v>弟弟</v>
       </c>
       <c r="C30" t="str">
-        <v>assets/1787326449218-09s9ucram4.jpg</v>
+        <v>assets/1787326773577-13q5out2d0.jpg</v>
       </c>
       <c r="D30" t="str">
         <v>是</v>
@@ -2133,7 +2133,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>德国</v>
+        <v>四川宜宾</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -2177,13 +2177,13 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>棕虎补丁</v>
+        <v>金棕虎斑</v>
       </c>
       <c r="B31" t="str">
         <v>妹妹</v>
       </c>
       <c r="C31" t="str">
-        <v>assets/1787326277374-8ti107m5ki.jpg</v>
+        <v>assets/1787326548993-89s929m2hg.jpg</v>
       </c>
       <c r="D31" t="str">
         <v>是</v>
@@ -2192,7 +2192,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>广东深圳</v>
+        <v>上海</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -2236,13 +2236,13 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>烟灰色</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B32" t="str">
         <v>弟弟</v>
       </c>
       <c r="C32" t="str">
-        <v>assets/1787326236952-2pmwche4t3.jpg</v>
+        <v>assets/1787326449218-09s9ucram4.jpg</v>
       </c>
       <c r="D32" t="str">
         <v>是</v>
@@ -2251,7 +2251,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>福建泉州</v>
+        <v>德国</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -2295,13 +2295,13 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>银虎斑</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B33" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C33" t="str">
-        <v>assets/1787326184557-90v6clkwen.jpg</v>
+        <v>assets/1787326277374-8ti107m5ki.jpg</v>
       </c>
       <c r="D33" t="str">
         <v>是</v>
@@ -2310,7 +2310,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>福建福州</v>
+        <v>广东深圳</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -2354,13 +2354,13 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>棕虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B34" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C34" t="str">
-        <v>assets/1787326046155-4tk23nq4dj.jpg</v>
+        <v>assets/1787326236952-2pmwche4t3.jpg</v>
       </c>
       <c r="D34" t="str">
         <v>是</v>
@@ -2369,7 +2369,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>广西贵港</v>
+        <v>福建泉州</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -2413,13 +2413,13 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>凯米尔色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B35" t="str">
         <v>弟弟</v>
       </c>
       <c r="C35" t="str">
-        <v>assets/1787325862706-wq18k3ej56.jpg</v>
+        <v>assets/1787326184557-90v6clkwen.jpg</v>
       </c>
       <c r="D35" t="str">
         <v>是</v>
@@ -2428,7 +2428,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>江苏苏州</v>
+        <v>福建福州</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -2472,13 +2472,13 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>凯米尔色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B36" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C36" t="str">
-        <v>assets/1787325743258-a7oac7hzlo.jpg</v>
+        <v>assets/1787326046155-4tk23nq4dj.jpg</v>
       </c>
       <c r="D36" t="str">
         <v>是</v>
@@ -2487,7 +2487,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>江苏苏州</v>
+        <v>广西贵港</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -2531,13 +2531,13 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>银虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B37" t="str">
         <v>弟弟</v>
       </c>
       <c r="C37" t="str">
-        <v>assets/1787325706797-kgk81ghccy.jpg</v>
+        <v>assets/1787325862706-wq18k3ej56.jpg</v>
       </c>
       <c r="D37" t="str">
         <v>是</v>
@@ -2546,7 +2546,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>北京</v>
+        <v>江苏苏州</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -2590,13 +2590,13 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>蓝虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B38" t="str">
         <v>弟弟</v>
       </c>
       <c r="C38" t="str">
-        <v>assets/1787325603704-lahzgrm7fa.jpg,assets/1787325690106-wgu3spujit.jpg</v>
+        <v>assets/1787325743258-a7oac7hzlo.jpg</v>
       </c>
       <c r="D38" t="str">
         <v>是</v>
@@ -2605,7 +2605,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>上海</v>
+        <v>江苏苏州</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -2649,13 +2649,13 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B39" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C39" t="str">
-        <v>assets/1787325554341-608thexrne.jpg</v>
+        <v>assets/1787325706797-kgk81ghccy.jpg</v>
       </c>
       <c r="D39" t="str">
         <v>是</v>
@@ -2664,7 +2664,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>江苏苏州</v>
+        <v>北京</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -2708,13 +2708,13 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>浅色银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B40" t="str">
         <v>弟弟</v>
       </c>
       <c r="C40" t="str">
-        <v>assets/1787325480828-q90pskoiw3.jpg</v>
+        <v>assets/1787325603704-lahzgrm7fa.jpg,assets/1787325690106-wgu3spujit.jpg</v>
       </c>
       <c r="D40" t="str">
         <v>是</v>
@@ -2723,7 +2723,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>四川成都</v>
+        <v>上海</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -2767,13 +2767,13 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>浅色银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B41" t="str">
         <v>妹妹</v>
       </c>
       <c r="C41" t="str">
-        <v>assets/1787325448999-a2pg8176fu.jpg</v>
+        <v>assets/1787325554341-608thexrne.jpg</v>
       </c>
       <c r="D41" t="str">
         <v>是</v>
@@ -2782,7 +2782,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>中国台湾</v>
+        <v>江苏苏州</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -2826,13 +2826,13 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>棕虎斑</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B42" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C42" t="str">
-        <v>assets/1787325357634-k55zlfhmqj.jpg</v>
+        <v>assets/1787325480828-q90pskoiw3.jpg</v>
       </c>
       <c r="D42" t="str">
         <v>是</v>
@@ -2841,7 +2841,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>浙江杭州</v>
+        <v>四川成都</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -2885,13 +2885,13 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>烟灰色</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B43" t="str">
         <v>妹妹</v>
       </c>
       <c r="C43" t="str">
-        <v>assets/1787325237876-t19isaq5gu.jpg</v>
+        <v>assets/1787325448999-a2pg8176fu.jpg</v>
       </c>
       <c r="D43" t="str">
         <v>是</v>
@@ -2900,7 +2900,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>辽宁沈阳</v>
+        <v>中国台湾</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2944,13 +2944,13 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>金棕虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B44" t="str">
         <v>妹妹</v>
       </c>
       <c r="C44" t="str">
-        <v>assets/1787325199931-e7wms9qtya.jpg</v>
+        <v>assets/1787325357634-k55zlfhmqj.jpg</v>
       </c>
       <c r="D44" t="str">
         <v>是</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>四川成都</v>
+        <v>浙江杭州</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -3003,13 +3003,13 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>蓝虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B45" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C45" t="str">
-        <v>assets/1787325172354-4sa8uzaey2.jpg</v>
+        <v>assets/1787325237876-t19isaq5gu.jpg</v>
       </c>
       <c r="D45" t="str">
         <v>是</v>
@@ -3018,7 +3018,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>中国香港</v>
+        <v>辽宁沈阳</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -3062,13 +3062,13 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>烟灰色</v>
+        <v>金棕虎斑</v>
       </c>
       <c r="B46" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C46" t="str">
-        <v>assets/1787325109283-y7mvkk6qg4.jpg</v>
+        <v>assets/1787325199931-e7wms9qtya.jpg</v>
       </c>
       <c r="D46" t="str">
         <v>是</v>
@@ -3077,7 +3077,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>中国澳门</v>
+        <v>四川成都</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -3127,7 +3127,7 @@
         <v>弟弟</v>
       </c>
       <c r="C47" t="str">
-        <v>assets/1787325033629-y3ygps3zaj.jpg</v>
+        <v>assets/1787325172354-4sa8uzaey2.jpg</v>
       </c>
       <c r="D47" t="str">
         <v>是</v>
@@ -3136,7 +3136,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>山东青岛</v>
+        <v>中国香港</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -3186,7 +3186,7 @@
         <v>弟弟</v>
       </c>
       <c r="C48" t="str">
-        <v>assets/1787324954998-w5m5jox439.jpg</v>
+        <v>assets/1787325109283-y7mvkk6qg4.jpg</v>
       </c>
       <c r="D48" t="str">
         <v>是</v>
@@ -3195,7 +3195,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>海南海口</v>
+        <v>中国澳门</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -3239,13 +3239,13 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>棕虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B49" t="str">
         <v>弟弟</v>
       </c>
       <c r="C49" t="str">
-        <v>assets/1787324905909-zrz8o79kdf.jpg</v>
+        <v>assets/1787325033629-y3ygps3zaj.jpg</v>
       </c>
       <c r="D49" t="str">
         <v>是</v>
@@ -3254,7 +3254,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>内蒙古</v>
+        <v>山东青岛</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -3304,7 +3304,7 @@
         <v>弟弟</v>
       </c>
       <c r="C50" t="str">
-        <v>assets/1787324880505-gbh0sn7b6j.jpg</v>
+        <v>assets/1787324954998-w5m5jox439.jpg</v>
       </c>
       <c r="D50" t="str">
         <v>是</v>
@@ -3313,7 +3313,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>中国香港</v>
+        <v>海南海口</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -3357,13 +3357,13 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B51" t="str">
         <v>弟弟</v>
       </c>
       <c r="C51" t="str">
-        <v>assets/1787324806613-31yyz14tsf.jpg</v>
+        <v>assets/1787324905909-zrz8o79kdf.jpg</v>
       </c>
       <c r="D51" t="str">
         <v>是</v>
@@ -3372,7 +3372,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>四川成都</v>
+        <v>内蒙古</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -3416,13 +3416,13 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>红虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B52" t="str">
         <v>弟弟</v>
       </c>
       <c r="C52" t="str">
-        <v>assets/1787324789658-uz6ephkdsh.jpg</v>
+        <v>assets/1787324880505-gbh0sn7b6j.jpg</v>
       </c>
       <c r="D52" t="str">
         <v>是</v>
@@ -3431,7 +3431,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>湖北武汉</v>
+        <v>中国香港</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -3481,7 +3481,7 @@
         <v>弟弟</v>
       </c>
       <c r="C53" t="str">
-        <v>assets/1787324522658-smn44crast.jpg</v>
+        <v>assets/1787324806613-31yyz14tsf.jpg</v>
       </c>
       <c r="D53" t="str">
         <v>是</v>
@@ -3490,7 +3490,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>湖北武汉</v>
+        <v>四川成都</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -3534,13 +3534,13 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>棕虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B54" t="str">
         <v>弟弟</v>
       </c>
       <c r="C54" t="str">
-        <v>assets/1787324365608-6xtrjp7euz.jpg</v>
+        <v>assets/1787324789658-uz6ephkdsh.jpg</v>
       </c>
       <c r="D54" t="str">
         <v>是</v>
@@ -3549,7 +3549,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>新疆</v>
+        <v>湖北武汉</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -3593,13 +3593,13 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>浅凯米尔</v>
+        <v>烟灰色</v>
       </c>
       <c r="B55" t="str">
         <v>弟弟</v>
       </c>
       <c r="C55" t="str">
-        <v>assets/1787324331029-d74lcuycf6.jpg</v>
+        <v>assets/1787324522658-smn44crast.jpg</v>
       </c>
       <c r="D55" t="str">
         <v>是</v>
@@ -3608,7 +3608,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>四川成都</v>
+        <v>湖北武汉</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -3652,13 +3652,13 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>红虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B56" t="str">
         <v>弟弟</v>
       </c>
       <c r="C56" t="str">
-        <v>assets/1787324297469-ans1lse2l5.jpg</v>
+        <v>assets/1787324365608-6xtrjp7euz.jpg</v>
       </c>
       <c r="D56" t="str">
         <v>是</v>
@@ -3667,7 +3667,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>四川乐山</v>
+        <v>新疆</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -3711,13 +3711,13 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>红虎斑</v>
+        <v>浅凯米尔</v>
       </c>
       <c r="B57" t="str">
         <v>弟弟</v>
       </c>
       <c r="C57" t="str">
-        <v>assets/1787324256827-7w383z4bg1.jpg</v>
+        <v>assets/1787324331029-d74lcuycf6.jpg</v>
       </c>
       <c r="D57" t="str">
         <v>是</v>
@@ -3726,7 +3726,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>中国台湾</v>
+        <v>四川成都</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -3770,13 +3770,13 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B58" t="str">
         <v>弟弟</v>
       </c>
       <c r="C58" t="str">
-        <v>assets/1787324228262-y3vwn6i4zk.jpg</v>
+        <v>assets/1787324297469-ans1lse2l5.jpg</v>
       </c>
       <c r="D58" t="str">
         <v>是</v>
@@ -3785,7 +3785,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>四川成都</v>
+        <v>四川乐山</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -3829,13 +3829,13 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>凯米尔色</v>
+        <v>红虎斑</v>
       </c>
       <c r="B59" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C59" t="str">
-        <v>assets/1787324201418-9tk4ik75mo.jpg</v>
+        <v>assets/1787324256827-7w383z4bg1.jpg</v>
       </c>
       <c r="D59" t="str">
         <v>是</v>
@@ -3844,7 +3844,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>江苏南京</v>
+        <v>中国台湾</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -3888,13 +3888,13 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B60" t="str">
         <v>弟弟</v>
       </c>
       <c r="C60" t="str">
-        <v>assets/1787324092513-jpa2rmkci2.jpg</v>
+        <v>assets/1787324228262-y3vwn6i4zk.jpg</v>
       </c>
       <c r="D60" t="str">
         <v>是</v>
@@ -3903,7 +3903,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>江苏南京</v>
+        <v>四川成都</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -3947,13 +3947,13 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>银虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B61" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C61" t="str">
-        <v>assets/1787323318612-soge38hpsf.jpg</v>
+        <v>assets/1787324201418-9tk4ik75mo.jpg</v>
       </c>
       <c r="D61" t="str">
         <v>是</v>
@@ -3962,7 +3962,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>上海</v>
+        <v>江苏南京</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -4012,7 +4012,7 @@
         <v>弟弟</v>
       </c>
       <c r="C62" t="str">
-        <v>assets/1787323235892-7yq8ioq01e.jpg</v>
+        <v>assets/1787324092513-jpa2rmkci2.jpg</v>
       </c>
       <c r="D62" t="str">
         <v>是</v>
@@ -4021,7 +4021,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>四川成都</v>
+        <v>江苏南京</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -4068,10 +4068,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B63" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C63" t="str">
-        <v>assets/1787322988096-6e2f54q7vo.jpg</v>
+        <v>assets/1787323318612-soge38hpsf.jpg</v>
       </c>
       <c r="D63" t="str">
         <v>是</v>
@@ -4080,7 +4080,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>浙江宁波</v>
+        <v>上海</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -4124,13 +4124,13 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>银虎斑补丁</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B64" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C64" t="str">
-        <v>assets/1787322938518-85ev8bs2k5.jpg</v>
+        <v>assets/1787323235892-7yq8ioq01e.jpg</v>
       </c>
       <c r="D64" t="str">
         <v>是</v>
@@ -4139,7 +4139,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>马来西亚</v>
+        <v>四川成都</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -4186,10 +4186,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B65" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C65" t="str">
-        <v>assets/1787322881183-tzu9xtw2sg.jpg</v>
+        <v>assets/1787322988096-6e2f54q7vo.jpg</v>
       </c>
       <c r="D65" t="str">
         <v>是</v>
@@ -4198,7 +4198,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>陕西西安</v>
+        <v>浙江宁波</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -4242,13 +4242,13 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>纯黑色</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B66" t="str">
         <v>妹妹</v>
       </c>
       <c r="C66" t="str">
-        <v>assets/1787322840098-nhy4jjyx7k.jpg</v>
+        <v>assets/1787322938518-85ev8bs2k5.jpg</v>
       </c>
       <c r="D66" t="str">
         <v>是</v>
@@ -4257,7 +4257,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>广西南宁</v>
+        <v>马来西亚</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -4301,13 +4301,13 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B67" t="str">
         <v>弟弟</v>
       </c>
       <c r="C67" t="str">
-        <v>assets/1787322760950-gn3qgego4s.jpg</v>
+        <v>assets/1787322881183-tzu9xtw2sg.jpg</v>
       </c>
       <c r="D67" t="str">
         <v>是</v>
@@ -4316,7 +4316,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>广西南宁</v>
+        <v>陕西西安</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -4360,13 +4360,13 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>红虎斑</v>
+        <v>纯黑色</v>
       </c>
       <c r="B68" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C68" t="str">
-        <v>assets/1787322605982-04n50xegt2.jpg</v>
+        <v>assets/1787322840098-nhy4jjyx7k.jpg</v>
       </c>
       <c r="D68" t="str">
         <v>是</v>
@@ -4375,7 +4375,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>上海</v>
+        <v>广西南宁</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -4419,13 +4419,13 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B69" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C69" t="str">
-        <v>assets/1787322490045-kog3ru43dy.jpg</v>
+        <v>assets/1787322760950-gn3qgego4s.jpg</v>
       </c>
       <c r="D69" t="str">
         <v>是</v>
@@ -4434,7 +4434,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>上海</v>
+        <v>广西南宁</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -4484,7 +4484,7 @@
         <v>弟弟</v>
       </c>
       <c r="C70" t="str">
-        <v>assets/1787322419996-0m33yx89nm.jpg</v>
+        <v>assets/1787322605982-04n50xegt2.jpg</v>
       </c>
       <c r="D70" t="str">
         <v>是</v>
@@ -4493,7 +4493,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>广东广州</v>
+        <v>上海</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -4537,13 +4537,13 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>浅色银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B71" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C71" t="str">
-        <v>assets/1787322377730-vj5csj2mll.jpg</v>
+        <v>assets/1787322490045-kog3ru43dy.jpg</v>
       </c>
       <c r="D71" t="str">
         <v>是</v>
@@ -4552,7 +4552,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>柬埔寨</v>
+        <v>上海</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -4596,13 +4596,13 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>蓝虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B72" t="str">
         <v>弟弟</v>
       </c>
       <c r="C72" t="str">
-        <v>assets/1787322269611-53yaj5ideu.jpg</v>
+        <v>assets/1787322419996-0m33yx89nm.jpg</v>
       </c>
       <c r="D72" t="str">
         <v>是</v>
@@ -4611,7 +4611,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>山东枣庄</v>
+        <v>广东广州</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -4655,13 +4655,13 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>银虎斑</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B73" t="str">
         <v>弟弟</v>
       </c>
       <c r="C73" t="str">
-        <v>assets/1787321989528-7d6liuhuk9.jpg</v>
+        <v>assets/1787322377730-vj5csj2mll.jpg</v>
       </c>
       <c r="D73" t="str">
         <v>是</v>
@@ -4670,7 +4670,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>陕西西安</v>
+        <v>柬埔寨</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -4714,13 +4714,13 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B74" t="str">
         <v>弟弟</v>
       </c>
       <c r="C74" t="str">
-        <v>assets/1787321941642-xlrc1no2ua.jpg</v>
+        <v>assets/1787322269611-53yaj5ideu.jpg</v>
       </c>
       <c r="D74" t="str">
         <v>是</v>
@@ -4729,7 +4729,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>山东东营</v>
+        <v>山东枣庄</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -4773,13 +4773,13 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>凯米尔色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B75" t="str">
         <v>弟弟</v>
       </c>
       <c r="C75" t="str">
-        <v>assets/1787321903535-6orj7qcgzn.jpg</v>
+        <v>assets/1787321989528-7d6liuhuk9.jpg</v>
       </c>
       <c r="D75" t="str">
         <v>是</v>
@@ -4788,7 +4788,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>中国台湾</v>
+        <v>陕西西安</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -4832,13 +4832,13 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>烟灰色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B76" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C76" t="str">
-        <v>assets/1787321858985-v4qej7cq7g.jpg</v>
+        <v>assets/1787321941642-xlrc1no2ua.jpg</v>
       </c>
       <c r="D76" t="str">
         <v>是</v>
@@ -4847,7 +4847,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>中国台湾</v>
+        <v>山东东营</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -4891,13 +4891,13 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>银虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B77" t="str">
         <v>弟弟</v>
       </c>
       <c r="C77" t="str">
-        <v>assets/1787321834306-efgnyhujon.jpg</v>
+        <v>assets/1787321903535-6orj7qcgzn.jpg</v>
       </c>
       <c r="D77" t="str">
         <v>是</v>
@@ -4906,7 +4906,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>北京</v>
+        <v>中国台湾</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -4950,13 +4950,13 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B78" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C78" t="str">
-        <v>assets/1787321439916-uttgpbkogb.jpg</v>
+        <v>assets/1787321858985-v4qej7cq7g.jpg</v>
       </c>
       <c r="D78" t="str">
         <v>是</v>
@@ -4965,7 +4965,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>安徽合肥</v>
+        <v>中国台湾</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -5015,7 +5015,7 @@
         <v>弟弟</v>
       </c>
       <c r="C79" t="str">
-        <v>assets/1787321419210-51hhgurygq.jpg</v>
+        <v>assets/1787321834306-efgnyhujon.jpg</v>
       </c>
       <c r="D79" t="str">
         <v>是</v>
@@ -5024,7 +5024,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>上海</v>
+        <v>北京</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -5068,13 +5068,13 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>凯米尔色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B80" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C80" t="str">
-        <v>assets/1787321363369-bzjn51j5il.jpg</v>
+        <v>assets/1787321439916-uttgpbkogb.jpg</v>
       </c>
       <c r="D80" t="str">
         <v>是</v>
@@ -5083,7 +5083,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>中国台湾</v>
+        <v>安徽合肥</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -5127,13 +5127,13 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B81" t="str">
         <v>弟弟</v>
       </c>
       <c r="C81" t="str">
-        <v>assets/1787321332559-87p6spuch3.jpg</v>
+        <v>assets/1787321419210-51hhgurygq.jpg</v>
       </c>
       <c r="D81" t="str">
         <v>是</v>
@@ -5142,7 +5142,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>中国台湾</v>
+        <v>上海</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -5186,13 +5186,13 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>棕虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B82" t="str">
         <v>妹妹</v>
       </c>
       <c r="C82" t="str">
-        <v>assets/1787321232531-59lnzv8y98.jpg</v>
+        <v>assets/1787321363369-bzjn51j5il.jpg</v>
       </c>
       <c r="D82" t="str">
         <v>是</v>
@@ -5201,7 +5201,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>北京</v>
+        <v>中国台湾</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -5245,13 +5245,13 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B83" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C83" t="str">
-        <v>assets/1787319975814-g1pfa56vfp.jpg</v>
+        <v>assets/1787321332559-87p6spuch3.jpg</v>
       </c>
       <c r="D83" t="str">
         <v>是</v>
@@ -5260,7 +5260,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>浙江宁波</v>
+        <v>中国台湾</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -5304,13 +5304,13 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B84" t="str">
         <v>妹妹</v>
       </c>
       <c r="C84" t="str">
-        <v>assets/1787319800704-v3qeu062ak.jpg</v>
+        <v>assets/1787321232531-59lnzv8y98.jpg</v>
       </c>
       <c r="D84" t="str">
         <v>是</v>
@@ -5319,7 +5319,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>河北唐山</v>
+        <v>北京</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -5369,7 +5369,7 @@
         <v>妹妹</v>
       </c>
       <c r="C85" t="str">
-        <v>assets/1787319745369-zn66xr3bvb.jpg</v>
+        <v>assets/1787319975814-g1pfa56vfp.jpg</v>
       </c>
       <c r="D85" t="str">
         <v>是</v>
@@ -5378,7 +5378,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>河北石家庄</v>
+        <v>浙江宁波</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -5422,13 +5422,13 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>棕虎补丁</v>
+        <v>银虎斑</v>
       </c>
       <c r="B86" t="str">
         <v>妹妹</v>
       </c>
       <c r="C86" t="str">
-        <v>assets/1787319547969-zqlq35fxxt.jpg</v>
+        <v>assets/1787319800704-v3qeu062ak.jpg</v>
       </c>
       <c r="D86" t="str">
         <v>是</v>
@@ -5437,7 +5437,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>韩国</v>
+        <v>河北唐山</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -5481,13 +5481,13 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>蓝银虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B87" t="str">
         <v>妹妹</v>
       </c>
       <c r="C87" t="str">
-        <v>assets/1787319501376-xscwljnu1j.jpg</v>
+        <v>assets/1787319745369-zn66xr3bvb.jpg</v>
       </c>
       <c r="D87" t="str">
         <v>是</v>
@@ -5496,7 +5496,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>美国</v>
+        <v>河北石家庄</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -5540,13 +5540,13 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>棕虎斑</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B88" t="str">
         <v>妹妹</v>
       </c>
       <c r="C88" t="str">
-        <v>assets/1787319443529-4a0zqikufx.jpg</v>
+        <v>assets/1787319547969-zqlq35fxxt.jpg</v>
       </c>
       <c r="D88" t="str">
         <v>是</v>
@@ -5555,7 +5555,7 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>中国台湾</v>
+        <v>韩国</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -5599,13 +5599,13 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>蓝虎斑</v>
+        <v>蓝银虎斑</v>
       </c>
       <c r="B89" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C89" t="str">
-        <v>assets/1787319356194-lr2d5680i9.jpg</v>
+        <v>assets/1787319501376-xscwljnu1j.jpg</v>
       </c>
       <c r="D89" t="str">
         <v>是</v>
@@ -5614,7 +5614,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>中国台湾</v>
+        <v>美国</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -5664,7 +5664,7 @@
         <v>妹妹</v>
       </c>
       <c r="C90" t="str">
-        <v>assets/1787319208828-aizqo4blcv.jpg</v>
+        <v>assets/1787319443529-4a0zqikufx.jpg</v>
       </c>
       <c r="D90" t="str">
         <v>是</v>
@@ -5673,7 +5673,7 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>山东淄博</v>
+        <v>中国台湾</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -5717,13 +5717,13 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B91" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C91" t="str">
-        <v>assets/1787319162970-cc2v8ovnni.jpg</v>
+        <v>assets/1787319356194-lr2d5680i9.jpg</v>
       </c>
       <c r="D91" t="str">
         <v>是</v>
@@ -5732,7 +5732,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>韩国</v>
+        <v>中国台湾</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -5776,13 +5776,13 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>棕虎补丁</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B92" t="str">
         <v>妹妹</v>
       </c>
       <c r="C92" t="str">
-        <v>assets/1787319098214-8pwa9yx2wc.jpg</v>
+        <v>assets/1787319208828-aizqo4blcv.jpg</v>
       </c>
       <c r="D92" t="str">
         <v>是</v>
@@ -5791,7 +5791,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>四川成都</v>
+        <v>山东淄博</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -5838,10 +5838,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B93" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C93" t="str">
-        <v>assets/1787318867999-3gxdddp72x.jpg</v>
+        <v>assets/1787319162970-cc2v8ovnni.jpg</v>
       </c>
       <c r="D93" t="str">
         <v>是</v>
@@ -5850,7 +5850,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>广东广州</v>
+        <v>韩国</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -5894,13 +5894,13 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>银虎斑</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B94" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C94" t="str">
-        <v>assets/1787318609722-0ojb3aikwi.jpg</v>
+        <v>assets/1787319098214-8pwa9yx2wc.jpg</v>
       </c>
       <c r="D94" t="str">
         <v>是</v>
@@ -5909,7 +5909,7 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>黑龙江鹤岗</v>
+        <v>四川成都</v>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -5953,13 +5953,13 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>蓝虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B95" t="str">
         <v>弟弟</v>
       </c>
       <c r="C95" t="str">
-        <v>assets/1787318530612-779fbkfcoi.jpg</v>
+        <v>assets/1787318867999-3gxdddp72x.jpg</v>
       </c>
       <c r="D95" t="str">
         <v>是</v>
@@ -5968,7 +5968,7 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>天津</v>
+        <v>广东广州</v>
       </c>
       <c r="G95" t="str">
         <v/>
@@ -6018,7 +6018,7 @@
         <v>弟弟</v>
       </c>
       <c r="C96" t="str">
-        <v>assets/1787318365475-sj87wtsai3.jpg</v>
+        <v>assets/1787318609722-0ojb3aikwi.jpg</v>
       </c>
       <c r="D96" t="str">
         <v>是</v>
@@ -6027,7 +6027,7 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>山西朔州</v>
+        <v>黑龙江鹤岗</v>
       </c>
       <c r="G96" t="str">
         <v/>
@@ -6057,7 +6057,7 @@
         <v/>
       </c>
       <c r="P96" t="str">
-        <v>已接猫</v>
+        <v/>
       </c>
       <c r="Q96" t="str">
         <v/>
@@ -6071,13 +6071,13 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B97" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C97" t="str">
-        <v>assets/1787318326155-ia4noopjhq.jpg</v>
+        <v>assets/1787318530612-779fbkfcoi.jpg</v>
       </c>
       <c r="D97" t="str">
         <v>是</v>
@@ -6086,7 +6086,7 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>贵州</v>
+        <v>天津</v>
       </c>
       <c r="G97" t="str">
         <v/>
@@ -6130,22 +6130,22 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B98" t="str">
         <v>弟弟</v>
       </c>
       <c r="C98" t="str">
-        <v>assets/1787304479674-w0trechn4p.jpg</v>
+        <v>assets/1787318365475-sj87wtsai3.jpg</v>
       </c>
       <c r="D98" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E98" t="str">
-        <v>2026-06-06</v>
+        <v/>
       </c>
       <c r="F98" t="str">
-        <v/>
+        <v>山西朔州</v>
       </c>
       <c r="G98" t="str">
         <v/>
@@ -6175,7 +6175,7 @@
         <v/>
       </c>
       <c r="P98" t="str">
-        <v/>
+        <v>已接猫</v>
       </c>
       <c r="Q98" t="str">
         <v/>
@@ -6184,27 +6184,27 @@
         <v/>
       </c>
       <c r="S98" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>纯黑色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B99" t="str">
         <v>妹妹</v>
       </c>
       <c r="C99" t="str">
-        <v>assets/1787283819124-4v7d1w01la.jpg</v>
+        <v>assets/1787318326155-ia4noopjhq.jpg</v>
       </c>
       <c r="D99" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E99" t="str">
-        <v>2026-02-20</v>
+        <v/>
       </c>
       <c r="F99" t="str">
-        <v/>
+        <v>贵州</v>
       </c>
       <c r="G99" t="str">
         <v/>
@@ -6243,24 +6243,24 @@
         <v/>
       </c>
       <c r="S99" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>阴影色NS12</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B100" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C100" t="str">
-        <v>assets/1787283212708-jdnyi6ecci.jpg</v>
+        <v>assets/1787304479674-w0trechn4p.jpg</v>
       </c>
       <c r="D100" t="str">
         <v>否</v>
       </c>
       <c r="E100" t="str">
-        <v>2026-05-28</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F100" t="str">
         <v/>
@@ -6307,22 +6307,22 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>阴影色NS11</v>
+        <v>纯黑色</v>
       </c>
       <c r="B101" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C101" t="str">
-        <v>assets/1787283153501-s2tjg9spwu.jpg</v>
+        <v>assets/1787283819124-4v7d1w01la.jpg</v>
       </c>
       <c r="D101" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E101" t="str">
-        <v>2026-06-15</v>
+        <v>2026-02-20</v>
       </c>
       <c r="F101" t="str">
-        <v>重庆</v>
+        <v/>
       </c>
       <c r="G101" t="str">
         <v/>
@@ -6366,19 +6366,19 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>浅烟灰色</v>
+        <v>阴影色NS12</v>
       </c>
       <c r="B102" t="str">
         <v>妹妹</v>
       </c>
       <c r="C102" t="str">
-        <v>assets/1787283092677-i4d8tyrjtf.jpg</v>
+        <v>assets/1787283212708-jdnyi6ecci.jpg</v>
       </c>
       <c r="D102" t="str">
         <v>否</v>
       </c>
       <c r="E102" t="str">
-        <v>2026-03-21</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F102" t="str">
         <v/>
@@ -6425,22 +6425,22 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>棕虎斑</v>
+        <v>阴影色NS11</v>
       </c>
       <c r="B103" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C103" t="str">
-        <v>assets/1787283031104-bpyq9wy2tl.jpg</v>
+        <v>assets/1787283153501-s2tjg9spwu.jpg</v>
       </c>
       <c r="D103" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E103" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F103" t="str">
-        <v/>
+        <v>重庆</v>
       </c>
       <c r="G103" t="str">
         <v/>
@@ -6484,19 +6484,19 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>棕虎斑</v>
+        <v>浅烟灰色</v>
       </c>
       <c r="B104" t="str">
         <v>妹妹</v>
       </c>
       <c r="C104" t="str">
-        <v>assets/1787282991501-2fjfws0rqw.jpg</v>
+        <v>assets/1787283092677-i4d8tyrjtf.jpg</v>
       </c>
       <c r="D104" t="str">
         <v>否</v>
       </c>
       <c r="E104" t="str">
-        <v>2026-06-06</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F104" t="str">
         <v/>
@@ -6549,13 +6549,13 @@
         <v>妹妹</v>
       </c>
       <c r="C105" t="str">
-        <v>assets/1787282942262-syr48fym6c.jpg</v>
+        <v>assets/1787283031104-bpyq9wy2tl.jpg</v>
       </c>
       <c r="D105" t="str">
         <v>否</v>
       </c>
       <c r="E105" t="str">
-        <v>2026-06-15</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F105" t="str">
         <v/>
@@ -6605,10 +6605,10 @@
         <v>棕虎斑</v>
       </c>
       <c r="B106" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C106" t="str">
-        <v>assets/1787282819855-7vhx3m0v40.jpg</v>
+        <v>assets/1787282991501-2fjfws0rqw.jpg</v>
       </c>
       <c r="D106" t="str">
         <v>否</v>
@@ -6667,13 +6667,13 @@
         <v>妹妹</v>
       </c>
       <c r="C107" t="str">
-        <v>assets/1787282703381-2uakw592b4.jpg</v>
+        <v>assets/1787282942262-syr48fym6c.jpg</v>
       </c>
       <c r="D107" t="str">
         <v>否</v>
       </c>
       <c r="E107" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F107" t="str">
         <v/>
@@ -6720,13 +6720,13 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B108" t="str">
         <v>弟弟</v>
       </c>
       <c r="C108" t="str">
-        <v>assets/1787282649397-9hc31ncrpc.jpg</v>
+        <v>assets/1787282819855-7vhx3m0v40.jpg</v>
       </c>
       <c r="D108" t="str">
         <v>否</v>
@@ -6779,13 +6779,13 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B109" t="str">
         <v>妹妹</v>
       </c>
       <c r="C109" t="str">
-        <v>assets/1787282617957-svcoyyznpg.jpg</v>
+        <v>assets/1787282703381-2uakw592b4.jpg</v>
       </c>
       <c r="D109" t="str">
         <v>否</v>
@@ -6844,7 +6844,7 @@
         <v>弟弟</v>
       </c>
       <c r="C110" t="str">
-        <v>assets/1787282419632-78nixqjzua.jpg</v>
+        <v>assets/1787282649397-9hc31ncrpc.jpg</v>
       </c>
       <c r="D110" t="str">
         <v>否</v>
@@ -6897,19 +6897,19 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>纯黑色</v>
+        <v>烟灰色</v>
       </c>
       <c r="B111" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C111" t="str">
-        <v>assets/1787282349942-2cfuyn7xlc.jpg</v>
+        <v>assets/1787282617957-svcoyyznpg.jpg</v>
       </c>
       <c r="D111" t="str">
         <v>否</v>
       </c>
       <c r="E111" t="str">
-        <v>2026-03-21</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F111" t="str">
         <v/>
@@ -6956,19 +6956,19 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B112" t="str">
         <v>弟弟</v>
       </c>
       <c r="C112" t="str">
-        <v>assets/1787282064159-6b4z8c5msd.jpg</v>
+        <v>assets/1787282419632-78nixqjzua.jpg</v>
       </c>
       <c r="D112" t="str">
         <v>否</v>
       </c>
       <c r="E112" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F112" t="str">
         <v/>
@@ -7015,19 +7015,19 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>阴影色NS11</v>
+        <v>纯黑色</v>
       </c>
       <c r="B113" t="str">
         <v>弟弟</v>
       </c>
       <c r="C113" t="str">
-        <v>assets/1787280590041-vzcwebdok1.jpg</v>
+        <v>assets/1787282349942-2cfuyn7xlc.jpg</v>
       </c>
       <c r="D113" t="str">
         <v>否</v>
       </c>
       <c r="E113" t="str">
-        <v>2026-05-28</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F113" t="str">
         <v/>
@@ -7074,19 +7074,19 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>浅色银虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B114" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C114" t="str">
-        <v>assets/1787281786169-9ia0h837ct.jpg</v>
+        <v>assets/1787282064159-6b4z8c5msd.jpg</v>
       </c>
       <c r="D114" t="str">
         <v>否</v>
       </c>
       <c r="E114" t="str">
-        <v>2026-06-15</v>
+        <v>2026-06-10</v>
       </c>
       <c r="F114" t="str">
         <v/>
@@ -7133,22 +7133,22 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>浅烟灰色</v>
+        <v>阴影色NS11</v>
       </c>
       <c r="B115" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C115" t="str">
-        <v>assets/1785843720843-63qz159daui.jpg</v>
+        <v>assets/1787280590041-vzcwebdok1.jpg</v>
       </c>
       <c r="D115" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E115" t="str">
-        <v>2026-03-21</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F115" t="str">
-        <v>四川成都</v>
+        <v/>
       </c>
       <c r="G115" t="str">
         <v/>
@@ -7192,22 +7192,22 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>凯米尔色</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B116" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C116" t="str">
-        <v>assets/1787301984056-iu6afro5z5.jpg, assets/1785843763310-elg05ur61ri.jpg</v>
+        <v>assets/1787281786169-9ia0h837ct.jpg</v>
       </c>
       <c r="D116" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E116" t="str">
-        <v>2026-02-14</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F116" t="str">
-        <v>上海浦东</v>
+        <v/>
       </c>
       <c r="G116" t="str">
         <v/>
@@ -7251,22 +7251,22 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>银虎斑补丁</v>
+        <v>浅烟灰色</v>
       </c>
       <c r="B117" t="str">
         <v>妹妹</v>
       </c>
       <c r="C117" t="str">
-        <v>assets/1785843820715-9kz7gy4mbr7.jpg</v>
+        <v>assets/1785843720843-63qz159daui.jpg</v>
       </c>
       <c r="D117" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E117" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F117" t="str">
-        <v/>
+        <v>四川成都</v>
       </c>
       <c r="G117" t="str">
         <v/>
@@ -7310,22 +7310,22 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>烟灰色</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B118" t="str">
         <v>弟弟</v>
       </c>
       <c r="C118" t="str">
-        <v>assets/1785843953805-mxl3x1982io.jpg</v>
+        <v>assets/1787301984056-iu6afro5z5.jpg, assets/1785843763310-elg05ur61ri.jpg</v>
       </c>
       <c r="D118" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E118" t="str">
-        <v>2026-05-18</v>
+        <v>2026-02-14</v>
       </c>
       <c r="F118" t="str">
-        <v/>
+        <v>上海浦东</v>
       </c>
       <c r="G118" t="str">
         <v/>
@@ -7369,19 +7369,19 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>棕虎斑玳瑁</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B119" t="str">
         <v>妹妹</v>
       </c>
       <c r="C119" t="str">
-        <v>assets/1785844013835-ek4xpcje7kh.jpg</v>
+        <v>assets/1785843820715-9kz7gy4mbr7.jpg</v>
       </c>
       <c r="D119" t="str">
         <v>否</v>
       </c>
       <c r="E119" t="str">
-        <v>2026-02-14</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F119" t="str">
         <v/>
@@ -7428,19 +7428,19 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>银虎斑补丁</v>
+        <v>烟灰色</v>
       </c>
       <c r="B120" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C120" t="str">
-        <v>assets/1785844434338-ek5zbdgdcne.jpg</v>
+        <v>assets/1785843953805-mxl3x1982io.jpg</v>
       </c>
       <c r="D120" t="str">
         <v>否</v>
       </c>
       <c r="E120" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F120" t="str">
         <v/>
@@ -7487,22 +7487,22 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑玳瑁</v>
       </c>
       <c r="B121" t="str">
         <v>妹妹</v>
       </c>
       <c r="C121" t="str">
-        <v>assets/1785838787730-s5f333sc3u.jpg</v>
+        <v>assets/1785844013835-ek4xpcje7kh.jpg</v>
       </c>
       <c r="D121" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E121" t="str">
-        <v>2026-06-05</v>
+        <v>2026-02-14</v>
       </c>
       <c r="F121" t="str">
-        <v>湖北恩施</v>
+        <v/>
       </c>
       <c r="G121" t="str">
         <v/>
@@ -7546,22 +7546,22 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>银虎斑</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B122" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C122" t="str">
-        <v>assets/1785842296661-6qw3zs3as8h.jpg</v>
+        <v>assets/1785844434338-ek5zbdgdcne.jpg</v>
       </c>
       <c r="D122" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E122" t="str">
-        <v>2026-06-05</v>
+        <v>2026-05-24</v>
       </c>
       <c r="F122" t="str">
-        <v>湖北恩施</v>
+        <v/>
       </c>
       <c r="G122" t="str">
         <v/>
@@ -7608,19 +7608,19 @@
         <v>银虎斑</v>
       </c>
       <c r="B123" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C123" t="str">
-        <v>assets/1785842429109-porc98rel5.jpg</v>
+        <v>assets/1785838787730-s5f333sc3u.jpg</v>
       </c>
       <c r="D123" t="str">
         <v>是</v>
       </c>
       <c r="E123" t="str">
-        <v>2025-11-05</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F123" t="str">
-        <v>韩国</v>
+        <v>湖北恩施</v>
       </c>
       <c r="G123" t="str">
         <v/>
@@ -7667,19 +7667,19 @@
         <v>银虎斑</v>
       </c>
       <c r="B124" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C124" t="str">
-        <v>assets/1785842594141-fcglbzjp509.jpg</v>
+        <v>assets/1785842296661-6qw3zs3as8h.jpg</v>
       </c>
       <c r="D124" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E124" t="str">
-        <v>2026-05-18</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F124" t="str">
-        <v/>
+        <v>湖北恩施</v>
       </c>
       <c r="G124" t="str">
         <v/>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B125" t="str">
         <v>弟弟</v>
       </c>
       <c r="C125" t="str">
-        <v>assets/1785842639100-82k775dhwiv.jpg</v>
+        <v>assets/1785842429109-porc98rel5.jpg</v>
       </c>
       <c r="D125" t="str">
         <v>是</v>
       </c>
       <c r="E125" t="str">
-        <v>2026-05-28</v>
+        <v>2025-11-05</v>
       </c>
       <c r="F125" t="str">
-        <v>四川自贡</v>
+        <v>韩国</v>
       </c>
       <c r="G125" t="str">
         <v/>
@@ -7782,19 +7782,19 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B126" t="str">
         <v>妹妹</v>
       </c>
       <c r="C126" t="str">
-        <v>assets/1785842684502-mnhr0r96eee.jpg</v>
+        <v>assets/1785842594141-fcglbzjp509.jpg</v>
       </c>
       <c r="D126" t="str">
         <v>否</v>
       </c>
       <c r="E126" t="str">
-        <v>2026-06-06</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F126" t="str">
         <v/>
@@ -7841,22 +7841,22 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>纯黑色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B127" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C127" t="str">
-        <v>assets/1785842779532-5u1j0igrw1s.jpg</v>
+        <v>assets/1785842639100-82k775dhwiv.jpg</v>
       </c>
       <c r="D127" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E127" t="str">
-        <v>2026-03-05</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F127" t="str">
-        <v/>
+        <v>四川自贡</v>
       </c>
       <c r="G127" t="str">
         <v/>
@@ -7900,22 +7900,22 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B128" t="str">
         <v>妹妹</v>
       </c>
       <c r="C128" t="str">
-        <v>assets/1785842817046-6keqv4rw4yf.jpg</v>
+        <v>assets/1785842684502-mnhr0r96eee.jpg</v>
       </c>
       <c r="D128" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E128" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F128" t="str">
-        <v>韩国</v>
+        <v/>
       </c>
       <c r="G128" t="str">
         <v/>
@@ -7959,22 +7959,22 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>浅色银虎斑</v>
+        <v>纯黑色</v>
       </c>
       <c r="B129" t="str">
         <v>妹妹</v>
       </c>
       <c r="C129" t="str">
-        <v>assets/1785842950972-a88lbrskpc.jpg</v>
+        <v>assets/1785842779532-5u1j0igrw1s.jpg</v>
       </c>
       <c r="D129" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E129" t="str">
-        <v>2026-06-05</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F129" t="str">
-        <v>河北邢台</v>
+        <v/>
       </c>
       <c r="G129" t="str">
         <v/>
@@ -8018,22 +8018,22 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B130" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C130" t="str">
-        <v>assets/1785843011477-n3l1wi6ech.jpg</v>
+        <v>assets/1785842817046-6keqv4rw4yf.jpg</v>
       </c>
       <c r="D130" t="str">
         <v>是</v>
       </c>
       <c r="E130" t="str">
-        <v>2026-06-05</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F130" t="str">
-        <v>四川自贡</v>
+        <v>韩国</v>
       </c>
       <c r="G130" t="str">
         <v/>
@@ -8077,22 +8077,22 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>蓝虎斑</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B131" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C131" t="str">
-        <v>assets/1785843237517-ga449iqess5.jpg</v>
+        <v>assets/1785842950972-a88lbrskpc.jpg</v>
       </c>
       <c r="D131" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E131" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F131" t="str">
-        <v/>
+        <v>河北邢台</v>
       </c>
       <c r="G131" t="str">
         <v/>
@@ -8136,22 +8136,22 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>棕虎斑补丁</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B132" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C132" t="str">
-        <v>assets/1785842523893-7nwnnhwi4ns.jpg</v>
+        <v>assets/1785843011477-n3l1wi6ech.jpg</v>
       </c>
       <c r="D132" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E132" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F132" t="str">
-        <v/>
+        <v>四川自贡</v>
       </c>
       <c r="G132" t="str">
         <v/>
@@ -8198,16 +8198,16 @@
         <v>蓝虎斑</v>
       </c>
       <c r="B133" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C133" t="str">
-        <v>assets/1785843497557-st27fk8drqi.jpg</v>
+        <v>assets/1785843237517-ga449iqess5.jpg</v>
       </c>
       <c r="D133" t="str">
         <v>否</v>
       </c>
       <c r="E133" t="str">
-        <v>2026-04-05</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F133" t="str">
         <v/>
@@ -8254,13 +8254,13 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑补丁</v>
       </c>
       <c r="B134" t="str">
         <v>妹妹</v>
       </c>
       <c r="C134" t="str">
-        <v>assets/1785843621923-ylhakbtw13i.jpg</v>
+        <v>assets/1785842523893-7nwnnhwi4ns.jpg</v>
       </c>
       <c r="D134" t="str">
         <v>否</v>
@@ -8313,19 +8313,19 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B135" t="str">
         <v>妹妹</v>
       </c>
       <c r="C135" t="str">
-        <v>assets/1785843663884-sfxvpmiet7.jpg</v>
+        <v>assets/1785843497557-st27fk8drqi.jpg</v>
       </c>
       <c r="D135" t="str">
         <v>否</v>
       </c>
       <c r="E135" t="str">
-        <v>2026-03-05</v>
+        <v>2026-04-05</v>
       </c>
       <c r="F135" t="str">
         <v/>
@@ -8372,52 +8372,52 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>蓝虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B136" t="str">
         <v>妹妹</v>
       </c>
       <c r="C136" t="str">
-        <v>assets/1785852601940-o236xtv7yx.jpeg</v>
+        <v>assets/1785843621923-ylhakbtw13i.jpg</v>
       </c>
       <c r="D136" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E136" t="str">
-        <v>2026-02-20</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F136" t="str">
-        <v>荷兰</v>
+        <v/>
       </c>
       <c r="G136" t="str">
-        <v>阿泽</v>
+        <v/>
       </c>
       <c r="H136" t="str">
-        <v>小辫子</v>
+        <v/>
       </c>
       <c r="I136" t="str">
-        <v>驺驺</v>
+        <v/>
       </c>
       <c r="J136" t="str">
-        <v>2026-07-02</v>
+        <v/>
       </c>
       <c r="K136" t="str">
         <v/>
       </c>
       <c r="L136" t="str">
-        <v>2026-07-02</v>
+        <v/>
       </c>
       <c r="M136" t="str">
-        <v>2026-08-03</v>
+        <v/>
       </c>
       <c r="N136" t="str">
-        <v>2026-11-04</v>
+        <v/>
       </c>
       <c r="O136" t="str">
-        <v>2026-08-03 · 血清检测,2026-07-02 · 打疫苗 · assets/diary/zouzou-depart.jpg,2026-07-30 · 6.2斤 · 五个月10天了 · assets/feedback/zouzou-1.jpg</v>
+        <v/>
       </c>
       <c r="P136" t="str">
-        <v>已付定金</v>
+        <v/>
       </c>
       <c r="Q136" t="str">
         <v/>
@@ -8426,27 +8426,27 @@
         <v/>
       </c>
       <c r="S136" t="str">
-        <v>否</v>
+        <v/>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>红虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B137" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C137" t="str">
-        <v>assets/1785853950207-cedor66ou2q.jpeg</v>
+        <v>assets/1785843663884-sfxvpmiet7.jpg</v>
       </c>
       <c r="D137" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E137" t="str">
-        <v/>
+        <v>2026-03-05</v>
       </c>
       <c r="F137" t="str">
-        <v>广东广州</v>
+        <v/>
       </c>
       <c r="G137" t="str">
         <v/>
@@ -8490,52 +8490,52 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>红虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B138" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C138" t="str">
-        <v>assets/1785854129383-c8qkvl537x.jpeg</v>
+        <v>assets/1785852601940-o236xtv7yx.jpeg</v>
       </c>
       <c r="D138" t="str">
         <v>是</v>
       </c>
       <c r="E138" t="str">
-        <v/>
+        <v>2026-02-20</v>
       </c>
       <c r="F138" t="str">
-        <v>广东广州</v>
+        <v>荷兰</v>
       </c>
       <c r="G138" t="str">
-        <v/>
+        <v>阿泽</v>
       </c>
       <c r="H138" t="str">
-        <v/>
+        <v>小辫子</v>
       </c>
       <c r="I138" t="str">
-        <v/>
+        <v>驺驺</v>
       </c>
       <c r="J138" t="str">
-        <v/>
+        <v>2026-07-02</v>
       </c>
       <c r="K138" t="str">
         <v/>
       </c>
       <c r="L138" t="str">
-        <v/>
+        <v>2026-07-02</v>
       </c>
       <c r="M138" t="str">
-        <v/>
+        <v>2026-08-03</v>
       </c>
       <c r="N138" t="str">
-        <v/>
+        <v>2026-11-04</v>
       </c>
       <c r="O138" t="str">
-        <v/>
+        <v>2026-08-03 · 血清检测,2026-07-02 · 打疫苗 · assets/diary/zouzou-depart.jpg,2026-07-30 · 6.2斤 · 五个月10天了 · assets/feedback/zouzou-1.jpg</v>
       </c>
       <c r="P138" t="str">
-        <v/>
+        <v>已付定金</v>
       </c>
       <c r="Q138" t="str">
         <v/>
@@ -8544,18 +8544,18 @@
         <v/>
       </c>
       <c r="S138" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B139" t="str">
         <v>弟弟</v>
       </c>
       <c r="C139" t="str">
-        <v>assets/1785854166720-48r17hry9cd.jpeg</v>
+        <v>assets/1785853950207-cedor66ou2q.jpeg</v>
       </c>
       <c r="D139" t="str">
         <v>是</v>
@@ -8564,7 +8564,7 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>山西朔州</v>
+        <v>广东广州</v>
       </c>
       <c r="G139" t="str">
         <v/>
@@ -8608,13 +8608,13 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B140" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C140" t="str">
-        <v>assets/1785854224521-2cpg6xipfn6.jpeg</v>
+        <v>assets/1785854129383-c8qkvl537x.jpeg</v>
       </c>
       <c r="D140" t="str">
         <v>是</v>
@@ -8623,7 +8623,7 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>浙江宁波</v>
+        <v>广东广州</v>
       </c>
       <c r="G140" t="str">
         <v/>
@@ -8673,7 +8673,7 @@
         <v>弟弟</v>
       </c>
       <c r="C141" t="str">
-        <v>assets/1785854260793-steez4s972l.jpeg</v>
+        <v>assets/1785854166720-48r17hry9cd.jpeg</v>
       </c>
       <c r="D141" t="str">
         <v>是</v>
@@ -8682,7 +8682,7 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>陕西西安</v>
+        <v>山西朔州</v>
       </c>
       <c r="G141" t="str">
         <v/>
@@ -8729,10 +8729,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B142" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C142" t="str">
-        <v>assets/1785854319988-cohio08aod5.jpeg</v>
+        <v>assets/1785854224521-2cpg6xipfn6.jpeg</v>
       </c>
       <c r="D142" t="str">
         <v>是</v>
@@ -8741,7 +8741,7 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>黑龙江漠河</v>
+        <v>浙江宁波</v>
       </c>
       <c r="G142" t="str">
         <v/>
@@ -8785,13 +8785,13 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B143" t="str">
         <v>弟弟</v>
       </c>
       <c r="C143" t="str">
-        <v>assets/1785854520974-96b8b1ekqd9.jpeg</v>
+        <v>assets/1785854260793-steez4s972l.jpeg</v>
       </c>
       <c r="D143" t="str">
         <v>是</v>
@@ -8800,7 +8800,7 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>日本</v>
+        <v>陕西西安</v>
       </c>
       <c r="G143" t="str">
         <v/>
@@ -8847,10 +8847,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B144" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C144" t="str">
-        <v>assets/1785854664100-haqoiu1h7hj.jpeg</v>
+        <v>assets/1785854319988-cohio08aod5.jpeg</v>
       </c>
       <c r="D144" t="str">
         <v>是</v>
@@ -8859,7 +8859,7 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>浙江杭州</v>
+        <v>黑龙江漠河</v>
       </c>
       <c r="G144" t="str">
         <v/>
@@ -8903,13 +8903,13 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B145" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C145" t="str">
-        <v>assets/1785854690732-orrs40sx9rs.jpeg</v>
+        <v>assets/1785854520974-96b8b1ekqd9.jpeg</v>
       </c>
       <c r="D145" t="str">
         <v>是</v>
@@ -8918,7 +8918,7 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>贵州安顺</v>
+        <v>日本</v>
       </c>
       <c r="G145" t="str">
         <v/>
@@ -8968,7 +8968,7 @@
         <v>妹妹</v>
       </c>
       <c r="C146" t="str">
-        <v>assets/1785854734122-wcpmib4m7.jpeg</v>
+        <v>assets/1785854664100-haqoiu1h7hj.jpeg</v>
       </c>
       <c r="D146" t="str">
         <v>是</v>
@@ -8977,7 +8977,7 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>山东青岛</v>
+        <v>浙江杭州</v>
       </c>
       <c r="G146" t="str">
         <v/>
@@ -9024,10 +9024,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B147" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C147" t="str">
-        <v>assets/1785854758707-1kxdkfvs6jc.jpeg</v>
+        <v>assets/1785854690732-orrs40sx9rs.jpeg</v>
       </c>
       <c r="D147" t="str">
         <v>是</v>
@@ -9036,7 +9036,7 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>黑龙江漠河</v>
+        <v>贵州安顺</v>
       </c>
       <c r="G147" t="str">
         <v/>
@@ -9080,13 +9080,13 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>纯蓝色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B148" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C148" t="str">
-        <v>assets/1785854784780-3g0u60pdo93.jpeg</v>
+        <v>assets/1785854734122-wcpmib4m7.jpeg</v>
       </c>
       <c r="D148" t="str">
         <v>是</v>
@@ -9095,7 +9095,7 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>河南鹤壁</v>
+        <v>山东青岛</v>
       </c>
       <c r="G148" t="str">
         <v/>
@@ -9145,7 +9145,7 @@
         <v>弟弟</v>
       </c>
       <c r="C149" t="str">
-        <v>assets/1785854813179-8oyxr0h2bbu.jpeg</v>
+        <v>assets/1785854758707-1kxdkfvs6jc.jpeg</v>
       </c>
       <c r="D149" t="str">
         <v>是</v>
@@ -9154,7 +9154,7 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>陕西西安</v>
+        <v>黑龙江漠河</v>
       </c>
       <c r="G149" t="str">
         <v/>
@@ -9198,13 +9198,13 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>棕虎斑</v>
+        <v>纯蓝色</v>
       </c>
       <c r="B150" t="str">
         <v>弟弟</v>
       </c>
       <c r="C150" t="str">
-        <v>assets/1785854838933-uq6amircyzd.jpeg</v>
+        <v>assets/1785854784780-3g0u60pdo93.jpeg</v>
       </c>
       <c r="D150" t="str">
         <v>是</v>
@@ -9213,7 +9213,7 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>四川成都</v>
+        <v>河南鹤壁</v>
       </c>
       <c r="G150" t="str">
         <v/>
@@ -9257,22 +9257,22 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>烟灰色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B151" t="str">
         <v>弟弟</v>
       </c>
       <c r="C151" t="str">
-        <v>assets/1785854869973-za3p6wikqpo.jpeg</v>
+        <v>assets/1785854813179-8oyxr0h2bbu.jpeg</v>
       </c>
       <c r="D151" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E151" t="str">
-        <v>2026-05-18</v>
+        <v/>
       </c>
       <c r="F151" t="str">
-        <v/>
+        <v>陕西西安</v>
       </c>
       <c r="G151" t="str">
         <v/>
@@ -9316,13 +9316,13 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B152" t="str">
         <v>弟弟</v>
       </c>
       <c r="C152" t="str">
-        <v>assets/1785854997023-mawkallt2a.jpeg</v>
+        <v>assets/1785854838933-uq6amircyzd.jpeg</v>
       </c>
       <c r="D152" t="str">
         <v>是</v>
@@ -9331,7 +9331,7 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>新加坡</v>
+        <v>四川成都</v>
       </c>
       <c r="G152" t="str">
         <v/>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>凯米尔色</v>
+        <v>烟灰色</v>
       </c>
       <c r="B153" t="str">
         <v>弟弟</v>
       </c>
       <c r="C153" t="str">
-        <v>assets/1785855043327-wdc5pxwm34k.jpeg</v>
+        <v>assets/1785854869973-za3p6wikqpo.jpeg</v>
       </c>
       <c r="D153" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E153" t="str">
-        <v/>
+        <v>2026-05-18</v>
       </c>
       <c r="F153" t="str">
-        <v>上海浦东</v>
+        <v/>
       </c>
       <c r="G153" t="str">
         <v/>
@@ -9434,22 +9434,22 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B154" t="str">
         <v>弟弟</v>
       </c>
       <c r="C154" t="str">
-        <v>assets/1785912551260-jplefm937nk.jpeg, assets/videos/02.mp4</v>
+        <v>assets/1785854997023-mawkallt2a.jpeg</v>
       </c>
       <c r="D154" t="str">
         <v>是</v>
       </c>
       <c r="E154" t="str">
-        <v>2026-06-06</v>
+        <v/>
       </c>
       <c r="F154" t="str">
-        <v>浙江温州</v>
+        <v>新加坡</v>
       </c>
       <c r="G154" t="str">
         <v/>
@@ -9493,66 +9493,184 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
+        <v>凯米尔色</v>
+      </c>
+      <c r="B155" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C155" t="str">
+        <v>assets/1785855043327-wdc5pxwm34k.jpeg</v>
+      </c>
+      <c r="D155" t="str">
+        <v>是</v>
+      </c>
+      <c r="E155" t="str">
+        <v/>
+      </c>
+      <c r="F155" t="str">
+        <v>上海浦东</v>
+      </c>
+      <c r="G155" t="str">
+        <v/>
+      </c>
+      <c r="H155" t="str">
+        <v/>
+      </c>
+      <c r="I155" t="str">
+        <v/>
+      </c>
+      <c r="J155" t="str">
+        <v/>
+      </c>
+      <c r="K155" t="str">
+        <v/>
+      </c>
+      <c r="L155" t="str">
+        <v/>
+      </c>
+      <c r="M155" t="str">
+        <v/>
+      </c>
+      <c r="N155" t="str">
+        <v/>
+      </c>
+      <c r="O155" t="str">
+        <v/>
+      </c>
+      <c r="P155" t="str">
+        <v/>
+      </c>
+      <c r="Q155" t="str">
+        <v/>
+      </c>
+      <c r="R155" t="str">
+        <v/>
+      </c>
+      <c r="S155" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
         <v>棕虎斑</v>
       </c>
-      <c r="B155" t="str">
+      <c r="B156" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C156" t="str">
+        <v>assets/1785912551260-jplefm937nk.jpeg, assets/videos/02.mp4</v>
+      </c>
+      <c r="D156" t="str">
+        <v>是</v>
+      </c>
+      <c r="E156" t="str">
+        <v>2026-06-06</v>
+      </c>
+      <c r="F156" t="str">
+        <v>浙江温州</v>
+      </c>
+      <c r="G156" t="str">
+        <v/>
+      </c>
+      <c r="H156" t="str">
+        <v/>
+      </c>
+      <c r="I156" t="str">
+        <v/>
+      </c>
+      <c r="J156" t="str">
+        <v/>
+      </c>
+      <c r="K156" t="str">
+        <v/>
+      </c>
+      <c r="L156" t="str">
+        <v/>
+      </c>
+      <c r="M156" t="str">
+        <v/>
+      </c>
+      <c r="N156" t="str">
+        <v/>
+      </c>
+      <c r="O156" t="str">
+        <v/>
+      </c>
+      <c r="P156" t="str">
+        <v/>
+      </c>
+      <c r="Q156" t="str">
+        <v/>
+      </c>
+      <c r="R156" t="str">
+        <v/>
+      </c>
+      <c r="S156" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>棕虎斑</v>
+      </c>
+      <c r="B157" t="str">
         <v>妹妹</v>
       </c>
-      <c r="C155" t="str">
+      <c r="C157" t="str">
         <v>assets/1785912694000-m20f5kvvrr.jpeg</v>
       </c>
-      <c r="D155" t="str">
-        <v>否</v>
-      </c>
-      <c r="E155" t="str">
+      <c r="D157" t="str">
+        <v>否</v>
+      </c>
+      <c r="E157" t="str">
         <v>2026-06-06</v>
       </c>
-      <c r="F155" t="str">
-        <v/>
-      </c>
-      <c r="G155" t="str">
-        <v/>
-      </c>
-      <c r="H155" t="str">
-        <v/>
-      </c>
-      <c r="I155" t="str">
-        <v/>
-      </c>
-      <c r="J155" t="str">
-        <v/>
-      </c>
-      <c r="K155" t="str">
-        <v/>
-      </c>
-      <c r="L155" t="str">
-        <v/>
-      </c>
-      <c r="M155" t="str">
-        <v/>
-      </c>
-      <c r="N155" t="str">
-        <v/>
-      </c>
-      <c r="O155" t="str">
-        <v/>
-      </c>
-      <c r="P155" t="str">
-        <v/>
-      </c>
-      <c r="Q155" t="str">
-        <v/>
-      </c>
-      <c r="R155" t="str">
-        <v/>
-      </c>
-      <c r="S155" t="str">
+      <c r="F157" t="str">
+        <v/>
+      </c>
+      <c r="G157" t="str">
+        <v/>
+      </c>
+      <c r="H157" t="str">
+        <v/>
+      </c>
+      <c r="I157" t="str">
+        <v/>
+      </c>
+      <c r="J157" t="str">
+        <v/>
+      </c>
+      <c r="K157" t="str">
+        <v/>
+      </c>
+      <c r="L157" t="str">
+        <v/>
+      </c>
+      <c r="M157" t="str">
+        <v/>
+      </c>
+      <c r="N157" t="str">
+        <v/>
+      </c>
+      <c r="O157" t="str">
+        <v/>
+      </c>
+      <c r="P157" t="str">
+        <v/>
+      </c>
+      <c r="Q157" t="str">
+        <v/>
+      </c>
+      <c r="R157" t="str">
+        <v/>
+      </c>
+      <c r="S157" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S155"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S157"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -537,7 +537,7 @@
         <v>否</v>
       </c>
       <c r="E3" t="str">
-        <v/>
+        <v>2026-06-10</v>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -552,7 +552,7 @@
         <v/>
       </c>
       <c r="J3" t="str">
-        <v>2026-06-10</v>
+        <v/>
       </c>
       <c r="K3" t="str">
         <v/>

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S157"/>
+  <dimension ref="A1:S163"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -466,19 +466,19 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B2" t="str">
         <v>弟弟</v>
       </c>
       <c r="C2" t="str">
-        <v>assets/1787479268842-7en9nzy302.jpg</v>
+        <v>assets/1787837910484-r7urrsuib0.jpg</v>
       </c>
       <c r="D2" t="str">
         <v>否</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-06-10</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -493,7 +493,7 @@
         <v/>
       </c>
       <c r="J2" t="str">
-        <v>2026-06-10</v>
+        <v/>
       </c>
       <c r="K2" t="str">
         <v/>
@@ -531,7 +531,7 @@
         <v>妹妹</v>
       </c>
       <c r="C3" t="str">
-        <v>assets/1787479242639-32zuh5lham.jpg</v>
+        <v>assets/1787837846581-6q9nxgad35.jpg</v>
       </c>
       <c r="D3" t="str">
         <v>否</v>
@@ -584,22 +584,22 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>棕虎斑</v>
+        <v>凯米尔</v>
       </c>
       <c r="B4" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C4" t="str">
-        <v>assets/1787466121255-21jto2cugv.jpg</v>
+        <v>assets/1787837779354-hkuyvt39iz.jpg</v>
       </c>
       <c r="D4" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E4" t="str">
-        <v/>
+        <v>2026-06-26</v>
       </c>
       <c r="F4" t="str">
-        <v>四川广安</v>
+        <v/>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -646,10 +646,10 @@
         <v>烟灰色</v>
       </c>
       <c r="B5" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C5" t="str">
-        <v>assets/1787388322060-uj8bkwqgnv.jpg</v>
+        <v>assets/1787837690599-rd37ukkrgw.jpg</v>
       </c>
       <c r="D5" t="str">
         <v>否</v>
@@ -705,19 +705,19 @@
         <v>棕虎斑</v>
       </c>
       <c r="B6" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C6" t="str">
-        <v>assets/1787388277490-e6u506cx0r.jpg</v>
+        <v>assets/1787837648423-9riberz3tq.jpg</v>
       </c>
       <c r="D6" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E6" t="str">
         <v>2026-06-06</v>
       </c>
       <c r="F6" t="str">
-        <v/>
+        <v>北京</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -761,22 +761,22 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B7" t="str">
         <v>弟弟</v>
       </c>
       <c r="C7" t="str">
-        <v>assets/1787328436957-x30od0gw28.jpg</v>
+        <v>assets/1787837594903-wtnbv2fz89.jpg</v>
       </c>
       <c r="D7" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E7" t="str">
-        <v/>
+        <v>2026-06-10</v>
       </c>
       <c r="F7" t="str">
-        <v>江苏苏州</v>
+        <v/>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -820,22 +820,22 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B8" t="str">
         <v>弟弟</v>
       </c>
       <c r="C8" t="str">
-        <v>assets/1787328420967-viv9v8nbjn.jpg</v>
+        <v>assets/1787479268842-7en9nzy302.jpg</v>
       </c>
       <c r="D8" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E8" t="str">
-        <v/>
+        <v>2026-06-10</v>
       </c>
       <c r="F8" t="str">
-        <v>辽宁东港</v>
+        <v/>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -847,7 +847,7 @@
         <v/>
       </c>
       <c r="J8" t="str">
-        <v/>
+        <v>2026-06-10</v>
       </c>
       <c r="K8" t="str">
         <v/>
@@ -879,22 +879,22 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>棕虎斑</v>
+        <v>纯黑色</v>
       </c>
       <c r="B9" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C9" t="str">
-        <v>assets/1787327967245-m62ohievcl.jpg</v>
+        <v>assets/1787479242639-32zuh5lham.jpg</v>
       </c>
       <c r="D9" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E9" t="str">
-        <v/>
+        <v>2026-06-10</v>
       </c>
       <c r="F9" t="str">
-        <v>福建福州</v>
+        <v/>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -938,13 +938,13 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B10" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C10" t="str">
-        <v>assets/1787327853521-js8ljh3ulj.jpg</v>
+        <v>assets/1787466121255-21jto2cugv.jpg</v>
       </c>
       <c r="D10" t="str">
         <v>是</v>
@@ -953,7 +953,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>上海</v>
+        <v>四川广安</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -997,22 +997,22 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>纯蓝色</v>
+        <v>烟灰色</v>
       </c>
       <c r="B11" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C11" t="str">
-        <v>assets/1787327793837-znk2knoo6p.jpg</v>
+        <v>assets/1787388322060-uj8bkwqgnv.jpg</v>
       </c>
       <c r="D11" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E11" t="str">
-        <v/>
+        <v>2026-06-06</v>
       </c>
       <c r="F11" t="str">
-        <v>河南鹤壁</v>
+        <v/>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -1056,22 +1056,22 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B12" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C12" t="str">
-        <v>assets/1787327752832-kkpmp21os3.jpg</v>
+        <v>assets/1787388277490-e6u506cx0r.jpg</v>
       </c>
       <c r="D12" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E12" t="str">
-        <v/>
+        <v>2026-06-06</v>
       </c>
       <c r="F12" t="str">
-        <v>陕西西安</v>
+        <v/>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -1118,10 +1118,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B13" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C13" t="str">
-        <v>assets/1787327605711-4o2f6v6ybp.jpg</v>
+        <v>assets/1787328436957-x30od0gw28.jpg</v>
       </c>
       <c r="D13" t="str">
         <v>是</v>
@@ -1130,7 +1130,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>陕西西安</v>
+        <v>江苏苏州</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -1174,13 +1174,13 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B14" t="str">
         <v>弟弟</v>
       </c>
       <c r="C14" t="str">
-        <v>assets/1787327573762-h23cux94p2.jpg</v>
+        <v>assets/1787328420967-viv9v8nbjn.jpg</v>
       </c>
       <c r="D14" t="str">
         <v>是</v>
@@ -1189,7 +1189,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>北京</v>
+        <v>辽宁东港</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -1233,13 +1233,13 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B15" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C15" t="str">
-        <v>assets/1787327496557-9daggljg4g.jpg</v>
+        <v>assets/1787327967245-m62ohievcl.jpg</v>
       </c>
       <c r="D15" t="str">
         <v>是</v>
@@ -1248,7 +1248,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>黑龙江哈尔滨</v>
+        <v>福建福州</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -1292,13 +1292,13 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>烟灰色</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B16" t="str">
         <v>弟弟</v>
       </c>
       <c r="C16" t="str">
-        <v>assets/1787327456560-p4yhq4qvrv.jpg</v>
+        <v>assets/1787327853521-js8ljh3ulj.jpg</v>
       </c>
       <c r="D16" t="str">
         <v>是</v>
@@ -1307,7 +1307,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>甘肃嘉峪关</v>
+        <v>上海</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1351,13 +1351,13 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>蓝虎斑</v>
+        <v>纯蓝色</v>
       </c>
       <c r="B17" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C17" t="str">
-        <v>assets/1787327421713-zg7np4yzkc.jpg</v>
+        <v>assets/1787327793837-znk2knoo6p.jpg</v>
       </c>
       <c r="D17" t="str">
         <v>是</v>
@@ -1366,7 +1366,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>安徽合肥</v>
+        <v>河南鹤壁</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1416,7 +1416,7 @@
         <v>弟弟</v>
       </c>
       <c r="C18" t="str">
-        <v>assets/1787327337811-u5u2pdew3.jpg</v>
+        <v>assets/1787327752832-kkpmp21os3.jpg</v>
       </c>
       <c r="D18" t="str">
         <v>是</v>
@@ -1425,7 +1425,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>安徽合肥</v>
+        <v>陕西西安</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1469,13 +1469,13 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B19" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C19" t="str">
-        <v>assets/1787327309143-6c1dan1sev.jpg</v>
+        <v>assets/1787327605711-4o2f6v6ybp.jpg</v>
       </c>
       <c r="D19" t="str">
         <v>是</v>
@@ -1484,7 +1484,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>四川成都</v>
+        <v>陕西西安</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1534,7 +1534,7 @@
         <v>弟弟</v>
       </c>
       <c r="C20" t="str">
-        <v>assets/1787327277453-w89ujg69fm.jpg</v>
+        <v>assets/1787327573762-h23cux94p2.jpg</v>
       </c>
       <c r="D20" t="str">
         <v>是</v>
@@ -1543,7 +1543,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>四川成都</v>
+        <v>北京</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1587,13 +1587,13 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>蓝银虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B21" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C21" t="str">
-        <v>assets/1787327232159-lkrcl588a5.jpg</v>
+        <v>assets/1787327496557-9daggljg4g.jpg</v>
       </c>
       <c r="D21" t="str">
         <v>是</v>
@@ -1602,7 +1602,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>四川成都</v>
+        <v>黑龙江哈尔滨</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1646,13 +1646,13 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>玳瑁色</v>
+        <v>烟灰色</v>
       </c>
       <c r="B22" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C22" t="str">
-        <v>assets/1787327182347-3az0z7sys2.jpg</v>
+        <v>assets/1787327456560-p4yhq4qvrv.jpg</v>
       </c>
       <c r="D22" t="str">
         <v>是</v>
@@ -1661,7 +1661,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>四川内江</v>
+        <v>甘肃嘉峪关</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1705,13 +1705,13 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>棕虎补丁</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B23" t="str">
         <v>妹妹</v>
       </c>
       <c r="C23" t="str">
-        <v>assets/1787327143756-4xtgfy5ozu.jpg</v>
+        <v>assets/1787327421713-zg7np4yzkc.jpg</v>
       </c>
       <c r="D23" t="str">
         <v>是</v>
@@ -1720,7 +1720,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>贵州贵阳</v>
+        <v>安徽合肥</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1764,13 +1764,13 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>黑烟色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B24" t="str">
         <v>弟弟</v>
       </c>
       <c r="C24" t="str">
-        <v>assets/1787327101790-tqjlseog5y.jpg</v>
+        <v>assets/1787327337811-u5u2pdew3.jpg</v>
       </c>
       <c r="D24" t="str">
         <v>是</v>
@@ -1779,7 +1779,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>浙江杭州</v>
+        <v>安徽合肥</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1823,13 +1823,13 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B25" t="str">
         <v>弟弟</v>
       </c>
       <c r="C25" t="str">
-        <v>assets/1787327019632-l1780lu2hj.jpg</v>
+        <v>assets/1787327309143-6c1dan1sev.jpg</v>
       </c>
       <c r="D25" t="str">
         <v>是</v>
@@ -1838,7 +1838,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>山东威海</v>
+        <v>四川成都</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1882,13 +1882,13 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>棕虎补丁</v>
+        <v>银虎斑</v>
       </c>
       <c r="B26" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C26" t="str">
-        <v>assets/1787326905275-plz3fpgo97.jpg</v>
+        <v>assets/1787327277453-w89ujg69fm.jpg</v>
       </c>
       <c r="D26" t="str">
         <v>是</v>
@@ -1897,7 +1897,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>浙江杭州</v>
+        <v>四川成都</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1941,13 +1941,13 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>蓝虎斑</v>
+        <v>蓝银虎斑</v>
       </c>
       <c r="B27" t="str">
         <v>弟弟</v>
       </c>
       <c r="C27" t="str">
-        <v>assets/1787326874462-z9rzs7wg17.jpg</v>
+        <v>assets/1787327232159-lkrcl588a5.jpg</v>
       </c>
       <c r="D27" t="str">
         <v>是</v>
@@ -2000,13 +2000,13 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>凯米尔色</v>
+        <v>玳瑁色</v>
       </c>
       <c r="B28" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C28" t="str">
-        <v>assets/1787326843271-0uhv7b9p89.jpg</v>
+        <v>assets/1787327182347-3az0z7sys2.jpg</v>
       </c>
       <c r="D28" t="str">
         <v>是</v>
@@ -2015,7 +2015,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>四川成都</v>
+        <v>四川内江</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -2059,13 +2059,13 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>凯米尔</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B29" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C29" t="str">
-        <v>assets/1787326814713-p5oavnlulg.jpg</v>
+        <v>assets/1787327143756-4xtgfy5ozu.jpg</v>
       </c>
       <c r="D29" t="str">
         <v>是</v>
@@ -2074,7 +2074,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>四川成都</v>
+        <v>贵州贵阳</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -2118,13 +2118,13 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>棕虎斑</v>
+        <v>黑烟色</v>
       </c>
       <c r="B30" t="str">
         <v>弟弟</v>
       </c>
       <c r="C30" t="str">
-        <v>assets/1787326773577-13q5out2d0.jpg</v>
+        <v>assets/1787327101790-tqjlseog5y.jpg</v>
       </c>
       <c r="D30" t="str">
         <v>是</v>
@@ -2133,7 +2133,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>四川宜宾</v>
+        <v>浙江杭州</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -2177,13 +2177,13 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>金棕虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B31" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C31" t="str">
-        <v>assets/1787326548993-89s929m2hg.jpg</v>
+        <v>assets/1787327019632-l1780lu2hj.jpg</v>
       </c>
       <c r="D31" t="str">
         <v>是</v>
@@ -2192,7 +2192,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>上海</v>
+        <v>山东威海</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -2236,13 +2236,13 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>凯米尔色</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B32" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C32" t="str">
-        <v>assets/1787326449218-09s9ucram4.jpg</v>
+        <v>assets/1787326905275-plz3fpgo97.jpg</v>
       </c>
       <c r="D32" t="str">
         <v>是</v>
@@ -2251,7 +2251,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>德国</v>
+        <v>浙江杭州</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -2295,13 +2295,13 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>棕虎补丁</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B33" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C33" t="str">
-        <v>assets/1787326277374-8ti107m5ki.jpg</v>
+        <v>assets/1787326874462-z9rzs7wg17.jpg</v>
       </c>
       <c r="D33" t="str">
         <v>是</v>
@@ -2310,7 +2310,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>广东深圳</v>
+        <v>四川成都</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -2354,13 +2354,13 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>烟灰色</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B34" t="str">
         <v>弟弟</v>
       </c>
       <c r="C34" t="str">
-        <v>assets/1787326236952-2pmwche4t3.jpg</v>
+        <v>assets/1787326843271-0uhv7b9p89.jpg</v>
       </c>
       <c r="D34" t="str">
         <v>是</v>
@@ -2369,7 +2369,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>福建泉州</v>
+        <v>四川成都</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -2413,13 +2413,13 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>银虎斑</v>
+        <v>凯米尔</v>
       </c>
       <c r="B35" t="str">
         <v>弟弟</v>
       </c>
       <c r="C35" t="str">
-        <v>assets/1787326184557-90v6clkwen.jpg</v>
+        <v>assets/1787326814713-p5oavnlulg.jpg</v>
       </c>
       <c r="D35" t="str">
         <v>是</v>
@@ -2428,7 +2428,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>福建福州</v>
+        <v>四川成都</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -2475,10 +2475,10 @@
         <v>棕虎斑</v>
       </c>
       <c r="B36" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C36" t="str">
-        <v>assets/1787326046155-4tk23nq4dj.jpg</v>
+        <v>assets/1787326773577-13q5out2d0.jpg</v>
       </c>
       <c r="D36" t="str">
         <v>是</v>
@@ -2487,7 +2487,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>广西贵港</v>
+        <v>四川宜宾</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -2531,13 +2531,13 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>凯米尔色</v>
+        <v>金棕虎斑</v>
       </c>
       <c r="B37" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C37" t="str">
-        <v>assets/1787325862706-wq18k3ej56.jpg</v>
+        <v>assets/1787326548993-89s929m2hg.jpg</v>
       </c>
       <c r="D37" t="str">
         <v>是</v>
@@ -2546,7 +2546,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>江苏苏州</v>
+        <v>上海</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -2596,7 +2596,7 @@
         <v>弟弟</v>
       </c>
       <c r="C38" t="str">
-        <v>assets/1787325743258-a7oac7hzlo.jpg</v>
+        <v>assets/1787326449218-09s9ucram4.jpg</v>
       </c>
       <c r="D38" t="str">
         <v>是</v>
@@ -2605,7 +2605,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>江苏苏州</v>
+        <v>德国</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -2649,13 +2649,13 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>银虎斑</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B39" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C39" t="str">
-        <v>assets/1787325706797-kgk81ghccy.jpg</v>
+        <v>assets/1787326277374-8ti107m5ki.jpg</v>
       </c>
       <c r="D39" t="str">
         <v>是</v>
@@ -2664,7 +2664,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>北京</v>
+        <v>广东深圳</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -2708,13 +2708,13 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>蓝虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B40" t="str">
         <v>弟弟</v>
       </c>
       <c r="C40" t="str">
-        <v>assets/1787325603704-lahzgrm7fa.jpg,assets/1787325690106-wgu3spujit.jpg</v>
+        <v>assets/1787326236952-2pmwche4t3.jpg</v>
       </c>
       <c r="D40" t="str">
         <v>是</v>
@@ -2723,7 +2723,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>上海</v>
+        <v>福建泉州</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -2767,13 +2767,13 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B41" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C41" t="str">
-        <v>assets/1787325554341-608thexrne.jpg</v>
+        <v>assets/1787326184557-90v6clkwen.jpg</v>
       </c>
       <c r="D41" t="str">
         <v>是</v>
@@ -2782,7 +2782,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>江苏苏州</v>
+        <v>福建福州</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -2826,13 +2826,13 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>浅色银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B42" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C42" t="str">
-        <v>assets/1787325480828-q90pskoiw3.jpg</v>
+        <v>assets/1787326046155-4tk23nq4dj.jpg</v>
       </c>
       <c r="D42" t="str">
         <v>是</v>
@@ -2841,7 +2841,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>四川成都</v>
+        <v>广西贵港</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -2885,13 +2885,13 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>浅色银虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B43" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C43" t="str">
-        <v>assets/1787325448999-a2pg8176fu.jpg</v>
+        <v>assets/1787325862706-wq18k3ej56.jpg</v>
       </c>
       <c r="D43" t="str">
         <v>是</v>
@@ -2900,7 +2900,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>中国台湾</v>
+        <v>江苏苏州</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2944,13 +2944,13 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>棕虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B44" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C44" t="str">
-        <v>assets/1787325357634-k55zlfhmqj.jpg</v>
+        <v>assets/1787325743258-a7oac7hzlo.jpg</v>
       </c>
       <c r="D44" t="str">
         <v>是</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>浙江杭州</v>
+        <v>江苏苏州</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -3003,13 +3003,13 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>烟灰色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B45" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C45" t="str">
-        <v>assets/1787325237876-t19isaq5gu.jpg</v>
+        <v>assets/1787325706797-kgk81ghccy.jpg</v>
       </c>
       <c r="D45" t="str">
         <v>是</v>
@@ -3018,7 +3018,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>辽宁沈阳</v>
+        <v>北京</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -3062,13 +3062,13 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>金棕虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B46" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C46" t="str">
-        <v>assets/1787325199931-e7wms9qtya.jpg</v>
+        <v>assets/1787325603704-lahzgrm7fa.jpg,assets/1787325690106-wgu3spujit.jpg</v>
       </c>
       <c r="D46" t="str">
         <v>是</v>
@@ -3077,7 +3077,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>四川成都</v>
+        <v>上海</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -3121,13 +3121,13 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B47" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C47" t="str">
-        <v>assets/1787325172354-4sa8uzaey2.jpg</v>
+        <v>assets/1787325554341-608thexrne.jpg</v>
       </c>
       <c r="D47" t="str">
         <v>是</v>
@@ -3136,7 +3136,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>中国香港</v>
+        <v>江苏苏州</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -3180,13 +3180,13 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>烟灰色</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B48" t="str">
         <v>弟弟</v>
       </c>
       <c r="C48" t="str">
-        <v>assets/1787325109283-y7mvkk6qg4.jpg</v>
+        <v>assets/1787325480828-q90pskoiw3.jpg</v>
       </c>
       <c r="D48" t="str">
         <v>是</v>
@@ -3195,7 +3195,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>中国澳门</v>
+        <v>四川成都</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -3239,13 +3239,13 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>蓝虎斑</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B49" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C49" t="str">
-        <v>assets/1787325033629-y3ygps3zaj.jpg</v>
+        <v>assets/1787325448999-a2pg8176fu.jpg</v>
       </c>
       <c r="D49" t="str">
         <v>是</v>
@@ -3254,7 +3254,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>山东青岛</v>
+        <v>中国台湾</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -3298,13 +3298,13 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B50" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C50" t="str">
-        <v>assets/1787324954998-w5m5jox439.jpg</v>
+        <v>assets/1787325357634-k55zlfhmqj.jpg</v>
       </c>
       <c r="D50" t="str">
         <v>是</v>
@@ -3313,7 +3313,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>海南海口</v>
+        <v>浙江杭州</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -3357,13 +3357,13 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>棕虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B51" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C51" t="str">
-        <v>assets/1787324905909-zrz8o79kdf.jpg</v>
+        <v>assets/1787325237876-t19isaq5gu.jpg</v>
       </c>
       <c r="D51" t="str">
         <v>是</v>
@@ -3372,7 +3372,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>内蒙古</v>
+        <v>辽宁沈阳</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -3416,13 +3416,13 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>烟灰色</v>
+        <v>金棕虎斑</v>
       </c>
       <c r="B52" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C52" t="str">
-        <v>assets/1787324880505-gbh0sn7b6j.jpg</v>
+        <v>assets/1787325199931-e7wms9qtya.jpg</v>
       </c>
       <c r="D52" t="str">
         <v>是</v>
@@ -3431,7 +3431,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>中国香港</v>
+        <v>四川成都</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -3475,13 +3475,13 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>烟灰色</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B53" t="str">
         <v>弟弟</v>
       </c>
       <c r="C53" t="str">
-        <v>assets/1787324806613-31yyz14tsf.jpg</v>
+        <v>assets/1787325172354-4sa8uzaey2.jpg</v>
       </c>
       <c r="D53" t="str">
         <v>是</v>
@@ -3490,7 +3490,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>四川成都</v>
+        <v>中国香港</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -3534,13 +3534,13 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>红虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B54" t="str">
         <v>弟弟</v>
       </c>
       <c r="C54" t="str">
-        <v>assets/1787324789658-uz6ephkdsh.jpg</v>
+        <v>assets/1787325109283-y7mvkk6qg4.jpg</v>
       </c>
       <c r="D54" t="str">
         <v>是</v>
@@ -3549,7 +3549,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>湖北武汉</v>
+        <v>中国澳门</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -3593,13 +3593,13 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>烟灰色</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B55" t="str">
         <v>弟弟</v>
       </c>
       <c r="C55" t="str">
-        <v>assets/1787324522658-smn44crast.jpg</v>
+        <v>assets/1787325033629-y3ygps3zaj.jpg</v>
       </c>
       <c r="D55" t="str">
         <v>是</v>
@@ -3608,7 +3608,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>湖北武汉</v>
+        <v>山东青岛</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -3652,13 +3652,13 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>棕虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B56" t="str">
         <v>弟弟</v>
       </c>
       <c r="C56" t="str">
-        <v>assets/1787324365608-6xtrjp7euz.jpg</v>
+        <v>assets/1787324954998-w5m5jox439.jpg</v>
       </c>
       <c r="D56" t="str">
         <v>是</v>
@@ -3667,7 +3667,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>新疆</v>
+        <v>海南海口</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -3711,13 +3711,13 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>浅凯米尔</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B57" t="str">
         <v>弟弟</v>
       </c>
       <c r="C57" t="str">
-        <v>assets/1787324331029-d74lcuycf6.jpg</v>
+        <v>assets/1787324905909-zrz8o79kdf.jpg</v>
       </c>
       <c r="D57" t="str">
         <v>是</v>
@@ -3726,7 +3726,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>四川成都</v>
+        <v>内蒙古</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -3770,13 +3770,13 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>红虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B58" t="str">
         <v>弟弟</v>
       </c>
       <c r="C58" t="str">
-        <v>assets/1787324297469-ans1lse2l5.jpg</v>
+        <v>assets/1787324880505-gbh0sn7b6j.jpg</v>
       </c>
       <c r="D58" t="str">
         <v>是</v>
@@ -3785,7 +3785,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>四川乐山</v>
+        <v>中国香港</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -3829,13 +3829,13 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>红虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B59" t="str">
         <v>弟弟</v>
       </c>
       <c r="C59" t="str">
-        <v>assets/1787324256827-7w383z4bg1.jpg</v>
+        <v>assets/1787324806613-31yyz14tsf.jpg</v>
       </c>
       <c r="D59" t="str">
         <v>是</v>
@@ -3844,7 +3844,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>中国台湾</v>
+        <v>四川成都</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -3888,13 +3888,13 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B60" t="str">
         <v>弟弟</v>
       </c>
       <c r="C60" t="str">
-        <v>assets/1787324228262-y3vwn6i4zk.jpg</v>
+        <v>assets/1787324789658-uz6ephkdsh.jpg</v>
       </c>
       <c r="D60" t="str">
         <v>是</v>
@@ -3903,7 +3903,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>四川成都</v>
+        <v>湖北武汉</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -3947,13 +3947,13 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>凯米尔色</v>
+        <v>烟灰色</v>
       </c>
       <c r="B61" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C61" t="str">
-        <v>assets/1787324201418-9tk4ik75mo.jpg</v>
+        <v>assets/1787324522658-smn44crast.jpg</v>
       </c>
       <c r="D61" t="str">
         <v>是</v>
@@ -3962,7 +3962,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>江苏南京</v>
+        <v>湖北武汉</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -4012,7 +4012,7 @@
         <v>弟弟</v>
       </c>
       <c r="C62" t="str">
-        <v>assets/1787324092513-jpa2rmkci2.jpg</v>
+        <v>assets/1787324365608-6xtrjp7euz.jpg</v>
       </c>
       <c r="D62" t="str">
         <v>是</v>
@@ -4021,7 +4021,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>江苏南京</v>
+        <v>新疆</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -4065,13 +4065,13 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>银虎斑</v>
+        <v>浅凯米尔</v>
       </c>
       <c r="B63" t="str">
         <v>弟弟</v>
       </c>
       <c r="C63" t="str">
-        <v>assets/1787323318612-soge38hpsf.jpg</v>
+        <v>assets/1787324331029-d74lcuycf6.jpg</v>
       </c>
       <c r="D63" t="str">
         <v>是</v>
@@ -4080,7 +4080,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>上海</v>
+        <v>四川成都</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -4124,13 +4124,13 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>棕虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B64" t="str">
         <v>弟弟</v>
       </c>
       <c r="C64" t="str">
-        <v>assets/1787323235892-7yq8ioq01e.jpg</v>
+        <v>assets/1787324297469-ans1lse2l5.jpg</v>
       </c>
       <c r="D64" t="str">
         <v>是</v>
@@ -4139,7 +4139,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>四川成都</v>
+        <v>四川乐山</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -4183,13 +4183,13 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B65" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C65" t="str">
-        <v>assets/1787322988096-6e2f54q7vo.jpg</v>
+        <v>assets/1787324256827-7w383z4bg1.jpg</v>
       </c>
       <c r="D65" t="str">
         <v>是</v>
@@ -4198,7 +4198,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>浙江宁波</v>
+        <v>中国台湾</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -4242,13 +4242,13 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>银虎斑补丁</v>
+        <v>银虎斑</v>
       </c>
       <c r="B66" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C66" t="str">
-        <v>assets/1787322938518-85ev8bs2k5.jpg</v>
+        <v>assets/1787324228262-y3vwn6i4zk.jpg</v>
       </c>
       <c r="D66" t="str">
         <v>是</v>
@@ -4257,7 +4257,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>马来西亚</v>
+        <v>四川成都</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -4301,13 +4301,13 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>银虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B67" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C67" t="str">
-        <v>assets/1787322881183-tzu9xtw2sg.jpg</v>
+        <v>assets/1787324201418-9tk4ik75mo.jpg</v>
       </c>
       <c r="D67" t="str">
         <v>是</v>
@@ -4316,7 +4316,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>陕西西安</v>
+        <v>江苏南京</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -4360,13 +4360,13 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>纯黑色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B68" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C68" t="str">
-        <v>assets/1787322840098-nhy4jjyx7k.jpg</v>
+        <v>assets/1787324092513-jpa2rmkci2.jpg</v>
       </c>
       <c r="D68" t="str">
         <v>是</v>
@@ -4375,7 +4375,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>广西南宁</v>
+        <v>江苏南京</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -4419,13 +4419,13 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B69" t="str">
         <v>弟弟</v>
       </c>
       <c r="C69" t="str">
-        <v>assets/1787322760950-gn3qgego4s.jpg</v>
+        <v>assets/1787323318612-soge38hpsf.jpg</v>
       </c>
       <c r="D69" t="str">
         <v>是</v>
@@ -4434,7 +4434,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>广西南宁</v>
+        <v>上海</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -4478,13 +4478,13 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>红虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B70" t="str">
         <v>弟弟</v>
       </c>
       <c r="C70" t="str">
-        <v>assets/1787322605982-04n50xegt2.jpg</v>
+        <v>assets/1787323235892-7yq8ioq01e.jpg</v>
       </c>
       <c r="D70" t="str">
         <v>是</v>
@@ -4493,7 +4493,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>上海</v>
+        <v>四川成都</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -4537,13 +4537,13 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>蓝虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B71" t="str">
         <v>妹妹</v>
       </c>
       <c r="C71" t="str">
-        <v>assets/1787322490045-kog3ru43dy.jpg</v>
+        <v>assets/1787322988096-6e2f54q7vo.jpg</v>
       </c>
       <c r="D71" t="str">
         <v>是</v>
@@ -4552,7 +4552,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>上海</v>
+        <v>浙江宁波</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -4596,13 +4596,13 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>红虎斑</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B72" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C72" t="str">
-        <v>assets/1787322419996-0m33yx89nm.jpg</v>
+        <v>assets/1787322938518-85ev8bs2k5.jpg</v>
       </c>
       <c r="D72" t="str">
         <v>是</v>
@@ -4611,7 +4611,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>广东广州</v>
+        <v>马来西亚</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -4655,13 +4655,13 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>浅色银虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B73" t="str">
         <v>弟弟</v>
       </c>
       <c r="C73" t="str">
-        <v>assets/1787322377730-vj5csj2mll.jpg</v>
+        <v>assets/1787322881183-tzu9xtw2sg.jpg</v>
       </c>
       <c r="D73" t="str">
         <v>是</v>
@@ -4670,7 +4670,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>柬埔寨</v>
+        <v>陕西西安</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -4714,13 +4714,13 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>蓝虎斑</v>
+        <v>纯黑色</v>
       </c>
       <c r="B74" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C74" t="str">
-        <v>assets/1787322269611-53yaj5ideu.jpg</v>
+        <v>assets/1787322840098-nhy4jjyx7k.jpg</v>
       </c>
       <c r="D74" t="str">
         <v>是</v>
@@ -4729,7 +4729,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>山东枣庄</v>
+        <v>广西南宁</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -4773,13 +4773,13 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B75" t="str">
         <v>弟弟</v>
       </c>
       <c r="C75" t="str">
-        <v>assets/1787321989528-7d6liuhuk9.jpg</v>
+        <v>assets/1787322760950-gn3qgego4s.jpg</v>
       </c>
       <c r="D75" t="str">
         <v>是</v>
@@ -4788,7 +4788,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>陕西西安</v>
+        <v>广西南宁</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -4832,13 +4832,13 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B76" t="str">
         <v>弟弟</v>
       </c>
       <c r="C76" t="str">
-        <v>assets/1787321941642-xlrc1no2ua.jpg</v>
+        <v>assets/1787322605982-04n50xegt2.jpg</v>
       </c>
       <c r="D76" t="str">
         <v>是</v>
@@ -4847,7 +4847,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>山东东营</v>
+        <v>上海</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -4891,13 +4891,13 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>凯米尔色</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B77" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C77" t="str">
-        <v>assets/1787321903535-6orj7qcgzn.jpg</v>
+        <v>assets/1787322490045-kog3ru43dy.jpg</v>
       </c>
       <c r="D77" t="str">
         <v>是</v>
@@ -4906,7 +4906,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>中国台湾</v>
+        <v>上海</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -4950,13 +4950,13 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>烟灰色</v>
+        <v>红虎斑</v>
       </c>
       <c r="B78" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C78" t="str">
-        <v>assets/1787321858985-v4qej7cq7g.jpg</v>
+        <v>assets/1787322419996-0m33yx89nm.jpg</v>
       </c>
       <c r="D78" t="str">
         <v>是</v>
@@ -4965,7 +4965,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>中国台湾</v>
+        <v>广东广州</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -5009,13 +5009,13 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>银虎斑</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B79" t="str">
         <v>弟弟</v>
       </c>
       <c r="C79" t="str">
-        <v>assets/1787321834306-efgnyhujon.jpg</v>
+        <v>assets/1787322377730-vj5csj2mll.jpg</v>
       </c>
       <c r="D79" t="str">
         <v>是</v>
@@ -5024,7 +5024,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>北京</v>
+        <v>柬埔寨</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -5068,13 +5068,13 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B80" t="str">
         <v>弟弟</v>
       </c>
       <c r="C80" t="str">
-        <v>assets/1787321439916-uttgpbkogb.jpg</v>
+        <v>assets/1787322269611-53yaj5ideu.jpg</v>
       </c>
       <c r="D80" t="str">
         <v>是</v>
@@ -5083,7 +5083,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>安徽合肥</v>
+        <v>山东枣庄</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -5133,7 +5133,7 @@
         <v>弟弟</v>
       </c>
       <c r="C81" t="str">
-        <v>assets/1787321419210-51hhgurygq.jpg</v>
+        <v>assets/1787321989528-7d6liuhuk9.jpg</v>
       </c>
       <c r="D81" t="str">
         <v>是</v>
@@ -5142,7 +5142,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>上海</v>
+        <v>陕西西安</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -5186,13 +5186,13 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>凯米尔色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B82" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C82" t="str">
-        <v>assets/1787321363369-bzjn51j5il.jpg</v>
+        <v>assets/1787321941642-xlrc1no2ua.jpg</v>
       </c>
       <c r="D82" t="str">
         <v>是</v>
@@ -5201,7 +5201,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>中国台湾</v>
+        <v>山东东营</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -5245,13 +5245,13 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>棕虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B83" t="str">
         <v>弟弟</v>
       </c>
       <c r="C83" t="str">
-        <v>assets/1787321332559-87p6spuch3.jpg</v>
+        <v>assets/1787321903535-6orj7qcgzn.jpg</v>
       </c>
       <c r="D83" t="str">
         <v>是</v>
@@ -5304,13 +5304,13 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>棕虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B84" t="str">
         <v>妹妹</v>
       </c>
       <c r="C84" t="str">
-        <v>assets/1787321232531-59lnzv8y98.jpg</v>
+        <v>assets/1787321858985-v4qej7cq7g.jpg</v>
       </c>
       <c r="D84" t="str">
         <v>是</v>
@@ -5319,7 +5319,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>北京</v>
+        <v>中国台湾</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -5366,10 +5366,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B85" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C85" t="str">
-        <v>assets/1787319975814-g1pfa56vfp.jpg</v>
+        <v>assets/1787321834306-efgnyhujon.jpg</v>
       </c>
       <c r="D85" t="str">
         <v>是</v>
@@ -5378,7 +5378,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>浙江宁波</v>
+        <v>北京</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -5425,10 +5425,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B86" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C86" t="str">
-        <v>assets/1787319800704-v3qeu062ak.jpg</v>
+        <v>assets/1787321439916-uttgpbkogb.jpg</v>
       </c>
       <c r="D86" t="str">
         <v>是</v>
@@ -5437,7 +5437,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>河北唐山</v>
+        <v>安徽合肥</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -5484,10 +5484,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B87" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C87" t="str">
-        <v>assets/1787319745369-zn66xr3bvb.jpg</v>
+        <v>assets/1787321419210-51hhgurygq.jpg</v>
       </c>
       <c r="D87" t="str">
         <v>是</v>
@@ -5496,7 +5496,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>河北石家庄</v>
+        <v>上海</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -5540,13 +5540,13 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>棕虎补丁</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B88" t="str">
         <v>妹妹</v>
       </c>
       <c r="C88" t="str">
-        <v>assets/1787319547969-zqlq35fxxt.jpg</v>
+        <v>assets/1787321363369-bzjn51j5il.jpg</v>
       </c>
       <c r="D88" t="str">
         <v>是</v>
@@ -5555,7 +5555,7 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>韩国</v>
+        <v>中国台湾</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -5599,13 +5599,13 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>蓝银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B89" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C89" t="str">
-        <v>assets/1787319501376-xscwljnu1j.jpg</v>
+        <v>assets/1787321332559-87p6spuch3.jpg</v>
       </c>
       <c r="D89" t="str">
         <v>是</v>
@@ -5614,7 +5614,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>美国</v>
+        <v>中国台湾</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -5664,7 +5664,7 @@
         <v>妹妹</v>
       </c>
       <c r="C90" t="str">
-        <v>assets/1787319443529-4a0zqikufx.jpg</v>
+        <v>assets/1787321232531-59lnzv8y98.jpg</v>
       </c>
       <c r="D90" t="str">
         <v>是</v>
@@ -5673,7 +5673,7 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>中国台湾</v>
+        <v>北京</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -5717,13 +5717,13 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>蓝虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B91" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C91" t="str">
-        <v>assets/1787319356194-lr2d5680i9.jpg</v>
+        <v>assets/1787319975814-g1pfa56vfp.jpg</v>
       </c>
       <c r="D91" t="str">
         <v>是</v>
@@ -5732,7 +5732,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>中国台湾</v>
+        <v>浙江宁波</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -5776,13 +5776,13 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B92" t="str">
         <v>妹妹</v>
       </c>
       <c r="C92" t="str">
-        <v>assets/1787319208828-aizqo4blcv.jpg</v>
+        <v>assets/1787319800704-v3qeu062ak.jpg</v>
       </c>
       <c r="D92" t="str">
         <v>是</v>
@@ -5791,7 +5791,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>山东淄博</v>
+        <v>河北唐山</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -5841,7 +5841,7 @@
         <v>妹妹</v>
       </c>
       <c r="C93" t="str">
-        <v>assets/1787319162970-cc2v8ovnni.jpg</v>
+        <v>assets/1787319745369-zn66xr3bvb.jpg</v>
       </c>
       <c r="D93" t="str">
         <v>是</v>
@@ -5850,7 +5850,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>韩国</v>
+        <v>河北石家庄</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -5900,7 +5900,7 @@
         <v>妹妹</v>
       </c>
       <c r="C94" t="str">
-        <v>assets/1787319098214-8pwa9yx2wc.jpg</v>
+        <v>assets/1787319547969-zqlq35fxxt.jpg</v>
       </c>
       <c r="D94" t="str">
         <v>是</v>
@@ -5909,7 +5909,7 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>四川成都</v>
+        <v>韩国</v>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -5953,13 +5953,13 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>银虎斑</v>
+        <v>蓝银虎斑</v>
       </c>
       <c r="B95" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C95" t="str">
-        <v>assets/1787318867999-3gxdddp72x.jpg</v>
+        <v>assets/1787319501376-xscwljnu1j.jpg</v>
       </c>
       <c r="D95" t="str">
         <v>是</v>
@@ -5968,7 +5968,7 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>广东广州</v>
+        <v>美国</v>
       </c>
       <c r="G95" t="str">
         <v/>
@@ -6012,13 +6012,13 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B96" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C96" t="str">
-        <v>assets/1787318609722-0ojb3aikwi.jpg</v>
+        <v>assets/1787319443529-4a0zqikufx.jpg</v>
       </c>
       <c r="D96" t="str">
         <v>是</v>
@@ -6027,7 +6027,7 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>黑龙江鹤岗</v>
+        <v>中国台湾</v>
       </c>
       <c r="G96" t="str">
         <v/>
@@ -6077,7 +6077,7 @@
         <v>弟弟</v>
       </c>
       <c r="C97" t="str">
-        <v>assets/1787318530612-779fbkfcoi.jpg</v>
+        <v>assets/1787319356194-lr2d5680i9.jpg</v>
       </c>
       <c r="D97" t="str">
         <v>是</v>
@@ -6086,7 +6086,7 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>天津</v>
+        <v>中国台湾</v>
       </c>
       <c r="G97" t="str">
         <v/>
@@ -6130,13 +6130,13 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B98" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C98" t="str">
-        <v>assets/1787318365475-sj87wtsai3.jpg</v>
+        <v>assets/1787319208828-aizqo4blcv.jpg</v>
       </c>
       <c r="D98" t="str">
         <v>是</v>
@@ -6145,7 +6145,7 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>山西朔州</v>
+        <v>山东淄博</v>
       </c>
       <c r="G98" t="str">
         <v/>
@@ -6175,7 +6175,7 @@
         <v/>
       </c>
       <c r="P98" t="str">
-        <v>已接猫</v>
+        <v/>
       </c>
       <c r="Q98" t="str">
         <v/>
@@ -6195,7 +6195,7 @@
         <v>妹妹</v>
       </c>
       <c r="C99" t="str">
-        <v>assets/1787318326155-ia4noopjhq.jpg</v>
+        <v>assets/1787319162970-cc2v8ovnni.jpg</v>
       </c>
       <c r="D99" t="str">
         <v>是</v>
@@ -6204,7 +6204,7 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>贵州</v>
+        <v>韩国</v>
       </c>
       <c r="G99" t="str">
         <v/>
@@ -6248,22 +6248,22 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>棕虎斑</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B100" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C100" t="str">
-        <v>assets/1787304479674-w0trechn4p.jpg</v>
+        <v>assets/1787319098214-8pwa9yx2wc.jpg</v>
       </c>
       <c r="D100" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E100" t="str">
-        <v>2026-06-06</v>
+        <v/>
       </c>
       <c r="F100" t="str">
-        <v/>
+        <v>四川成都</v>
       </c>
       <c r="G100" t="str">
         <v/>
@@ -6302,27 +6302,27 @@
         <v/>
       </c>
       <c r="S100" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>纯黑色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B101" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C101" t="str">
-        <v>assets/1787283819124-4v7d1w01la.jpg</v>
+        <v>assets/1787318867999-3gxdddp72x.jpg</v>
       </c>
       <c r="D101" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E101" t="str">
-        <v>2026-02-20</v>
+        <v/>
       </c>
       <c r="F101" t="str">
-        <v/>
+        <v>广东广州</v>
       </c>
       <c r="G101" t="str">
         <v/>
@@ -6361,27 +6361,27 @@
         <v/>
       </c>
       <c r="S101" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>阴影色NS12</v>
+        <v>银虎斑</v>
       </c>
       <c r="B102" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C102" t="str">
-        <v>assets/1787283212708-jdnyi6ecci.jpg</v>
+        <v>assets/1787318609722-0ojb3aikwi.jpg</v>
       </c>
       <c r="D102" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E102" t="str">
-        <v>2026-05-28</v>
+        <v/>
       </c>
       <c r="F102" t="str">
-        <v/>
+        <v>黑龙江鹤岗</v>
       </c>
       <c r="G102" t="str">
         <v/>
@@ -6420,27 +6420,27 @@
         <v/>
       </c>
       <c r="S102" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>阴影色NS11</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B103" t="str">
         <v>弟弟</v>
       </c>
       <c r="C103" t="str">
-        <v>assets/1787283153501-s2tjg9spwu.jpg</v>
+        <v>assets/1787318530612-779fbkfcoi.jpg</v>
       </c>
       <c r="D103" t="str">
         <v>是</v>
       </c>
       <c r="E103" t="str">
-        <v>2026-06-15</v>
+        <v/>
       </c>
       <c r="F103" t="str">
-        <v>重庆</v>
+        <v>天津</v>
       </c>
       <c r="G103" t="str">
         <v/>
@@ -6479,27 +6479,27 @@
         <v/>
       </c>
       <c r="S103" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>浅烟灰色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B104" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C104" t="str">
-        <v>assets/1787283092677-i4d8tyrjtf.jpg</v>
+        <v>assets/1787318365475-sj87wtsai3.jpg</v>
       </c>
       <c r="D104" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E104" t="str">
-        <v>2026-03-21</v>
+        <v/>
       </c>
       <c r="F104" t="str">
-        <v/>
+        <v>山西朔州</v>
       </c>
       <c r="G104" t="str">
         <v/>
@@ -6529,7 +6529,7 @@
         <v/>
       </c>
       <c r="P104" t="str">
-        <v/>
+        <v>已接猫</v>
       </c>
       <c r="Q104" t="str">
         <v/>
@@ -6538,27 +6538,27 @@
         <v/>
       </c>
       <c r="S104" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B105" t="str">
         <v>妹妹</v>
       </c>
       <c r="C105" t="str">
-        <v>assets/1787283031104-bpyq9wy2tl.jpg</v>
+        <v>assets/1787318326155-ia4noopjhq.jpg</v>
       </c>
       <c r="D105" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E105" t="str">
-        <v>2026-06-06</v>
+        <v/>
       </c>
       <c r="F105" t="str">
-        <v/>
+        <v>贵州</v>
       </c>
       <c r="G105" t="str">
         <v/>
@@ -6597,7 +6597,7 @@
         <v/>
       </c>
       <c r="S105" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="106">
@@ -6605,10 +6605,10 @@
         <v>棕虎斑</v>
       </c>
       <c r="B106" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C106" t="str">
-        <v>assets/1787282991501-2fjfws0rqw.jpg</v>
+        <v>assets/1787304479674-w0trechn4p.jpg</v>
       </c>
       <c r="D106" t="str">
         <v>否</v>
@@ -6661,19 +6661,19 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>棕虎斑</v>
+        <v>纯黑色</v>
       </c>
       <c r="B107" t="str">
         <v>妹妹</v>
       </c>
       <c r="C107" t="str">
-        <v>assets/1787282942262-syr48fym6c.jpg</v>
+        <v>assets/1787283819124-4v7d1w01la.jpg</v>
       </c>
       <c r="D107" t="str">
         <v>否</v>
       </c>
       <c r="E107" t="str">
-        <v>2026-06-15</v>
+        <v>2026-02-20</v>
       </c>
       <c r="F107" t="str">
         <v/>
@@ -6720,19 +6720,19 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>棕虎斑</v>
+        <v>阴影色NS12</v>
       </c>
       <c r="B108" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C108" t="str">
-        <v>assets/1787282819855-7vhx3m0v40.jpg</v>
+        <v>assets/1787283212708-jdnyi6ecci.jpg</v>
       </c>
       <c r="D108" t="str">
         <v>否</v>
       </c>
       <c r="E108" t="str">
-        <v>2026-06-06</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F108" t="str">
         <v/>
@@ -6779,22 +6779,22 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>棕虎斑</v>
+        <v>阴影色NS11</v>
       </c>
       <c r="B109" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C109" t="str">
-        <v>assets/1787282703381-2uakw592b4.jpg</v>
+        <v>assets/1787283153501-s2tjg9spwu.jpg</v>
       </c>
       <c r="D109" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E109" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F109" t="str">
-        <v/>
+        <v>重庆</v>
       </c>
       <c r="G109" t="str">
         <v/>
@@ -6838,19 +6838,19 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>烟灰色</v>
+        <v>浅烟灰色</v>
       </c>
       <c r="B110" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C110" t="str">
-        <v>assets/1787282649397-9hc31ncrpc.jpg</v>
+        <v>assets/1787283092677-i4d8tyrjtf.jpg</v>
       </c>
       <c r="D110" t="str">
         <v>否</v>
       </c>
       <c r="E110" t="str">
-        <v>2026-06-06</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F110" t="str">
         <v/>
@@ -6897,13 +6897,13 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B111" t="str">
         <v>妹妹</v>
       </c>
       <c r="C111" t="str">
-        <v>assets/1787282617957-svcoyyznpg.jpg</v>
+        <v>assets/1787283031104-bpyq9wy2tl.jpg</v>
       </c>
       <c r="D111" t="str">
         <v>否</v>
@@ -6956,13 +6956,13 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B112" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C112" t="str">
-        <v>assets/1787282419632-78nixqjzua.jpg</v>
+        <v>assets/1787282991501-2fjfws0rqw.jpg</v>
       </c>
       <c r="D112" t="str">
         <v>否</v>
@@ -7015,19 +7015,19 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>纯黑色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B113" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C113" t="str">
-        <v>assets/1787282349942-2cfuyn7xlc.jpg</v>
+        <v>assets/1787282942262-syr48fym6c.jpg</v>
       </c>
       <c r="D113" t="str">
         <v>否</v>
       </c>
       <c r="E113" t="str">
-        <v>2026-03-21</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F113" t="str">
         <v/>
@@ -7074,19 +7074,19 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B114" t="str">
         <v>弟弟</v>
       </c>
       <c r="C114" t="str">
-        <v>assets/1787282064159-6b4z8c5msd.jpg</v>
+        <v>assets/1787282819855-7vhx3m0v40.jpg</v>
       </c>
       <c r="D114" t="str">
         <v>否</v>
       </c>
       <c r="E114" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F114" t="str">
         <v/>
@@ -7133,19 +7133,19 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>阴影色NS11</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B115" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C115" t="str">
-        <v>assets/1787280590041-vzcwebdok1.jpg</v>
+        <v>assets/1787282703381-2uakw592b4.jpg</v>
       </c>
       <c r="D115" t="str">
         <v>否</v>
       </c>
       <c r="E115" t="str">
-        <v>2026-05-28</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F115" t="str">
         <v/>
@@ -7192,19 +7192,19 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>浅色银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B116" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C116" t="str">
-        <v>assets/1787281786169-9ia0h837ct.jpg</v>
+        <v>assets/1787282649397-9hc31ncrpc.jpg</v>
       </c>
       <c r="D116" t="str">
         <v>否</v>
       </c>
       <c r="E116" t="str">
-        <v>2026-06-15</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F116" t="str">
         <v/>
@@ -7251,22 +7251,22 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>浅烟灰色</v>
+        <v>烟灰色</v>
       </c>
       <c r="B117" t="str">
         <v>妹妹</v>
       </c>
       <c r="C117" t="str">
-        <v>assets/1785843720843-63qz159daui.jpg</v>
+        <v>assets/1787282617957-svcoyyznpg.jpg</v>
       </c>
       <c r="D117" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E117" t="str">
-        <v>2026-03-21</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F117" t="str">
-        <v>四川成都</v>
+        <v/>
       </c>
       <c r="G117" t="str">
         <v/>
@@ -7310,22 +7310,22 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>凯米尔色</v>
+        <v>烟灰色</v>
       </c>
       <c r="B118" t="str">
         <v>弟弟</v>
       </c>
       <c r="C118" t="str">
-        <v>assets/1787301984056-iu6afro5z5.jpg, assets/1785843763310-elg05ur61ri.jpg</v>
+        <v>assets/1787282419632-78nixqjzua.jpg</v>
       </c>
       <c r="D118" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E118" t="str">
-        <v>2026-02-14</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F118" t="str">
-        <v>上海浦东</v>
+        <v/>
       </c>
       <c r="G118" t="str">
         <v/>
@@ -7369,19 +7369,19 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>银虎斑补丁</v>
+        <v>纯黑色</v>
       </c>
       <c r="B119" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C119" t="str">
-        <v>assets/1785843820715-9kz7gy4mbr7.jpg</v>
+        <v>assets/1787282349942-2cfuyn7xlc.jpg</v>
       </c>
       <c r="D119" t="str">
         <v>否</v>
       </c>
       <c r="E119" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F119" t="str">
         <v/>
@@ -7428,19 +7428,19 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>烟灰色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B120" t="str">
         <v>弟弟</v>
       </c>
       <c r="C120" t="str">
-        <v>assets/1785843953805-mxl3x1982io.jpg</v>
+        <v>assets/1787282064159-6b4z8c5msd.jpg</v>
       </c>
       <c r="D120" t="str">
         <v>否</v>
       </c>
       <c r="E120" t="str">
-        <v>2026-05-18</v>
+        <v>2026-06-10</v>
       </c>
       <c r="F120" t="str">
         <v/>
@@ -7487,19 +7487,19 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>棕虎斑玳瑁</v>
+        <v>阴影色NS11</v>
       </c>
       <c r="B121" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C121" t="str">
-        <v>assets/1785844013835-ek4xpcje7kh.jpg</v>
+        <v>assets/1787280590041-vzcwebdok1.jpg</v>
       </c>
       <c r="D121" t="str">
         <v>否</v>
       </c>
       <c r="E121" t="str">
-        <v>2026-02-14</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F121" t="str">
         <v/>
@@ -7546,19 +7546,19 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>银虎斑补丁</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B122" t="str">
         <v>妹妹</v>
       </c>
       <c r="C122" t="str">
-        <v>assets/1785844434338-ek5zbdgdcne.jpg</v>
+        <v>assets/1787281786169-9ia0h837ct.jpg</v>
       </c>
       <c r="D122" t="str">
         <v>否</v>
       </c>
       <c r="E122" t="str">
-        <v>2026-05-24</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F122" t="str">
         <v/>
@@ -7605,22 +7605,22 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>银虎斑</v>
+        <v>浅烟灰色</v>
       </c>
       <c r="B123" t="str">
         <v>妹妹</v>
       </c>
       <c r="C123" t="str">
-        <v>assets/1785838787730-s5f333sc3u.jpg</v>
+        <v>assets/1785843720843-63qz159daui.jpg</v>
       </c>
       <c r="D123" t="str">
         <v>是</v>
       </c>
       <c r="E123" t="str">
-        <v>2026-06-05</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F123" t="str">
-        <v>湖北恩施</v>
+        <v>四川成都</v>
       </c>
       <c r="G123" t="str">
         <v/>
@@ -7664,22 +7664,22 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>银虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B124" t="str">
         <v>弟弟</v>
       </c>
       <c r="C124" t="str">
-        <v>assets/1785842296661-6qw3zs3as8h.jpg</v>
+        <v>assets/1787301984056-iu6afro5z5.jpg, assets/1785843763310-elg05ur61ri.jpg</v>
       </c>
       <c r="D124" t="str">
         <v>是</v>
       </c>
       <c r="E124" t="str">
-        <v>2026-06-05</v>
+        <v>2026-02-14</v>
       </c>
       <c r="F124" t="str">
-        <v>湖北恩施</v>
+        <v>上海浦东</v>
       </c>
       <c r="G124" t="str">
         <v/>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>银虎斑</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B125" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C125" t="str">
-        <v>assets/1785842429109-porc98rel5.jpg</v>
+        <v>assets/1785843820715-9kz7gy4mbr7.jpg</v>
       </c>
       <c r="D125" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E125" t="str">
-        <v>2025-11-05</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F125" t="str">
-        <v>韩国</v>
+        <v/>
       </c>
       <c r="G125" t="str">
         <v/>
@@ -7782,13 +7782,13 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B126" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C126" t="str">
-        <v>assets/1785842594141-fcglbzjp509.jpg</v>
+        <v>assets/1785843953805-mxl3x1982io.jpg</v>
       </c>
       <c r="D126" t="str">
         <v>否</v>
@@ -7841,22 +7841,22 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>棕虎斑</v>
+        <v>棕虎斑玳瑁</v>
       </c>
       <c r="B127" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C127" t="str">
-        <v>assets/1785842639100-82k775dhwiv.jpg</v>
+        <v>assets/1785844013835-ek4xpcje7kh.jpg</v>
       </c>
       <c r="D127" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E127" t="str">
-        <v>2026-05-28</v>
+        <v>2026-02-14</v>
       </c>
       <c r="F127" t="str">
-        <v>四川自贡</v>
+        <v/>
       </c>
       <c r="G127" t="str">
         <v/>
@@ -7900,19 +7900,19 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B128" t="str">
         <v>妹妹</v>
       </c>
       <c r="C128" t="str">
-        <v>assets/1785842684502-mnhr0r96eee.jpg</v>
+        <v>assets/1785844434338-ek5zbdgdcne.jpg</v>
       </c>
       <c r="D128" t="str">
         <v>否</v>
       </c>
       <c r="E128" t="str">
-        <v>2026-06-06</v>
+        <v>2026-05-24</v>
       </c>
       <c r="F128" t="str">
         <v/>
@@ -7959,22 +7959,22 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>纯黑色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B129" t="str">
         <v>妹妹</v>
       </c>
       <c r="C129" t="str">
-        <v>assets/1785842779532-5u1j0igrw1s.jpg</v>
+        <v>assets/1785838787730-s5f333sc3u.jpg</v>
       </c>
       <c r="D129" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E129" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F129" t="str">
-        <v/>
+        <v>湖北恩施</v>
       </c>
       <c r="G129" t="str">
         <v/>
@@ -8021,19 +8021,19 @@
         <v>银虎斑</v>
       </c>
       <c r="B130" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C130" t="str">
-        <v>assets/1785842817046-6keqv4rw4yf.jpg</v>
+        <v>assets/1785842296661-6qw3zs3as8h.jpg</v>
       </c>
       <c r="D130" t="str">
         <v>是</v>
       </c>
       <c r="E130" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F130" t="str">
-        <v>韩国</v>
+        <v>湖北恩施</v>
       </c>
       <c r="G130" t="str">
         <v/>
@@ -8077,22 +8077,22 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>浅色银虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B131" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C131" t="str">
-        <v>assets/1785842950972-a88lbrskpc.jpg</v>
+        <v>assets/1785842429109-porc98rel5.jpg</v>
       </c>
       <c r="D131" t="str">
         <v>是</v>
       </c>
       <c r="E131" t="str">
-        <v>2026-06-05</v>
+        <v>2025-11-05</v>
       </c>
       <c r="F131" t="str">
-        <v>河北邢台</v>
+        <v>韩国</v>
       </c>
       <c r="G131" t="str">
         <v/>
@@ -8136,22 +8136,22 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B132" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C132" t="str">
-        <v>assets/1785843011477-n3l1wi6ech.jpg</v>
+        <v>assets/1785842594141-fcglbzjp509.jpg</v>
       </c>
       <c r="D132" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E132" t="str">
-        <v>2026-06-05</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F132" t="str">
-        <v>四川自贡</v>
+        <v/>
       </c>
       <c r="G132" t="str">
         <v/>
@@ -8195,22 +8195,22 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B133" t="str">
         <v>弟弟</v>
       </c>
       <c r="C133" t="str">
-        <v>assets/1785843237517-ga449iqess5.jpg</v>
+        <v>assets/1785842639100-82k775dhwiv.jpg</v>
       </c>
       <c r="D133" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E133" t="str">
-        <v>2026-03-05</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F133" t="str">
-        <v/>
+        <v>四川自贡</v>
       </c>
       <c r="G133" t="str">
         <v/>
@@ -8254,19 +8254,19 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>棕虎斑补丁</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B134" t="str">
         <v>妹妹</v>
       </c>
       <c r="C134" t="str">
-        <v>assets/1785842523893-7nwnnhwi4ns.jpg</v>
+        <v>assets/1785842684502-mnhr0r96eee.jpg</v>
       </c>
       <c r="D134" t="str">
         <v>否</v>
       </c>
       <c r="E134" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F134" t="str">
         <v/>
@@ -8313,19 +8313,19 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>蓝虎斑</v>
+        <v>纯黑色</v>
       </c>
       <c r="B135" t="str">
         <v>妹妹</v>
       </c>
       <c r="C135" t="str">
-        <v>assets/1785843497557-st27fk8drqi.jpg</v>
+        <v>assets/1785842779532-5u1j0igrw1s.jpg</v>
       </c>
       <c r="D135" t="str">
         <v>否</v>
       </c>
       <c r="E135" t="str">
-        <v>2026-04-05</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F135" t="str">
         <v/>
@@ -8378,16 +8378,16 @@
         <v>妹妹</v>
       </c>
       <c r="C136" t="str">
-        <v>assets/1785843621923-ylhakbtw13i.jpg</v>
+        <v>assets/1785842817046-6keqv4rw4yf.jpg</v>
       </c>
       <c r="D136" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E136" t="str">
         <v>2026-03-05</v>
       </c>
       <c r="F136" t="str">
-        <v/>
+        <v>韩国</v>
       </c>
       <c r="G136" t="str">
         <v/>
@@ -8431,22 +8431,22 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>银虎斑</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B137" t="str">
         <v>妹妹</v>
       </c>
       <c r="C137" t="str">
-        <v>assets/1785843663884-sfxvpmiet7.jpg</v>
+        <v>assets/1785842950972-a88lbrskpc.jpg</v>
       </c>
       <c r="D137" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E137" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F137" t="str">
-        <v/>
+        <v>河北邢台</v>
       </c>
       <c r="G137" t="str">
         <v/>
@@ -8490,52 +8490,52 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B138" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C138" t="str">
-        <v>assets/1785852601940-o236xtv7yx.jpeg</v>
+        <v>assets/1785843011477-n3l1wi6ech.jpg</v>
       </c>
       <c r="D138" t="str">
         <v>是</v>
       </c>
       <c r="E138" t="str">
-        <v>2026-02-20</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F138" t="str">
-        <v>荷兰</v>
+        <v>四川自贡</v>
       </c>
       <c r="G138" t="str">
-        <v>阿泽</v>
+        <v/>
       </c>
       <c r="H138" t="str">
-        <v>小辫子</v>
+        <v/>
       </c>
       <c r="I138" t="str">
-        <v>驺驺</v>
+        <v/>
       </c>
       <c r="J138" t="str">
-        <v>2026-07-02</v>
+        <v/>
       </c>
       <c r="K138" t="str">
         <v/>
       </c>
       <c r="L138" t="str">
-        <v>2026-07-02</v>
+        <v/>
       </c>
       <c r="M138" t="str">
-        <v>2026-08-03</v>
+        <v/>
       </c>
       <c r="N138" t="str">
-        <v>2026-11-04</v>
+        <v/>
       </c>
       <c r="O138" t="str">
-        <v>2026-08-03 · 血清检测,2026-07-02 · 打疫苗 · assets/diary/zouzou-depart.jpg,2026-07-30 · 6.2斤 · 五个月10天了 · assets/feedback/zouzou-1.jpg</v>
+        <v/>
       </c>
       <c r="P138" t="str">
-        <v>已付定金</v>
+        <v/>
       </c>
       <c r="Q138" t="str">
         <v/>
@@ -8544,27 +8544,27 @@
         <v/>
       </c>
       <c r="S138" t="str">
-        <v>否</v>
+        <v/>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>红虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B139" t="str">
         <v>弟弟</v>
       </c>
       <c r="C139" t="str">
-        <v>assets/1785853950207-cedor66ou2q.jpeg</v>
+        <v>assets/1785843237517-ga449iqess5.jpg</v>
       </c>
       <c r="D139" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E139" t="str">
-        <v/>
+        <v>2026-03-05</v>
       </c>
       <c r="F139" t="str">
-        <v>广东广州</v>
+        <v/>
       </c>
       <c r="G139" t="str">
         <v/>
@@ -8608,22 +8608,22 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>红虎斑</v>
+        <v>棕虎斑补丁</v>
       </c>
       <c r="B140" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C140" t="str">
-        <v>assets/1785854129383-c8qkvl537x.jpeg</v>
+        <v>assets/1785842523893-7nwnnhwi4ns.jpg</v>
       </c>
       <c r="D140" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E140" t="str">
-        <v/>
+        <v>2026-03-05</v>
       </c>
       <c r="F140" t="str">
-        <v>广东广州</v>
+        <v/>
       </c>
       <c r="G140" t="str">
         <v/>
@@ -8667,22 +8667,22 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B141" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C141" t="str">
-        <v>assets/1785854166720-48r17hry9cd.jpeg</v>
+        <v>assets/1785843497557-st27fk8drqi.jpg</v>
       </c>
       <c r="D141" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E141" t="str">
-        <v/>
+        <v>2026-04-05</v>
       </c>
       <c r="F141" t="str">
-        <v>山西朔州</v>
+        <v/>
       </c>
       <c r="G141" t="str">
         <v/>
@@ -8732,16 +8732,16 @@
         <v>妹妹</v>
       </c>
       <c r="C142" t="str">
-        <v>assets/1785854224521-2cpg6xipfn6.jpeg</v>
+        <v>assets/1785843621923-ylhakbtw13i.jpg</v>
       </c>
       <c r="D142" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E142" t="str">
-        <v/>
+        <v>2026-03-05</v>
       </c>
       <c r="F142" t="str">
-        <v>浙江宁波</v>
+        <v/>
       </c>
       <c r="G142" t="str">
         <v/>
@@ -8788,19 +8788,19 @@
         <v>银虎斑</v>
       </c>
       <c r="B143" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C143" t="str">
-        <v>assets/1785854260793-steez4s972l.jpeg</v>
+        <v>assets/1785843663884-sfxvpmiet7.jpg</v>
       </c>
       <c r="D143" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E143" t="str">
-        <v/>
+        <v>2026-03-05</v>
       </c>
       <c r="F143" t="str">
-        <v>陕西西安</v>
+        <v/>
       </c>
       <c r="G143" t="str">
         <v/>
@@ -8844,52 +8844,52 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B144" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C144" t="str">
-        <v>assets/1785854319988-cohio08aod5.jpeg</v>
+        <v>assets/1785852601940-o236xtv7yx.jpeg</v>
       </c>
       <c r="D144" t="str">
         <v>是</v>
       </c>
       <c r="E144" t="str">
-        <v/>
+        <v>2026-02-20</v>
       </c>
       <c r="F144" t="str">
-        <v>黑龙江漠河</v>
+        <v>荷兰</v>
       </c>
       <c r="G144" t="str">
-        <v/>
+        <v>阿泽</v>
       </c>
       <c r="H144" t="str">
-        <v/>
+        <v>小辫子</v>
       </c>
       <c r="I144" t="str">
-        <v/>
+        <v>驺驺</v>
       </c>
       <c r="J144" t="str">
-        <v/>
+        <v>2026-07-02</v>
       </c>
       <c r="K144" t="str">
         <v/>
       </c>
       <c r="L144" t="str">
-        <v/>
+        <v>2026-07-02</v>
       </c>
       <c r="M144" t="str">
-        <v/>
+        <v>2026-08-03</v>
       </c>
       <c r="N144" t="str">
-        <v/>
+        <v>2026-11-04</v>
       </c>
       <c r="O144" t="str">
-        <v/>
+        <v>2026-08-03 · 血清检测,2026-07-02 · 打疫苗 · assets/diary/zouzou-depart.jpg,2026-07-30 · 6.2斤 · 五个月10天了 · assets/feedback/zouzou-1.jpg</v>
       </c>
       <c r="P144" t="str">
-        <v/>
+        <v>已付定金</v>
       </c>
       <c r="Q144" t="str">
         <v/>
@@ -8898,18 +8898,18 @@
         <v/>
       </c>
       <c r="S144" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>棕虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B145" t="str">
         <v>弟弟</v>
       </c>
       <c r="C145" t="str">
-        <v>assets/1785854520974-96b8b1ekqd9.jpeg</v>
+        <v>assets/1785853950207-cedor66ou2q.jpeg</v>
       </c>
       <c r="D145" t="str">
         <v>是</v>
@@ -8918,7 +8918,7 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>日本</v>
+        <v>广东广州</v>
       </c>
       <c r="G145" t="str">
         <v/>
@@ -8962,13 +8962,13 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B146" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C146" t="str">
-        <v>assets/1785854664100-haqoiu1h7hj.jpeg</v>
+        <v>assets/1785854129383-c8qkvl537x.jpeg</v>
       </c>
       <c r="D146" t="str">
         <v>是</v>
@@ -8977,7 +8977,7 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>浙江杭州</v>
+        <v>广东广州</v>
       </c>
       <c r="G146" t="str">
         <v/>
@@ -9024,10 +9024,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B147" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C147" t="str">
-        <v>assets/1785854690732-orrs40sx9rs.jpeg</v>
+        <v>assets/1785854166720-48r17hry9cd.jpeg</v>
       </c>
       <c r="D147" t="str">
         <v>是</v>
@@ -9036,7 +9036,7 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>贵州安顺</v>
+        <v>山西朔州</v>
       </c>
       <c r="G147" t="str">
         <v/>
@@ -9086,7 +9086,7 @@
         <v>妹妹</v>
       </c>
       <c r="C148" t="str">
-        <v>assets/1785854734122-wcpmib4m7.jpeg</v>
+        <v>assets/1785854224521-2cpg6xipfn6.jpeg</v>
       </c>
       <c r="D148" t="str">
         <v>是</v>
@@ -9095,7 +9095,7 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>山东青岛</v>
+        <v>浙江宁波</v>
       </c>
       <c r="G148" t="str">
         <v/>
@@ -9145,7 +9145,7 @@
         <v>弟弟</v>
       </c>
       <c r="C149" t="str">
-        <v>assets/1785854758707-1kxdkfvs6jc.jpeg</v>
+        <v>assets/1785854260793-steez4s972l.jpeg</v>
       </c>
       <c r="D149" t="str">
         <v>是</v>
@@ -9154,7 +9154,7 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>黑龙江漠河</v>
+        <v>陕西西安</v>
       </c>
       <c r="G149" t="str">
         <v/>
@@ -9198,13 +9198,13 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>纯蓝色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B150" t="str">
         <v>弟弟</v>
       </c>
       <c r="C150" t="str">
-        <v>assets/1785854784780-3g0u60pdo93.jpeg</v>
+        <v>assets/1785854319988-cohio08aod5.jpeg</v>
       </c>
       <c r="D150" t="str">
         <v>是</v>
@@ -9213,7 +9213,7 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>河南鹤壁</v>
+        <v>黑龙江漠河</v>
       </c>
       <c r="G150" t="str">
         <v/>
@@ -9257,13 +9257,13 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B151" t="str">
         <v>弟弟</v>
       </c>
       <c r="C151" t="str">
-        <v>assets/1785854813179-8oyxr0h2bbu.jpeg</v>
+        <v>assets/1785854520974-96b8b1ekqd9.jpeg</v>
       </c>
       <c r="D151" t="str">
         <v>是</v>
@@ -9272,7 +9272,7 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>陕西西安</v>
+        <v>日本</v>
       </c>
       <c r="G151" t="str">
         <v/>
@@ -9316,13 +9316,13 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B152" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C152" t="str">
-        <v>assets/1785854838933-uq6amircyzd.jpeg</v>
+        <v>assets/1785854664100-haqoiu1h7hj.jpeg</v>
       </c>
       <c r="D152" t="str">
         <v>是</v>
@@ -9331,7 +9331,7 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>四川成都</v>
+        <v>浙江杭州</v>
       </c>
       <c r="G152" t="str">
         <v/>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>烟灰色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B153" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C153" t="str">
-        <v>assets/1785854869973-za3p6wikqpo.jpeg</v>
+        <v>assets/1785854690732-orrs40sx9rs.jpeg</v>
       </c>
       <c r="D153" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E153" t="str">
-        <v>2026-05-18</v>
+        <v/>
       </c>
       <c r="F153" t="str">
-        <v/>
+        <v>贵州安顺</v>
       </c>
       <c r="G153" t="str">
         <v/>
@@ -9437,10 +9437,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B154" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C154" t="str">
-        <v>assets/1785854997023-mawkallt2a.jpeg</v>
+        <v>assets/1785854734122-wcpmib4m7.jpeg</v>
       </c>
       <c r="D154" t="str">
         <v>是</v>
@@ -9449,7 +9449,7 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>新加坡</v>
+        <v>山东青岛</v>
       </c>
       <c r="G154" t="str">
         <v/>
@@ -9493,13 +9493,13 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>凯米尔色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B155" t="str">
         <v>弟弟</v>
       </c>
       <c r="C155" t="str">
-        <v>assets/1785855043327-wdc5pxwm34k.jpeg</v>
+        <v>assets/1785854758707-1kxdkfvs6jc.jpeg</v>
       </c>
       <c r="D155" t="str">
         <v>是</v>
@@ -9508,7 +9508,7 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>上海浦东</v>
+        <v>黑龙江漠河</v>
       </c>
       <c r="G155" t="str">
         <v/>
@@ -9552,22 +9552,22 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>棕虎斑</v>
+        <v>纯蓝色</v>
       </c>
       <c r="B156" t="str">
         <v>弟弟</v>
       </c>
       <c r="C156" t="str">
-        <v>assets/1785912551260-jplefm937nk.jpeg, assets/videos/02.mp4</v>
+        <v>assets/1785854784780-3g0u60pdo93.jpeg</v>
       </c>
       <c r="D156" t="str">
         <v>是</v>
       </c>
       <c r="E156" t="str">
-        <v>2026-06-06</v>
+        <v/>
       </c>
       <c r="F156" t="str">
-        <v>浙江温州</v>
+        <v>河南鹤壁</v>
       </c>
       <c r="G156" t="str">
         <v/>
@@ -9611,66 +9611,420 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
+        <v>银虎斑</v>
+      </c>
+      <c r="B157" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C157" t="str">
+        <v>assets/1785854813179-8oyxr0h2bbu.jpeg</v>
+      </c>
+      <c r="D157" t="str">
+        <v>是</v>
+      </c>
+      <c r="E157" t="str">
+        <v/>
+      </c>
+      <c r="F157" t="str">
+        <v>陕西西安</v>
+      </c>
+      <c r="G157" t="str">
+        <v/>
+      </c>
+      <c r="H157" t="str">
+        <v/>
+      </c>
+      <c r="I157" t="str">
+        <v/>
+      </c>
+      <c r="J157" t="str">
+        <v/>
+      </c>
+      <c r="K157" t="str">
+        <v/>
+      </c>
+      <c r="L157" t="str">
+        <v/>
+      </c>
+      <c r="M157" t="str">
+        <v/>
+      </c>
+      <c r="N157" t="str">
+        <v/>
+      </c>
+      <c r="O157" t="str">
+        <v/>
+      </c>
+      <c r="P157" t="str">
+        <v/>
+      </c>
+      <c r="Q157" t="str">
+        <v/>
+      </c>
+      <c r="R157" t="str">
+        <v/>
+      </c>
+      <c r="S157" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
         <v>棕虎斑</v>
       </c>
-      <c r="B157" t="str">
+      <c r="B158" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C158" t="str">
+        <v>assets/1785854838933-uq6amircyzd.jpeg</v>
+      </c>
+      <c r="D158" t="str">
+        <v>是</v>
+      </c>
+      <c r="E158" t="str">
+        <v/>
+      </c>
+      <c r="F158" t="str">
+        <v>四川成都</v>
+      </c>
+      <c r="G158" t="str">
+        <v/>
+      </c>
+      <c r="H158" t="str">
+        <v/>
+      </c>
+      <c r="I158" t="str">
+        <v/>
+      </c>
+      <c r="J158" t="str">
+        <v/>
+      </c>
+      <c r="K158" t="str">
+        <v/>
+      </c>
+      <c r="L158" t="str">
+        <v/>
+      </c>
+      <c r="M158" t="str">
+        <v/>
+      </c>
+      <c r="N158" t="str">
+        <v/>
+      </c>
+      <c r="O158" t="str">
+        <v/>
+      </c>
+      <c r="P158" t="str">
+        <v/>
+      </c>
+      <c r="Q158" t="str">
+        <v/>
+      </c>
+      <c r="R158" t="str">
+        <v/>
+      </c>
+      <c r="S158" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>烟灰色</v>
+      </c>
+      <c r="B159" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C159" t="str">
+        <v>assets/1785854869973-za3p6wikqpo.jpeg</v>
+      </c>
+      <c r="D159" t="str">
+        <v>否</v>
+      </c>
+      <c r="E159" t="str">
+        <v>2026-05-18</v>
+      </c>
+      <c r="F159" t="str">
+        <v/>
+      </c>
+      <c r="G159" t="str">
+        <v/>
+      </c>
+      <c r="H159" t="str">
+        <v/>
+      </c>
+      <c r="I159" t="str">
+        <v/>
+      </c>
+      <c r="J159" t="str">
+        <v/>
+      </c>
+      <c r="K159" t="str">
+        <v/>
+      </c>
+      <c r="L159" t="str">
+        <v/>
+      </c>
+      <c r="M159" t="str">
+        <v/>
+      </c>
+      <c r="N159" t="str">
+        <v/>
+      </c>
+      <c r="O159" t="str">
+        <v/>
+      </c>
+      <c r="P159" t="str">
+        <v/>
+      </c>
+      <c r="Q159" t="str">
+        <v/>
+      </c>
+      <c r="R159" t="str">
+        <v/>
+      </c>
+      <c r="S159" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>银虎斑</v>
+      </c>
+      <c r="B160" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C160" t="str">
+        <v>assets/1785854997023-mawkallt2a.jpeg</v>
+      </c>
+      <c r="D160" t="str">
+        <v>是</v>
+      </c>
+      <c r="E160" t="str">
+        <v/>
+      </c>
+      <c r="F160" t="str">
+        <v>新加坡</v>
+      </c>
+      <c r="G160" t="str">
+        <v/>
+      </c>
+      <c r="H160" t="str">
+        <v/>
+      </c>
+      <c r="I160" t="str">
+        <v/>
+      </c>
+      <c r="J160" t="str">
+        <v/>
+      </c>
+      <c r="K160" t="str">
+        <v/>
+      </c>
+      <c r="L160" t="str">
+        <v/>
+      </c>
+      <c r="M160" t="str">
+        <v/>
+      </c>
+      <c r="N160" t="str">
+        <v/>
+      </c>
+      <c r="O160" t="str">
+        <v/>
+      </c>
+      <c r="P160" t="str">
+        <v/>
+      </c>
+      <c r="Q160" t="str">
+        <v/>
+      </c>
+      <c r="R160" t="str">
+        <v/>
+      </c>
+      <c r="S160" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>凯米尔色</v>
+      </c>
+      <c r="B161" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C161" t="str">
+        <v>assets/1785855043327-wdc5pxwm34k.jpeg</v>
+      </c>
+      <c r="D161" t="str">
+        <v>是</v>
+      </c>
+      <c r="E161" t="str">
+        <v/>
+      </c>
+      <c r="F161" t="str">
+        <v>上海浦东</v>
+      </c>
+      <c r="G161" t="str">
+        <v/>
+      </c>
+      <c r="H161" t="str">
+        <v/>
+      </c>
+      <c r="I161" t="str">
+        <v/>
+      </c>
+      <c r="J161" t="str">
+        <v/>
+      </c>
+      <c r="K161" t="str">
+        <v/>
+      </c>
+      <c r="L161" t="str">
+        <v/>
+      </c>
+      <c r="M161" t="str">
+        <v/>
+      </c>
+      <c r="N161" t="str">
+        <v/>
+      </c>
+      <c r="O161" t="str">
+        <v/>
+      </c>
+      <c r="P161" t="str">
+        <v/>
+      </c>
+      <c r="Q161" t="str">
+        <v/>
+      </c>
+      <c r="R161" t="str">
+        <v/>
+      </c>
+      <c r="S161" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>棕虎斑</v>
+      </c>
+      <c r="B162" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C162" t="str">
+        <v>assets/1785912551260-jplefm937nk.jpeg, assets/videos/02.mp4</v>
+      </c>
+      <c r="D162" t="str">
+        <v>是</v>
+      </c>
+      <c r="E162" t="str">
+        <v>2026-06-06</v>
+      </c>
+      <c r="F162" t="str">
+        <v>浙江温州</v>
+      </c>
+      <c r="G162" t="str">
+        <v/>
+      </c>
+      <c r="H162" t="str">
+        <v/>
+      </c>
+      <c r="I162" t="str">
+        <v/>
+      </c>
+      <c r="J162" t="str">
+        <v/>
+      </c>
+      <c r="K162" t="str">
+        <v/>
+      </c>
+      <c r="L162" t="str">
+        <v/>
+      </c>
+      <c r="M162" t="str">
+        <v/>
+      </c>
+      <c r="N162" t="str">
+        <v/>
+      </c>
+      <c r="O162" t="str">
+        <v/>
+      </c>
+      <c r="P162" t="str">
+        <v/>
+      </c>
+      <c r="Q162" t="str">
+        <v/>
+      </c>
+      <c r="R162" t="str">
+        <v/>
+      </c>
+      <c r="S162" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>棕虎斑</v>
+      </c>
+      <c r="B163" t="str">
         <v>妹妹</v>
       </c>
-      <c r="C157" t="str">
+      <c r="C163" t="str">
         <v>assets/1785912694000-m20f5kvvrr.jpeg</v>
       </c>
-      <c r="D157" t="str">
-        <v>否</v>
-      </c>
-      <c r="E157" t="str">
+      <c r="D163" t="str">
+        <v>否</v>
+      </c>
+      <c r="E163" t="str">
         <v>2026-06-06</v>
       </c>
-      <c r="F157" t="str">
-        <v/>
-      </c>
-      <c r="G157" t="str">
-        <v/>
-      </c>
-      <c r="H157" t="str">
-        <v/>
-      </c>
-      <c r="I157" t="str">
-        <v/>
-      </c>
-      <c r="J157" t="str">
-        <v/>
-      </c>
-      <c r="K157" t="str">
-        <v/>
-      </c>
-      <c r="L157" t="str">
-        <v/>
-      </c>
-      <c r="M157" t="str">
-        <v/>
-      </c>
-      <c r="N157" t="str">
-        <v/>
-      </c>
-      <c r="O157" t="str">
-        <v/>
-      </c>
-      <c r="P157" t="str">
-        <v/>
-      </c>
-      <c r="Q157" t="str">
-        <v/>
-      </c>
-      <c r="R157" t="str">
-        <v/>
-      </c>
-      <c r="S157" t="str">
+      <c r="F163" t="str">
+        <v/>
+      </c>
+      <c r="G163" t="str">
+        <v/>
+      </c>
+      <c r="H163" t="str">
+        <v/>
+      </c>
+      <c r="I163" t="str">
+        <v/>
+      </c>
+      <c r="J163" t="str">
+        <v/>
+      </c>
+      <c r="K163" t="str">
+        <v/>
+      </c>
+      <c r="L163" t="str">
+        <v/>
+      </c>
+      <c r="M163" t="str">
+        <v/>
+      </c>
+      <c r="N163" t="str">
+        <v/>
+      </c>
+      <c r="O163" t="str">
+        <v/>
+      </c>
+      <c r="P163" t="str">
+        <v/>
+      </c>
+      <c r="Q163" t="str">
+        <v/>
+      </c>
+      <c r="R163" t="str">
+        <v/>
+      </c>
+      <c r="S163" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S157"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S163"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -6611,13 +6611,13 @@
         <v>assets/1787304479674-w0trechn4p.jpg</v>
       </c>
       <c r="D106" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E106" t="str">
         <v>2026-06-06</v>
       </c>
       <c r="F106" t="str">
-        <v/>
+        <v>北京</v>
       </c>
       <c r="G106" t="str">
         <v/>

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -7083,13 +7083,13 @@
         <v>assets/1787282819855-7vhx3m0v40.jpg</v>
       </c>
       <c r="D114" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E114" t="str">
         <v>2026-06-06</v>
       </c>
       <c r="F114" t="str">
-        <v/>
+        <v>北京</v>
       </c>
       <c r="G114" t="str">
         <v/>

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -9738,13 +9738,13 @@
         <v>assets/1785854869973-za3p6wikqpo.jpeg</v>
       </c>
       <c r="D159" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E159" t="str">
         <v>2026-05-18</v>
       </c>
       <c r="F159" t="str">
-        <v/>
+        <v>四川成都</v>
       </c>
       <c r="G159" t="str">
         <v/>

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S163"/>
+  <dimension ref="A1:S168"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -466,19 +466,19 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>银虎斑</v>
+        <v>凯米尔</v>
       </c>
       <c r="B2" t="str">
         <v>弟弟</v>
       </c>
       <c r="C2" t="str">
-        <v>assets/1787837910484-r7urrsuib0.jpg</v>
+        <v>assets/1788014088852-oqkg79cki9.jpg</v>
       </c>
       <c r="D2" t="str">
         <v>否</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-05-18</v>
+        <v>2026-06-26</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -525,19 +525,19 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>纯黑色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B3" t="str">
         <v>妹妹</v>
       </c>
       <c r="C3" t="str">
-        <v>assets/1787837846581-6q9nxgad35.jpg</v>
+        <v>assets/1788014050978-9a2sguuo1u.jpg</v>
       </c>
       <c r="D3" t="str">
         <v>否</v>
       </c>
       <c r="E3" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -584,19 +584,19 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>凯米尔</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B4" t="str">
         <v>弟弟</v>
       </c>
       <c r="C4" t="str">
-        <v>assets/1787837779354-hkuyvt39iz.jpg</v>
+        <v>assets/1788013924404-gmlh0hfjae.jpg</v>
       </c>
       <c r="D4" t="str">
         <v>否</v>
       </c>
       <c r="E4" t="str">
-        <v>2026-06-26</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -643,19 +643,19 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>烟灰色</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B5" t="str">
         <v>弟弟</v>
       </c>
       <c r="C5" t="str">
-        <v>assets/1787837690599-rd37ukkrgw.jpg</v>
+        <v>assets/1788013889955-wpykaycfde.jpg</v>
       </c>
       <c r="D5" t="str">
         <v>否</v>
       </c>
       <c r="E5" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-26</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -702,22 +702,22 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B6" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C6" t="str">
-        <v>assets/1787837648423-9riberz3tq.jpg</v>
+        <v>assets/1788013810551-b90h1mwfiq.jpg</v>
       </c>
       <c r="D6" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E6" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-26</v>
       </c>
       <c r="F6" t="str">
-        <v>北京</v>
+        <v/>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -761,19 +761,19 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B7" t="str">
         <v>弟弟</v>
       </c>
       <c r="C7" t="str">
-        <v>assets/1787837594903-wtnbv2fz89.jpg</v>
+        <v>assets/1787837910484-r7urrsuib0.jpg</v>
       </c>
       <c r="D7" t="str">
         <v>否</v>
       </c>
       <c r="E7" t="str">
-        <v>2026-06-10</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F7" t="str">
         <v/>
@@ -820,13 +820,13 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>棕虎斑</v>
+        <v>纯黑色</v>
       </c>
       <c r="B8" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C8" t="str">
-        <v>assets/1787479268842-7en9nzy302.jpg</v>
+        <v>assets/1787837846581-6q9nxgad35.jpg</v>
       </c>
       <c r="D8" t="str">
         <v>否</v>
@@ -847,7 +847,7 @@
         <v/>
       </c>
       <c r="J8" t="str">
-        <v>2026-06-10</v>
+        <v/>
       </c>
       <c r="K8" t="str">
         <v/>
@@ -879,19 +879,19 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>纯黑色</v>
+        <v>凯米尔</v>
       </c>
       <c r="B9" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C9" t="str">
-        <v>assets/1787479242639-32zuh5lham.jpg</v>
+        <v>assets/1787837779354-hkuyvt39iz.jpg</v>
       </c>
       <c r="D9" t="str">
         <v>否</v>
       </c>
       <c r="E9" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-26</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -938,22 +938,22 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>棕虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B10" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C10" t="str">
-        <v>assets/1787466121255-21jto2cugv.jpg</v>
+        <v>assets/1787837690599-rd37ukkrgw.jpg</v>
       </c>
       <c r="D10" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E10" t="str">
-        <v/>
+        <v>2026-06-06</v>
       </c>
       <c r="F10" t="str">
-        <v>四川广安</v>
+        <v/>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -997,22 +997,22 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B11" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C11" t="str">
-        <v>assets/1787388322060-uj8bkwqgnv.jpg</v>
+        <v>assets/1787837648423-9riberz3tq.jpg</v>
       </c>
       <c r="D11" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E11" t="str">
         <v>2026-06-06</v>
       </c>
       <c r="F11" t="str">
-        <v/>
+        <v>北京</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -1059,16 +1059,16 @@
         <v>棕虎斑</v>
       </c>
       <c r="B12" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C12" t="str">
-        <v>assets/1787388277490-e6u506cx0r.jpg</v>
+        <v>assets/1787837594903-wtnbv2fz89.jpg</v>
       </c>
       <c r="D12" t="str">
         <v>否</v>
       </c>
       <c r="E12" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-10</v>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -1115,22 +1115,22 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B13" t="str">
         <v>弟弟</v>
       </c>
       <c r="C13" t="str">
-        <v>assets/1787328436957-x30od0gw28.jpg</v>
+        <v>assets/1787479268842-7en9nzy302.jpg</v>
       </c>
       <c r="D13" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E13" t="str">
-        <v/>
+        <v>2026-06-10</v>
       </c>
       <c r="F13" t="str">
-        <v>江苏苏州</v>
+        <v/>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -1142,7 +1142,7 @@
         <v/>
       </c>
       <c r="J13" t="str">
-        <v/>
+        <v>2026-06-10</v>
       </c>
       <c r="K13" t="str">
         <v/>
@@ -1174,22 +1174,22 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>蓝虎斑</v>
+        <v>纯黑色</v>
       </c>
       <c r="B14" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C14" t="str">
-        <v>assets/1787328420967-viv9v8nbjn.jpg</v>
+        <v>assets/1787479242639-32zuh5lham.jpg</v>
       </c>
       <c r="D14" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E14" t="str">
-        <v/>
+        <v>2026-06-10</v>
       </c>
       <c r="F14" t="str">
-        <v>辽宁东港</v>
+        <v/>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -1236,10 +1236,10 @@
         <v>棕虎斑</v>
       </c>
       <c r="B15" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C15" t="str">
-        <v>assets/1787327967245-m62ohievcl.jpg</v>
+        <v>assets/1787466121255-21jto2cugv.jpg</v>
       </c>
       <c r="D15" t="str">
         <v>是</v>
@@ -1248,7 +1248,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>福建福州</v>
+        <v>四川广安</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -1292,22 +1292,22 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>蓝虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B16" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C16" t="str">
-        <v>assets/1787327853521-js8ljh3ulj.jpg</v>
+        <v>assets/1787388322060-uj8bkwqgnv.jpg</v>
       </c>
       <c r="D16" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E16" t="str">
-        <v/>
+        <v>2026-06-06</v>
       </c>
       <c r="F16" t="str">
-        <v>上海</v>
+        <v/>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1351,22 +1351,22 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>纯蓝色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B17" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C17" t="str">
-        <v>assets/1787327793837-znk2knoo6p.jpg</v>
+        <v>assets/1787388277490-e6u506cx0r.jpg</v>
       </c>
       <c r="D17" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E17" t="str">
-        <v/>
+        <v>2026-06-06</v>
       </c>
       <c r="F17" t="str">
-        <v>河南鹤壁</v>
+        <v/>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1416,7 +1416,7 @@
         <v>弟弟</v>
       </c>
       <c r="C18" t="str">
-        <v>assets/1787327752832-kkpmp21os3.jpg</v>
+        <v>assets/1787328436957-x30od0gw28.jpg</v>
       </c>
       <c r="D18" t="str">
         <v>是</v>
@@ -1425,7 +1425,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>陕西西安</v>
+        <v>江苏苏州</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1469,13 +1469,13 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B19" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C19" t="str">
-        <v>assets/1787327605711-4o2f6v6ybp.jpg</v>
+        <v>assets/1787328420967-viv9v8nbjn.jpg</v>
       </c>
       <c r="D19" t="str">
         <v>是</v>
@@ -1484,7 +1484,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>陕西西安</v>
+        <v>辽宁东港</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1528,13 +1528,13 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B20" t="str">
         <v>弟弟</v>
       </c>
       <c r="C20" t="str">
-        <v>assets/1787327573762-h23cux94p2.jpg</v>
+        <v>assets/1787327967245-m62ohievcl.jpg</v>
       </c>
       <c r="D20" t="str">
         <v>是</v>
@@ -1543,7 +1543,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>北京</v>
+        <v>福建福州</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1587,13 +1587,13 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B21" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C21" t="str">
-        <v>assets/1787327496557-9daggljg4g.jpg</v>
+        <v>assets/1787327853521-js8ljh3ulj.jpg</v>
       </c>
       <c r="D21" t="str">
         <v>是</v>
@@ -1602,7 +1602,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>黑龙江哈尔滨</v>
+        <v>上海</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1646,13 +1646,13 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>烟灰色</v>
+        <v>纯蓝色</v>
       </c>
       <c r="B22" t="str">
         <v>弟弟</v>
       </c>
       <c r="C22" t="str">
-        <v>assets/1787327456560-p4yhq4qvrv.jpg</v>
+        <v>assets/1787327793837-znk2knoo6p.jpg</v>
       </c>
       <c r="D22" t="str">
         <v>是</v>
@@ -1661,7 +1661,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>甘肃嘉峪关</v>
+        <v>河南鹤壁</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1705,13 +1705,13 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>蓝虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B23" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C23" t="str">
-        <v>assets/1787327421713-zg7np4yzkc.jpg</v>
+        <v>assets/1787327752832-kkpmp21os3.jpg</v>
       </c>
       <c r="D23" t="str">
         <v>是</v>
@@ -1720,7 +1720,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>安徽合肥</v>
+        <v>陕西西安</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1767,10 +1767,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B24" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C24" t="str">
-        <v>assets/1787327337811-u5u2pdew3.jpg</v>
+        <v>assets/1787327605711-4o2f6v6ybp.jpg</v>
       </c>
       <c r="D24" t="str">
         <v>是</v>
@@ -1779,7 +1779,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>安徽合肥</v>
+        <v>陕西西安</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1823,13 +1823,13 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B25" t="str">
         <v>弟弟</v>
       </c>
       <c r="C25" t="str">
-        <v>assets/1787327309143-6c1dan1sev.jpg</v>
+        <v>assets/1787327573762-h23cux94p2.jpg</v>
       </c>
       <c r="D25" t="str">
         <v>是</v>
@@ -1838,7 +1838,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>四川成都</v>
+        <v>北京</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1885,10 +1885,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B26" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C26" t="str">
-        <v>assets/1787327277453-w89ujg69fm.jpg</v>
+        <v>assets/1787327496557-9daggljg4g.jpg</v>
       </c>
       <c r="D26" t="str">
         <v>是</v>
@@ -1897,7 +1897,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>四川成都</v>
+        <v>黑龙江哈尔滨</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1941,13 +1941,13 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>蓝银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B27" t="str">
         <v>弟弟</v>
       </c>
       <c r="C27" t="str">
-        <v>assets/1787327232159-lkrcl588a5.jpg</v>
+        <v>assets/1787327456560-p4yhq4qvrv.jpg</v>
       </c>
       <c r="D27" t="str">
         <v>是</v>
@@ -1956,7 +1956,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>四川成都</v>
+        <v>甘肃嘉峪关</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -2000,13 +2000,13 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>玳瑁色</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B28" t="str">
         <v>妹妹</v>
       </c>
       <c r="C28" t="str">
-        <v>assets/1787327182347-3az0z7sys2.jpg</v>
+        <v>assets/1787327421713-zg7np4yzkc.jpg</v>
       </c>
       <c r="D28" t="str">
         <v>是</v>
@@ -2015,7 +2015,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>四川内江</v>
+        <v>安徽合肥</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -2059,13 +2059,13 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>棕虎补丁</v>
+        <v>银虎斑</v>
       </c>
       <c r="B29" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C29" t="str">
-        <v>assets/1787327143756-4xtgfy5ozu.jpg</v>
+        <v>assets/1787327337811-u5u2pdew3.jpg</v>
       </c>
       <c r="D29" t="str">
         <v>是</v>
@@ -2074,7 +2074,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>贵州贵阳</v>
+        <v>安徽合肥</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -2118,13 +2118,13 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>黑烟色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B30" t="str">
         <v>弟弟</v>
       </c>
       <c r="C30" t="str">
-        <v>assets/1787327101790-tqjlseog5y.jpg</v>
+        <v>assets/1787327309143-6c1dan1sev.jpg</v>
       </c>
       <c r="D30" t="str">
         <v>是</v>
@@ -2133,7 +2133,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>浙江杭州</v>
+        <v>四川成都</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -2177,13 +2177,13 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>烟灰色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B31" t="str">
         <v>弟弟</v>
       </c>
       <c r="C31" t="str">
-        <v>assets/1787327019632-l1780lu2hj.jpg</v>
+        <v>assets/1787327277453-w89ujg69fm.jpg</v>
       </c>
       <c r="D31" t="str">
         <v>是</v>
@@ -2192,7 +2192,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>山东威海</v>
+        <v>四川成都</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -2236,13 +2236,13 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>棕虎补丁</v>
+        <v>蓝银虎斑</v>
       </c>
       <c r="B32" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C32" t="str">
-        <v>assets/1787326905275-plz3fpgo97.jpg</v>
+        <v>assets/1787327232159-lkrcl588a5.jpg</v>
       </c>
       <c r="D32" t="str">
         <v>是</v>
@@ -2251,7 +2251,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>浙江杭州</v>
+        <v>四川成都</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -2295,13 +2295,13 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>蓝虎斑</v>
+        <v>玳瑁色</v>
       </c>
       <c r="B33" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C33" t="str">
-        <v>assets/1787326874462-z9rzs7wg17.jpg</v>
+        <v>assets/1787327182347-3az0z7sys2.jpg</v>
       </c>
       <c r="D33" t="str">
         <v>是</v>
@@ -2310,7 +2310,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>四川成都</v>
+        <v>四川内江</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -2354,13 +2354,13 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>凯米尔色</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B34" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C34" t="str">
-        <v>assets/1787326843271-0uhv7b9p89.jpg</v>
+        <v>assets/1787327143756-4xtgfy5ozu.jpg</v>
       </c>
       <c r="D34" t="str">
         <v>是</v>
@@ -2369,7 +2369,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>四川成都</v>
+        <v>贵州贵阳</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -2413,13 +2413,13 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>凯米尔</v>
+        <v>黑烟色</v>
       </c>
       <c r="B35" t="str">
         <v>弟弟</v>
       </c>
       <c r="C35" t="str">
-        <v>assets/1787326814713-p5oavnlulg.jpg</v>
+        <v>assets/1787327101790-tqjlseog5y.jpg</v>
       </c>
       <c r="D35" t="str">
         <v>是</v>
@@ -2428,7 +2428,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>四川成都</v>
+        <v>浙江杭州</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -2472,13 +2472,13 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>棕虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B36" t="str">
         <v>弟弟</v>
       </c>
       <c r="C36" t="str">
-        <v>assets/1787326773577-13q5out2d0.jpg</v>
+        <v>assets/1787327019632-l1780lu2hj.jpg</v>
       </c>
       <c r="D36" t="str">
         <v>是</v>
@@ -2487,7 +2487,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>四川宜宾</v>
+        <v>山东威海</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -2531,13 +2531,13 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>金棕虎斑</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B37" t="str">
         <v>妹妹</v>
       </c>
       <c r="C37" t="str">
-        <v>assets/1787326548993-89s929m2hg.jpg</v>
+        <v>assets/1787326905275-plz3fpgo97.jpg</v>
       </c>
       <c r="D37" t="str">
         <v>是</v>
@@ -2546,7 +2546,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>上海</v>
+        <v>浙江杭州</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -2590,13 +2590,13 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>凯米尔色</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B38" t="str">
         <v>弟弟</v>
       </c>
       <c r="C38" t="str">
-        <v>assets/1787326449218-09s9ucram4.jpg</v>
+        <v>assets/1787326874462-z9rzs7wg17.jpg</v>
       </c>
       <c r="D38" t="str">
         <v>是</v>
@@ -2605,7 +2605,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>德国</v>
+        <v>四川成都</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -2649,13 +2649,13 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>棕虎补丁</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B39" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C39" t="str">
-        <v>assets/1787326277374-8ti107m5ki.jpg</v>
+        <v>assets/1787326843271-0uhv7b9p89.jpg</v>
       </c>
       <c r="D39" t="str">
         <v>是</v>
@@ -2664,7 +2664,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>广东深圳</v>
+        <v>四川成都</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -2708,13 +2708,13 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>烟灰色</v>
+        <v>凯米尔</v>
       </c>
       <c r="B40" t="str">
         <v>弟弟</v>
       </c>
       <c r="C40" t="str">
-        <v>assets/1787326236952-2pmwche4t3.jpg</v>
+        <v>assets/1787326814713-p5oavnlulg.jpg</v>
       </c>
       <c r="D40" t="str">
         <v>是</v>
@@ -2723,7 +2723,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>福建泉州</v>
+        <v>四川成都</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -2767,13 +2767,13 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B41" t="str">
         <v>弟弟</v>
       </c>
       <c r="C41" t="str">
-        <v>assets/1787326184557-90v6clkwen.jpg</v>
+        <v>assets/1787326773577-13q5out2d0.jpg</v>
       </c>
       <c r="D41" t="str">
         <v>是</v>
@@ -2782,7 +2782,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>福建福州</v>
+        <v>四川宜宾</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -2826,13 +2826,13 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>棕虎斑</v>
+        <v>金棕虎斑</v>
       </c>
       <c r="B42" t="str">
         <v>妹妹</v>
       </c>
       <c r="C42" t="str">
-        <v>assets/1787326046155-4tk23nq4dj.jpg</v>
+        <v>assets/1787326548993-89s929m2hg.jpg</v>
       </c>
       <c r="D42" t="str">
         <v>是</v>
@@ -2841,7 +2841,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>广西贵港</v>
+        <v>上海</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -2891,7 +2891,7 @@
         <v>弟弟</v>
       </c>
       <c r="C43" t="str">
-        <v>assets/1787325862706-wq18k3ej56.jpg</v>
+        <v>assets/1787326449218-09s9ucram4.jpg</v>
       </c>
       <c r="D43" t="str">
         <v>是</v>
@@ -2900,7 +2900,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>江苏苏州</v>
+        <v>德国</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2944,13 +2944,13 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>凯米尔色</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B44" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C44" t="str">
-        <v>assets/1787325743258-a7oac7hzlo.jpg</v>
+        <v>assets/1787326277374-8ti107m5ki.jpg</v>
       </c>
       <c r="D44" t="str">
         <v>是</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>江苏苏州</v>
+        <v>广东深圳</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -3003,13 +3003,13 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B45" t="str">
         <v>弟弟</v>
       </c>
       <c r="C45" t="str">
-        <v>assets/1787325706797-kgk81ghccy.jpg</v>
+        <v>assets/1787326236952-2pmwche4t3.jpg</v>
       </c>
       <c r="D45" t="str">
         <v>是</v>
@@ -3018,7 +3018,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>北京</v>
+        <v>福建泉州</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -3062,13 +3062,13 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>蓝虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B46" t="str">
         <v>弟弟</v>
       </c>
       <c r="C46" t="str">
-        <v>assets/1787325603704-lahzgrm7fa.jpg,assets/1787325690106-wgu3spujit.jpg</v>
+        <v>assets/1787326184557-90v6clkwen.jpg</v>
       </c>
       <c r="D46" t="str">
         <v>是</v>
@@ -3077,7 +3077,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>上海</v>
+        <v>福建福州</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -3127,7 +3127,7 @@
         <v>妹妹</v>
       </c>
       <c r="C47" t="str">
-        <v>assets/1787325554341-608thexrne.jpg</v>
+        <v>assets/1787326046155-4tk23nq4dj.jpg</v>
       </c>
       <c r="D47" t="str">
         <v>是</v>
@@ -3136,7 +3136,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>江苏苏州</v>
+        <v>广西贵港</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -3180,13 +3180,13 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>浅色银虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B48" t="str">
         <v>弟弟</v>
       </c>
       <c r="C48" t="str">
-        <v>assets/1787325480828-q90pskoiw3.jpg</v>
+        <v>assets/1787325862706-wq18k3ej56.jpg</v>
       </c>
       <c r="D48" t="str">
         <v>是</v>
@@ -3195,7 +3195,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>四川成都</v>
+        <v>江苏苏州</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -3239,13 +3239,13 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>浅色银虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B49" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C49" t="str">
-        <v>assets/1787325448999-a2pg8176fu.jpg</v>
+        <v>assets/1787325743258-a7oac7hzlo.jpg</v>
       </c>
       <c r="D49" t="str">
         <v>是</v>
@@ -3254,7 +3254,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>中国台湾</v>
+        <v>江苏苏州</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -3298,13 +3298,13 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B50" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C50" t="str">
-        <v>assets/1787325357634-k55zlfhmqj.jpg</v>
+        <v>assets/1787325706797-kgk81ghccy.jpg</v>
       </c>
       <c r="D50" t="str">
         <v>是</v>
@@ -3313,7 +3313,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>浙江杭州</v>
+        <v>北京</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -3357,13 +3357,13 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>烟灰色</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B51" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C51" t="str">
-        <v>assets/1787325237876-t19isaq5gu.jpg</v>
+        <v>assets/1787325603704-lahzgrm7fa.jpg,assets/1787325690106-wgu3spujit.jpg</v>
       </c>
       <c r="D51" t="str">
         <v>是</v>
@@ -3372,7 +3372,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>辽宁沈阳</v>
+        <v>上海</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -3416,13 +3416,13 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>金棕虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B52" t="str">
         <v>妹妹</v>
       </c>
       <c r="C52" t="str">
-        <v>assets/1787325199931-e7wms9qtya.jpg</v>
+        <v>assets/1787325554341-608thexrne.jpg</v>
       </c>
       <c r="D52" t="str">
         <v>是</v>
@@ -3431,7 +3431,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>四川成都</v>
+        <v>江苏苏州</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -3475,13 +3475,13 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>蓝虎斑</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B53" t="str">
         <v>弟弟</v>
       </c>
       <c r="C53" t="str">
-        <v>assets/1787325172354-4sa8uzaey2.jpg</v>
+        <v>assets/1787325480828-q90pskoiw3.jpg</v>
       </c>
       <c r="D53" t="str">
         <v>是</v>
@@ -3490,7 +3490,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>中国香港</v>
+        <v>四川成都</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -3534,13 +3534,13 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>烟灰色</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B54" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C54" t="str">
-        <v>assets/1787325109283-y7mvkk6qg4.jpg</v>
+        <v>assets/1787325448999-a2pg8176fu.jpg</v>
       </c>
       <c r="D54" t="str">
         <v>是</v>
@@ -3549,7 +3549,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>中国澳门</v>
+        <v>中国台湾</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -3593,13 +3593,13 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B55" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C55" t="str">
-        <v>assets/1787325033629-y3ygps3zaj.jpg</v>
+        <v>assets/1787325357634-k55zlfhmqj.jpg</v>
       </c>
       <c r="D55" t="str">
         <v>是</v>
@@ -3608,7 +3608,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>山东青岛</v>
+        <v>浙江杭州</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -3655,10 +3655,10 @@
         <v>烟灰色</v>
       </c>
       <c r="B56" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C56" t="str">
-        <v>assets/1787324954998-w5m5jox439.jpg</v>
+        <v>assets/1787325237876-t19isaq5gu.jpg</v>
       </c>
       <c r="D56" t="str">
         <v>是</v>
@@ -3667,7 +3667,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>海南海口</v>
+        <v>辽宁沈阳</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -3711,13 +3711,13 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>棕虎斑</v>
+        <v>金棕虎斑</v>
       </c>
       <c r="B57" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C57" t="str">
-        <v>assets/1787324905909-zrz8o79kdf.jpg</v>
+        <v>assets/1787325199931-e7wms9qtya.jpg</v>
       </c>
       <c r="D57" t="str">
         <v>是</v>
@@ -3726,7 +3726,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>内蒙古</v>
+        <v>四川成都</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -3770,13 +3770,13 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>烟灰色</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B58" t="str">
         <v>弟弟</v>
       </c>
       <c r="C58" t="str">
-        <v>assets/1787324880505-gbh0sn7b6j.jpg</v>
+        <v>assets/1787325172354-4sa8uzaey2.jpg</v>
       </c>
       <c r="D58" t="str">
         <v>是</v>
@@ -3835,7 +3835,7 @@
         <v>弟弟</v>
       </c>
       <c r="C59" t="str">
-        <v>assets/1787324806613-31yyz14tsf.jpg</v>
+        <v>assets/1787325109283-y7mvkk6qg4.jpg</v>
       </c>
       <c r="D59" t="str">
         <v>是</v>
@@ -3844,7 +3844,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>四川成都</v>
+        <v>中国澳门</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -3888,13 +3888,13 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>红虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B60" t="str">
         <v>弟弟</v>
       </c>
       <c r="C60" t="str">
-        <v>assets/1787324789658-uz6ephkdsh.jpg</v>
+        <v>assets/1787325033629-y3ygps3zaj.jpg</v>
       </c>
       <c r="D60" t="str">
         <v>是</v>
@@ -3903,7 +3903,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>湖北武汉</v>
+        <v>山东青岛</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -3953,7 +3953,7 @@
         <v>弟弟</v>
       </c>
       <c r="C61" t="str">
-        <v>assets/1787324522658-smn44crast.jpg</v>
+        <v>assets/1787324954998-w5m5jox439.jpg</v>
       </c>
       <c r="D61" t="str">
         <v>是</v>
@@ -3962,7 +3962,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>湖北武汉</v>
+        <v>海南海口</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -4012,7 +4012,7 @@
         <v>弟弟</v>
       </c>
       <c r="C62" t="str">
-        <v>assets/1787324365608-6xtrjp7euz.jpg</v>
+        <v>assets/1787324905909-zrz8o79kdf.jpg</v>
       </c>
       <c r="D62" t="str">
         <v>是</v>
@@ -4021,7 +4021,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>新疆</v>
+        <v>内蒙古</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -4065,13 +4065,13 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>浅凯米尔</v>
+        <v>烟灰色</v>
       </c>
       <c r="B63" t="str">
         <v>弟弟</v>
       </c>
       <c r="C63" t="str">
-        <v>assets/1787324331029-d74lcuycf6.jpg</v>
+        <v>assets/1787324880505-gbh0sn7b6j.jpg</v>
       </c>
       <c r="D63" t="str">
         <v>是</v>
@@ -4080,7 +4080,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>四川成都</v>
+        <v>中国香港</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -4124,13 +4124,13 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>红虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B64" t="str">
         <v>弟弟</v>
       </c>
       <c r="C64" t="str">
-        <v>assets/1787324297469-ans1lse2l5.jpg</v>
+        <v>assets/1787324806613-31yyz14tsf.jpg</v>
       </c>
       <c r="D64" t="str">
         <v>是</v>
@@ -4139,7 +4139,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>四川乐山</v>
+        <v>四川成都</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -4189,7 +4189,7 @@
         <v>弟弟</v>
       </c>
       <c r="C65" t="str">
-        <v>assets/1787324256827-7w383z4bg1.jpg</v>
+        <v>assets/1787324789658-uz6ephkdsh.jpg</v>
       </c>
       <c r="D65" t="str">
         <v>是</v>
@@ -4198,7 +4198,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>中国台湾</v>
+        <v>湖北武汉</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -4242,13 +4242,13 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B66" t="str">
         <v>弟弟</v>
       </c>
       <c r="C66" t="str">
-        <v>assets/1787324228262-y3vwn6i4zk.jpg</v>
+        <v>assets/1787324522658-smn44crast.jpg</v>
       </c>
       <c r="D66" t="str">
         <v>是</v>
@@ -4257,7 +4257,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>四川成都</v>
+        <v>湖北武汉</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -4301,13 +4301,13 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>凯米尔色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B67" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C67" t="str">
-        <v>assets/1787324201418-9tk4ik75mo.jpg</v>
+        <v>assets/1787324365608-6xtrjp7euz.jpg</v>
       </c>
       <c r="D67" t="str">
         <v>是</v>
@@ -4316,7 +4316,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>江苏南京</v>
+        <v>新疆</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -4360,13 +4360,13 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>棕虎斑</v>
+        <v>浅凯米尔</v>
       </c>
       <c r="B68" t="str">
         <v>弟弟</v>
       </c>
       <c r="C68" t="str">
-        <v>assets/1787324092513-jpa2rmkci2.jpg</v>
+        <v>assets/1787324331029-d74lcuycf6.jpg</v>
       </c>
       <c r="D68" t="str">
         <v>是</v>
@@ -4375,7 +4375,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>江苏南京</v>
+        <v>四川成都</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -4419,13 +4419,13 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B69" t="str">
         <v>弟弟</v>
       </c>
       <c r="C69" t="str">
-        <v>assets/1787323318612-soge38hpsf.jpg</v>
+        <v>assets/1787324297469-ans1lse2l5.jpg</v>
       </c>
       <c r="D69" t="str">
         <v>是</v>
@@ -4434,7 +4434,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>上海</v>
+        <v>四川乐山</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -4478,13 +4478,13 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>棕虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B70" t="str">
         <v>弟弟</v>
       </c>
       <c r="C70" t="str">
-        <v>assets/1787323235892-7yq8ioq01e.jpg</v>
+        <v>assets/1787324256827-7w383z4bg1.jpg</v>
       </c>
       <c r="D70" t="str">
         <v>是</v>
@@ -4493,7 +4493,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>四川成都</v>
+        <v>中国台湾</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -4540,10 +4540,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B71" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C71" t="str">
-        <v>assets/1787322988096-6e2f54q7vo.jpg</v>
+        <v>assets/1787324228262-y3vwn6i4zk.jpg</v>
       </c>
       <c r="D71" t="str">
         <v>是</v>
@@ -4552,7 +4552,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>浙江宁波</v>
+        <v>四川成都</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -4596,13 +4596,13 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>银虎斑补丁</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B72" t="str">
         <v>妹妹</v>
       </c>
       <c r="C72" t="str">
-        <v>assets/1787322938518-85ev8bs2k5.jpg</v>
+        <v>assets/1787324201418-9tk4ik75mo.jpg</v>
       </c>
       <c r="D72" t="str">
         <v>是</v>
@@ -4611,7 +4611,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>马来西亚</v>
+        <v>江苏南京</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -4655,13 +4655,13 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B73" t="str">
         <v>弟弟</v>
       </c>
       <c r="C73" t="str">
-        <v>assets/1787322881183-tzu9xtw2sg.jpg</v>
+        <v>assets/1787324092513-jpa2rmkci2.jpg</v>
       </c>
       <c r="D73" t="str">
         <v>是</v>
@@ -4670,7 +4670,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>陕西西安</v>
+        <v>江苏南京</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -4714,13 +4714,13 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>纯黑色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B74" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C74" t="str">
-        <v>assets/1787322840098-nhy4jjyx7k.jpg</v>
+        <v>assets/1787323318612-soge38hpsf.jpg</v>
       </c>
       <c r="D74" t="str">
         <v>是</v>
@@ -4729,7 +4729,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>广西南宁</v>
+        <v>上海</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -4779,7 +4779,7 @@
         <v>弟弟</v>
       </c>
       <c r="C75" t="str">
-        <v>assets/1787322760950-gn3qgego4s.jpg</v>
+        <v>assets/1787323235892-7yq8ioq01e.jpg</v>
       </c>
       <c r="D75" t="str">
         <v>是</v>
@@ -4788,7 +4788,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>广西南宁</v>
+        <v>四川成都</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -4832,13 +4832,13 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>红虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B76" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C76" t="str">
-        <v>assets/1787322605982-04n50xegt2.jpg</v>
+        <v>assets/1787322988096-6e2f54q7vo.jpg</v>
       </c>
       <c r="D76" t="str">
         <v>是</v>
@@ -4847,7 +4847,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>上海</v>
+        <v>浙江宁波</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -4891,13 +4891,13 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>蓝虎斑</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B77" t="str">
         <v>妹妹</v>
       </c>
       <c r="C77" t="str">
-        <v>assets/1787322490045-kog3ru43dy.jpg</v>
+        <v>assets/1787322938518-85ev8bs2k5.jpg</v>
       </c>
       <c r="D77" t="str">
         <v>是</v>
@@ -4906,7 +4906,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>上海</v>
+        <v>马来西亚</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -4950,13 +4950,13 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>红虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B78" t="str">
         <v>弟弟</v>
       </c>
       <c r="C78" t="str">
-        <v>assets/1787322419996-0m33yx89nm.jpg</v>
+        <v>assets/1787322881183-tzu9xtw2sg.jpg</v>
       </c>
       <c r="D78" t="str">
         <v>是</v>
@@ -4965,7 +4965,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>广东广州</v>
+        <v>陕西西安</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -5009,13 +5009,13 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>浅色银虎斑</v>
+        <v>纯黑色</v>
       </c>
       <c r="B79" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C79" t="str">
-        <v>assets/1787322377730-vj5csj2mll.jpg</v>
+        <v>assets/1787322840098-nhy4jjyx7k.jpg</v>
       </c>
       <c r="D79" t="str">
         <v>是</v>
@@ -5024,7 +5024,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>柬埔寨</v>
+        <v>广西南宁</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -5068,13 +5068,13 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B80" t="str">
         <v>弟弟</v>
       </c>
       <c r="C80" t="str">
-        <v>assets/1787322269611-53yaj5ideu.jpg</v>
+        <v>assets/1787322760950-gn3qgego4s.jpg</v>
       </c>
       <c r="D80" t="str">
         <v>是</v>
@@ -5083,7 +5083,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>山东枣庄</v>
+        <v>广西南宁</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -5127,13 +5127,13 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B81" t="str">
         <v>弟弟</v>
       </c>
       <c r="C81" t="str">
-        <v>assets/1787321989528-7d6liuhuk9.jpg</v>
+        <v>assets/1787322605982-04n50xegt2.jpg</v>
       </c>
       <c r="D81" t="str">
         <v>是</v>
@@ -5142,7 +5142,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>陕西西安</v>
+        <v>上海</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -5186,13 +5186,13 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B82" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C82" t="str">
-        <v>assets/1787321941642-xlrc1no2ua.jpg</v>
+        <v>assets/1787322490045-kog3ru43dy.jpg</v>
       </c>
       <c r="D82" t="str">
         <v>是</v>
@@ -5201,7 +5201,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>山东东营</v>
+        <v>上海</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -5245,13 +5245,13 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>凯米尔色</v>
+        <v>红虎斑</v>
       </c>
       <c r="B83" t="str">
         <v>弟弟</v>
       </c>
       <c r="C83" t="str">
-        <v>assets/1787321903535-6orj7qcgzn.jpg</v>
+        <v>assets/1787322419996-0m33yx89nm.jpg</v>
       </c>
       <c r="D83" t="str">
         <v>是</v>
@@ -5260,7 +5260,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>中国台湾</v>
+        <v>广东广州</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -5304,13 +5304,13 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>烟灰色</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B84" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C84" t="str">
-        <v>assets/1787321858985-v4qej7cq7g.jpg</v>
+        <v>assets/1787322377730-vj5csj2mll.jpg</v>
       </c>
       <c r="D84" t="str">
         <v>是</v>
@@ -5319,7 +5319,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>中国台湾</v>
+        <v>柬埔寨</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -5363,13 +5363,13 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B85" t="str">
         <v>弟弟</v>
       </c>
       <c r="C85" t="str">
-        <v>assets/1787321834306-efgnyhujon.jpg</v>
+        <v>assets/1787322269611-53yaj5ideu.jpg</v>
       </c>
       <c r="D85" t="str">
         <v>是</v>
@@ -5378,7 +5378,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>北京</v>
+        <v>山东枣庄</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -5428,7 +5428,7 @@
         <v>弟弟</v>
       </c>
       <c r="C86" t="str">
-        <v>assets/1787321439916-uttgpbkogb.jpg</v>
+        <v>assets/1787321989528-7d6liuhuk9.jpg</v>
       </c>
       <c r="D86" t="str">
         <v>是</v>
@@ -5437,7 +5437,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>安徽合肥</v>
+        <v>陕西西安</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -5487,7 +5487,7 @@
         <v>弟弟</v>
       </c>
       <c r="C87" t="str">
-        <v>assets/1787321419210-51hhgurygq.jpg</v>
+        <v>assets/1787321941642-xlrc1no2ua.jpg</v>
       </c>
       <c r="D87" t="str">
         <v>是</v>
@@ -5496,7 +5496,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>上海</v>
+        <v>山东东营</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -5543,10 +5543,10 @@
         <v>凯米尔色</v>
       </c>
       <c r="B88" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C88" t="str">
-        <v>assets/1787321363369-bzjn51j5il.jpg</v>
+        <v>assets/1787321903535-6orj7qcgzn.jpg</v>
       </c>
       <c r="D88" t="str">
         <v>是</v>
@@ -5599,13 +5599,13 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>棕虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B89" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C89" t="str">
-        <v>assets/1787321332559-87p6spuch3.jpg</v>
+        <v>assets/1787321858985-v4qej7cq7g.jpg</v>
       </c>
       <c r="D89" t="str">
         <v>是</v>
@@ -5658,13 +5658,13 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B90" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C90" t="str">
-        <v>assets/1787321232531-59lnzv8y98.jpg</v>
+        <v>assets/1787321834306-efgnyhujon.jpg</v>
       </c>
       <c r="D90" t="str">
         <v>是</v>
@@ -5720,10 +5720,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B91" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C91" t="str">
-        <v>assets/1787319975814-g1pfa56vfp.jpg</v>
+        <v>assets/1787321439916-uttgpbkogb.jpg</v>
       </c>
       <c r="D91" t="str">
         <v>是</v>
@@ -5732,7 +5732,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>浙江宁波</v>
+        <v>安徽合肥</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -5779,10 +5779,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B92" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C92" t="str">
-        <v>assets/1787319800704-v3qeu062ak.jpg</v>
+        <v>assets/1787321419210-51hhgurygq.jpg</v>
       </c>
       <c r="D92" t="str">
         <v>是</v>
@@ -5791,7 +5791,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>河北唐山</v>
+        <v>上海</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -5835,13 +5835,13 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>银虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B93" t="str">
         <v>妹妹</v>
       </c>
       <c r="C93" t="str">
-        <v>assets/1787319745369-zn66xr3bvb.jpg</v>
+        <v>assets/1787321363369-bzjn51j5il.jpg</v>
       </c>
       <c r="D93" t="str">
         <v>是</v>
@@ -5850,7 +5850,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>河北石家庄</v>
+        <v>中国台湾</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -5894,13 +5894,13 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>棕虎补丁</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B94" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C94" t="str">
-        <v>assets/1787319547969-zqlq35fxxt.jpg</v>
+        <v>assets/1787321332559-87p6spuch3.jpg</v>
       </c>
       <c r="D94" t="str">
         <v>是</v>
@@ -5909,7 +5909,7 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>韩国</v>
+        <v>中国台湾</v>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -5953,13 +5953,13 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>蓝银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B95" t="str">
         <v>妹妹</v>
       </c>
       <c r="C95" t="str">
-        <v>assets/1787319501376-xscwljnu1j.jpg</v>
+        <v>assets/1787321232531-59lnzv8y98.jpg</v>
       </c>
       <c r="D95" t="str">
         <v>是</v>
@@ -5968,7 +5968,7 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>美国</v>
+        <v>北京</v>
       </c>
       <c r="G95" t="str">
         <v/>
@@ -6012,13 +6012,13 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B96" t="str">
         <v>妹妹</v>
       </c>
       <c r="C96" t="str">
-        <v>assets/1787319443529-4a0zqikufx.jpg</v>
+        <v>assets/1787319975814-g1pfa56vfp.jpg</v>
       </c>
       <c r="D96" t="str">
         <v>是</v>
@@ -6027,7 +6027,7 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>中国台湾</v>
+        <v>浙江宁波</v>
       </c>
       <c r="G96" t="str">
         <v/>
@@ -6071,13 +6071,13 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>蓝虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B97" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C97" t="str">
-        <v>assets/1787319356194-lr2d5680i9.jpg</v>
+        <v>assets/1787319800704-v3qeu062ak.jpg</v>
       </c>
       <c r="D97" t="str">
         <v>是</v>
@@ -6086,7 +6086,7 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>中国台湾</v>
+        <v>河北唐山</v>
       </c>
       <c r="G97" t="str">
         <v/>
@@ -6130,13 +6130,13 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B98" t="str">
         <v>妹妹</v>
       </c>
       <c r="C98" t="str">
-        <v>assets/1787319208828-aizqo4blcv.jpg</v>
+        <v>assets/1787319745369-zn66xr3bvb.jpg</v>
       </c>
       <c r="D98" t="str">
         <v>是</v>
@@ -6145,7 +6145,7 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>山东淄博</v>
+        <v>河北石家庄</v>
       </c>
       <c r="G98" t="str">
         <v/>
@@ -6189,13 +6189,13 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>银虎斑</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B99" t="str">
         <v>妹妹</v>
       </c>
       <c r="C99" t="str">
-        <v>assets/1787319162970-cc2v8ovnni.jpg</v>
+        <v>assets/1787319547969-zqlq35fxxt.jpg</v>
       </c>
       <c r="D99" t="str">
         <v>是</v>
@@ -6248,13 +6248,13 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>棕虎补丁</v>
+        <v>蓝银虎斑</v>
       </c>
       <c r="B100" t="str">
         <v>妹妹</v>
       </c>
       <c r="C100" t="str">
-        <v>assets/1787319098214-8pwa9yx2wc.jpg</v>
+        <v>assets/1787319501376-xscwljnu1j.jpg</v>
       </c>
       <c r="D100" t="str">
         <v>是</v>
@@ -6263,7 +6263,7 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>四川成都</v>
+        <v>美国</v>
       </c>
       <c r="G100" t="str">
         <v/>
@@ -6307,13 +6307,13 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B101" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C101" t="str">
-        <v>assets/1787318867999-3gxdddp72x.jpg</v>
+        <v>assets/1787319443529-4a0zqikufx.jpg</v>
       </c>
       <c r="D101" t="str">
         <v>是</v>
@@ -6322,7 +6322,7 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>广东广州</v>
+        <v>中国台湾</v>
       </c>
       <c r="G101" t="str">
         <v/>
@@ -6366,13 +6366,13 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B102" t="str">
         <v>弟弟</v>
       </c>
       <c r="C102" t="str">
-        <v>assets/1787318609722-0ojb3aikwi.jpg</v>
+        <v>assets/1787319356194-lr2d5680i9.jpg</v>
       </c>
       <c r="D102" t="str">
         <v>是</v>
@@ -6381,7 +6381,7 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>黑龙江鹤岗</v>
+        <v>中国台湾</v>
       </c>
       <c r="G102" t="str">
         <v/>
@@ -6425,13 +6425,13 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B103" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C103" t="str">
-        <v>assets/1787318530612-779fbkfcoi.jpg</v>
+        <v>assets/1787319208828-aizqo4blcv.jpg</v>
       </c>
       <c r="D103" t="str">
         <v>是</v>
@@ -6440,7 +6440,7 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>天津</v>
+        <v>山东淄博</v>
       </c>
       <c r="G103" t="str">
         <v/>
@@ -6487,10 +6487,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B104" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C104" t="str">
-        <v>assets/1787318365475-sj87wtsai3.jpg</v>
+        <v>assets/1787319162970-cc2v8ovnni.jpg</v>
       </c>
       <c r="D104" t="str">
         <v>是</v>
@@ -6499,7 +6499,7 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>山西朔州</v>
+        <v>韩国</v>
       </c>
       <c r="G104" t="str">
         <v/>
@@ -6529,7 +6529,7 @@
         <v/>
       </c>
       <c r="P104" t="str">
-        <v>已接猫</v>
+        <v/>
       </c>
       <c r="Q104" t="str">
         <v/>
@@ -6543,13 +6543,13 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>银虎斑</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B105" t="str">
         <v>妹妹</v>
       </c>
       <c r="C105" t="str">
-        <v>assets/1787318326155-ia4noopjhq.jpg</v>
+        <v>assets/1787319098214-8pwa9yx2wc.jpg</v>
       </c>
       <c r="D105" t="str">
         <v>是</v>
@@ -6558,7 +6558,7 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>贵州</v>
+        <v>四川成都</v>
       </c>
       <c r="G105" t="str">
         <v/>
@@ -6602,22 +6602,22 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B106" t="str">
         <v>弟弟</v>
       </c>
       <c r="C106" t="str">
-        <v>assets/1787304479674-w0trechn4p.jpg</v>
+        <v>assets/1787318867999-3gxdddp72x.jpg</v>
       </c>
       <c r="D106" t="str">
         <v>是</v>
       </c>
       <c r="E106" t="str">
-        <v>2026-06-06</v>
+        <v/>
       </c>
       <c r="F106" t="str">
-        <v>北京</v>
+        <v>广东广州</v>
       </c>
       <c r="G106" t="str">
         <v/>
@@ -6656,27 +6656,27 @@
         <v/>
       </c>
       <c r="S106" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>纯黑色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B107" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C107" t="str">
-        <v>assets/1787283819124-4v7d1w01la.jpg</v>
+        <v>assets/1787318609722-0ojb3aikwi.jpg</v>
       </c>
       <c r="D107" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E107" t="str">
-        <v>2026-02-20</v>
+        <v/>
       </c>
       <c r="F107" t="str">
-        <v/>
+        <v>黑龙江鹤岗</v>
       </c>
       <c r="G107" t="str">
         <v/>
@@ -6715,27 +6715,27 @@
         <v/>
       </c>
       <c r="S107" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>阴影色NS12</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B108" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C108" t="str">
-        <v>assets/1787283212708-jdnyi6ecci.jpg</v>
+        <v>assets/1787318530612-779fbkfcoi.jpg</v>
       </c>
       <c r="D108" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E108" t="str">
-        <v>2026-05-28</v>
+        <v/>
       </c>
       <c r="F108" t="str">
-        <v/>
+        <v>天津</v>
       </c>
       <c r="G108" t="str">
         <v/>
@@ -6774,27 +6774,27 @@
         <v/>
       </c>
       <c r="S108" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>阴影色NS11</v>
+        <v>银虎斑</v>
       </c>
       <c r="B109" t="str">
         <v>弟弟</v>
       </c>
       <c r="C109" t="str">
-        <v>assets/1787283153501-s2tjg9spwu.jpg</v>
+        <v>assets/1787318365475-sj87wtsai3.jpg</v>
       </c>
       <c r="D109" t="str">
         <v>是</v>
       </c>
       <c r="E109" t="str">
-        <v>2026-06-15</v>
+        <v/>
       </c>
       <c r="F109" t="str">
-        <v>重庆</v>
+        <v>山西朔州</v>
       </c>
       <c r="G109" t="str">
         <v/>
@@ -6824,7 +6824,7 @@
         <v/>
       </c>
       <c r="P109" t="str">
-        <v/>
+        <v>已接猫</v>
       </c>
       <c r="Q109" t="str">
         <v/>
@@ -6833,27 +6833,27 @@
         <v/>
       </c>
       <c r="S109" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>浅烟灰色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B110" t="str">
         <v>妹妹</v>
       </c>
       <c r="C110" t="str">
-        <v>assets/1787283092677-i4d8tyrjtf.jpg</v>
+        <v>assets/1787318326155-ia4noopjhq.jpg</v>
       </c>
       <c r="D110" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E110" t="str">
-        <v>2026-03-21</v>
+        <v/>
       </c>
       <c r="F110" t="str">
-        <v/>
+        <v>贵州</v>
       </c>
       <c r="G110" t="str">
         <v/>
@@ -6892,7 +6892,7 @@
         <v/>
       </c>
       <c r="S110" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="111">
@@ -6900,19 +6900,19 @@
         <v>棕虎斑</v>
       </c>
       <c r="B111" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C111" t="str">
-        <v>assets/1787283031104-bpyq9wy2tl.jpg</v>
+        <v>assets/1787304479674-w0trechn4p.jpg</v>
       </c>
       <c r="D111" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E111" t="str">
         <v>2026-06-06</v>
       </c>
       <c r="F111" t="str">
-        <v/>
+        <v>北京</v>
       </c>
       <c r="G111" t="str">
         <v/>
@@ -6956,19 +6956,19 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>棕虎斑</v>
+        <v>纯黑色</v>
       </c>
       <c r="B112" t="str">
         <v>妹妹</v>
       </c>
       <c r="C112" t="str">
-        <v>assets/1787282991501-2fjfws0rqw.jpg</v>
+        <v>assets/1787283819124-4v7d1w01la.jpg</v>
       </c>
       <c r="D112" t="str">
         <v>否</v>
       </c>
       <c r="E112" t="str">
-        <v>2026-06-06</v>
+        <v>2026-02-20</v>
       </c>
       <c r="F112" t="str">
         <v/>
@@ -7015,19 +7015,19 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>棕虎斑</v>
+        <v>阴影色NS12</v>
       </c>
       <c r="B113" t="str">
         <v>妹妹</v>
       </c>
       <c r="C113" t="str">
-        <v>assets/1787282942262-syr48fym6c.jpg</v>
+        <v>assets/1787283212708-jdnyi6ecci.jpg</v>
       </c>
       <c r="D113" t="str">
         <v>否</v>
       </c>
       <c r="E113" t="str">
-        <v>2026-06-15</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F113" t="str">
         <v/>
@@ -7074,22 +7074,22 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>棕虎斑</v>
+        <v>阴影色NS11</v>
       </c>
       <c r="B114" t="str">
         <v>弟弟</v>
       </c>
       <c r="C114" t="str">
-        <v>assets/1787282819855-7vhx3m0v40.jpg</v>
+        <v>assets/1787283153501-s2tjg9spwu.jpg</v>
       </c>
       <c r="D114" t="str">
         <v>是</v>
       </c>
       <c r="E114" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F114" t="str">
-        <v>北京</v>
+        <v>重庆</v>
       </c>
       <c r="G114" t="str">
         <v/>
@@ -7133,19 +7133,19 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>棕虎斑</v>
+        <v>浅烟灰色</v>
       </c>
       <c r="B115" t="str">
         <v>妹妹</v>
       </c>
       <c r="C115" t="str">
-        <v>assets/1787282703381-2uakw592b4.jpg</v>
+        <v>assets/1787283092677-i4d8tyrjtf.jpg</v>
       </c>
       <c r="D115" t="str">
         <v>否</v>
       </c>
       <c r="E115" t="str">
-        <v>2026-06-06</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F115" t="str">
         <v/>
@@ -7192,13 +7192,13 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B116" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C116" t="str">
-        <v>assets/1787282649397-9hc31ncrpc.jpg</v>
+        <v>assets/1787283031104-bpyq9wy2tl.jpg</v>
       </c>
       <c r="D116" t="str">
         <v>否</v>
@@ -7251,13 +7251,13 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B117" t="str">
         <v>妹妹</v>
       </c>
       <c r="C117" t="str">
-        <v>assets/1787282617957-svcoyyznpg.jpg</v>
+        <v>assets/1787282991501-2fjfws0rqw.jpg</v>
       </c>
       <c r="D117" t="str">
         <v>否</v>
@@ -7310,19 +7310,19 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B118" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C118" t="str">
-        <v>assets/1787282419632-78nixqjzua.jpg</v>
+        <v>assets/1787282942262-syr48fym6c.jpg</v>
       </c>
       <c r="D118" t="str">
         <v>否</v>
       </c>
       <c r="E118" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F118" t="str">
         <v/>
@@ -7369,22 +7369,22 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>纯黑色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B119" t="str">
         <v>弟弟</v>
       </c>
       <c r="C119" t="str">
-        <v>assets/1787282349942-2cfuyn7xlc.jpg</v>
+        <v>assets/1787282819855-7vhx3m0v40.jpg</v>
       </c>
       <c r="D119" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E119" t="str">
-        <v>2026-03-21</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F119" t="str">
-        <v/>
+        <v>北京</v>
       </c>
       <c r="G119" t="str">
         <v/>
@@ -7428,19 +7428,19 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B120" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C120" t="str">
-        <v>assets/1787282064159-6b4z8c5msd.jpg</v>
+        <v>assets/1787282703381-2uakw592b4.jpg</v>
       </c>
       <c r="D120" t="str">
         <v>否</v>
       </c>
       <c r="E120" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F120" t="str">
         <v/>
@@ -7487,19 +7487,19 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>阴影色NS11</v>
+        <v>烟灰色</v>
       </c>
       <c r="B121" t="str">
         <v>弟弟</v>
       </c>
       <c r="C121" t="str">
-        <v>assets/1787280590041-vzcwebdok1.jpg</v>
+        <v>assets/1787282649397-9hc31ncrpc.jpg</v>
       </c>
       <c r="D121" t="str">
         <v>否</v>
       </c>
       <c r="E121" t="str">
-        <v>2026-05-28</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F121" t="str">
         <v/>
@@ -7546,19 +7546,19 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>浅色银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B122" t="str">
         <v>妹妹</v>
       </c>
       <c r="C122" t="str">
-        <v>assets/1787281786169-9ia0h837ct.jpg</v>
+        <v>assets/1787282617957-svcoyyznpg.jpg</v>
       </c>
       <c r="D122" t="str">
         <v>否</v>
       </c>
       <c r="E122" t="str">
-        <v>2026-06-15</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F122" t="str">
         <v/>
@@ -7605,22 +7605,22 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>浅烟灰色</v>
+        <v>烟灰色</v>
       </c>
       <c r="B123" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C123" t="str">
-        <v>assets/1785843720843-63qz159daui.jpg</v>
+        <v>assets/1787282419632-78nixqjzua.jpg</v>
       </c>
       <c r="D123" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E123" t="str">
-        <v>2026-03-21</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F123" t="str">
-        <v>四川成都</v>
+        <v/>
       </c>
       <c r="G123" t="str">
         <v/>
@@ -7664,22 +7664,22 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>凯米尔色</v>
+        <v>纯黑色</v>
       </c>
       <c r="B124" t="str">
         <v>弟弟</v>
       </c>
       <c r="C124" t="str">
-        <v>assets/1787301984056-iu6afro5z5.jpg, assets/1785843763310-elg05ur61ri.jpg</v>
+        <v>assets/1787282349942-2cfuyn7xlc.jpg</v>
       </c>
       <c r="D124" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E124" t="str">
-        <v>2026-02-14</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F124" t="str">
-        <v>上海浦东</v>
+        <v/>
       </c>
       <c r="G124" t="str">
         <v/>
@@ -7723,19 +7723,19 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>银虎斑补丁</v>
+        <v>银虎斑</v>
       </c>
       <c r="B125" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C125" t="str">
-        <v>assets/1785843820715-9kz7gy4mbr7.jpg</v>
+        <v>assets/1787282064159-6b4z8c5msd.jpg</v>
       </c>
       <c r="D125" t="str">
         <v>否</v>
       </c>
       <c r="E125" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-10</v>
       </c>
       <c r="F125" t="str">
         <v/>
@@ -7782,19 +7782,19 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>烟灰色</v>
+        <v>阴影色NS11</v>
       </c>
       <c r="B126" t="str">
         <v>弟弟</v>
       </c>
       <c r="C126" t="str">
-        <v>assets/1785843953805-mxl3x1982io.jpg</v>
+        <v>assets/1787280590041-vzcwebdok1.jpg</v>
       </c>
       <c r="D126" t="str">
         <v>否</v>
       </c>
       <c r="E126" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F126" t="str">
         <v/>
@@ -7841,19 +7841,19 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>棕虎斑玳瑁</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B127" t="str">
         <v>妹妹</v>
       </c>
       <c r="C127" t="str">
-        <v>assets/1785844013835-ek4xpcje7kh.jpg</v>
+        <v>assets/1787281786169-9ia0h837ct.jpg</v>
       </c>
       <c r="D127" t="str">
         <v>否</v>
       </c>
       <c r="E127" t="str">
-        <v>2026-02-14</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F127" t="str">
         <v/>
@@ -7900,22 +7900,22 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>银虎斑补丁</v>
+        <v>浅烟灰色</v>
       </c>
       <c r="B128" t="str">
         <v>妹妹</v>
       </c>
       <c r="C128" t="str">
-        <v>assets/1785844434338-ek5zbdgdcne.jpg</v>
+        <v>assets/1785843720843-63qz159daui.jpg</v>
       </c>
       <c r="D128" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E128" t="str">
-        <v>2026-05-24</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F128" t="str">
-        <v/>
+        <v>四川成都</v>
       </c>
       <c r="G128" t="str">
         <v/>
@@ -7959,22 +7959,22 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>银虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B129" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C129" t="str">
-        <v>assets/1785838787730-s5f333sc3u.jpg</v>
+        <v>assets/1787301984056-iu6afro5z5.jpg, assets/1785843763310-elg05ur61ri.jpg</v>
       </c>
       <c r="D129" t="str">
         <v>是</v>
       </c>
       <c r="E129" t="str">
-        <v>2026-06-05</v>
+        <v>2026-02-14</v>
       </c>
       <c r="F129" t="str">
-        <v>湖北恩施</v>
+        <v>上海浦东</v>
       </c>
       <c r="G129" t="str">
         <v/>
@@ -8018,22 +8018,22 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>银虎斑</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B130" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C130" t="str">
-        <v>assets/1785842296661-6qw3zs3as8h.jpg</v>
+        <v>assets/1785843820715-9kz7gy4mbr7.jpg</v>
       </c>
       <c r="D130" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E130" t="str">
-        <v>2026-06-05</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F130" t="str">
-        <v>湖北恩施</v>
+        <v/>
       </c>
       <c r="G130" t="str">
         <v/>
@@ -8077,22 +8077,22 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B131" t="str">
         <v>弟弟</v>
       </c>
       <c r="C131" t="str">
-        <v>assets/1785842429109-porc98rel5.jpg</v>
+        <v>assets/1785843953805-mxl3x1982io.jpg</v>
       </c>
       <c r="D131" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E131" t="str">
-        <v>2025-11-05</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F131" t="str">
-        <v>韩国</v>
+        <v/>
       </c>
       <c r="G131" t="str">
         <v/>
@@ -8136,19 +8136,19 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑玳瑁</v>
       </c>
       <c r="B132" t="str">
         <v>妹妹</v>
       </c>
       <c r="C132" t="str">
-        <v>assets/1785842594141-fcglbzjp509.jpg</v>
+        <v>assets/1785844013835-ek4xpcje7kh.jpg</v>
       </c>
       <c r="D132" t="str">
         <v>否</v>
       </c>
       <c r="E132" t="str">
-        <v>2026-05-18</v>
+        <v>2026-02-14</v>
       </c>
       <c r="F132" t="str">
         <v/>
@@ -8195,22 +8195,22 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B133" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C133" t="str">
-        <v>assets/1785842639100-82k775dhwiv.jpg</v>
+        <v>assets/1785844434338-ek5zbdgdcne.jpg</v>
       </c>
       <c r="D133" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E133" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-24</v>
       </c>
       <c r="F133" t="str">
-        <v>四川自贡</v>
+        <v/>
       </c>
       <c r="G133" t="str">
         <v/>
@@ -8254,22 +8254,22 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B134" t="str">
         <v>妹妹</v>
       </c>
       <c r="C134" t="str">
-        <v>assets/1785842684502-mnhr0r96eee.jpg</v>
+        <v>assets/1785838787730-s5f333sc3u.jpg</v>
       </c>
       <c r="D134" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E134" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F134" t="str">
-        <v/>
+        <v>湖北恩施</v>
       </c>
       <c r="G134" t="str">
         <v/>
@@ -8313,22 +8313,22 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>纯黑色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B135" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C135" t="str">
-        <v>assets/1785842779532-5u1j0igrw1s.jpg</v>
+        <v>assets/1785842296661-6qw3zs3as8h.jpg</v>
       </c>
       <c r="D135" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E135" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F135" t="str">
-        <v/>
+        <v>湖北恩施</v>
       </c>
       <c r="G135" t="str">
         <v/>
@@ -8375,16 +8375,16 @@
         <v>银虎斑</v>
       </c>
       <c r="B136" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C136" t="str">
-        <v>assets/1785842817046-6keqv4rw4yf.jpg</v>
+        <v>assets/1785842429109-porc98rel5.jpg</v>
       </c>
       <c r="D136" t="str">
         <v>是</v>
       </c>
       <c r="E136" t="str">
-        <v>2026-03-05</v>
+        <v>2025-11-05</v>
       </c>
       <c r="F136" t="str">
         <v>韩国</v>
@@ -8431,22 +8431,22 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>浅色银虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B137" t="str">
         <v>妹妹</v>
       </c>
       <c r="C137" t="str">
-        <v>assets/1785842950972-a88lbrskpc.jpg</v>
+        <v>assets/1785842594141-fcglbzjp509.jpg</v>
       </c>
       <c r="D137" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E137" t="str">
-        <v>2026-06-05</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F137" t="str">
-        <v>河北邢台</v>
+        <v/>
       </c>
       <c r="G137" t="str">
         <v/>
@@ -8496,13 +8496,13 @@
         <v>弟弟</v>
       </c>
       <c r="C138" t="str">
-        <v>assets/1785843011477-n3l1wi6ech.jpg</v>
+        <v>assets/1785842639100-82k775dhwiv.jpg</v>
       </c>
       <c r="D138" t="str">
         <v>是</v>
       </c>
       <c r="E138" t="str">
-        <v>2026-06-05</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F138" t="str">
         <v>四川自贡</v>
@@ -8549,19 +8549,19 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B139" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C139" t="str">
-        <v>assets/1785843237517-ga449iqess5.jpg</v>
+        <v>assets/1785842684502-mnhr0r96eee.jpg</v>
       </c>
       <c r="D139" t="str">
         <v>否</v>
       </c>
       <c r="E139" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F139" t="str">
         <v/>
@@ -8608,13 +8608,13 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>棕虎斑补丁</v>
+        <v>纯黑色</v>
       </c>
       <c r="B140" t="str">
         <v>妹妹</v>
       </c>
       <c r="C140" t="str">
-        <v>assets/1785842523893-7nwnnhwi4ns.jpg</v>
+        <v>assets/1785842779532-5u1j0igrw1s.jpg</v>
       </c>
       <c r="D140" t="str">
         <v>否</v>
@@ -8667,22 +8667,22 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>蓝虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B141" t="str">
         <v>妹妹</v>
       </c>
       <c r="C141" t="str">
-        <v>assets/1785843497557-st27fk8drqi.jpg</v>
+        <v>assets/1785842817046-6keqv4rw4yf.jpg</v>
       </c>
       <c r="D141" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E141" t="str">
-        <v>2026-04-05</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F141" t="str">
-        <v/>
+        <v>韩国</v>
       </c>
       <c r="G141" t="str">
         <v/>
@@ -8726,22 +8726,22 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>银虎斑</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B142" t="str">
         <v>妹妹</v>
       </c>
       <c r="C142" t="str">
-        <v>assets/1785843621923-ylhakbtw13i.jpg</v>
+        <v>assets/1785842950972-a88lbrskpc.jpg</v>
       </c>
       <c r="D142" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E142" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F142" t="str">
-        <v/>
+        <v>河北邢台</v>
       </c>
       <c r="G142" t="str">
         <v/>
@@ -8785,22 +8785,22 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B143" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C143" t="str">
-        <v>assets/1785843663884-sfxvpmiet7.jpg</v>
+        <v>assets/1785843011477-n3l1wi6ech.jpg</v>
       </c>
       <c r="D143" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E143" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F143" t="str">
-        <v/>
+        <v>四川自贡</v>
       </c>
       <c r="G143" t="str">
         <v/>
@@ -8847,49 +8847,49 @@
         <v>蓝虎斑</v>
       </c>
       <c r="B144" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C144" t="str">
-        <v>assets/1785852601940-o236xtv7yx.jpeg</v>
+        <v>assets/1785843237517-ga449iqess5.jpg</v>
       </c>
       <c r="D144" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E144" t="str">
-        <v>2026-02-20</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F144" t="str">
-        <v>荷兰</v>
+        <v/>
       </c>
       <c r="G144" t="str">
-        <v>阿泽</v>
+        <v/>
       </c>
       <c r="H144" t="str">
-        <v>小辫子</v>
+        <v/>
       </c>
       <c r="I144" t="str">
-        <v>驺驺</v>
+        <v/>
       </c>
       <c r="J144" t="str">
-        <v>2026-07-02</v>
+        <v/>
       </c>
       <c r="K144" t="str">
         <v/>
       </c>
       <c r="L144" t="str">
-        <v>2026-07-02</v>
+        <v/>
       </c>
       <c r="M144" t="str">
-        <v>2026-08-03</v>
+        <v/>
       </c>
       <c r="N144" t="str">
-        <v>2026-11-04</v>
+        <v/>
       </c>
       <c r="O144" t="str">
-        <v>2026-08-03 · 血清检测,2026-07-02 · 打疫苗 · assets/diary/zouzou-depart.jpg,2026-07-30 · 6.2斤 · 五个月10天了 · assets/feedback/zouzou-1.jpg</v>
+        <v/>
       </c>
       <c r="P144" t="str">
-        <v>已付定金</v>
+        <v/>
       </c>
       <c r="Q144" t="str">
         <v/>
@@ -8898,27 +8898,27 @@
         <v/>
       </c>
       <c r="S144" t="str">
-        <v>否</v>
+        <v/>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>红虎斑</v>
+        <v>棕虎斑补丁</v>
       </c>
       <c r="B145" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C145" t="str">
-        <v>assets/1785853950207-cedor66ou2q.jpeg</v>
+        <v>assets/1785842523893-7nwnnhwi4ns.jpg</v>
       </c>
       <c r="D145" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E145" t="str">
-        <v/>
+        <v>2026-03-05</v>
       </c>
       <c r="F145" t="str">
-        <v>广东广州</v>
+        <v/>
       </c>
       <c r="G145" t="str">
         <v/>
@@ -8962,22 +8962,22 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>红虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B146" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C146" t="str">
-        <v>assets/1785854129383-c8qkvl537x.jpeg</v>
+        <v>assets/1785843497557-st27fk8drqi.jpg</v>
       </c>
       <c r="D146" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E146" t="str">
-        <v/>
+        <v>2026-04-05</v>
       </c>
       <c r="F146" t="str">
-        <v>广东广州</v>
+        <v/>
       </c>
       <c r="G146" t="str">
         <v/>
@@ -9024,19 +9024,19 @@
         <v>银虎斑</v>
       </c>
       <c r="B147" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C147" t="str">
-        <v>assets/1785854166720-48r17hry9cd.jpeg</v>
+        <v>assets/1785843621923-ylhakbtw13i.jpg</v>
       </c>
       <c r="D147" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E147" t="str">
-        <v/>
+        <v>2026-03-05</v>
       </c>
       <c r="F147" t="str">
-        <v>山西朔州</v>
+        <v/>
       </c>
       <c r="G147" t="str">
         <v/>
@@ -9086,16 +9086,16 @@
         <v>妹妹</v>
       </c>
       <c r="C148" t="str">
-        <v>assets/1785854224521-2cpg6xipfn6.jpeg</v>
+        <v>assets/1785843663884-sfxvpmiet7.jpg</v>
       </c>
       <c r="D148" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E148" t="str">
-        <v/>
+        <v>2026-03-05</v>
       </c>
       <c r="F148" t="str">
-        <v>浙江宁波</v>
+        <v/>
       </c>
       <c r="G148" t="str">
         <v/>
@@ -9139,52 +9139,52 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B149" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C149" t="str">
-        <v>assets/1785854260793-steez4s972l.jpeg</v>
+        <v>assets/1785852601940-o236xtv7yx.jpeg</v>
       </c>
       <c r="D149" t="str">
         <v>是</v>
       </c>
       <c r="E149" t="str">
-        <v/>
+        <v>2026-02-20</v>
       </c>
       <c r="F149" t="str">
-        <v>陕西西安</v>
+        <v>荷兰</v>
       </c>
       <c r="G149" t="str">
-        <v/>
+        <v>阿泽</v>
       </c>
       <c r="H149" t="str">
-        <v/>
+        <v>小辫子</v>
       </c>
       <c r="I149" t="str">
-        <v/>
+        <v>驺驺</v>
       </c>
       <c r="J149" t="str">
-        <v/>
+        <v>2026-07-02</v>
       </c>
       <c r="K149" t="str">
         <v/>
       </c>
       <c r="L149" t="str">
-        <v/>
+        <v>2026-07-02</v>
       </c>
       <c r="M149" t="str">
-        <v/>
+        <v>2026-08-03</v>
       </c>
       <c r="N149" t="str">
-        <v/>
+        <v>2026-11-04</v>
       </c>
       <c r="O149" t="str">
-        <v/>
+        <v>2026-08-03 · 血清检测,2026-07-02 · 打疫苗 · assets/diary/zouzou-depart.jpg,2026-07-30 · 6.2斤 · 五个月10天了 · assets/feedback/zouzou-1.jpg</v>
       </c>
       <c r="P149" t="str">
-        <v/>
+        <v>已付定金</v>
       </c>
       <c r="Q149" t="str">
         <v/>
@@ -9193,18 +9193,18 @@
         <v/>
       </c>
       <c r="S149" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B150" t="str">
         <v>弟弟</v>
       </c>
       <c r="C150" t="str">
-        <v>assets/1785854319988-cohio08aod5.jpeg</v>
+        <v>assets/1785853950207-cedor66ou2q.jpeg</v>
       </c>
       <c r="D150" t="str">
         <v>是</v>
@@ -9213,7 +9213,7 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>黑龙江漠河</v>
+        <v>广东广州</v>
       </c>
       <c r="G150" t="str">
         <v/>
@@ -9257,13 +9257,13 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>棕虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B151" t="str">
         <v>弟弟</v>
       </c>
       <c r="C151" t="str">
-        <v>assets/1785854520974-96b8b1ekqd9.jpeg</v>
+        <v>assets/1785854129383-c8qkvl537x.jpeg</v>
       </c>
       <c r="D151" t="str">
         <v>是</v>
@@ -9272,7 +9272,7 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>日本</v>
+        <v>广东广州</v>
       </c>
       <c r="G151" t="str">
         <v/>
@@ -9319,10 +9319,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B152" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C152" t="str">
-        <v>assets/1785854664100-haqoiu1h7hj.jpeg</v>
+        <v>assets/1785854166720-48r17hry9cd.jpeg</v>
       </c>
       <c r="D152" t="str">
         <v>是</v>
@@ -9331,7 +9331,7 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>浙江杭州</v>
+        <v>山西朔州</v>
       </c>
       <c r="G152" t="str">
         <v/>
@@ -9381,7 +9381,7 @@
         <v>妹妹</v>
       </c>
       <c r="C153" t="str">
-        <v>assets/1785854690732-orrs40sx9rs.jpeg</v>
+        <v>assets/1785854224521-2cpg6xipfn6.jpeg</v>
       </c>
       <c r="D153" t="str">
         <v>是</v>
@@ -9390,7 +9390,7 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>贵州安顺</v>
+        <v>浙江宁波</v>
       </c>
       <c r="G153" t="str">
         <v/>
@@ -9437,10 +9437,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B154" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C154" t="str">
-        <v>assets/1785854734122-wcpmib4m7.jpeg</v>
+        <v>assets/1785854260793-steez4s972l.jpeg</v>
       </c>
       <c r="D154" t="str">
         <v>是</v>
@@ -9449,7 +9449,7 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>山东青岛</v>
+        <v>陕西西安</v>
       </c>
       <c r="G154" t="str">
         <v/>
@@ -9499,7 +9499,7 @@
         <v>弟弟</v>
       </c>
       <c r="C155" t="str">
-        <v>assets/1785854758707-1kxdkfvs6jc.jpeg</v>
+        <v>assets/1785854319988-cohio08aod5.jpeg</v>
       </c>
       <c r="D155" t="str">
         <v>是</v>
@@ -9552,13 +9552,13 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>纯蓝色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B156" t="str">
         <v>弟弟</v>
       </c>
       <c r="C156" t="str">
-        <v>assets/1785854784780-3g0u60pdo93.jpeg</v>
+        <v>assets/1785854520974-96b8b1ekqd9.jpeg</v>
       </c>
       <c r="D156" t="str">
         <v>是</v>
@@ -9567,7 +9567,7 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>河南鹤壁</v>
+        <v>日本</v>
       </c>
       <c r="G156" t="str">
         <v/>
@@ -9614,10 +9614,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B157" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C157" t="str">
-        <v>assets/1785854813179-8oyxr0h2bbu.jpeg</v>
+        <v>assets/1785854664100-haqoiu1h7hj.jpeg</v>
       </c>
       <c r="D157" t="str">
         <v>是</v>
@@ -9626,7 +9626,7 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>陕西西安</v>
+        <v>浙江杭州</v>
       </c>
       <c r="G157" t="str">
         <v/>
@@ -9670,13 +9670,13 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B158" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C158" t="str">
-        <v>assets/1785854838933-uq6amircyzd.jpeg</v>
+        <v>assets/1785854690732-orrs40sx9rs.jpeg</v>
       </c>
       <c r="D158" t="str">
         <v>是</v>
@@ -9685,7 +9685,7 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>四川成都</v>
+        <v>贵州安顺</v>
       </c>
       <c r="G158" t="str">
         <v/>
@@ -9729,22 +9729,22 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>烟灰色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B159" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C159" t="str">
-        <v>assets/1785854869973-za3p6wikqpo.jpeg</v>
+        <v>assets/1785854734122-wcpmib4m7.jpeg</v>
       </c>
       <c r="D159" t="str">
         <v>是</v>
       </c>
       <c r="E159" t="str">
-        <v>2026-05-18</v>
+        <v/>
       </c>
       <c r="F159" t="str">
-        <v>四川成都</v>
+        <v>山东青岛</v>
       </c>
       <c r="G159" t="str">
         <v/>
@@ -9794,7 +9794,7 @@
         <v>弟弟</v>
       </c>
       <c r="C160" t="str">
-        <v>assets/1785854997023-mawkallt2a.jpeg</v>
+        <v>assets/1785854758707-1kxdkfvs6jc.jpeg</v>
       </c>
       <c r="D160" t="str">
         <v>是</v>
@@ -9803,7 +9803,7 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>新加坡</v>
+        <v>黑龙江漠河</v>
       </c>
       <c r="G160" t="str">
         <v/>
@@ -9847,13 +9847,13 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>凯米尔色</v>
+        <v>纯蓝色</v>
       </c>
       <c r="B161" t="str">
         <v>弟弟</v>
       </c>
       <c r="C161" t="str">
-        <v>assets/1785855043327-wdc5pxwm34k.jpeg</v>
+        <v>assets/1785854784780-3g0u60pdo93.jpeg</v>
       </c>
       <c r="D161" t="str">
         <v>是</v>
@@ -9862,7 +9862,7 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>上海浦东</v>
+        <v>河南鹤壁</v>
       </c>
       <c r="G161" t="str">
         <v/>
@@ -9906,22 +9906,22 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B162" t="str">
         <v>弟弟</v>
       </c>
       <c r="C162" t="str">
-        <v>assets/1785912551260-jplefm937nk.jpeg, assets/videos/02.mp4</v>
+        <v>assets/1785854813179-8oyxr0h2bbu.jpeg</v>
       </c>
       <c r="D162" t="str">
         <v>是</v>
       </c>
       <c r="E162" t="str">
-        <v>2026-06-06</v>
+        <v/>
       </c>
       <c r="F162" t="str">
-        <v>浙江温州</v>
+        <v>陕西西安</v>
       </c>
       <c r="G162" t="str">
         <v/>
@@ -9968,63 +9968,358 @@
         <v>棕虎斑</v>
       </c>
       <c r="B163" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C163" t="str">
+        <v>assets/1785854838933-uq6amircyzd.jpeg</v>
+      </c>
+      <c r="D163" t="str">
+        <v>是</v>
+      </c>
+      <c r="E163" t="str">
+        <v/>
+      </c>
+      <c r="F163" t="str">
+        <v>四川成都</v>
+      </c>
+      <c r="G163" t="str">
+        <v/>
+      </c>
+      <c r="H163" t="str">
+        <v/>
+      </c>
+      <c r="I163" t="str">
+        <v/>
+      </c>
+      <c r="J163" t="str">
+        <v/>
+      </c>
+      <c r="K163" t="str">
+        <v/>
+      </c>
+      <c r="L163" t="str">
+        <v/>
+      </c>
+      <c r="M163" t="str">
+        <v/>
+      </c>
+      <c r="N163" t="str">
+        <v/>
+      </c>
+      <c r="O163" t="str">
+        <v/>
+      </c>
+      <c r="P163" t="str">
+        <v/>
+      </c>
+      <c r="Q163" t="str">
+        <v/>
+      </c>
+      <c r="R163" t="str">
+        <v/>
+      </c>
+      <c r="S163" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v>烟灰色</v>
+      </c>
+      <c r="B164" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C164" t="str">
+        <v>assets/1785854869973-za3p6wikqpo.jpeg</v>
+      </c>
+      <c r="D164" t="str">
+        <v>是</v>
+      </c>
+      <c r="E164" t="str">
+        <v>2026-05-18</v>
+      </c>
+      <c r="F164" t="str">
+        <v>四川成都</v>
+      </c>
+      <c r="G164" t="str">
+        <v/>
+      </c>
+      <c r="H164" t="str">
+        <v/>
+      </c>
+      <c r="I164" t="str">
+        <v/>
+      </c>
+      <c r="J164" t="str">
+        <v/>
+      </c>
+      <c r="K164" t="str">
+        <v/>
+      </c>
+      <c r="L164" t="str">
+        <v/>
+      </c>
+      <c r="M164" t="str">
+        <v/>
+      </c>
+      <c r="N164" t="str">
+        <v/>
+      </c>
+      <c r="O164" t="str">
+        <v/>
+      </c>
+      <c r="P164" t="str">
+        <v/>
+      </c>
+      <c r="Q164" t="str">
+        <v/>
+      </c>
+      <c r="R164" t="str">
+        <v/>
+      </c>
+      <c r="S164" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v>银虎斑</v>
+      </c>
+      <c r="B165" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C165" t="str">
+        <v>assets/1785854997023-mawkallt2a.jpeg</v>
+      </c>
+      <c r="D165" t="str">
+        <v>是</v>
+      </c>
+      <c r="E165" t="str">
+        <v/>
+      </c>
+      <c r="F165" t="str">
+        <v>新加坡</v>
+      </c>
+      <c r="G165" t="str">
+        <v/>
+      </c>
+      <c r="H165" t="str">
+        <v/>
+      </c>
+      <c r="I165" t="str">
+        <v/>
+      </c>
+      <c r="J165" t="str">
+        <v/>
+      </c>
+      <c r="K165" t="str">
+        <v/>
+      </c>
+      <c r="L165" t="str">
+        <v/>
+      </c>
+      <c r="M165" t="str">
+        <v/>
+      </c>
+      <c r="N165" t="str">
+        <v/>
+      </c>
+      <c r="O165" t="str">
+        <v/>
+      </c>
+      <c r="P165" t="str">
+        <v/>
+      </c>
+      <c r="Q165" t="str">
+        <v/>
+      </c>
+      <c r="R165" t="str">
+        <v/>
+      </c>
+      <c r="S165" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="str">
+        <v>凯米尔色</v>
+      </c>
+      <c r="B166" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C166" t="str">
+        <v>assets/1785855043327-wdc5pxwm34k.jpeg</v>
+      </c>
+      <c r="D166" t="str">
+        <v>是</v>
+      </c>
+      <c r="E166" t="str">
+        <v/>
+      </c>
+      <c r="F166" t="str">
+        <v>上海浦东</v>
+      </c>
+      <c r="G166" t="str">
+        <v/>
+      </c>
+      <c r="H166" t="str">
+        <v/>
+      </c>
+      <c r="I166" t="str">
+        <v/>
+      </c>
+      <c r="J166" t="str">
+        <v/>
+      </c>
+      <c r="K166" t="str">
+        <v/>
+      </c>
+      <c r="L166" t="str">
+        <v/>
+      </c>
+      <c r="M166" t="str">
+        <v/>
+      </c>
+      <c r="N166" t="str">
+        <v/>
+      </c>
+      <c r="O166" t="str">
+        <v/>
+      </c>
+      <c r="P166" t="str">
+        <v/>
+      </c>
+      <c r="Q166" t="str">
+        <v/>
+      </c>
+      <c r="R166" t="str">
+        <v/>
+      </c>
+      <c r="S166" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v>棕虎斑</v>
+      </c>
+      <c r="B167" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C167" t="str">
+        <v>assets/1785912551260-jplefm937nk.jpeg, assets/videos/02.mp4</v>
+      </c>
+      <c r="D167" t="str">
+        <v>是</v>
+      </c>
+      <c r="E167" t="str">
+        <v>2026-06-06</v>
+      </c>
+      <c r="F167" t="str">
+        <v>浙江温州</v>
+      </c>
+      <c r="G167" t="str">
+        <v/>
+      </c>
+      <c r="H167" t="str">
+        <v/>
+      </c>
+      <c r="I167" t="str">
+        <v/>
+      </c>
+      <c r="J167" t="str">
+        <v/>
+      </c>
+      <c r="K167" t="str">
+        <v/>
+      </c>
+      <c r="L167" t="str">
+        <v/>
+      </c>
+      <c r="M167" t="str">
+        <v/>
+      </c>
+      <c r="N167" t="str">
+        <v/>
+      </c>
+      <c r="O167" t="str">
+        <v/>
+      </c>
+      <c r="P167" t="str">
+        <v/>
+      </c>
+      <c r="Q167" t="str">
+        <v/>
+      </c>
+      <c r="R167" t="str">
+        <v/>
+      </c>
+      <c r="S167" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="str">
+        <v>棕虎斑</v>
+      </c>
+      <c r="B168" t="str">
         <v>妹妹</v>
       </c>
-      <c r="C163" t="str">
+      <c r="C168" t="str">
         <v>assets/1785912694000-m20f5kvvrr.jpeg</v>
       </c>
-      <c r="D163" t="str">
-        <v>否</v>
-      </c>
-      <c r="E163" t="str">
+      <c r="D168" t="str">
+        <v>否</v>
+      </c>
+      <c r="E168" t="str">
         <v>2026-06-06</v>
       </c>
-      <c r="F163" t="str">
-        <v/>
-      </c>
-      <c r="G163" t="str">
-        <v/>
-      </c>
-      <c r="H163" t="str">
-        <v/>
-      </c>
-      <c r="I163" t="str">
-        <v/>
-      </c>
-      <c r="J163" t="str">
-        <v/>
-      </c>
-      <c r="K163" t="str">
-        <v/>
-      </c>
-      <c r="L163" t="str">
-        <v/>
-      </c>
-      <c r="M163" t="str">
-        <v/>
-      </c>
-      <c r="N163" t="str">
-        <v/>
-      </c>
-      <c r="O163" t="str">
-        <v/>
-      </c>
-      <c r="P163" t="str">
-        <v/>
-      </c>
-      <c r="Q163" t="str">
-        <v/>
-      </c>
-      <c r="R163" t="str">
-        <v/>
-      </c>
-      <c r="S163" t="str">
+      <c r="F168" t="str">
+        <v/>
+      </c>
+      <c r="G168" t="str">
+        <v/>
+      </c>
+      <c r="H168" t="str">
+        <v/>
+      </c>
+      <c r="I168" t="str">
+        <v/>
+      </c>
+      <c r="J168" t="str">
+        <v/>
+      </c>
+      <c r="K168" t="str">
+        <v/>
+      </c>
+      <c r="L168" t="str">
+        <v/>
+      </c>
+      <c r="M168" t="str">
+        <v/>
+      </c>
+      <c r="N168" t="str">
+        <v/>
+      </c>
+      <c r="O168" t="str">
+        <v/>
+      </c>
+      <c r="P168" t="str">
+        <v/>
+      </c>
+      <c r="Q168" t="str">
+        <v/>
+      </c>
+      <c r="R168" t="str">
+        <v/>
+      </c>
+      <c r="S168" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S163"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S168"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S168"/>
+  <dimension ref="A1:S171"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -466,13 +466,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>凯米尔</v>
+        <v>红虎斑</v>
       </c>
       <c r="B2" t="str">
         <v>弟弟</v>
       </c>
       <c r="C2" t="str">
-        <v>assets/1788014088852-oqkg79cki9.jpg</v>
+        <v>assets/1788442386268-ilpasqz91m.jpg</v>
       </c>
       <c r="D2" t="str">
         <v>否</v>
@@ -525,19 +525,19 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>棕虎斑</v>
+        <v>浅银虎斑</v>
       </c>
       <c r="B3" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C3" t="str">
-        <v>assets/1788014050978-9a2sguuo1u.jpg</v>
+        <v>assets/1788442356842-bbleakpy85.jpg</v>
       </c>
       <c r="D3" t="str">
         <v>否</v>
       </c>
       <c r="E3" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -584,19 +584,19 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>棕虎斑</v>
+        <v>浅烟灰色</v>
       </c>
       <c r="B4" t="str">
         <v>弟弟</v>
       </c>
       <c r="C4" t="str">
-        <v>assets/1788013924404-gmlh0hfjae.jpg</v>
+        <v>assets/1788442221802-et3crh0tww.jpg</v>
       </c>
       <c r="D4" t="str">
         <v>否</v>
       </c>
       <c r="E4" t="str">
-        <v>2026-06-15</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -643,22 +643,22 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>凯米尔色</v>
+        <v>凯米尔</v>
       </c>
       <c r="B5" t="str">
         <v>弟弟</v>
       </c>
       <c r="C5" t="str">
-        <v>assets/1788013889955-wpykaycfde.jpg</v>
+        <v>assets/1788014088852-oqkg79cki9.jpg</v>
       </c>
       <c r="D5" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E5" t="str">
         <v>2026-06-26</v>
       </c>
       <c r="F5" t="str">
-        <v/>
+        <v>湖北襄阳</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -702,19 +702,19 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>银虎斑补丁</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B6" t="str">
         <v>妹妹</v>
       </c>
       <c r="C6" t="str">
-        <v>assets/1788013810551-b90h1mwfiq.jpg</v>
+        <v>assets/1788014050978-9a2sguuo1u.jpg</v>
       </c>
       <c r="D6" t="str">
         <v>否</v>
       </c>
       <c r="E6" t="str">
-        <v>2026-06-26</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -761,22 +761,22 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B7" t="str">
         <v>弟弟</v>
       </c>
       <c r="C7" t="str">
-        <v>assets/1787837910484-r7urrsuib0.jpg</v>
+        <v>assets/1788013924404-gmlh0hfjae.jpg</v>
       </c>
       <c r="D7" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E7" t="str">
-        <v>2026-05-18</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F7" t="str">
-        <v/>
+        <v>浙江嘉兴</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -820,22 +820,22 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>纯黑色</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B8" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C8" t="str">
-        <v>assets/1787837846581-6q9nxgad35.jpg</v>
+        <v>assets/1788013889955-wpykaycfde.jpg</v>
       </c>
       <c r="D8" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E8" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-26</v>
       </c>
       <c r="F8" t="str">
-        <v/>
+        <v>湖北襄阳</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -879,13 +879,13 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>凯米尔</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B9" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C9" t="str">
-        <v>assets/1787837779354-hkuyvt39iz.jpg</v>
+        <v>assets/1788013810551-b90h1mwfiq.jpg</v>
       </c>
       <c r="D9" t="str">
         <v>否</v>
@@ -938,22 +938,22 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>烟灰色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B10" t="str">
         <v>弟弟</v>
       </c>
       <c r="C10" t="str">
-        <v>assets/1787837690599-rd37ukkrgw.jpg</v>
+        <v>assets/1787837910484-r7urrsuib0.jpg</v>
       </c>
       <c r="D10" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E10" t="str">
-        <v>2026-06-06</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F10" t="str">
-        <v/>
+        <v>香港</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -997,22 +997,22 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>棕虎斑</v>
+        <v>纯黑色</v>
       </c>
       <c r="B11" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C11" t="str">
-        <v>assets/1787837648423-9riberz3tq.jpg</v>
+        <v>assets/1787837846581-6q9nxgad35.jpg</v>
       </c>
       <c r="D11" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E11" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-10</v>
       </c>
       <c r="F11" t="str">
-        <v>北京</v>
+        <v/>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -1056,19 +1056,19 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>棕虎斑</v>
+        <v>凯米尔</v>
       </c>
       <c r="B12" t="str">
         <v>弟弟</v>
       </c>
       <c r="C12" t="str">
-        <v>assets/1787837594903-wtnbv2fz89.jpg</v>
+        <v>assets/1787837779354-hkuyvt39iz.jpg</v>
       </c>
       <c r="D12" t="str">
         <v>否</v>
       </c>
       <c r="E12" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-26</v>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -1115,19 +1115,19 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>棕虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B13" t="str">
         <v>弟弟</v>
       </c>
       <c r="C13" t="str">
-        <v>assets/1787479268842-7en9nzy302.jpg</v>
+        <v>assets/1787837690599-rd37ukkrgw.jpg</v>
       </c>
       <c r="D13" t="str">
         <v>否</v>
       </c>
       <c r="E13" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F13" t="str">
         <v/>
@@ -1142,7 +1142,7 @@
         <v/>
       </c>
       <c r="J13" t="str">
-        <v>2026-06-10</v>
+        <v/>
       </c>
       <c r="K13" t="str">
         <v/>
@@ -1174,22 +1174,22 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>纯黑色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B14" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C14" t="str">
-        <v>assets/1787479242639-32zuh5lham.jpg</v>
+        <v>assets/1787837648423-9riberz3tq.jpg</v>
       </c>
       <c r="D14" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E14" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F14" t="str">
-        <v/>
+        <v>北京</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -1236,19 +1236,19 @@
         <v>棕虎斑</v>
       </c>
       <c r="B15" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C15" t="str">
-        <v>assets/1787466121255-21jto2cugv.jpg</v>
+        <v>assets/1787837594903-wtnbv2fz89.jpg</v>
       </c>
       <c r="D15" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E15" t="str">
-        <v/>
+        <v>2026-06-10</v>
       </c>
       <c r="F15" t="str">
-        <v>四川广安</v>
+        <v/>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -1292,19 +1292,19 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B16" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C16" t="str">
-        <v>assets/1787388322060-uj8bkwqgnv.jpg</v>
+        <v>assets/1787479268842-7en9nzy302.jpg</v>
       </c>
       <c r="D16" t="str">
         <v>否</v>
       </c>
       <c r="E16" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-10</v>
       </c>
       <c r="F16" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v/>
       </c>
       <c r="J16" t="str">
-        <v/>
+        <v>2026-06-10</v>
       </c>
       <c r="K16" t="str">
         <v/>
@@ -1351,19 +1351,19 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>棕虎斑</v>
+        <v>纯黑色</v>
       </c>
       <c r="B17" t="str">
         <v>妹妹</v>
       </c>
       <c r="C17" t="str">
-        <v>assets/1787388277490-e6u506cx0r.jpg</v>
+        <v>assets/1787479242639-32zuh5lham.jpg</v>
       </c>
       <c r="D17" t="str">
         <v>否</v>
       </c>
       <c r="E17" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-10</v>
       </c>
       <c r="F17" t="str">
         <v/>
@@ -1410,13 +1410,13 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B18" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C18" t="str">
-        <v>assets/1787328436957-x30od0gw28.jpg</v>
+        <v>assets/1787466121255-21jto2cugv.jpg</v>
       </c>
       <c r="D18" t="str">
         <v>是</v>
@@ -1425,7 +1425,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>江苏苏州</v>
+        <v>四川广安</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1469,22 +1469,22 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>蓝虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B19" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C19" t="str">
-        <v>assets/1787328420967-viv9v8nbjn.jpg</v>
+        <v>assets/1787388322060-uj8bkwqgnv.jpg</v>
       </c>
       <c r="D19" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E19" t="str">
-        <v/>
+        <v>2026-06-06</v>
       </c>
       <c r="F19" t="str">
-        <v>辽宁东港</v>
+        <v/>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1531,19 +1531,19 @@
         <v>棕虎斑</v>
       </c>
       <c r="B20" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C20" t="str">
-        <v>assets/1787327967245-m62ohievcl.jpg</v>
+        <v>assets/1787388277490-e6u506cx0r.jpg</v>
       </c>
       <c r="D20" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E20" t="str">
-        <v/>
+        <v>2026-06-06</v>
       </c>
       <c r="F20" t="str">
-        <v>福建福州</v>
+        <v/>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1587,13 +1587,13 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>蓝虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B21" t="str">
         <v>弟弟</v>
       </c>
       <c r="C21" t="str">
-        <v>assets/1787327853521-js8ljh3ulj.jpg</v>
+        <v>assets/1787328436957-x30od0gw28.jpg</v>
       </c>
       <c r="D21" t="str">
         <v>是</v>
@@ -1602,7 +1602,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>上海</v>
+        <v>江苏苏州</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1646,13 +1646,13 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>纯蓝色</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B22" t="str">
         <v>弟弟</v>
       </c>
       <c r="C22" t="str">
-        <v>assets/1787327793837-znk2knoo6p.jpg</v>
+        <v>assets/1787328420967-viv9v8nbjn.jpg</v>
       </c>
       <c r="D22" t="str">
         <v>是</v>
@@ -1661,7 +1661,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>河南鹤壁</v>
+        <v>辽宁东港</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1705,13 +1705,13 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B23" t="str">
         <v>弟弟</v>
       </c>
       <c r="C23" t="str">
-        <v>assets/1787327752832-kkpmp21os3.jpg</v>
+        <v>assets/1787327967245-m62ohievcl.jpg</v>
       </c>
       <c r="D23" t="str">
         <v>是</v>
@@ -1720,7 +1720,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>陕西西安</v>
+        <v>福建福州</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1764,13 +1764,13 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B24" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C24" t="str">
-        <v>assets/1787327605711-4o2f6v6ybp.jpg</v>
+        <v>assets/1787327853521-js8ljh3ulj.jpg</v>
       </c>
       <c r="D24" t="str">
         <v>是</v>
@@ -1779,7 +1779,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>陕西西安</v>
+        <v>上海</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1823,13 +1823,13 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>银虎斑</v>
+        <v>纯蓝色</v>
       </c>
       <c r="B25" t="str">
         <v>弟弟</v>
       </c>
       <c r="C25" t="str">
-        <v>assets/1787327573762-h23cux94p2.jpg</v>
+        <v>assets/1787327793837-znk2knoo6p.jpg</v>
       </c>
       <c r="D25" t="str">
         <v>是</v>
@@ -1838,7 +1838,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>北京</v>
+        <v>河南鹤壁</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1885,10 +1885,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B26" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C26" t="str">
-        <v>assets/1787327496557-9daggljg4g.jpg</v>
+        <v>assets/1787327752832-kkpmp21os3.jpg</v>
       </c>
       <c r="D26" t="str">
         <v>是</v>
@@ -1897,7 +1897,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>黑龙江哈尔滨</v>
+        <v>陕西西安</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1941,13 +1941,13 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>烟灰色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B27" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C27" t="str">
-        <v>assets/1787327456560-p4yhq4qvrv.jpg</v>
+        <v>assets/1787327605711-4o2f6v6ybp.jpg</v>
       </c>
       <c r="D27" t="str">
         <v>是</v>
@@ -1956,7 +1956,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>甘肃嘉峪关</v>
+        <v>陕西西安</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -2000,13 +2000,13 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>蓝虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B28" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C28" t="str">
-        <v>assets/1787327421713-zg7np4yzkc.jpg</v>
+        <v>assets/1787327573762-h23cux94p2.jpg</v>
       </c>
       <c r="D28" t="str">
         <v>是</v>
@@ -2015,7 +2015,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>安徽合肥</v>
+        <v>北京</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -2062,10 +2062,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B29" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C29" t="str">
-        <v>assets/1787327337811-u5u2pdew3.jpg</v>
+        <v>assets/1787327496557-9daggljg4g.jpg</v>
       </c>
       <c r="D29" t="str">
         <v>是</v>
@@ -2074,7 +2074,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>安徽合肥</v>
+        <v>黑龙江哈尔滨</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -2118,13 +2118,13 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>棕虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B30" t="str">
         <v>弟弟</v>
       </c>
       <c r="C30" t="str">
-        <v>assets/1787327309143-6c1dan1sev.jpg</v>
+        <v>assets/1787327456560-p4yhq4qvrv.jpg</v>
       </c>
       <c r="D30" t="str">
         <v>是</v>
@@ -2133,7 +2133,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>四川成都</v>
+        <v>甘肃嘉峪关</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -2177,13 +2177,13 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B31" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C31" t="str">
-        <v>assets/1787327277453-w89ujg69fm.jpg</v>
+        <v>assets/1787327421713-zg7np4yzkc.jpg</v>
       </c>
       <c r="D31" t="str">
         <v>是</v>
@@ -2192,7 +2192,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>四川成都</v>
+        <v>安徽合肥</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -2236,13 +2236,13 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>蓝银虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B32" t="str">
         <v>弟弟</v>
       </c>
       <c r="C32" t="str">
-        <v>assets/1787327232159-lkrcl588a5.jpg</v>
+        <v>assets/1787327337811-u5u2pdew3.jpg</v>
       </c>
       <c r="D32" t="str">
         <v>是</v>
@@ -2251,7 +2251,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>四川成都</v>
+        <v>安徽合肥</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -2295,13 +2295,13 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>玳瑁色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B33" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C33" t="str">
-        <v>assets/1787327182347-3az0z7sys2.jpg</v>
+        <v>assets/1787327309143-6c1dan1sev.jpg</v>
       </c>
       <c r="D33" t="str">
         <v>是</v>
@@ -2310,7 +2310,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>四川内江</v>
+        <v>四川成都</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -2354,13 +2354,13 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>棕虎补丁</v>
+        <v>银虎斑</v>
       </c>
       <c r="B34" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C34" t="str">
-        <v>assets/1787327143756-4xtgfy5ozu.jpg</v>
+        <v>assets/1787327277453-w89ujg69fm.jpg</v>
       </c>
       <c r="D34" t="str">
         <v>是</v>
@@ -2369,7 +2369,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>贵州贵阳</v>
+        <v>四川成都</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -2413,13 +2413,13 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>黑烟色</v>
+        <v>蓝银虎斑</v>
       </c>
       <c r="B35" t="str">
         <v>弟弟</v>
       </c>
       <c r="C35" t="str">
-        <v>assets/1787327101790-tqjlseog5y.jpg</v>
+        <v>assets/1787327232159-lkrcl588a5.jpg</v>
       </c>
       <c r="D35" t="str">
         <v>是</v>
@@ -2428,7 +2428,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>浙江杭州</v>
+        <v>四川成都</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -2472,13 +2472,13 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>烟灰色</v>
+        <v>玳瑁色</v>
       </c>
       <c r="B36" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C36" t="str">
-        <v>assets/1787327019632-l1780lu2hj.jpg</v>
+        <v>assets/1787327182347-3az0z7sys2.jpg</v>
       </c>
       <c r="D36" t="str">
         <v>是</v>
@@ -2487,7 +2487,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>山东威海</v>
+        <v>四川内江</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -2537,7 +2537,7 @@
         <v>妹妹</v>
       </c>
       <c r="C37" t="str">
-        <v>assets/1787326905275-plz3fpgo97.jpg</v>
+        <v>assets/1787327143756-4xtgfy5ozu.jpg</v>
       </c>
       <c r="D37" t="str">
         <v>是</v>
@@ -2546,7 +2546,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>浙江杭州</v>
+        <v>贵州贵阳</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -2590,13 +2590,13 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>蓝虎斑</v>
+        <v>黑烟色</v>
       </c>
       <c r="B38" t="str">
         <v>弟弟</v>
       </c>
       <c r="C38" t="str">
-        <v>assets/1787326874462-z9rzs7wg17.jpg</v>
+        <v>assets/1787327101790-tqjlseog5y.jpg</v>
       </c>
       <c r="D38" t="str">
         <v>是</v>
@@ -2605,7 +2605,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>四川成都</v>
+        <v>浙江杭州</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -2649,13 +2649,13 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>凯米尔色</v>
+        <v>烟灰色</v>
       </c>
       <c r="B39" t="str">
         <v>弟弟</v>
       </c>
       <c r="C39" t="str">
-        <v>assets/1787326843271-0uhv7b9p89.jpg</v>
+        <v>assets/1787327019632-l1780lu2hj.jpg</v>
       </c>
       <c r="D39" t="str">
         <v>是</v>
@@ -2664,7 +2664,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>四川成都</v>
+        <v>山东威海</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -2708,13 +2708,13 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>凯米尔</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B40" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C40" t="str">
-        <v>assets/1787326814713-p5oavnlulg.jpg</v>
+        <v>assets/1787326905275-plz3fpgo97.jpg</v>
       </c>
       <c r="D40" t="str">
         <v>是</v>
@@ -2723,7 +2723,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>四川成都</v>
+        <v>浙江杭州</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -2767,13 +2767,13 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>棕虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B41" t="str">
         <v>弟弟</v>
       </c>
       <c r="C41" t="str">
-        <v>assets/1787326773577-13q5out2d0.jpg</v>
+        <v>assets/1787326874462-z9rzs7wg17.jpg</v>
       </c>
       <c r="D41" t="str">
         <v>是</v>
@@ -2782,7 +2782,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>四川宜宾</v>
+        <v>四川成都</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -2826,13 +2826,13 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>金棕虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B42" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C42" t="str">
-        <v>assets/1787326548993-89s929m2hg.jpg</v>
+        <v>assets/1787326843271-0uhv7b9p89.jpg</v>
       </c>
       <c r="D42" t="str">
         <v>是</v>
@@ -2841,7 +2841,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>上海</v>
+        <v>四川成都</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -2885,13 +2885,13 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>凯米尔色</v>
+        <v>凯米尔</v>
       </c>
       <c r="B43" t="str">
         <v>弟弟</v>
       </c>
       <c r="C43" t="str">
-        <v>assets/1787326449218-09s9ucram4.jpg</v>
+        <v>assets/1787326814713-p5oavnlulg.jpg</v>
       </c>
       <c r="D43" t="str">
         <v>是</v>
@@ -2900,7 +2900,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>德国</v>
+        <v>四川成都</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2944,13 +2944,13 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>棕虎补丁</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B44" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C44" t="str">
-        <v>assets/1787326277374-8ti107m5ki.jpg</v>
+        <v>assets/1787326773577-13q5out2d0.jpg</v>
       </c>
       <c r="D44" t="str">
         <v>是</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>广东深圳</v>
+        <v>四川宜宾</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -3003,13 +3003,13 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>烟灰色</v>
+        <v>金棕虎斑</v>
       </c>
       <c r="B45" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C45" t="str">
-        <v>assets/1787326236952-2pmwche4t3.jpg</v>
+        <v>assets/1787326548993-89s929m2hg.jpg</v>
       </c>
       <c r="D45" t="str">
         <v>是</v>
@@ -3018,7 +3018,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>福建泉州</v>
+        <v>上海</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -3062,13 +3062,13 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>银虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B46" t="str">
         <v>弟弟</v>
       </c>
       <c r="C46" t="str">
-        <v>assets/1787326184557-90v6clkwen.jpg</v>
+        <v>assets/1787326449218-09s9ucram4.jpg</v>
       </c>
       <c r="D46" t="str">
         <v>是</v>
@@ -3077,7 +3077,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>福建福州</v>
+        <v>德国</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -3121,13 +3121,13 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>棕虎斑</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B47" t="str">
         <v>妹妹</v>
       </c>
       <c r="C47" t="str">
-        <v>assets/1787326046155-4tk23nq4dj.jpg</v>
+        <v>assets/1787326277374-8ti107m5ki.jpg</v>
       </c>
       <c r="D47" t="str">
         <v>是</v>
@@ -3136,7 +3136,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>广西贵港</v>
+        <v>广东深圳</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -3180,13 +3180,13 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>凯米尔色</v>
+        <v>烟灰色</v>
       </c>
       <c r="B48" t="str">
         <v>弟弟</v>
       </c>
       <c r="C48" t="str">
-        <v>assets/1787325862706-wq18k3ej56.jpg</v>
+        <v>assets/1787326236952-2pmwche4t3.jpg</v>
       </c>
       <c r="D48" t="str">
         <v>是</v>
@@ -3195,7 +3195,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>江苏苏州</v>
+        <v>福建泉州</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -3239,13 +3239,13 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>凯米尔色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B49" t="str">
         <v>弟弟</v>
       </c>
       <c r="C49" t="str">
-        <v>assets/1787325743258-a7oac7hzlo.jpg</v>
+        <v>assets/1787326184557-90v6clkwen.jpg</v>
       </c>
       <c r="D49" t="str">
         <v>是</v>
@@ -3254,7 +3254,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>江苏苏州</v>
+        <v>福建福州</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -3298,13 +3298,13 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B50" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C50" t="str">
-        <v>assets/1787325706797-kgk81ghccy.jpg</v>
+        <v>assets/1787326046155-4tk23nq4dj.jpg</v>
       </c>
       <c r="D50" t="str">
         <v>是</v>
@@ -3313,7 +3313,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>北京</v>
+        <v>广西贵港</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -3357,13 +3357,13 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>蓝虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B51" t="str">
         <v>弟弟</v>
       </c>
       <c r="C51" t="str">
-        <v>assets/1787325603704-lahzgrm7fa.jpg,assets/1787325690106-wgu3spujit.jpg</v>
+        <v>assets/1787325862706-wq18k3ej56.jpg</v>
       </c>
       <c r="D51" t="str">
         <v>是</v>
@@ -3372,7 +3372,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>上海</v>
+        <v>江苏苏州</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -3416,13 +3416,13 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>棕虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B52" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C52" t="str">
-        <v>assets/1787325554341-608thexrne.jpg</v>
+        <v>assets/1787325743258-a7oac7hzlo.jpg</v>
       </c>
       <c r="D52" t="str">
         <v>是</v>
@@ -3475,13 +3475,13 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>浅色银虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B53" t="str">
         <v>弟弟</v>
       </c>
       <c r="C53" t="str">
-        <v>assets/1787325480828-q90pskoiw3.jpg</v>
+        <v>assets/1787325706797-kgk81ghccy.jpg</v>
       </c>
       <c r="D53" t="str">
         <v>是</v>
@@ -3490,7 +3490,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>四川成都</v>
+        <v>北京</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -3534,13 +3534,13 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>浅色银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B54" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C54" t="str">
-        <v>assets/1787325448999-a2pg8176fu.jpg</v>
+        <v>assets/1787325603704-lahzgrm7fa.jpg,assets/1787325690106-wgu3spujit.jpg</v>
       </c>
       <c r="D54" t="str">
         <v>是</v>
@@ -3549,7 +3549,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>中国台湾</v>
+        <v>上海</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>妹妹</v>
       </c>
       <c r="C55" t="str">
-        <v>assets/1787325357634-k55zlfhmqj.jpg</v>
+        <v>assets/1787325554341-608thexrne.jpg</v>
       </c>
       <c r="D55" t="str">
         <v>是</v>
@@ -3608,7 +3608,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>浙江杭州</v>
+        <v>江苏苏州</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -3652,13 +3652,13 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>烟灰色</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B56" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C56" t="str">
-        <v>assets/1787325237876-t19isaq5gu.jpg</v>
+        <v>assets/1787325480828-q90pskoiw3.jpg</v>
       </c>
       <c r="D56" t="str">
         <v>是</v>
@@ -3667,7 +3667,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>辽宁沈阳</v>
+        <v>四川成都</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -3711,13 +3711,13 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>金棕虎斑</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B57" t="str">
         <v>妹妹</v>
       </c>
       <c r="C57" t="str">
-        <v>assets/1787325199931-e7wms9qtya.jpg</v>
+        <v>assets/1787325448999-a2pg8176fu.jpg</v>
       </c>
       <c r="D57" t="str">
         <v>是</v>
@@ -3726,7 +3726,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>四川成都</v>
+        <v>中国台湾</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -3770,13 +3770,13 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B58" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C58" t="str">
-        <v>assets/1787325172354-4sa8uzaey2.jpg</v>
+        <v>assets/1787325357634-k55zlfhmqj.jpg</v>
       </c>
       <c r="D58" t="str">
         <v>是</v>
@@ -3785,7 +3785,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>中国香港</v>
+        <v>浙江杭州</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -3832,10 +3832,10 @@
         <v>烟灰色</v>
       </c>
       <c r="B59" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C59" t="str">
-        <v>assets/1787325109283-y7mvkk6qg4.jpg</v>
+        <v>assets/1787325237876-t19isaq5gu.jpg</v>
       </c>
       <c r="D59" t="str">
         <v>是</v>
@@ -3844,7 +3844,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>中国澳门</v>
+        <v>辽宁沈阳</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -3888,13 +3888,13 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>蓝虎斑</v>
+        <v>金棕虎斑</v>
       </c>
       <c r="B60" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C60" t="str">
-        <v>assets/1787325033629-y3ygps3zaj.jpg</v>
+        <v>assets/1787325199931-e7wms9qtya.jpg</v>
       </c>
       <c r="D60" t="str">
         <v>是</v>
@@ -3903,7 +3903,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>山东青岛</v>
+        <v>四川成都</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -3947,13 +3947,13 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>烟灰色</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B61" t="str">
         <v>弟弟</v>
       </c>
       <c r="C61" t="str">
-        <v>assets/1787324954998-w5m5jox439.jpg</v>
+        <v>assets/1787325172354-4sa8uzaey2.jpg</v>
       </c>
       <c r="D61" t="str">
         <v>是</v>
@@ -3962,7 +3962,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>海南海口</v>
+        <v>中国香港</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -4006,13 +4006,13 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>棕虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B62" t="str">
         <v>弟弟</v>
       </c>
       <c r="C62" t="str">
-        <v>assets/1787324905909-zrz8o79kdf.jpg</v>
+        <v>assets/1787325109283-y7mvkk6qg4.jpg</v>
       </c>
       <c r="D62" t="str">
         <v>是</v>
@@ -4021,7 +4021,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>内蒙古</v>
+        <v>中国澳门</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -4065,13 +4065,13 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>烟灰色</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B63" t="str">
         <v>弟弟</v>
       </c>
       <c r="C63" t="str">
-        <v>assets/1787324880505-gbh0sn7b6j.jpg</v>
+        <v>assets/1787325033629-y3ygps3zaj.jpg</v>
       </c>
       <c r="D63" t="str">
         <v>是</v>
@@ -4080,7 +4080,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>中国香港</v>
+        <v>山东青岛</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -4130,7 +4130,7 @@
         <v>弟弟</v>
       </c>
       <c r="C64" t="str">
-        <v>assets/1787324806613-31yyz14tsf.jpg</v>
+        <v>assets/1787324954998-w5m5jox439.jpg</v>
       </c>
       <c r="D64" t="str">
         <v>是</v>
@@ -4139,7 +4139,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>四川成都</v>
+        <v>海南海口</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -4183,13 +4183,13 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>红虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B65" t="str">
         <v>弟弟</v>
       </c>
       <c r="C65" t="str">
-        <v>assets/1787324789658-uz6ephkdsh.jpg</v>
+        <v>assets/1787324905909-zrz8o79kdf.jpg</v>
       </c>
       <c r="D65" t="str">
         <v>是</v>
@@ -4198,7 +4198,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>湖北武汉</v>
+        <v>内蒙古</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -4248,7 +4248,7 @@
         <v>弟弟</v>
       </c>
       <c r="C66" t="str">
-        <v>assets/1787324522658-smn44crast.jpg</v>
+        <v>assets/1787324880505-gbh0sn7b6j.jpg</v>
       </c>
       <c r="D66" t="str">
         <v>是</v>
@@ -4257,7 +4257,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>湖北武汉</v>
+        <v>中国香港</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -4301,13 +4301,13 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>棕虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B67" t="str">
         <v>弟弟</v>
       </c>
       <c r="C67" t="str">
-        <v>assets/1787324365608-6xtrjp7euz.jpg</v>
+        <v>assets/1787324806613-31yyz14tsf.jpg</v>
       </c>
       <c r="D67" t="str">
         <v>是</v>
@@ -4316,7 +4316,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>新疆</v>
+        <v>四川成都</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -4360,13 +4360,13 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>浅凯米尔</v>
+        <v>红虎斑</v>
       </c>
       <c r="B68" t="str">
         <v>弟弟</v>
       </c>
       <c r="C68" t="str">
-        <v>assets/1787324331029-d74lcuycf6.jpg</v>
+        <v>assets/1787324789658-uz6ephkdsh.jpg</v>
       </c>
       <c r="D68" t="str">
         <v>是</v>
@@ -4375,7 +4375,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>四川成都</v>
+        <v>湖北武汉</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -4419,13 +4419,13 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>红虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B69" t="str">
         <v>弟弟</v>
       </c>
       <c r="C69" t="str">
-        <v>assets/1787324297469-ans1lse2l5.jpg</v>
+        <v>assets/1787324522658-smn44crast.jpg</v>
       </c>
       <c r="D69" t="str">
         <v>是</v>
@@ -4434,7 +4434,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>四川乐山</v>
+        <v>湖北武汉</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -4478,13 +4478,13 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>红虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B70" t="str">
         <v>弟弟</v>
       </c>
       <c r="C70" t="str">
-        <v>assets/1787324256827-7w383z4bg1.jpg</v>
+        <v>assets/1787324365608-6xtrjp7euz.jpg</v>
       </c>
       <c r="D70" t="str">
         <v>是</v>
@@ -4493,7 +4493,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>中国台湾</v>
+        <v>新疆</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -4537,13 +4537,13 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>银虎斑</v>
+        <v>浅凯米尔</v>
       </c>
       <c r="B71" t="str">
         <v>弟弟</v>
       </c>
       <c r="C71" t="str">
-        <v>assets/1787324228262-y3vwn6i4zk.jpg</v>
+        <v>assets/1787324331029-d74lcuycf6.jpg</v>
       </c>
       <c r="D71" t="str">
         <v>是</v>
@@ -4596,13 +4596,13 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>凯米尔色</v>
+        <v>红虎斑</v>
       </c>
       <c r="B72" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C72" t="str">
-        <v>assets/1787324201418-9tk4ik75mo.jpg</v>
+        <v>assets/1787324297469-ans1lse2l5.jpg</v>
       </c>
       <c r="D72" t="str">
         <v>是</v>
@@ -4611,7 +4611,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>江苏南京</v>
+        <v>四川乐山</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -4655,13 +4655,13 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>棕虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B73" t="str">
         <v>弟弟</v>
       </c>
       <c r="C73" t="str">
-        <v>assets/1787324092513-jpa2rmkci2.jpg</v>
+        <v>assets/1787324256827-7w383z4bg1.jpg</v>
       </c>
       <c r="D73" t="str">
         <v>是</v>
@@ -4670,7 +4670,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>江苏南京</v>
+        <v>中国台湾</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -4720,7 +4720,7 @@
         <v>弟弟</v>
       </c>
       <c r="C74" t="str">
-        <v>assets/1787323318612-soge38hpsf.jpg</v>
+        <v>assets/1787324228262-y3vwn6i4zk.jpg</v>
       </c>
       <c r="D74" t="str">
         <v>是</v>
@@ -4729,7 +4729,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>上海</v>
+        <v>四川成都</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -4773,13 +4773,13 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>棕虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B75" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C75" t="str">
-        <v>assets/1787323235892-7yq8ioq01e.jpg</v>
+        <v>assets/1787324201418-9tk4ik75mo.jpg</v>
       </c>
       <c r="D75" t="str">
         <v>是</v>
@@ -4788,7 +4788,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>四川成都</v>
+        <v>江苏南京</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -4832,13 +4832,13 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B76" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C76" t="str">
-        <v>assets/1787322988096-6e2f54q7vo.jpg</v>
+        <v>assets/1787324092513-jpa2rmkci2.jpg</v>
       </c>
       <c r="D76" t="str">
         <v>是</v>
@@ -4847,7 +4847,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>浙江宁波</v>
+        <v>江苏南京</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -4891,13 +4891,13 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>银虎斑补丁</v>
+        <v>银虎斑</v>
       </c>
       <c r="B77" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C77" t="str">
-        <v>assets/1787322938518-85ev8bs2k5.jpg</v>
+        <v>assets/1787323318612-soge38hpsf.jpg</v>
       </c>
       <c r="D77" t="str">
         <v>是</v>
@@ -4906,7 +4906,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>马来西亚</v>
+        <v>上海</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -4950,13 +4950,13 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B78" t="str">
         <v>弟弟</v>
       </c>
       <c r="C78" t="str">
-        <v>assets/1787322881183-tzu9xtw2sg.jpg</v>
+        <v>assets/1787323235892-7yq8ioq01e.jpg</v>
       </c>
       <c r="D78" t="str">
         <v>是</v>
@@ -4965,7 +4965,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>陕西西安</v>
+        <v>四川成都</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -5009,13 +5009,13 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>纯黑色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B79" t="str">
         <v>妹妹</v>
       </c>
       <c r="C79" t="str">
-        <v>assets/1787322840098-nhy4jjyx7k.jpg</v>
+        <v>assets/1787322988096-6e2f54q7vo.jpg</v>
       </c>
       <c r="D79" t="str">
         <v>是</v>
@@ -5024,7 +5024,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>广西南宁</v>
+        <v>浙江宁波</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -5068,13 +5068,13 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B80" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C80" t="str">
-        <v>assets/1787322760950-gn3qgego4s.jpg</v>
+        <v>assets/1787322938518-85ev8bs2k5.jpg</v>
       </c>
       <c r="D80" t="str">
         <v>是</v>
@@ -5083,7 +5083,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>广西南宁</v>
+        <v>马来西亚</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -5127,13 +5127,13 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>红虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B81" t="str">
         <v>弟弟</v>
       </c>
       <c r="C81" t="str">
-        <v>assets/1787322605982-04n50xegt2.jpg</v>
+        <v>assets/1787322881183-tzu9xtw2sg.jpg</v>
       </c>
       <c r="D81" t="str">
         <v>是</v>
@@ -5142,7 +5142,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>上海</v>
+        <v>陕西西安</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -5186,13 +5186,13 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>蓝虎斑</v>
+        <v>纯黑色</v>
       </c>
       <c r="B82" t="str">
         <v>妹妹</v>
       </c>
       <c r="C82" t="str">
-        <v>assets/1787322490045-kog3ru43dy.jpg</v>
+        <v>assets/1787322840098-nhy4jjyx7k.jpg</v>
       </c>
       <c r="D82" t="str">
         <v>是</v>
@@ -5201,7 +5201,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>上海</v>
+        <v>广西南宁</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -5245,13 +5245,13 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>红虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B83" t="str">
         <v>弟弟</v>
       </c>
       <c r="C83" t="str">
-        <v>assets/1787322419996-0m33yx89nm.jpg</v>
+        <v>assets/1787322760950-gn3qgego4s.jpg</v>
       </c>
       <c r="D83" t="str">
         <v>是</v>
@@ -5260,7 +5260,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>广东广州</v>
+        <v>广西南宁</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -5304,13 +5304,13 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>浅色银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B84" t="str">
         <v>弟弟</v>
       </c>
       <c r="C84" t="str">
-        <v>assets/1787322377730-vj5csj2mll.jpg</v>
+        <v>assets/1787322605982-04n50xegt2.jpg</v>
       </c>
       <c r="D84" t="str">
         <v>是</v>
@@ -5319,7 +5319,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>柬埔寨</v>
+        <v>上海</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -5366,10 +5366,10 @@
         <v>蓝虎斑</v>
       </c>
       <c r="B85" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C85" t="str">
-        <v>assets/1787322269611-53yaj5ideu.jpg</v>
+        <v>assets/1787322490045-kog3ru43dy.jpg</v>
       </c>
       <c r="D85" t="str">
         <v>是</v>
@@ -5378,7 +5378,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>山东枣庄</v>
+        <v>上海</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -5422,13 +5422,13 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B86" t="str">
         <v>弟弟</v>
       </c>
       <c r="C86" t="str">
-        <v>assets/1787321989528-7d6liuhuk9.jpg</v>
+        <v>assets/1787322419996-0m33yx89nm.jpg</v>
       </c>
       <c r="D86" t="str">
         <v>是</v>
@@ -5437,7 +5437,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>陕西西安</v>
+        <v>广东广州</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -5481,13 +5481,13 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>银虎斑</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B87" t="str">
         <v>弟弟</v>
       </c>
       <c r="C87" t="str">
-        <v>assets/1787321941642-xlrc1no2ua.jpg</v>
+        <v>assets/1787322377730-vj5csj2mll.jpg</v>
       </c>
       <c r="D87" t="str">
         <v>是</v>
@@ -5496,7 +5496,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>山东东营</v>
+        <v>柬埔寨</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -5540,13 +5540,13 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>凯米尔色</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B88" t="str">
         <v>弟弟</v>
       </c>
       <c r="C88" t="str">
-        <v>assets/1787321903535-6orj7qcgzn.jpg</v>
+        <v>assets/1787322269611-53yaj5ideu.jpg</v>
       </c>
       <c r="D88" t="str">
         <v>是</v>
@@ -5555,7 +5555,7 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>中国台湾</v>
+        <v>山东枣庄</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -5599,13 +5599,13 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>烟灰色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B89" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C89" t="str">
-        <v>assets/1787321858985-v4qej7cq7g.jpg</v>
+        <v>assets/1787321989528-7d6liuhuk9.jpg</v>
       </c>
       <c r="D89" t="str">
         <v>是</v>
@@ -5614,7 +5614,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>中国台湾</v>
+        <v>陕西西安</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -5664,7 +5664,7 @@
         <v>弟弟</v>
       </c>
       <c r="C90" t="str">
-        <v>assets/1787321834306-efgnyhujon.jpg</v>
+        <v>assets/1787321941642-xlrc1no2ua.jpg</v>
       </c>
       <c r="D90" t="str">
         <v>是</v>
@@ -5673,7 +5673,7 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>北京</v>
+        <v>山东东营</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -5717,13 +5717,13 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>银虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B91" t="str">
         <v>弟弟</v>
       </c>
       <c r="C91" t="str">
-        <v>assets/1787321439916-uttgpbkogb.jpg</v>
+        <v>assets/1787321903535-6orj7qcgzn.jpg</v>
       </c>
       <c r="D91" t="str">
         <v>是</v>
@@ -5732,7 +5732,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>安徽合肥</v>
+        <v>中国台湾</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -5776,13 +5776,13 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B92" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C92" t="str">
-        <v>assets/1787321419210-51hhgurygq.jpg</v>
+        <v>assets/1787321858985-v4qej7cq7g.jpg</v>
       </c>
       <c r="D92" t="str">
         <v>是</v>
@@ -5791,7 +5791,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>上海</v>
+        <v>中国台湾</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -5835,13 +5835,13 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>凯米尔色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B93" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C93" t="str">
-        <v>assets/1787321363369-bzjn51j5il.jpg</v>
+        <v>assets/1787321834306-efgnyhujon.jpg</v>
       </c>
       <c r="D93" t="str">
         <v>是</v>
@@ -5850,7 +5850,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>中国台湾</v>
+        <v>北京</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -5894,13 +5894,13 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B94" t="str">
         <v>弟弟</v>
       </c>
       <c r="C94" t="str">
-        <v>assets/1787321332559-87p6spuch3.jpg</v>
+        <v>assets/1787321439916-uttgpbkogb.jpg</v>
       </c>
       <c r="D94" t="str">
         <v>是</v>
@@ -5909,7 +5909,7 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>中国台湾</v>
+        <v>安徽合肥</v>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -5953,13 +5953,13 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B95" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C95" t="str">
-        <v>assets/1787321232531-59lnzv8y98.jpg</v>
+        <v>assets/1787321419210-51hhgurygq.jpg</v>
       </c>
       <c r="D95" t="str">
         <v>是</v>
@@ -5968,7 +5968,7 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>北京</v>
+        <v>上海</v>
       </c>
       <c r="G95" t="str">
         <v/>
@@ -6012,13 +6012,13 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>银虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B96" t="str">
         <v>妹妹</v>
       </c>
       <c r="C96" t="str">
-        <v>assets/1787319975814-g1pfa56vfp.jpg</v>
+        <v>assets/1787321363369-bzjn51j5il.jpg</v>
       </c>
       <c r="D96" t="str">
         <v>是</v>
@@ -6027,7 +6027,7 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>浙江宁波</v>
+        <v>中国台湾</v>
       </c>
       <c r="G96" t="str">
         <v/>
@@ -6071,13 +6071,13 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B97" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C97" t="str">
-        <v>assets/1787319800704-v3qeu062ak.jpg</v>
+        <v>assets/1787321332559-87p6spuch3.jpg</v>
       </c>
       <c r="D97" t="str">
         <v>是</v>
@@ -6086,7 +6086,7 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>河北唐山</v>
+        <v>中国台湾</v>
       </c>
       <c r="G97" t="str">
         <v/>
@@ -6130,13 +6130,13 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B98" t="str">
         <v>妹妹</v>
       </c>
       <c r="C98" t="str">
-        <v>assets/1787319745369-zn66xr3bvb.jpg</v>
+        <v>assets/1787321232531-59lnzv8y98.jpg</v>
       </c>
       <c r="D98" t="str">
         <v>是</v>
@@ -6145,7 +6145,7 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>河北石家庄</v>
+        <v>北京</v>
       </c>
       <c r="G98" t="str">
         <v/>
@@ -6189,13 +6189,13 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>棕虎补丁</v>
+        <v>银虎斑</v>
       </c>
       <c r="B99" t="str">
         <v>妹妹</v>
       </c>
       <c r="C99" t="str">
-        <v>assets/1787319547969-zqlq35fxxt.jpg</v>
+        <v>assets/1787319975814-g1pfa56vfp.jpg</v>
       </c>
       <c r="D99" t="str">
         <v>是</v>
@@ -6204,7 +6204,7 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>韩国</v>
+        <v>浙江宁波</v>
       </c>
       <c r="G99" t="str">
         <v/>
@@ -6248,13 +6248,13 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>蓝银虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B100" t="str">
         <v>妹妹</v>
       </c>
       <c r="C100" t="str">
-        <v>assets/1787319501376-xscwljnu1j.jpg</v>
+        <v>assets/1787319800704-v3qeu062ak.jpg</v>
       </c>
       <c r="D100" t="str">
         <v>是</v>
@@ -6263,7 +6263,7 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>美国</v>
+        <v>河北唐山</v>
       </c>
       <c r="G100" t="str">
         <v/>
@@ -6307,13 +6307,13 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B101" t="str">
         <v>妹妹</v>
       </c>
       <c r="C101" t="str">
-        <v>assets/1787319443529-4a0zqikufx.jpg</v>
+        <v>assets/1787319745369-zn66xr3bvb.jpg</v>
       </c>
       <c r="D101" t="str">
         <v>是</v>
@@ -6322,7 +6322,7 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>中国台湾</v>
+        <v>河北石家庄</v>
       </c>
       <c r="G101" t="str">
         <v/>
@@ -6366,13 +6366,13 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B102" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C102" t="str">
-        <v>assets/1787319356194-lr2d5680i9.jpg</v>
+        <v>assets/1787319547969-zqlq35fxxt.jpg</v>
       </c>
       <c r="D102" t="str">
         <v>是</v>
@@ -6381,7 +6381,7 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>中国台湾</v>
+        <v>韩国</v>
       </c>
       <c r="G102" t="str">
         <v/>
@@ -6425,13 +6425,13 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>棕虎斑</v>
+        <v>蓝银虎斑</v>
       </c>
       <c r="B103" t="str">
         <v>妹妹</v>
       </c>
       <c r="C103" t="str">
-        <v>assets/1787319208828-aizqo4blcv.jpg</v>
+        <v>assets/1787319501376-xscwljnu1j.jpg</v>
       </c>
       <c r="D103" t="str">
         <v>是</v>
@@ -6440,7 +6440,7 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>山东淄博</v>
+        <v>美国</v>
       </c>
       <c r="G103" t="str">
         <v/>
@@ -6484,13 +6484,13 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B104" t="str">
         <v>妹妹</v>
       </c>
       <c r="C104" t="str">
-        <v>assets/1787319162970-cc2v8ovnni.jpg</v>
+        <v>assets/1787319443529-4a0zqikufx.jpg</v>
       </c>
       <c r="D104" t="str">
         <v>是</v>
@@ -6499,7 +6499,7 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>韩国</v>
+        <v>中国台湾</v>
       </c>
       <c r="G104" t="str">
         <v/>
@@ -6543,13 +6543,13 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>棕虎补丁</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B105" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C105" t="str">
-        <v>assets/1787319098214-8pwa9yx2wc.jpg</v>
+        <v>assets/1787319356194-lr2d5680i9.jpg</v>
       </c>
       <c r="D105" t="str">
         <v>是</v>
@@ -6558,7 +6558,7 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>四川成都</v>
+        <v>中国台湾</v>
       </c>
       <c r="G105" t="str">
         <v/>
@@ -6602,13 +6602,13 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B106" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C106" t="str">
-        <v>assets/1787318867999-3gxdddp72x.jpg</v>
+        <v>assets/1787319208828-aizqo4blcv.jpg</v>
       </c>
       <c r="D106" t="str">
         <v>是</v>
@@ -6617,7 +6617,7 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>广东广州</v>
+        <v>山东淄博</v>
       </c>
       <c r="G106" t="str">
         <v/>
@@ -6664,10 +6664,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B107" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C107" t="str">
-        <v>assets/1787318609722-0ojb3aikwi.jpg</v>
+        <v>assets/1787319162970-cc2v8ovnni.jpg</v>
       </c>
       <c r="D107" t="str">
         <v>是</v>
@@ -6676,7 +6676,7 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>黑龙江鹤岗</v>
+        <v>韩国</v>
       </c>
       <c r="G107" t="str">
         <v/>
@@ -6720,13 +6720,13 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B108" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C108" t="str">
-        <v>assets/1787318530612-779fbkfcoi.jpg</v>
+        <v>assets/1787319098214-8pwa9yx2wc.jpg</v>
       </c>
       <c r="D108" t="str">
         <v>是</v>
@@ -6735,7 +6735,7 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>天津</v>
+        <v>四川成都</v>
       </c>
       <c r="G108" t="str">
         <v/>
@@ -6785,7 +6785,7 @@
         <v>弟弟</v>
       </c>
       <c r="C109" t="str">
-        <v>assets/1787318365475-sj87wtsai3.jpg</v>
+        <v>assets/1787318867999-3gxdddp72x.jpg</v>
       </c>
       <c r="D109" t="str">
         <v>是</v>
@@ -6794,7 +6794,7 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>山西朔州</v>
+        <v>广东广州</v>
       </c>
       <c r="G109" t="str">
         <v/>
@@ -6824,7 +6824,7 @@
         <v/>
       </c>
       <c r="P109" t="str">
-        <v>已接猫</v>
+        <v/>
       </c>
       <c r="Q109" t="str">
         <v/>
@@ -6841,10 +6841,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B110" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C110" t="str">
-        <v>assets/1787318326155-ia4noopjhq.jpg</v>
+        <v>assets/1787318609722-0ojb3aikwi.jpg</v>
       </c>
       <c r="D110" t="str">
         <v>是</v>
@@ -6853,7 +6853,7 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>贵州</v>
+        <v>黑龙江鹤岗</v>
       </c>
       <c r="G110" t="str">
         <v/>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>棕虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B111" t="str">
         <v>弟弟</v>
       </c>
       <c r="C111" t="str">
-        <v>assets/1787304479674-w0trechn4p.jpg</v>
+        <v>assets/1787318530612-779fbkfcoi.jpg</v>
       </c>
       <c r="D111" t="str">
         <v>是</v>
       </c>
       <c r="E111" t="str">
-        <v>2026-06-06</v>
+        <v/>
       </c>
       <c r="F111" t="str">
-        <v>北京</v>
+        <v>天津</v>
       </c>
       <c r="G111" t="str">
         <v/>
@@ -6951,27 +6951,27 @@
         <v/>
       </c>
       <c r="S111" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>纯黑色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B112" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C112" t="str">
-        <v>assets/1787283819124-4v7d1w01la.jpg</v>
+        <v>assets/1787318365475-sj87wtsai3.jpg</v>
       </c>
       <c r="D112" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E112" t="str">
-        <v>2026-02-20</v>
+        <v/>
       </c>
       <c r="F112" t="str">
-        <v/>
+        <v>山西朔州</v>
       </c>
       <c r="G112" t="str">
         <v/>
@@ -7001,7 +7001,7 @@
         <v/>
       </c>
       <c r="P112" t="str">
-        <v/>
+        <v>已接猫</v>
       </c>
       <c r="Q112" t="str">
         <v/>
@@ -7010,27 +7010,27 @@
         <v/>
       </c>
       <c r="S112" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>阴影色NS12</v>
+        <v>银虎斑</v>
       </c>
       <c r="B113" t="str">
         <v>妹妹</v>
       </c>
       <c r="C113" t="str">
-        <v>assets/1787283212708-jdnyi6ecci.jpg</v>
+        <v>assets/1787318326155-ia4noopjhq.jpg</v>
       </c>
       <c r="D113" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E113" t="str">
-        <v>2026-05-28</v>
+        <v/>
       </c>
       <c r="F113" t="str">
-        <v/>
+        <v>贵州</v>
       </c>
       <c r="G113" t="str">
         <v/>
@@ -7069,27 +7069,27 @@
         <v/>
       </c>
       <c r="S113" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>阴影色NS11</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B114" t="str">
         <v>弟弟</v>
       </c>
       <c r="C114" t="str">
-        <v>assets/1787283153501-s2tjg9spwu.jpg</v>
+        <v>assets/1787304479674-w0trechn4p.jpg</v>
       </c>
       <c r="D114" t="str">
         <v>是</v>
       </c>
       <c r="E114" t="str">
-        <v>2026-06-15</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F114" t="str">
-        <v>重庆</v>
+        <v>北京</v>
       </c>
       <c r="G114" t="str">
         <v/>
@@ -7133,19 +7133,19 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>浅烟灰色</v>
+        <v>纯黑色</v>
       </c>
       <c r="B115" t="str">
         <v>妹妹</v>
       </c>
       <c r="C115" t="str">
-        <v>assets/1787283092677-i4d8tyrjtf.jpg</v>
+        <v>assets/1787283819124-4v7d1w01la.jpg</v>
       </c>
       <c r="D115" t="str">
         <v>否</v>
       </c>
       <c r="E115" t="str">
-        <v>2026-03-21</v>
+        <v>2026-02-20</v>
       </c>
       <c r="F115" t="str">
         <v/>
@@ -7192,19 +7192,19 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>棕虎斑</v>
+        <v>阴影色NS12</v>
       </c>
       <c r="B116" t="str">
         <v>妹妹</v>
       </c>
       <c r="C116" t="str">
-        <v>assets/1787283031104-bpyq9wy2tl.jpg</v>
+        <v>assets/1787283212708-jdnyi6ecci.jpg</v>
       </c>
       <c r="D116" t="str">
         <v>否</v>
       </c>
       <c r="E116" t="str">
-        <v>2026-06-06</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F116" t="str">
         <v/>
@@ -7251,22 +7251,22 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>棕虎斑</v>
+        <v>阴影色NS11</v>
       </c>
       <c r="B117" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C117" t="str">
-        <v>assets/1787282991501-2fjfws0rqw.jpg</v>
+        <v>assets/1787283153501-s2tjg9spwu.jpg</v>
       </c>
       <c r="D117" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E117" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F117" t="str">
-        <v/>
+        <v>重庆</v>
       </c>
       <c r="G117" t="str">
         <v/>
@@ -7310,19 +7310,19 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>棕虎斑</v>
+        <v>浅烟灰色</v>
       </c>
       <c r="B118" t="str">
         <v>妹妹</v>
       </c>
       <c r="C118" t="str">
-        <v>assets/1787282942262-syr48fym6c.jpg</v>
+        <v>assets/1787283092677-i4d8tyrjtf.jpg</v>
       </c>
       <c r="D118" t="str">
         <v>否</v>
       </c>
       <c r="E118" t="str">
-        <v>2026-06-15</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F118" t="str">
         <v/>
@@ -7372,19 +7372,19 @@
         <v>棕虎斑</v>
       </c>
       <c r="B119" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C119" t="str">
-        <v>assets/1787282819855-7vhx3m0v40.jpg</v>
+        <v>assets/1787283031104-bpyq9wy2tl.jpg</v>
       </c>
       <c r="D119" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E119" t="str">
         <v>2026-06-06</v>
       </c>
       <c r="F119" t="str">
-        <v>北京</v>
+        <v/>
       </c>
       <c r="G119" t="str">
         <v/>
@@ -7434,7 +7434,7 @@
         <v>妹妹</v>
       </c>
       <c r="C120" t="str">
-        <v>assets/1787282703381-2uakw592b4.jpg</v>
+        <v>assets/1787282991501-2fjfws0rqw.jpg</v>
       </c>
       <c r="D120" t="str">
         <v>否</v>
@@ -7487,19 +7487,19 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B121" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C121" t="str">
-        <v>assets/1787282649397-9hc31ncrpc.jpg</v>
+        <v>assets/1787282942262-syr48fym6c.jpg</v>
       </c>
       <c r="D121" t="str">
         <v>否</v>
       </c>
       <c r="E121" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F121" t="str">
         <v/>
@@ -7546,22 +7546,22 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B122" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C122" t="str">
-        <v>assets/1787282617957-svcoyyznpg.jpg</v>
+        <v>assets/1787282819855-7vhx3m0v40.jpg</v>
       </c>
       <c r="D122" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E122" t="str">
         <v>2026-06-06</v>
       </c>
       <c r="F122" t="str">
-        <v/>
+        <v>北京</v>
       </c>
       <c r="G122" t="str">
         <v/>
@@ -7605,13 +7605,13 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B123" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C123" t="str">
-        <v>assets/1787282419632-78nixqjzua.jpg</v>
+        <v>assets/1787282703381-2uakw592b4.jpg</v>
       </c>
       <c r="D123" t="str">
         <v>否</v>
@@ -7664,19 +7664,19 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>纯黑色</v>
+        <v>烟灰色</v>
       </c>
       <c r="B124" t="str">
         <v>弟弟</v>
       </c>
       <c r="C124" t="str">
-        <v>assets/1787282349942-2cfuyn7xlc.jpg</v>
+        <v>assets/1787282649397-9hc31ncrpc.jpg</v>
       </c>
       <c r="D124" t="str">
         <v>否</v>
       </c>
       <c r="E124" t="str">
-        <v>2026-03-21</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F124" t="str">
         <v/>
@@ -7723,19 +7723,19 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B125" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C125" t="str">
-        <v>assets/1787282064159-6b4z8c5msd.jpg</v>
+        <v>assets/1787282617957-svcoyyznpg.jpg</v>
       </c>
       <c r="D125" t="str">
         <v>否</v>
       </c>
       <c r="E125" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F125" t="str">
         <v/>
@@ -7782,19 +7782,19 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>阴影色NS11</v>
+        <v>烟灰色</v>
       </c>
       <c r="B126" t="str">
         <v>弟弟</v>
       </c>
       <c r="C126" t="str">
-        <v>assets/1787280590041-vzcwebdok1.jpg</v>
+        <v>assets/1787282419632-78nixqjzua.jpg</v>
       </c>
       <c r="D126" t="str">
         <v>否</v>
       </c>
       <c r="E126" t="str">
-        <v>2026-05-28</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F126" t="str">
         <v/>
@@ -7841,19 +7841,19 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>浅色银虎斑</v>
+        <v>纯黑色</v>
       </c>
       <c r="B127" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C127" t="str">
-        <v>assets/1787281786169-9ia0h837ct.jpg</v>
+        <v>assets/1787282349942-2cfuyn7xlc.jpg</v>
       </c>
       <c r="D127" t="str">
         <v>否</v>
       </c>
       <c r="E127" t="str">
-        <v>2026-06-15</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F127" t="str">
         <v/>
@@ -7900,22 +7900,22 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>浅烟灰色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B128" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C128" t="str">
-        <v>assets/1785843720843-63qz159daui.jpg</v>
+        <v>assets/1787282064159-6b4z8c5msd.jpg</v>
       </c>
       <c r="D128" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E128" t="str">
-        <v>2026-03-21</v>
+        <v>2026-06-10</v>
       </c>
       <c r="F128" t="str">
-        <v>四川成都</v>
+        <v/>
       </c>
       <c r="G128" t="str">
         <v/>
@@ -7959,22 +7959,22 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>凯米尔色</v>
+        <v>阴影色NS11</v>
       </c>
       <c r="B129" t="str">
         <v>弟弟</v>
       </c>
       <c r="C129" t="str">
-        <v>assets/1787301984056-iu6afro5z5.jpg, assets/1785843763310-elg05ur61ri.jpg</v>
+        <v>assets/1787280590041-vzcwebdok1.jpg</v>
       </c>
       <c r="D129" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E129" t="str">
-        <v>2026-02-14</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F129" t="str">
-        <v>上海浦东</v>
+        <v/>
       </c>
       <c r="G129" t="str">
         <v/>
@@ -8018,19 +8018,19 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>银虎斑补丁</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B130" t="str">
         <v>妹妹</v>
       </c>
       <c r="C130" t="str">
-        <v>assets/1785843820715-9kz7gy4mbr7.jpg</v>
+        <v>assets/1787281786169-9ia0h837ct.jpg</v>
       </c>
       <c r="D130" t="str">
         <v>否</v>
       </c>
       <c r="E130" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F130" t="str">
         <v/>
@@ -8077,22 +8077,22 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>烟灰色</v>
+        <v>浅烟灰色</v>
       </c>
       <c r="B131" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C131" t="str">
-        <v>assets/1785843953805-mxl3x1982io.jpg</v>
+        <v>assets/1785843720843-63qz159daui.jpg</v>
       </c>
       <c r="D131" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E131" t="str">
-        <v>2026-05-18</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F131" t="str">
-        <v/>
+        <v>四川成都</v>
       </c>
       <c r="G131" t="str">
         <v/>
@@ -8136,22 +8136,22 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>棕虎斑玳瑁</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B132" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C132" t="str">
-        <v>assets/1785844013835-ek4xpcje7kh.jpg</v>
+        <v>assets/1787301984056-iu6afro5z5.jpg, assets/1785843763310-elg05ur61ri.jpg</v>
       </c>
       <c r="D132" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E132" t="str">
         <v>2026-02-14</v>
       </c>
       <c r="F132" t="str">
-        <v/>
+        <v>上海浦东</v>
       </c>
       <c r="G132" t="str">
         <v/>
@@ -8201,13 +8201,13 @@
         <v>妹妹</v>
       </c>
       <c r="C133" t="str">
-        <v>assets/1785844434338-ek5zbdgdcne.jpg</v>
+        <v>assets/1785843820715-9kz7gy4mbr7.jpg</v>
       </c>
       <c r="D133" t="str">
         <v>否</v>
       </c>
       <c r="E133" t="str">
-        <v>2026-05-24</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F133" t="str">
         <v/>
@@ -8254,22 +8254,22 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B134" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C134" t="str">
-        <v>assets/1785838787730-s5f333sc3u.jpg</v>
+        <v>assets/1785843953805-mxl3x1982io.jpg</v>
       </c>
       <c r="D134" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E134" t="str">
-        <v>2026-06-05</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F134" t="str">
-        <v>湖北恩施</v>
+        <v/>
       </c>
       <c r="G134" t="str">
         <v/>
@@ -8313,22 +8313,22 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑玳瑁</v>
       </c>
       <c r="B135" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C135" t="str">
-        <v>assets/1785842296661-6qw3zs3as8h.jpg</v>
+        <v>assets/1785844013835-ek4xpcje7kh.jpg</v>
       </c>
       <c r="D135" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E135" t="str">
-        <v>2026-06-05</v>
+        <v>2026-02-14</v>
       </c>
       <c r="F135" t="str">
-        <v>湖北恩施</v>
+        <v/>
       </c>
       <c r="G135" t="str">
         <v/>
@@ -8372,22 +8372,22 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>银虎斑</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B136" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C136" t="str">
-        <v>assets/1785842429109-porc98rel5.jpg</v>
+        <v>assets/1785844434338-ek5zbdgdcne.jpg</v>
       </c>
       <c r="D136" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E136" t="str">
-        <v>2025-11-05</v>
+        <v>2026-05-24</v>
       </c>
       <c r="F136" t="str">
-        <v>韩国</v>
+        <v/>
       </c>
       <c r="G136" t="str">
         <v/>
@@ -8437,16 +8437,16 @@
         <v>妹妹</v>
       </c>
       <c r="C137" t="str">
-        <v>assets/1785842594141-fcglbzjp509.jpg</v>
+        <v>assets/1785838787730-s5f333sc3u.jpg</v>
       </c>
       <c r="D137" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E137" t="str">
-        <v>2026-05-18</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F137" t="str">
-        <v/>
+        <v>湖北恩施</v>
       </c>
       <c r="G137" t="str">
         <v/>
@@ -8490,22 +8490,22 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B138" t="str">
         <v>弟弟</v>
       </c>
       <c r="C138" t="str">
-        <v>assets/1785842639100-82k775dhwiv.jpg</v>
+        <v>assets/1785842296661-6qw3zs3as8h.jpg</v>
       </c>
       <c r="D138" t="str">
         <v>是</v>
       </c>
       <c r="E138" t="str">
-        <v>2026-05-28</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F138" t="str">
-        <v>四川自贡</v>
+        <v>湖北恩施</v>
       </c>
       <c r="G138" t="str">
         <v/>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B139" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C139" t="str">
-        <v>assets/1785842684502-mnhr0r96eee.jpg</v>
+        <v>assets/1785842429109-porc98rel5.jpg</v>
       </c>
       <c r="D139" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E139" t="str">
-        <v>2026-06-06</v>
+        <v>2025-11-05</v>
       </c>
       <c r="F139" t="str">
-        <v/>
+        <v>韩国</v>
       </c>
       <c r="G139" t="str">
         <v/>
@@ -8608,19 +8608,19 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>纯黑色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B140" t="str">
         <v>妹妹</v>
       </c>
       <c r="C140" t="str">
-        <v>assets/1785842779532-5u1j0igrw1s.jpg</v>
+        <v>assets/1785842594141-fcglbzjp509.jpg</v>
       </c>
       <c r="D140" t="str">
         <v>否</v>
       </c>
       <c r="E140" t="str">
-        <v>2026-03-05</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F140" t="str">
         <v/>
@@ -8667,22 +8667,22 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B141" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C141" t="str">
-        <v>assets/1785842817046-6keqv4rw4yf.jpg</v>
+        <v>assets/1785842639100-82k775dhwiv.jpg</v>
       </c>
       <c r="D141" t="str">
         <v>是</v>
       </c>
       <c r="E141" t="str">
-        <v>2026-03-05</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F141" t="str">
-        <v>韩国</v>
+        <v>四川自贡</v>
       </c>
       <c r="G141" t="str">
         <v/>
@@ -8726,22 +8726,22 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>浅色银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B142" t="str">
         <v>妹妹</v>
       </c>
       <c r="C142" t="str">
-        <v>assets/1785842950972-a88lbrskpc.jpg</v>
+        <v>assets/1785842684502-mnhr0r96eee.jpg</v>
       </c>
       <c r="D142" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E142" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F142" t="str">
-        <v>河北邢台</v>
+        <v/>
       </c>
       <c r="G142" t="str">
         <v/>
@@ -8785,22 +8785,22 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>棕虎斑</v>
+        <v>纯黑色</v>
       </c>
       <c r="B143" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C143" t="str">
-        <v>assets/1785843011477-n3l1wi6ech.jpg</v>
+        <v>assets/1785842779532-5u1j0igrw1s.jpg</v>
       </c>
       <c r="D143" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E143" t="str">
-        <v>2026-06-05</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F143" t="str">
-        <v>四川自贡</v>
+        <v/>
       </c>
       <c r="G143" t="str">
         <v/>
@@ -8844,22 +8844,22 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>蓝虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B144" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C144" t="str">
-        <v>assets/1785843237517-ga449iqess5.jpg</v>
+        <v>assets/1785842817046-6keqv4rw4yf.jpg</v>
       </c>
       <c r="D144" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E144" t="str">
         <v>2026-03-05</v>
       </c>
       <c r="F144" t="str">
-        <v/>
+        <v>韩国</v>
       </c>
       <c r="G144" t="str">
         <v/>
@@ -8903,22 +8903,22 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>棕虎斑补丁</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B145" t="str">
         <v>妹妹</v>
       </c>
       <c r="C145" t="str">
-        <v>assets/1785842523893-7nwnnhwi4ns.jpg</v>
+        <v>assets/1785842950972-a88lbrskpc.jpg</v>
       </c>
       <c r="D145" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E145" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F145" t="str">
-        <v/>
+        <v>河北邢台</v>
       </c>
       <c r="G145" t="str">
         <v/>
@@ -8962,22 +8962,22 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B146" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C146" t="str">
-        <v>assets/1785843497557-st27fk8drqi.jpg</v>
+        <v>assets/1785843011477-n3l1wi6ech.jpg</v>
       </c>
       <c r="D146" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E146" t="str">
-        <v>2026-04-05</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F146" t="str">
-        <v/>
+        <v>四川自贡</v>
       </c>
       <c r="G146" t="str">
         <v/>
@@ -9021,13 +9021,13 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B147" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C147" t="str">
-        <v>assets/1785843621923-ylhakbtw13i.jpg</v>
+        <v>assets/1785843237517-ga449iqess5.jpg</v>
       </c>
       <c r="D147" t="str">
         <v>否</v>
@@ -9080,13 +9080,13 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑补丁</v>
       </c>
       <c r="B148" t="str">
         <v>妹妹</v>
       </c>
       <c r="C148" t="str">
-        <v>assets/1785843663884-sfxvpmiet7.jpg</v>
+        <v>assets/1785842523893-7nwnnhwi4ns.jpg</v>
       </c>
       <c r="D148" t="str">
         <v>否</v>
@@ -9145,46 +9145,46 @@
         <v>妹妹</v>
       </c>
       <c r="C149" t="str">
-        <v>assets/1785852601940-o236xtv7yx.jpeg</v>
+        <v>assets/1785843497557-st27fk8drqi.jpg</v>
       </c>
       <c r="D149" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E149" t="str">
-        <v>2026-02-20</v>
+        <v>2026-04-05</v>
       </c>
       <c r="F149" t="str">
-        <v>荷兰</v>
+        <v/>
       </c>
       <c r="G149" t="str">
-        <v>阿泽</v>
+        <v/>
       </c>
       <c r="H149" t="str">
-        <v>小辫子</v>
+        <v/>
       </c>
       <c r="I149" t="str">
-        <v>驺驺</v>
+        <v/>
       </c>
       <c r="J149" t="str">
-        <v>2026-07-02</v>
+        <v/>
       </c>
       <c r="K149" t="str">
         <v/>
       </c>
       <c r="L149" t="str">
-        <v>2026-07-02</v>
+        <v/>
       </c>
       <c r="M149" t="str">
-        <v>2026-08-03</v>
+        <v/>
       </c>
       <c r="N149" t="str">
-        <v>2026-11-04</v>
+        <v/>
       </c>
       <c r="O149" t="str">
-        <v>2026-08-03 · 血清检测,2026-07-02 · 打疫苗 · assets/diary/zouzou-depart.jpg,2026-07-30 · 6.2斤 · 五个月10天了 · assets/feedback/zouzou-1.jpg</v>
+        <v/>
       </c>
       <c r="P149" t="str">
-        <v>已付定金</v>
+        <v/>
       </c>
       <c r="Q149" t="str">
         <v/>
@@ -9193,27 +9193,27 @@
         <v/>
       </c>
       <c r="S149" t="str">
-        <v>否</v>
+        <v/>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>红虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B150" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C150" t="str">
-        <v>assets/1785853950207-cedor66ou2q.jpeg</v>
+        <v>assets/1785843621923-ylhakbtw13i.jpg</v>
       </c>
       <c r="D150" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E150" t="str">
-        <v/>
+        <v>2026-03-05</v>
       </c>
       <c r="F150" t="str">
-        <v>广东广州</v>
+        <v/>
       </c>
       <c r="G150" t="str">
         <v/>
@@ -9257,22 +9257,22 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>红虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B151" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C151" t="str">
-        <v>assets/1785854129383-c8qkvl537x.jpeg</v>
+        <v>assets/1785843663884-sfxvpmiet7.jpg</v>
       </c>
       <c r="D151" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E151" t="str">
-        <v/>
+        <v>2026-03-05</v>
       </c>
       <c r="F151" t="str">
-        <v>广东广州</v>
+        <v/>
       </c>
       <c r="G151" t="str">
         <v/>
@@ -9316,52 +9316,52 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B152" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C152" t="str">
-        <v>assets/1785854166720-48r17hry9cd.jpeg</v>
+        <v>assets/1785852601940-o236xtv7yx.jpeg</v>
       </c>
       <c r="D152" t="str">
         <v>是</v>
       </c>
       <c r="E152" t="str">
-        <v/>
+        <v>2026-02-20</v>
       </c>
       <c r="F152" t="str">
-        <v>山西朔州</v>
+        <v>荷兰</v>
       </c>
       <c r="G152" t="str">
-        <v/>
+        <v>阿泽</v>
       </c>
       <c r="H152" t="str">
-        <v/>
+        <v>小辫子</v>
       </c>
       <c r="I152" t="str">
-        <v/>
+        <v>驺驺</v>
       </c>
       <c r="J152" t="str">
-        <v/>
+        <v>2026-07-02</v>
       </c>
       <c r="K152" t="str">
         <v/>
       </c>
       <c r="L152" t="str">
-        <v/>
+        <v>2026-07-02</v>
       </c>
       <c r="M152" t="str">
-        <v/>
+        <v>2026-08-03</v>
       </c>
       <c r="N152" t="str">
-        <v/>
+        <v>2026-11-04</v>
       </c>
       <c r="O152" t="str">
-        <v/>
+        <v>2026-08-03 · 血清检测,2026-07-02 · 打疫苗 · assets/diary/zouzou-depart.jpg,2026-07-30 · 6.2斤 · 五个月10天了 · assets/feedback/zouzou-1.jpg</v>
       </c>
       <c r="P152" t="str">
-        <v/>
+        <v>已付定金</v>
       </c>
       <c r="Q152" t="str">
         <v/>
@@ -9370,18 +9370,18 @@
         <v/>
       </c>
       <c r="S152" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B153" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C153" t="str">
-        <v>assets/1785854224521-2cpg6xipfn6.jpeg</v>
+        <v>assets/1785853950207-cedor66ou2q.jpeg</v>
       </c>
       <c r="D153" t="str">
         <v>是</v>
@@ -9390,7 +9390,7 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>浙江宁波</v>
+        <v>广东广州</v>
       </c>
       <c r="G153" t="str">
         <v/>
@@ -9434,13 +9434,13 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B154" t="str">
         <v>弟弟</v>
       </c>
       <c r="C154" t="str">
-        <v>assets/1785854260793-steez4s972l.jpeg</v>
+        <v>assets/1785854129383-c8qkvl537x.jpeg</v>
       </c>
       <c r="D154" t="str">
         <v>是</v>
@@ -9449,7 +9449,7 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>陕西西安</v>
+        <v>广东广州</v>
       </c>
       <c r="G154" t="str">
         <v/>
@@ -9499,7 +9499,7 @@
         <v>弟弟</v>
       </c>
       <c r="C155" t="str">
-        <v>assets/1785854319988-cohio08aod5.jpeg</v>
+        <v>assets/1785854166720-48r17hry9cd.jpeg</v>
       </c>
       <c r="D155" t="str">
         <v>是</v>
@@ -9508,7 +9508,7 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>黑龙江漠河</v>
+        <v>山西朔州</v>
       </c>
       <c r="G155" t="str">
         <v/>
@@ -9552,13 +9552,13 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B156" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C156" t="str">
-        <v>assets/1785854520974-96b8b1ekqd9.jpeg</v>
+        <v>assets/1785854224521-2cpg6xipfn6.jpeg</v>
       </c>
       <c r="D156" t="str">
         <v>是</v>
@@ -9567,7 +9567,7 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>日本</v>
+        <v>浙江宁波</v>
       </c>
       <c r="G156" t="str">
         <v/>
@@ -9614,10 +9614,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B157" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C157" t="str">
-        <v>assets/1785854664100-haqoiu1h7hj.jpeg</v>
+        <v>assets/1785854260793-steez4s972l.jpeg</v>
       </c>
       <c r="D157" t="str">
         <v>是</v>
@@ -9626,7 +9626,7 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>浙江杭州</v>
+        <v>陕西西安</v>
       </c>
       <c r="G157" t="str">
         <v/>
@@ -9673,10 +9673,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B158" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C158" t="str">
-        <v>assets/1785854690732-orrs40sx9rs.jpeg</v>
+        <v>assets/1785854319988-cohio08aod5.jpeg</v>
       </c>
       <c r="D158" t="str">
         <v>是</v>
@@ -9685,7 +9685,7 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>贵州安顺</v>
+        <v>黑龙江漠河</v>
       </c>
       <c r="G158" t="str">
         <v/>
@@ -9729,13 +9729,13 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B159" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C159" t="str">
-        <v>assets/1785854734122-wcpmib4m7.jpeg</v>
+        <v>assets/1785854520974-96b8b1ekqd9.jpeg</v>
       </c>
       <c r="D159" t="str">
         <v>是</v>
@@ -9744,7 +9744,7 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>山东青岛</v>
+        <v>日本</v>
       </c>
       <c r="G159" t="str">
         <v/>
@@ -9791,10 +9791,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B160" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C160" t="str">
-        <v>assets/1785854758707-1kxdkfvs6jc.jpeg</v>
+        <v>assets/1785854664100-haqoiu1h7hj.jpeg</v>
       </c>
       <c r="D160" t="str">
         <v>是</v>
@@ -9803,7 +9803,7 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>黑龙江漠河</v>
+        <v>浙江杭州</v>
       </c>
       <c r="G160" t="str">
         <v/>
@@ -9847,13 +9847,13 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>纯蓝色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B161" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C161" t="str">
-        <v>assets/1785854784780-3g0u60pdo93.jpeg</v>
+        <v>assets/1785854690732-orrs40sx9rs.jpeg</v>
       </c>
       <c r="D161" t="str">
         <v>是</v>
@@ -9862,7 +9862,7 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>河南鹤壁</v>
+        <v>贵州安顺</v>
       </c>
       <c r="G161" t="str">
         <v/>
@@ -9909,10 +9909,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B162" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C162" t="str">
-        <v>assets/1785854813179-8oyxr0h2bbu.jpeg</v>
+        <v>assets/1785854734122-wcpmib4m7.jpeg</v>
       </c>
       <c r="D162" t="str">
         <v>是</v>
@@ -9921,7 +9921,7 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>陕西西安</v>
+        <v>山东青岛</v>
       </c>
       <c r="G162" t="str">
         <v/>
@@ -9965,13 +9965,13 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B163" t="str">
         <v>弟弟</v>
       </c>
       <c r="C163" t="str">
-        <v>assets/1785854838933-uq6amircyzd.jpeg</v>
+        <v>assets/1785854758707-1kxdkfvs6jc.jpeg</v>
       </c>
       <c r="D163" t="str">
         <v>是</v>
@@ -9980,7 +9980,7 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>四川成都</v>
+        <v>黑龙江漠河</v>
       </c>
       <c r="G163" t="str">
         <v/>
@@ -10024,22 +10024,22 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>烟灰色</v>
+        <v>纯蓝色</v>
       </c>
       <c r="B164" t="str">
         <v>弟弟</v>
       </c>
       <c r="C164" t="str">
-        <v>assets/1785854869973-za3p6wikqpo.jpeg</v>
+        <v>assets/1785854784780-3g0u60pdo93.jpeg</v>
       </c>
       <c r="D164" t="str">
         <v>是</v>
       </c>
       <c r="E164" t="str">
-        <v>2026-05-18</v>
+        <v/>
       </c>
       <c r="F164" t="str">
-        <v>四川成都</v>
+        <v>河南鹤壁</v>
       </c>
       <c r="G164" t="str">
         <v/>
@@ -10089,7 +10089,7 @@
         <v>弟弟</v>
       </c>
       <c r="C165" t="str">
-        <v>assets/1785854997023-mawkallt2a.jpeg</v>
+        <v>assets/1785854813179-8oyxr0h2bbu.jpeg</v>
       </c>
       <c r="D165" t="str">
         <v>是</v>
@@ -10098,7 +10098,7 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>新加坡</v>
+        <v>陕西西安</v>
       </c>
       <c r="G165" t="str">
         <v/>
@@ -10142,13 +10142,13 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>凯米尔色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B166" t="str">
         <v>弟弟</v>
       </c>
       <c r="C166" t="str">
-        <v>assets/1785855043327-wdc5pxwm34k.jpeg</v>
+        <v>assets/1785854838933-uq6amircyzd.jpeg</v>
       </c>
       <c r="D166" t="str">
         <v>是</v>
@@ -10157,7 +10157,7 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>上海浦东</v>
+        <v>四川成都</v>
       </c>
       <c r="G166" t="str">
         <v/>
@@ -10201,22 +10201,22 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>棕虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B167" t="str">
         <v>弟弟</v>
       </c>
       <c r="C167" t="str">
-        <v>assets/1785912551260-jplefm937nk.jpeg, assets/videos/02.mp4</v>
+        <v>assets/1785854869973-za3p6wikqpo.jpeg</v>
       </c>
       <c r="D167" t="str">
         <v>是</v>
       </c>
       <c r="E167" t="str">
-        <v>2026-06-06</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F167" t="str">
-        <v>浙江温州</v>
+        <v>四川成都</v>
       </c>
       <c r="G167" t="str">
         <v/>
@@ -10260,66 +10260,243 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
+        <v>银虎斑</v>
+      </c>
+      <c r="B168" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C168" t="str">
+        <v>assets/1785854997023-mawkallt2a.jpeg</v>
+      </c>
+      <c r="D168" t="str">
+        <v>是</v>
+      </c>
+      <c r="E168" t="str">
+        <v/>
+      </c>
+      <c r="F168" t="str">
+        <v>新加坡</v>
+      </c>
+      <c r="G168" t="str">
+        <v/>
+      </c>
+      <c r="H168" t="str">
+        <v/>
+      </c>
+      <c r="I168" t="str">
+        <v/>
+      </c>
+      <c r="J168" t="str">
+        <v/>
+      </c>
+      <c r="K168" t="str">
+        <v/>
+      </c>
+      <c r="L168" t="str">
+        <v/>
+      </c>
+      <c r="M168" t="str">
+        <v/>
+      </c>
+      <c r="N168" t="str">
+        <v/>
+      </c>
+      <c r="O168" t="str">
+        <v/>
+      </c>
+      <c r="P168" t="str">
+        <v/>
+      </c>
+      <c r="Q168" t="str">
+        <v/>
+      </c>
+      <c r="R168" t="str">
+        <v/>
+      </c>
+      <c r="S168" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="str">
+        <v>凯米尔色</v>
+      </c>
+      <c r="B169" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C169" t="str">
+        <v>assets/1785855043327-wdc5pxwm34k.jpeg</v>
+      </c>
+      <c r="D169" t="str">
+        <v>是</v>
+      </c>
+      <c r="E169" t="str">
+        <v/>
+      </c>
+      <c r="F169" t="str">
+        <v>上海浦东</v>
+      </c>
+      <c r="G169" t="str">
+        <v/>
+      </c>
+      <c r="H169" t="str">
+        <v/>
+      </c>
+      <c r="I169" t="str">
+        <v/>
+      </c>
+      <c r="J169" t="str">
+        <v/>
+      </c>
+      <c r="K169" t="str">
+        <v/>
+      </c>
+      <c r="L169" t="str">
+        <v/>
+      </c>
+      <c r="M169" t="str">
+        <v/>
+      </c>
+      <c r="N169" t="str">
+        <v/>
+      </c>
+      <c r="O169" t="str">
+        <v/>
+      </c>
+      <c r="P169" t="str">
+        <v/>
+      </c>
+      <c r="Q169" t="str">
+        <v/>
+      </c>
+      <c r="R169" t="str">
+        <v/>
+      </c>
+      <c r="S169" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="str">
         <v>棕虎斑</v>
       </c>
-      <c r="B168" t="str">
+      <c r="B170" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C170" t="str">
+        <v>assets/1785912551260-jplefm937nk.jpeg, assets/videos/02.mp4</v>
+      </c>
+      <c r="D170" t="str">
+        <v>是</v>
+      </c>
+      <c r="E170" t="str">
+        <v>2026-06-06</v>
+      </c>
+      <c r="F170" t="str">
+        <v>浙江温州</v>
+      </c>
+      <c r="G170" t="str">
+        <v/>
+      </c>
+      <c r="H170" t="str">
+        <v/>
+      </c>
+      <c r="I170" t="str">
+        <v/>
+      </c>
+      <c r="J170" t="str">
+        <v/>
+      </c>
+      <c r="K170" t="str">
+        <v/>
+      </c>
+      <c r="L170" t="str">
+        <v/>
+      </c>
+      <c r="M170" t="str">
+        <v/>
+      </c>
+      <c r="N170" t="str">
+        <v/>
+      </c>
+      <c r="O170" t="str">
+        <v/>
+      </c>
+      <c r="P170" t="str">
+        <v/>
+      </c>
+      <c r="Q170" t="str">
+        <v/>
+      </c>
+      <c r="R170" t="str">
+        <v/>
+      </c>
+      <c r="S170" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="str">
+        <v>棕虎斑</v>
+      </c>
+      <c r="B171" t="str">
         <v>妹妹</v>
       </c>
-      <c r="C168" t="str">
+      <c r="C171" t="str">
         <v>assets/1785912694000-m20f5kvvrr.jpeg</v>
       </c>
-      <c r="D168" t="str">
-        <v>否</v>
-      </c>
-      <c r="E168" t="str">
+      <c r="D171" t="str">
+        <v>否</v>
+      </c>
+      <c r="E171" t="str">
         <v>2026-06-06</v>
       </c>
-      <c r="F168" t="str">
-        <v/>
-      </c>
-      <c r="G168" t="str">
-        <v/>
-      </c>
-      <c r="H168" t="str">
-        <v/>
-      </c>
-      <c r="I168" t="str">
-        <v/>
-      </c>
-      <c r="J168" t="str">
-        <v/>
-      </c>
-      <c r="K168" t="str">
-        <v/>
-      </c>
-      <c r="L168" t="str">
-        <v/>
-      </c>
-      <c r="M168" t="str">
-        <v/>
-      </c>
-      <c r="N168" t="str">
-        <v/>
-      </c>
-      <c r="O168" t="str">
-        <v/>
-      </c>
-      <c r="P168" t="str">
-        <v/>
-      </c>
-      <c r="Q168" t="str">
-        <v/>
-      </c>
-      <c r="R168" t="str">
-        <v/>
-      </c>
-      <c r="S168" t="str">
+      <c r="F171" t="str">
+        <v/>
+      </c>
+      <c r="G171" t="str">
+        <v/>
+      </c>
+      <c r="H171" t="str">
+        <v/>
+      </c>
+      <c r="I171" t="str">
+        <v/>
+      </c>
+      <c r="J171" t="str">
+        <v/>
+      </c>
+      <c r="K171" t="str">
+        <v/>
+      </c>
+      <c r="L171" t="str">
+        <v/>
+      </c>
+      <c r="M171" t="str">
+        <v/>
+      </c>
+      <c r="N171" t="str">
+        <v/>
+      </c>
+      <c r="O171" t="str">
+        <v/>
+      </c>
+      <c r="P171" t="str">
+        <v/>
+      </c>
+      <c r="Q171" t="str">
+        <v/>
+      </c>
+      <c r="R171" t="str">
+        <v/>
+      </c>
+      <c r="S171" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S168"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S171"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -7319,13 +7319,13 @@
         <v>assets/1787283092677-i4d8tyrjtf.jpg</v>
       </c>
       <c r="D118" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E118" t="str">
         <v>2026-03-21</v>
       </c>
       <c r="F118" t="str">
-        <v/>
+        <v>中国澳门</v>
       </c>
       <c r="G118" t="str">
         <v/>

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S171"/>
+  <dimension ref="A1:S173"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -466,19 +466,19 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>红虎斑</v>
+        <v>阴影色NS12</v>
       </c>
       <c r="B2" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C2" t="str">
-        <v>assets/1788442386268-ilpasqz91m.jpg</v>
+        <v>assets/1788534744815-pzs6jqs2pm.jpg</v>
       </c>
       <c r="D2" t="str">
         <v>否</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-06-26</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -525,13 +525,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>浅银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B3" t="str">
         <v>弟弟</v>
       </c>
       <c r="C3" t="str">
-        <v>assets/1788442356842-bbleakpy85.jpg</v>
+        <v>assets/1788534522775-my4ggv0pwo.jpg</v>
       </c>
       <c r="D3" t="str">
         <v>否</v>
@@ -584,19 +584,19 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>浅烟灰色</v>
+        <v>红虎斑</v>
       </c>
       <c r="B4" t="str">
         <v>弟弟</v>
       </c>
       <c r="C4" t="str">
-        <v>assets/1788442221802-et3crh0tww.jpg</v>
+        <v>assets/1788442386268-ilpasqz91m.jpg</v>
       </c>
       <c r="D4" t="str">
         <v>否</v>
       </c>
       <c r="E4" t="str">
-        <v>2026-03-21</v>
+        <v>2026-06-26</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -643,22 +643,22 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>凯米尔</v>
+        <v>浅银虎斑</v>
       </c>
       <c r="B5" t="str">
         <v>弟弟</v>
       </c>
       <c r="C5" t="str">
-        <v>assets/1788014088852-oqkg79cki9.jpg</v>
+        <v>assets/1788442356842-bbleakpy85.jpg</v>
       </c>
       <c r="D5" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E5" t="str">
-        <v>2026-06-26</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F5" t="str">
-        <v>湖北襄阳</v>
+        <v/>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -702,19 +702,19 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>棕虎斑</v>
+        <v>浅烟灰色</v>
       </c>
       <c r="B6" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C6" t="str">
-        <v>assets/1788014050978-9a2sguuo1u.jpg</v>
+        <v>assets/1788442221802-et3crh0tww.jpg</v>
       </c>
       <c r="D6" t="str">
         <v>否</v>
       </c>
       <c r="E6" t="str">
-        <v>2026-06-06</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -761,22 +761,22 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>棕虎斑</v>
+        <v>凯米尔</v>
       </c>
       <c r="B7" t="str">
         <v>弟弟</v>
       </c>
       <c r="C7" t="str">
-        <v>assets/1788013924404-gmlh0hfjae.jpg</v>
+        <v>assets/1788014088852-oqkg79cki9.jpg</v>
       </c>
       <c r="D7" t="str">
         <v>是</v>
       </c>
       <c r="E7" t="str">
-        <v>2026-06-15</v>
+        <v>2026-06-26</v>
       </c>
       <c r="F7" t="str">
-        <v>浙江嘉兴</v>
+        <v>湖北襄阳</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -820,22 +820,22 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>凯米尔色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B8" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C8" t="str">
-        <v>assets/1788013889955-wpykaycfde.jpg</v>
+        <v>assets/1788014050978-9a2sguuo1u.jpg</v>
       </c>
       <c r="D8" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E8" t="str">
-        <v>2026-06-26</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F8" t="str">
-        <v>湖北襄阳</v>
+        <v/>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -879,22 +879,22 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>银虎斑补丁</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B9" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C9" t="str">
-        <v>assets/1788013810551-b90h1mwfiq.jpg</v>
+        <v>assets/1788013924404-gmlh0hfjae.jpg</v>
       </c>
       <c r="D9" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E9" t="str">
-        <v>2026-06-26</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F9" t="str">
-        <v/>
+        <v>浙江嘉兴</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -938,22 +938,22 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>银虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B10" t="str">
         <v>弟弟</v>
       </c>
       <c r="C10" t="str">
-        <v>assets/1787837910484-r7urrsuib0.jpg</v>
+        <v>assets/1788013889955-wpykaycfde.jpg</v>
       </c>
       <c r="D10" t="str">
         <v>是</v>
       </c>
       <c r="E10" t="str">
-        <v>2026-05-18</v>
+        <v>2026-06-26</v>
       </c>
       <c r="F10" t="str">
-        <v>香港</v>
+        <v>湖北襄阳</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -997,19 +997,19 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>纯黑色</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B11" t="str">
         <v>妹妹</v>
       </c>
       <c r="C11" t="str">
-        <v>assets/1787837846581-6q9nxgad35.jpg</v>
+        <v>assets/1788013810551-b90h1mwfiq.jpg</v>
       </c>
       <c r="D11" t="str">
         <v>否</v>
       </c>
       <c r="E11" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-26</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -1056,22 +1056,22 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>凯米尔</v>
+        <v>银虎斑</v>
       </c>
       <c r="B12" t="str">
         <v>弟弟</v>
       </c>
       <c r="C12" t="str">
-        <v>assets/1787837779354-hkuyvt39iz.jpg</v>
+        <v>assets/1787837910484-r7urrsuib0.jpg</v>
       </c>
       <c r="D12" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E12" t="str">
-        <v>2026-06-26</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F12" t="str">
-        <v/>
+        <v>香港</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -1115,19 +1115,19 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>烟灰色</v>
+        <v>纯黑色</v>
       </c>
       <c r="B13" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C13" t="str">
-        <v>assets/1787837690599-rd37ukkrgw.jpg</v>
+        <v>assets/1787837846581-6q9nxgad35.jpg</v>
       </c>
       <c r="D13" t="str">
         <v>否</v>
       </c>
       <c r="E13" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-10</v>
       </c>
       <c r="F13" t="str">
         <v/>
@@ -1174,22 +1174,22 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>棕虎斑</v>
+        <v>凯米尔</v>
       </c>
       <c r="B14" t="str">
         <v>弟弟</v>
       </c>
       <c r="C14" t="str">
-        <v>assets/1787837648423-9riberz3tq.jpg</v>
+        <v>assets/1787837779354-hkuyvt39iz.jpg</v>
       </c>
       <c r="D14" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E14" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-26</v>
       </c>
       <c r="F14" t="str">
-        <v>北京</v>
+        <v/>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -1233,19 +1233,19 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>棕虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B15" t="str">
         <v>弟弟</v>
       </c>
       <c r="C15" t="str">
-        <v>assets/1787837594903-wtnbv2fz89.jpg</v>
+        <v>assets/1787837690599-rd37ukkrgw.jpg</v>
       </c>
       <c r="D15" t="str">
         <v>否</v>
       </c>
       <c r="E15" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F15" t="str">
         <v/>
@@ -1298,16 +1298,16 @@
         <v>弟弟</v>
       </c>
       <c r="C16" t="str">
-        <v>assets/1787479268842-7en9nzy302.jpg</v>
+        <v>assets/1787837648423-9riberz3tq.jpg</v>
       </c>
       <c r="D16" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E16" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F16" t="str">
-        <v/>
+        <v>北京</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v/>
       </c>
       <c r="J16" t="str">
-        <v>2026-06-10</v>
+        <v/>
       </c>
       <c r="K16" t="str">
         <v/>
@@ -1351,13 +1351,13 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>纯黑色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B17" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C17" t="str">
-        <v>assets/1787479242639-32zuh5lham.jpg</v>
+        <v>assets/1787837594903-wtnbv2fz89.jpg</v>
       </c>
       <c r="D17" t="str">
         <v>否</v>
@@ -1413,19 +1413,19 @@
         <v>棕虎斑</v>
       </c>
       <c r="B18" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C18" t="str">
-        <v>assets/1787466121255-21jto2cugv.jpg</v>
+        <v>assets/1787479268842-7en9nzy302.jpg</v>
       </c>
       <c r="D18" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E18" t="str">
-        <v/>
+        <v>2026-06-10</v>
       </c>
       <c r="F18" t="str">
-        <v>四川广安</v>
+        <v/>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1437,7 +1437,7 @@
         <v/>
       </c>
       <c r="J18" t="str">
-        <v/>
+        <v>2026-06-10</v>
       </c>
       <c r="K18" t="str">
         <v/>
@@ -1469,19 +1469,19 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>烟灰色</v>
+        <v>纯黑色</v>
       </c>
       <c r="B19" t="str">
         <v>妹妹</v>
       </c>
       <c r="C19" t="str">
-        <v>assets/1787388322060-uj8bkwqgnv.jpg</v>
+        <v>assets/1787479242639-32zuh5lham.jpg</v>
       </c>
       <c r="D19" t="str">
         <v>否</v>
       </c>
       <c r="E19" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-10</v>
       </c>
       <c r="F19" t="str">
         <v/>
@@ -1534,16 +1534,16 @@
         <v>妹妹</v>
       </c>
       <c r="C20" t="str">
-        <v>assets/1787388277490-e6u506cx0r.jpg</v>
+        <v>assets/1787466121255-21jto2cugv.jpg</v>
       </c>
       <c r="D20" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E20" t="str">
-        <v>2026-06-06</v>
+        <v/>
       </c>
       <c r="F20" t="str">
-        <v/>
+        <v>四川广安</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B21" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C21" t="str">
-        <v>assets/1787328436957-x30od0gw28.jpg</v>
+        <v>assets/1787388322060-uj8bkwqgnv.jpg</v>
       </c>
       <c r="D21" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E21" t="str">
-        <v/>
+        <v>2026-06-06</v>
       </c>
       <c r="F21" t="str">
-        <v>江苏苏州</v>
+        <v/>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1646,22 +1646,22 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B22" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C22" t="str">
-        <v>assets/1787328420967-viv9v8nbjn.jpg</v>
+        <v>assets/1787388277490-e6u506cx0r.jpg</v>
       </c>
       <c r="D22" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E22" t="str">
-        <v/>
+        <v>2026-06-06</v>
       </c>
       <c r="F22" t="str">
-        <v>辽宁东港</v>
+        <v/>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1705,13 +1705,13 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B23" t="str">
         <v>弟弟</v>
       </c>
       <c r="C23" t="str">
-        <v>assets/1787327967245-m62ohievcl.jpg</v>
+        <v>assets/1787328436957-x30od0gw28.jpg</v>
       </c>
       <c r="D23" t="str">
         <v>是</v>
@@ -1720,7 +1720,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>福建福州</v>
+        <v>江苏苏州</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1770,7 +1770,7 @@
         <v>弟弟</v>
       </c>
       <c r="C24" t="str">
-        <v>assets/1787327853521-js8ljh3ulj.jpg</v>
+        <v>assets/1787328420967-viv9v8nbjn.jpg</v>
       </c>
       <c r="D24" t="str">
         <v>是</v>
@@ -1779,7 +1779,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>上海</v>
+        <v>辽宁东港</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1823,13 +1823,13 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>纯蓝色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B25" t="str">
         <v>弟弟</v>
       </c>
       <c r="C25" t="str">
-        <v>assets/1787327793837-znk2knoo6p.jpg</v>
+        <v>assets/1787327967245-m62ohievcl.jpg</v>
       </c>
       <c r="D25" t="str">
         <v>是</v>
@@ -1838,7 +1838,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>河南鹤壁</v>
+        <v>福建福州</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1882,13 +1882,13 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B26" t="str">
         <v>弟弟</v>
       </c>
       <c r="C26" t="str">
-        <v>assets/1787327752832-kkpmp21os3.jpg</v>
+        <v>assets/1787327853521-js8ljh3ulj.jpg</v>
       </c>
       <c r="D26" t="str">
         <v>是</v>
@@ -1897,7 +1897,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>陕西西安</v>
+        <v>上海</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1941,13 +1941,13 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>银虎斑</v>
+        <v>纯蓝色</v>
       </c>
       <c r="B27" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C27" t="str">
-        <v>assets/1787327605711-4o2f6v6ybp.jpg</v>
+        <v>assets/1787327793837-znk2knoo6p.jpg</v>
       </c>
       <c r="D27" t="str">
         <v>是</v>
@@ -1956,7 +1956,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>陕西西安</v>
+        <v>河南鹤壁</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -2006,7 +2006,7 @@
         <v>弟弟</v>
       </c>
       <c r="C28" t="str">
-        <v>assets/1787327573762-h23cux94p2.jpg</v>
+        <v>assets/1787327752832-kkpmp21os3.jpg</v>
       </c>
       <c r="D28" t="str">
         <v>是</v>
@@ -2015,7 +2015,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>北京</v>
+        <v>陕西西安</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -2065,7 +2065,7 @@
         <v>妹妹</v>
       </c>
       <c r="C29" t="str">
-        <v>assets/1787327496557-9daggljg4g.jpg</v>
+        <v>assets/1787327605711-4o2f6v6ybp.jpg</v>
       </c>
       <c r="D29" t="str">
         <v>是</v>
@@ -2074,7 +2074,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>黑龙江哈尔滨</v>
+        <v>陕西西安</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -2118,13 +2118,13 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>烟灰色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B30" t="str">
         <v>弟弟</v>
       </c>
       <c r="C30" t="str">
-        <v>assets/1787327456560-p4yhq4qvrv.jpg</v>
+        <v>assets/1787327573762-h23cux94p2.jpg</v>
       </c>
       <c r="D30" t="str">
         <v>是</v>
@@ -2133,7 +2133,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>甘肃嘉峪关</v>
+        <v>北京</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -2177,13 +2177,13 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>蓝虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B31" t="str">
         <v>妹妹</v>
       </c>
       <c r="C31" t="str">
-        <v>assets/1787327421713-zg7np4yzkc.jpg</v>
+        <v>assets/1787327496557-9daggljg4g.jpg</v>
       </c>
       <c r="D31" t="str">
         <v>是</v>
@@ -2192,7 +2192,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>安徽合肥</v>
+        <v>黑龙江哈尔滨</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -2236,13 +2236,13 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B32" t="str">
         <v>弟弟</v>
       </c>
       <c r="C32" t="str">
-        <v>assets/1787327337811-u5u2pdew3.jpg</v>
+        <v>assets/1787327456560-p4yhq4qvrv.jpg</v>
       </c>
       <c r="D32" t="str">
         <v>是</v>
@@ -2251,7 +2251,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>安徽合肥</v>
+        <v>甘肃嘉峪关</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -2295,13 +2295,13 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>棕虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B33" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C33" t="str">
-        <v>assets/1787327309143-6c1dan1sev.jpg</v>
+        <v>assets/1787327421713-zg7np4yzkc.jpg</v>
       </c>
       <c r="D33" t="str">
         <v>是</v>
@@ -2310,7 +2310,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>四川成都</v>
+        <v>安徽合肥</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -2360,7 +2360,7 @@
         <v>弟弟</v>
       </c>
       <c r="C34" t="str">
-        <v>assets/1787327277453-w89ujg69fm.jpg</v>
+        <v>assets/1787327337811-u5u2pdew3.jpg</v>
       </c>
       <c r="D34" t="str">
         <v>是</v>
@@ -2369,7 +2369,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>四川成都</v>
+        <v>安徽合肥</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -2413,13 +2413,13 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>蓝银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B35" t="str">
         <v>弟弟</v>
       </c>
       <c r="C35" t="str">
-        <v>assets/1787327232159-lkrcl588a5.jpg</v>
+        <v>assets/1787327309143-6c1dan1sev.jpg</v>
       </c>
       <c r="D35" t="str">
         <v>是</v>
@@ -2472,13 +2472,13 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>玳瑁色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B36" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C36" t="str">
-        <v>assets/1787327182347-3az0z7sys2.jpg</v>
+        <v>assets/1787327277453-w89ujg69fm.jpg</v>
       </c>
       <c r="D36" t="str">
         <v>是</v>
@@ -2487,7 +2487,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>四川内江</v>
+        <v>四川成都</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -2531,13 +2531,13 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>棕虎补丁</v>
+        <v>蓝银虎斑</v>
       </c>
       <c r="B37" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C37" t="str">
-        <v>assets/1787327143756-4xtgfy5ozu.jpg</v>
+        <v>assets/1787327232159-lkrcl588a5.jpg</v>
       </c>
       <c r="D37" t="str">
         <v>是</v>
@@ -2546,7 +2546,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>贵州贵阳</v>
+        <v>四川成都</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -2590,13 +2590,13 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>黑烟色</v>
+        <v>玳瑁色</v>
       </c>
       <c r="B38" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C38" t="str">
-        <v>assets/1787327101790-tqjlseog5y.jpg</v>
+        <v>assets/1787327182347-3az0z7sys2.jpg</v>
       </c>
       <c r="D38" t="str">
         <v>是</v>
@@ -2605,7 +2605,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>浙江杭州</v>
+        <v>四川内江</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -2649,13 +2649,13 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>烟灰色</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B39" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C39" t="str">
-        <v>assets/1787327019632-l1780lu2hj.jpg</v>
+        <v>assets/1787327143756-4xtgfy5ozu.jpg</v>
       </c>
       <c r="D39" t="str">
         <v>是</v>
@@ -2664,7 +2664,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>山东威海</v>
+        <v>贵州贵阳</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -2708,13 +2708,13 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>棕虎补丁</v>
+        <v>黑烟色</v>
       </c>
       <c r="B40" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C40" t="str">
-        <v>assets/1787326905275-plz3fpgo97.jpg</v>
+        <v>assets/1787327101790-tqjlseog5y.jpg</v>
       </c>
       <c r="D40" t="str">
         <v>是</v>
@@ -2767,13 +2767,13 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>蓝虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B41" t="str">
         <v>弟弟</v>
       </c>
       <c r="C41" t="str">
-        <v>assets/1787326874462-z9rzs7wg17.jpg</v>
+        <v>assets/1787327019632-l1780lu2hj.jpg</v>
       </c>
       <c r="D41" t="str">
         <v>是</v>
@@ -2782,7 +2782,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>四川成都</v>
+        <v>山东威海</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -2826,13 +2826,13 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>凯米尔色</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B42" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C42" t="str">
-        <v>assets/1787326843271-0uhv7b9p89.jpg</v>
+        <v>assets/1787326905275-plz3fpgo97.jpg</v>
       </c>
       <c r="D42" t="str">
         <v>是</v>
@@ -2841,7 +2841,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>四川成都</v>
+        <v>浙江杭州</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -2885,13 +2885,13 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>凯米尔</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B43" t="str">
         <v>弟弟</v>
       </c>
       <c r="C43" t="str">
-        <v>assets/1787326814713-p5oavnlulg.jpg</v>
+        <v>assets/1787326874462-z9rzs7wg17.jpg</v>
       </c>
       <c r="D43" t="str">
         <v>是</v>
@@ -2944,13 +2944,13 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>棕虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B44" t="str">
         <v>弟弟</v>
       </c>
       <c r="C44" t="str">
-        <v>assets/1787326773577-13q5out2d0.jpg</v>
+        <v>assets/1787326843271-0uhv7b9p89.jpg</v>
       </c>
       <c r="D44" t="str">
         <v>是</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>四川宜宾</v>
+        <v>四川成都</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -3003,13 +3003,13 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>金棕虎斑</v>
+        <v>凯米尔</v>
       </c>
       <c r="B45" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C45" t="str">
-        <v>assets/1787326548993-89s929m2hg.jpg</v>
+        <v>assets/1787326814713-p5oavnlulg.jpg</v>
       </c>
       <c r="D45" t="str">
         <v>是</v>
@@ -3018,7 +3018,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>上海</v>
+        <v>四川成都</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -3062,13 +3062,13 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>凯米尔色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B46" t="str">
         <v>弟弟</v>
       </c>
       <c r="C46" t="str">
-        <v>assets/1787326449218-09s9ucram4.jpg</v>
+        <v>assets/1787326773577-13q5out2d0.jpg</v>
       </c>
       <c r="D46" t="str">
         <v>是</v>
@@ -3077,7 +3077,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>德国</v>
+        <v>四川宜宾</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -3121,13 +3121,13 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>棕虎补丁</v>
+        <v>金棕虎斑</v>
       </c>
       <c r="B47" t="str">
         <v>妹妹</v>
       </c>
       <c r="C47" t="str">
-        <v>assets/1787326277374-8ti107m5ki.jpg</v>
+        <v>assets/1787326548993-89s929m2hg.jpg</v>
       </c>
       <c r="D47" t="str">
         <v>是</v>
@@ -3136,7 +3136,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>广东深圳</v>
+        <v>上海</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -3180,13 +3180,13 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>烟灰色</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B48" t="str">
         <v>弟弟</v>
       </c>
       <c r="C48" t="str">
-        <v>assets/1787326236952-2pmwche4t3.jpg</v>
+        <v>assets/1787326449218-09s9ucram4.jpg</v>
       </c>
       <c r="D48" t="str">
         <v>是</v>
@@ -3195,7 +3195,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>福建泉州</v>
+        <v>德国</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -3239,13 +3239,13 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>银虎斑</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B49" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C49" t="str">
-        <v>assets/1787326184557-90v6clkwen.jpg</v>
+        <v>assets/1787326277374-8ti107m5ki.jpg</v>
       </c>
       <c r="D49" t="str">
         <v>是</v>
@@ -3254,7 +3254,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>福建福州</v>
+        <v>广东深圳</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -3298,13 +3298,13 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>棕虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B50" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C50" t="str">
-        <v>assets/1787326046155-4tk23nq4dj.jpg</v>
+        <v>assets/1787326236952-2pmwche4t3.jpg</v>
       </c>
       <c r="D50" t="str">
         <v>是</v>
@@ -3313,7 +3313,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>广西贵港</v>
+        <v>福建泉州</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -3357,13 +3357,13 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>凯米尔色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B51" t="str">
         <v>弟弟</v>
       </c>
       <c r="C51" t="str">
-        <v>assets/1787325862706-wq18k3ej56.jpg</v>
+        <v>assets/1787326184557-90v6clkwen.jpg</v>
       </c>
       <c r="D51" t="str">
         <v>是</v>
@@ -3372,7 +3372,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>江苏苏州</v>
+        <v>福建福州</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -3416,13 +3416,13 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>凯米尔色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B52" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C52" t="str">
-        <v>assets/1787325743258-a7oac7hzlo.jpg</v>
+        <v>assets/1787326046155-4tk23nq4dj.jpg</v>
       </c>
       <c r="D52" t="str">
         <v>是</v>
@@ -3431,7 +3431,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>江苏苏州</v>
+        <v>广西贵港</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -3475,13 +3475,13 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>银虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B53" t="str">
         <v>弟弟</v>
       </c>
       <c r="C53" t="str">
-        <v>assets/1787325706797-kgk81ghccy.jpg</v>
+        <v>assets/1787325862706-wq18k3ej56.jpg</v>
       </c>
       <c r="D53" t="str">
         <v>是</v>
@@ -3490,7 +3490,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>北京</v>
+        <v>江苏苏州</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -3534,13 +3534,13 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>蓝虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B54" t="str">
         <v>弟弟</v>
       </c>
       <c r="C54" t="str">
-        <v>assets/1787325603704-lahzgrm7fa.jpg,assets/1787325690106-wgu3spujit.jpg</v>
+        <v>assets/1787325743258-a7oac7hzlo.jpg</v>
       </c>
       <c r="D54" t="str">
         <v>是</v>
@@ -3549,7 +3549,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>上海</v>
+        <v>江苏苏州</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -3593,13 +3593,13 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B55" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C55" t="str">
-        <v>assets/1787325554341-608thexrne.jpg</v>
+        <v>assets/1787325706797-kgk81ghccy.jpg</v>
       </c>
       <c r="D55" t="str">
         <v>是</v>
@@ -3608,7 +3608,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>江苏苏州</v>
+        <v>北京</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -3652,13 +3652,13 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>浅色银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B56" t="str">
         <v>弟弟</v>
       </c>
       <c r="C56" t="str">
-        <v>assets/1787325480828-q90pskoiw3.jpg</v>
+        <v>assets/1787325603704-lahzgrm7fa.jpg,assets/1787325690106-wgu3spujit.jpg</v>
       </c>
       <c r="D56" t="str">
         <v>是</v>
@@ -3667,7 +3667,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>四川成都</v>
+        <v>上海</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -3711,13 +3711,13 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>浅色银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B57" t="str">
         <v>妹妹</v>
       </c>
       <c r="C57" t="str">
-        <v>assets/1787325448999-a2pg8176fu.jpg</v>
+        <v>assets/1787325554341-608thexrne.jpg</v>
       </c>
       <c r="D57" t="str">
         <v>是</v>
@@ -3726,7 +3726,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>中国台湾</v>
+        <v>江苏苏州</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -3770,13 +3770,13 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>棕虎斑</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B58" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C58" t="str">
-        <v>assets/1787325357634-k55zlfhmqj.jpg</v>
+        <v>assets/1787325480828-q90pskoiw3.jpg</v>
       </c>
       <c r="D58" t="str">
         <v>是</v>
@@ -3785,7 +3785,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>浙江杭州</v>
+        <v>四川成都</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -3829,13 +3829,13 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>烟灰色</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B59" t="str">
         <v>妹妹</v>
       </c>
       <c r="C59" t="str">
-        <v>assets/1787325237876-t19isaq5gu.jpg</v>
+        <v>assets/1787325448999-a2pg8176fu.jpg</v>
       </c>
       <c r="D59" t="str">
         <v>是</v>
@@ -3844,7 +3844,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>辽宁沈阳</v>
+        <v>中国台湾</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -3888,13 +3888,13 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>金棕虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B60" t="str">
         <v>妹妹</v>
       </c>
       <c r="C60" t="str">
-        <v>assets/1787325199931-e7wms9qtya.jpg</v>
+        <v>assets/1787325357634-k55zlfhmqj.jpg</v>
       </c>
       <c r="D60" t="str">
         <v>是</v>
@@ -3903,7 +3903,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>四川成都</v>
+        <v>浙江杭州</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -3947,13 +3947,13 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>蓝虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B61" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C61" t="str">
-        <v>assets/1787325172354-4sa8uzaey2.jpg</v>
+        <v>assets/1787325237876-t19isaq5gu.jpg</v>
       </c>
       <c r="D61" t="str">
         <v>是</v>
@@ -3962,7 +3962,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>中国香港</v>
+        <v>辽宁沈阳</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -4006,13 +4006,13 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>烟灰色</v>
+        <v>金棕虎斑</v>
       </c>
       <c r="B62" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C62" t="str">
-        <v>assets/1787325109283-y7mvkk6qg4.jpg</v>
+        <v>assets/1787325199931-e7wms9qtya.jpg</v>
       </c>
       <c r="D62" t="str">
         <v>是</v>
@@ -4021,7 +4021,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>中国澳门</v>
+        <v>四川成都</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -4071,7 +4071,7 @@
         <v>弟弟</v>
       </c>
       <c r="C63" t="str">
-        <v>assets/1787325033629-y3ygps3zaj.jpg</v>
+        <v>assets/1787325172354-4sa8uzaey2.jpg</v>
       </c>
       <c r="D63" t="str">
         <v>是</v>
@@ -4080,7 +4080,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>山东青岛</v>
+        <v>中国香港</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -4130,7 +4130,7 @@
         <v>弟弟</v>
       </c>
       <c r="C64" t="str">
-        <v>assets/1787324954998-w5m5jox439.jpg</v>
+        <v>assets/1787325109283-y7mvkk6qg4.jpg</v>
       </c>
       <c r="D64" t="str">
         <v>是</v>
@@ -4139,7 +4139,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>海南海口</v>
+        <v>中国澳门</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -4183,13 +4183,13 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>棕虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B65" t="str">
         <v>弟弟</v>
       </c>
       <c r="C65" t="str">
-        <v>assets/1787324905909-zrz8o79kdf.jpg</v>
+        <v>assets/1787325033629-y3ygps3zaj.jpg</v>
       </c>
       <c r="D65" t="str">
         <v>是</v>
@@ -4198,7 +4198,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>内蒙古</v>
+        <v>山东青岛</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -4248,7 +4248,7 @@
         <v>弟弟</v>
       </c>
       <c r="C66" t="str">
-        <v>assets/1787324880505-gbh0sn7b6j.jpg</v>
+        <v>assets/1787324954998-w5m5jox439.jpg</v>
       </c>
       <c r="D66" t="str">
         <v>是</v>
@@ -4257,7 +4257,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>中国香港</v>
+        <v>海南海口</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -4301,13 +4301,13 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B67" t="str">
         <v>弟弟</v>
       </c>
       <c r="C67" t="str">
-        <v>assets/1787324806613-31yyz14tsf.jpg</v>
+        <v>assets/1787324905909-zrz8o79kdf.jpg</v>
       </c>
       <c r="D67" t="str">
         <v>是</v>
@@ -4316,7 +4316,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>四川成都</v>
+        <v>内蒙古</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -4360,13 +4360,13 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>红虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B68" t="str">
         <v>弟弟</v>
       </c>
       <c r="C68" t="str">
-        <v>assets/1787324789658-uz6ephkdsh.jpg</v>
+        <v>assets/1787324880505-gbh0sn7b6j.jpg</v>
       </c>
       <c r="D68" t="str">
         <v>是</v>
@@ -4375,7 +4375,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>湖北武汉</v>
+        <v>中国香港</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -4425,7 +4425,7 @@
         <v>弟弟</v>
       </c>
       <c r="C69" t="str">
-        <v>assets/1787324522658-smn44crast.jpg</v>
+        <v>assets/1787324806613-31yyz14tsf.jpg</v>
       </c>
       <c r="D69" t="str">
         <v>是</v>
@@ -4434,7 +4434,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>湖北武汉</v>
+        <v>四川成都</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -4478,13 +4478,13 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>棕虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B70" t="str">
         <v>弟弟</v>
       </c>
       <c r="C70" t="str">
-        <v>assets/1787324365608-6xtrjp7euz.jpg</v>
+        <v>assets/1787324789658-uz6ephkdsh.jpg</v>
       </c>
       <c r="D70" t="str">
         <v>是</v>
@@ -4493,7 +4493,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>新疆</v>
+        <v>湖北武汉</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -4537,13 +4537,13 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>浅凯米尔</v>
+        <v>烟灰色</v>
       </c>
       <c r="B71" t="str">
         <v>弟弟</v>
       </c>
       <c r="C71" t="str">
-        <v>assets/1787324331029-d74lcuycf6.jpg</v>
+        <v>assets/1787324522658-smn44crast.jpg</v>
       </c>
       <c r="D71" t="str">
         <v>是</v>
@@ -4552,7 +4552,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>四川成都</v>
+        <v>湖北武汉</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -4596,13 +4596,13 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>红虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B72" t="str">
         <v>弟弟</v>
       </c>
       <c r="C72" t="str">
-        <v>assets/1787324297469-ans1lse2l5.jpg</v>
+        <v>assets/1787324365608-6xtrjp7euz.jpg</v>
       </c>
       <c r="D72" t="str">
         <v>是</v>
@@ -4611,7 +4611,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>四川乐山</v>
+        <v>新疆</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -4655,13 +4655,13 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>红虎斑</v>
+        <v>浅凯米尔</v>
       </c>
       <c r="B73" t="str">
         <v>弟弟</v>
       </c>
       <c r="C73" t="str">
-        <v>assets/1787324256827-7w383z4bg1.jpg</v>
+        <v>assets/1787324331029-d74lcuycf6.jpg</v>
       </c>
       <c r="D73" t="str">
         <v>是</v>
@@ -4670,7 +4670,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>中国台湾</v>
+        <v>四川成都</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -4714,13 +4714,13 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B74" t="str">
         <v>弟弟</v>
       </c>
       <c r="C74" t="str">
-        <v>assets/1787324228262-y3vwn6i4zk.jpg</v>
+        <v>assets/1787324297469-ans1lse2l5.jpg</v>
       </c>
       <c r="D74" t="str">
         <v>是</v>
@@ -4729,7 +4729,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>四川成都</v>
+        <v>四川乐山</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -4773,13 +4773,13 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>凯米尔色</v>
+        <v>红虎斑</v>
       </c>
       <c r="B75" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C75" t="str">
-        <v>assets/1787324201418-9tk4ik75mo.jpg</v>
+        <v>assets/1787324256827-7w383z4bg1.jpg</v>
       </c>
       <c r="D75" t="str">
         <v>是</v>
@@ -4788,7 +4788,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>江苏南京</v>
+        <v>中国台湾</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -4832,13 +4832,13 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B76" t="str">
         <v>弟弟</v>
       </c>
       <c r="C76" t="str">
-        <v>assets/1787324092513-jpa2rmkci2.jpg</v>
+        <v>assets/1787324228262-y3vwn6i4zk.jpg</v>
       </c>
       <c r="D76" t="str">
         <v>是</v>
@@ -4847,7 +4847,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>江苏南京</v>
+        <v>四川成都</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -4891,13 +4891,13 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>银虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B77" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C77" t="str">
-        <v>assets/1787323318612-soge38hpsf.jpg</v>
+        <v>assets/1787324201418-9tk4ik75mo.jpg</v>
       </c>
       <c r="D77" t="str">
         <v>是</v>
@@ -4906,7 +4906,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>上海</v>
+        <v>江苏南京</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -4956,7 +4956,7 @@
         <v>弟弟</v>
       </c>
       <c r="C78" t="str">
-        <v>assets/1787323235892-7yq8ioq01e.jpg</v>
+        <v>assets/1787324092513-jpa2rmkci2.jpg</v>
       </c>
       <c r="D78" t="str">
         <v>是</v>
@@ -4965,7 +4965,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>四川成都</v>
+        <v>江苏南京</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -5012,10 +5012,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B79" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C79" t="str">
-        <v>assets/1787322988096-6e2f54q7vo.jpg</v>
+        <v>assets/1787323318612-soge38hpsf.jpg</v>
       </c>
       <c r="D79" t="str">
         <v>是</v>
@@ -5024,7 +5024,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>浙江宁波</v>
+        <v>上海</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -5068,13 +5068,13 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>银虎斑补丁</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B80" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C80" t="str">
-        <v>assets/1787322938518-85ev8bs2k5.jpg</v>
+        <v>assets/1787323235892-7yq8ioq01e.jpg</v>
       </c>
       <c r="D80" t="str">
         <v>是</v>
@@ -5083,7 +5083,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>马来西亚</v>
+        <v>四川成都</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -5130,10 +5130,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B81" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C81" t="str">
-        <v>assets/1787322881183-tzu9xtw2sg.jpg</v>
+        <v>assets/1787322988096-6e2f54q7vo.jpg</v>
       </c>
       <c r="D81" t="str">
         <v>是</v>
@@ -5142,7 +5142,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>陕西西安</v>
+        <v>浙江宁波</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -5186,13 +5186,13 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>纯黑色</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B82" t="str">
         <v>妹妹</v>
       </c>
       <c r="C82" t="str">
-        <v>assets/1787322840098-nhy4jjyx7k.jpg</v>
+        <v>assets/1787322938518-85ev8bs2k5.jpg</v>
       </c>
       <c r="D82" t="str">
         <v>是</v>
@@ -5201,7 +5201,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>广西南宁</v>
+        <v>马来西亚</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -5245,13 +5245,13 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B83" t="str">
         <v>弟弟</v>
       </c>
       <c r="C83" t="str">
-        <v>assets/1787322760950-gn3qgego4s.jpg</v>
+        <v>assets/1787322881183-tzu9xtw2sg.jpg</v>
       </c>
       <c r="D83" t="str">
         <v>是</v>
@@ -5260,7 +5260,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>广西南宁</v>
+        <v>陕西西安</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -5304,13 +5304,13 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>红虎斑</v>
+        <v>纯黑色</v>
       </c>
       <c r="B84" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C84" t="str">
-        <v>assets/1787322605982-04n50xegt2.jpg</v>
+        <v>assets/1787322840098-nhy4jjyx7k.jpg</v>
       </c>
       <c r="D84" t="str">
         <v>是</v>
@@ -5319,7 +5319,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>上海</v>
+        <v>广西南宁</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -5363,13 +5363,13 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B85" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C85" t="str">
-        <v>assets/1787322490045-kog3ru43dy.jpg</v>
+        <v>assets/1787322760950-gn3qgego4s.jpg</v>
       </c>
       <c r="D85" t="str">
         <v>是</v>
@@ -5378,7 +5378,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>上海</v>
+        <v>广西南宁</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -5428,7 +5428,7 @@
         <v>弟弟</v>
       </c>
       <c r="C86" t="str">
-        <v>assets/1787322419996-0m33yx89nm.jpg</v>
+        <v>assets/1787322605982-04n50xegt2.jpg</v>
       </c>
       <c r="D86" t="str">
         <v>是</v>
@@ -5437,7 +5437,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>广东广州</v>
+        <v>上海</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -5481,13 +5481,13 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>浅色银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B87" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C87" t="str">
-        <v>assets/1787322377730-vj5csj2mll.jpg</v>
+        <v>assets/1787322490045-kog3ru43dy.jpg</v>
       </c>
       <c r="D87" t="str">
         <v>是</v>
@@ -5496,7 +5496,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>柬埔寨</v>
+        <v>上海</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -5540,13 +5540,13 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>蓝虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B88" t="str">
         <v>弟弟</v>
       </c>
       <c r="C88" t="str">
-        <v>assets/1787322269611-53yaj5ideu.jpg</v>
+        <v>assets/1787322419996-0m33yx89nm.jpg</v>
       </c>
       <c r="D88" t="str">
         <v>是</v>
@@ -5555,7 +5555,7 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>山东枣庄</v>
+        <v>广东广州</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -5599,13 +5599,13 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>银虎斑</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B89" t="str">
         <v>弟弟</v>
       </c>
       <c r="C89" t="str">
-        <v>assets/1787321989528-7d6liuhuk9.jpg</v>
+        <v>assets/1787322377730-vj5csj2mll.jpg</v>
       </c>
       <c r="D89" t="str">
         <v>是</v>
@@ -5614,7 +5614,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>陕西西安</v>
+        <v>柬埔寨</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -5658,13 +5658,13 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B90" t="str">
         <v>弟弟</v>
       </c>
       <c r="C90" t="str">
-        <v>assets/1787321941642-xlrc1no2ua.jpg</v>
+        <v>assets/1787322269611-53yaj5ideu.jpg</v>
       </c>
       <c r="D90" t="str">
         <v>是</v>
@@ -5673,7 +5673,7 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>山东东营</v>
+        <v>山东枣庄</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -5717,13 +5717,13 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>凯米尔色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B91" t="str">
         <v>弟弟</v>
       </c>
       <c r="C91" t="str">
-        <v>assets/1787321903535-6orj7qcgzn.jpg</v>
+        <v>assets/1787321989528-7d6liuhuk9.jpg</v>
       </c>
       <c r="D91" t="str">
         <v>是</v>
@@ -5732,7 +5732,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>中国台湾</v>
+        <v>陕西西安</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -5776,13 +5776,13 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>烟灰色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B92" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C92" t="str">
-        <v>assets/1787321858985-v4qej7cq7g.jpg</v>
+        <v>assets/1787321941642-xlrc1no2ua.jpg</v>
       </c>
       <c r="D92" t="str">
         <v>是</v>
@@ -5791,7 +5791,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>中国台湾</v>
+        <v>山东东营</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -5835,13 +5835,13 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>银虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B93" t="str">
         <v>弟弟</v>
       </c>
       <c r="C93" t="str">
-        <v>assets/1787321834306-efgnyhujon.jpg</v>
+        <v>assets/1787321903535-6orj7qcgzn.jpg</v>
       </c>
       <c r="D93" t="str">
         <v>是</v>
@@ -5850,7 +5850,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>北京</v>
+        <v>中国台湾</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -5894,13 +5894,13 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B94" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C94" t="str">
-        <v>assets/1787321439916-uttgpbkogb.jpg</v>
+        <v>assets/1787321858985-v4qej7cq7g.jpg</v>
       </c>
       <c r="D94" t="str">
         <v>是</v>
@@ -5909,7 +5909,7 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>安徽合肥</v>
+        <v>中国台湾</v>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -5959,7 +5959,7 @@
         <v>弟弟</v>
       </c>
       <c r="C95" t="str">
-        <v>assets/1787321419210-51hhgurygq.jpg</v>
+        <v>assets/1787321834306-efgnyhujon.jpg</v>
       </c>
       <c r="D95" t="str">
         <v>是</v>
@@ -5968,7 +5968,7 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>上海</v>
+        <v>北京</v>
       </c>
       <c r="G95" t="str">
         <v/>
@@ -6012,13 +6012,13 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>凯米尔色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B96" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C96" t="str">
-        <v>assets/1787321363369-bzjn51j5il.jpg</v>
+        <v>assets/1787321439916-uttgpbkogb.jpg</v>
       </c>
       <c r="D96" t="str">
         <v>是</v>
@@ -6027,7 +6027,7 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>中国台湾</v>
+        <v>安徽合肥</v>
       </c>
       <c r="G96" t="str">
         <v/>
@@ -6071,13 +6071,13 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B97" t="str">
         <v>弟弟</v>
       </c>
       <c r="C97" t="str">
-        <v>assets/1787321332559-87p6spuch3.jpg</v>
+        <v>assets/1787321419210-51hhgurygq.jpg</v>
       </c>
       <c r="D97" t="str">
         <v>是</v>
@@ -6086,7 +6086,7 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>中国台湾</v>
+        <v>上海</v>
       </c>
       <c r="G97" t="str">
         <v/>
@@ -6130,13 +6130,13 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>棕虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B98" t="str">
         <v>妹妹</v>
       </c>
       <c r="C98" t="str">
-        <v>assets/1787321232531-59lnzv8y98.jpg</v>
+        <v>assets/1787321363369-bzjn51j5il.jpg</v>
       </c>
       <c r="D98" t="str">
         <v>是</v>
@@ -6145,7 +6145,7 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>北京</v>
+        <v>中国台湾</v>
       </c>
       <c r="G98" t="str">
         <v/>
@@ -6189,13 +6189,13 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B99" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C99" t="str">
-        <v>assets/1787319975814-g1pfa56vfp.jpg</v>
+        <v>assets/1787321332559-87p6spuch3.jpg</v>
       </c>
       <c r="D99" t="str">
         <v>是</v>
@@ -6204,7 +6204,7 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>浙江宁波</v>
+        <v>中国台湾</v>
       </c>
       <c r="G99" t="str">
         <v/>
@@ -6248,13 +6248,13 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B100" t="str">
         <v>妹妹</v>
       </c>
       <c r="C100" t="str">
-        <v>assets/1787319800704-v3qeu062ak.jpg</v>
+        <v>assets/1787321232531-59lnzv8y98.jpg</v>
       </c>
       <c r="D100" t="str">
         <v>是</v>
@@ -6263,7 +6263,7 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>河北唐山</v>
+        <v>北京</v>
       </c>
       <c r="G100" t="str">
         <v/>
@@ -6313,7 +6313,7 @@
         <v>妹妹</v>
       </c>
       <c r="C101" t="str">
-        <v>assets/1787319745369-zn66xr3bvb.jpg</v>
+        <v>assets/1787319975814-g1pfa56vfp.jpg</v>
       </c>
       <c r="D101" t="str">
         <v>是</v>
@@ -6322,7 +6322,7 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>河北石家庄</v>
+        <v>浙江宁波</v>
       </c>
       <c r="G101" t="str">
         <v/>
@@ -6366,13 +6366,13 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>棕虎补丁</v>
+        <v>银虎斑</v>
       </c>
       <c r="B102" t="str">
         <v>妹妹</v>
       </c>
       <c r="C102" t="str">
-        <v>assets/1787319547969-zqlq35fxxt.jpg</v>
+        <v>assets/1787319800704-v3qeu062ak.jpg</v>
       </c>
       <c r="D102" t="str">
         <v>是</v>
@@ -6381,7 +6381,7 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>韩国</v>
+        <v>河北唐山</v>
       </c>
       <c r="G102" t="str">
         <v/>
@@ -6425,13 +6425,13 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>蓝银虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B103" t="str">
         <v>妹妹</v>
       </c>
       <c r="C103" t="str">
-        <v>assets/1787319501376-xscwljnu1j.jpg</v>
+        <v>assets/1787319745369-zn66xr3bvb.jpg</v>
       </c>
       <c r="D103" t="str">
         <v>是</v>
@@ -6440,7 +6440,7 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>美国</v>
+        <v>河北石家庄</v>
       </c>
       <c r="G103" t="str">
         <v/>
@@ -6484,13 +6484,13 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>棕虎斑</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B104" t="str">
         <v>妹妹</v>
       </c>
       <c r="C104" t="str">
-        <v>assets/1787319443529-4a0zqikufx.jpg</v>
+        <v>assets/1787319547969-zqlq35fxxt.jpg</v>
       </c>
       <c r="D104" t="str">
         <v>是</v>
@@ -6499,7 +6499,7 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>中国台湾</v>
+        <v>韩国</v>
       </c>
       <c r="G104" t="str">
         <v/>
@@ -6543,13 +6543,13 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>蓝虎斑</v>
+        <v>蓝银虎斑</v>
       </c>
       <c r="B105" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C105" t="str">
-        <v>assets/1787319356194-lr2d5680i9.jpg</v>
+        <v>assets/1787319501376-xscwljnu1j.jpg</v>
       </c>
       <c r="D105" t="str">
         <v>是</v>
@@ -6558,7 +6558,7 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>中国台湾</v>
+        <v>美国</v>
       </c>
       <c r="G105" t="str">
         <v/>
@@ -6608,7 +6608,7 @@
         <v>妹妹</v>
       </c>
       <c r="C106" t="str">
-        <v>assets/1787319208828-aizqo4blcv.jpg</v>
+        <v>assets/1787319443529-4a0zqikufx.jpg</v>
       </c>
       <c r="D106" t="str">
         <v>是</v>
@@ -6617,7 +6617,7 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>山东淄博</v>
+        <v>中国台湾</v>
       </c>
       <c r="G106" t="str">
         <v/>
@@ -6661,13 +6661,13 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B107" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C107" t="str">
-        <v>assets/1787319162970-cc2v8ovnni.jpg</v>
+        <v>assets/1787319356194-lr2d5680i9.jpg</v>
       </c>
       <c r="D107" t="str">
         <v>是</v>
@@ -6676,7 +6676,7 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>韩国</v>
+        <v>中国台湾</v>
       </c>
       <c r="G107" t="str">
         <v/>
@@ -6720,13 +6720,13 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>棕虎补丁</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B108" t="str">
         <v>妹妹</v>
       </c>
       <c r="C108" t="str">
-        <v>assets/1787319098214-8pwa9yx2wc.jpg</v>
+        <v>assets/1787319208828-aizqo4blcv.jpg</v>
       </c>
       <c r="D108" t="str">
         <v>是</v>
@@ -6735,7 +6735,7 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>四川成都</v>
+        <v>山东淄博</v>
       </c>
       <c r="G108" t="str">
         <v/>
@@ -6782,10 +6782,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B109" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C109" t="str">
-        <v>assets/1787318867999-3gxdddp72x.jpg</v>
+        <v>assets/1787319162970-cc2v8ovnni.jpg</v>
       </c>
       <c r="D109" t="str">
         <v>是</v>
@@ -6794,7 +6794,7 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>广东广州</v>
+        <v>韩国</v>
       </c>
       <c r="G109" t="str">
         <v/>
@@ -6838,13 +6838,13 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>银虎斑</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B110" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C110" t="str">
-        <v>assets/1787318609722-0ojb3aikwi.jpg</v>
+        <v>assets/1787319098214-8pwa9yx2wc.jpg</v>
       </c>
       <c r="D110" t="str">
         <v>是</v>
@@ -6853,7 +6853,7 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>黑龙江鹤岗</v>
+        <v>四川成都</v>
       </c>
       <c r="G110" t="str">
         <v/>
@@ -6897,13 +6897,13 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>蓝虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B111" t="str">
         <v>弟弟</v>
       </c>
       <c r="C111" t="str">
-        <v>assets/1787318530612-779fbkfcoi.jpg</v>
+        <v>assets/1787318867999-3gxdddp72x.jpg</v>
       </c>
       <c r="D111" t="str">
         <v>是</v>
@@ -6912,7 +6912,7 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>天津</v>
+        <v>广东广州</v>
       </c>
       <c r="G111" t="str">
         <v/>
@@ -6962,7 +6962,7 @@
         <v>弟弟</v>
       </c>
       <c r="C112" t="str">
-        <v>assets/1787318365475-sj87wtsai3.jpg</v>
+        <v>assets/1787318609722-0ojb3aikwi.jpg</v>
       </c>
       <c r="D112" t="str">
         <v>是</v>
@@ -6971,7 +6971,7 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>山西朔州</v>
+        <v>黑龙江鹤岗</v>
       </c>
       <c r="G112" t="str">
         <v/>
@@ -7001,7 +7001,7 @@
         <v/>
       </c>
       <c r="P112" t="str">
-        <v>已接猫</v>
+        <v/>
       </c>
       <c r="Q112" t="str">
         <v/>
@@ -7015,13 +7015,13 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B113" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C113" t="str">
-        <v>assets/1787318326155-ia4noopjhq.jpg</v>
+        <v>assets/1787318530612-779fbkfcoi.jpg</v>
       </c>
       <c r="D113" t="str">
         <v>是</v>
@@ -7030,7 +7030,7 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>贵州</v>
+        <v>天津</v>
       </c>
       <c r="G113" t="str">
         <v/>
@@ -7074,22 +7074,22 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B114" t="str">
         <v>弟弟</v>
       </c>
       <c r="C114" t="str">
-        <v>assets/1787304479674-w0trechn4p.jpg</v>
+        <v>assets/1787318365475-sj87wtsai3.jpg</v>
       </c>
       <c r="D114" t="str">
         <v>是</v>
       </c>
       <c r="E114" t="str">
-        <v>2026-06-06</v>
+        <v/>
       </c>
       <c r="F114" t="str">
-        <v>北京</v>
+        <v>山西朔州</v>
       </c>
       <c r="G114" t="str">
         <v/>
@@ -7119,7 +7119,7 @@
         <v/>
       </c>
       <c r="P114" t="str">
-        <v/>
+        <v>已接猫</v>
       </c>
       <c r="Q114" t="str">
         <v/>
@@ -7128,27 +7128,27 @@
         <v/>
       </c>
       <c r="S114" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>纯黑色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B115" t="str">
         <v>妹妹</v>
       </c>
       <c r="C115" t="str">
-        <v>assets/1787283819124-4v7d1w01la.jpg</v>
+        <v>assets/1787318326155-ia4noopjhq.jpg</v>
       </c>
       <c r="D115" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E115" t="str">
-        <v>2026-02-20</v>
+        <v/>
       </c>
       <c r="F115" t="str">
-        <v/>
+        <v>贵州</v>
       </c>
       <c r="G115" t="str">
         <v/>
@@ -7187,27 +7187,27 @@
         <v/>
       </c>
       <c r="S115" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>阴影色NS12</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B116" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C116" t="str">
-        <v>assets/1787283212708-jdnyi6ecci.jpg</v>
+        <v>assets/1787304479674-w0trechn4p.jpg</v>
       </c>
       <c r="D116" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E116" t="str">
-        <v>2026-05-28</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F116" t="str">
-        <v/>
+        <v>北京</v>
       </c>
       <c r="G116" t="str">
         <v/>
@@ -7251,22 +7251,22 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>阴影色NS11</v>
+        <v>纯黑色</v>
       </c>
       <c r="B117" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C117" t="str">
-        <v>assets/1787283153501-s2tjg9spwu.jpg</v>
+        <v>assets/1787283819124-4v7d1w01la.jpg</v>
       </c>
       <c r="D117" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E117" t="str">
-        <v>2026-06-15</v>
+        <v>2026-02-20</v>
       </c>
       <c r="F117" t="str">
-        <v>重庆</v>
+        <v/>
       </c>
       <c r="G117" t="str">
         <v/>
@@ -7310,22 +7310,22 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>浅烟灰色</v>
+        <v>阴影色NS12</v>
       </c>
       <c r="B118" t="str">
         <v>妹妹</v>
       </c>
       <c r="C118" t="str">
-        <v>assets/1787283092677-i4d8tyrjtf.jpg</v>
+        <v>assets/1787283212708-jdnyi6ecci.jpg</v>
       </c>
       <c r="D118" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E118" t="str">
-        <v>2026-03-21</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F118" t="str">
-        <v>中国澳门</v>
+        <v/>
       </c>
       <c r="G118" t="str">
         <v/>
@@ -7369,22 +7369,22 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>棕虎斑</v>
+        <v>阴影色NS11</v>
       </c>
       <c r="B119" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C119" t="str">
-        <v>assets/1787283031104-bpyq9wy2tl.jpg</v>
+        <v>assets/1787283153501-s2tjg9spwu.jpg</v>
       </c>
       <c r="D119" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E119" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F119" t="str">
-        <v/>
+        <v>重庆</v>
       </c>
       <c r="G119" t="str">
         <v/>
@@ -7428,22 +7428,22 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>棕虎斑</v>
+        <v>浅烟灰色</v>
       </c>
       <c r="B120" t="str">
         <v>妹妹</v>
       </c>
       <c r="C120" t="str">
-        <v>assets/1787282991501-2fjfws0rqw.jpg</v>
+        <v>assets/1787283092677-i4d8tyrjtf.jpg</v>
       </c>
       <c r="D120" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E120" t="str">
-        <v>2026-06-06</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F120" t="str">
-        <v/>
+        <v>中国澳门</v>
       </c>
       <c r="G120" t="str">
         <v/>
@@ -7493,13 +7493,13 @@
         <v>妹妹</v>
       </c>
       <c r="C121" t="str">
-        <v>assets/1787282942262-syr48fym6c.jpg</v>
+        <v>assets/1787283031104-bpyq9wy2tl.jpg</v>
       </c>
       <c r="D121" t="str">
         <v>否</v>
       </c>
       <c r="E121" t="str">
-        <v>2026-06-15</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F121" t="str">
         <v/>
@@ -7549,19 +7549,19 @@
         <v>棕虎斑</v>
       </c>
       <c r="B122" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C122" t="str">
-        <v>assets/1787282819855-7vhx3m0v40.jpg</v>
+        <v>assets/1787282991501-2fjfws0rqw.jpg</v>
       </c>
       <c r="D122" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E122" t="str">
         <v>2026-06-06</v>
       </c>
       <c r="F122" t="str">
-        <v>北京</v>
+        <v/>
       </c>
       <c r="G122" t="str">
         <v/>
@@ -7611,13 +7611,13 @@
         <v>妹妹</v>
       </c>
       <c r="C123" t="str">
-        <v>assets/1787282703381-2uakw592b4.jpg</v>
+        <v>assets/1787282942262-syr48fym6c.jpg</v>
       </c>
       <c r="D123" t="str">
         <v>否</v>
       </c>
       <c r="E123" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F123" t="str">
         <v/>
@@ -7664,22 +7664,22 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B124" t="str">
         <v>弟弟</v>
       </c>
       <c r="C124" t="str">
-        <v>assets/1787282649397-9hc31ncrpc.jpg</v>
+        <v>assets/1787282819855-7vhx3m0v40.jpg</v>
       </c>
       <c r="D124" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E124" t="str">
         <v>2026-06-06</v>
       </c>
       <c r="F124" t="str">
-        <v/>
+        <v>北京</v>
       </c>
       <c r="G124" t="str">
         <v/>
@@ -7723,13 +7723,13 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B125" t="str">
         <v>妹妹</v>
       </c>
       <c r="C125" t="str">
-        <v>assets/1787282617957-svcoyyznpg.jpg</v>
+        <v>assets/1787282703381-2uakw592b4.jpg</v>
       </c>
       <c r="D125" t="str">
         <v>否</v>
@@ -7788,7 +7788,7 @@
         <v>弟弟</v>
       </c>
       <c r="C126" t="str">
-        <v>assets/1787282419632-78nixqjzua.jpg</v>
+        <v>assets/1787282649397-9hc31ncrpc.jpg</v>
       </c>
       <c r="D126" t="str">
         <v>否</v>
@@ -7841,19 +7841,19 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>纯黑色</v>
+        <v>烟灰色</v>
       </c>
       <c r="B127" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C127" t="str">
-        <v>assets/1787282349942-2cfuyn7xlc.jpg</v>
+        <v>assets/1787282617957-svcoyyznpg.jpg</v>
       </c>
       <c r="D127" t="str">
         <v>否</v>
       </c>
       <c r="E127" t="str">
-        <v>2026-03-21</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F127" t="str">
         <v/>
@@ -7900,19 +7900,19 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B128" t="str">
         <v>弟弟</v>
       </c>
       <c r="C128" t="str">
-        <v>assets/1787282064159-6b4z8c5msd.jpg</v>
+        <v>assets/1787282419632-78nixqjzua.jpg</v>
       </c>
       <c r="D128" t="str">
         <v>否</v>
       </c>
       <c r="E128" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F128" t="str">
         <v/>
@@ -7959,19 +7959,19 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>阴影色NS11</v>
+        <v>纯黑色</v>
       </c>
       <c r="B129" t="str">
         <v>弟弟</v>
       </c>
       <c r="C129" t="str">
-        <v>assets/1787280590041-vzcwebdok1.jpg</v>
+        <v>assets/1787282349942-2cfuyn7xlc.jpg</v>
       </c>
       <c r="D129" t="str">
         <v>否</v>
       </c>
       <c r="E129" t="str">
-        <v>2026-05-28</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F129" t="str">
         <v/>
@@ -8018,19 +8018,19 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>浅色银虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B130" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C130" t="str">
-        <v>assets/1787281786169-9ia0h837ct.jpg</v>
+        <v>assets/1787282064159-6b4z8c5msd.jpg</v>
       </c>
       <c r="D130" t="str">
         <v>否</v>
       </c>
       <c r="E130" t="str">
-        <v>2026-06-15</v>
+        <v>2026-06-10</v>
       </c>
       <c r="F130" t="str">
         <v/>
@@ -8077,22 +8077,22 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>浅烟灰色</v>
+        <v>阴影色NS11</v>
       </c>
       <c r="B131" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C131" t="str">
-        <v>assets/1785843720843-63qz159daui.jpg</v>
+        <v>assets/1787280590041-vzcwebdok1.jpg</v>
       </c>
       <c r="D131" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E131" t="str">
-        <v>2026-03-21</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F131" t="str">
-        <v>四川成都</v>
+        <v/>
       </c>
       <c r="G131" t="str">
         <v/>
@@ -8136,22 +8136,22 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>凯米尔色</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B132" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C132" t="str">
-        <v>assets/1787301984056-iu6afro5z5.jpg, assets/1785843763310-elg05ur61ri.jpg</v>
+        <v>assets/1787281786169-9ia0h837ct.jpg</v>
       </c>
       <c r="D132" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E132" t="str">
-        <v>2026-02-14</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F132" t="str">
-        <v>上海浦东</v>
+        <v/>
       </c>
       <c r="G132" t="str">
         <v/>
@@ -8195,22 +8195,22 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>银虎斑补丁</v>
+        <v>浅烟灰色</v>
       </c>
       <c r="B133" t="str">
         <v>妹妹</v>
       </c>
       <c r="C133" t="str">
-        <v>assets/1785843820715-9kz7gy4mbr7.jpg</v>
+        <v>assets/1785843720843-63qz159daui.jpg</v>
       </c>
       <c r="D133" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E133" t="str">
-        <v>2026-03-05</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F133" t="str">
-        <v/>
+        <v>四川成都</v>
       </c>
       <c r="G133" t="str">
         <v/>
@@ -8254,22 +8254,22 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>烟灰色</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B134" t="str">
         <v>弟弟</v>
       </c>
       <c r="C134" t="str">
-        <v>assets/1785843953805-mxl3x1982io.jpg</v>
+        <v>assets/1787301984056-iu6afro5z5.jpg, assets/1785843763310-elg05ur61ri.jpg</v>
       </c>
       <c r="D134" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E134" t="str">
-        <v>2026-05-18</v>
+        <v>2026-02-14</v>
       </c>
       <c r="F134" t="str">
-        <v/>
+        <v>上海浦东</v>
       </c>
       <c r="G134" t="str">
         <v/>
@@ -8313,19 +8313,19 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>棕虎斑玳瑁</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B135" t="str">
         <v>妹妹</v>
       </c>
       <c r="C135" t="str">
-        <v>assets/1785844013835-ek4xpcje7kh.jpg</v>
+        <v>assets/1785843820715-9kz7gy4mbr7.jpg</v>
       </c>
       <c r="D135" t="str">
         <v>否</v>
       </c>
       <c r="E135" t="str">
-        <v>2026-02-14</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F135" t="str">
         <v/>
@@ -8372,19 +8372,19 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>银虎斑补丁</v>
+        <v>烟灰色</v>
       </c>
       <c r="B136" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C136" t="str">
-        <v>assets/1785844434338-ek5zbdgdcne.jpg</v>
+        <v>assets/1785843953805-mxl3x1982io.jpg</v>
       </c>
       <c r="D136" t="str">
         <v>否</v>
       </c>
       <c r="E136" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F136" t="str">
         <v/>
@@ -8431,22 +8431,22 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑玳瑁</v>
       </c>
       <c r="B137" t="str">
         <v>妹妹</v>
       </c>
       <c r="C137" t="str">
-        <v>assets/1785838787730-s5f333sc3u.jpg</v>
+        <v>assets/1785844013835-ek4xpcje7kh.jpg</v>
       </c>
       <c r="D137" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E137" t="str">
-        <v>2026-06-05</v>
+        <v>2026-02-14</v>
       </c>
       <c r="F137" t="str">
-        <v>湖北恩施</v>
+        <v/>
       </c>
       <c r="G137" t="str">
         <v/>
@@ -8490,22 +8490,22 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>银虎斑</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B138" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C138" t="str">
-        <v>assets/1785842296661-6qw3zs3as8h.jpg</v>
+        <v>assets/1785844434338-ek5zbdgdcne.jpg</v>
       </c>
       <c r="D138" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E138" t="str">
-        <v>2026-06-05</v>
+        <v>2026-05-24</v>
       </c>
       <c r="F138" t="str">
-        <v>湖北恩施</v>
+        <v/>
       </c>
       <c r="G138" t="str">
         <v/>
@@ -8552,19 +8552,19 @@
         <v>银虎斑</v>
       </c>
       <c r="B139" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C139" t="str">
-        <v>assets/1785842429109-porc98rel5.jpg</v>
+        <v>assets/1785838787730-s5f333sc3u.jpg</v>
       </c>
       <c r="D139" t="str">
         <v>是</v>
       </c>
       <c r="E139" t="str">
-        <v>2025-11-05</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F139" t="str">
-        <v>韩国</v>
+        <v>湖北恩施</v>
       </c>
       <c r="G139" t="str">
         <v/>
@@ -8611,19 +8611,19 @@
         <v>银虎斑</v>
       </c>
       <c r="B140" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C140" t="str">
-        <v>assets/1785842594141-fcglbzjp509.jpg</v>
+        <v>assets/1785842296661-6qw3zs3as8h.jpg</v>
       </c>
       <c r="D140" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E140" t="str">
-        <v>2026-05-18</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F140" t="str">
-        <v/>
+        <v>湖北恩施</v>
       </c>
       <c r="G140" t="str">
         <v/>
@@ -8667,22 +8667,22 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B141" t="str">
         <v>弟弟</v>
       </c>
       <c r="C141" t="str">
-        <v>assets/1785842639100-82k775dhwiv.jpg</v>
+        <v>assets/1785842429109-porc98rel5.jpg</v>
       </c>
       <c r="D141" t="str">
         <v>是</v>
       </c>
       <c r="E141" t="str">
-        <v>2026-05-28</v>
+        <v>2025-11-05</v>
       </c>
       <c r="F141" t="str">
-        <v>四川自贡</v>
+        <v>韩国</v>
       </c>
       <c r="G141" t="str">
         <v/>
@@ -8726,19 +8726,19 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B142" t="str">
         <v>妹妹</v>
       </c>
       <c r="C142" t="str">
-        <v>assets/1785842684502-mnhr0r96eee.jpg</v>
+        <v>assets/1785842594141-fcglbzjp509.jpg</v>
       </c>
       <c r="D142" t="str">
         <v>否</v>
       </c>
       <c r="E142" t="str">
-        <v>2026-06-06</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F142" t="str">
         <v/>
@@ -8785,22 +8785,22 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>纯黑色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B143" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C143" t="str">
-        <v>assets/1785842779532-5u1j0igrw1s.jpg</v>
+        <v>assets/1785842639100-82k775dhwiv.jpg</v>
       </c>
       <c r="D143" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E143" t="str">
-        <v>2026-03-05</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F143" t="str">
-        <v/>
+        <v>四川自贡</v>
       </c>
       <c r="G143" t="str">
         <v/>
@@ -8844,22 +8844,22 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B144" t="str">
         <v>妹妹</v>
       </c>
       <c r="C144" t="str">
-        <v>assets/1785842817046-6keqv4rw4yf.jpg</v>
+        <v>assets/1785842684502-mnhr0r96eee.jpg</v>
       </c>
       <c r="D144" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E144" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F144" t="str">
-        <v>韩国</v>
+        <v/>
       </c>
       <c r="G144" t="str">
         <v/>
@@ -8903,22 +8903,22 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>浅色银虎斑</v>
+        <v>纯黑色</v>
       </c>
       <c r="B145" t="str">
         <v>妹妹</v>
       </c>
       <c r="C145" t="str">
-        <v>assets/1785842950972-a88lbrskpc.jpg</v>
+        <v>assets/1785842779532-5u1j0igrw1s.jpg</v>
       </c>
       <c r="D145" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E145" t="str">
-        <v>2026-06-05</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F145" t="str">
-        <v>河北邢台</v>
+        <v/>
       </c>
       <c r="G145" t="str">
         <v/>
@@ -8962,22 +8962,22 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B146" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C146" t="str">
-        <v>assets/1785843011477-n3l1wi6ech.jpg</v>
+        <v>assets/1785842817046-6keqv4rw4yf.jpg</v>
       </c>
       <c r="D146" t="str">
         <v>是</v>
       </c>
       <c r="E146" t="str">
-        <v>2026-06-05</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F146" t="str">
-        <v>四川自贡</v>
+        <v>韩国</v>
       </c>
       <c r="G146" t="str">
         <v/>
@@ -9021,22 +9021,22 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>蓝虎斑</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B147" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C147" t="str">
-        <v>assets/1785843237517-ga449iqess5.jpg</v>
+        <v>assets/1785842950972-a88lbrskpc.jpg</v>
       </c>
       <c r="D147" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E147" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F147" t="str">
-        <v/>
+        <v>河北邢台</v>
       </c>
       <c r="G147" t="str">
         <v/>
@@ -9080,22 +9080,22 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>棕虎斑补丁</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B148" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C148" t="str">
-        <v>assets/1785842523893-7nwnnhwi4ns.jpg</v>
+        <v>assets/1785843011477-n3l1wi6ech.jpg</v>
       </c>
       <c r="D148" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E148" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F148" t="str">
-        <v/>
+        <v>四川自贡</v>
       </c>
       <c r="G148" t="str">
         <v/>
@@ -9142,16 +9142,16 @@
         <v>蓝虎斑</v>
       </c>
       <c r="B149" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C149" t="str">
-        <v>assets/1785843497557-st27fk8drqi.jpg</v>
+        <v>assets/1785843237517-ga449iqess5.jpg</v>
       </c>
       <c r="D149" t="str">
         <v>否</v>
       </c>
       <c r="E149" t="str">
-        <v>2026-04-05</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F149" t="str">
         <v/>
@@ -9198,13 +9198,13 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑补丁</v>
       </c>
       <c r="B150" t="str">
         <v>妹妹</v>
       </c>
       <c r="C150" t="str">
-        <v>assets/1785843621923-ylhakbtw13i.jpg</v>
+        <v>assets/1785842523893-7nwnnhwi4ns.jpg</v>
       </c>
       <c r="D150" t="str">
         <v>否</v>
@@ -9257,19 +9257,19 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B151" t="str">
         <v>妹妹</v>
       </c>
       <c r="C151" t="str">
-        <v>assets/1785843663884-sfxvpmiet7.jpg</v>
+        <v>assets/1785843497557-st27fk8drqi.jpg</v>
       </c>
       <c r="D151" t="str">
         <v>否</v>
       </c>
       <c r="E151" t="str">
-        <v>2026-03-05</v>
+        <v>2026-04-05</v>
       </c>
       <c r="F151" t="str">
         <v/>
@@ -9316,52 +9316,52 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>蓝虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B152" t="str">
         <v>妹妹</v>
       </c>
       <c r="C152" t="str">
-        <v>assets/1785852601940-o236xtv7yx.jpeg</v>
+        <v>assets/1785843621923-ylhakbtw13i.jpg</v>
       </c>
       <c r="D152" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E152" t="str">
-        <v>2026-02-20</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F152" t="str">
-        <v>荷兰</v>
+        <v/>
       </c>
       <c r="G152" t="str">
-        <v>阿泽</v>
+        <v/>
       </c>
       <c r="H152" t="str">
-        <v>小辫子</v>
+        <v/>
       </c>
       <c r="I152" t="str">
-        <v>驺驺</v>
+        <v/>
       </c>
       <c r="J152" t="str">
-        <v>2026-07-02</v>
+        <v/>
       </c>
       <c r="K152" t="str">
         <v/>
       </c>
       <c r="L152" t="str">
-        <v>2026-07-02</v>
+        <v/>
       </c>
       <c r="M152" t="str">
-        <v>2026-08-03</v>
+        <v/>
       </c>
       <c r="N152" t="str">
-        <v>2026-11-04</v>
+        <v/>
       </c>
       <c r="O152" t="str">
-        <v>2026-08-03 · 血清检测,2026-07-02 · 打疫苗 · assets/diary/zouzou-depart.jpg,2026-07-30 · 6.2斤 · 五个月10天了 · assets/feedback/zouzou-1.jpg</v>
+        <v/>
       </c>
       <c r="P152" t="str">
-        <v>已付定金</v>
+        <v/>
       </c>
       <c r="Q152" t="str">
         <v/>
@@ -9370,27 +9370,27 @@
         <v/>
       </c>
       <c r="S152" t="str">
-        <v>否</v>
+        <v/>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>红虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B153" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C153" t="str">
-        <v>assets/1785853950207-cedor66ou2q.jpeg</v>
+        <v>assets/1785843663884-sfxvpmiet7.jpg</v>
       </c>
       <c r="D153" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E153" t="str">
-        <v/>
+        <v>2026-03-05</v>
       </c>
       <c r="F153" t="str">
-        <v>广东广州</v>
+        <v/>
       </c>
       <c r="G153" t="str">
         <v/>
@@ -9434,52 +9434,52 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>红虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B154" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C154" t="str">
-        <v>assets/1785854129383-c8qkvl537x.jpeg</v>
+        <v>assets/1785852601940-o236xtv7yx.jpeg</v>
       </c>
       <c r="D154" t="str">
         <v>是</v>
       </c>
       <c r="E154" t="str">
-        <v/>
+        <v>2026-02-20</v>
       </c>
       <c r="F154" t="str">
-        <v>广东广州</v>
+        <v>荷兰</v>
       </c>
       <c r="G154" t="str">
-        <v/>
+        <v>阿泽</v>
       </c>
       <c r="H154" t="str">
-        <v/>
+        <v>小辫子</v>
       </c>
       <c r="I154" t="str">
-        <v/>
+        <v>驺驺</v>
       </c>
       <c r="J154" t="str">
-        <v/>
+        <v>2026-07-02</v>
       </c>
       <c r="K154" t="str">
         <v/>
       </c>
       <c r="L154" t="str">
-        <v/>
+        <v>2026-07-02</v>
       </c>
       <c r="M154" t="str">
-        <v/>
+        <v>2026-08-03</v>
       </c>
       <c r="N154" t="str">
-        <v/>
+        <v>2026-11-04</v>
       </c>
       <c r="O154" t="str">
-        <v/>
+        <v>2026-08-03 · 血清检测,2026-07-02 · 打疫苗 · assets/diary/zouzou-depart.jpg,2026-07-30 · 6.2斤 · 五个月10天了 · assets/feedback/zouzou-1.jpg</v>
       </c>
       <c r="P154" t="str">
-        <v/>
+        <v>已付定金</v>
       </c>
       <c r="Q154" t="str">
         <v/>
@@ -9488,18 +9488,18 @@
         <v/>
       </c>
       <c r="S154" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B155" t="str">
         <v>弟弟</v>
       </c>
       <c r="C155" t="str">
-        <v>assets/1785854166720-48r17hry9cd.jpeg</v>
+        <v>assets/1785853950207-cedor66ou2q.jpeg</v>
       </c>
       <c r="D155" t="str">
         <v>是</v>
@@ -9508,7 +9508,7 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>山西朔州</v>
+        <v>广东广州</v>
       </c>
       <c r="G155" t="str">
         <v/>
@@ -9552,13 +9552,13 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B156" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C156" t="str">
-        <v>assets/1785854224521-2cpg6xipfn6.jpeg</v>
+        <v>assets/1785854129383-c8qkvl537x.jpeg</v>
       </c>
       <c r="D156" t="str">
         <v>是</v>
@@ -9567,7 +9567,7 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>浙江宁波</v>
+        <v>广东广州</v>
       </c>
       <c r="G156" t="str">
         <v/>
@@ -9617,7 +9617,7 @@
         <v>弟弟</v>
       </c>
       <c r="C157" t="str">
-        <v>assets/1785854260793-steez4s972l.jpeg</v>
+        <v>assets/1785854166720-48r17hry9cd.jpeg</v>
       </c>
       <c r="D157" t="str">
         <v>是</v>
@@ -9626,7 +9626,7 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>陕西西安</v>
+        <v>山西朔州</v>
       </c>
       <c r="G157" t="str">
         <v/>
@@ -9673,10 +9673,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B158" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C158" t="str">
-        <v>assets/1785854319988-cohio08aod5.jpeg</v>
+        <v>assets/1785854224521-2cpg6xipfn6.jpeg</v>
       </c>
       <c r="D158" t="str">
         <v>是</v>
@@ -9685,7 +9685,7 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>黑龙江漠河</v>
+        <v>浙江宁波</v>
       </c>
       <c r="G158" t="str">
         <v/>
@@ -9729,13 +9729,13 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B159" t="str">
         <v>弟弟</v>
       </c>
       <c r="C159" t="str">
-        <v>assets/1785854520974-96b8b1ekqd9.jpeg</v>
+        <v>assets/1785854260793-steez4s972l.jpeg</v>
       </c>
       <c r="D159" t="str">
         <v>是</v>
@@ -9744,7 +9744,7 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>日本</v>
+        <v>陕西西安</v>
       </c>
       <c r="G159" t="str">
         <v/>
@@ -9791,10 +9791,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B160" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C160" t="str">
-        <v>assets/1785854664100-haqoiu1h7hj.jpeg</v>
+        <v>assets/1785854319988-cohio08aod5.jpeg</v>
       </c>
       <c r="D160" t="str">
         <v>是</v>
@@ -9803,7 +9803,7 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>浙江杭州</v>
+        <v>黑龙江漠河</v>
       </c>
       <c r="G160" t="str">
         <v/>
@@ -9847,13 +9847,13 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B161" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C161" t="str">
-        <v>assets/1785854690732-orrs40sx9rs.jpeg</v>
+        <v>assets/1785854520974-96b8b1ekqd9.jpeg</v>
       </c>
       <c r="D161" t="str">
         <v>是</v>
@@ -9862,7 +9862,7 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>贵州安顺</v>
+        <v>日本</v>
       </c>
       <c r="G161" t="str">
         <v/>
@@ -9912,7 +9912,7 @@
         <v>妹妹</v>
       </c>
       <c r="C162" t="str">
-        <v>assets/1785854734122-wcpmib4m7.jpeg</v>
+        <v>assets/1785854664100-haqoiu1h7hj.jpeg</v>
       </c>
       <c r="D162" t="str">
         <v>是</v>
@@ -9921,7 +9921,7 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>山东青岛</v>
+        <v>浙江杭州</v>
       </c>
       <c r="G162" t="str">
         <v/>
@@ -9968,10 +9968,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B163" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C163" t="str">
-        <v>assets/1785854758707-1kxdkfvs6jc.jpeg</v>
+        <v>assets/1785854690732-orrs40sx9rs.jpeg</v>
       </c>
       <c r="D163" t="str">
         <v>是</v>
@@ -9980,7 +9980,7 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>黑龙江漠河</v>
+        <v>贵州安顺</v>
       </c>
       <c r="G163" t="str">
         <v/>
@@ -10024,13 +10024,13 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>纯蓝色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B164" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C164" t="str">
-        <v>assets/1785854784780-3g0u60pdo93.jpeg</v>
+        <v>assets/1785854734122-wcpmib4m7.jpeg</v>
       </c>
       <c r="D164" t="str">
         <v>是</v>
@@ -10039,7 +10039,7 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>河南鹤壁</v>
+        <v>山东青岛</v>
       </c>
       <c r="G164" t="str">
         <v/>
@@ -10089,7 +10089,7 @@
         <v>弟弟</v>
       </c>
       <c r="C165" t="str">
-        <v>assets/1785854813179-8oyxr0h2bbu.jpeg</v>
+        <v>assets/1785854758707-1kxdkfvs6jc.jpeg</v>
       </c>
       <c r="D165" t="str">
         <v>是</v>
@@ -10098,7 +10098,7 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>陕西西安</v>
+        <v>黑龙江漠河</v>
       </c>
       <c r="G165" t="str">
         <v/>
@@ -10142,13 +10142,13 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>棕虎斑</v>
+        <v>纯蓝色</v>
       </c>
       <c r="B166" t="str">
         <v>弟弟</v>
       </c>
       <c r="C166" t="str">
-        <v>assets/1785854838933-uq6amircyzd.jpeg</v>
+        <v>assets/1785854784780-3g0u60pdo93.jpeg</v>
       </c>
       <c r="D166" t="str">
         <v>是</v>
@@ -10157,7 +10157,7 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>四川成都</v>
+        <v>河南鹤壁</v>
       </c>
       <c r="G166" t="str">
         <v/>
@@ -10201,22 +10201,22 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>烟灰色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B167" t="str">
         <v>弟弟</v>
       </c>
       <c r="C167" t="str">
-        <v>assets/1785854869973-za3p6wikqpo.jpeg</v>
+        <v>assets/1785854813179-8oyxr0h2bbu.jpeg</v>
       </c>
       <c r="D167" t="str">
         <v>是</v>
       </c>
       <c r="E167" t="str">
-        <v>2026-05-18</v>
+        <v/>
       </c>
       <c r="F167" t="str">
-        <v>四川成都</v>
+        <v>陕西西安</v>
       </c>
       <c r="G167" t="str">
         <v/>
@@ -10260,13 +10260,13 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B168" t="str">
         <v>弟弟</v>
       </c>
       <c r="C168" t="str">
-        <v>assets/1785854997023-mawkallt2a.jpeg</v>
+        <v>assets/1785854838933-uq6amircyzd.jpeg</v>
       </c>
       <c r="D168" t="str">
         <v>是</v>
@@ -10275,7 +10275,7 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>新加坡</v>
+        <v>四川成都</v>
       </c>
       <c r="G168" t="str">
         <v/>
@@ -10319,22 +10319,22 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>凯米尔色</v>
+        <v>烟灰色</v>
       </c>
       <c r="B169" t="str">
         <v>弟弟</v>
       </c>
       <c r="C169" t="str">
-        <v>assets/1785855043327-wdc5pxwm34k.jpeg</v>
+        <v>assets/1785854869973-za3p6wikqpo.jpeg</v>
       </c>
       <c r="D169" t="str">
         <v>是</v>
       </c>
       <c r="E169" t="str">
-        <v/>
+        <v>2026-05-18</v>
       </c>
       <c r="F169" t="str">
-        <v>上海浦东</v>
+        <v>四川成都</v>
       </c>
       <c r="G169" t="str">
         <v/>
@@ -10378,22 +10378,22 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B170" t="str">
         <v>弟弟</v>
       </c>
       <c r="C170" t="str">
-        <v>assets/1785912551260-jplefm937nk.jpeg, assets/videos/02.mp4</v>
+        <v>assets/1785854997023-mawkallt2a.jpeg</v>
       </c>
       <c r="D170" t="str">
         <v>是</v>
       </c>
       <c r="E170" t="str">
-        <v>2026-06-06</v>
+        <v/>
       </c>
       <c r="F170" t="str">
-        <v>浙江温州</v>
+        <v>新加坡</v>
       </c>
       <c r="G170" t="str">
         <v/>
@@ -10437,66 +10437,184 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
+        <v>凯米尔色</v>
+      </c>
+      <c r="B171" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C171" t="str">
+        <v>assets/1785855043327-wdc5pxwm34k.jpeg</v>
+      </c>
+      <c r="D171" t="str">
+        <v>是</v>
+      </c>
+      <c r="E171" t="str">
+        <v/>
+      </c>
+      <c r="F171" t="str">
+        <v>上海浦东</v>
+      </c>
+      <c r="G171" t="str">
+        <v/>
+      </c>
+      <c r="H171" t="str">
+        <v/>
+      </c>
+      <c r="I171" t="str">
+        <v/>
+      </c>
+      <c r="J171" t="str">
+        <v/>
+      </c>
+      <c r="K171" t="str">
+        <v/>
+      </c>
+      <c r="L171" t="str">
+        <v/>
+      </c>
+      <c r="M171" t="str">
+        <v/>
+      </c>
+      <c r="N171" t="str">
+        <v/>
+      </c>
+      <c r="O171" t="str">
+        <v/>
+      </c>
+      <c r="P171" t="str">
+        <v/>
+      </c>
+      <c r="Q171" t="str">
+        <v/>
+      </c>
+      <c r="R171" t="str">
+        <v/>
+      </c>
+      <c r="S171" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="str">
         <v>棕虎斑</v>
       </c>
-      <c r="B171" t="str">
+      <c r="B172" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C172" t="str">
+        <v>assets/1785912551260-jplefm937nk.jpeg, assets/videos/02.mp4</v>
+      </c>
+      <c r="D172" t="str">
+        <v>是</v>
+      </c>
+      <c r="E172" t="str">
+        <v>2026-06-06</v>
+      </c>
+      <c r="F172" t="str">
+        <v>浙江温州</v>
+      </c>
+      <c r="G172" t="str">
+        <v/>
+      </c>
+      <c r="H172" t="str">
+        <v/>
+      </c>
+      <c r="I172" t="str">
+        <v/>
+      </c>
+      <c r="J172" t="str">
+        <v/>
+      </c>
+      <c r="K172" t="str">
+        <v/>
+      </c>
+      <c r="L172" t="str">
+        <v/>
+      </c>
+      <c r="M172" t="str">
+        <v/>
+      </c>
+      <c r="N172" t="str">
+        <v/>
+      </c>
+      <c r="O172" t="str">
+        <v/>
+      </c>
+      <c r="P172" t="str">
+        <v/>
+      </c>
+      <c r="Q172" t="str">
+        <v/>
+      </c>
+      <c r="R172" t="str">
+        <v/>
+      </c>
+      <c r="S172" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="str">
+        <v>棕虎斑</v>
+      </c>
+      <c r="B173" t="str">
         <v>妹妹</v>
       </c>
-      <c r="C171" t="str">
+      <c r="C173" t="str">
         <v>assets/1785912694000-m20f5kvvrr.jpeg</v>
       </c>
-      <c r="D171" t="str">
-        <v>否</v>
-      </c>
-      <c r="E171" t="str">
+      <c r="D173" t="str">
+        <v>否</v>
+      </c>
+      <c r="E173" t="str">
         <v>2026-06-06</v>
       </c>
-      <c r="F171" t="str">
-        <v/>
-      </c>
-      <c r="G171" t="str">
-        <v/>
-      </c>
-      <c r="H171" t="str">
-        <v/>
-      </c>
-      <c r="I171" t="str">
-        <v/>
-      </c>
-      <c r="J171" t="str">
-        <v/>
-      </c>
-      <c r="K171" t="str">
-        <v/>
-      </c>
-      <c r="L171" t="str">
-        <v/>
-      </c>
-      <c r="M171" t="str">
-        <v/>
-      </c>
-      <c r="N171" t="str">
-        <v/>
-      </c>
-      <c r="O171" t="str">
-        <v/>
-      </c>
-      <c r="P171" t="str">
-        <v/>
-      </c>
-      <c r="Q171" t="str">
-        <v/>
-      </c>
-      <c r="R171" t="str">
-        <v/>
-      </c>
-      <c r="S171" t="str">
+      <c r="F173" t="str">
+        <v/>
+      </c>
+      <c r="G173" t="str">
+        <v/>
+      </c>
+      <c r="H173" t="str">
+        <v/>
+      </c>
+      <c r="I173" t="str">
+        <v/>
+      </c>
+      <c r="J173" t="str">
+        <v/>
+      </c>
+      <c r="K173" t="str">
+        <v/>
+      </c>
+      <c r="L173" t="str">
+        <v/>
+      </c>
+      <c r="M173" t="str">
+        <v/>
+      </c>
+      <c r="N173" t="str">
+        <v/>
+      </c>
+      <c r="O173" t="str">
+        <v/>
+      </c>
+      <c r="P173" t="str">
+        <v/>
+      </c>
+      <c r="Q173" t="str">
+        <v/>
+      </c>
+      <c r="R173" t="str">
+        <v/>
+      </c>
+      <c r="S173" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S171"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S173"/>
   </ignoredErrors>
 </worksheet>
 </file>
